--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-07 Close</t>
+          <t>2026-09-08 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-09-07 Change</t>
+          <t>2026-09-08 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-07 Change %</t>
+          <t>2026-09-08 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-09-08 Close</t>
+          <t>2026-09-09 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-09-08 Change</t>
+          <t>2026-09-09 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-09-08 Change %</t>
+          <t>2026-09-09 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-09-09 Close</t>
+          <t>2026-09-10 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-09-09 Change</t>
+          <t>2026-09-10 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-09-09 Change %</t>
+          <t>2026-09-10 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-09-10 Close</t>
+          <t>2026-09-11 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-09-10 Change</t>
+          <t>2026-09-11 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-09-10 Change %</t>
+          <t>2026-09-11 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-09-11 Close</t>
+          <t>2026-09-14 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-09-11 Change</t>
+          <t>2026-09-14 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-09-11 Change %</t>
+          <t>2026-09-14 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>167.6</v>
+        <v>164.9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9</v>
+        <v>-2.7</v>
       </c>
       <c r="F3" t="n">
-        <v>0.54</v>
+        <v>-1.61</v>
       </c>
       <c r="G3" t="n">
-        <v>164.9</v>
+        <v>166</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.7</v>
+        <v>1.1</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.61</v>
+        <v>0.67</v>
       </c>
       <c r="J3" t="n">
-        <v>166</v>
+        <v>164.7</v>
       </c>
       <c r="K3" t="n">
-        <v>1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="L3" t="n">
-        <v>0.67</v>
+        <v>-0.78</v>
       </c>
       <c r="M3" t="n">
-        <v>164.7</v>
+        <v>163.3</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.78</v>
+        <v>-0.85</v>
       </c>
       <c r="P3" t="n">
-        <v>164.7</v>
+        <v>163.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.78</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>239.6</v>
+        <v>239.4</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2</v>
+        <v>-0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>0.93</v>
+        <v>-0.08</v>
       </c>
       <c r="G4" t="n">
-        <v>239.4</v>
+        <v>242.6</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.2</v>
+        <v>3.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08</v>
+        <v>1.34</v>
       </c>
       <c r="J4" t="n">
-        <v>242.6</v>
+        <v>241.8</v>
       </c>
       <c r="K4" t="n">
-        <v>3.2</v>
+        <v>-0.8</v>
       </c>
       <c r="L4" t="n">
-        <v>1.34</v>
+        <v>-0.33</v>
       </c>
       <c r="M4" t="n">
         <v>241.8</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>241.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.38</v>
+        <v>6.3</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.16</v>
+        <v>-0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.45</v>
+        <v>-1.25</v>
       </c>
       <c r="G5" t="n">
         <v>6.3</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>6.3</v>
+        <v>6.38</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="M5" t="n">
-        <v>6.38</v>
+        <v>6.36</v>
       </c>
       <c r="N5" t="n">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="O5" t="n">
-        <v>1.27</v>
+        <v>-0.31</v>
       </c>
       <c r="P5" t="n">
-        <v>6.38</v>
+        <v>6.36</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="R5" t="n">
-        <v>1.27</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="6">
@@ -766,46 +766,46 @@
         <v>7.51</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.47</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>7.51</v>
+        <v>7.55</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="J6" t="n">
-        <v>7.55</v>
+        <v>7.61</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="L6" t="n">
-        <v>0.53</v>
+        <v>0.79</v>
       </c>
       <c r="M6" t="n">
         <v>7.61</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>7.61</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.95</v>
+        <v>5.88</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.12</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.98</v>
+        <v>-1.18</v>
       </c>
       <c r="G7" t="n">
-        <v>5.88</v>
+        <v>5.91</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.18</v>
+        <v>0.51</v>
       </c>
       <c r="J7" t="n">
-        <v>5.91</v>
+        <v>5.97</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="L7" t="n">
-        <v>0.51</v>
+        <v>1.02</v>
       </c>
       <c r="M7" t="n">
-        <v>5.97</v>
+        <v>6.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="P7" t="n">
-        <v>5.97</v>
+        <v>6.05</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.529999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.23</v>
+        <v>0.03</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.36</v>
+        <v>0.31</v>
       </c>
       <c r="G8" t="n">
-        <v>9.56</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="I8" t="n">
-        <v>0.31</v>
+        <v>0.52</v>
       </c>
       <c r="J8" t="n">
-        <v>9.609999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="L8" t="n">
-        <v>0.52</v>
+        <v>1.66</v>
       </c>
       <c r="M8" t="n">
-        <v>9.77</v>
+        <v>9.75</v>
       </c>
       <c r="N8" t="n">
-        <v>0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="O8" t="n">
-        <v>1.66</v>
+        <v>-0.2</v>
       </c>
       <c r="P8" t="n">
-        <v>9.77</v>
+        <v>9.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="R8" t="n">
-        <v>1.66</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.88</v>
+        <v>7.86</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.11</v>
+        <v>-0.02</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.38</v>
+        <v>-0.25</v>
       </c>
       <c r="G9" t="n">
-        <v>7.86</v>
+        <v>7.89</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.25</v>
+        <v>0.38</v>
       </c>
       <c r="J9" t="n">
-        <v>7.89</v>
+        <v>8.06</v>
       </c>
       <c r="K9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="N9" t="n">
         <v>0.03</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="M9" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.17</v>
-      </c>
       <c r="O9" t="n">
-        <v>2.15</v>
+        <v>0.37</v>
       </c>
       <c r="P9" t="n">
-        <v>8.06</v>
+        <v>8.09</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.17</v>
+        <v>0.03</v>
       </c>
       <c r="R9" t="n">
-        <v>2.15</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="10">
@@ -1014,46 +1014,46 @@
         <v>51.9</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.45</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.72</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>51.9</v>
+        <v>51.85</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="J10" t="n">
-        <v>51.85</v>
+        <v>52.15</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.05</v>
+        <v>0.3</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1</v>
+        <v>0.58</v>
       </c>
       <c r="M10" t="n">
-        <v>52.15</v>
+        <v>51.95</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="O10" t="n">
-        <v>0.58</v>
+        <v>-0.38</v>
       </c>
       <c r="P10" t="n">
-        <v>52.15</v>
+        <v>51.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="R10" t="n">
-        <v>0.58</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.72</v>
+        <v>4.91</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.46</v>
+        <v>4.03</v>
       </c>
       <c r="G11" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="H11" t="n">
-        <v>0.19</v>
+        <v>0.01</v>
       </c>
       <c r="I11" t="n">
-        <v>4.03</v>
+        <v>0.2</v>
       </c>
       <c r="J11" t="n">
-        <v>4.92</v>
+        <v>4.84</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2</v>
+        <v>-1.63</v>
       </c>
       <c r="M11" t="n">
-        <v>4.84</v>
+        <v>4.78</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.63</v>
+        <v>-1.24</v>
       </c>
       <c r="P11" t="n">
-        <v>4.84</v>
+        <v>4.78</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.63</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.960000000000001</v>
+        <v>10.35</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2</v>
+        <v>0.39</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.97</v>
+        <v>3.92</v>
       </c>
       <c r="G12" t="n">
-        <v>10.35</v>
+        <v>10.43</v>
       </c>
       <c r="H12" t="n">
-        <v>0.39</v>
+        <v>0.08</v>
       </c>
       <c r="I12" t="n">
-        <v>3.92</v>
+        <v>0.77</v>
       </c>
       <c r="J12" t="n">
-        <v>10.43</v>
+        <v>10.09</v>
       </c>
       <c r="K12" t="n">
-        <v>0.08</v>
+        <v>-0.34</v>
       </c>
       <c r="L12" t="n">
-        <v>0.77</v>
+        <v>-3.26</v>
       </c>
       <c r="M12" t="n">
-        <v>10.09</v>
+        <v>9.98</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.34</v>
+        <v>-0.11</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.26</v>
+        <v>-1.09</v>
       </c>
       <c r="P12" t="n">
-        <v>10.09</v>
+        <v>9.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.34</v>
+        <v>-0.11</v>
       </c>
       <c r="R12" t="n">
-        <v>-3.26</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24.88</v>
+        <v>25.86</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.18</v>
+        <v>0.98</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.72</v>
+        <v>3.94</v>
       </c>
       <c r="G13" t="n">
-        <v>25.86</v>
+        <v>25.82</v>
       </c>
       <c r="H13" t="n">
-        <v>0.98</v>
+        <v>-0.04</v>
       </c>
       <c r="I13" t="n">
-        <v>3.94</v>
+        <v>-0.15</v>
       </c>
       <c r="J13" t="n">
-        <v>25.82</v>
+        <v>25.02</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.04</v>
+        <v>-0.8</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.15</v>
+        <v>-3.1</v>
       </c>
       <c r="M13" t="n">
-        <v>25.02</v>
+        <v>24.38</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.8</v>
+        <v>-0.64</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.1</v>
+        <v>-2.56</v>
       </c>
       <c r="P13" t="n">
-        <v>25.02</v>
+        <v>24.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.8</v>
+        <v>-0.64</v>
       </c>
       <c r="R13" t="n">
-        <v>-3.1</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.51</v>
+        <v>1.52</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="H14" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="I14" t="n">
-        <v>1.52</v>
+        <v>2.5</v>
       </c>
       <c r="J14" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="K14" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="L14" t="n">
-        <v>2.5</v>
+        <v>-1.46</v>
       </c>
       <c r="M14" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.46</v>
+        <v>-1.98</v>
       </c>
       <c r="P14" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.46</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="15">
@@ -1321,16 +1321,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.43</v>
+        <v>5.41</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="F15" t="n">
-        <v>1.12</v>
+        <v>-0.37</v>
       </c>
       <c r="G15" t="n">
-        <v>5.41</v>
+        <v>5.39</v>
       </c>
       <c r="H15" t="n">
         <v>-0.02</v>
@@ -1339,31 +1339,31 @@
         <v>-0.37</v>
       </c>
       <c r="J15" t="n">
-        <v>5.39</v>
+        <v>5.23</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.02</v>
+        <v>-0.16</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.37</v>
+        <v>-2.97</v>
       </c>
       <c r="M15" t="n">
-        <v>5.23</v>
+        <v>5.29</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.16</v>
+        <v>0.06</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.97</v>
+        <v>1.15</v>
       </c>
       <c r="P15" t="n">
-        <v>5.23</v>
+        <v>5.29</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.16</v>
+        <v>0.06</v>
       </c>
       <c r="R15" t="n">
-        <v>-2.97</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.41</v>
+        <v>4.46</v>
       </c>
       <c r="E16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.22</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="K16" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F16" t="n">
+      <c r="L16" t="n">
         <v>-0.45</v>
       </c>
-      <c r="G16" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-0.22</v>
-      </c>
       <c r="M16" t="n">
-        <v>4.43</v>
+        <v>4.44</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.45</v>
+        <v>0.23</v>
       </c>
       <c r="P16" t="n">
-        <v>4.43</v>
+        <v>4.44</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.45</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.35</v>
+        <v>3.38</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.59</v>
+        <v>0.9</v>
       </c>
       <c r="G17" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="H17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>1.18</v>
       </c>
       <c r="J17" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="K17" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="L17" t="n">
-        <v>1.18</v>
+        <v>-0.29</v>
       </c>
       <c r="M17" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.29</v>
+        <v>-2.35</v>
       </c>
       <c r="P17" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.29</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="18">
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="E18" t="n">
         <v>-0.01</v>
@@ -1516,40 +1516,40 @@
         <v>-0.32</v>
       </c>
       <c r="G18" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.32</v>
+        <v>-0.63</v>
       </c>
       <c r="J18" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.63</v>
+        <v>0.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="N18" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="O18" t="n">
-        <v>0.32</v>
+        <v>-0.96</v>
       </c>
       <c r="P18" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="R18" t="n">
-        <v>0.32</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>56.25</v>
+        <v>55.25</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.57</v>
+        <v>-1.78</v>
       </c>
       <c r="G19" t="n">
-        <v>55.25</v>
+        <v>55.45</v>
       </c>
       <c r="H19" t="n">
-        <v>-1</v>
+        <v>0.2</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.78</v>
+        <v>0.36</v>
       </c>
       <c r="J19" t="n">
-        <v>55.45</v>
+        <v>54.85</v>
       </c>
       <c r="K19" t="n">
-        <v>0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="L19" t="n">
-        <v>0.36</v>
+        <v>-1.08</v>
       </c>
       <c r="M19" t="n">
-        <v>54.85</v>
+        <v>54</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6</v>
+        <v>-0.85</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.08</v>
+        <v>-1.55</v>
       </c>
       <c r="P19" t="n">
-        <v>54.85</v>
+        <v>54</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.6</v>
+        <v>-0.85</v>
       </c>
       <c r="R19" t="n">
-        <v>-1.08</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>30.56</v>
+        <v>29.62</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.34</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1</v>
+        <v>-3.08</v>
       </c>
       <c r="G20" t="n">
-        <v>29.62</v>
+        <v>29.48</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.14</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.08</v>
+        <v>-0.47</v>
       </c>
       <c r="J20" t="n">
-        <v>29.48</v>
+        <v>30.14</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.14</v>
+        <v>0.66</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.47</v>
+        <v>2.24</v>
       </c>
       <c r="M20" t="n">
-        <v>30.14</v>
+        <v>29.6</v>
       </c>
       <c r="N20" t="n">
-        <v>0.66</v>
+        <v>-0.54</v>
       </c>
       <c r="O20" t="n">
-        <v>2.24</v>
+        <v>-1.79</v>
       </c>
       <c r="P20" t="n">
-        <v>30.14</v>
+        <v>29.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.66</v>
+        <v>-0.54</v>
       </c>
       <c r="R20" t="n">
-        <v>2.24</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="21">
@@ -1696,46 +1696,46 @@
         <v>4.58</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.72</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-0.66</v>
       </c>
       <c r="J21" t="n">
-        <v>4.55</v>
+        <v>4.61</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.66</v>
+        <v>1.32</v>
       </c>
       <c r="M21" t="n">
-        <v>4.61</v>
+        <v>4.52</v>
       </c>
       <c r="N21" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="O21" t="n">
-        <v>1.32</v>
+        <v>-1.95</v>
       </c>
       <c r="P21" t="n">
-        <v>4.61</v>
+        <v>4.52</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="R21" t="n">
-        <v>1.32</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79.09999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.55</v>
+        <v>-0.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.25</v>
       </c>
       <c r="G22" t="n">
+        <v>78.95</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J22" t="n">
+        <v>78.84999999999999</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="M22" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="H22" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="J22" t="n">
-        <v>78.95</v>
-      </c>
-      <c r="K22" t="n">
+      <c r="N22" t="n">
         <v>0.05</v>
       </c>
-      <c r="L22" t="n">
+      <c r="O22" t="n">
         <v>0.06</v>
       </c>
-      <c r="M22" t="n">
-        <v>78.84999999999999</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-0.13</v>
-      </c>
       <c r="P22" t="n">
-        <v>78.84999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.13</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>23.8</v>
+        <v>23.62</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4</v>
+        <v>-0.18</v>
       </c>
       <c r="F23" t="n">
-        <v>1.71</v>
+        <v>-0.76</v>
       </c>
       <c r="G23" t="n">
-        <v>23.62</v>
+        <v>23.48</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.18</v>
+        <v>-0.14</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.76</v>
+        <v>-0.59</v>
       </c>
       <c r="J23" t="n">
-        <v>23.48</v>
+        <v>22.98</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.14</v>
+        <v>-0.5</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.59</v>
+        <v>-2.13</v>
       </c>
       <c r="M23" t="n">
         <v>22.98</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.13</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>22.98</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>-2.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.8</v>
+        <v>16.41</v>
       </c>
       <c r="E24" t="n">
-        <v>0.35</v>
+        <v>-0.39</v>
       </c>
       <c r="F24" t="n">
-        <v>2.13</v>
+        <v>-2.32</v>
       </c>
       <c r="G24" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="I24" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="J24" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="M24" t="n">
         <v>16.41</v>
       </c>
-      <c r="H24" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-2.32</v>
-      </c>
-      <c r="J24" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="L24" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="M24" t="n">
-        <v>16.74</v>
-      </c>
       <c r="N24" t="n">
-        <v>-0.2</v>
+        <v>-0.33</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.18</v>
+        <v>-1.97</v>
       </c>
       <c r="P24" t="n">
-        <v>16.74</v>
+        <v>16.41</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2</v>
+        <v>-0.33</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.18</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>27.5</v>
+        <v>26.92</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.58</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.31</v>
+        <v>-2.11</v>
       </c>
       <c r="G25" t="n">
-        <v>26.92</v>
+        <v>26.38</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.58</v>
+        <v>-0.54</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.11</v>
+        <v>-2.01</v>
       </c>
       <c r="J25" t="n">
-        <v>26.38</v>
+        <v>25.92</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.54</v>
+        <v>-0.46</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.01</v>
+        <v>-1.74</v>
       </c>
       <c r="M25" t="n">
-        <v>25.92</v>
+        <v>26.36</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.46</v>
+        <v>0.44</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.74</v>
+        <v>1.7</v>
       </c>
       <c r="P25" t="n">
-        <v>25.92</v>
+        <v>26.36</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.46</v>
+        <v>0.44</v>
       </c>
       <c r="R25" t="n">
-        <v>-1.74</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>41.16</v>
+        <v>38.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.44</v>
+        <v>-2.96</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.06</v>
+        <v>-7.19</v>
       </c>
       <c r="G26" t="n">
-        <v>38.2</v>
+        <v>38.22</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.96</v>
+        <v>0.02</v>
       </c>
       <c r="I26" t="n">
-        <v>-7.19</v>
+        <v>0.05</v>
       </c>
       <c r="J26" t="n">
-        <v>38.22</v>
+        <v>37.48</v>
       </c>
       <c r="K26" t="n">
-        <v>0.02</v>
+        <v>-0.74</v>
       </c>
       <c r="L26" t="n">
-        <v>0.05</v>
+        <v>-1.94</v>
       </c>
       <c r="M26" t="n">
-        <v>37.48</v>
+        <v>35.46</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.74</v>
+        <v>-2.02</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.94</v>
+        <v>-5.39</v>
       </c>
       <c r="P26" t="n">
-        <v>37.48</v>
+        <v>35.46</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.74</v>
+        <v>-2.02</v>
       </c>
       <c r="R26" t="n">
-        <v>-1.94</v>
+        <v>-5.39</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>438.4</v>
+        <v>435.4</v>
       </c>
       <c r="E27" t="n">
-        <v>-4.4</v>
+        <v>-3</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.99</v>
+        <v>-0.68</v>
       </c>
       <c r="G27" t="n">
-        <v>435.4</v>
+        <v>434</v>
       </c>
       <c r="H27" t="n">
-        <v>-3</v>
+        <v>-1.4</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.68</v>
+        <v>-0.32</v>
       </c>
       <c r="J27" t="n">
-        <v>434</v>
+        <v>425.6</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.4</v>
+        <v>-8.4</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.32</v>
+        <v>-1.94</v>
       </c>
       <c r="M27" t="n">
-        <v>425.6</v>
+        <v>428.4</v>
       </c>
       <c r="N27" t="n">
-        <v>-8.4</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.94</v>
+        <v>0.66</v>
       </c>
       <c r="P27" t="n">
-        <v>425.6</v>
+        <v>428.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>-8.4</v>
+        <v>2.8</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.94</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>109.6</v>
+        <v>109.5</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.5</v>
+        <v>-0.1</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.45</v>
+        <v>-0.09</v>
       </c>
       <c r="G28" t="n">
-        <v>109.5</v>
+        <v>109.8</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.09</v>
+        <v>0.27</v>
       </c>
       <c r="J28" t="n">
-        <v>109.8</v>
+        <v>106.9</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3</v>
+        <v>-2.9</v>
       </c>
       <c r="L28" t="n">
-        <v>0.27</v>
+        <v>-2.64</v>
       </c>
       <c r="M28" t="n">
-        <v>106.9</v>
+        <v>107.5</v>
       </c>
       <c r="N28" t="n">
-        <v>-2.9</v>
+        <v>0.6</v>
       </c>
       <c r="O28" t="n">
-        <v>-2.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P28" t="n">
-        <v>106.9</v>
+        <v>107.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>-2.9</v>
+        <v>0.6</v>
       </c>
       <c r="R28" t="n">
-        <v>-2.64</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>108.8</v>
+        <v>108.6</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.6</v>
+        <v>-0.2</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.45</v>
+        <v>-0.18</v>
       </c>
       <c r="G29" t="n">
-        <v>108.6</v>
+        <v>106.3</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2</v>
+        <v>-2.3</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.18</v>
+        <v>-2.12</v>
       </c>
       <c r="J29" t="n">
-        <v>106.3</v>
+        <v>105.5</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.3</v>
+        <v>-0.8</v>
       </c>
       <c r="L29" t="n">
-        <v>-2.12</v>
+        <v>-0.75</v>
       </c>
       <c r="M29" t="n">
-        <v>105.5</v>
+        <v>106.2</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.8</v>
+        <v>0.7</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.75</v>
+        <v>0.66</v>
       </c>
       <c r="P29" t="n">
-        <v>105.5</v>
+        <v>106.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.8</v>
+        <v>0.7</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.75</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>80.05</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.7</v>
+        <v>0.55</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.08</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G30" t="n">
-        <v>80.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="H30" t="n">
-        <v>0.55</v>
+        <v>-2.8</v>
       </c>
       <c r="I30" t="n">
-        <v>0.6899999999999999</v>
+        <v>-3.47</v>
       </c>
       <c r="J30" t="n">
-        <v>77.8</v>
+        <v>74.75</v>
       </c>
       <c r="K30" t="n">
-        <v>-2.8</v>
+        <v>-3.05</v>
       </c>
       <c r="L30" t="n">
-        <v>-3.47</v>
+        <v>-3.92</v>
       </c>
       <c r="M30" t="n">
-        <v>74.75</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>-3.05</v>
+        <v>0.35</v>
       </c>
       <c r="O30" t="n">
-        <v>-3.92</v>
+        <v>0.47</v>
       </c>
       <c r="P30" t="n">
-        <v>74.75</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>-3.05</v>
+        <v>0.35</v>
       </c>
       <c r="R30" t="n">
-        <v>-3.92</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>91.40000000000001</v>
+        <v>89.55</v>
       </c>
       <c r="E31" t="n">
-        <v>-4.5</v>
+        <v>-1.85</v>
       </c>
       <c r="F31" t="n">
-        <v>-4.69</v>
+        <v>-2.02</v>
       </c>
       <c r="G31" t="n">
-        <v>89.55</v>
+        <v>92.2</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.85</v>
+        <v>2.65</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.02</v>
+        <v>2.96</v>
       </c>
       <c r="J31" t="n">
-        <v>92.2</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>2.65</v>
+        <v>-3.05</v>
       </c>
       <c r="L31" t="n">
-        <v>2.96</v>
+        <v>-3.31</v>
       </c>
       <c r="M31" t="n">
-        <v>89.15000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>-3.05</v>
+        <v>-0.05</v>
       </c>
       <c r="O31" t="n">
-        <v>-3.31</v>
+        <v>-0.06</v>
       </c>
       <c r="P31" t="n">
-        <v>89.15000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="Q31" t="n">
-        <v>-3.05</v>
+        <v>-0.05</v>
       </c>
       <c r="R31" t="n">
-        <v>-3.31</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>68.3</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>1.1</v>
+        <v>-2.95</v>
       </c>
       <c r="F32" t="n">
-        <v>1.64</v>
+        <v>-4.32</v>
       </c>
       <c r="G32" t="n">
-        <v>65.34999999999999</v>
+        <v>65</v>
       </c>
       <c r="H32" t="n">
-        <v>-2.95</v>
+        <v>-0.35</v>
       </c>
       <c r="I32" t="n">
-        <v>-4.32</v>
+        <v>-0.54</v>
       </c>
       <c r="J32" t="n">
-        <v>65</v>
+        <v>63.45</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.35</v>
+        <v>-1.55</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.54</v>
+        <v>-2.38</v>
       </c>
       <c r="M32" t="n">
-        <v>63.45</v>
+        <v>63.15</v>
       </c>
       <c r="N32" t="n">
-        <v>-1.55</v>
+        <v>-0.3</v>
       </c>
       <c r="O32" t="n">
-        <v>-2.38</v>
+        <v>-0.47</v>
       </c>
       <c r="P32" t="n">
-        <v>63.45</v>
+        <v>63.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>-1.55</v>
+        <v>-0.3</v>
       </c>
       <c r="R32" t="n">
-        <v>-2.38</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>84.5</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.65</v>
+        <v>-0.65</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.92</v>
+        <v>-0.77</v>
       </c>
       <c r="G33" t="n">
-        <v>83.84999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.65</v>
+        <v>-2.05</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.77</v>
+        <v>-2.44</v>
       </c>
       <c r="J33" t="n">
-        <v>81.8</v>
+        <v>79.55</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.05</v>
+        <v>-2.25</v>
       </c>
       <c r="L33" t="n">
-        <v>-2.44</v>
+        <v>-2.75</v>
       </c>
       <c r="M33" t="n">
-        <v>79.55</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>-2.25</v>
+        <v>0.3</v>
       </c>
       <c r="O33" t="n">
-        <v>-2.75</v>
+        <v>0.38</v>
       </c>
       <c r="P33" t="n">
-        <v>79.55</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>-2.25</v>
+        <v>0.3</v>
       </c>
       <c r="R33" t="n">
-        <v>-2.75</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>33.98</v>
+        <v>33.04</v>
       </c>
       <c r="E34" t="n">
-        <v>0.32</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>0.95</v>
+        <v>-2.77</v>
       </c>
       <c r="G34" t="n">
-        <v>33.04</v>
+        <v>32.32</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.72</v>
       </c>
       <c r="I34" t="n">
-        <v>-2.77</v>
+        <v>-2.18</v>
       </c>
       <c r="J34" t="n">
-        <v>32.32</v>
+        <v>31.66</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="L34" t="n">
-        <v>-2.18</v>
+        <v>-2.04</v>
       </c>
       <c r="M34" t="n">
-        <v>31.66</v>
+        <v>31.26</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.66</v>
+        <v>-0.4</v>
       </c>
       <c r="O34" t="n">
-        <v>-2.04</v>
+        <v>-1.26</v>
       </c>
       <c r="P34" t="n">
-        <v>31.66</v>
+        <v>31.26</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.66</v>
+        <v>-0.4</v>
       </c>
       <c r="R34" t="n">
-        <v>-2.04</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.44</v>
+        <v>4.37</v>
       </c>
       <c r="E35" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-1.58</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="H35" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F35" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="G35" t="n">
-        <v>4.37</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
       <c r="I35" t="n">
-        <v>-1.58</v>
+        <v>-0.92</v>
       </c>
       <c r="J35" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.92</v>
+        <v>-1.85</v>
       </c>
       <c r="M35" t="n">
-        <v>4.33</v>
+        <v>4.24</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.92</v>
+        <v>-0.24</v>
       </c>
       <c r="P35" t="n">
-        <v>4.33</v>
+        <v>4.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.92</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.56</v>
+        <v>9.41</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.09</v>
+        <v>-0.15</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.93</v>
+        <v>-1.57</v>
       </c>
       <c r="G36" t="n">
-        <v>9.41</v>
+        <v>9.33</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.15</v>
+        <v>-0.08</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.57</v>
+        <v>-0.85</v>
       </c>
       <c r="J36" t="n">
-        <v>9.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.08</v>
+        <v>-0.19</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.85</v>
+        <v>-2.04</v>
       </c>
       <c r="M36" t="n">
-        <v>9.33</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.85</v>
+        <v>-0.22</v>
       </c>
       <c r="P36" t="n">
-        <v>9.33</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.85</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="E37" t="n">
-        <v>-4.8</v>
+        <v>-2</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.17</v>
+        <v>-0.5</v>
       </c>
       <c r="G37" t="n">
-        <v>402</v>
+        <v>400.4</v>
       </c>
       <c r="H37" t="n">
-        <v>-2</v>
+        <v>-1.6</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="J37" t="n">
-        <v>400.4</v>
+        <v>397</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.6</v>
+        <v>-3.4</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.4</v>
+        <v>-0.85</v>
       </c>
       <c r="M37" t="n">
-        <v>397</v>
+        <v>392.6</v>
       </c>
       <c r="N37" t="n">
-        <v>-3.4</v>
+        <v>-4.4</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.85</v>
+        <v>-1.11</v>
       </c>
       <c r="P37" t="n">
-        <v>397</v>
+        <v>392.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>-3.4</v>
+        <v>-4.4</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.85</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.18</v>
+        <v>14.03</v>
       </c>
       <c r="E38" t="n">
-        <v>0.05</v>
+        <v>-0.15</v>
       </c>
       <c r="F38" t="n">
-        <v>0.35</v>
+        <v>-1.06</v>
       </c>
       <c r="G38" t="n">
-        <v>14.03</v>
+        <v>13.79</v>
       </c>
       <c r="H38" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="J38" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="L38" t="n">
+        <v>-2.97</v>
+      </c>
+      <c r="M38" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="N38" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O38" t="n">
         <v>-0.15</v>
       </c>
-      <c r="I38" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="J38" t="n">
-        <v>13.79</v>
-      </c>
-      <c r="K38" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="L38" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="M38" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="N38" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="O38" t="n">
-        <v>-2.97</v>
-      </c>
       <c r="P38" t="n">
-        <v>13.38</v>
+        <v>13.36</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.41</v>
+        <v>-0.02</v>
       </c>
       <c r="R38" t="n">
-        <v>-2.97</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>572.5</v>
+        <v>562</v>
       </c>
       <c r="E39" t="n">
-        <v>-2</v>
+        <v>-10.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.35</v>
+        <v>-1.83</v>
       </c>
       <c r="G39" t="n">
         <v>562</v>
       </c>
       <c r="H39" t="n">
-        <v>-10.5</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.83</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>562</v>
+        <v>561.5</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="M39" t="n">
-        <v>561.5</v>
+        <v>547.5</v>
       </c>
       <c r="N39" t="n">
-        <v>-0.5</v>
+        <v>-14</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.09</v>
+        <v>-2.49</v>
       </c>
       <c r="P39" t="n">
-        <v>561.5</v>
+        <v>547.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>-0.5</v>
+        <v>-14</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.09</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>42</v>
+        <v>42.38</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4</v>
+        <v>0.38</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.23</v>
+        <v>0.9</v>
       </c>
       <c r="G40" t="n">
-        <v>42.38</v>
+        <v>42.3</v>
       </c>
       <c r="H40" t="n">
-        <v>0.38</v>
+        <v>-0.08</v>
       </c>
       <c r="I40" t="n">
-        <v>0.9</v>
+        <v>-0.19</v>
       </c>
       <c r="J40" t="n">
-        <v>42.3</v>
+        <v>41.6</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.08</v>
+        <v>-0.7</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.19</v>
+        <v>-1.65</v>
       </c>
       <c r="M40" t="n">
-        <v>41.6</v>
+        <v>41.34</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.7</v>
+        <v>-0.26</v>
       </c>
       <c r="O40" t="n">
-        <v>-1.65</v>
+        <v>-0.62</v>
       </c>
       <c r="P40" t="n">
-        <v>41.6</v>
+        <v>41.34</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.7</v>
+        <v>-0.26</v>
       </c>
       <c r="R40" t="n">
-        <v>-1.65</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.88</v>
+        <v>31.7</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.39</v>
+        <v>-0.18</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.21</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>31.7</v>
+        <v>31.35</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.18</v>
+        <v>-0.35</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="J41" t="n">
-        <v>31.35</v>
+        <v>31.39</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.35</v>
+        <v>0.04</v>
       </c>
       <c r="L41" t="n">
-        <v>-1.1</v>
+        <v>0.13</v>
       </c>
       <c r="M41" t="n">
-        <v>31.39</v>
+        <v>31.6</v>
       </c>
       <c r="N41" t="n">
-        <v>0.04</v>
+        <v>0.21</v>
       </c>
       <c r="O41" t="n">
-        <v>0.13</v>
+        <v>0.67</v>
       </c>
       <c r="P41" t="n">
-        <v>31.39</v>
+        <v>31.6</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.04</v>
+        <v>0.21</v>
       </c>
       <c r="R41" t="n">
-        <v>0.13</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>78.47</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.18</v>
+        <v>-0.37</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.23</v>
+        <v>-0.47</v>
       </c>
       <c r="G42" t="n">
-        <v>78.09999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.37</v>
+        <v>-0.6</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.47</v>
+        <v>-0.77</v>
       </c>
       <c r="J42" t="n">
-        <v>77.5</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.6</v>
+        <v>-0.71</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.77</v>
+        <v>-0.92</v>
       </c>
       <c r="M42" t="n">
-        <v>76.79000000000001</v>
+        <v>77</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.71</v>
+        <v>0.21</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.92</v>
+        <v>0.27</v>
       </c>
       <c r="P42" t="n">
-        <v>76.79000000000001</v>
+        <v>77</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.71</v>
+        <v>0.21</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.92</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>41.75</v>
+        <v>41.6</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.26</v>
+        <v>-0.15</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.62</v>
+        <v>-0.36</v>
       </c>
       <c r="G43" t="n">
-        <v>41.6</v>
+        <v>41.18</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.15</v>
+        <v>-0.42</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.36</v>
+        <v>-1.01</v>
       </c>
       <c r="J43" t="n">
-        <v>41.18</v>
+        <v>40.99</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.42</v>
+        <v>-0.19</v>
       </c>
       <c r="L43" t="n">
-        <v>-1.01</v>
+        <v>-0.46</v>
       </c>
       <c r="M43" t="n">
-        <v>40.99</v>
+        <v>41.26</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.19</v>
+        <v>0.27</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.46</v>
+        <v>0.66</v>
       </c>
       <c r="P43" t="n">
-        <v>40.99</v>
+        <v>41.26</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.19</v>
+        <v>0.27</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.46</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.11</v>
+        <v>6.21</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="G44" t="n">
-        <v>6.21</v>
+        <v>6.19</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1</v>
+        <v>-0.02</v>
       </c>
       <c r="I44" t="n">
-        <v>1.64</v>
+        <v>-0.32</v>
       </c>
       <c r="J44" t="n">
-        <v>6.19</v>
+        <v>6.1</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.32</v>
+        <v>-1.45</v>
       </c>
       <c r="M44" t="n">
         <v>6.1</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>-1.45</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>6.1</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>-1.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G45" t="n">
         <v>2.17</v>
       </c>
-      <c r="E45" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2.19</v>
-      </c>
       <c r="H45" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="I45" t="n">
-        <v>0.92</v>
+        <v>-0.91</v>
       </c>
       <c r="J45" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="K45" t="n">
         <v>-0.02</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.91</v>
+        <v>-0.92</v>
       </c>
       <c r="M45" t="n">
         <v>2.15</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.92</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
         <v>2.15</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.97</v>
+        <v>4.06</v>
       </c>
       <c r="E46" t="n">
         <v>0.09</v>
       </c>
       <c r="F46" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="G46" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="H46" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="I46" t="n">
-        <v>2.27</v>
+        <v>-1.48</v>
       </c>
       <c r="J46" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>-1.48</v>
+        <v>-1.75</v>
       </c>
       <c r="M46" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="O46" t="n">
-        <v>-1.75</v>
+        <v>-0.51</v>
       </c>
       <c r="P46" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="R46" t="n">
-        <v>-1.75</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>10.34</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.76</v>
+        <v>-0.58</v>
       </c>
       <c r="G47" t="n">
-        <v>10.34</v>
+        <v>10.37</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.58</v>
+        <v>0.29</v>
       </c>
       <c r="J47" t="n">
-        <v>10.37</v>
+        <v>10.27</v>
       </c>
       <c r="K47" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="L47" t="n">
-        <v>0.29</v>
+        <v>-0.96</v>
       </c>
       <c r="M47" t="n">
-        <v>10.27</v>
+        <v>10.24</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.96</v>
+        <v>-0.29</v>
       </c>
       <c r="P47" t="n">
-        <v>10.27</v>
+        <v>10.24</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.96</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="E48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="H48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F48" t="n">
-        <v>-1.49</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.01</v>
-      </c>
       <c r="I48" t="n">
-        <v>3.03</v>
+        <v>-1.47</v>
       </c>
       <c r="J48" t="n">
-        <v>0.335</v>
+        <v>0.325</v>
       </c>
       <c r="K48" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="N48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L48" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="N48" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="O48" t="n">
-        <v>-2.99</v>
+        <v>-1.54</v>
       </c>
       <c r="P48" t="n">
-        <v>0.325</v>
+        <v>0.32</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>-2.99</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="G49" t="n">
         <v>4.56</v>
       </c>
-      <c r="E49" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="G49" t="n">
-        <v>4.54</v>
-      </c>
       <c r="H49" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="M49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N49" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I49" t="n">
+      <c r="O49" t="n">
         <v>-0.44</v>
       </c>
-      <c r="J49" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="M49" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="N49" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="O49" t="n">
-        <v>-0.88</v>
-      </c>
       <c r="P49" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.88</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="E50" t="n">
         <v>-0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.88</v>
+        <v>-0.89</v>
       </c>
       <c r="G50" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J50" t="n">
         <v>1.11</v>
       </c>
-      <c r="H50" t="n">
+      <c r="K50" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I50" t="n">
+      <c r="L50" t="n">
         <v>-0.89</v>
       </c>
-      <c r="J50" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0.9</v>
-      </c>
       <c r="M50" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="O50" t="n">
-        <v>-0.89</v>
+        <v>-1.8</v>
       </c>
       <c r="P50" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="R50" t="n">
-        <v>-0.89</v>
+        <v>-1.8</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4.94</v>
+        <v>5.14</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="G51" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
       <c r="H51" t="n">
-        <v>0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="I51" t="n">
-        <v>4.05</v>
+        <v>-0.39</v>
       </c>
       <c r="J51" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="K51" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="M51" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="N51" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L51" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="M51" t="n">
-        <v>5</v>
-      </c>
-      <c r="N51" t="n">
-        <v>-0.12</v>
-      </c>
       <c r="O51" t="n">
-        <v>-2.34</v>
+        <v>-0.4</v>
       </c>
       <c r="P51" t="n">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="R51" t="n">
-        <v>-2.34</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.79</v>
+        <v>11.88</v>
       </c>
       <c r="E52" t="n">
-        <v>0.25</v>
+        <v>0.09</v>
       </c>
       <c r="F52" t="n">
-        <v>2.17</v>
+        <v>0.76</v>
       </c>
       <c r="G52" t="n">
-        <v>11.88</v>
+        <v>11.8</v>
       </c>
       <c r="H52" t="n">
-        <v>0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="I52" t="n">
-        <v>0.76</v>
+        <v>-0.67</v>
       </c>
       <c r="J52" t="n">
-        <v>11.8</v>
+        <v>11.47</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.67</v>
+        <v>-2.8</v>
       </c>
       <c r="M52" t="n">
-        <v>11.47</v>
+        <v>11.43</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.33</v>
+        <v>-0.04</v>
       </c>
       <c r="O52" t="n">
-        <v>-2.8</v>
+        <v>-0.35</v>
       </c>
       <c r="P52" t="n">
-        <v>11.47</v>
+        <v>11.43</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.33</v>
+        <v>-0.04</v>
       </c>
       <c r="R52" t="n">
-        <v>-2.8</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.6</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>-0.21</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>-2.44</v>
       </c>
       <c r="G53" t="n">
-        <v>8.390000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="I53" t="n">
-        <v>-2.44</v>
+        <v>-0.48</v>
       </c>
       <c r="J53" t="n">
-        <v>8.35</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.04</v>
+        <v>-0.13</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.48</v>
+        <v>-1.56</v>
       </c>
       <c r="M53" t="n">
-        <v>8.220000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="O53" t="n">
-        <v>-1.56</v>
+        <v>-0.73</v>
       </c>
       <c r="P53" t="n">
-        <v>8.220000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="R53" t="n">
-        <v>-1.56</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="54">
@@ -3748,40 +3748,40 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.45</v>
+        <v>0.445</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>-1.11</v>
       </c>
       <c r="J54" t="n">
         <v>0.445</v>
       </c>
       <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L54" t="n">
-        <v>-1.11</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>-1.12</v>
       </c>
       <c r="P54" t="n">
-        <v>0.445</v>
+        <v>0.44</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="55">
@@ -3801,31 +3801,31 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.625</v>
+        <v>0.62</v>
       </c>
       <c r="E55" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.62</v>
+        <v>0.615</v>
       </c>
       <c r="H55" t="n">
         <v>-0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.8</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J55" t="n">
         <v>0.615</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0.615</v>
@@ -3881,31 +3881,31 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.415</v>
+        <v>0.41</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="M56" t="n">
         <v>0.41</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
         <v>0.41</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.8</v>
+        <v>3.73</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.52</v>
+        <v>-1.84</v>
       </c>
       <c r="G57" t="n">
         <v>3.73</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.84</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>-0.54</v>
       </c>
       <c r="M57" t="n">
         <v>3.71</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>-0.54</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
         <v>3.71</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>-0.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.077</v>
+        <v>0.075</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>-2.6</v>
       </c>
       <c r="G58" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.002</v>
+        <v>0.001</v>
       </c>
       <c r="I58" t="n">
-        <v>-2.6</v>
+        <v>1.33</v>
       </c>
       <c r="J58" t="n">
         <v>0.076</v>
       </c>
       <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="N58" t="n">
         <v>0.001</v>
       </c>
-      <c r="L58" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="P58" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>25.13</v>
+        <v>24.9</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.17</v>
+        <v>-0.23</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.67</v>
+        <v>-0.92</v>
       </c>
       <c r="G59" t="n">
-        <v>24.9</v>
+        <v>24.78</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.23</v>
+        <v>-0.12</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.92</v>
+        <v>-0.48</v>
       </c>
       <c r="J59" t="n">
-        <v>24.78</v>
+        <v>24.68</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.48</v>
+        <v>-0.4</v>
       </c>
       <c r="M59" t="n">
-        <v>24.68</v>
+        <v>24.3</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.1</v>
+        <v>-0.38</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.4</v>
+        <v>-1.54</v>
       </c>
       <c r="P59" t="n">
-        <v>24.68</v>
+        <v>24.3</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.1</v>
+        <v>-0.38</v>
       </c>
       <c r="R59" t="n">
-        <v>-0.4</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="60">
@@ -4111,16 +4111,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="E60" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>0.32</v>
+        <v>-0.32</v>
       </c>
       <c r="G60" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="H60" t="n">
         <v>-0.01</v>
@@ -4129,7 +4129,7 @@
         <v>-0.32</v>
       </c>
       <c r="J60" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="K60" t="n">
         <v>-0.01</v>
@@ -4141,19 +4141,19 @@
         <v>3.11</v>
       </c>
       <c r="N60" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
         <v>3.11</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -4173,16 +4173,16 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.925</v>
+        <v>0.93</v>
       </c>
       <c r="E61" t="n">
-        <v>0.01</v>
+        <v>0.005</v>
       </c>
       <c r="F61" t="n">
-        <v>1.09</v>
+        <v>0.54</v>
       </c>
       <c r="G61" t="n">
-        <v>0.93</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="H61" t="n">
         <v>0.005</v>
@@ -4191,31 +4191,31 @@
         <v>0.54</v>
       </c>
       <c r="J61" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="K61" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="L61" t="n">
-        <v>0.54</v>
+        <v>-0.53</v>
       </c>
       <c r="M61" t="n">
-        <v>0.93</v>
+        <v>0.915</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.005</v>
+        <v>-0.015</v>
       </c>
       <c r="O61" t="n">
-        <v>-0.53</v>
+        <v>-1.61</v>
       </c>
       <c r="P61" t="n">
-        <v>0.93</v>
+        <v>0.915</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.005</v>
+        <v>-0.015</v>
       </c>
       <c r="R61" t="n">
-        <v>-0.53</v>
+        <v>-1.61</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-08 Close</t>
+          <t>2026-09-09 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-09-08 Change</t>
+          <t>2026-09-09 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-08 Change %</t>
+          <t>2026-09-09 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-09-09 Close</t>
+          <t>2026-09-10 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-09-09 Change</t>
+          <t>2026-09-10 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-09-09 Change %</t>
+          <t>2026-09-10 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-09-10 Close</t>
+          <t>2026-09-11 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-09-10 Change</t>
+          <t>2026-09-11 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-09-10 Change %</t>
+          <t>2026-09-11 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-09-11 Close</t>
+          <t>2026-09-14 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-09-11 Change</t>
+          <t>2026-09-14 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-09-11 Change %</t>
+          <t>2026-09-14 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-09-14 Close</t>
+          <t>2026-09-15 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-09-14 Change</t>
+          <t>2026-09-15 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-09-14 Change %</t>
+          <t>2026-09-15 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>166</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G3" t="n">
+        <v>164.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-1.3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="J3" t="n">
+        <v>163.3</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="M3" t="n">
         <v>164.9</v>
       </c>
-      <c r="E3" t="n">
-        <v>-2.7</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="G3" t="n">
-        <v>166</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="J3" t="n">
-        <v>164.7</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-1.3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="M3" t="n">
-        <v>163.3</v>
-      </c>
       <c r="N3" t="n">
-        <v>-1.4</v>
+        <v>1.6</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.85</v>
+        <v>0.98</v>
       </c>
       <c r="P3" t="n">
-        <v>163.3</v>
+        <v>164.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.4</v>
+        <v>1.6</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.85</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>239.4</v>
+        <v>242.6</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2</v>
+        <v>3.2</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.08</v>
+        <v>1.34</v>
       </c>
       <c r="G4" t="n">
-        <v>242.6</v>
+        <v>241.8</v>
       </c>
       <c r="H4" t="n">
-        <v>3.2</v>
+        <v>-0.8</v>
       </c>
       <c r="I4" t="n">
-        <v>1.34</v>
+        <v>-0.33</v>
       </c>
       <c r="J4" t="n">
         <v>241.8</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>241.8</v>
+        <v>246.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="P4" t="n">
-        <v>241.8</v>
+        <v>246.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="5">
@@ -704,46 +704,46 @@
         <v>6.3</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>6.3</v>
+        <v>6.38</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="J5" t="n">
-        <v>6.38</v>
+        <v>6.36</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="L5" t="n">
-        <v>1.27</v>
+        <v>-0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>6.36</v>
+        <v>6.41</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.31</v>
+        <v>0.79</v>
       </c>
       <c r="P5" t="n">
-        <v>6.36</v>
+        <v>6.41</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.31</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.51</v>
+        <v>7.55</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="G6" t="n">
-        <v>7.55</v>
+        <v>7.61</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="I6" t="n">
-        <v>0.53</v>
+        <v>0.79</v>
       </c>
       <c r="J6" t="n">
         <v>7.61</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>7.61</v>
+        <v>7.65</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="P6" t="n">
-        <v>7.61</v>
+        <v>7.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.88</v>
+        <v>5.91</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.18</v>
+        <v>0.51</v>
       </c>
       <c r="G7" t="n">
-        <v>5.91</v>
+        <v>5.97</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="I7" t="n">
-        <v>0.51</v>
+        <v>1.02</v>
       </c>
       <c r="J7" t="n">
-        <v>5.97</v>
+        <v>6.05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="M7" t="n">
-        <v>6.05</v>
+        <v>6.09</v>
       </c>
       <c r="N7" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="O7" t="n">
-        <v>1.34</v>
+        <v>0.66</v>
       </c>
       <c r="P7" t="n">
-        <v>6.05</v>
+        <v>6.09</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="R7" t="n">
-        <v>1.34</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.56</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F8" t="n">
-        <v>0.31</v>
+        <v>0.52</v>
       </c>
       <c r="G8" t="n">
-        <v>9.609999999999999</v>
+        <v>9.77</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="I8" t="n">
-        <v>0.52</v>
+        <v>1.66</v>
       </c>
       <c r="J8" t="n">
-        <v>9.77</v>
+        <v>9.75</v>
       </c>
       <c r="K8" t="n">
-        <v>0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="L8" t="n">
-        <v>1.66</v>
+        <v>-0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>9.75</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.02</v>
+        <v>0.14</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2</v>
+        <v>1.44</v>
       </c>
       <c r="P8" t="n">
-        <v>9.75</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.02</v>
+        <v>0.14</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.2</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.86</v>
+        <v>7.89</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.25</v>
+        <v>0.38</v>
       </c>
       <c r="G9" t="n">
-        <v>7.89</v>
+        <v>8.06</v>
       </c>
       <c r="H9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="K9" t="n">
         <v>0.03</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.17</v>
-      </c>
       <c r="L9" t="n">
-        <v>2.15</v>
+        <v>0.37</v>
       </c>
       <c r="M9" t="n">
-        <v>8.09</v>
+        <v>8.16</v>
       </c>
       <c r="N9" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.37</v>
+        <v>0.87</v>
       </c>
       <c r="P9" t="n">
-        <v>8.09</v>
+        <v>8.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>0.37</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51.9</v>
+        <v>51.85</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="G10" t="n">
-        <v>51.85</v>
+        <v>52.15</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.05</v>
+        <v>0.3</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1</v>
+        <v>0.58</v>
       </c>
       <c r="J10" t="n">
-        <v>52.15</v>
+        <v>51.95</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="L10" t="n">
-        <v>0.58</v>
+        <v>-0.38</v>
       </c>
       <c r="M10" t="n">
-        <v>51.95</v>
+        <v>52.75</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2</v>
+        <v>0.8</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.38</v>
+        <v>1.54</v>
       </c>
       <c r="P10" t="n">
-        <v>51.95</v>
+        <v>52.75</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.2</v>
+        <v>0.8</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.38</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.91</v>
+        <v>4.92</v>
       </c>
       <c r="E11" t="n">
-        <v>0.19</v>
+        <v>0.01</v>
       </c>
       <c r="F11" t="n">
-        <v>4.03</v>
+        <v>0.2</v>
       </c>
       <c r="G11" t="n">
-        <v>4.92</v>
+        <v>4.84</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2</v>
+        <v>-1.63</v>
       </c>
       <c r="J11" t="n">
-        <v>4.84</v>
+        <v>4.78</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.63</v>
+        <v>-1.24</v>
       </c>
       <c r="M11" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.24</v>
+        <v>-0.84</v>
       </c>
       <c r="P11" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.24</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.35</v>
+        <v>10.43</v>
       </c>
       <c r="E12" t="n">
-        <v>0.39</v>
+        <v>0.08</v>
       </c>
       <c r="F12" t="n">
-        <v>3.92</v>
+        <v>0.77</v>
       </c>
       <c r="G12" t="n">
-        <v>10.43</v>
+        <v>10.09</v>
       </c>
       <c r="H12" t="n">
-        <v>0.08</v>
+        <v>-0.34</v>
       </c>
       <c r="I12" t="n">
-        <v>0.77</v>
+        <v>-3.26</v>
       </c>
       <c r="J12" t="n">
-        <v>10.09</v>
+        <v>9.98</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.34</v>
+        <v>-0.11</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.26</v>
+        <v>-1.09</v>
       </c>
       <c r="M12" t="n">
-        <v>9.98</v>
+        <v>9.92</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.11</v>
+        <v>-0.06</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.09</v>
+        <v>-0.6</v>
       </c>
       <c r="P12" t="n">
-        <v>9.98</v>
+        <v>9.92</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.11</v>
+        <v>-0.06</v>
       </c>
       <c r="R12" t="n">
-        <v>-1.09</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>25.86</v>
+        <v>25.82</v>
       </c>
       <c r="E13" t="n">
-        <v>0.98</v>
+        <v>-0.04</v>
       </c>
       <c r="F13" t="n">
-        <v>3.94</v>
+        <v>-0.15</v>
       </c>
       <c r="G13" t="n">
-        <v>25.82</v>
+        <v>25.02</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.04</v>
+        <v>-0.8</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.15</v>
+        <v>-3.1</v>
       </c>
       <c r="J13" t="n">
-        <v>25.02</v>
+        <v>24.38</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.8</v>
+        <v>-0.64</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.1</v>
+        <v>-2.56</v>
       </c>
       <c r="M13" t="n">
-        <v>24.38</v>
+        <v>24.46</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.64</v>
+        <v>0.08</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.56</v>
+        <v>0.33</v>
       </c>
       <c r="P13" t="n">
-        <v>24.38</v>
+        <v>24.46</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.64</v>
+        <v>0.08</v>
       </c>
       <c r="R13" t="n">
-        <v>-2.56</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="E14" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="F14" t="n">
-        <v>1.52</v>
+        <v>2.5</v>
       </c>
       <c r="G14" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="H14" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5</v>
+        <v>-1.46</v>
       </c>
       <c r="J14" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.46</v>
+        <v>-1.98</v>
       </c>
       <c r="M14" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.98</v>
+        <v>-1.01</v>
       </c>
       <c r="P14" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.98</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="15">
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.41</v>
+        <v>5.39</v>
       </c>
       <c r="E15" t="n">
         <v>-0.02</v>
@@ -1330,40 +1330,40 @@
         <v>-0.37</v>
       </c>
       <c r="G15" t="n">
-        <v>5.39</v>
+        <v>5.23</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.02</v>
+        <v>-0.16</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.37</v>
+        <v>-2.97</v>
       </c>
       <c r="J15" t="n">
-        <v>5.23</v>
+        <v>5.29</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.16</v>
+        <v>0.06</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.97</v>
+        <v>1.15</v>
       </c>
       <c r="M15" t="n">
-        <v>5.29</v>
+        <v>5.24</v>
       </c>
       <c r="N15" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="O15" t="n">
-        <v>1.15</v>
+        <v>-0.95</v>
       </c>
       <c r="P15" t="n">
-        <v>5.29</v>
+        <v>5.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="R15" t="n">
-        <v>1.15</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
       <c r="E16" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="F16" t="n">
-        <v>1.13</v>
+        <v>-0.22</v>
       </c>
       <c r="G16" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.22</v>
+        <v>-0.45</v>
       </c>
       <c r="J16" t="n">
-        <v>4.43</v>
+        <v>4.44</v>
       </c>
       <c r="K16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="N16" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L16" t="n">
+      <c r="O16" t="n">
         <v>-0.45</v>
       </c>
-      <c r="M16" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.23</v>
-      </c>
       <c r="P16" t="n">
-        <v>4.44</v>
+        <v>4.42</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="R16" t="n">
-        <v>0.23</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.38</v>
+        <v>3.42</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9</v>
+        <v>1.18</v>
       </c>
       <c r="G17" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="H17" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>1.18</v>
+        <v>-0.29</v>
       </c>
       <c r="J17" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.29</v>
+        <v>-2.35</v>
       </c>
       <c r="M17" t="n">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.35</v>
+        <v>0.6</v>
       </c>
       <c r="P17" t="n">
-        <v>3.33</v>
+        <v>3.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="R17" t="n">
-        <v>-2.35</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="E18" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.96</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N18" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F18" t="n">
+      <c r="O18" t="n">
         <v>-0.32</v>
       </c>
-      <c r="G18" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-0.63</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="O18" t="n">
-        <v>-0.96</v>
-      </c>
       <c r="P18" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.96</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>55.25</v>
+        <v>55.45</v>
       </c>
       <c r="E19" t="n">
-        <v>-1</v>
+        <v>0.2</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.78</v>
+        <v>0.36</v>
       </c>
       <c r="G19" t="n">
-        <v>55.45</v>
+        <v>54.85</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="I19" t="n">
-        <v>0.36</v>
+        <v>-1.08</v>
       </c>
       <c r="J19" t="n">
-        <v>54.85</v>
+        <v>54</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6</v>
+        <v>-0.85</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.08</v>
+        <v>-1.55</v>
       </c>
       <c r="M19" t="n">
-        <v>54</v>
+        <v>53.6</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.85</v>
+        <v>-0.4</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.55</v>
+        <v>-0.74</v>
       </c>
       <c r="P19" t="n">
-        <v>54</v>
+        <v>53.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.85</v>
+        <v>-0.4</v>
       </c>
       <c r="R19" t="n">
-        <v>-1.55</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.62</v>
+        <v>29.48</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.14</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.08</v>
+        <v>-0.47</v>
       </c>
       <c r="G20" t="n">
-        <v>29.48</v>
+        <v>30.14</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.14</v>
+        <v>0.66</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.47</v>
+        <v>2.24</v>
       </c>
       <c r="J20" t="n">
-        <v>30.14</v>
+        <v>29.6</v>
       </c>
       <c r="K20" t="n">
-        <v>0.66</v>
+        <v>-0.54</v>
       </c>
       <c r="L20" t="n">
-        <v>2.24</v>
+        <v>-1.79</v>
       </c>
       <c r="M20" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.54</v>
+        <v>0.2</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.79</v>
+        <v>0.68</v>
       </c>
       <c r="P20" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.54</v>
+        <v>0.2</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.79</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-0.66</v>
       </c>
       <c r="G21" t="n">
-        <v>4.55</v>
+        <v>4.61</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.66</v>
+        <v>1.32</v>
       </c>
       <c r="J21" t="n">
-        <v>4.61</v>
+        <v>4.52</v>
       </c>
       <c r="K21" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="L21" t="n">
-        <v>1.32</v>
+        <v>-1.95</v>
       </c>
       <c r="M21" t="n">
-        <v>4.52</v>
+        <v>4.59</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.95</v>
+        <v>1.55</v>
       </c>
       <c r="P21" t="n">
-        <v>4.52</v>
+        <v>4.59</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>-1.95</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
+        <v>78.95</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G22" t="n">
+        <v>78.84999999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="J22" t="n">
         <v>78.90000000000001</v>
       </c>
-      <c r="E22" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="G22" t="n">
-        <v>78.95</v>
-      </c>
-      <c r="H22" t="n">
+      <c r="K22" t="n">
         <v>0.05</v>
       </c>
-      <c r="I22" t="n">
+      <c r="L22" t="n">
         <v>0.06</v>
       </c>
-      <c r="J22" t="n">
-        <v>78.84999999999999</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-0.13</v>
-      </c>
       <c r="M22" t="n">
-        <v>78.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="N22" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="O22" t="n">
-        <v>0.06</v>
+        <v>0.38</v>
       </c>
       <c r="P22" t="n">
-        <v>78.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="R22" t="n">
-        <v>0.06</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>23.62</v>
+        <v>23.48</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.18</v>
+        <v>-0.14</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.76</v>
+        <v>-0.59</v>
       </c>
       <c r="G23" t="n">
-        <v>23.48</v>
+        <v>22.98</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.14</v>
+        <v>-0.5</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.59</v>
+        <v>-2.13</v>
       </c>
       <c r="J23" t="n">
         <v>22.98</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.13</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>22.98</v>
+        <v>22.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>-1.65</v>
       </c>
       <c r="P23" t="n">
-        <v>22.98</v>
+        <v>22.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>-1.65</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
+        <v>16.94</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="F24" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="G24" t="n">
+        <v>16.74</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="J24" t="n">
         <v>16.41</v>
       </c>
-      <c r="E24" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-2.32</v>
-      </c>
-      <c r="G24" t="n">
-        <v>16.94</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="I24" t="n">
-        <v>3.23</v>
-      </c>
-      <c r="J24" t="n">
-        <v>16.74</v>
-      </c>
       <c r="K24" t="n">
-        <v>-0.2</v>
+        <v>-0.33</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.18</v>
+        <v>-1.97</v>
       </c>
       <c r="M24" t="n">
-        <v>16.41</v>
+        <v>16.24</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.33</v>
+        <v>-0.17</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.97</v>
+        <v>-1.04</v>
       </c>
       <c r="P24" t="n">
-        <v>16.41</v>
+        <v>16.24</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.33</v>
+        <v>-0.17</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.97</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.92</v>
+        <v>26.38</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.58</v>
+        <v>-0.54</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.11</v>
+        <v>-2.01</v>
       </c>
       <c r="G25" t="n">
-        <v>26.38</v>
+        <v>25.92</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.54</v>
+        <v>-0.46</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.01</v>
+        <v>-1.74</v>
       </c>
       <c r="J25" t="n">
-        <v>25.92</v>
+        <v>26.36</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.46</v>
+        <v>0.44</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.74</v>
+        <v>1.7</v>
       </c>
       <c r="M25" t="n">
-        <v>26.36</v>
+        <v>27.16</v>
       </c>
       <c r="N25" t="n">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="O25" t="n">
-        <v>1.7</v>
+        <v>3.03</v>
       </c>
       <c r="P25" t="n">
-        <v>26.36</v>
+        <v>27.16</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.7</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>38.2</v>
+        <v>38.22</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.96</v>
+        <v>0.02</v>
       </c>
       <c r="F26" t="n">
-        <v>-7.19</v>
+        <v>0.05</v>
       </c>
       <c r="G26" t="n">
-        <v>38.22</v>
+        <v>37.48</v>
       </c>
       <c r="H26" t="n">
-        <v>0.02</v>
+        <v>-0.74</v>
       </c>
       <c r="I26" t="n">
-        <v>0.05</v>
+        <v>-1.94</v>
       </c>
       <c r="J26" t="n">
-        <v>37.48</v>
+        <v>35.46</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.74</v>
+        <v>-2.02</v>
       </c>
       <c r="L26" t="n">
-        <v>-1.94</v>
+        <v>-5.39</v>
       </c>
       <c r="M26" t="n">
-        <v>35.46</v>
+        <v>33.1</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.02</v>
+        <v>-2.36</v>
       </c>
       <c r="O26" t="n">
-        <v>-5.39</v>
+        <v>-6.66</v>
       </c>
       <c r="P26" t="n">
-        <v>35.46</v>
+        <v>33.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.02</v>
+        <v>-2.36</v>
       </c>
       <c r="R26" t="n">
-        <v>-5.39</v>
+        <v>-6.66</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>435.4</v>
+        <v>434</v>
       </c>
       <c r="E27" t="n">
-        <v>-3</v>
+        <v>-1.4</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.68</v>
+        <v>-0.32</v>
       </c>
       <c r="G27" t="n">
-        <v>434</v>
+        <v>425.6</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.4</v>
+        <v>-8.4</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.32</v>
+        <v>-1.94</v>
       </c>
       <c r="J27" t="n">
-        <v>425.6</v>
+        <v>428.4</v>
       </c>
       <c r="K27" t="n">
-        <v>-8.4</v>
+        <v>2.8</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.94</v>
+        <v>0.66</v>
       </c>
       <c r="M27" t="n">
-        <v>428.4</v>
+        <v>430.6</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="O27" t="n">
-        <v>0.66</v>
+        <v>0.51</v>
       </c>
       <c r="P27" t="n">
-        <v>428.4</v>
+        <v>430.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="R27" t="n">
-        <v>0.66</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>109.5</v>
+        <v>109.8</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.09</v>
+        <v>0.27</v>
       </c>
       <c r="G28" t="n">
-        <v>109.8</v>
+        <v>106.9</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3</v>
+        <v>-2.9</v>
       </c>
       <c r="I28" t="n">
-        <v>0.27</v>
+        <v>-2.64</v>
       </c>
       <c r="J28" t="n">
-        <v>106.9</v>
+        <v>107.5</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.9</v>
+        <v>0.6</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>107.5</v>
+        <v>105.9</v>
       </c>
       <c r="N28" t="n">
-        <v>0.6</v>
+        <v>-1.6</v>
       </c>
       <c r="O28" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.49</v>
       </c>
       <c r="P28" t="n">
-        <v>107.5</v>
+        <v>105.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.6</v>
+        <v>-1.6</v>
       </c>
       <c r="R28" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>108.6</v>
+        <v>106.3</v>
       </c>
       <c r="E29" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-2.12</v>
+      </c>
+      <c r="G29" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="J29" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M29" t="n">
+        <v>106</v>
+      </c>
+      <c r="N29" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F29" t="n">
-        <v>-0.18</v>
-      </c>
-      <c r="G29" t="n">
-        <v>106.3</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-2.12</v>
-      </c>
-      <c r="J29" t="n">
-        <v>105.5</v>
-      </c>
-      <c r="K29" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="L29" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="M29" t="n">
-        <v>106.2</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.7</v>
-      </c>
       <c r="O29" t="n">
-        <v>0.66</v>
+        <v>-0.19</v>
       </c>
       <c r="P29" t="n">
-        <v>106.2</v>
+        <v>106</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="R29" t="n">
-        <v>0.66</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>80.59999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="E30" t="n">
-        <v>0.55</v>
+        <v>-2.8</v>
       </c>
       <c r="F30" t="n">
-        <v>0.6899999999999999</v>
+        <v>-3.47</v>
       </c>
       <c r="G30" t="n">
-        <v>77.8</v>
+        <v>74.75</v>
       </c>
       <c r="H30" t="n">
-        <v>-2.8</v>
+        <v>-3.05</v>
       </c>
       <c r="I30" t="n">
-        <v>-3.47</v>
+        <v>-3.92</v>
       </c>
       <c r="J30" t="n">
-        <v>74.75</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-3.05</v>
+        <v>0.35</v>
       </c>
       <c r="L30" t="n">
-        <v>-3.92</v>
+        <v>0.47</v>
       </c>
       <c r="M30" t="n">
-        <v>75.09999999999999</v>
+        <v>75.05</v>
       </c>
       <c r="N30" t="n">
-        <v>0.35</v>
+        <v>-0.05</v>
       </c>
       <c r="O30" t="n">
-        <v>0.47</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="P30" t="n">
-        <v>75.09999999999999</v>
+        <v>75.05</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.35</v>
+        <v>-0.05</v>
       </c>
       <c r="R30" t="n">
-        <v>0.47</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>89.55</v>
+        <v>92.2</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.85</v>
+        <v>2.65</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.02</v>
+        <v>2.96</v>
       </c>
       <c r="G31" t="n">
-        <v>92.2</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>2.65</v>
+        <v>-3.05</v>
       </c>
       <c r="I31" t="n">
-        <v>2.96</v>
+        <v>-3.31</v>
       </c>
       <c r="J31" t="n">
-        <v>89.15000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.05</v>
+        <v>-0.05</v>
       </c>
       <c r="L31" t="n">
-        <v>-3.31</v>
+        <v>-0.06</v>
       </c>
       <c r="M31" t="n">
-        <v>89.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.05</v>
+        <v>0.2</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.06</v>
+        <v>0.22</v>
       </c>
       <c r="P31" t="n">
-        <v>89.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.05</v>
+        <v>0.2</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.06</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>65.34999999999999</v>
+        <v>65</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.95</v>
+        <v>-0.35</v>
       </c>
       <c r="F32" t="n">
-        <v>-4.32</v>
+        <v>-0.54</v>
       </c>
       <c r="G32" t="n">
-        <v>65</v>
+        <v>63.45</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.35</v>
+        <v>-1.55</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.54</v>
+        <v>-2.38</v>
       </c>
       <c r="J32" t="n">
-        <v>63.45</v>
+        <v>63.15</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.55</v>
+        <v>-0.3</v>
       </c>
       <c r="L32" t="n">
-        <v>-2.38</v>
+        <v>-0.47</v>
       </c>
       <c r="M32" t="n">
-        <v>63.15</v>
+        <v>61.3</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.3</v>
+        <v>-1.85</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.47</v>
+        <v>-2.93</v>
       </c>
       <c r="P32" t="n">
-        <v>63.15</v>
+        <v>61.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.3</v>
+        <v>-1.85</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.47</v>
+        <v>-2.93</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>83.84999999999999</v>
+        <v>81.8</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.65</v>
+        <v>-2.05</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.77</v>
+        <v>-2.44</v>
       </c>
       <c r="G33" t="n">
-        <v>81.8</v>
+        <v>79.55</v>
       </c>
       <c r="H33" t="n">
-        <v>-2.05</v>
+        <v>-2.25</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.44</v>
+        <v>-2.75</v>
       </c>
       <c r="J33" t="n">
-        <v>79.55</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>-2.25</v>
+        <v>0.3</v>
       </c>
       <c r="L33" t="n">
-        <v>-2.75</v>
+        <v>0.38</v>
       </c>
       <c r="M33" t="n">
-        <v>79.84999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="N33" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="O33" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="P33" t="n">
-        <v>79.84999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="R33" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>33.04</v>
+        <v>32.32</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.72</v>
       </c>
       <c r="F34" t="n">
-        <v>-2.77</v>
+        <v>-2.18</v>
       </c>
       <c r="G34" t="n">
-        <v>32.32</v>
+        <v>31.66</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="I34" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="J34" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="M34" t="n">
+        <v>30.58</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="O34" t="n">
         <v>-2.18</v>
       </c>
-      <c r="J34" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="L34" t="n">
-        <v>-2.04</v>
-      </c>
-      <c r="M34" t="n">
-        <v>31.26</v>
-      </c>
-      <c r="N34" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="O34" t="n">
-        <v>-1.26</v>
-      </c>
       <c r="P34" t="n">
-        <v>31.26</v>
+        <v>30.58</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.4</v>
+        <v>-0.68</v>
       </c>
       <c r="R34" t="n">
-        <v>-1.26</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="35">
@@ -2561,31 +2561,31 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.37</v>
+        <v>4.33</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.58</v>
+        <v>-0.92</v>
       </c>
       <c r="G35" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.92</v>
+        <v>-1.85</v>
       </c>
       <c r="J35" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="L35" t="n">
-        <v>-1.85</v>
+        <v>-0.24</v>
       </c>
       <c r="M35" t="n">
         <v>4.24</v>
@@ -2623,31 +2623,31 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.41</v>
+        <v>9.33</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.15</v>
+        <v>-0.08</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.57</v>
+        <v>-0.85</v>
       </c>
       <c r="G36" t="n">
-        <v>9.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.08</v>
+        <v>-0.19</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.85</v>
+        <v>-2.04</v>
       </c>
       <c r="J36" t="n">
-        <v>9.140000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.19</v>
+        <v>-0.02</v>
       </c>
       <c r="L36" t="n">
-        <v>-2.04</v>
+        <v>-0.22</v>
       </c>
       <c r="M36" t="n">
         <v>9.119999999999999</v>
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>402</v>
+        <v>400.4</v>
       </c>
       <c r="E37" t="n">
-        <v>-2</v>
+        <v>-1.6</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
       <c r="G37" t="n">
-        <v>400.4</v>
+        <v>397</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.6</v>
+        <v>-3.4</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4</v>
+        <v>-0.85</v>
       </c>
       <c r="J37" t="n">
-        <v>397</v>
+        <v>392.6</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.4</v>
+        <v>-4.4</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.85</v>
+        <v>-1.11</v>
       </c>
       <c r="M37" t="n">
-        <v>392.6</v>
+        <v>397.4</v>
       </c>
       <c r="N37" t="n">
-        <v>-4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O37" t="n">
-        <v>-1.11</v>
+        <v>1.22</v>
       </c>
       <c r="P37" t="n">
-        <v>392.6</v>
+        <v>397.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>-4.4</v>
+        <v>4.8</v>
       </c>
       <c r="R37" t="n">
-        <v>-1.11</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.03</v>
+        <v>13.79</v>
       </c>
       <c r="E38" t="n">
+        <v>-0.24</v>
+      </c>
+      <c r="F38" t="n">
+        <v>-1.71</v>
+      </c>
+      <c r="G38" t="n">
+        <v>13.38</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.41</v>
+      </c>
+      <c r="I38" t="n">
+        <v>-2.97</v>
+      </c>
+      <c r="J38" t="n">
+        <v>13.36</v>
+      </c>
+      <c r="K38" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L38" t="n">
         <v>-0.15</v>
       </c>
-      <c r="F38" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="G38" t="n">
-        <v>13.79</v>
-      </c>
-      <c r="H38" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="I38" t="n">
-        <v>-1.71</v>
-      </c>
-      <c r="J38" t="n">
-        <v>13.38</v>
-      </c>
-      <c r="K38" t="n">
-        <v>-0.41</v>
-      </c>
-      <c r="L38" t="n">
-        <v>-2.97</v>
-      </c>
       <c r="M38" t="n">
-        <v>13.36</v>
+        <v>13</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.02</v>
+        <v>-0.36</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.15</v>
+        <v>-2.69</v>
       </c>
       <c r="P38" t="n">
-        <v>13.36</v>
+        <v>13</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.02</v>
+        <v>-0.36</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.15</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="39">
@@ -2812,46 +2812,46 @@
         <v>562</v>
       </c>
       <c r="E39" t="n">
-        <v>-10.5</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.83</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>562</v>
+        <v>561.5</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="J39" t="n">
-        <v>561.5</v>
+        <v>547.5</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.5</v>
+        <v>-14</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.09</v>
+        <v>-2.49</v>
       </c>
       <c r="M39" t="n">
-        <v>547.5</v>
+        <v>549</v>
       </c>
       <c r="N39" t="n">
-        <v>-14</v>
+        <v>1.5</v>
       </c>
       <c r="O39" t="n">
-        <v>-2.49</v>
+        <v>0.27</v>
       </c>
       <c r="P39" t="n">
-        <v>547.5</v>
+        <v>549</v>
       </c>
       <c r="Q39" t="n">
-        <v>-14</v>
+        <v>1.5</v>
       </c>
       <c r="R39" t="n">
-        <v>-2.49</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>42.38</v>
+        <v>42.3</v>
       </c>
       <c r="E40" t="n">
-        <v>0.38</v>
+        <v>-0.08</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9</v>
+        <v>-0.19</v>
       </c>
       <c r="G40" t="n">
-        <v>42.3</v>
+        <v>41.6</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.08</v>
+        <v>-0.7</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.19</v>
+        <v>-1.65</v>
       </c>
       <c r="J40" t="n">
-        <v>41.6</v>
+        <v>41.34</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.7</v>
+        <v>-0.26</v>
       </c>
       <c r="L40" t="n">
-        <v>-1.65</v>
+        <v>-0.62</v>
       </c>
       <c r="M40" t="n">
-        <v>41.34</v>
+        <v>42.02</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.26</v>
+        <v>0.68</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.62</v>
+        <v>1.64</v>
       </c>
       <c r="P40" t="n">
-        <v>41.34</v>
+        <v>42.02</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.26</v>
+        <v>0.68</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.62</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.7</v>
+        <v>31.35</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.18</v>
+        <v>-0.35</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.1</v>
       </c>
       <c r="G41" t="n">
-        <v>31.35</v>
+        <v>31.39</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.35</v>
+        <v>0.04</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.1</v>
+        <v>0.13</v>
       </c>
       <c r="J41" t="n">
-        <v>31.39</v>
+        <v>31.6</v>
       </c>
       <c r="K41" t="n">
-        <v>0.04</v>
+        <v>0.21</v>
       </c>
       <c r="L41" t="n">
-        <v>0.13</v>
+        <v>0.67</v>
       </c>
       <c r="M41" t="n">
-        <v>31.6</v>
+        <v>31.85</v>
       </c>
       <c r="N41" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="O41" t="n">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="P41" t="n">
-        <v>31.6</v>
+        <v>31.85</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="R41" t="n">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>78.09999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.37</v>
+        <v>-0.6</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.47</v>
+        <v>-0.77</v>
       </c>
       <c r="G42" t="n">
-        <v>77.5</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.6</v>
+        <v>-0.71</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.77</v>
+        <v>-0.92</v>
       </c>
       <c r="J42" t="n">
-        <v>76.79000000000001</v>
+        <v>77</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.71</v>
+        <v>0.21</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.92</v>
+        <v>0.27</v>
       </c>
       <c r="M42" t="n">
-        <v>77</v>
+        <v>77.66</v>
       </c>
       <c r="N42" t="n">
-        <v>0.21</v>
+        <v>0.66</v>
       </c>
       <c r="O42" t="n">
-        <v>0.27</v>
+        <v>0.86</v>
       </c>
       <c r="P42" t="n">
-        <v>77</v>
+        <v>77.66</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.21</v>
+        <v>0.66</v>
       </c>
       <c r="R42" t="n">
-        <v>0.27</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>41.6</v>
+        <v>41.18</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.15</v>
+        <v>-0.42</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.36</v>
+        <v>-1.01</v>
       </c>
       <c r="G43" t="n">
-        <v>41.18</v>
+        <v>40.99</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.42</v>
+        <v>-0.19</v>
       </c>
       <c r="I43" t="n">
-        <v>-1.01</v>
+        <v>-0.46</v>
       </c>
       <c r="J43" t="n">
-        <v>40.99</v>
+        <v>41.26</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.19</v>
+        <v>0.27</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.46</v>
+        <v>0.66</v>
       </c>
       <c r="M43" t="n">
-        <v>41.26</v>
+        <v>42.33</v>
       </c>
       <c r="N43" t="n">
-        <v>0.27</v>
+        <v>1.07</v>
       </c>
       <c r="O43" t="n">
-        <v>0.66</v>
+        <v>2.59</v>
       </c>
       <c r="P43" t="n">
-        <v>41.26</v>
+        <v>42.33</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.27</v>
+        <v>1.07</v>
       </c>
       <c r="R43" t="n">
-        <v>0.66</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.21</v>
+        <v>6.19</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1</v>
+        <v>-0.02</v>
       </c>
       <c r="F44" t="n">
-        <v>1.64</v>
+        <v>-0.32</v>
       </c>
       <c r="G44" t="n">
-        <v>6.19</v>
+        <v>6.1</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.32</v>
+        <v>-1.45</v>
       </c>
       <c r="J44" t="n">
         <v>6.1</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>-1.45</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="P44" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="E45" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="F45" t="n">
-        <v>0.92</v>
+        <v>-0.91</v>
       </c>
       <c r="G45" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="H45" t="n">
         <v>-0.02</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.91</v>
+        <v>-0.92</v>
       </c>
       <c r="J45" t="n">
         <v>2.15</v>
       </c>
       <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="N45" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L45" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>-0.93</v>
       </c>
       <c r="P45" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="E46" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="F46" t="n">
-        <v>2.27</v>
+        <v>-1.48</v>
       </c>
       <c r="G46" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.48</v>
+        <v>-1.75</v>
       </c>
       <c r="J46" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="L46" t="n">
-        <v>-1.75</v>
+        <v>-0.51</v>
       </c>
       <c r="M46" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="O46" t="n">
-        <v>-0.51</v>
+        <v>-1.02</v>
       </c>
       <c r="P46" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.51</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.34</v>
+        <v>10.37</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.58</v>
+        <v>0.29</v>
       </c>
       <c r="G47" t="n">
-        <v>10.37</v>
+        <v>10.27</v>
       </c>
       <c r="H47" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="I47" t="n">
-        <v>0.29</v>
+        <v>-0.96</v>
       </c>
       <c r="J47" t="n">
-        <v>10.27</v>
+        <v>10.24</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.96</v>
+        <v>-0.29</v>
       </c>
       <c r="M47" t="n">
-        <v>10.24</v>
+        <v>10.22</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.29</v>
+        <v>-0.2</v>
       </c>
       <c r="P47" t="n">
-        <v>10.24</v>
+        <v>10.22</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.29</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.34</v>
+        <v>0.335</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="F48" t="n">
-        <v>3.03</v>
+        <v>-1.47</v>
       </c>
       <c r="G48" t="n">
-        <v>0.335</v>
+        <v>0.325</v>
       </c>
       <c r="H48" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I48" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="K48" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="L48" t="n">
-        <v>-2.99</v>
+        <v>-1.54</v>
       </c>
       <c r="M48" t="n">
         <v>0.32</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0.32</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.54</v>
+        <v>4.56</v>
       </c>
       <c r="E49" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K49" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F49" t="n">
+      <c r="L49" t="n">
         <v>-0.44</v>
       </c>
-      <c r="G49" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="J49" t="n">
-        <v>4.52</v>
-      </c>
-      <c r="K49" t="n">
+      <c r="M49" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="N49" t="n">
         <v>-0.04</v>
       </c>
-      <c r="L49" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="M49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="N49" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="O49" t="n">
-        <v>-0.44</v>
+        <v>-0.89</v>
       </c>
       <c r="P49" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.44</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G50" t="n">
         <v>1.11</v>
       </c>
-      <c r="E50" t="n">
+      <c r="H50" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F50" t="n">
+      <c r="I50" t="n">
         <v>-0.89</v>
       </c>
-      <c r="G50" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="H50" t="n">
+      <c r="J50" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N50" t="n">
         <v>0.01</v>
       </c>
-      <c r="I50" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="K50" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="L50" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N50" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="O50" t="n">
-        <v>-1.8</v>
+        <v>0.92</v>
       </c>
       <c r="P50" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="R50" t="n">
-        <v>-1.8</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.14</v>
+        <v>5.12</v>
       </c>
       <c r="E51" t="n">
-        <v>0.2</v>
+        <v>-0.02</v>
       </c>
       <c r="F51" t="n">
-        <v>4.05</v>
+        <v>-0.39</v>
       </c>
       <c r="G51" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="H51" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="J51" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="K51" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I51" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="J51" t="n">
-        <v>5</v>
-      </c>
-      <c r="K51" t="n">
-        <v>-0.12</v>
-      </c>
       <c r="L51" t="n">
-        <v>-2.34</v>
+        <v>-0.4</v>
       </c>
       <c r="M51" t="n">
-        <v>4.98</v>
+        <v>5.11</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.02</v>
+        <v>0.13</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.4</v>
+        <v>2.61</v>
       </c>
       <c r="P51" t="n">
-        <v>4.98</v>
+        <v>5.11</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.02</v>
+        <v>0.13</v>
       </c>
       <c r="R51" t="n">
-        <v>-0.4</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.88</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="n">
-        <v>0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="F52" t="n">
-        <v>0.76</v>
+        <v>-0.67</v>
       </c>
       <c r="G52" t="n">
-        <v>11.8</v>
+        <v>11.47</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.67</v>
+        <v>-2.8</v>
       </c>
       <c r="J52" t="n">
-        <v>11.47</v>
+        <v>11.43</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.33</v>
+        <v>-0.04</v>
       </c>
       <c r="L52" t="n">
-        <v>-2.8</v>
+        <v>-0.35</v>
       </c>
       <c r="M52" t="n">
-        <v>11.43</v>
+        <v>11.33</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.35</v>
+        <v>-0.87</v>
       </c>
       <c r="P52" t="n">
-        <v>11.43</v>
+        <v>11.33</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.35</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.390000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.21</v>
+        <v>-0.04</v>
       </c>
       <c r="F53" t="n">
-        <v>-2.44</v>
+        <v>-0.48</v>
       </c>
       <c r="G53" t="n">
-        <v>8.35</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.04</v>
+        <v>-0.13</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.48</v>
+        <v>-1.56</v>
       </c>
       <c r="J53" t="n">
-        <v>8.220000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="L53" t="n">
-        <v>-1.56</v>
+        <v>-0.73</v>
       </c>
       <c r="M53" t="n">
-        <v>8.16</v>
+        <v>8.15</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.73</v>
+        <v>-0.12</v>
       </c>
       <c r="P53" t="n">
-        <v>8.16</v>
+        <v>8.15</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.73</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="54">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.45</v>
+        <v>0.445</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>-1.11</v>
       </c>
       <c r="G54" t="n">
         <v>0.445</v>
       </c>
       <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I54" t="n">
-        <v>-1.11</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>-1.12</v>
       </c>
       <c r="M54" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="N54" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="O54" t="n">
-        <v>-1.12</v>
+        <v>2.27</v>
       </c>
       <c r="P54" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="Q54" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="R54" t="n">
-        <v>-1.12</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="55">
@@ -3801,22 +3801,22 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.62</v>
+        <v>0.615</v>
       </c>
       <c r="E55" t="n">
         <v>-0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.8</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="G55" t="n">
         <v>0.615</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0.615</v>
@@ -3872,22 +3872,22 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.415</v>
+        <v>0.41</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="J56" t="n">
         <v>0.41</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0.41</v>
@@ -3928,46 +3928,46 @@
         <v>3.73</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.84</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>-0.54</v>
       </c>
       <c r="J57" t="n">
         <v>3.71</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.54</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
       <c r="P57" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.6</v>
+        <v>1.33</v>
       </c>
       <c r="G58" t="n">
         <v>0.076</v>
       </c>
       <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="K58" t="n">
         <v>0.001</v>
       </c>
-      <c r="I58" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="J58" t="n">
+      <c r="L58" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="M58" t="n">
         <v>0.076</v>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.077</v>
-      </c>
       <c r="N58" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="O58" t="n">
-        <v>1.32</v>
+        <v>-1.3</v>
       </c>
       <c r="P58" t="n">
-        <v>0.077</v>
+        <v>0.076</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="R58" t="n">
-        <v>1.32</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>24.9</v>
+        <v>24.78</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.23</v>
+        <v>-0.12</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.92</v>
+        <v>-0.48</v>
       </c>
       <c r="G59" t="n">
-        <v>24.78</v>
+        <v>24.68</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.48</v>
+        <v>-0.4</v>
       </c>
       <c r="J59" t="n">
-        <v>24.68</v>
+        <v>24.3</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.1</v>
+        <v>-0.38</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.4</v>
+        <v>-1.54</v>
       </c>
       <c r="M59" t="n">
-        <v>24.3</v>
+        <v>22.91</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.38</v>
+        <v>-1.39</v>
       </c>
       <c r="O59" t="n">
-        <v>-1.54</v>
+        <v>-5.72</v>
       </c>
       <c r="P59" t="n">
-        <v>24.3</v>
+        <v>22.91</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.38</v>
+        <v>-1.39</v>
       </c>
       <c r="R59" t="n">
-        <v>-1.54</v>
+        <v>-5.72</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="E60" t="n">
         <v>-0.01</v>
@@ -4120,7 +4120,7 @@
         <v>-0.32</v>
       </c>
       <c r="G60" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="H60" t="n">
         <v>-0.01</v>
@@ -4132,28 +4132,28 @@
         <v>3.11</v>
       </c>
       <c r="K60" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N60" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L60" t="n">
+      <c r="O60" t="n">
         <v>-0.32</v>
       </c>
-      <c r="M60" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0</v>
-      </c>
       <c r="P60" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="61">
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.93</v>
+        <v>0.9350000000000001</v>
       </c>
       <c r="E61" t="n">
         <v>0.005</v>
@@ -4182,40 +4182,40 @@
         <v>0.54</v>
       </c>
       <c r="G61" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="H61" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="I61" t="n">
-        <v>0.54</v>
+        <v>-0.53</v>
       </c>
       <c r="J61" t="n">
-        <v>0.93</v>
+        <v>0.915</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.005</v>
+        <v>-0.015</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.53</v>
+        <v>-1.61</v>
       </c>
       <c r="M61" t="n">
-        <v>0.915</v>
+        <v>0.885</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.015</v>
+        <v>-0.03</v>
       </c>
       <c r="O61" t="n">
-        <v>-1.61</v>
+        <v>-3.28</v>
       </c>
       <c r="P61" t="n">
-        <v>0.915</v>
+        <v>0.885</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.015</v>
+        <v>-0.03</v>
       </c>
       <c r="R61" t="n">
-        <v>-1.61</v>
+        <v>-3.28</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-09 Close</t>
+          <t>2026-09-10 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-09-09 Change</t>
+          <t>2026-09-10 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-09 Change %</t>
+          <t>2026-09-10 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-09-10 Close</t>
+          <t>2026-09-11 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-09-10 Change</t>
+          <t>2026-09-11 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-09-10 Change %</t>
+          <t>2026-09-11 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-09-11 Close</t>
+          <t>2026-09-14 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-09-11 Change</t>
+          <t>2026-09-14 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-09-11 Change %</t>
+          <t>2026-09-14 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-09-14 Close</t>
+          <t>2026-09-15 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-09-14 Change</t>
+          <t>2026-09-15 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-09-14 Change %</t>
+          <t>2026-09-15 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-09-15 Close</t>
+          <t>2026-09-16 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-09-15 Change</t>
+          <t>2026-09-16 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-09-15 Change %</t>
+          <t>2026-09-16 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>166</v>
+        <v>164.7</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1</v>
+        <v>-1.3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.67</v>
+        <v>-0.78</v>
       </c>
       <c r="G3" t="n">
-        <v>164.7</v>
+        <v>163.3</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.78</v>
+        <v>-0.85</v>
       </c>
       <c r="J3" t="n">
-        <v>163.3</v>
+        <v>164.9</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.4</v>
+        <v>1.6</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.85</v>
+        <v>0.98</v>
       </c>
       <c r="M3" t="n">
-        <v>164.9</v>
+        <v>159.6</v>
       </c>
       <c r="N3" t="n">
-        <v>1.6</v>
+        <v>-5.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0.98</v>
+        <v>-3.21</v>
       </c>
       <c r="P3" t="n">
-        <v>164.9</v>
+        <v>159.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.6</v>
+        <v>-5.3</v>
       </c>
       <c r="R3" t="n">
-        <v>0.98</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>242.6</v>
+        <v>241.8</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2</v>
+        <v>-0.8</v>
       </c>
       <c r="F4" t="n">
-        <v>1.34</v>
+        <v>-0.33</v>
       </c>
       <c r="G4" t="n">
         <v>241.8</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>241.8</v>
+        <v>246.6</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M4" t="n">
-        <v>246.6</v>
+        <v>238</v>
       </c>
       <c r="N4" t="n">
-        <v>4.8</v>
+        <v>-8.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.99</v>
+        <v>-3.49</v>
       </c>
       <c r="P4" t="n">
-        <v>246.6</v>
+        <v>238</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.8</v>
+        <v>-8.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.99</v>
+        <v>-3.49</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.3</v>
+        <v>6.38</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="G5" t="n">
-        <v>6.38</v>
+        <v>6.36</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="I5" t="n">
-        <v>1.27</v>
+        <v>-0.31</v>
       </c>
       <c r="J5" t="n">
-        <v>6.36</v>
+        <v>6.41</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.31</v>
+        <v>0.79</v>
       </c>
       <c r="M5" t="n">
-        <v>6.41</v>
+        <v>6.31</v>
       </c>
       <c r="N5" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.79</v>
+        <v>-1.56</v>
       </c>
       <c r="P5" t="n">
-        <v>6.41</v>
+        <v>6.31</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.79</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.55</v>
+        <v>7.61</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="F6" t="n">
-        <v>0.53</v>
+        <v>0.79</v>
       </c>
       <c r="G6" t="n">
         <v>7.61</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>7.61</v>
+        <v>7.65</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="M6" t="n">
-        <v>7.65</v>
+        <v>7.49</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04</v>
+        <v>-0.16</v>
       </c>
       <c r="O6" t="n">
-        <v>0.53</v>
+        <v>-2.09</v>
       </c>
       <c r="P6" t="n">
-        <v>7.65</v>
+        <v>7.49</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.04</v>
+        <v>-0.16</v>
       </c>
       <c r="R6" t="n">
-        <v>0.53</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.91</v>
+        <v>5.97</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="F7" t="n">
-        <v>0.51</v>
+        <v>1.02</v>
       </c>
       <c r="G7" t="n">
-        <v>5.97</v>
+        <v>6.05</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="J7" t="n">
-        <v>6.05</v>
+        <v>6.09</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="L7" t="n">
-        <v>1.34</v>
+        <v>0.66</v>
       </c>
       <c r="M7" t="n">
-        <v>6.09</v>
+        <v>5.95</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04</v>
+        <v>-0.14</v>
       </c>
       <c r="O7" t="n">
-        <v>0.66</v>
+        <v>-2.3</v>
       </c>
       <c r="P7" t="n">
-        <v>6.09</v>
+        <v>5.95</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04</v>
+        <v>-0.14</v>
       </c>
       <c r="R7" t="n">
-        <v>0.66</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="G8" t="n">
+        <v>9.75</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="J8" t="n">
+        <v>9.890000000000001</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M8" t="n">
         <v>9.609999999999999</v>
       </c>
-      <c r="E8" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9.77</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="J8" t="n">
-        <v>9.75</v>
-      </c>
-      <c r="K8" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L8" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>9.890000000000001</v>
-      </c>
       <c r="N8" t="n">
-        <v>0.14</v>
+        <v>-0.28</v>
       </c>
       <c r="O8" t="n">
-        <v>1.44</v>
+        <v>-2.83</v>
       </c>
       <c r="P8" t="n">
-        <v>9.890000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.14</v>
+        <v>-0.28</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.89</v>
+        <v>8.06</v>
       </c>
       <c r="E9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.09</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.03</v>
       </c>
-      <c r="F9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="G9" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.17</v>
-      </c>
       <c r="I9" t="n">
-        <v>2.15</v>
+        <v>0.37</v>
       </c>
       <c r="J9" t="n">
-        <v>8.09</v>
+        <v>8.16</v>
       </c>
       <c r="K9" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.37</v>
+        <v>0.87</v>
       </c>
       <c r="M9" t="n">
-        <v>8.16</v>
+        <v>8.02</v>
       </c>
       <c r="N9" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="O9" t="n">
-        <v>0.87</v>
+        <v>-1.72</v>
       </c>
       <c r="P9" t="n">
-        <v>8.16</v>
+        <v>8.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="R9" t="n">
-        <v>0.87</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51.85</v>
+        <v>52.15</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.05</v>
+        <v>0.3</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1</v>
+        <v>0.58</v>
       </c>
       <c r="G10" t="n">
-        <v>52.15</v>
+        <v>51.95</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>0.58</v>
+        <v>-0.38</v>
       </c>
       <c r="J10" t="n">
-        <v>51.95</v>
+        <v>52.75</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.2</v>
+        <v>0.8</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.38</v>
+        <v>1.54</v>
       </c>
       <c r="M10" t="n">
-        <v>52.75</v>
+        <v>51.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.8</v>
+        <v>-1.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.54</v>
+        <v>-2.94</v>
       </c>
       <c r="P10" t="n">
-        <v>52.75</v>
+        <v>51.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8</v>
+        <v>-1.55</v>
       </c>
       <c r="R10" t="n">
-        <v>1.54</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.92</v>
+        <v>4.84</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2</v>
+        <v>-1.63</v>
       </c>
       <c r="G11" t="n">
-        <v>4.84</v>
+        <v>4.78</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.63</v>
+        <v>-1.24</v>
       </c>
       <c r="J11" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.24</v>
+        <v>-0.84</v>
       </c>
       <c r="M11" t="n">
-        <v>4.74</v>
+        <v>4.63</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.04</v>
+        <v>-0.11</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.84</v>
+        <v>-2.32</v>
       </c>
       <c r="P11" t="n">
-        <v>4.74</v>
+        <v>4.63</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.04</v>
+        <v>-0.11</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.84</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.43</v>
+        <v>10.09</v>
       </c>
       <c r="E12" t="n">
-        <v>0.08</v>
+        <v>-0.34</v>
       </c>
       <c r="F12" t="n">
-        <v>0.77</v>
+        <v>-3.26</v>
       </c>
       <c r="G12" t="n">
-        <v>10.09</v>
+        <v>9.98</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.34</v>
+        <v>-0.11</v>
       </c>
       <c r="I12" t="n">
-        <v>-3.26</v>
+        <v>-1.09</v>
       </c>
       <c r="J12" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="M12" t="n">
         <v>9.98</v>
       </c>
-      <c r="K12" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="L12" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="M12" t="n">
-        <v>9.92</v>
-      </c>
       <c r="N12" t="n">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.6</v>
+        <v>0.6</v>
       </c>
       <c r="P12" t="n">
-        <v>9.92</v>
+        <v>9.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.6</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>25.82</v>
+        <v>25.02</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.04</v>
+        <v>-0.8</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.15</v>
+        <v>-3.1</v>
       </c>
       <c r="G13" t="n">
-        <v>25.02</v>
+        <v>24.38</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.8</v>
+        <v>-0.64</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.1</v>
+        <v>-2.56</v>
       </c>
       <c r="J13" t="n">
-        <v>24.38</v>
+        <v>24.46</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.64</v>
+        <v>0.08</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.56</v>
+        <v>0.33</v>
       </c>
       <c r="M13" t="n">
-        <v>24.46</v>
+        <v>24.48</v>
       </c>
       <c r="N13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O13" t="n">
         <v>0.08</v>
       </c>
-      <c r="O13" t="n">
-        <v>0.33</v>
-      </c>
       <c r="P13" t="n">
-        <v>24.46</v>
+        <v>24.48</v>
       </c>
       <c r="Q13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="R13" t="n">
         <v>0.08</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.33</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="E14" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="F14" t="n">
-        <v>2.5</v>
+        <v>-1.46</v>
       </c>
       <c r="G14" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.46</v>
+        <v>-1.98</v>
       </c>
       <c r="J14" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.98</v>
+        <v>-1.01</v>
       </c>
       <c r="M14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.01</v>
+        <v>-0.51</v>
       </c>
       <c r="P14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.01</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.39</v>
+        <v>5.23</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.02</v>
+        <v>-0.16</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.37</v>
+        <v>-2.97</v>
       </c>
       <c r="G15" t="n">
-        <v>5.23</v>
+        <v>5.29</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.16</v>
+        <v>0.06</v>
       </c>
       <c r="I15" t="n">
-        <v>-2.97</v>
+        <v>1.15</v>
       </c>
       <c r="J15" t="n">
-        <v>5.29</v>
+        <v>5.24</v>
       </c>
       <c r="K15" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="L15" t="n">
-        <v>1.15</v>
+        <v>-0.95</v>
       </c>
       <c r="M15" t="n">
-        <v>5.24</v>
+        <v>5.17</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.95</v>
+        <v>-1.34</v>
       </c>
       <c r="P15" t="n">
-        <v>5.24</v>
+        <v>5.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.95</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.22</v>
+        <v>-0.45</v>
       </c>
       <c r="G16" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="K16" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="M16" t="n">
         <v>4.43</v>
       </c>
-      <c r="H16" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="K16" t="n">
+      <c r="N16" t="n">
         <v>0.01</v>
       </c>
-      <c r="L16" t="n">
+      <c r="O16" t="n">
         <v>0.23</v>
       </c>
-      <c r="M16" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-0.45</v>
-      </c>
       <c r="P16" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.45</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="F17" t="n">
-        <v>1.18</v>
+        <v>-0.29</v>
       </c>
       <c r="G17" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="H17" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="N17" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I17" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-2.35</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.02</v>
-      </c>
       <c r="O17" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
       <c r="P17" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="18">
@@ -1507,34 +1507,34 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.63</v>
+        <v>0.32</v>
       </c>
       <c r="G18" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="I18" t="n">
-        <v>0.32</v>
+        <v>-0.96</v>
       </c>
       <c r="J18" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.96</v>
+        <v>-0.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="N18" t="n">
         <v>-0.01</v>
@@ -1543,7 +1543,7 @@
         <v>-0.32</v>
       </c>
       <c r="P18" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.01</v>
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>55.45</v>
+        <v>54.85</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="F19" t="n">
-        <v>0.36</v>
+        <v>-1.08</v>
       </c>
       <c r="G19" t="n">
-        <v>54.85</v>
+        <v>54</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6</v>
+        <v>-0.85</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.08</v>
+        <v>-1.55</v>
       </c>
       <c r="J19" t="n">
-        <v>54</v>
+        <v>53.6</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.85</v>
+        <v>-0.4</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.55</v>
+        <v>-0.74</v>
       </c>
       <c r="M19" t="n">
-        <v>53.6</v>
+        <v>53.05</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4</v>
+        <v>-0.55</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.74</v>
+        <v>-1.03</v>
       </c>
       <c r="P19" t="n">
-        <v>53.6</v>
+        <v>53.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4</v>
+        <v>-0.55</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.74</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.48</v>
+        <v>30.14</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.14</v>
+        <v>0.66</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.47</v>
+        <v>2.24</v>
       </c>
       <c r="G20" t="n">
-        <v>30.14</v>
+        <v>29.6</v>
       </c>
       <c r="H20" t="n">
-        <v>0.66</v>
+        <v>-0.54</v>
       </c>
       <c r="I20" t="n">
-        <v>2.24</v>
+        <v>-1.79</v>
       </c>
       <c r="J20" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.54</v>
+        <v>0.2</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.79</v>
+        <v>0.68</v>
       </c>
       <c r="M20" t="n">
-        <v>29.8</v>
+        <v>28.96</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2</v>
+        <v>-0.84</v>
       </c>
       <c r="O20" t="n">
-        <v>0.68</v>
+        <v>-2.82</v>
       </c>
       <c r="P20" t="n">
-        <v>29.8</v>
+        <v>28.96</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.2</v>
+        <v>-0.84</v>
       </c>
       <c r="R20" t="n">
-        <v>0.68</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.55</v>
+        <v>4.61</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.66</v>
+        <v>1.32</v>
       </c>
       <c r="G21" t="n">
-        <v>4.61</v>
+        <v>4.52</v>
       </c>
       <c r="H21" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="I21" t="n">
-        <v>1.32</v>
+        <v>-1.95</v>
       </c>
       <c r="J21" t="n">
-        <v>4.52</v>
+        <v>4.59</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.95</v>
+        <v>1.55</v>
       </c>
       <c r="M21" t="n">
-        <v>4.59</v>
+        <v>4.49</v>
       </c>
       <c r="N21" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="O21" t="n">
-        <v>1.55</v>
+        <v>-2.18</v>
       </c>
       <c r="P21" t="n">
-        <v>4.59</v>
+        <v>4.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.55</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>78.95</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="E22" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="G22" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="H22" t="n">
         <v>0.05</v>
       </c>
-      <c r="F22" t="n">
+      <c r="I22" t="n">
         <v>0.06</v>
       </c>
-      <c r="G22" t="n">
-        <v>78.84999999999999</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-0.13</v>
-      </c>
       <c r="J22" t="n">
-        <v>78.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="K22" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="L22" t="n">
-        <v>0.06</v>
+        <v>0.38</v>
       </c>
       <c r="M22" t="n">
-        <v>79.2</v>
+        <v>79.05</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3</v>
+        <v>-0.15</v>
       </c>
       <c r="O22" t="n">
-        <v>0.38</v>
+        <v>-0.19</v>
       </c>
       <c r="P22" t="n">
-        <v>79.2</v>
+        <v>79.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.3</v>
+        <v>-0.15</v>
       </c>
       <c r="R22" t="n">
-        <v>0.38</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>23.48</v>
+        <v>22.98</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.14</v>
+        <v>-0.5</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.59</v>
+        <v>-2.13</v>
       </c>
       <c r="G23" t="n">
         <v>22.98</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.13</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>22.98</v>
+        <v>22.6</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-1.65</v>
       </c>
       <c r="M23" t="n">
-        <v>22.6</v>
+        <v>22.46</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.38</v>
+        <v>-0.14</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.65</v>
+        <v>-0.62</v>
       </c>
       <c r="P23" t="n">
-        <v>22.6</v>
+        <v>22.46</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.38</v>
+        <v>-0.14</v>
       </c>
       <c r="R23" t="n">
-        <v>-1.65</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.94</v>
+        <v>16.74</v>
       </c>
       <c r="E24" t="n">
-        <v>0.53</v>
+        <v>-0.2</v>
       </c>
       <c r="F24" t="n">
-        <v>3.23</v>
+        <v>-1.18</v>
       </c>
       <c r="G24" t="n">
-        <v>16.74</v>
+        <v>16.41</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2</v>
+        <v>-0.33</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.18</v>
+        <v>-1.97</v>
       </c>
       <c r="J24" t="n">
-        <v>16.41</v>
+        <v>16.24</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.33</v>
+        <v>-0.17</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.97</v>
+        <v>-1.04</v>
       </c>
       <c r="M24" t="n">
-        <v>16.24</v>
+        <v>15.88</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.17</v>
+        <v>-0.36</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.04</v>
+        <v>-2.22</v>
       </c>
       <c r="P24" t="n">
-        <v>16.24</v>
+        <v>15.88</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.17</v>
+        <v>-0.36</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.04</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.38</v>
+        <v>25.92</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.54</v>
+        <v>-0.46</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.01</v>
+        <v>-1.74</v>
       </c>
       <c r="G25" t="n">
-        <v>25.92</v>
+        <v>26.36</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.46</v>
+        <v>0.44</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.74</v>
+        <v>1.7</v>
       </c>
       <c r="J25" t="n">
-        <v>26.36</v>
+        <v>27.16</v>
       </c>
       <c r="K25" t="n">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="L25" t="n">
-        <v>1.7</v>
+        <v>3.03</v>
       </c>
       <c r="M25" t="n">
-        <v>27.16</v>
+        <v>26.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.8</v>
+        <v>-0.66</v>
       </c>
       <c r="O25" t="n">
-        <v>3.03</v>
+        <v>-2.43</v>
       </c>
       <c r="P25" t="n">
-        <v>27.16</v>
+        <v>26.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.8</v>
+        <v>-0.66</v>
       </c>
       <c r="R25" t="n">
-        <v>3.03</v>
+        <v>-2.43</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>38.22</v>
+        <v>37.48</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02</v>
+        <v>-0.74</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05</v>
+        <v>-1.94</v>
       </c>
       <c r="G26" t="n">
-        <v>37.48</v>
+        <v>35.46</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.74</v>
+        <v>-2.02</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.94</v>
+        <v>-5.39</v>
       </c>
       <c r="J26" t="n">
-        <v>35.46</v>
+        <v>33.1</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.02</v>
+        <v>-2.36</v>
       </c>
       <c r="L26" t="n">
-        <v>-5.39</v>
+        <v>-6.66</v>
       </c>
       <c r="M26" t="n">
-        <v>33.1</v>
+        <v>32.06</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.36</v>
+        <v>-1.04</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.66</v>
+        <v>-3.14</v>
       </c>
       <c r="P26" t="n">
-        <v>33.1</v>
+        <v>32.06</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.36</v>
+        <v>-1.04</v>
       </c>
       <c r="R26" t="n">
-        <v>-6.66</v>
+        <v>-3.14</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>434</v>
+        <v>425.6</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.4</v>
+        <v>-8.4</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.32</v>
+        <v>-1.94</v>
       </c>
       <c r="G27" t="n">
-        <v>425.6</v>
+        <v>428.4</v>
       </c>
       <c r="H27" t="n">
-        <v>-8.4</v>
+        <v>2.8</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.94</v>
+        <v>0.66</v>
       </c>
       <c r="J27" t="n">
-        <v>428.4</v>
+        <v>430.6</v>
       </c>
       <c r="K27" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="L27" t="n">
-        <v>0.66</v>
+        <v>0.51</v>
       </c>
       <c r="M27" t="n">
-        <v>430.6</v>
+        <v>438.8</v>
       </c>
       <c r="N27" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>0.51</v>
+        <v>1.9</v>
       </c>
       <c r="P27" t="n">
-        <v>430.6</v>
+        <v>438.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="R27" t="n">
-        <v>0.51</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>109.8</v>
+        <v>106.9</v>
       </c>
       <c r="E28" t="n">
-        <v>0.3</v>
+        <v>-2.9</v>
       </c>
       <c r="F28" t="n">
-        <v>0.27</v>
+        <v>-2.64</v>
       </c>
       <c r="G28" t="n">
-        <v>106.9</v>
+        <v>107.5</v>
       </c>
       <c r="H28" t="n">
-        <v>-2.9</v>
+        <v>0.6</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>107.5</v>
+        <v>105.9</v>
       </c>
       <c r="K28" t="n">
-        <v>0.6</v>
+        <v>-1.6</v>
       </c>
       <c r="L28" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.49</v>
       </c>
       <c r="M28" t="n">
-        <v>105.9</v>
+        <v>107.2</v>
       </c>
       <c r="N28" t="n">
-        <v>-1.6</v>
+        <v>1.3</v>
       </c>
       <c r="O28" t="n">
-        <v>-1.49</v>
+        <v>1.23</v>
       </c>
       <c r="P28" t="n">
-        <v>105.9</v>
+        <v>107.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1.6</v>
+        <v>1.3</v>
       </c>
       <c r="R28" t="n">
-        <v>-1.49</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="G29" t="n">
+        <v>106.2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J29" t="n">
+        <v>106</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="M29" t="n">
         <v>106.3</v>
       </c>
-      <c r="E29" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="F29" t="n">
-        <v>-2.12</v>
-      </c>
-      <c r="G29" t="n">
-        <v>105.5</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-0.8</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-0.75</v>
-      </c>
-      <c r="J29" t="n">
-        <v>106.2</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.66</v>
-      </c>
-      <c r="M29" t="n">
-        <v>106</v>
-      </c>
       <c r="N29" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.19</v>
+        <v>0.28</v>
       </c>
       <c r="P29" t="n">
-        <v>106</v>
+        <v>106.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.19</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>77.8</v>
+        <v>74.75</v>
       </c>
       <c r="E30" t="n">
-        <v>-2.8</v>
+        <v>-3.05</v>
       </c>
       <c r="F30" t="n">
-        <v>-3.47</v>
+        <v>-3.92</v>
       </c>
       <c r="G30" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J30" t="n">
+        <v>75.05</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="M30" t="n">
         <v>74.75</v>
       </c>
-      <c r="H30" t="n">
-        <v>-3.05</v>
-      </c>
-      <c r="I30" t="n">
-        <v>-3.92</v>
-      </c>
-      <c r="J30" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="M30" t="n">
-        <v>75.05</v>
-      </c>
       <c r="N30" t="n">
-        <v>-0.05</v>
+        <v>-0.3</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.4</v>
       </c>
       <c r="P30" t="n">
-        <v>75.05</v>
+        <v>74.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.05</v>
+        <v>-0.3</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>92.2</v>
+        <v>89.15000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>2.65</v>
+        <v>-3.05</v>
       </c>
       <c r="F31" t="n">
-        <v>2.96</v>
+        <v>-3.31</v>
       </c>
       <c r="G31" t="n">
-        <v>89.15000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>-3.05</v>
+        <v>-0.05</v>
       </c>
       <c r="I31" t="n">
-        <v>-3.31</v>
+        <v>-0.06</v>
       </c>
       <c r="J31" t="n">
-        <v>89.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.05</v>
+        <v>0.2</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.06</v>
+        <v>0.22</v>
       </c>
       <c r="M31" t="n">
-        <v>89.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="O31" t="n">
-        <v>0.22</v>
+        <v>-0.45</v>
       </c>
       <c r="P31" t="n">
-        <v>89.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0.22</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>65</v>
+        <v>63.45</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.35</v>
+        <v>-1.55</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.54</v>
+        <v>-2.38</v>
       </c>
       <c r="G32" t="n">
-        <v>63.45</v>
+        <v>63.15</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.55</v>
+        <v>-0.3</v>
       </c>
       <c r="I32" t="n">
-        <v>-2.38</v>
+        <v>-0.47</v>
       </c>
       <c r="J32" t="n">
-        <v>63.15</v>
+        <v>61.3</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.3</v>
+        <v>-1.85</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.47</v>
+        <v>-2.93</v>
       </c>
       <c r="M32" t="n">
-        <v>61.3</v>
+        <v>60.75</v>
       </c>
       <c r="N32" t="n">
-        <v>-1.85</v>
+        <v>-0.55</v>
       </c>
       <c r="O32" t="n">
-        <v>-2.93</v>
+        <v>-0.9</v>
       </c>
       <c r="P32" t="n">
-        <v>61.3</v>
+        <v>60.75</v>
       </c>
       <c r="Q32" t="n">
-        <v>-1.85</v>
+        <v>-0.55</v>
       </c>
       <c r="R32" t="n">
-        <v>-2.93</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>81.8</v>
+        <v>79.55</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.05</v>
+        <v>-2.25</v>
       </c>
       <c r="F33" t="n">
-        <v>-2.44</v>
+        <v>-2.75</v>
       </c>
       <c r="G33" t="n">
-        <v>79.55</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>-2.25</v>
+        <v>0.3</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.75</v>
+        <v>0.38</v>
       </c>
       <c r="J33" t="n">
-        <v>79.84999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="K33" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="L33" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="M33" t="n">
-        <v>80.2</v>
+        <v>79.05</v>
       </c>
       <c r="N33" t="n">
-        <v>0.35</v>
+        <v>-1.15</v>
       </c>
       <c r="O33" t="n">
-        <v>0.44</v>
+        <v>-1.43</v>
       </c>
       <c r="P33" t="n">
-        <v>80.2</v>
+        <v>79.05</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.35</v>
+        <v>-1.15</v>
       </c>
       <c r="R33" t="n">
-        <v>0.44</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>32.32</v>
+        <v>31.66</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.72</v>
+        <v>-0.66</v>
       </c>
       <c r="F34" t="n">
+        <v>-2.04</v>
+      </c>
+      <c r="G34" t="n">
+        <v>31.26</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="J34" t="n">
+        <v>30.58</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="L34" t="n">
         <v>-2.18</v>
       </c>
-      <c r="G34" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="I34" t="n">
-        <v>-2.04</v>
-      </c>
-      <c r="J34" t="n">
-        <v>31.26</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="L34" t="n">
-        <v>-1.26</v>
-      </c>
       <c r="M34" t="n">
-        <v>30.58</v>
+        <v>29.8</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.68</v>
+        <v>-0.78</v>
       </c>
       <c r="O34" t="n">
-        <v>-2.18</v>
+        <v>-2.55</v>
       </c>
       <c r="P34" t="n">
-        <v>30.58</v>
+        <v>29.8</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.68</v>
+        <v>-0.78</v>
       </c>
       <c r="R34" t="n">
-        <v>-2.18</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.33</v>
+        <v>4.25</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.92</v>
+        <v>-1.85</v>
       </c>
       <c r="G35" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.85</v>
+        <v>-0.24</v>
       </c>
       <c r="J35" t="n">
         <v>4.24</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.24</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>4.24</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.24</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>4.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.33</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.08</v>
+        <v>-0.19</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.85</v>
+        <v>-2.04</v>
       </c>
       <c r="G36" t="n">
-        <v>9.140000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.19</v>
+        <v>-0.02</v>
       </c>
       <c r="I36" t="n">
-        <v>-2.04</v>
+        <v>-0.22</v>
       </c>
       <c r="J36" t="n">
-        <v>9.119999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.22</v>
+        <v>-0.11</v>
       </c>
       <c r="M36" t="n">
-        <v>9.119999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.22</v>
+        <v>-0.11</v>
       </c>
       <c r="P36" t="n">
-        <v>9.119999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.22</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>400.4</v>
+        <v>397</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.6</v>
+        <v>-3.4</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.4</v>
+        <v>-0.85</v>
       </c>
       <c r="G37" t="n">
-        <v>397</v>
+        <v>392.6</v>
       </c>
       <c r="H37" t="n">
-        <v>-3.4</v>
+        <v>-4.4</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.85</v>
+        <v>-1.11</v>
       </c>
       <c r="J37" t="n">
-        <v>392.6</v>
+        <v>397.4</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L37" t="n">
-        <v>-1.11</v>
+        <v>1.22</v>
       </c>
       <c r="M37" t="n">
-        <v>397.4</v>
+        <v>393.8</v>
       </c>
       <c r="N37" t="n">
-        <v>4.8</v>
+        <v>-3.6</v>
       </c>
       <c r="O37" t="n">
-        <v>1.22</v>
+        <v>-0.91</v>
       </c>
       <c r="P37" t="n">
-        <v>397.4</v>
+        <v>393.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.8</v>
+        <v>-3.6</v>
       </c>
       <c r="R37" t="n">
-        <v>1.22</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.79</v>
+        <v>13.38</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.24</v>
+        <v>-0.41</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.71</v>
+        <v>-2.97</v>
       </c>
       <c r="G38" t="n">
-        <v>13.38</v>
+        <v>13.36</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.41</v>
+        <v>-0.02</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.97</v>
+        <v>-0.15</v>
       </c>
       <c r="J38" t="n">
-        <v>13.36</v>
+        <v>13</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.02</v>
+        <v>-0.36</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.15</v>
+        <v>-2.69</v>
       </c>
       <c r="M38" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.36</v>
+        <v>-0.2</v>
       </c>
       <c r="O38" t="n">
-        <v>-2.69</v>
+        <v>-1.54</v>
       </c>
       <c r="P38" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.36</v>
+        <v>-0.2</v>
       </c>
       <c r="R38" t="n">
-        <v>-2.69</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>562</v>
+        <v>561.5</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="G39" t="n">
-        <v>561.5</v>
+        <v>547.5</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.5</v>
+        <v>-14</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.09</v>
+        <v>-2.49</v>
       </c>
       <c r="J39" t="n">
-        <v>547.5</v>
+        <v>549</v>
       </c>
       <c r="K39" t="n">
-        <v>-14</v>
+        <v>1.5</v>
       </c>
       <c r="L39" t="n">
-        <v>-2.49</v>
+        <v>0.27</v>
       </c>
       <c r="M39" t="n">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="N39" t="n">
-        <v>1.5</v>
+        <v>-33</v>
       </c>
       <c r="O39" t="n">
-        <v>0.27</v>
+        <v>-6.01</v>
       </c>
       <c r="P39" t="n">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.5</v>
+        <v>-33</v>
       </c>
       <c r="R39" t="n">
-        <v>0.27</v>
+        <v>-6.01</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>42.3</v>
+        <v>41.6</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.08</v>
+        <v>-0.7</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.19</v>
+        <v>-1.65</v>
       </c>
       <c r="G40" t="n">
-        <v>41.6</v>
+        <v>41.34</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.7</v>
+        <v>-0.26</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.65</v>
+        <v>-0.62</v>
       </c>
       <c r="J40" t="n">
-        <v>41.34</v>
+        <v>42.02</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.26</v>
+        <v>0.68</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.62</v>
+        <v>1.64</v>
       </c>
       <c r="M40" t="n">
-        <v>42.02</v>
+        <v>40.38</v>
       </c>
       <c r="N40" t="n">
-        <v>0.68</v>
+        <v>-1.64</v>
       </c>
       <c r="O40" t="n">
-        <v>1.64</v>
+        <v>-3.9</v>
       </c>
       <c r="P40" t="n">
-        <v>42.02</v>
+        <v>40.38</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.68</v>
+        <v>-1.64</v>
       </c>
       <c r="R40" t="n">
-        <v>1.64</v>
+        <v>-3.9</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.35</v>
+        <v>31.39</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.35</v>
+        <v>0.04</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.1</v>
+        <v>0.13</v>
       </c>
       <c r="G41" t="n">
-        <v>31.39</v>
+        <v>31.6</v>
       </c>
       <c r="H41" t="n">
-        <v>0.04</v>
+        <v>0.21</v>
       </c>
       <c r="I41" t="n">
-        <v>0.13</v>
+        <v>0.67</v>
       </c>
       <c r="J41" t="n">
-        <v>31.6</v>
+        <v>31.85</v>
       </c>
       <c r="K41" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="L41" t="n">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="M41" t="n">
-        <v>31.85</v>
+        <v>31</v>
       </c>
       <c r="N41" t="n">
-        <v>0.25</v>
+        <v>-0.85</v>
       </c>
       <c r="O41" t="n">
-        <v>0.79</v>
+        <v>-2.67</v>
       </c>
       <c r="P41" t="n">
-        <v>31.85</v>
+        <v>31</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.25</v>
+        <v>-0.85</v>
       </c>
       <c r="R41" t="n">
-        <v>0.79</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>77.5</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.6</v>
+        <v>-0.71</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.77</v>
+        <v>-0.92</v>
       </c>
       <c r="G42" t="n">
-        <v>76.79000000000001</v>
+        <v>77</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.71</v>
+        <v>0.21</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.92</v>
+        <v>0.27</v>
       </c>
       <c r="J42" t="n">
-        <v>77</v>
+        <v>77.66</v>
       </c>
       <c r="K42" t="n">
-        <v>0.21</v>
+        <v>0.66</v>
       </c>
       <c r="L42" t="n">
-        <v>0.27</v>
+        <v>0.86</v>
       </c>
       <c r="M42" t="n">
-        <v>77.66</v>
+        <v>76.75</v>
       </c>
       <c r="N42" t="n">
-        <v>0.66</v>
+        <v>-0.91</v>
       </c>
       <c r="O42" t="n">
-        <v>0.86</v>
+        <v>-1.17</v>
       </c>
       <c r="P42" t="n">
-        <v>77.66</v>
+        <v>76.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.66</v>
+        <v>-0.91</v>
       </c>
       <c r="R42" t="n">
-        <v>0.86</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>41.18</v>
+        <v>40.99</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.42</v>
+        <v>-0.19</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.01</v>
+        <v>-0.46</v>
       </c>
       <c r="G43" t="n">
-        <v>40.99</v>
+        <v>41.26</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.19</v>
+        <v>0.27</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.46</v>
+        <v>0.66</v>
       </c>
       <c r="J43" t="n">
-        <v>41.26</v>
+        <v>42.33</v>
       </c>
       <c r="K43" t="n">
-        <v>0.27</v>
+        <v>1.07</v>
       </c>
       <c r="L43" t="n">
-        <v>0.66</v>
+        <v>2.59</v>
       </c>
       <c r="M43" t="n">
-        <v>42.33</v>
+        <v>41.33</v>
       </c>
       <c r="N43" t="n">
-        <v>1.07</v>
+        <v>-1</v>
       </c>
       <c r="O43" t="n">
-        <v>2.59</v>
+        <v>-2.36</v>
       </c>
       <c r="P43" t="n">
-        <v>42.33</v>
+        <v>41.33</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.07</v>
+        <v>-1</v>
       </c>
       <c r="R43" t="n">
-        <v>2.59</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.19</v>
+        <v>6.1</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.32</v>
+        <v>-1.45</v>
       </c>
       <c r="G44" t="n">
         <v>6.1</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>-1.45</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="M44" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="N44" t="n">
         <v>-0.05</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.82</v>
+        <v>-0.83</v>
       </c>
       <c r="P44" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="Q44" t="n">
         <v>-0.05</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.82</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="E45" t="n">
         <v>-0.02</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.91</v>
+        <v>-0.92</v>
       </c>
       <c r="G45" t="n">
         <v>2.15</v>
       </c>
       <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="K45" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I45" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>-0.93</v>
       </c>
       <c r="M45" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.93</v>
+        <v>-0.47</v>
       </c>
       <c r="P45" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.93</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>3.93</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.48</v>
+        <v>-1.75</v>
       </c>
       <c r="G46" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.75</v>
+        <v>-0.51</v>
       </c>
       <c r="J46" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.51</v>
+        <v>-1.02</v>
       </c>
       <c r="M46" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="O46" t="n">
-        <v>-1.02</v>
+        <v>-0.26</v>
       </c>
       <c r="P46" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="R46" t="n">
-        <v>-1.02</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.37</v>
+        <v>10.27</v>
       </c>
       <c r="E47" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="F47" t="n">
-        <v>0.29</v>
+        <v>-0.96</v>
       </c>
       <c r="G47" t="n">
-        <v>10.27</v>
+        <v>10.24</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.96</v>
+        <v>-0.29</v>
       </c>
       <c r="J47" t="n">
-        <v>10.24</v>
+        <v>10.22</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.29</v>
+        <v>-0.2</v>
       </c>
       <c r="M47" t="n">
-        <v>10.22</v>
+        <v>10.13</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.2</v>
+        <v>-0.88</v>
       </c>
       <c r="P47" t="n">
-        <v>10.22</v>
+        <v>10.13</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.2</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.335</v>
+        <v>0.325</v>
       </c>
       <c r="E48" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-2.99</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F48" t="n">
-        <v>-1.47</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="I48" t="n">
-        <v>-2.99</v>
+        <v>-1.54</v>
       </c>
       <c r="J48" t="n">
         <v>0.32</v>
       </c>
       <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="N48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L48" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>-1.56</v>
       </c>
       <c r="P48" t="n">
-        <v>0.32</v>
+        <v>0.315</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>-1.56</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.56</v>
+        <v>4.52</v>
       </c>
       <c r="E49" t="n">
-        <v>0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="F49" t="n">
-        <v>0.44</v>
+        <v>-0.88</v>
       </c>
       <c r="G49" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="H49" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="K49" t="n">
         <v>-0.04</v>
       </c>
-      <c r="I49" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="J49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="K49" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="L49" t="n">
-        <v>-0.44</v>
+        <v>-0.89</v>
       </c>
       <c r="M49" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.89</v>
+        <v>-0.22</v>
       </c>
       <c r="P49" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.89</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-0.89</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="M50" t="n">
         <v>1.12</v>
       </c>
-      <c r="E50" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="I50" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="K50" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L50" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.1</v>
-      </c>
       <c r="N50" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="O50" t="n">
-        <v>0.92</v>
+        <v>1.82</v>
       </c>
       <c r="P50" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="R50" t="n">
-        <v>0.92</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.12</v>
+        <v>5</v>
       </c>
       <c r="E51" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-2.34</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="H51" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F51" t="n">
+      <c r="I51" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="L51" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="M51" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="N51" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O51" t="n">
         <v>-0.39</v>
       </c>
-      <c r="G51" t="n">
-        <v>5</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="I51" t="n">
-        <v>-2.34</v>
-      </c>
-      <c r="J51" t="n">
-        <v>4.98</v>
-      </c>
-      <c r="K51" t="n">
+      <c r="P51" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="Q51" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L51" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="M51" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="O51" t="n">
-        <v>2.61</v>
-      </c>
-      <c r="P51" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0.13</v>
-      </c>
       <c r="R51" t="n">
-        <v>2.61</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.47</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.08</v>
+        <v>-0.33</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.67</v>
+        <v>-2.8</v>
       </c>
       <c r="G52" t="n">
-        <v>11.47</v>
+        <v>11.43</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.33</v>
+        <v>-0.04</v>
       </c>
       <c r="I52" t="n">
-        <v>-2.8</v>
+        <v>-0.35</v>
       </c>
       <c r="J52" t="n">
-        <v>11.43</v>
+        <v>11.33</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.35</v>
+        <v>-0.87</v>
       </c>
       <c r="M52" t="n">
-        <v>11.33</v>
+        <v>11.2</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.87</v>
+        <v>-1.15</v>
       </c>
       <c r="P52" t="n">
-        <v>11.33</v>
+        <v>11.2</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.87</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.35</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.04</v>
+        <v>-0.13</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.48</v>
+        <v>-1.56</v>
       </c>
       <c r="G53" t="n">
-        <v>8.220000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.56</v>
+        <v>-0.73</v>
       </c>
       <c r="J53" t="n">
-        <v>8.16</v>
+        <v>8.15</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.73</v>
+        <v>-0.12</v>
       </c>
       <c r="M53" t="n">
-        <v>8.15</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.12</v>
+        <v>-1.23</v>
       </c>
       <c r="P53" t="n">
-        <v>8.15</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.12</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="54">
@@ -3742,46 +3742,46 @@
         <v>0.445</v>
       </c>
       <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F54" t="n">
+      <c r="I54" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L54" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="N54" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="O54" t="n">
         <v>-1.11</v>
       </c>
-      <c r="G54" t="n">
+      <c r="P54" t="n">
         <v>0.445</v>
       </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="K54" t="n">
+      <c r="Q54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L54" t="n">
-        <v>-1.12</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O54" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0.01</v>
-      </c>
       <c r="R54" t="n">
-        <v>2.27</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="55">
@@ -3804,10 +3804,10 @@
         <v>0.615</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0.615</v>
@@ -3863,22 +3863,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.415</v>
+        <v>0.41</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>-1.2</v>
       </c>
       <c r="G56" t="n">
         <v>0.41</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0.41</v>
@@ -3890,22 +3890,22 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>-4.88</v>
       </c>
       <c r="P56" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>-4.88</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>-0.54</v>
       </c>
       <c r="G57" t="n">
         <v>3.71</v>
       </c>
       <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N57" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I57" t="n">
+      <c r="O57" t="n">
         <v>-0.54</v>
       </c>
-      <c r="J57" t="n">
-        <v>3.71</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O57" t="n">
-        <v>0.27</v>
-      </c>
       <c r="P57" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="R57" t="n">
-        <v>0.27</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="58">
@@ -3990,46 +3990,46 @@
         <v>0.076</v>
       </c>
       <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="H58" t="n">
         <v>0.001</v>
       </c>
-      <c r="F58" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="G58" t="n">
+      <c r="I58" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="J58" t="n">
         <v>0.076</v>
       </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.077</v>
-      </c>
       <c r="K58" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="L58" t="n">
-        <v>1.32</v>
+        <v>-1.3</v>
       </c>
       <c r="M58" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="N58" t="n">
         <v>-0.001</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.3</v>
+        <v>-1.32</v>
       </c>
       <c r="P58" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="Q58" t="n">
         <v>-0.001</v>
       </c>
       <c r="R58" t="n">
-        <v>-1.3</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>24.78</v>
+        <v>24.68</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.48</v>
+        <v>-0.4</v>
       </c>
       <c r="G59" t="n">
-        <v>24.68</v>
+        <v>24.3</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.1</v>
+        <v>-0.38</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.4</v>
+        <v>-1.54</v>
       </c>
       <c r="J59" t="n">
-        <v>24.3</v>
+        <v>22.91</v>
       </c>
       <c r="K59" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="L59" t="n">
+        <v>-5.72</v>
+      </c>
+      <c r="M59" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="N59" t="n">
         <v>-0.38</v>
       </c>
-      <c r="L59" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="M59" t="n">
-        <v>22.91</v>
-      </c>
-      <c r="N59" t="n">
-        <v>-1.39</v>
-      </c>
       <c r="O59" t="n">
-        <v>-5.72</v>
+        <v>-1.66</v>
       </c>
       <c r="P59" t="n">
-        <v>22.91</v>
+        <v>22.53</v>
       </c>
       <c r="Q59" t="n">
-        <v>-1.39</v>
+        <v>-0.38</v>
       </c>
       <c r="R59" t="n">
-        <v>-5.72</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="E60" t="n">
         <v>-0.01</v>
@@ -4123,37 +4123,37 @@
         <v>3.11</v>
       </c>
       <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K60" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I60" t="n">
+      <c r="L60" t="n">
         <v>-0.32</v>
       </c>
-      <c r="J60" t="n">
+      <c r="M60" t="n">
         <v>3.11</v>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.1</v>
-      </c>
       <c r="N60" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.32</v>
+        <v>0.32</v>
       </c>
       <c r="P60" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.32</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.9350000000000001</v>
+        <v>0.93</v>
       </c>
       <c r="E61" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="F61" t="n">
-        <v>0.54</v>
+        <v>-0.53</v>
       </c>
       <c r="G61" t="n">
-        <v>0.93</v>
+        <v>0.915</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.005</v>
+        <v>-0.015</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.53</v>
+        <v>-1.61</v>
       </c>
       <c r="J61" t="n">
-        <v>0.915</v>
+        <v>0.885</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.015</v>
+        <v>-0.03</v>
       </c>
       <c r="L61" t="n">
-        <v>-1.61</v>
+        <v>-3.28</v>
       </c>
       <c r="M61" t="n">
-        <v>0.885</v>
+        <v>0.875</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="O61" t="n">
-        <v>-3.28</v>
+        <v>-1.13</v>
       </c>
       <c r="P61" t="n">
-        <v>0.885</v>
+        <v>0.875</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="R61" t="n">
-        <v>-3.28</v>
+        <v>-1.13</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-10 Close</t>
+          <t>2026-09-11 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-09-10 Change</t>
+          <t>2026-09-11 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-10 Change %</t>
+          <t>2026-09-11 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-09-11 Close</t>
+          <t>2026-09-14 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-09-11 Change</t>
+          <t>2026-09-14 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-09-11 Change %</t>
+          <t>2026-09-14 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-09-14 Close</t>
+          <t>2026-09-15 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-09-14 Change</t>
+          <t>2026-09-15 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-09-14 Change %</t>
+          <t>2026-09-15 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-09-15 Close</t>
+          <t>2026-09-16 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-09-15 Change</t>
+          <t>2026-09-16 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-09-15 Change %</t>
+          <t>2026-09-16 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-09-16 Close</t>
+          <t>2026-09-17 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-09-16 Change</t>
+          <t>2026-09-17 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-09-16 Change %</t>
+          <t>2026-09-17 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>164.7</v>
+        <v>163.3</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.3</v>
+        <v>-1.4</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.78</v>
+        <v>-0.85</v>
       </c>
       <c r="G3" t="n">
-        <v>163.3</v>
+        <v>164.9</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.4</v>
+        <v>1.6</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.85</v>
+        <v>0.98</v>
       </c>
       <c r="J3" t="n">
-        <v>164.9</v>
+        <v>159.6</v>
       </c>
       <c r="K3" t="n">
-        <v>1.6</v>
+        <v>-5.3</v>
       </c>
       <c r="L3" t="n">
-        <v>0.98</v>
+        <v>-3.21</v>
       </c>
       <c r="M3" t="n">
-        <v>159.6</v>
+        <v>160.9</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.3</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
-        <v>-3.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>159.6</v>
+        <v>160.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>-5.3</v>
+        <v>1.3</v>
       </c>
       <c r="R3" t="n">
-        <v>-3.21</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -642,46 +642,46 @@
         <v>241.8</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.33</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>241.8</v>
+        <v>246.6</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="J4" t="n">
-        <v>246.6</v>
+        <v>238</v>
       </c>
       <c r="K4" t="n">
-        <v>4.8</v>
+        <v>-8.6</v>
       </c>
       <c r="L4" t="n">
-        <v>1.99</v>
+        <v>-3.49</v>
       </c>
       <c r="M4" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="N4" t="n">
-        <v>-8.6</v>
+        <v>6</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.49</v>
+        <v>2.52</v>
       </c>
       <c r="P4" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="Q4" t="n">
-        <v>-8.6</v>
+        <v>6</v>
       </c>
       <c r="R4" t="n">
-        <v>-3.49</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.38</v>
+        <v>6.36</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="F5" t="n">
-        <v>1.27</v>
+        <v>-0.31</v>
       </c>
       <c r="G5" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="J5" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="M5" t="n">
         <v>6.36</v>
       </c>
-      <c r="H5" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="K5" t="n">
+      <c r="N5" t="n">
         <v>0.05</v>
       </c>
-      <c r="L5" t="n">
+      <c r="O5" t="n">
         <v>0.79</v>
       </c>
-      <c r="M5" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="N5" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="O5" t="n">
-        <v>-1.56</v>
-      </c>
       <c r="P5" t="n">
-        <v>6.31</v>
+        <v>6.36</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.56</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="6">
@@ -766,46 +766,46 @@
         <v>7.61</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.79</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>7.61</v>
+        <v>7.65</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="J6" t="n">
-        <v>7.65</v>
+        <v>7.49</v>
       </c>
       <c r="K6" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="M6" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="N6" t="n">
         <v>0.04</v>
       </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
         <v>0.53</v>
       </c>
-      <c r="M6" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="O6" t="n">
-        <v>-2.09</v>
-      </c>
       <c r="P6" t="n">
-        <v>7.49</v>
+        <v>7.53</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.16</v>
+        <v>0.04</v>
       </c>
       <c r="R6" t="n">
-        <v>-2.09</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.97</v>
+        <v>6.05</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="G7" t="n">
-        <v>6.05</v>
+        <v>6.09</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1.34</v>
+        <v>0.66</v>
       </c>
       <c r="J7" t="n">
-        <v>6.09</v>
+        <v>5.95</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04</v>
+        <v>-0.14</v>
       </c>
       <c r="L7" t="n">
-        <v>0.66</v>
+        <v>-2.3</v>
       </c>
       <c r="M7" t="n">
-        <v>5.95</v>
+        <v>5.98</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.3</v>
+        <v>0.5</v>
       </c>
       <c r="P7" t="n">
-        <v>5.95</v>
+        <v>5.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="R7" t="n">
-        <v>-2.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.77</v>
+        <v>9.75</v>
       </c>
       <c r="E8" t="n">
-        <v>0.16</v>
+        <v>-0.02</v>
       </c>
       <c r="F8" t="n">
-        <v>1.66</v>
+        <v>-0.2</v>
       </c>
       <c r="G8" t="n">
-        <v>9.75</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.02</v>
+        <v>0.14</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2</v>
+        <v>1.44</v>
       </c>
       <c r="J8" t="n">
-        <v>9.890000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.14</v>
+        <v>-0.28</v>
       </c>
       <c r="L8" t="n">
-        <v>1.44</v>
+        <v>-2.83</v>
       </c>
       <c r="M8" t="n">
-        <v>9.609999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.28</v>
+        <v>0.03</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.83</v>
+        <v>0.31</v>
       </c>
       <c r="P8" t="n">
-        <v>9.609999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.28</v>
+        <v>0.03</v>
       </c>
       <c r="R8" t="n">
-        <v>-2.83</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.06</v>
+        <v>8.09</v>
       </c>
       <c r="E9" t="n">
-        <v>0.17</v>
+        <v>0.03</v>
       </c>
       <c r="F9" t="n">
-        <v>2.15</v>
+        <v>0.37</v>
       </c>
       <c r="G9" t="n">
-        <v>8.09</v>
+        <v>8.16</v>
       </c>
       <c r="H9" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I9" t="n">
-        <v>0.37</v>
+        <v>0.87</v>
       </c>
       <c r="J9" t="n">
-        <v>8.16</v>
+        <v>8.02</v>
       </c>
       <c r="K9" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="L9" t="n">
-        <v>0.87</v>
+        <v>-1.72</v>
       </c>
       <c r="M9" t="n">
-        <v>8.02</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.14</v>
+        <v>0.1</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.72</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>8.02</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.14</v>
+        <v>0.1</v>
       </c>
       <c r="R9" t="n">
-        <v>-1.72</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>52.15</v>
+        <v>51.95</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="F10" t="n">
-        <v>0.58</v>
+        <v>-0.38</v>
       </c>
       <c r="G10" t="n">
-        <v>51.95</v>
+        <v>52.75</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2</v>
+        <v>0.8</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.38</v>
+        <v>1.54</v>
       </c>
       <c r="J10" t="n">
-        <v>52.75</v>
+        <v>51.2</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8</v>
+        <v>-1.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.54</v>
+        <v>-2.94</v>
       </c>
       <c r="M10" t="n">
-        <v>51.2</v>
+        <v>51.35</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.55</v>
+        <v>0.15</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.94</v>
+        <v>0.29</v>
       </c>
       <c r="P10" t="n">
-        <v>51.2</v>
+        <v>51.35</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.55</v>
+        <v>0.15</v>
       </c>
       <c r="R10" t="n">
-        <v>-2.94</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.84</v>
+        <v>4.78</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.63</v>
+        <v>-1.24</v>
       </c>
       <c r="G11" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.24</v>
+        <v>-0.84</v>
       </c>
       <c r="J11" t="n">
-        <v>4.74</v>
+        <v>4.63</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.04</v>
+        <v>-0.11</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.84</v>
+        <v>-2.32</v>
       </c>
       <c r="M11" t="n">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.11</v>
+        <v>-0.02</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.32</v>
+        <v>-0.43</v>
       </c>
       <c r="P11" t="n">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.11</v>
+        <v>-0.02</v>
       </c>
       <c r="R11" t="n">
-        <v>-2.32</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.09</v>
+        <v>9.98</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.34</v>
+        <v>-0.11</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.26</v>
+        <v>-1.09</v>
       </c>
       <c r="G12" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="J12" t="n">
         <v>9.98</v>
       </c>
-      <c r="H12" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="I12" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="J12" t="n">
-        <v>9.92</v>
-      </c>
       <c r="K12" t="n">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6</v>
+        <v>0.6</v>
       </c>
       <c r="M12" t="n">
-        <v>9.98</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>0.06</v>
+        <v>-0.19</v>
       </c>
       <c r="O12" t="n">
-        <v>0.6</v>
+        <v>-1.9</v>
       </c>
       <c r="P12" t="n">
-        <v>9.98</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.06</v>
+        <v>-0.19</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>25.02</v>
+        <v>24.38</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.8</v>
+        <v>-0.64</v>
       </c>
       <c r="F13" t="n">
-        <v>-3.1</v>
+        <v>-2.56</v>
       </c>
       <c r="G13" t="n">
-        <v>24.38</v>
+        <v>24.46</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.64</v>
+        <v>0.08</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.56</v>
+        <v>0.33</v>
       </c>
       <c r="J13" t="n">
-        <v>24.46</v>
+        <v>24.48</v>
       </c>
       <c r="K13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L13" t="n">
         <v>0.08</v>
       </c>
-      <c r="L13" t="n">
-        <v>0.33</v>
-      </c>
       <c r="M13" t="n">
-        <v>24.48</v>
+        <v>24.36</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02</v>
+        <v>-0.12</v>
       </c>
       <c r="O13" t="n">
-        <v>0.08</v>
+        <v>-0.49</v>
       </c>
       <c r="P13" t="n">
-        <v>24.48</v>
+        <v>24.36</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.02</v>
+        <v>-0.12</v>
       </c>
       <c r="R13" t="n">
-        <v>0.08</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.46</v>
+        <v>-1.98</v>
       </c>
       <c r="G14" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.98</v>
+        <v>-1.01</v>
       </c>
       <c r="J14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.01</v>
+        <v>-0.51</v>
       </c>
       <c r="M14" t="n">
         <v>1.95</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>1.95</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.23</v>
+        <v>5.29</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.16</v>
+        <v>0.06</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.97</v>
+        <v>1.15</v>
       </c>
       <c r="G15" t="n">
-        <v>5.29</v>
+        <v>5.24</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="I15" t="n">
-        <v>1.15</v>
+        <v>-0.95</v>
       </c>
       <c r="J15" t="n">
-        <v>5.24</v>
+        <v>5.17</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.95</v>
+        <v>-1.34</v>
       </c>
       <c r="M15" t="n">
-        <v>5.17</v>
+        <v>5.11</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.34</v>
+        <v>-1.16</v>
       </c>
       <c r="P15" t="n">
-        <v>5.17</v>
+        <v>5.11</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.34</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="16">
@@ -1383,34 +1383,34 @@
         </is>
       </c>
       <c r="D16" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="J16" t="n">
         <v>4.43</v>
       </c>
-      <c r="E16" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="G16" t="n">
+      <c r="K16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M16" t="n">
         <v>4.44</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4.43</v>
       </c>
       <c r="N16" t="n">
         <v>0.01</v>
@@ -1419,7 +1419,7 @@
         <v>0.23</v>
       </c>
       <c r="P16" t="n">
-        <v>4.43</v>
+        <v>4.44</v>
       </c>
       <c r="Q16" t="n">
         <v>0.01</v>
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="E17" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-2.35</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="K17" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F17" t="n">
-        <v>-0.29</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="H17" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="I17" t="n">
-        <v>-2.35</v>
-      </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="M17" t="n">
         <v>3.35</v>
       </c>
-      <c r="K17" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.34</v>
-      </c>
       <c r="N17" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="P17" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="18">
@@ -1507,25 +1507,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.14</v>
+        <v>3.11</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F18" t="n">
-        <v>0.32</v>
+        <v>-0.96</v>
       </c>
       <c r="G18" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.96</v>
+        <v>-0.32</v>
       </c>
       <c r="J18" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="K18" t="n">
         <v>-0.01</v>
@@ -1537,19 +1537,19 @@
         <v>3.09</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>3.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>54.85</v>
+        <v>54</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.6</v>
+        <v>-0.85</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.08</v>
+        <v>-1.55</v>
       </c>
       <c r="G19" t="n">
-        <v>54</v>
+        <v>53.6</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.85</v>
+        <v>-0.4</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.55</v>
+        <v>-0.74</v>
       </c>
       <c r="J19" t="n">
-        <v>53.6</v>
+        <v>53.05</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4</v>
+        <v>-0.55</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.74</v>
+        <v>-1.03</v>
       </c>
       <c r="M19" t="n">
-        <v>53.05</v>
+        <v>52.8</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.55</v>
+        <v>-0.25</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.03</v>
+        <v>-0.47</v>
       </c>
       <c r="P19" t="n">
-        <v>53.05</v>
+        <v>52.8</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.55</v>
+        <v>-0.25</v>
       </c>
       <c r="R19" t="n">
-        <v>-1.03</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>30.14</v>
+        <v>29.6</v>
       </c>
       <c r="E20" t="n">
-        <v>0.66</v>
+        <v>-0.54</v>
       </c>
       <c r="F20" t="n">
-        <v>2.24</v>
+        <v>-1.79</v>
       </c>
       <c r="G20" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.54</v>
+        <v>0.2</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.79</v>
+        <v>0.68</v>
       </c>
       <c r="J20" t="n">
-        <v>29.8</v>
+        <v>28.96</v>
       </c>
       <c r="K20" t="n">
-        <v>0.2</v>
+        <v>-0.84</v>
       </c>
       <c r="L20" t="n">
-        <v>0.68</v>
+        <v>-2.82</v>
       </c>
       <c r="M20" t="n">
-        <v>28.96</v>
+        <v>28.54</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.84</v>
+        <v>-0.42</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.82</v>
+        <v>-1.45</v>
       </c>
       <c r="P20" t="n">
-        <v>28.96</v>
+        <v>28.54</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.84</v>
+        <v>-0.42</v>
       </c>
       <c r="R20" t="n">
-        <v>-2.82</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.61</v>
+        <v>4.52</v>
       </c>
       <c r="E21" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="F21" t="n">
-        <v>1.32</v>
+        <v>-1.95</v>
       </c>
       <c r="G21" t="n">
-        <v>4.52</v>
+        <v>4.59</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.95</v>
+        <v>1.55</v>
       </c>
       <c r="J21" t="n">
-        <v>4.59</v>
+        <v>4.49</v>
       </c>
       <c r="K21" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="L21" t="n">
-        <v>1.55</v>
+        <v>-2.18</v>
       </c>
       <c r="M21" t="n">
-        <v>4.49</v>
+        <v>4.53</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1</v>
+        <v>0.04</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.18</v>
+        <v>0.89</v>
       </c>
       <c r="P21" t="n">
-        <v>4.49</v>
+        <v>4.53</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.1</v>
+        <v>0.04</v>
       </c>
       <c r="R21" t="n">
-        <v>-2.18</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>78.84999999999999</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.13</v>
+        <v>0.06</v>
       </c>
       <c r="G22" t="n">
-        <v>78.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="H22" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="I22" t="n">
-        <v>0.06</v>
+        <v>0.38</v>
       </c>
       <c r="J22" t="n">
-        <v>79.2</v>
+        <v>79.05</v>
       </c>
       <c r="K22" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="M22" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="N22" t="n">
         <v>0.3</v>
       </c>
-      <c r="L22" t="n">
+      <c r="O22" t="n">
         <v>0.38</v>
       </c>
-      <c r="M22" t="n">
-        <v>79.05</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-0.19</v>
-      </c>
       <c r="P22" t="n">
-        <v>79.05</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.15</v>
+        <v>0.3</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.19</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="23">
@@ -1820,46 +1820,46 @@
         <v>22.98</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.13</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>22.98</v>
+        <v>22.6</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>-1.65</v>
       </c>
       <c r="J23" t="n">
-        <v>22.6</v>
+        <v>22.46</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.38</v>
+        <v>-0.14</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.65</v>
+        <v>-0.62</v>
       </c>
       <c r="M23" t="n">
-        <v>22.46</v>
+        <v>22.62</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.14</v>
+        <v>0.16</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.62</v>
+        <v>0.71</v>
       </c>
       <c r="P23" t="n">
-        <v>22.46</v>
+        <v>22.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.14</v>
+        <v>0.16</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.62</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.74</v>
+        <v>16.41</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2</v>
+        <v>-0.33</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.18</v>
+        <v>-1.97</v>
       </c>
       <c r="G24" t="n">
-        <v>16.41</v>
+        <v>16.24</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.33</v>
+        <v>-0.17</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.97</v>
+        <v>-1.04</v>
       </c>
       <c r="J24" t="n">
-        <v>16.24</v>
+        <v>15.88</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.17</v>
+        <v>-0.36</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.04</v>
+        <v>-2.22</v>
       </c>
       <c r="M24" t="n">
-        <v>15.88</v>
+        <v>15.95</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.36</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.22</v>
+        <v>0.44</v>
       </c>
       <c r="P24" t="n">
-        <v>15.88</v>
+        <v>15.95</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.36</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R24" t="n">
-        <v>-2.22</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.92</v>
+        <v>26.36</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.46</v>
+        <v>0.44</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.74</v>
+        <v>1.7</v>
       </c>
       <c r="G25" t="n">
-        <v>26.36</v>
+        <v>27.16</v>
       </c>
       <c r="H25" t="n">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="I25" t="n">
-        <v>1.7</v>
+        <v>3.03</v>
       </c>
       <c r="J25" t="n">
-        <v>27.16</v>
+        <v>26.5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.8</v>
+        <v>-0.66</v>
       </c>
       <c r="L25" t="n">
-        <v>3.03</v>
+        <v>-2.43</v>
       </c>
       <c r="M25" t="n">
-        <v>26.5</v>
+        <v>26.18</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.66</v>
+        <v>-0.32</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.43</v>
+        <v>-1.21</v>
       </c>
       <c r="P25" t="n">
-        <v>26.5</v>
+        <v>26.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.66</v>
+        <v>-0.32</v>
       </c>
       <c r="R25" t="n">
-        <v>-2.43</v>
+        <v>-1.21</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>37.48</v>
+        <v>35.46</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.74</v>
+        <v>-2.02</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.94</v>
+        <v>-5.39</v>
       </c>
       <c r="G26" t="n">
-        <v>35.46</v>
+        <v>33.1</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.02</v>
+        <v>-2.36</v>
       </c>
       <c r="I26" t="n">
-        <v>-5.39</v>
+        <v>-6.66</v>
       </c>
       <c r="J26" t="n">
-        <v>33.1</v>
+        <v>32.06</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.36</v>
+        <v>-1.04</v>
       </c>
       <c r="L26" t="n">
-        <v>-6.66</v>
+        <v>-3.14</v>
       </c>
       <c r="M26" t="n">
-        <v>32.06</v>
+        <v>32.88</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.04</v>
+        <v>0.82</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.14</v>
+        <v>2.56</v>
       </c>
       <c r="P26" t="n">
-        <v>32.06</v>
+        <v>32.88</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.04</v>
+        <v>0.82</v>
       </c>
       <c r="R26" t="n">
-        <v>-3.14</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>425.6</v>
+        <v>428.4</v>
       </c>
       <c r="E27" t="n">
-        <v>-8.4</v>
+        <v>2.8</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.94</v>
+        <v>0.66</v>
       </c>
       <c r="G27" t="n">
-        <v>428.4</v>
+        <v>430.6</v>
       </c>
       <c r="H27" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="I27" t="n">
-        <v>0.66</v>
+        <v>0.51</v>
       </c>
       <c r="J27" t="n">
-        <v>430.6</v>
+        <v>438.8</v>
       </c>
       <c r="K27" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>0.51</v>
+        <v>1.9</v>
       </c>
       <c r="M27" t="n">
-        <v>438.8</v>
+        <v>433.4</v>
       </c>
       <c r="N27" t="n">
-        <v>8.199999999999999</v>
+        <v>-5.4</v>
       </c>
       <c r="O27" t="n">
-        <v>1.9</v>
+        <v>-1.23</v>
       </c>
       <c r="P27" t="n">
-        <v>438.8</v>
+        <v>433.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>8.199999999999999</v>
+        <v>-5.4</v>
       </c>
       <c r="R27" t="n">
-        <v>1.9</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>106.9</v>
+        <v>107.5</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.9</v>
+        <v>0.6</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.64</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G28" t="n">
-        <v>107.5</v>
+        <v>105.9</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6</v>
+        <v>-1.6</v>
       </c>
       <c r="I28" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.49</v>
       </c>
       <c r="J28" t="n">
-        <v>105.9</v>
+        <v>107.2</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.6</v>
+        <v>1.3</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.49</v>
+        <v>1.23</v>
       </c>
       <c r="M28" t="n">
-        <v>107.2</v>
+        <v>106.2</v>
       </c>
       <c r="N28" t="n">
-        <v>1.3</v>
+        <v>-1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.23</v>
+        <v>-0.93</v>
       </c>
       <c r="P28" t="n">
-        <v>107.2</v>
+        <v>106.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.3</v>
+        <v>-1</v>
       </c>
       <c r="R28" t="n">
-        <v>1.23</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>105.5</v>
+        <v>106.2</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.8</v>
+        <v>0.7</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.75</v>
+        <v>0.66</v>
       </c>
       <c r="G29" t="n">
-        <v>106.2</v>
+        <v>106</v>
       </c>
       <c r="H29" t="n">
-        <v>0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="I29" t="n">
-        <v>0.66</v>
+        <v>-0.19</v>
       </c>
       <c r="J29" t="n">
-        <v>106</v>
+        <v>106.3</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.19</v>
+        <v>0.28</v>
       </c>
       <c r="M29" t="n">
-        <v>106.3</v>
+        <v>105.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="O29" t="n">
-        <v>0.28</v>
+        <v>-0.38</v>
       </c>
       <c r="P29" t="n">
-        <v>106.3</v>
+        <v>105.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0.28</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="30">
@@ -2251,34 +2251,34 @@
         </is>
       </c>
       <c r="D30" t="n">
+        <v>75.09999999999999</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G30" t="n">
+        <v>75.05</v>
+      </c>
+      <c r="H30" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I30" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="J30" t="n">
         <v>74.75</v>
       </c>
-      <c r="E30" t="n">
-        <v>-3.05</v>
-      </c>
-      <c r="F30" t="n">
-        <v>-3.92</v>
-      </c>
-      <c r="G30" t="n">
-        <v>75.09999999999999</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="J30" t="n">
-        <v>75.05</v>
-      </c>
       <c r="K30" t="n">
-        <v>-0.05</v>
+        <v>-0.3</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.4</v>
       </c>
       <c r="M30" t="n">
-        <v>74.75</v>
+        <v>74.45</v>
       </c>
       <c r="N30" t="n">
         <v>-0.3</v>
@@ -2287,7 +2287,7 @@
         <v>-0.4</v>
       </c>
       <c r="P30" t="n">
-        <v>74.75</v>
+        <v>74.45</v>
       </c>
       <c r="Q30" t="n">
         <v>-0.3</v>
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>89.15000000000001</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-3.05</v>
+        <v>-0.05</v>
       </c>
       <c r="F31" t="n">
-        <v>-3.31</v>
+        <v>-0.06</v>
       </c>
       <c r="G31" t="n">
-        <v>89.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.05</v>
+        <v>0.2</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.06</v>
+        <v>0.22</v>
       </c>
       <c r="J31" t="n">
-        <v>89.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="L31" t="n">
-        <v>0.22</v>
+        <v>-0.45</v>
       </c>
       <c r="M31" t="n">
-        <v>88.90000000000001</v>
+        <v>88.05</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.4</v>
+        <v>-0.85</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.45</v>
+        <v>-0.96</v>
       </c>
       <c r="P31" t="n">
-        <v>88.90000000000001</v>
+        <v>88.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.4</v>
+        <v>-0.85</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.45</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>63.45</v>
+        <v>63.15</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.55</v>
+        <v>-0.3</v>
       </c>
       <c r="F32" t="n">
-        <v>-2.38</v>
+        <v>-0.47</v>
       </c>
       <c r="G32" t="n">
-        <v>63.15</v>
+        <v>61.3</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3</v>
+        <v>-1.85</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.47</v>
+        <v>-2.93</v>
       </c>
       <c r="J32" t="n">
-        <v>61.3</v>
+        <v>60.75</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.85</v>
+        <v>-0.55</v>
       </c>
       <c r="L32" t="n">
-        <v>-2.93</v>
+        <v>-0.9</v>
       </c>
       <c r="M32" t="n">
-        <v>60.75</v>
+        <v>63.65</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.55</v>
+        <v>2.9</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.9</v>
+        <v>4.77</v>
       </c>
       <c r="P32" t="n">
-        <v>60.75</v>
+        <v>63.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.55</v>
+        <v>2.9</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.9</v>
+        <v>4.77</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>79.55</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-2.25</v>
+        <v>0.3</v>
       </c>
       <c r="F33" t="n">
-        <v>-2.75</v>
+        <v>0.38</v>
       </c>
       <c r="G33" t="n">
-        <v>79.84999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="H33" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="I33" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="J33" t="n">
-        <v>80.2</v>
+        <v>79.05</v>
       </c>
       <c r="K33" t="n">
-        <v>0.35</v>
+        <v>-1.15</v>
       </c>
       <c r="L33" t="n">
-        <v>0.44</v>
+        <v>-1.43</v>
       </c>
       <c r="M33" t="n">
-        <v>79.05</v>
+        <v>79.2</v>
       </c>
       <c r="N33" t="n">
-        <v>-1.15</v>
+        <v>0.15</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.43</v>
+        <v>0.19</v>
       </c>
       <c r="P33" t="n">
-        <v>79.05</v>
+        <v>79.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>-1.15</v>
+        <v>0.15</v>
       </c>
       <c r="R33" t="n">
-        <v>-1.43</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>31.66</v>
+        <v>31.26</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.66</v>
+        <v>-0.4</v>
       </c>
       <c r="F34" t="n">
-        <v>-2.04</v>
+        <v>-1.26</v>
       </c>
       <c r="G34" t="n">
-        <v>31.26</v>
+        <v>30.58</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.4</v>
+        <v>-0.68</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.26</v>
+        <v>-2.18</v>
       </c>
       <c r="J34" t="n">
-        <v>30.58</v>
+        <v>29.8</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.68</v>
+        <v>-0.78</v>
       </c>
       <c r="L34" t="n">
-        <v>-2.18</v>
+        <v>-2.55</v>
       </c>
       <c r="M34" t="n">
-        <v>29.8</v>
+        <v>29.66</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.78</v>
+        <v>-0.14</v>
       </c>
       <c r="O34" t="n">
-        <v>-2.55</v>
+        <v>-0.47</v>
       </c>
       <c r="P34" t="n">
-        <v>29.8</v>
+        <v>29.66</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.78</v>
+        <v>-0.14</v>
       </c>
       <c r="R34" t="n">
-        <v>-2.55</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.85</v>
+        <v>-0.24</v>
       </c>
       <c r="G35" t="n">
         <v>4.24</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.24</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="M35" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="P35" t="n">
-        <v>4.24</v>
+        <v>4.21</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.140000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.19</v>
+        <v>-0.02</v>
       </c>
       <c r="F36" t="n">
-        <v>-2.04</v>
+        <v>-0.22</v>
       </c>
       <c r="G36" t="n">
-        <v>9.119999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.22</v>
+        <v>-0.11</v>
       </c>
       <c r="J36" t="n">
-        <v>9.109999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.11</v>
+        <v>-0.66</v>
       </c>
       <c r="M36" t="n">
-        <v>9.109999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.11</v>
+        <v>-0.66</v>
       </c>
       <c r="P36" t="n">
-        <v>9.109999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.11</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>397</v>
+        <v>392.6</v>
       </c>
       <c r="E37" t="n">
-        <v>-3.4</v>
+        <v>-4.4</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.85</v>
+        <v>-1.11</v>
       </c>
       <c r="G37" t="n">
-        <v>392.6</v>
+        <v>397.4</v>
       </c>
       <c r="H37" t="n">
-        <v>-4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.11</v>
+        <v>1.22</v>
       </c>
       <c r="J37" t="n">
-        <v>397.4</v>
+        <v>393.8</v>
       </c>
       <c r="K37" t="n">
-        <v>4.8</v>
+        <v>-3.6</v>
       </c>
       <c r="L37" t="n">
-        <v>1.22</v>
+        <v>-0.91</v>
       </c>
       <c r="M37" t="n">
-        <v>393.8</v>
+        <v>395.6</v>
       </c>
       <c r="N37" t="n">
-        <v>-3.6</v>
+        <v>1.8</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.91</v>
+        <v>0.46</v>
       </c>
       <c r="P37" t="n">
-        <v>393.8</v>
+        <v>395.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>-3.6</v>
+        <v>1.8</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.91</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.38</v>
+        <v>13.36</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.41</v>
+        <v>-0.02</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.97</v>
+        <v>-0.15</v>
       </c>
       <c r="G38" t="n">
-        <v>13.36</v>
+        <v>13</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.02</v>
+        <v>-0.36</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.15</v>
+        <v>-2.69</v>
       </c>
       <c r="J38" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.36</v>
+        <v>-0.2</v>
       </c>
       <c r="L38" t="n">
-        <v>-2.69</v>
+        <v>-1.54</v>
       </c>
       <c r="M38" t="n">
-        <v>12.8</v>
+        <v>12.08</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.2</v>
+        <v>-0.72</v>
       </c>
       <c r="O38" t="n">
-        <v>-1.54</v>
+        <v>-5.62</v>
       </c>
       <c r="P38" t="n">
-        <v>12.8</v>
+        <v>12.08</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.2</v>
+        <v>-0.72</v>
       </c>
       <c r="R38" t="n">
-        <v>-1.54</v>
+        <v>-5.62</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>561.5</v>
+        <v>547.5</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.5</v>
+        <v>-14</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.09</v>
+        <v>-2.49</v>
       </c>
       <c r="G39" t="n">
-        <v>547.5</v>
+        <v>549</v>
       </c>
       <c r="H39" t="n">
-        <v>-14</v>
+        <v>1.5</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.49</v>
+        <v>0.27</v>
       </c>
       <c r="J39" t="n">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="K39" t="n">
-        <v>1.5</v>
+        <v>-33</v>
       </c>
       <c r="L39" t="n">
-        <v>0.27</v>
+        <v>-6.01</v>
       </c>
       <c r="M39" t="n">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="N39" t="n">
-        <v>-33</v>
+        <v>-15</v>
       </c>
       <c r="O39" t="n">
-        <v>-6.01</v>
+        <v>-2.91</v>
       </c>
       <c r="P39" t="n">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="Q39" t="n">
-        <v>-33</v>
+        <v>-15</v>
       </c>
       <c r="R39" t="n">
-        <v>-6.01</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>41.6</v>
+        <v>41.34</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.7</v>
+        <v>-0.26</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.65</v>
+        <v>-0.62</v>
       </c>
       <c r="G40" t="n">
-        <v>41.34</v>
+        <v>42.02</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.26</v>
+        <v>0.68</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.62</v>
+        <v>1.64</v>
       </c>
       <c r="J40" t="n">
-        <v>42.02</v>
+        <v>40.38</v>
       </c>
       <c r="K40" t="n">
-        <v>0.68</v>
+        <v>-1.64</v>
       </c>
       <c r="L40" t="n">
-        <v>1.64</v>
+        <v>-3.9</v>
       </c>
       <c r="M40" t="n">
-        <v>40.38</v>
+        <v>40.42</v>
       </c>
       <c r="N40" t="n">
-        <v>-1.64</v>
+        <v>0.04</v>
       </c>
       <c r="O40" t="n">
-        <v>-3.9</v>
+        <v>0.1</v>
       </c>
       <c r="P40" t="n">
-        <v>40.38</v>
+        <v>40.42</v>
       </c>
       <c r="Q40" t="n">
-        <v>-1.64</v>
+        <v>0.04</v>
       </c>
       <c r="R40" t="n">
-        <v>-3.9</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.39</v>
+        <v>31.6</v>
       </c>
       <c r="E41" t="n">
-        <v>0.04</v>
+        <v>0.21</v>
       </c>
       <c r="F41" t="n">
-        <v>0.13</v>
+        <v>0.67</v>
       </c>
       <c r="G41" t="n">
-        <v>31.6</v>
+        <v>31.85</v>
       </c>
       <c r="H41" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="I41" t="n">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="J41" t="n">
-        <v>31.85</v>
+        <v>31</v>
       </c>
       <c r="K41" t="n">
-        <v>0.25</v>
+        <v>-0.85</v>
       </c>
       <c r="L41" t="n">
-        <v>0.79</v>
+        <v>-2.67</v>
       </c>
       <c r="M41" t="n">
-        <v>31</v>
+        <v>31.18</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.85</v>
+        <v>0.18</v>
       </c>
       <c r="O41" t="n">
-        <v>-2.67</v>
+        <v>0.58</v>
       </c>
       <c r="P41" t="n">
-        <v>31</v>
+        <v>31.18</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.85</v>
+        <v>0.18</v>
       </c>
       <c r="R41" t="n">
-        <v>-2.67</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>76.79000000000001</v>
+        <v>77</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.71</v>
+        <v>0.21</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.92</v>
+        <v>0.27</v>
       </c>
       <c r="G42" t="n">
-        <v>77</v>
+        <v>77.66</v>
       </c>
       <c r="H42" t="n">
-        <v>0.21</v>
+        <v>0.66</v>
       </c>
       <c r="I42" t="n">
-        <v>0.27</v>
+        <v>0.86</v>
       </c>
       <c r="J42" t="n">
-        <v>77.66</v>
+        <v>76.75</v>
       </c>
       <c r="K42" t="n">
-        <v>0.66</v>
+        <v>-0.91</v>
       </c>
       <c r="L42" t="n">
-        <v>0.86</v>
+        <v>-1.17</v>
       </c>
       <c r="M42" t="n">
-        <v>76.75</v>
+        <v>76.8</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.91</v>
+        <v>0.05</v>
       </c>
       <c r="O42" t="n">
-        <v>-1.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P42" t="n">
-        <v>76.75</v>
+        <v>76.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.91</v>
+        <v>0.05</v>
       </c>
       <c r="R42" t="n">
-        <v>-1.17</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>40.99</v>
+        <v>41.26</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.19</v>
+        <v>0.27</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.46</v>
+        <v>0.66</v>
       </c>
       <c r="G43" t="n">
-        <v>41.26</v>
+        <v>42.33</v>
       </c>
       <c r="H43" t="n">
-        <v>0.27</v>
+        <v>1.07</v>
       </c>
       <c r="I43" t="n">
-        <v>0.66</v>
+        <v>2.59</v>
       </c>
       <c r="J43" t="n">
-        <v>42.33</v>
+        <v>41.33</v>
       </c>
       <c r="K43" t="n">
-        <v>1.07</v>
+        <v>-1</v>
       </c>
       <c r="L43" t="n">
-        <v>2.59</v>
+        <v>-2.36</v>
       </c>
       <c r="M43" t="n">
-        <v>41.33</v>
+        <v>41.21</v>
       </c>
       <c r="N43" t="n">
-        <v>-1</v>
+        <v>-0.12</v>
       </c>
       <c r="O43" t="n">
-        <v>-2.36</v>
+        <v>-0.29</v>
       </c>
       <c r="P43" t="n">
-        <v>41.33</v>
+        <v>41.21</v>
       </c>
       <c r="Q43" t="n">
-        <v>-1</v>
+        <v>-0.12</v>
       </c>
       <c r="R43" t="n">
-        <v>-2.36</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="44">
@@ -3122,31 +3122,31 @@
         <v>6.1</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.45</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="J44" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="K44" t="n">
         <v>-0.05</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.82</v>
+        <v>-0.83</v>
       </c>
       <c r="M44" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="N44" t="n">
         <v>-0.05</v>
@@ -3155,7 +3155,7 @@
         <v>-0.83</v>
       </c>
       <c r="P44" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="Q44" t="n">
         <v>-0.05</v>
@@ -3184,31 +3184,31 @@
         <v>2.15</v>
       </c>
       <c r="E45" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="H45" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F45" t="n">
-        <v>-0.92</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>-0.93</v>
       </c>
       <c r="J45" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.93</v>
+        <v>-0.47</v>
       </c>
       <c r="M45" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="N45" t="n">
         <v>-0.01</v>
@@ -3217,7 +3217,7 @@
         <v>-0.47</v>
       </c>
       <c r="P45" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="Q45" t="n">
         <v>-0.01</v>
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.93</v>
+        <v>3.91</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.75</v>
+        <v>-0.51</v>
       </c>
       <c r="G46" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="H46" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="N46" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I46" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="K46" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="L46" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="N46" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="O46" t="n">
-        <v>-0.26</v>
+        <v>-0.52</v>
       </c>
       <c r="P46" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.26</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.27</v>
+        <v>10.24</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.96</v>
+        <v>-0.29</v>
       </c>
       <c r="G47" t="n">
-        <v>10.24</v>
+        <v>10.22</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.29</v>
+        <v>-0.2</v>
       </c>
       <c r="J47" t="n">
-        <v>10.22</v>
+        <v>10.13</v>
       </c>
       <c r="K47" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="L47" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="M47" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="N47" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L47" t="n">
+      <c r="O47" t="n">
         <v>-0.2</v>
       </c>
-      <c r="M47" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="N47" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="O47" t="n">
-        <v>-0.88</v>
-      </c>
       <c r="P47" t="n">
-        <v>10.13</v>
+        <v>10.11</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.88</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.325</v>
+        <v>0.32</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.99</v>
+        <v>-1.54</v>
       </c>
       <c r="G48" t="n">
         <v>0.32</v>
       </c>
       <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="K48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I48" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>-1.56</v>
       </c>
       <c r="M48" t="n">
-        <v>0.315</v>
+        <v>0.31</v>
       </c>
       <c r="N48" t="n">
         <v>-0.005</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.56</v>
+        <v>-1.59</v>
       </c>
       <c r="P48" t="n">
-        <v>0.315</v>
+        <v>0.31</v>
       </c>
       <c r="Q48" t="n">
         <v>-0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>-1.56</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.52</v>
+        <v>4.5</v>
       </c>
       <c r="E49" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="H49" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F49" t="n">
-        <v>-0.88</v>
-      </c>
-      <c r="G49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="I49" t="n">
-        <v>-0.44</v>
+        <v>-0.89</v>
       </c>
       <c r="J49" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.89</v>
+        <v>-0.22</v>
       </c>
       <c r="M49" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.22</v>
+        <v>-0.67</v>
       </c>
       <c r="P49" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.22</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.89</v>
+        <v>-1.8</v>
       </c>
       <c r="G50" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.8</v>
+        <v>0.92</v>
       </c>
       <c r="J50" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K50" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L50" t="n">
-        <v>0.92</v>
+        <v>1.82</v>
       </c>
       <c r="M50" t="n">
         <v>1.12</v>
       </c>
       <c r="N50" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
         <v>1.12</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5</v>
+        <v>4.98</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.34</v>
+        <v>-0.4</v>
       </c>
       <c r="G51" t="n">
-        <v>4.98</v>
+        <v>5.11</v>
       </c>
       <c r="H51" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="K51" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I51" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="J51" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0.13</v>
-      </c>
       <c r="L51" t="n">
-        <v>2.61</v>
+        <v>-0.39</v>
       </c>
       <c r="M51" t="n">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.39</v>
+        <v>-0.79</v>
       </c>
       <c r="P51" t="n">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="R51" t="n">
-        <v>-0.39</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.47</v>
+        <v>11.43</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.33</v>
+        <v>-0.04</v>
       </c>
       <c r="F52" t="n">
-        <v>-2.8</v>
+        <v>-0.35</v>
       </c>
       <c r="G52" t="n">
-        <v>11.43</v>
+        <v>11.33</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.35</v>
+        <v>-0.87</v>
       </c>
       <c r="J52" t="n">
-        <v>11.33</v>
+        <v>11.2</v>
       </c>
       <c r="K52" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="L52" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="M52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="N52" t="n">
         <v>-0.1</v>
       </c>
-      <c r="L52" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="M52" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="N52" t="n">
-        <v>-0.13</v>
-      </c>
       <c r="O52" t="n">
-        <v>-1.15</v>
+        <v>-0.89</v>
       </c>
       <c r="P52" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="R52" t="n">
-        <v>-1.15</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.220000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.13</v>
+        <v>-0.06</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.56</v>
+        <v>-0.73</v>
       </c>
       <c r="G53" t="n">
-        <v>8.16</v>
+        <v>8.15</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.73</v>
+        <v>-0.12</v>
       </c>
       <c r="J53" t="n">
-        <v>8.15</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.12</v>
+        <v>-1.23</v>
       </c>
       <c r="M53" t="n">
-        <v>8.050000000000001</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.1</v>
+        <v>-0.02</v>
       </c>
       <c r="O53" t="n">
-        <v>-1.23</v>
+        <v>-0.25</v>
       </c>
       <c r="P53" t="n">
-        <v>8.050000000000001</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.1</v>
+        <v>-0.02</v>
       </c>
       <c r="R53" t="n">
-        <v>-1.23</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="54">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="D54" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-1.12</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="J54" t="n">
         <v>0.445</v>
       </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
+      <c r="K54" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="L54" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="M54" t="n">
         <v>0.44</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="I54" t="n">
-        <v>-1.12</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L54" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0.445</v>
       </c>
       <c r="N54" t="n">
         <v>-0.005</v>
       </c>
       <c r="O54" t="n">
-        <v>-1.11</v>
+        <v>-1.12</v>
       </c>
       <c r="P54" t="n">
-        <v>0.445</v>
+        <v>0.44</v>
       </c>
       <c r="Q54" t="n">
         <v>-0.005</v>
       </c>
       <c r="R54" t="n">
-        <v>-1.11</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="55">
@@ -3866,10 +3866,10 @@
         <v>0.41</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.2</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0.41</v>
@@ -3881,31 +3881,31 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>-4.88</v>
       </c>
       <c r="M56" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="O56" t="n">
-        <v>-4.88</v>
+        <v>2.56</v>
       </c>
       <c r="P56" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="R56" t="n">
-        <v>-4.88</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="57">
@@ -3928,46 +3928,46 @@
         <v>3.71</v>
       </c>
       <c r="E57" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K57" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F57" t="n">
+      <c r="L57" t="n">
         <v>-0.54</v>
       </c>
-      <c r="G57" t="n">
+      <c r="M57" t="n">
         <v>3.71</v>
       </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="K57" t="n">
+      <c r="N57" t="n">
         <v>0.01</v>
       </c>
-      <c r="L57" t="n">
+      <c r="O57" t="n">
         <v>0.27</v>
       </c>
-      <c r="M57" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N57" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O57" t="n">
-        <v>-0.54</v>
-      </c>
       <c r="P57" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="R57" t="n">
-        <v>-0.54</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="G58" t="n">
         <v>0.076</v>
       </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.077</v>
-      </c>
       <c r="H58" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="I58" t="n">
-        <v>1.32</v>
+        <v>-1.3</v>
       </c>
       <c r="J58" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="K58" t="n">
         <v>-0.001</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.3</v>
+        <v>-1.32</v>
       </c>
       <c r="M58" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="N58" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P58" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="R58" t="n">
-        <v>-1.32</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>24.68</v>
+        <v>24.3</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.1</v>
+        <v>-0.38</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.4</v>
+        <v>-1.54</v>
       </c>
       <c r="G59" t="n">
-        <v>24.3</v>
+        <v>22.91</v>
       </c>
       <c r="H59" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="I59" t="n">
+        <v>-5.72</v>
+      </c>
+      <c r="J59" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="K59" t="n">
         <v>-0.38</v>
       </c>
-      <c r="I59" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="J59" t="n">
-        <v>22.91</v>
-      </c>
-      <c r="K59" t="n">
-        <v>-1.39</v>
-      </c>
       <c r="L59" t="n">
-        <v>-5.72</v>
+        <v>-1.66</v>
       </c>
       <c r="M59" t="n">
-        <v>22.53</v>
+        <v>22.38</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="O59" t="n">
-        <v>-1.66</v>
+        <v>-0.67</v>
       </c>
       <c r="P59" t="n">
-        <v>22.53</v>
+        <v>22.38</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="R59" t="n">
-        <v>-1.66</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="60">
@@ -4114,31 +4114,31 @@
         <v>3.11</v>
       </c>
       <c r="E60" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="H60" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F60" t="n">
+      <c r="I60" t="n">
         <v>-0.32</v>
       </c>
-      <c r="G60" t="n">
+      <c r="J60" t="n">
         <v>3.11</v>
       </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3.1</v>
-      </c>
       <c r="K60" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.32</v>
+        <v>0.32</v>
       </c>
       <c r="M60" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="N60" t="n">
         <v>0.01</v>
@@ -4147,7 +4147,7 @@
         <v>0.32</v>
       </c>
       <c r="P60" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="Q60" t="n">
         <v>0.01</v>
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.93</v>
+        <v>0.915</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.005</v>
+        <v>-0.015</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.53</v>
+        <v>-1.61</v>
       </c>
       <c r="G61" t="n">
-        <v>0.915</v>
+        <v>0.885</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.015</v>
+        <v>-0.03</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.61</v>
+        <v>-3.28</v>
       </c>
       <c r="J61" t="n">
-        <v>0.885</v>
+        <v>0.875</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="L61" t="n">
-        <v>-3.28</v>
+        <v>-1.13</v>
       </c>
       <c r="M61" t="n">
-        <v>0.875</v>
+        <v>0.89</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.01</v>
+        <v>0.015</v>
       </c>
       <c r="O61" t="n">
-        <v>-1.13</v>
+        <v>1.71</v>
       </c>
       <c r="P61" t="n">
-        <v>0.875</v>
+        <v>0.89</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.01</v>
+        <v>0.015</v>
       </c>
       <c r="R61" t="n">
-        <v>-1.13</v>
+        <v>1.71</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-11 Close</t>
+          <t>2026-09-14 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-09-11 Change</t>
+          <t>2026-09-14 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-11 Change %</t>
+          <t>2026-09-14 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-09-14 Close</t>
+          <t>2026-09-15 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-09-14 Change</t>
+          <t>2026-09-15 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-09-14 Change %</t>
+          <t>2026-09-15 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-09-15 Close</t>
+          <t>2026-09-16 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-09-15 Change</t>
+          <t>2026-09-16 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-09-15 Change %</t>
+          <t>2026-09-16 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-09-16 Close</t>
+          <t>2026-09-17 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-09-16 Change</t>
+          <t>2026-09-17 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-09-16 Change %</t>
+          <t>2026-09-17 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-09-17 Close</t>
+          <t>2026-09-18 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-09-17 Change</t>
+          <t>2026-09-18 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-09-17 Change %</t>
+          <t>2026-09-18 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>163.3</v>
+        <v>164.9</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.4</v>
+        <v>1.6</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.85</v>
+        <v>0.98</v>
       </c>
       <c r="G3" t="n">
-        <v>164.9</v>
+        <v>159.6</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6</v>
+        <v>-5.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.98</v>
+        <v>-3.21</v>
       </c>
       <c r="J3" t="n">
-        <v>159.6</v>
+        <v>160.9</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.3</v>
+        <v>1.3</v>
       </c>
       <c r="L3" t="n">
-        <v>-3.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>160.9</v>
+        <v>159.8</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>-1.1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.68</v>
       </c>
       <c r="P3" t="n">
-        <v>160.9</v>
+        <v>161.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.13</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>241.8</v>
+        <v>246.6</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="G4" t="n">
-        <v>246.6</v>
+        <v>238</v>
       </c>
       <c r="H4" t="n">
-        <v>4.8</v>
+        <v>-8.6</v>
       </c>
       <c r="I4" t="n">
-        <v>1.99</v>
+        <v>-3.49</v>
       </c>
       <c r="J4" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="K4" t="n">
-        <v>-8.6</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.49</v>
+        <v>2.52</v>
       </c>
       <c r="M4" t="n">
-        <v>244</v>
+        <v>243.4</v>
       </c>
       <c r="N4" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="O4" t="n">
-        <v>2.52</v>
+        <v>-0.25</v>
       </c>
       <c r="P4" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="Q4" t="n">
-        <v>6</v>
+        <v>1.6</v>
       </c>
       <c r="R4" t="n">
-        <v>2.52</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="J5" t="n">
         <v>6.36</v>
       </c>
-      <c r="E5" t="n">
+      <c r="K5" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="M5" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="O5" t="n">
+        <v>-0.63</v>
+      </c>
+      <c r="P5" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="Q5" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F5" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="G5" t="n">
-        <v>6.41</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="J5" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-1.56</v>
-      </c>
-      <c r="M5" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="O5" t="n">
-        <v>0.79</v>
-      </c>
-      <c r="P5" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>0.05</v>
-      </c>
       <c r="R5" t="n">
-        <v>0.79</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.61</v>
+        <v>7.65</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="G6" t="n">
-        <v>7.65</v>
+        <v>7.49</v>
       </c>
       <c r="H6" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="K6" t="n">
         <v>0.04</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
         <v>0.53</v>
       </c>
-      <c r="J6" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="K6" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="L6" t="n">
-        <v>-2.09</v>
-      </c>
       <c r="M6" t="n">
-        <v>7.53</v>
+        <v>7.52</v>
       </c>
       <c r="N6" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="O6" t="n">
-        <v>0.53</v>
+        <v>-0.13</v>
       </c>
       <c r="P6" t="n">
-        <v>7.53</v>
+        <v>7.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="R6" t="n">
-        <v>0.53</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.05</v>
+        <v>6.09</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="F7" t="n">
-        <v>1.34</v>
+        <v>0.66</v>
       </c>
       <c r="G7" t="n">
-        <v>6.09</v>
+        <v>5.95</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04</v>
+        <v>-0.14</v>
       </c>
       <c r="I7" t="n">
-        <v>0.66</v>
+        <v>-2.3</v>
       </c>
       <c r="J7" t="n">
-        <v>5.95</v>
+        <v>5.98</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.3</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
-        <v>5.98</v>
+        <v>5.99</v>
       </c>
       <c r="N7" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="P7" t="n">
-        <v>5.98</v>
+        <v>5.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.75</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02</v>
+        <v>0.14</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2</v>
+        <v>1.44</v>
       </c>
       <c r="G8" t="n">
-        <v>9.890000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.14</v>
+        <v>-0.28</v>
       </c>
       <c r="I8" t="n">
-        <v>1.44</v>
+        <v>-2.83</v>
       </c>
       <c r="J8" t="n">
-        <v>9.609999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.28</v>
+        <v>0.03</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.83</v>
+        <v>0.31</v>
       </c>
       <c r="M8" t="n">
-        <v>9.640000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="O8" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="P8" t="n">
-        <v>9.640000000000001</v>
+        <v>9.59</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="R8" t="n">
-        <v>0.31</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.09</v>
+        <v>8.16</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>0.37</v>
+        <v>0.87</v>
       </c>
       <c r="G9" t="n">
-        <v>8.16</v>
+        <v>8.02</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="I9" t="n">
-        <v>0.87</v>
+        <v>-1.72</v>
       </c>
       <c r="J9" t="n">
-        <v>8.02</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.14</v>
+        <v>0.1</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.72</v>
+        <v>1.25</v>
       </c>
       <c r="M9" t="n">
-        <v>8.119999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="O9" t="n">
-        <v>1.25</v>
+        <v>0.74</v>
       </c>
       <c r="P9" t="n">
-        <v>8.119999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51.95</v>
+        <v>52.75</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2</v>
+        <v>0.8</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.38</v>
+        <v>1.54</v>
       </c>
       <c r="G10" t="n">
-        <v>52.75</v>
+        <v>51.2</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8</v>
+        <v>-1.55</v>
       </c>
       <c r="I10" t="n">
-        <v>1.54</v>
+        <v>-2.94</v>
       </c>
       <c r="J10" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M10" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P10" t="n">
         <v>51.2</v>
       </c>
-      <c r="K10" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-2.94</v>
-      </c>
-      <c r="M10" t="n">
-        <v>51.35</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="P10" t="n">
-        <v>51.35</v>
-      </c>
       <c r="Q10" t="n">
-        <v>0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.29</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.78</v>
+        <v>4.74</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.24</v>
+        <v>-0.84</v>
       </c>
       <c r="G11" t="n">
-        <v>4.74</v>
+        <v>4.63</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.04</v>
+        <v>-0.11</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.84</v>
+        <v>-2.32</v>
       </c>
       <c r="J11" t="n">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.11</v>
+        <v>-0.02</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.32</v>
+        <v>-0.43</v>
       </c>
       <c r="M11" t="n">
-        <v>4.61</v>
+        <v>4.51</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.43</v>
+        <v>-2.17</v>
       </c>
       <c r="P11" t="n">
-        <v>4.61</v>
+        <v>4.51</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="G12" t="n">
         <v>9.98</v>
       </c>
-      <c r="E12" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="F12" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="G12" t="n">
-        <v>9.92</v>
-      </c>
       <c r="H12" t="n">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.6</v>
+        <v>0.6</v>
       </c>
       <c r="J12" t="n">
-        <v>9.98</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06</v>
+        <v>-0.19</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6</v>
+        <v>-1.9</v>
       </c>
       <c r="M12" t="n">
-        <v>9.789999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.19</v>
+        <v>-0.23</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.9</v>
+        <v>-2.35</v>
       </c>
       <c r="P12" t="n">
-        <v>9.789999999999999</v>
+        <v>9.49</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.19</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>-1.9</v>
+        <v>-0.73</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24.38</v>
+        <v>24.46</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.64</v>
+        <v>0.08</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.56</v>
+        <v>0.33</v>
       </c>
       <c r="G13" t="n">
-        <v>24.46</v>
+        <v>24.48</v>
       </c>
       <c r="H13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.08</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.33</v>
-      </c>
       <c r="J13" t="n">
-        <v>24.48</v>
+        <v>24.36</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02</v>
+        <v>-0.12</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08</v>
+        <v>-0.49</v>
       </c>
       <c r="M13" t="n">
-        <v>24.36</v>
+        <v>23.88</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.12</v>
+        <v>-0.48</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.49</v>
+        <v>-1.97</v>
       </c>
       <c r="P13" t="n">
-        <v>24.36</v>
+        <v>23.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.12</v>
+        <v>-0.28</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.49</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="14">
@@ -1259,43 +1259,43 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.98</v>
+        <v>-1.01</v>
       </c>
       <c r="G14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.01</v>
+        <v>-0.51</v>
       </c>
       <c r="J14" t="n">
         <v>1.95</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="P14" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.29</v>
+        <v>5.24</v>
       </c>
       <c r="E15" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.95</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-1.16</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="P15" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="Q15" t="n">
         <v>0.06</v>
       </c>
-      <c r="F15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5.24</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="P15" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-0.06</v>
-      </c>
       <c r="R15" t="n">
-        <v>-1.16</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="16">
@@ -1383,25 +1383,25 @@
         </is>
       </c>
       <c r="D16" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J16" t="n">
         <v>4.44</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="G16" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.43</v>
       </c>
       <c r="K16" t="n">
         <v>0.01</v>
@@ -1410,7 +1410,7 @@
         <v>0.23</v>
       </c>
       <c r="M16" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="N16" t="n">
         <v>0.01</v>
@@ -1419,13 +1419,13 @@
         <v>0.23</v>
       </c>
       <c r="P16" t="n">
-        <v>4.44</v>
+        <v>4.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="R16" t="n">
-        <v>0.23</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="M17" t="n">
         <v>3.33</v>
       </c>
-      <c r="E17" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="F17" t="n">
-        <v>-2.35</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="K17" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="L17" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.35</v>
-      </c>
       <c r="N17" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="O17" t="n">
-        <v>0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="P17" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="18">
@@ -1507,16 +1507,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.96</v>
+        <v>-0.32</v>
       </c>
       <c r="G18" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="H18" t="n">
         <v>-0.01</v>
@@ -1528,28 +1528,28 @@
         <v>3.09</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>-2.27</v>
       </c>
       <c r="P18" t="n">
-        <v>3.09</v>
+        <v>2.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>54</v>
+        <v>53.6</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.85</v>
+        <v>-0.4</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.55</v>
+        <v>-0.74</v>
       </c>
       <c r="G19" t="n">
-        <v>53.6</v>
+        <v>53.05</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4</v>
+        <v>-0.55</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.74</v>
+        <v>-1.03</v>
       </c>
       <c r="J19" t="n">
-        <v>53.05</v>
+        <v>52.8</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.55</v>
+        <v>-0.25</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.03</v>
+        <v>-0.47</v>
       </c>
       <c r="M19" t="n">
-        <v>52.8</v>
+        <v>52.85</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.25</v>
+        <v>0.05</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.47</v>
+        <v>0.09</v>
       </c>
       <c r="P19" t="n">
-        <v>52.8</v>
+        <v>53.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.25</v>
+        <v>0.35</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.47</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.6</v>
+        <v>29.8</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.54</v>
+        <v>0.2</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.79</v>
+        <v>0.68</v>
       </c>
       <c r="G20" t="n">
-        <v>29.8</v>
+        <v>28.96</v>
       </c>
       <c r="H20" t="n">
-        <v>0.2</v>
+        <v>-0.84</v>
       </c>
       <c r="I20" t="n">
-        <v>0.68</v>
+        <v>-2.82</v>
       </c>
       <c r="J20" t="n">
-        <v>28.96</v>
+        <v>28.54</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.84</v>
+        <v>-0.42</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.82</v>
+        <v>-1.45</v>
       </c>
       <c r="M20" t="n">
-        <v>28.54</v>
+        <v>28.64</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.42</v>
+        <v>0.1</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.45</v>
+        <v>0.35</v>
       </c>
       <c r="P20" t="n">
-        <v>28.54</v>
+        <v>29.38</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.42</v>
+        <v>0.74</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.45</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.52</v>
+        <v>4.59</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.95</v>
+        <v>1.55</v>
       </c>
       <c r="G21" t="n">
-        <v>4.59</v>
+        <v>4.49</v>
       </c>
       <c r="H21" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="I21" t="n">
-        <v>1.55</v>
+        <v>-2.18</v>
       </c>
       <c r="J21" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M21" t="n">
         <v>4.49</v>
       </c>
-      <c r="K21" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4.53</v>
-      </c>
       <c r="N21" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="O21" t="n">
-        <v>0.89</v>
+        <v>-0.88</v>
       </c>
       <c r="P21" t="n">
-        <v>4.53</v>
+        <v>4.43</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="R21" t="n">
-        <v>0.89</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>78.90000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="E22" t="n">
-        <v>0.05</v>
+        <v>0.3</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06</v>
+        <v>0.38</v>
       </c>
       <c r="G22" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="J22" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M22" t="n">
         <v>79.2</v>
       </c>
-      <c r="H22" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="J22" t="n">
+      <c r="N22" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="O22" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="P22" t="n">
         <v>79.05</v>
       </c>
-      <c r="K22" t="n">
+      <c r="Q22" t="n">
         <v>-0.15</v>
       </c>
-      <c r="L22" t="n">
+      <c r="R22" t="n">
         <v>-0.19</v>
-      </c>
-      <c r="M22" t="n">
-        <v>79.34999999999999</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="P22" t="n">
-        <v>79.34999999999999</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0.38</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22.98</v>
+        <v>22.6</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>-0.38</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>-1.65</v>
       </c>
       <c r="G23" t="n">
-        <v>22.6</v>
+        <v>22.46</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.38</v>
+        <v>-0.14</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.65</v>
+        <v>-0.62</v>
       </c>
       <c r="J23" t="n">
-        <v>22.46</v>
+        <v>22.62</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.14</v>
+        <v>0.16</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.62</v>
+        <v>0.71</v>
       </c>
       <c r="M23" t="n">
-        <v>22.62</v>
+        <v>22.44</v>
       </c>
       <c r="N23" t="n">
-        <v>0.16</v>
+        <v>-0.18</v>
       </c>
       <c r="O23" t="n">
-        <v>0.71</v>
+        <v>-0.8</v>
       </c>
       <c r="P23" t="n">
-        <v>22.62</v>
+        <v>22.84</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.16</v>
+        <v>0.4</v>
       </c>
       <c r="R23" t="n">
-        <v>0.71</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.41</v>
+        <v>16.24</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.33</v>
+        <v>-0.17</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.97</v>
+        <v>-1.04</v>
       </c>
       <c r="G24" t="n">
-        <v>16.24</v>
+        <v>15.88</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.17</v>
+        <v>-0.36</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.04</v>
+        <v>-2.22</v>
       </c>
       <c r="J24" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="M24" t="n">
         <v>15.88</v>
       </c>
-      <c r="K24" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="L24" t="n">
-        <v>-2.22</v>
-      </c>
-      <c r="M24" t="n">
-        <v>15.95</v>
-      </c>
       <c r="N24" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>0.44</v>
+        <v>-0.44</v>
       </c>
       <c r="P24" t="n">
-        <v>15.95</v>
+        <v>16.42</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="R24" t="n">
-        <v>0.44</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.36</v>
+        <v>27.16</v>
       </c>
       <c r="E25" t="n">
-        <v>0.44</v>
+        <v>0.8</v>
       </c>
       <c r="F25" t="n">
-        <v>1.7</v>
+        <v>3.03</v>
       </c>
       <c r="G25" t="n">
-        <v>27.16</v>
+        <v>26.5</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8</v>
+        <v>-0.66</v>
       </c>
       <c r="I25" t="n">
-        <v>3.03</v>
+        <v>-2.43</v>
       </c>
       <c r="J25" t="n">
-        <v>26.5</v>
+        <v>26.18</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.66</v>
+        <v>-0.32</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.43</v>
+        <v>-1.21</v>
       </c>
       <c r="M25" t="n">
-        <v>26.18</v>
+        <v>26.14</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.32</v>
+        <v>-0.04</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.21</v>
+        <v>-0.15</v>
       </c>
       <c r="P25" t="n">
-        <v>26.18</v>
+        <v>26.4</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.32</v>
+        <v>0.26</v>
       </c>
       <c r="R25" t="n">
-        <v>-1.21</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>35.46</v>
+        <v>33.1</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.02</v>
+        <v>-2.36</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.39</v>
+        <v>-6.66</v>
       </c>
       <c r="G26" t="n">
-        <v>33.1</v>
+        <v>32.06</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.36</v>
+        <v>-1.04</v>
       </c>
       <c r="I26" t="n">
-        <v>-6.66</v>
+        <v>-3.14</v>
       </c>
       <c r="J26" t="n">
-        <v>32.06</v>
+        <v>32.88</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.04</v>
+        <v>0.82</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.14</v>
+        <v>2.56</v>
       </c>
       <c r="M26" t="n">
-        <v>32.88</v>
+        <v>33.86</v>
       </c>
       <c r="N26" t="n">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="O26" t="n">
-        <v>2.56</v>
+        <v>2.98</v>
       </c>
       <c r="P26" t="n">
-        <v>32.88</v>
+        <v>37.94</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.82</v>
+        <v>4.08</v>
       </c>
       <c r="R26" t="n">
-        <v>2.56</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>428.4</v>
+        <v>430.6</v>
       </c>
       <c r="E27" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="F27" t="n">
-        <v>0.66</v>
+        <v>0.51</v>
       </c>
       <c r="G27" t="n">
-        <v>430.6</v>
+        <v>438.8</v>
       </c>
       <c r="H27" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>0.51</v>
+        <v>1.9</v>
       </c>
       <c r="J27" t="n">
-        <v>438.8</v>
+        <v>433.4</v>
       </c>
       <c r="K27" t="n">
-        <v>8.199999999999999</v>
+        <v>-5.4</v>
       </c>
       <c r="L27" t="n">
-        <v>1.9</v>
+        <v>-1.23</v>
       </c>
       <c r="M27" t="n">
-        <v>433.4</v>
+        <v>426</v>
       </c>
       <c r="N27" t="n">
-        <v>-5.4</v>
+        <v>-7.4</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.23</v>
+        <v>-1.71</v>
       </c>
       <c r="P27" t="n">
-        <v>433.4</v>
+        <v>419</v>
       </c>
       <c r="Q27" t="n">
-        <v>-5.4</v>
+        <v>-7</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.23</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>107.5</v>
+        <v>105.9</v>
       </c>
       <c r="E28" t="n">
-        <v>0.6</v>
+        <v>-1.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.49</v>
       </c>
       <c r="G28" t="n">
-        <v>105.9</v>
+        <v>107.2</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.6</v>
+        <v>1.3</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.49</v>
+        <v>1.23</v>
       </c>
       <c r="J28" t="n">
-        <v>107.2</v>
+        <v>106.2</v>
       </c>
       <c r="K28" t="n">
-        <v>1.3</v>
+        <v>-1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.23</v>
+        <v>-0.93</v>
       </c>
       <c r="M28" t="n">
-        <v>106.2</v>
+        <v>105.1</v>
       </c>
       <c r="N28" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.93</v>
+        <v>-1.04</v>
       </c>
       <c r="P28" t="n">
-        <v>106.2</v>
+        <v>109.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1</v>
+        <v>4.2</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.93</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>106.2</v>
+        <v>106</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7</v>
+        <v>-0.2</v>
       </c>
       <c r="F29" t="n">
-        <v>0.66</v>
+        <v>-0.19</v>
       </c>
       <c r="G29" t="n">
-        <v>106</v>
+        <v>106.3</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.19</v>
+        <v>0.28</v>
       </c>
       <c r="J29" t="n">
-        <v>106.3</v>
+        <v>105.9</v>
       </c>
       <c r="K29" t="n">
-        <v>0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="L29" t="n">
-        <v>0.28</v>
+        <v>-0.38</v>
       </c>
       <c r="M29" t="n">
-        <v>105.9</v>
+        <v>105</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.38</v>
+        <v>-0.85</v>
       </c>
       <c r="P29" t="n">
-        <v>105.9</v>
+        <v>105</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2251,25 +2251,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>75.09999999999999</v>
+        <v>75.05</v>
       </c>
       <c r="E30" t="n">
-        <v>0.35</v>
+        <v>-0.05</v>
       </c>
       <c r="F30" t="n">
-        <v>0.47</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G30" t="n">
-        <v>75.05</v>
+        <v>74.75</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.05</v>
+        <v>-0.3</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.4</v>
       </c>
       <c r="J30" t="n">
-        <v>74.75</v>
+        <v>74.45</v>
       </c>
       <c r="K30" t="n">
         <v>-0.3</v>
@@ -2278,22 +2278,22 @@
         <v>-0.4</v>
       </c>
       <c r="M30" t="n">
-        <v>74.45</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.3</v>
+        <v>-1.55</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.4</v>
+        <v>-2.08</v>
       </c>
       <c r="P30" t="n">
-        <v>74.45</v>
+        <v>73.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.4</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>89.09999999999999</v>
+        <v>89.3</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.05</v>
+        <v>0.2</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.06</v>
+        <v>0.22</v>
       </c>
       <c r="G31" t="n">
-        <v>89.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="I31" t="n">
-        <v>0.22</v>
+        <v>-0.45</v>
       </c>
       <c r="J31" t="n">
-        <v>88.90000000000001</v>
+        <v>88.05</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.4</v>
+        <v>-0.85</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.45</v>
+        <v>-0.96</v>
       </c>
       <c r="M31" t="n">
-        <v>88.05</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.85</v>
+        <v>-0.7</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.96</v>
+        <v>-0.8</v>
       </c>
       <c r="P31" t="n">
-        <v>88.05</v>
+        <v>87.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.85</v>
+        <v>-0.15</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.96</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>63.15</v>
+        <v>61.3</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3</v>
+        <v>-1.85</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.47</v>
+        <v>-2.93</v>
       </c>
       <c r="G32" t="n">
-        <v>61.3</v>
+        <v>60.75</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.85</v>
+        <v>-0.55</v>
       </c>
       <c r="I32" t="n">
-        <v>-2.93</v>
+        <v>-0.9</v>
       </c>
       <c r="J32" t="n">
-        <v>60.75</v>
+        <v>63.65</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.55</v>
+        <v>2.9</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.9</v>
+        <v>4.77</v>
       </c>
       <c r="M32" t="n">
-        <v>63.65</v>
+        <v>62.4</v>
       </c>
       <c r="N32" t="n">
-        <v>2.9</v>
+        <v>-1.25</v>
       </c>
       <c r="O32" t="n">
-        <v>4.77</v>
+        <v>-1.96</v>
       </c>
       <c r="P32" t="n">
-        <v>63.65</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
       <c r="R32" t="n">
-        <v>4.77</v>
+        <v>4.41</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>79.84999999999999</v>
+        <v>80.2</v>
       </c>
       <c r="E33" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="F33" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="G33" t="n">
-        <v>80.2</v>
+        <v>79.05</v>
       </c>
       <c r="H33" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="J33" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M33" t="n">
+        <v>81.15000000000001</v>
+      </c>
+      <c r="N33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="P33" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="Q33" t="n">
         <v>0.35</v>
       </c>
-      <c r="I33" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="J33" t="n">
-        <v>79.05</v>
-      </c>
-      <c r="K33" t="n">
-        <v>-1.15</v>
-      </c>
-      <c r="L33" t="n">
-        <v>-1.43</v>
-      </c>
-      <c r="M33" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="P33" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0.15</v>
-      </c>
       <c r="R33" t="n">
-        <v>0.19</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>31.26</v>
+        <v>30.58</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.4</v>
+        <v>-0.68</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.26</v>
+        <v>-2.18</v>
       </c>
       <c r="G34" t="n">
-        <v>30.58</v>
+        <v>29.8</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.68</v>
+        <v>-0.78</v>
       </c>
       <c r="I34" t="n">
-        <v>-2.18</v>
+        <v>-2.55</v>
       </c>
       <c r="J34" t="n">
-        <v>29.8</v>
+        <v>29.66</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.78</v>
+        <v>-0.14</v>
       </c>
       <c r="L34" t="n">
-        <v>-2.55</v>
+        <v>-0.47</v>
       </c>
       <c r="M34" t="n">
-        <v>29.66</v>
+        <v>29.94</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.14</v>
+        <v>0.28</v>
       </c>
       <c r="O34" t="n">
-        <v>-0.47</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P34" t="n">
-        <v>29.66</v>
+        <v>30.74</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.14</v>
+        <v>0.8</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.47</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="35">
@@ -2564,46 +2564,46 @@
         <v>4.24</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.24</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="H35" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="J35" t="n">
         <v>4.24</v>
       </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>4.21</v>
-      </c>
       <c r="K35" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.71</v>
+        <v>0.71</v>
       </c>
       <c r="M35" t="n">
-        <v>4.21</v>
+        <v>4.24</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.71</v>
+        <v>0.71</v>
       </c>
       <c r="P35" t="n">
-        <v>4.21</v>
+        <v>4.32</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.71</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.119999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.22</v>
+        <v>-0.11</v>
       </c>
       <c r="G36" t="n">
-        <v>9.109999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.11</v>
+        <v>-0.66</v>
       </c>
       <c r="J36" t="n">
-        <v>9.050000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.66</v>
+        <v>0.99</v>
       </c>
       <c r="M36" t="n">
-        <v>9.050000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.66</v>
+        <v>0.99</v>
       </c>
       <c r="P36" t="n">
-        <v>9.050000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.06</v>
+        <v>0.17</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.66</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>392.6</v>
+        <v>397.4</v>
       </c>
       <c r="E37" t="n">
-        <v>-4.4</v>
+        <v>4.8</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.11</v>
+        <v>1.22</v>
       </c>
       <c r="G37" t="n">
-        <v>397.4</v>
+        <v>393.8</v>
       </c>
       <c r="H37" t="n">
-        <v>4.8</v>
+        <v>-3.6</v>
       </c>
       <c r="I37" t="n">
-        <v>1.22</v>
+        <v>-0.91</v>
       </c>
       <c r="J37" t="n">
-        <v>393.8</v>
+        <v>395.6</v>
       </c>
       <c r="K37" t="n">
-        <v>-3.6</v>
+        <v>1.8</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.91</v>
+        <v>0.46</v>
       </c>
       <c r="M37" t="n">
-        <v>395.6</v>
+        <v>388.6</v>
       </c>
       <c r="N37" t="n">
-        <v>1.8</v>
+        <v>-7</v>
       </c>
       <c r="O37" t="n">
-        <v>0.46</v>
+        <v>-1.77</v>
       </c>
       <c r="P37" t="n">
-        <v>395.6</v>
+        <v>388</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.8</v>
+        <v>-0.6</v>
       </c>
       <c r="R37" t="n">
-        <v>0.46</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.36</v>
+        <v>13</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.02</v>
+        <v>-0.36</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.15</v>
+        <v>-2.69</v>
       </c>
       <c r="G38" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.36</v>
+        <v>-0.2</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.69</v>
+        <v>-1.54</v>
       </c>
       <c r="J38" t="n">
-        <v>12.8</v>
+        <v>12.08</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.2</v>
+        <v>-0.72</v>
       </c>
       <c r="L38" t="n">
-        <v>-1.54</v>
+        <v>-5.62</v>
       </c>
       <c r="M38" t="n">
-        <v>12.08</v>
+        <v>12.2</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.72</v>
+        <v>0.12</v>
       </c>
       <c r="O38" t="n">
-        <v>-5.62</v>
+        <v>0.99</v>
       </c>
       <c r="P38" t="n">
-        <v>12.08</v>
+        <v>12.24</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.72</v>
+        <v>0.04</v>
       </c>
       <c r="R38" t="n">
-        <v>-5.62</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>547.5</v>
+        <v>549</v>
       </c>
       <c r="E39" t="n">
-        <v>-14</v>
+        <v>1.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.49</v>
+        <v>0.27</v>
       </c>
       <c r="G39" t="n">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="H39" t="n">
-        <v>1.5</v>
+        <v>-33</v>
       </c>
       <c r="I39" t="n">
-        <v>0.27</v>
+        <v>-6.01</v>
       </c>
       <c r="J39" t="n">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="K39" t="n">
-        <v>-33</v>
+        <v>-15</v>
       </c>
       <c r="L39" t="n">
-        <v>-6.01</v>
+        <v>-2.91</v>
       </c>
       <c r="M39" t="n">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="N39" t="n">
-        <v>-15</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
-        <v>-2.91</v>
+        <v>1.2</v>
       </c>
       <c r="P39" t="n">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="Q39" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>-2.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>41.34</v>
+        <v>42.02</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.26</v>
+        <v>0.68</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.62</v>
+        <v>1.64</v>
       </c>
       <c r="G40" t="n">
-        <v>42.02</v>
+        <v>40.38</v>
       </c>
       <c r="H40" t="n">
-        <v>0.68</v>
+        <v>-1.64</v>
       </c>
       <c r="I40" t="n">
-        <v>1.64</v>
+        <v>-3.9</v>
       </c>
       <c r="J40" t="n">
-        <v>40.38</v>
+        <v>40.42</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.64</v>
+        <v>0.04</v>
       </c>
       <c r="L40" t="n">
-        <v>-3.9</v>
+        <v>0.1</v>
       </c>
       <c r="M40" t="n">
-        <v>40.42</v>
+        <v>41.18</v>
       </c>
       <c r="N40" t="n">
-        <v>0.04</v>
+        <v>0.76</v>
       </c>
       <c r="O40" t="n">
-        <v>0.1</v>
+        <v>1.88</v>
       </c>
       <c r="P40" t="n">
-        <v>40.42</v>
+        <v>42.04</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.04</v>
+        <v>0.86</v>
       </c>
       <c r="R40" t="n">
-        <v>0.1</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.6</v>
+        <v>31.85</v>
       </c>
       <c r="E41" t="n">
-        <v>0.21</v>
+        <v>0.25</v>
       </c>
       <c r="F41" t="n">
-        <v>0.67</v>
+        <v>0.79</v>
       </c>
       <c r="G41" t="n">
-        <v>31.85</v>
+        <v>31</v>
       </c>
       <c r="H41" t="n">
-        <v>0.25</v>
+        <v>-0.85</v>
       </c>
       <c r="I41" t="n">
-        <v>0.79</v>
+        <v>-2.67</v>
       </c>
       <c r="J41" t="n">
-        <v>31</v>
+        <v>31.18</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.85</v>
+        <v>0.18</v>
       </c>
       <c r="L41" t="n">
-        <v>-2.67</v>
+        <v>0.58</v>
       </c>
       <c r="M41" t="n">
-        <v>31.18</v>
+        <v>31.28</v>
       </c>
       <c r="N41" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="O41" t="n">
-        <v>0.58</v>
+        <v>0.32</v>
       </c>
       <c r="P41" t="n">
-        <v>31.18</v>
+        <v>31.38</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="R41" t="n">
-        <v>0.58</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>77</v>
+        <v>77.66</v>
       </c>
       <c r="E42" t="n">
-        <v>0.21</v>
+        <v>0.66</v>
       </c>
       <c r="F42" t="n">
-        <v>0.27</v>
+        <v>0.86</v>
       </c>
       <c r="G42" t="n">
-        <v>77.66</v>
+        <v>76.75</v>
       </c>
       <c r="H42" t="n">
-        <v>0.66</v>
+        <v>-0.91</v>
       </c>
       <c r="I42" t="n">
-        <v>0.86</v>
+        <v>-1.17</v>
       </c>
       <c r="J42" t="n">
-        <v>76.75</v>
+        <v>76.8</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.91</v>
+        <v>0.05</v>
       </c>
       <c r="L42" t="n">
-        <v>-1.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>76.8</v>
+        <v>76.94</v>
       </c>
       <c r="N42" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="O42" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="P42" t="n">
-        <v>76.8</v>
+        <v>76.86</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.05</v>
+        <v>-0.08</v>
       </c>
       <c r="R42" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>41.26</v>
+        <v>42.33</v>
       </c>
       <c r="E43" t="n">
-        <v>0.27</v>
+        <v>1.07</v>
       </c>
       <c r="F43" t="n">
-        <v>0.66</v>
+        <v>2.59</v>
       </c>
       <c r="G43" t="n">
-        <v>42.33</v>
+        <v>41.33</v>
       </c>
       <c r="H43" t="n">
-        <v>1.07</v>
+        <v>-1</v>
       </c>
       <c r="I43" t="n">
-        <v>2.59</v>
+        <v>-2.36</v>
       </c>
       <c r="J43" t="n">
-        <v>41.33</v>
+        <v>41.21</v>
       </c>
       <c r="K43" t="n">
-        <v>-1</v>
+        <v>-0.12</v>
       </c>
       <c r="L43" t="n">
-        <v>-2.36</v>
+        <v>-0.29</v>
       </c>
       <c r="M43" t="n">
-        <v>41.21</v>
+        <v>41.88</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.12</v>
+        <v>0.67</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.29</v>
+        <v>1.63</v>
       </c>
       <c r="P43" t="n">
-        <v>41.21</v>
+        <v>41.78</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.29</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="44">
@@ -3119,25 +3119,25 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.1</v>
+        <v>6.05</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="G44" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="H44" t="n">
         <v>-0.05</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.82</v>
+        <v>-0.83</v>
       </c>
       <c r="J44" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="K44" t="n">
         <v>-0.05</v>
@@ -3146,22 +3146,22 @@
         <v>-0.83</v>
       </c>
       <c r="M44" t="n">
-        <v>5.95</v>
+        <v>5.93</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.83</v>
+        <v>-0.34</v>
       </c>
       <c r="P44" t="n">
-        <v>5.95</v>
+        <v>5.9</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.83</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="45">
@@ -3181,25 +3181,25 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-0.93</v>
       </c>
       <c r="G45" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.93</v>
+        <v>-0.47</v>
       </c>
       <c r="J45" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="K45" t="n">
         <v>-0.01</v>
@@ -3208,16 +3208,16 @@
         <v>-0.47</v>
       </c>
       <c r="M45" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.47</v>
+        <v>0.95</v>
       </c>
       <c r="P45" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="Q45" t="n">
         <v>-0.01</v>
@@ -3243,43 +3243,43 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.91</v>
+        <v>3.87</v>
       </c>
       <c r="E46" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="K46" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F46" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="G46" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I46" t="n">
-        <v>-1.02</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.86</v>
-      </c>
-      <c r="K46" t="n">
+      <c r="L46" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="N46" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L46" t="n">
+      <c r="O46" t="n">
         <v>-0.26</v>
       </c>
-      <c r="M46" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="N46" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O46" t="n">
-        <v>-0.52</v>
-      </c>
       <c r="P46" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="Q46" t="n">
         <v>-0.02</v>
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.24</v>
+        <v>10.22</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.29</v>
+        <v>-0.2</v>
       </c>
       <c r="G47" t="n">
-        <v>10.22</v>
+        <v>10.13</v>
       </c>
       <c r="H47" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="J47" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="K47" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I47" t="n">
+      <c r="L47" t="n">
         <v>-0.2</v>
       </c>
-      <c r="J47" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="K47" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="L47" t="n">
-        <v>-0.88</v>
-      </c>
       <c r="M47" t="n">
-        <v>10.11</v>
+        <v>10.19</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.2</v>
+        <v>0.79</v>
       </c>
       <c r="P47" t="n">
-        <v>10.11</v>
+        <v>10.43</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.02</v>
+        <v>0.24</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.2</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="48">
@@ -3370,46 +3370,46 @@
         <v>0.32</v>
       </c>
       <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="H48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F48" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>-1.56</v>
       </c>
       <c r="J48" t="n">
-        <v>0.315</v>
+        <v>0.31</v>
       </c>
       <c r="K48" t="n">
         <v>-0.005</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.56</v>
+        <v>-1.59</v>
       </c>
       <c r="M48" t="n">
-        <v>0.31</v>
+        <v>0.305</v>
       </c>
       <c r="N48" t="n">
         <v>-0.005</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.59</v>
+        <v>-1.61</v>
       </c>
       <c r="P48" t="n">
         <v>0.31</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>-1.59</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.44</v>
+        <v>-0.89</v>
       </c>
       <c r="G49" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.89</v>
+        <v>-0.22</v>
       </c>
       <c r="J49" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.22</v>
+        <v>-0.67</v>
       </c>
       <c r="M49" t="n">
         <v>4.42</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.67</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>4.42</v>
+        <v>4.35</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.67</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.8</v>
+        <v>0.92</v>
       </c>
       <c r="G50" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="H50" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I50" t="n">
-        <v>0.92</v>
+        <v>1.82</v>
       </c>
       <c r="J50" t="n">
         <v>1.12</v>
       </c>
       <c r="K50" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
       <c r="P50" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4.98</v>
+        <v>5.11</v>
       </c>
       <c r="E51" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F51" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="H51" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F51" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="G51" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.13</v>
-      </c>
       <c r="I51" t="n">
-        <v>2.61</v>
+        <v>-0.39</v>
       </c>
       <c r="J51" t="n">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.39</v>
+        <v>-0.79</v>
       </c>
       <c r="M51" t="n">
-        <v>5.05</v>
+        <v>5.14</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.79</v>
+        <v>1.78</v>
       </c>
       <c r="P51" t="n">
-        <v>5.05</v>
+        <v>5.17</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="R51" t="n">
-        <v>-0.79</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.43</v>
+        <v>11.33</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.35</v>
+        <v>-0.87</v>
       </c>
       <c r="G52" t="n">
-        <v>11.33</v>
+        <v>11.2</v>
       </c>
       <c r="H52" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="J52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="K52" t="n">
         <v>-0.1</v>
       </c>
-      <c r="I52" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="J52" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="K52" t="n">
-        <v>-0.13</v>
-      </c>
       <c r="L52" t="n">
-        <v>-1.15</v>
+        <v>-0.89</v>
       </c>
       <c r="M52" t="n">
-        <v>11.1</v>
+        <v>11.12</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.89</v>
+        <v>0.18</v>
       </c>
       <c r="P52" t="n">
-        <v>11.1</v>
+        <v>11.03</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.89</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.16</v>
+        <v>8.15</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.73</v>
+        <v>-0.12</v>
       </c>
       <c r="G53" t="n">
-        <v>8.15</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.12</v>
+        <v>-1.23</v>
       </c>
       <c r="J53" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="M53" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P53" t="n">
         <v>8.050000000000001</v>
       </c>
-      <c r="K53" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="L53" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="M53" t="n">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="N53" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O53" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="P53" t="n">
-        <v>8.029999999999999</v>
-      </c>
       <c r="Q53" t="n">
-        <v>-0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.25</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="54">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="D54" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F54" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="I54" t="n">
+        <v>-1.11</v>
+      </c>
+      <c r="J54" t="n">
         <v>0.44</v>
-      </c>
-      <c r="E54" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="F54" t="n">
-        <v>-1.12</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I54" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.445</v>
       </c>
       <c r="K54" t="n">
         <v>-0.005</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.11</v>
+        <v>-1.12</v>
       </c>
       <c r="M54" t="n">
         <v>0.44</v>
       </c>
       <c r="N54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>-1.12</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
         <v>0.44</v>
       </c>
       <c r="Q54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>-1.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3828,22 +3828,22 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P55" t="n">
         <v>0.615</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3872,40 +3872,40 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="H56" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-4.88</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L56" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="N56" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="O56" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="Q56" t="n">
         <v>0</v>
       </c>
-      <c r="I56" t="n">
+      <c r="R56" t="n">
         <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="K56" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L56" t="n">
-        <v>-4.88</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O56" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="P56" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="R56" t="n">
-        <v>2.56</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="J57" t="n">
         <v>3.71</v>
       </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="H57" t="n">
+      <c r="K57" t="n">
         <v>0.01</v>
       </c>
-      <c r="I57" t="n">
+      <c r="L57" t="n">
         <v>0.27</v>
       </c>
-      <c r="J57" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="K57" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L57" t="n">
-        <v>-0.54</v>
-      </c>
       <c r="M57" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="N57" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="O57" t="n">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="P57" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="R57" t="n">
-        <v>0.27</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.077</v>
+        <v>0.076</v>
       </c>
       <c r="E58" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="F58" t="n">
-        <v>1.32</v>
+        <v>-1.3</v>
       </c>
       <c r="G58" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="H58" t="n">
         <v>-0.001</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.3</v>
+        <v>-1.32</v>
       </c>
       <c r="J58" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.32</v>
+        <v>1.33</v>
       </c>
       <c r="M58" t="n">
         <v>0.076</v>
       </c>
       <c r="N58" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
-        <v>0.076</v>
+        <v>0.074</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="R58" t="n">
-        <v>1.33</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>24.3</v>
+        <v>22.91</v>
       </c>
       <c r="E59" t="n">
+        <v>-1.39</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-5.72</v>
+      </c>
+      <c r="G59" t="n">
+        <v>22.53</v>
+      </c>
+      <c r="H59" t="n">
         <v>-0.38</v>
       </c>
-      <c r="F59" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="G59" t="n">
-        <v>22.91</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-1.39</v>
-      </c>
       <c r="I59" t="n">
-        <v>-5.72</v>
+        <v>-1.66</v>
       </c>
       <c r="J59" t="n">
-        <v>22.53</v>
+        <v>22.38</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="L59" t="n">
-        <v>-1.66</v>
+        <v>-0.67</v>
       </c>
       <c r="M59" t="n">
-        <v>22.38</v>
+        <v>22.27</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.15</v>
+        <v>-0.11</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.67</v>
+        <v>-0.49</v>
       </c>
       <c r="P59" t="n">
-        <v>22.38</v>
+        <v>22.2</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.15</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R59" t="n">
-        <v>-0.67</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="60">
@@ -4111,25 +4111,25 @@
         </is>
       </c>
       <c r="D60" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="G60" t="n">
         <v>3.11</v>
       </c>
-      <c r="E60" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" t="n">
-        <v>3.1</v>
-      </c>
       <c r="H60" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.32</v>
+        <v>0.32</v>
       </c>
       <c r="J60" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="K60" t="n">
         <v>0.01</v>
@@ -4141,19 +4141,19 @@
         <v>3.12</v>
       </c>
       <c r="N60" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="R60" t="n">
-        <v>0.32</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.915</v>
+        <v>0.885</v>
       </c>
       <c r="E61" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-3.28</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="L61" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="N61" t="n">
         <v>-0.015</v>
       </c>
-      <c r="F61" t="n">
-        <v>-1.61</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="I61" t="n">
-        <v>-3.28</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="K61" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="L61" t="n">
-        <v>-1.13</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0.015</v>
-      </c>
       <c r="O61" t="n">
-        <v>1.71</v>
+        <v>-1.69</v>
       </c>
       <c r="P61" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.015</v>
+        <v>0.005</v>
       </c>
       <c r="R61" t="n">
-        <v>1.71</v>
+        <v>0.57</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-14 Close</t>
+          <t>2026-09-15 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-09-14 Change</t>
+          <t>2026-09-15 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-14 Change %</t>
+          <t>2026-09-15 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-09-15 Close</t>
+          <t>2026-09-16 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-09-15 Change</t>
+          <t>2026-09-16 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-09-15 Change %</t>
+          <t>2026-09-16 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-09-16 Close</t>
+          <t>2026-09-17 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-09-16 Change</t>
+          <t>2026-09-17 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-09-16 Change %</t>
+          <t>2026-09-17 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-09-17 Close</t>
+          <t>2026-09-18 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-09-17 Change</t>
+          <t>2026-09-18 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-09-17 Change %</t>
+          <t>2026-09-18 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-09-18 Close</t>
+          <t>2026-09-21 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-09-18 Change</t>
+          <t>2026-09-21 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-09-18 Change %</t>
+          <t>2026-09-21 Change %</t>
         </is>
       </c>
     </row>
@@ -577,40 +577,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>164.9</v>
+        <v>159.6</v>
       </c>
       <c r="E3" t="n">
-        <v>1.6</v>
+        <v>-5.3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.98</v>
+        <v>-3.21</v>
       </c>
       <c r="G3" t="n">
-        <v>159.6</v>
+        <v>160.9</v>
       </c>
       <c r="H3" t="n">
-        <v>-5.3</v>
+        <v>1.3</v>
       </c>
       <c r="I3" t="n">
-        <v>-3.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>160.9</v>
+        <v>159.8</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3</v>
+        <v>-1.1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.68</v>
       </c>
       <c r="M3" t="n">
-        <v>159.8</v>
+        <v>161.6</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1</v>
+        <v>1.8</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.68</v>
+        <v>1.13</v>
       </c>
       <c r="P3" t="n">
         <v>161.6</v>
@@ -639,40 +639,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>246.6</v>
+        <v>238</v>
       </c>
       <c r="E4" t="n">
-        <v>4.8</v>
+        <v>-8.6</v>
       </c>
       <c r="F4" t="n">
-        <v>1.99</v>
+        <v>-3.49</v>
       </c>
       <c r="G4" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="H4" t="n">
-        <v>-8.6</v>
+        <v>6</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.49</v>
+        <v>2.52</v>
       </c>
       <c r="J4" t="n">
-        <v>244</v>
+        <v>243.4</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="L4" t="n">
-        <v>2.52</v>
+        <v>-0.25</v>
       </c>
       <c r="M4" t="n">
-        <v>243.4</v>
+        <v>245</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6</v>
+        <v>1.6</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.25</v>
+        <v>0.66</v>
       </c>
       <c r="P4" t="n">
         <v>245</v>
@@ -701,40 +701,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.41</v>
+        <v>6.31</v>
       </c>
       <c r="E5" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="G5" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="H5" t="n">
         <v>0.05</v>
       </c>
-      <c r="F5" t="n">
+      <c r="I5" t="n">
         <v>0.79</v>
       </c>
-      <c r="G5" t="n">
-        <v>6.31</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>-1.56</v>
-      </c>
       <c r="J5" t="n">
-        <v>6.36</v>
+        <v>6.32</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="L5" t="n">
-        <v>0.79</v>
+        <v>-0.63</v>
       </c>
       <c r="M5" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.63</v>
+        <v>-0.32</v>
       </c>
       <c r="P5" t="n">
         <v>6.3</v>
@@ -763,40 +763,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.65</v>
+        <v>7.49</v>
       </c>
       <c r="E6" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-2.09</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="H6" t="n">
         <v>0.04</v>
       </c>
-      <c r="F6" t="n">
+      <c r="I6" t="n">
         <v>0.53</v>
       </c>
-      <c r="G6" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="I6" t="n">
-        <v>-2.09</v>
-      </c>
       <c r="J6" t="n">
-        <v>7.53</v>
+        <v>7.52</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="L6" t="n">
-        <v>0.53</v>
+        <v>-0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>7.52</v>
+        <v>7.5</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.13</v>
+        <v>-0.27</v>
       </c>
       <c r="P6" t="n">
         <v>7.5</v>
@@ -825,40 +825,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.09</v>
+        <v>5.95</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04</v>
+        <v>-0.14</v>
       </c>
       <c r="F7" t="n">
-        <v>0.66</v>
+        <v>-2.3</v>
       </c>
       <c r="G7" t="n">
-        <v>5.95</v>
+        <v>5.98</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.3</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
-        <v>5.98</v>
+        <v>5.99</v>
       </c>
       <c r="K7" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="M7" t="n">
         <v>5.99</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>5.99</v>
@@ -887,40 +887,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.890000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>0.14</v>
+        <v>-0.28</v>
       </c>
       <c r="F8" t="n">
-        <v>1.44</v>
+        <v>-2.83</v>
       </c>
       <c r="G8" t="n">
-        <v>9.609999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.28</v>
+        <v>0.03</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.83</v>
+        <v>0.31</v>
       </c>
       <c r="J8" t="n">
-        <v>9.640000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="L8" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="M8" t="n">
-        <v>9.68</v>
+        <v>9.59</v>
       </c>
       <c r="N8" t="n">
-        <v>0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="O8" t="n">
-        <v>0.41</v>
+        <v>-0.93</v>
       </c>
       <c r="P8" t="n">
         <v>9.59</v>
@@ -949,40 +949,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.16</v>
+        <v>8.02</v>
       </c>
       <c r="E9" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="F9" t="n">
-        <v>0.87</v>
+        <v>-1.72</v>
       </c>
       <c r="G9" t="n">
-        <v>8.02</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.14</v>
+        <v>0.1</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.72</v>
+        <v>1.25</v>
       </c>
       <c r="J9" t="n">
-        <v>8.119999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="L9" t="n">
-        <v>1.25</v>
+        <v>0.74</v>
       </c>
       <c r="M9" t="n">
-        <v>8.18</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="O9" t="n">
-        <v>0.74</v>
+        <v>-0.49</v>
       </c>
       <c r="P9" t="n">
         <v>8.140000000000001</v>
@@ -1011,40 +1011,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>52.75</v>
+        <v>51.2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8</v>
+        <v>-1.55</v>
       </c>
       <c r="F10" t="n">
-        <v>1.54</v>
+        <v>-2.94</v>
       </c>
       <c r="G10" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J10" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M10" t="n">
         <v>51.2</v>
       </c>
-      <c r="H10" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-2.94</v>
-      </c>
-      <c r="J10" t="n">
-        <v>51.35</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="M10" t="n">
-        <v>51.3</v>
-      </c>
       <c r="N10" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="P10" t="n">
         <v>51.2</v>
@@ -1073,40 +1073,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.74</v>
+        <v>4.63</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.04</v>
+        <v>-0.11</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.84</v>
+        <v>-2.32</v>
       </c>
       <c r="G11" t="n">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.11</v>
+        <v>-0.02</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.32</v>
+        <v>-0.43</v>
       </c>
       <c r="J11" t="n">
-        <v>4.61</v>
+        <v>4.51</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.43</v>
+        <v>-2.17</v>
       </c>
       <c r="M11" t="n">
         <v>4.51</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.17</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>4.51</v>
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.92</v>
+        <v>9.98</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6</v>
+        <v>0.6</v>
       </c>
       <c r="G12" t="n">
-        <v>9.98</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>0.06</v>
+        <v>-0.19</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6</v>
+        <v>-1.9</v>
       </c>
       <c r="J12" t="n">
-        <v>9.789999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.19</v>
+        <v>-0.23</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.9</v>
+        <v>-2.35</v>
       </c>
       <c r="M12" t="n">
-        <v>9.56</v>
+        <v>9.49</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.23</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.35</v>
+        <v>-0.73</v>
       </c>
       <c r="P12" t="n">
         <v>9.49</v>
@@ -1197,40 +1197,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24.46</v>
+        <v>24.48</v>
       </c>
       <c r="E13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F13" t="n">
         <v>0.08</v>
       </c>
-      <c r="F13" t="n">
-        <v>0.33</v>
-      </c>
       <c r="G13" t="n">
-        <v>24.48</v>
+        <v>24.36</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02</v>
+        <v>-0.12</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08</v>
+        <v>-0.49</v>
       </c>
       <c r="J13" t="n">
-        <v>24.36</v>
+        <v>23.88</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.12</v>
+        <v>-0.48</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.49</v>
+        <v>-1.97</v>
       </c>
       <c r="M13" t="n">
-        <v>23.88</v>
+        <v>23.6</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.48</v>
+        <v>-0.28</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.97</v>
+        <v>-1.17</v>
       </c>
       <c r="P13" t="n">
         <v>23.6</v>
@@ -1259,40 +1259,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.01</v>
+        <v>-0.51</v>
       </c>
       <c r="G14" t="n">
         <v>1.95</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="M14" t="n">
         <v>1.92</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>1.92</v>
@@ -1321,40 +1321,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.24</v>
+        <v>5.17</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.95</v>
+        <v>-1.34</v>
       </c>
       <c r="G15" t="n">
-        <v>5.17</v>
+        <v>5.11</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.34</v>
+        <v>-1.16</v>
       </c>
       <c r="J15" t="n">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.16</v>
+        <v>-0.78</v>
       </c>
       <c r="M15" t="n">
-        <v>5.07</v>
+        <v>5.13</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.04</v>
+        <v>0.06</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.78</v>
+        <v>1.18</v>
       </c>
       <c r="P15" t="n">
         <v>5.13</v>
@@ -1383,16 +1383,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.42</v>
+        <v>4.43</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.45</v>
+        <v>0.23</v>
       </c>
       <c r="G16" t="n">
-        <v>4.43</v>
+        <v>4.44</v>
       </c>
       <c r="H16" t="n">
         <v>0.01</v>
@@ -1401,7 +1401,7 @@
         <v>0.23</v>
       </c>
       <c r="J16" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="K16" t="n">
         <v>0.01</v>
@@ -1410,13 +1410,13 @@
         <v>0.23</v>
       </c>
       <c r="M16" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="N16" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="O16" t="n">
-        <v>0.23</v>
+        <v>-0.45</v>
       </c>
       <c r="P16" t="n">
         <v>4.43</v>
@@ -1445,34 +1445,34 @@
         </is>
       </c>
       <c r="D17" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="G17" t="n">
         <v>3.35</v>
       </c>
-      <c r="E17" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.34</v>
-      </c>
       <c r="H17" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="J17" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="N17" t="n">
         <v>-0.02</v>
@@ -1507,7 +1507,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="E18" t="n">
         <v>-0.01</v>
@@ -1519,28 +1519,28 @@
         <v>3.09</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>-2.27</v>
       </c>
       <c r="M18" t="n">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.27</v>
+        <v>-1.32</v>
       </c>
       <c r="P18" t="n">
         <v>2.98</v>
@@ -1569,40 +1569,40 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>53.6</v>
+        <v>53.05</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4</v>
+        <v>-0.55</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.74</v>
+        <v>-1.03</v>
       </c>
       <c r="G19" t="n">
-        <v>53.05</v>
+        <v>52.8</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.55</v>
+        <v>-0.25</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.03</v>
+        <v>-0.47</v>
       </c>
       <c r="J19" t="n">
-        <v>52.8</v>
+        <v>52.85</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.25</v>
+        <v>0.05</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.47</v>
+        <v>0.09</v>
       </c>
       <c r="M19" t="n">
-        <v>52.85</v>
+        <v>53.2</v>
       </c>
       <c r="N19" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="O19" t="n">
-        <v>0.09</v>
+        <v>0.66</v>
       </c>
       <c r="P19" t="n">
         <v>53.2</v>
@@ -1631,40 +1631,40 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.8</v>
+        <v>28.96</v>
       </c>
       <c r="E20" t="n">
-        <v>0.2</v>
+        <v>-0.84</v>
       </c>
       <c r="F20" t="n">
-        <v>0.68</v>
+        <v>-2.82</v>
       </c>
       <c r="G20" t="n">
-        <v>28.96</v>
+        <v>28.54</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.84</v>
+        <v>-0.42</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.82</v>
+        <v>-1.45</v>
       </c>
       <c r="J20" t="n">
-        <v>28.54</v>
+        <v>28.64</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.42</v>
+        <v>0.1</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.45</v>
+        <v>0.35</v>
       </c>
       <c r="M20" t="n">
-        <v>28.64</v>
+        <v>29.38</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1</v>
+        <v>0.74</v>
       </c>
       <c r="O20" t="n">
-        <v>0.35</v>
+        <v>2.58</v>
       </c>
       <c r="P20" t="n">
         <v>29.38</v>
@@ -1693,40 +1693,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.59</v>
+        <v>4.49</v>
       </c>
       <c r="E21" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.1</v>
       </c>
       <c r="F21" t="n">
-        <v>1.55</v>
+        <v>-2.18</v>
       </c>
       <c r="G21" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J21" t="n">
         <v>4.49</v>
       </c>
-      <c r="H21" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4.53</v>
-      </c>
       <c r="K21" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="L21" t="n">
-        <v>0.89</v>
+        <v>-0.88</v>
       </c>
       <c r="M21" t="n">
-        <v>4.49</v>
+        <v>4.43</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.88</v>
+        <v>-1.34</v>
       </c>
       <c r="P21" t="n">
         <v>4.43</v>
@@ -1755,34 +1755,34 @@
         </is>
       </c>
       <c r="D22" t="n">
+        <v>79.05</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="G22" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J22" t="n">
         <v>79.2</v>
       </c>
-      <c r="E22" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="G22" t="n">
+      <c r="K22" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="M22" t="n">
         <v>79.05</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="J22" t="n">
-        <v>79.34999999999999</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="M22" t="n">
-        <v>79.2</v>
       </c>
       <c r="N22" t="n">
         <v>-0.15</v>
@@ -1817,40 +1817,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22.6</v>
+        <v>22.46</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.38</v>
+        <v>-0.14</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.65</v>
+        <v>-0.62</v>
       </c>
       <c r="G23" t="n">
-        <v>22.46</v>
+        <v>22.62</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.14</v>
+        <v>0.16</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.62</v>
+        <v>0.71</v>
       </c>
       <c r="J23" t="n">
-        <v>22.62</v>
+        <v>22.44</v>
       </c>
       <c r="K23" t="n">
-        <v>0.16</v>
+        <v>-0.18</v>
       </c>
       <c r="L23" t="n">
-        <v>0.71</v>
+        <v>-0.8</v>
       </c>
       <c r="M23" t="n">
-        <v>22.44</v>
+        <v>22.84</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.18</v>
+        <v>0.4</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8</v>
+        <v>1.78</v>
       </c>
       <c r="P23" t="n">
         <v>22.84</v>
@@ -1879,40 +1879,40 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.24</v>
+        <v>15.88</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.17</v>
+        <v>-0.36</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.04</v>
+        <v>-2.22</v>
       </c>
       <c r="G24" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="J24" t="n">
         <v>15.88</v>
       </c>
-      <c r="H24" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-2.22</v>
-      </c>
-      <c r="J24" t="n">
-        <v>15.95</v>
-      </c>
       <c r="K24" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>0.44</v>
+        <v>-0.44</v>
       </c>
       <c r="M24" t="n">
-        <v>15.88</v>
+        <v>16.42</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.44</v>
+        <v>3.4</v>
       </c>
       <c r="P24" t="n">
         <v>16.42</v>
@@ -1941,40 +1941,40 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>27.16</v>
+        <v>26.5</v>
       </c>
       <c r="E25" t="n">
-        <v>0.8</v>
+        <v>-0.66</v>
       </c>
       <c r="F25" t="n">
-        <v>3.03</v>
+        <v>-2.43</v>
       </c>
       <c r="G25" t="n">
-        <v>26.5</v>
+        <v>26.18</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.66</v>
+        <v>-0.32</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.43</v>
+        <v>-1.21</v>
       </c>
       <c r="J25" t="n">
-        <v>26.18</v>
+        <v>26.14</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.32</v>
+        <v>-0.04</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.21</v>
+        <v>-0.15</v>
       </c>
       <c r="M25" t="n">
-        <v>26.14</v>
+        <v>26.4</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.04</v>
+        <v>0.26</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.15</v>
+        <v>0.99</v>
       </c>
       <c r="P25" t="n">
         <v>26.4</v>
@@ -2003,40 +2003,40 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33.1</v>
+        <v>32.06</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.36</v>
+        <v>-1.04</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.66</v>
+        <v>-3.14</v>
       </c>
       <c r="G26" t="n">
-        <v>32.06</v>
+        <v>32.88</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.04</v>
+        <v>0.82</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.14</v>
+        <v>2.56</v>
       </c>
       <c r="J26" t="n">
-        <v>32.88</v>
+        <v>33.86</v>
       </c>
       <c r="K26" t="n">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="L26" t="n">
-        <v>2.56</v>
+        <v>2.98</v>
       </c>
       <c r="M26" t="n">
-        <v>33.86</v>
+        <v>37.94</v>
       </c>
       <c r="N26" t="n">
-        <v>0.98</v>
+        <v>4.08</v>
       </c>
       <c r="O26" t="n">
-        <v>2.98</v>
+        <v>12.05</v>
       </c>
       <c r="P26" t="n">
         <v>37.94</v>
@@ -2065,40 +2065,40 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>430.6</v>
+        <v>438.8</v>
       </c>
       <c r="E27" t="n">
-        <v>2.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.51</v>
+        <v>1.9</v>
       </c>
       <c r="G27" t="n">
-        <v>438.8</v>
+        <v>433.4</v>
       </c>
       <c r="H27" t="n">
-        <v>8.199999999999999</v>
+        <v>-5.4</v>
       </c>
       <c r="I27" t="n">
-        <v>1.9</v>
+        <v>-1.23</v>
       </c>
       <c r="J27" t="n">
-        <v>433.4</v>
+        <v>426</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.4</v>
+        <v>-7.4</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.23</v>
+        <v>-1.71</v>
       </c>
       <c r="M27" t="n">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="N27" t="n">
-        <v>-7.4</v>
+        <v>-7</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.71</v>
+        <v>-1.64</v>
       </c>
       <c r="P27" t="n">
         <v>419</v>
@@ -2127,40 +2127,40 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>105.9</v>
+        <v>107.2</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.6</v>
+        <v>1.3</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.49</v>
+        <v>1.23</v>
       </c>
       <c r="G28" t="n">
-        <v>107.2</v>
+        <v>106.2</v>
       </c>
       <c r="H28" t="n">
-        <v>1.3</v>
+        <v>-1</v>
       </c>
       <c r="I28" t="n">
-        <v>1.23</v>
+        <v>-0.93</v>
       </c>
       <c r="J28" t="n">
-        <v>106.2</v>
+        <v>105.1</v>
       </c>
       <c r="K28" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.93</v>
+        <v>-1.04</v>
       </c>
       <c r="M28" t="n">
-        <v>105.1</v>
+        <v>109.3</v>
       </c>
       <c r="N28" t="n">
-        <v>-1.1</v>
+        <v>4.2</v>
       </c>
       <c r="O28" t="n">
-        <v>-1.04</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
         <v>109.3</v>
@@ -2189,40 +2189,40 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>106</v>
+        <v>106.3</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.19</v>
+        <v>0.28</v>
       </c>
       <c r="G29" t="n">
-        <v>106.3</v>
+        <v>105.9</v>
       </c>
       <c r="H29" t="n">
-        <v>0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="I29" t="n">
-        <v>0.28</v>
+        <v>-0.38</v>
       </c>
       <c r="J29" t="n">
-        <v>105.9</v>
+        <v>105</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.38</v>
+        <v>-0.85</v>
       </c>
       <c r="M29" t="n">
         <v>105</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.85</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
         <v>105</v>
@@ -2251,16 +2251,16 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>75.05</v>
+        <v>74.75</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.05</v>
+        <v>-0.3</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.4</v>
       </c>
       <c r="G30" t="n">
-        <v>74.75</v>
+        <v>74.45</v>
       </c>
       <c r="H30" t="n">
         <v>-0.3</v>
@@ -2269,22 +2269,22 @@
         <v>-0.4</v>
       </c>
       <c r="J30" t="n">
-        <v>74.45</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.3</v>
+        <v>-1.55</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.4</v>
+        <v>-2.08</v>
       </c>
       <c r="M30" t="n">
-        <v>72.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="N30" t="n">
-        <v>-1.55</v>
+        <v>0.3</v>
       </c>
       <c r="O30" t="n">
-        <v>-2.08</v>
+        <v>0.41</v>
       </c>
       <c r="P30" t="n">
         <v>73.2</v>
@@ -2313,40 +2313,40 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>89.3</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2</v>
+        <v>-0.4</v>
       </c>
       <c r="F31" t="n">
-        <v>0.22</v>
+        <v>-0.45</v>
       </c>
       <c r="G31" t="n">
-        <v>88.90000000000001</v>
+        <v>88.05</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.4</v>
+        <v>-0.85</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.45</v>
+        <v>-0.96</v>
       </c>
       <c r="J31" t="n">
-        <v>88.05</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.85</v>
+        <v>-0.7</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.96</v>
+        <v>-0.8</v>
       </c>
       <c r="M31" t="n">
-        <v>87.34999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.7</v>
+        <v>-0.15</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.8</v>
+        <v>-0.17</v>
       </c>
       <c r="P31" t="n">
         <v>87.2</v>
@@ -2375,40 +2375,40 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>61.3</v>
+        <v>60.75</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.85</v>
+        <v>-0.55</v>
       </c>
       <c r="F32" t="n">
-        <v>-2.93</v>
+        <v>-0.9</v>
       </c>
       <c r="G32" t="n">
-        <v>60.75</v>
+        <v>63.65</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.55</v>
+        <v>2.9</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.9</v>
+        <v>4.77</v>
       </c>
       <c r="J32" t="n">
-        <v>63.65</v>
+        <v>62.4</v>
       </c>
       <c r="K32" t="n">
-        <v>2.9</v>
+        <v>-1.25</v>
       </c>
       <c r="L32" t="n">
-        <v>4.77</v>
+        <v>-1.96</v>
       </c>
       <c r="M32" t="n">
-        <v>62.4</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>-1.25</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
-        <v>-1.96</v>
+        <v>4.41</v>
       </c>
       <c r="P32" t="n">
         <v>65.15000000000001</v>
@@ -2437,40 +2437,40 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>80.2</v>
+        <v>79.05</v>
       </c>
       <c r="E33" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="F33" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="G33" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J33" t="n">
+        <v>81.15000000000001</v>
+      </c>
+      <c r="K33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L33" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="M33" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="N33" t="n">
         <v>0.35</v>
       </c>
-      <c r="F33" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="G33" t="n">
-        <v>79.05</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-1.15</v>
-      </c>
-      <c r="I33" t="n">
-        <v>-1.43</v>
-      </c>
-      <c r="J33" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="M33" t="n">
-        <v>81.15000000000001</v>
-      </c>
-      <c r="N33" t="n">
-        <v>1.95</v>
-      </c>
       <c r="O33" t="n">
-        <v>2.46</v>
+        <v>0.43</v>
       </c>
       <c r="P33" t="n">
         <v>81.5</v>
@@ -2499,40 +2499,40 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>30.58</v>
+        <v>29.8</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.68</v>
+        <v>-0.78</v>
       </c>
       <c r="F34" t="n">
-        <v>-2.18</v>
+        <v>-2.55</v>
       </c>
       <c r="G34" t="n">
-        <v>29.8</v>
+        <v>29.66</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.78</v>
+        <v>-0.14</v>
       </c>
       <c r="I34" t="n">
-        <v>-2.55</v>
+        <v>-0.47</v>
       </c>
       <c r="J34" t="n">
-        <v>29.66</v>
+        <v>29.94</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.14</v>
+        <v>0.28</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.47</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>29.94</v>
+        <v>30.74</v>
       </c>
       <c r="N34" t="n">
-        <v>0.28</v>
+        <v>0.8</v>
       </c>
       <c r="O34" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.67</v>
       </c>
       <c r="P34" t="n">
         <v>30.74</v>
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
+        <v>4.21</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="G35" t="n">
         <v>4.24</v>
       </c>
-      <c r="E35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>4.21</v>
-      </c>
       <c r="H35" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.71</v>
+        <v>0.71</v>
       </c>
       <c r="J35" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="K35" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="L35" t="n">
-        <v>0.71</v>
+        <v>-0.47</v>
       </c>
       <c r="M35" t="n">
-        <v>4.24</v>
+        <v>4.32</v>
       </c>
       <c r="N35" t="n">
-        <v>0.03</v>
+        <v>0.1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.71</v>
+        <v>2.37</v>
       </c>
       <c r="P35" t="n">
         <v>4.32</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="R35" t="n">
-        <v>1.89</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.109999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.11</v>
+        <v>-0.66</v>
       </c>
       <c r="G36" t="n">
-        <v>9.050000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.66</v>
+        <v>0.99</v>
       </c>
       <c r="J36" t="n">
-        <v>9.140000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="K36" t="n">
-        <v>0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="L36" t="n">
-        <v>0.99</v>
+        <v>-0.44</v>
       </c>
       <c r="M36" t="n">
-        <v>9.140000000000001</v>
+        <v>9.31</v>
       </c>
       <c r="N36" t="n">
-        <v>0.09</v>
+        <v>0.21</v>
       </c>
       <c r="O36" t="n">
-        <v>0.99</v>
+        <v>2.31</v>
       </c>
       <c r="P36" t="n">
         <v>9.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="R36" t="n">
-        <v>1.86</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="37">
@@ -2685,40 +2685,40 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>397.4</v>
+        <v>393.8</v>
       </c>
       <c r="E37" t="n">
-        <v>4.8</v>
+        <v>-3.6</v>
       </c>
       <c r="F37" t="n">
-        <v>1.22</v>
+        <v>-0.91</v>
       </c>
       <c r="G37" t="n">
-        <v>393.8</v>
+        <v>395.6</v>
       </c>
       <c r="H37" t="n">
-        <v>-3.6</v>
+        <v>1.8</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.91</v>
+        <v>0.46</v>
       </c>
       <c r="J37" t="n">
-        <v>395.6</v>
+        <v>388.6</v>
       </c>
       <c r="K37" t="n">
-        <v>1.8</v>
+        <v>-7</v>
       </c>
       <c r="L37" t="n">
-        <v>0.46</v>
+        <v>-1.77</v>
       </c>
       <c r="M37" t="n">
-        <v>388.6</v>
+        <v>388</v>
       </c>
       <c r="N37" t="n">
-        <v>-7</v>
+        <v>-0.6</v>
       </c>
       <c r="O37" t="n">
-        <v>-1.77</v>
+        <v>-0.15</v>
       </c>
       <c r="P37" t="n">
         <v>388</v>
@@ -2747,40 +2747,40 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.36</v>
+        <v>-0.2</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.69</v>
+        <v>-1.54</v>
       </c>
       <c r="G38" t="n">
-        <v>12.8</v>
+        <v>12.08</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.2</v>
+        <v>-0.72</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.54</v>
+        <v>-5.62</v>
       </c>
       <c r="J38" t="n">
-        <v>12.08</v>
+        <v>12.2</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.72</v>
+        <v>0.12</v>
       </c>
       <c r="L38" t="n">
-        <v>-5.62</v>
+        <v>0.99</v>
       </c>
       <c r="M38" t="n">
-        <v>12.2</v>
+        <v>12.24</v>
       </c>
       <c r="N38" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="O38" t="n">
-        <v>0.99</v>
+        <v>0.33</v>
       </c>
       <c r="P38" t="n">
         <v>12.24</v>
@@ -2809,40 +2809,40 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>549</v>
+        <v>516</v>
       </c>
       <c r="E39" t="n">
-        <v>1.5</v>
+        <v>-33</v>
       </c>
       <c r="F39" t="n">
-        <v>0.27</v>
+        <v>-6.01</v>
       </c>
       <c r="G39" t="n">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="H39" t="n">
-        <v>-33</v>
+        <v>-15</v>
       </c>
       <c r="I39" t="n">
-        <v>-6.01</v>
+        <v>-2.91</v>
       </c>
       <c r="J39" t="n">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="K39" t="n">
-        <v>-15</v>
+        <v>6</v>
       </c>
       <c r="L39" t="n">
-        <v>-2.91</v>
+        <v>1.2</v>
       </c>
       <c r="M39" t="n">
         <v>507</v>
       </c>
       <c r="N39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
         <v>507</v>
@@ -2871,40 +2871,40 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>42.02</v>
+        <v>40.38</v>
       </c>
       <c r="E40" t="n">
-        <v>0.68</v>
+        <v>-1.64</v>
       </c>
       <c r="F40" t="n">
-        <v>1.64</v>
+        <v>-3.9</v>
       </c>
       <c r="G40" t="n">
-        <v>40.38</v>
+        <v>40.42</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.64</v>
+        <v>0.04</v>
       </c>
       <c r="I40" t="n">
-        <v>-3.9</v>
+        <v>0.1</v>
       </c>
       <c r="J40" t="n">
-        <v>40.42</v>
+        <v>41.18</v>
       </c>
       <c r="K40" t="n">
-        <v>0.04</v>
+        <v>0.76</v>
       </c>
       <c r="L40" t="n">
-        <v>0.1</v>
+        <v>1.88</v>
       </c>
       <c r="M40" t="n">
-        <v>41.18</v>
+        <v>42.04</v>
       </c>
       <c r="N40" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="O40" t="n">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="P40" t="n">
         <v>42.04</v>
@@ -2933,34 +2933,34 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.85</v>
+        <v>31</v>
       </c>
       <c r="E41" t="n">
-        <v>0.25</v>
+        <v>-0.85</v>
       </c>
       <c r="F41" t="n">
-        <v>0.79</v>
+        <v>-2.67</v>
       </c>
       <c r="G41" t="n">
-        <v>31</v>
+        <v>31.18</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.85</v>
+        <v>0.18</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.67</v>
+        <v>0.58</v>
       </c>
       <c r="J41" t="n">
-        <v>31.18</v>
+        <v>31.28</v>
       </c>
       <c r="K41" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="L41" t="n">
-        <v>0.58</v>
+        <v>0.32</v>
       </c>
       <c r="M41" t="n">
-        <v>31.28</v>
+        <v>31.38</v>
       </c>
       <c r="N41" t="n">
         <v>0.1</v>
@@ -2995,40 +2995,40 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>77.66</v>
+        <v>76.75</v>
       </c>
       <c r="E42" t="n">
-        <v>0.66</v>
+        <v>-0.91</v>
       </c>
       <c r="F42" t="n">
-        <v>0.86</v>
+        <v>-1.17</v>
       </c>
       <c r="G42" t="n">
-        <v>76.75</v>
+        <v>76.8</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.91</v>
+        <v>0.05</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>76.8</v>
+        <v>76.94</v>
       </c>
       <c r="K42" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="L42" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="M42" t="n">
-        <v>76.94</v>
+        <v>76.86</v>
       </c>
       <c r="N42" t="n">
-        <v>0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="O42" t="n">
-        <v>0.18</v>
+        <v>-0.1</v>
       </c>
       <c r="P42" t="n">
         <v>76.86</v>
@@ -3057,40 +3057,40 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>42.33</v>
+        <v>41.33</v>
       </c>
       <c r="E43" t="n">
-        <v>1.07</v>
+        <v>-1</v>
       </c>
       <c r="F43" t="n">
-        <v>2.59</v>
+        <v>-2.36</v>
       </c>
       <c r="G43" t="n">
-        <v>41.33</v>
+        <v>41.21</v>
       </c>
       <c r="H43" t="n">
-        <v>-1</v>
+        <v>-0.12</v>
       </c>
       <c r="I43" t="n">
-        <v>-2.36</v>
+        <v>-0.29</v>
       </c>
       <c r="J43" t="n">
-        <v>41.21</v>
+        <v>41.88</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.12</v>
+        <v>0.67</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.29</v>
+        <v>1.63</v>
       </c>
       <c r="M43" t="n">
-        <v>41.88</v>
+        <v>41.78</v>
       </c>
       <c r="N43" t="n">
-        <v>0.67</v>
+        <v>-0.1</v>
       </c>
       <c r="O43" t="n">
-        <v>1.63</v>
+        <v>-0.24</v>
       </c>
       <c r="P43" t="n">
         <v>41.78</v>
@@ -3119,16 +3119,16 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="E44" t="n">
         <v>-0.05</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.82</v>
+        <v>-0.83</v>
       </c>
       <c r="G44" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="H44" t="n">
         <v>-0.05</v>
@@ -3137,22 +3137,22 @@
         <v>-0.83</v>
       </c>
       <c r="J44" t="n">
-        <v>5.95</v>
+        <v>5.93</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.83</v>
+        <v>-0.34</v>
       </c>
       <c r="M44" t="n">
-        <v>5.93</v>
+        <v>5.9</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.34</v>
+        <v>-0.51</v>
       </c>
       <c r="P44" t="n">
         <v>5.9</v>
@@ -3181,16 +3181,16 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.93</v>
+        <v>-0.47</v>
       </c>
       <c r="G45" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H45" t="n">
         <v>-0.01</v>
@@ -3199,22 +3199,22 @@
         <v>-0.47</v>
       </c>
       <c r="J45" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="K45" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="N45" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L45" t="n">
+      <c r="O45" t="n">
         <v>-0.47</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0.95</v>
       </c>
       <c r="P45" t="n">
         <v>2.12</v>
@@ -3243,40 +3243,40 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.02</v>
+        <v>-0.26</v>
       </c>
       <c r="G46" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="H46" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="K46" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I46" t="n">
+      <c r="L46" t="n">
         <v>-0.26</v>
       </c>
-      <c r="J46" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="N46" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L46" t="n">
+      <c r="O46" t="n">
         <v>-0.52</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="N46" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="O46" t="n">
-        <v>-0.26</v>
       </c>
       <c r="P46" t="n">
         <v>3.81</v>
@@ -3305,40 +3305,40 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.22</v>
+        <v>10.13</v>
       </c>
       <c r="E47" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.88</v>
+      </c>
+      <c r="G47" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="H47" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F47" t="n">
+      <c r="I47" t="n">
         <v>-0.2</v>
       </c>
-      <c r="G47" t="n">
-        <v>10.13</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="I47" t="n">
-        <v>-0.88</v>
-      </c>
       <c r="J47" t="n">
-        <v>10.11</v>
+        <v>10.19</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.2</v>
+        <v>0.79</v>
       </c>
       <c r="M47" t="n">
-        <v>10.19</v>
+        <v>10.43</v>
       </c>
       <c r="N47" t="n">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="O47" t="n">
-        <v>0.79</v>
+        <v>2.36</v>
       </c>
       <c r="P47" t="n">
         <v>10.43</v>
@@ -3367,40 +3367,40 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.32</v>
+        <v>0.315</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>-1.56</v>
       </c>
       <c r="G48" t="n">
-        <v>0.315</v>
+        <v>0.31</v>
       </c>
       <c r="H48" t="n">
         <v>-0.005</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.56</v>
+        <v>-1.59</v>
       </c>
       <c r="J48" t="n">
-        <v>0.31</v>
+        <v>0.305</v>
       </c>
       <c r="K48" t="n">
         <v>-0.005</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.59</v>
+        <v>-1.61</v>
       </c>
       <c r="M48" t="n">
-        <v>0.305</v>
+        <v>0.31</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.61</v>
+        <v>1.64</v>
       </c>
       <c r="P48" t="n">
         <v>0.31</v>
@@ -3429,40 +3429,40 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.46</v>
+        <v>4.45</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.89</v>
+        <v>-0.22</v>
       </c>
       <c r="G49" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.22</v>
+        <v>-0.67</v>
       </c>
       <c r="J49" t="n">
         <v>4.42</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.67</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.42</v>
+        <v>4.35</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>-1.58</v>
       </c>
       <c r="P49" t="n">
         <v>4.35</v>
@@ -3491,40 +3491,40 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="E50" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F50" t="n">
-        <v>0.92</v>
+        <v>1.82</v>
       </c>
       <c r="G50" t="n">
         <v>1.12</v>
       </c>
       <c r="H50" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
       <c r="M50" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="O50" t="n">
-        <v>-0.89</v>
+        <v>-4.5</v>
       </c>
       <c r="P50" t="n">
         <v>1.06</v>
@@ -3553,40 +3553,40 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.11</v>
+        <v>5.09</v>
       </c>
       <c r="E51" t="n">
-        <v>0.13</v>
+        <v>-0.02</v>
       </c>
       <c r="F51" t="n">
-        <v>2.61</v>
+        <v>-0.39</v>
       </c>
       <c r="G51" t="n">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.39</v>
+        <v>-0.79</v>
       </c>
       <c r="J51" t="n">
-        <v>5.05</v>
+        <v>5.14</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.79</v>
+        <v>1.78</v>
       </c>
       <c r="M51" t="n">
-        <v>5.14</v>
+        <v>5.17</v>
       </c>
       <c r="N51" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="O51" t="n">
-        <v>1.78</v>
+        <v>0.58</v>
       </c>
       <c r="P51" t="n">
         <v>5.17</v>
@@ -3615,40 +3615,40 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.33</v>
+        <v>11.2</v>
       </c>
       <c r="E52" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-1.15</v>
+      </c>
+      <c r="G52" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="H52" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F52" t="n">
-        <v>-0.87</v>
-      </c>
-      <c r="G52" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-0.13</v>
-      </c>
       <c r="I52" t="n">
-        <v>-1.15</v>
+        <v>-0.89</v>
       </c>
       <c r="J52" t="n">
-        <v>11.1</v>
+        <v>11.12</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.89</v>
+        <v>0.18</v>
       </c>
       <c r="M52" t="n">
-        <v>11.12</v>
+        <v>11.03</v>
       </c>
       <c r="N52" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="O52" t="n">
-        <v>0.18</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P52" t="n">
         <v>11.03</v>
@@ -3677,40 +3677,40 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.15</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.01</v>
+        <v>-0.1</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.12</v>
+        <v>-1.23</v>
       </c>
       <c r="G53" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I53" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="J53" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M53" t="n">
         <v>8.050000000000001</v>
       </c>
-      <c r="H53" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="I53" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="J53" t="n">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="K53" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L53" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="M53" t="n">
-        <v>8.140000000000001</v>
-      </c>
       <c r="N53" t="n">
-        <v>0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="O53" t="n">
-        <v>1.37</v>
+        <v>-1.11</v>
       </c>
       <c r="P53" t="n">
         <v>8.050000000000001</v>
@@ -3739,31 +3739,31 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.45</v>
+        <v>0.445</v>
       </c>
       <c r="E54" t="n">
-        <v>0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="F54" t="n">
-        <v>2.27</v>
+        <v>-1.11</v>
       </c>
       <c r="G54" t="n">
-        <v>0.445</v>
+        <v>0.44</v>
       </c>
       <c r="H54" t="n">
         <v>-0.005</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.11</v>
+        <v>-1.12</v>
       </c>
       <c r="J54" t="n">
         <v>0.44</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.12</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>0.44</v>
@@ -3819,22 +3819,22 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="M55" t="n">
         <v>0.615</v>
       </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0.62</v>
-      </c>
       <c r="N55" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P55" t="n">
         <v>0.615</v>
@@ -3863,40 +3863,40 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>-4.88</v>
       </c>
       <c r="G56" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I56" t="n">
-        <v>-4.88</v>
+        <v>2.56</v>
       </c>
       <c r="J56" t="n">
-        <v>0.4</v>
+        <v>0.395</v>
       </c>
       <c r="K56" t="n">
-        <v>0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="L56" t="n">
-        <v>2.56</v>
+        <v>-1.25</v>
       </c>
       <c r="M56" t="n">
         <v>0.395</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
         <v>0.395</v>
@@ -3925,40 +3925,40 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="E57" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="H57" t="n">
         <v>0.01</v>
       </c>
-      <c r="F57" t="n">
+      <c r="I57" t="n">
         <v>0.27</v>
       </c>
-      <c r="G57" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I57" t="n">
-        <v>-0.54</v>
-      </c>
       <c r="J57" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="K57" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L57" t="n">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="M57" t="n">
-        <v>3.73</v>
+        <v>3.68</v>
       </c>
       <c r="N57" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="O57" t="n">
-        <v>0.54</v>
+        <v>-1.34</v>
       </c>
       <c r="P57" t="n">
         <v>3.68</v>
@@ -3987,40 +3987,40 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.076</v>
+        <v>0.075</v>
       </c>
       <c r="E58" t="n">
         <v>-0.001</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.3</v>
+        <v>-1.32</v>
       </c>
       <c r="G58" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.32</v>
+        <v>1.33</v>
       </c>
       <c r="J58" t="n">
         <v>0.076</v>
       </c>
       <c r="K58" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.076</v>
+        <v>0.074</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>-2.63</v>
       </c>
       <c r="P58" t="n">
         <v>0.074</v>
@@ -4049,40 +4049,40 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22.91</v>
+        <v>22.53</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.39</v>
+        <v>-0.38</v>
       </c>
       <c r="F59" t="n">
-        <v>-5.72</v>
+        <v>-1.66</v>
       </c>
       <c r="G59" t="n">
-        <v>22.53</v>
+        <v>22.38</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.66</v>
+        <v>-0.67</v>
       </c>
       <c r="J59" t="n">
-        <v>22.38</v>
+        <v>22.27</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.15</v>
+        <v>-0.11</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.67</v>
+        <v>-0.49</v>
       </c>
       <c r="M59" t="n">
-        <v>22.27</v>
+        <v>22.2</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.49</v>
+        <v>-0.31</v>
       </c>
       <c r="P59" t="n">
         <v>22.2</v>
@@ -4111,16 +4111,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.32</v>
+        <v>0.32</v>
       </c>
       <c r="G60" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="H60" t="n">
         <v>0.01</v>
@@ -4132,19 +4132,19 @@
         <v>3.12</v>
       </c>
       <c r="K60" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="P60" t="n">
         <v>3.11</v>
@@ -4173,40 +4173,40 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.885</v>
+        <v>0.875</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.28</v>
+        <v>-1.13</v>
       </c>
       <c r="G61" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="I61" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="J61" t="n">
         <v>0.875</v>
       </c>
-      <c r="H61" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="I61" t="n">
-        <v>-1.13</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.89</v>
-      </c>
       <c r="K61" t="n">
-        <v>0.015</v>
+        <v>-0.015</v>
       </c>
       <c r="L61" t="n">
-        <v>1.71</v>
+        <v>-1.69</v>
       </c>
       <c r="M61" t="n">
-        <v>0.875</v>
+        <v>0.88</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.015</v>
+        <v>0.005</v>
       </c>
       <c r="O61" t="n">
-        <v>-1.69</v>
+        <v>0.57</v>
       </c>
       <c r="P61" t="n">
         <v>0.88</v>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-15 Close</t>
+          <t>2026-09-16 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-09-15 Change</t>
+          <t>2026-09-16 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-15 Change %</t>
+          <t>2026-09-16 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-09-16 Close</t>
+          <t>2026-09-17 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-09-16 Change</t>
+          <t>2026-09-17 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-09-16 Change %</t>
+          <t>2026-09-17 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-09-17 Close</t>
+          <t>2026-09-18 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-09-17 Change</t>
+          <t>2026-09-18 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-09-17 Change %</t>
+          <t>2026-09-18 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-09-18 Close</t>
+          <t>2026-09-21 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-09-18 Change</t>
+          <t>2026-09-21 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-09-18 Change %</t>
+          <t>2026-09-21 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-09-21 Close</t>
+          <t>2026-09-22 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-09-21 Change</t>
+          <t>2026-09-22 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-09-21 Change %</t>
+          <t>2026-09-22 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>159.6</v>
+        <v>160.9</v>
       </c>
       <c r="E3" t="n">
-        <v>-5.3</v>
+        <v>1.3</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.21</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>160.9</v>
+        <v>159.8</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3</v>
+        <v>-1.1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.68</v>
       </c>
       <c r="J3" t="n">
-        <v>159.8</v>
+        <v>161.6</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.1</v>
+        <v>1.8</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.68</v>
+        <v>1.13</v>
       </c>
       <c r="M3" t="n">
-        <v>161.6</v>
+        <v>161.5</v>
       </c>
       <c r="N3" t="n">
-        <v>1.8</v>
+        <v>-0.1</v>
       </c>
       <c r="O3" t="n">
-        <v>1.13</v>
+        <v>-0.06</v>
       </c>
       <c r="P3" t="n">
-        <v>161.6</v>
+        <v>161.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>-0.1</v>
       </c>
       <c r="R3" t="n">
-        <v>1.13</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E4" t="n">
-        <v>-8.6</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.49</v>
+        <v>2.52</v>
       </c>
       <c r="G4" t="n">
-        <v>244</v>
+        <v>243.4</v>
       </c>
       <c r="H4" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="I4" t="n">
-        <v>2.52</v>
+        <v>-0.25</v>
       </c>
       <c r="J4" t="n">
-        <v>243.4</v>
+        <v>245</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.6</v>
+        <v>1.6</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.25</v>
+        <v>0.66</v>
       </c>
       <c r="M4" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="N4" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="O4" t="n">
-        <v>0.66</v>
+        <v>0.41</v>
       </c>
       <c r="P4" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>0.66</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.31</v>
+        <v>6.36</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.56</v>
+        <v>0.79</v>
       </c>
       <c r="G5" t="n">
-        <v>6.36</v>
+        <v>6.32</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="I5" t="n">
-        <v>0.79</v>
+        <v>-0.63</v>
       </c>
       <c r="J5" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.63</v>
+        <v>-0.32</v>
       </c>
       <c r="M5" t="n">
-        <v>6.3</v>
+        <v>6.51</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.02</v>
+        <v>0.21</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.32</v>
+        <v>3.33</v>
       </c>
       <c r="P5" t="n">
-        <v>6.3</v>
+        <v>6.51</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.02</v>
+        <v>0.21</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.32</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.49</v>
+        <v>7.53</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.16</v>
+        <v>0.04</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.09</v>
+        <v>0.53</v>
       </c>
       <c r="G6" t="n">
-        <v>7.53</v>
+        <v>7.52</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0.53</v>
+        <v>-0.13</v>
       </c>
       <c r="J6" t="n">
-        <v>7.52</v>
+        <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.13</v>
+        <v>-0.27</v>
       </c>
       <c r="M6" t="n">
-        <v>7.5</v>
+        <v>7.58</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.27</v>
+        <v>1.07</v>
       </c>
       <c r="P6" t="n">
-        <v>7.5</v>
+        <v>7.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.27</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.95</v>
+        <v>5.98</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3</v>
+        <v>0.5</v>
       </c>
       <c r="G7" t="n">
-        <v>5.98</v>
+        <v>5.99</v>
       </c>
       <c r="H7" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="J7" t="n">
         <v>5.99</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5.99</v>
+        <v>6.06</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P7" t="n">
-        <v>5.99</v>
+        <v>6.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.609999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.28</v>
+        <v>0.03</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.83</v>
+        <v>0.31</v>
       </c>
       <c r="G8" t="n">
-        <v>9.640000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I8" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="J8" t="n">
-        <v>9.68</v>
+        <v>9.59</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="L8" t="n">
-        <v>0.41</v>
+        <v>-0.93</v>
       </c>
       <c r="M8" t="n">
-        <v>9.59</v>
+        <v>9.76</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.09</v>
+        <v>0.17</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.93</v>
+        <v>1.77</v>
       </c>
       <c r="P8" t="n">
-        <v>9.59</v>
+        <v>9.76</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.09</v>
+        <v>0.17</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.93</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.02</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.14</v>
+        <v>0.1</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.72</v>
+        <v>1.25</v>
       </c>
       <c r="G9" t="n">
-        <v>8.119999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="I9" t="n">
-        <v>1.25</v>
+        <v>0.74</v>
       </c>
       <c r="J9" t="n">
-        <v>8.18</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="L9" t="n">
-        <v>0.74</v>
+        <v>-0.49</v>
       </c>
       <c r="M9" t="n">
-        <v>8.140000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.04</v>
+        <v>0.12</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.49</v>
+        <v>1.47</v>
       </c>
       <c r="P9" t="n">
-        <v>8.140000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.04</v>
+        <v>0.12</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.49</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G10" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="J10" t="n">
         <v>51.2</v>
       </c>
-      <c r="E10" t="n">
-        <v>-1.55</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-2.94</v>
-      </c>
-      <c r="G10" t="n">
-        <v>51.35</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="J10" t="n">
-        <v>51.3</v>
-      </c>
       <c r="K10" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="M10" t="n">
-        <v>51.2</v>
+        <v>52.1</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.19</v>
+        <v>1.76</v>
       </c>
       <c r="P10" t="n">
-        <v>51.2</v>
+        <v>52.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.19</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.63</v>
+        <v>4.61</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.11</v>
+        <v>-0.02</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.32</v>
+        <v>-0.43</v>
       </c>
       <c r="G11" t="n">
-        <v>4.61</v>
+        <v>4.51</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.43</v>
+        <v>-2.17</v>
       </c>
       <c r="J11" t="n">
         <v>4.51</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.17</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.51</v>
+        <v>4.49</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="P11" t="n">
-        <v>4.51</v>
+        <v>4.49</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.98</v>
+        <v>9.789999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06</v>
+        <v>-0.19</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6</v>
+        <v>-1.9</v>
       </c>
       <c r="G12" t="n">
-        <v>9.789999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.19</v>
+        <v>-0.23</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.9</v>
+        <v>-2.35</v>
       </c>
       <c r="J12" t="n">
-        <v>9.56</v>
+        <v>9.49</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.23</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.35</v>
+        <v>-0.73</v>
       </c>
       <c r="M12" t="n">
-        <v>9.49</v>
+        <v>9.51</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.73</v>
+        <v>0.21</v>
       </c>
       <c r="P12" t="n">
-        <v>9.49</v>
+        <v>9.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.73</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24.48</v>
+        <v>24.36</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02</v>
+        <v>-0.12</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08</v>
+        <v>-0.49</v>
       </c>
       <c r="G13" t="n">
-        <v>24.36</v>
+        <v>23.88</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.12</v>
+        <v>-0.48</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.49</v>
+        <v>-1.97</v>
       </c>
       <c r="J13" t="n">
-        <v>23.88</v>
+        <v>23.6</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.48</v>
+        <v>-0.28</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.97</v>
+        <v>-1.17</v>
       </c>
       <c r="M13" t="n">
-        <v>23.6</v>
+        <v>23.94</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.28</v>
+        <v>0.34</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.17</v>
+        <v>1.44</v>
       </c>
       <c r="P13" t="n">
-        <v>23.6</v>
+        <v>23.94</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.28</v>
+        <v>0.34</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.17</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="14">
@@ -1262,46 +1262,46 @@
         <v>1.95</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="J14" t="n">
         <v>1.92</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>-1.04</v>
       </c>
       <c r="P14" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.17</v>
+        <v>5.11</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.34</v>
+        <v>-1.16</v>
       </c>
       <c r="G15" t="n">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.16</v>
+        <v>-0.78</v>
       </c>
       <c r="J15" t="n">
-        <v>5.07</v>
+        <v>5.13</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.04</v>
+        <v>0.06</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.78</v>
+        <v>1.18</v>
       </c>
       <c r="M15" t="n">
-        <v>5.13</v>
+        <v>5.25</v>
       </c>
       <c r="N15" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="O15" t="n">
-        <v>1.18</v>
+        <v>2.34</v>
       </c>
       <c r="P15" t="n">
-        <v>5.13</v>
+        <v>5.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="R15" t="n">
-        <v>1.18</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="16">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.43</v>
+        <v>4.44</v>
       </c>
       <c r="E16" t="n">
         <v>0.01</v>
@@ -1392,7 +1392,7 @@
         <v>0.23</v>
       </c>
       <c r="G16" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="H16" t="n">
         <v>0.01</v>
@@ -1401,31 +1401,31 @@
         <v>0.23</v>
       </c>
       <c r="J16" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="K16" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="L16" t="n">
-        <v>0.23</v>
+        <v>-0.45</v>
       </c>
       <c r="M16" t="n">
         <v>4.43</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>4.43</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1445,25 +1445,25 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3</v>
+        <v>0.3</v>
       </c>
       <c r="G17" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="I17" t="n">
-        <v>0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="J17" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="K17" t="n">
         <v>-0.02</v>
@@ -1475,19 +1475,19 @@
         <v>3.31</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>3.31</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1510,46 +1510,46 @@
         <v>3.09</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.32</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-2.27</v>
       </c>
       <c r="J18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="M18" t="n">
         <v>3.02</v>
       </c>
-      <c r="K18" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-2.27</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2.98</v>
-      </c>
       <c r="N18" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.32</v>
+        <v>1.34</v>
       </c>
       <c r="P18" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="R18" t="n">
-        <v>-1.32</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>53.05</v>
+        <v>52.8</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.55</v>
+        <v>-0.25</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.03</v>
+        <v>-0.47</v>
       </c>
       <c r="G19" t="n">
-        <v>52.8</v>
+        <v>52.85</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.25</v>
+        <v>0.05</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.47</v>
+        <v>0.09</v>
       </c>
       <c r="J19" t="n">
-        <v>52.85</v>
+        <v>53.2</v>
       </c>
       <c r="K19" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="L19" t="n">
-        <v>0.09</v>
+        <v>0.66</v>
       </c>
       <c r="M19" t="n">
-        <v>53.2</v>
+        <v>53.75</v>
       </c>
       <c r="N19" t="n">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="O19" t="n">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="P19" t="n">
-        <v>53.2</v>
+        <v>53.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="R19" t="n">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.96</v>
+        <v>28.54</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.84</v>
+        <v>-0.42</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.82</v>
+        <v>-1.45</v>
       </c>
       <c r="G20" t="n">
-        <v>28.54</v>
+        <v>28.64</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.42</v>
+        <v>0.1</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.45</v>
+        <v>0.35</v>
       </c>
       <c r="J20" t="n">
-        <v>28.64</v>
+        <v>29.38</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1</v>
+        <v>0.74</v>
       </c>
       <c r="L20" t="n">
-        <v>0.35</v>
+        <v>2.58</v>
       </c>
       <c r="M20" t="n">
-        <v>29.38</v>
+        <v>29.08</v>
       </c>
       <c r="N20" t="n">
-        <v>0.74</v>
+        <v>-0.3</v>
       </c>
       <c r="O20" t="n">
-        <v>2.58</v>
+        <v>-1.02</v>
       </c>
       <c r="P20" t="n">
-        <v>29.38</v>
+        <v>29.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.74</v>
+        <v>-0.3</v>
       </c>
       <c r="R20" t="n">
-        <v>2.58</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
+        <v>4.53</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G21" t="n">
         <v>4.49</v>
       </c>
-      <c r="E21" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-2.18</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.53</v>
-      </c>
       <c r="H21" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="I21" t="n">
-        <v>0.89</v>
+        <v>-0.88</v>
       </c>
       <c r="J21" t="n">
-        <v>4.49</v>
+        <v>4.43</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.88</v>
+        <v>-1.34</v>
       </c>
       <c r="M21" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.34</v>
+        <v>-0.45</v>
       </c>
       <c r="P21" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="R21" t="n">
-        <v>-1.34</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="22">
@@ -1755,25 +1755,25 @@
         </is>
       </c>
       <c r="D22" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="G22" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="J22" t="n">
         <v>79.05</v>
-      </c>
-      <c r="E22" t="n">
-        <v>-0.15</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="G22" t="n">
-        <v>79.34999999999999</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="J22" t="n">
-        <v>79.2</v>
       </c>
       <c r="K22" t="n">
         <v>-0.15</v>
@@ -1782,22 +1782,22 @@
         <v>-0.19</v>
       </c>
       <c r="M22" t="n">
-        <v>79.05</v>
+        <v>79.2</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.19</v>
+        <v>0.19</v>
       </c>
       <c r="P22" t="n">
-        <v>79.05</v>
+        <v>79.2</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.19</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22.46</v>
+        <v>22.62</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.14</v>
+        <v>0.16</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.62</v>
+        <v>0.71</v>
       </c>
       <c r="G23" t="n">
-        <v>22.62</v>
+        <v>22.44</v>
       </c>
       <c r="H23" t="n">
-        <v>0.16</v>
+        <v>-0.18</v>
       </c>
       <c r="I23" t="n">
-        <v>0.71</v>
+        <v>-0.8</v>
       </c>
       <c r="J23" t="n">
-        <v>22.44</v>
+        <v>22.84</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.18</v>
+        <v>0.4</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.8</v>
+        <v>1.78</v>
       </c>
       <c r="M23" t="n">
-        <v>22.84</v>
+        <v>23.54</v>
       </c>
       <c r="N23" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="O23" t="n">
-        <v>1.78</v>
+        <v>3.06</v>
       </c>
       <c r="P23" t="n">
-        <v>22.84</v>
+        <v>23.54</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="R23" t="n">
-        <v>1.78</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
+        <v>15.95</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="G24" t="n">
         <v>15.88</v>
       </c>
-      <c r="E24" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="F24" t="n">
-        <v>-2.22</v>
-      </c>
-      <c r="G24" t="n">
-        <v>15.95</v>
-      </c>
       <c r="H24" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>0.44</v>
+        <v>-0.44</v>
       </c>
       <c r="J24" t="n">
-        <v>15.88</v>
+        <v>16.42</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.44</v>
+        <v>3.4</v>
       </c>
       <c r="M24" t="n">
-        <v>16.42</v>
+        <v>16.21</v>
       </c>
       <c r="N24" t="n">
-        <v>0.54</v>
+        <v>-0.21</v>
       </c>
       <c r="O24" t="n">
-        <v>3.4</v>
+        <v>-1.28</v>
       </c>
       <c r="P24" t="n">
-        <v>16.42</v>
+        <v>16.21</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.54</v>
+        <v>-0.21</v>
       </c>
       <c r="R24" t="n">
-        <v>3.4</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.5</v>
+        <v>26.18</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.66</v>
+        <v>-0.32</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.43</v>
+        <v>-1.21</v>
       </c>
       <c r="G25" t="n">
-        <v>26.18</v>
+        <v>26.14</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.32</v>
+        <v>-0.04</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.21</v>
+        <v>-0.15</v>
       </c>
       <c r="J25" t="n">
-        <v>26.14</v>
+        <v>26.4</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.04</v>
+        <v>0.26</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.15</v>
+        <v>0.99</v>
       </c>
       <c r="M25" t="n">
-        <v>26.4</v>
+        <v>27.58</v>
       </c>
       <c r="N25" t="n">
-        <v>0.26</v>
+        <v>1.18</v>
       </c>
       <c r="O25" t="n">
-        <v>0.99</v>
+        <v>4.47</v>
       </c>
       <c r="P25" t="n">
-        <v>26.4</v>
+        <v>27.58</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.26</v>
+        <v>1.18</v>
       </c>
       <c r="R25" t="n">
-        <v>0.99</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>32.06</v>
+        <v>32.88</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.04</v>
+        <v>0.82</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.14</v>
+        <v>2.56</v>
       </c>
       <c r="G26" t="n">
-        <v>32.88</v>
+        <v>33.86</v>
       </c>
       <c r="H26" t="n">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="I26" t="n">
-        <v>2.56</v>
+        <v>2.98</v>
       </c>
       <c r="J26" t="n">
-        <v>33.86</v>
+        <v>37.94</v>
       </c>
       <c r="K26" t="n">
-        <v>0.98</v>
+        <v>4.08</v>
       </c>
       <c r="L26" t="n">
-        <v>2.98</v>
+        <v>12.05</v>
       </c>
       <c r="M26" t="n">
-        <v>37.94</v>
+        <v>42.58</v>
       </c>
       <c r="N26" t="n">
-        <v>4.08</v>
+        <v>4.64</v>
       </c>
       <c r="O26" t="n">
-        <v>12.05</v>
+        <v>12.23</v>
       </c>
       <c r="P26" t="n">
-        <v>37.94</v>
+        <v>42.58</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.08</v>
+        <v>4.64</v>
       </c>
       <c r="R26" t="n">
-        <v>12.05</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>438.8</v>
+        <v>433.4</v>
       </c>
       <c r="E27" t="n">
-        <v>8.199999999999999</v>
+        <v>-5.4</v>
       </c>
       <c r="F27" t="n">
-        <v>1.9</v>
+        <v>-1.23</v>
       </c>
       <c r="G27" t="n">
-        <v>433.4</v>
+        <v>426</v>
       </c>
       <c r="H27" t="n">
-        <v>-5.4</v>
+        <v>-7.4</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.23</v>
+        <v>-1.71</v>
       </c>
       <c r="J27" t="n">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.4</v>
+        <v>-7</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.71</v>
+        <v>-1.64</v>
       </c>
       <c r="M27" t="n">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="N27" t="n">
-        <v>-7</v>
+        <v>11</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.64</v>
+        <v>2.63</v>
       </c>
       <c r="P27" t="n">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="Q27" t="n">
-        <v>-7</v>
+        <v>11</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.64</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>107.2</v>
+        <v>106.2</v>
       </c>
       <c r="E28" t="n">
-        <v>1.3</v>
+        <v>-1</v>
       </c>
       <c r="F28" t="n">
-        <v>1.23</v>
+        <v>-0.93</v>
       </c>
       <c r="G28" t="n">
-        <v>106.2</v>
+        <v>105.1</v>
       </c>
       <c r="H28" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.93</v>
+        <v>-1.04</v>
       </c>
       <c r="J28" t="n">
-        <v>105.1</v>
+        <v>109.3</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.1</v>
+        <v>4.2</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.04</v>
+        <v>4</v>
       </c>
       <c r="M28" t="n">
-        <v>109.3</v>
+        <v>112.6</v>
       </c>
       <c r="N28" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="P28" t="n">
-        <v>109.3</v>
+        <v>112.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>4</v>
+        <v>3.02</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>106.3</v>
+        <v>105.9</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="F29" t="n">
-        <v>0.28</v>
+        <v>-0.38</v>
       </c>
       <c r="G29" t="n">
-        <v>105.9</v>
+        <v>105</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.38</v>
+        <v>-0.85</v>
       </c>
       <c r="J29" t="n">
         <v>105</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.85</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>105</v>
+        <v>105.4</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="P29" t="n">
-        <v>105</v>
+        <v>105.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="30">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>74.75</v>
+        <v>74.45</v>
       </c>
       <c r="E30" t="n">
         <v>-0.3</v>
@@ -2260,40 +2260,40 @@
         <v>-0.4</v>
       </c>
       <c r="G30" t="n">
-        <v>74.45</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.3</v>
+        <v>-1.55</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.4</v>
+        <v>-2.08</v>
       </c>
       <c r="J30" t="n">
-        <v>72.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.55</v>
+        <v>0.3</v>
       </c>
       <c r="L30" t="n">
-        <v>-2.08</v>
+        <v>0.41</v>
       </c>
       <c r="M30" t="n">
-        <v>73.2</v>
+        <v>74</v>
       </c>
       <c r="N30" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="O30" t="n">
-        <v>0.41</v>
+        <v>1.09</v>
       </c>
       <c r="P30" t="n">
-        <v>73.2</v>
+        <v>74</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0.41</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>88.90000000000001</v>
+        <v>88.05</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.4</v>
+        <v>-0.85</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.45</v>
+        <v>-0.96</v>
       </c>
       <c r="G31" t="n">
-        <v>88.05</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.85</v>
+        <v>-0.7</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.96</v>
+        <v>-0.8</v>
       </c>
       <c r="J31" t="n">
-        <v>87.34999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.7</v>
+        <v>-0.15</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.8</v>
+        <v>-0.17</v>
       </c>
       <c r="M31" t="n">
-        <v>87.2</v>
+        <v>89</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.15</v>
+        <v>1.8</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.17</v>
+        <v>2.06</v>
       </c>
       <c r="P31" t="n">
-        <v>87.2</v>
+        <v>89</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.15</v>
+        <v>1.8</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.17</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>60.75</v>
+        <v>63.65</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.55</v>
+        <v>2.9</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.9</v>
+        <v>4.77</v>
       </c>
       <c r="G32" t="n">
-        <v>63.65</v>
+        <v>62.4</v>
       </c>
       <c r="H32" t="n">
-        <v>2.9</v>
+        <v>-1.25</v>
       </c>
       <c r="I32" t="n">
-        <v>4.77</v>
+        <v>-1.96</v>
       </c>
       <c r="J32" t="n">
-        <v>62.4</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.25</v>
+        <v>2.75</v>
       </c>
       <c r="L32" t="n">
-        <v>-1.96</v>
+        <v>4.41</v>
       </c>
       <c r="M32" t="n">
-        <v>65.15000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>2.75</v>
+        <v>0.45</v>
       </c>
       <c r="O32" t="n">
-        <v>4.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P32" t="n">
-        <v>65.15000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.75</v>
+        <v>0.45</v>
       </c>
       <c r="R32" t="n">
-        <v>4.41</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>79.05</v>
+        <v>79.2</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.15</v>
+        <v>0.15</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.43</v>
+        <v>0.19</v>
       </c>
       <c r="G33" t="n">
-        <v>79.2</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>0.15</v>
+        <v>1.95</v>
       </c>
       <c r="I33" t="n">
-        <v>0.19</v>
+        <v>2.46</v>
       </c>
       <c r="J33" t="n">
-        <v>81.15000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="K33" t="n">
-        <v>1.95</v>
+        <v>0.35</v>
       </c>
       <c r="L33" t="n">
-        <v>2.46</v>
+        <v>0.43</v>
       </c>
       <c r="M33" t="n">
-        <v>81.5</v>
+        <v>81.2</v>
       </c>
       <c r="N33" t="n">
-        <v>0.35</v>
+        <v>-0.3</v>
       </c>
       <c r="O33" t="n">
-        <v>0.43</v>
+        <v>-0.37</v>
       </c>
       <c r="P33" t="n">
-        <v>81.5</v>
+        <v>81.2</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.35</v>
+        <v>-0.3</v>
       </c>
       <c r="R33" t="n">
-        <v>0.43</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>29.8</v>
+        <v>29.66</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.78</v>
+        <v>-0.14</v>
       </c>
       <c r="F34" t="n">
-        <v>-2.55</v>
+        <v>-0.47</v>
       </c>
       <c r="G34" t="n">
-        <v>29.66</v>
+        <v>29.94</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.14</v>
+        <v>0.28</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.47</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>29.94</v>
+        <v>30.74</v>
       </c>
       <c r="K34" t="n">
-        <v>0.28</v>
+        <v>0.8</v>
       </c>
       <c r="L34" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.67</v>
       </c>
       <c r="M34" t="n">
-        <v>30.74</v>
+        <v>30.82</v>
       </c>
       <c r="N34" t="n">
-        <v>0.8</v>
+        <v>0.08</v>
       </c>
       <c r="O34" t="n">
-        <v>2.67</v>
+        <v>0.26</v>
       </c>
       <c r="P34" t="n">
-        <v>30.74</v>
+        <v>30.82</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.8</v>
+        <v>0.08</v>
       </c>
       <c r="R34" t="n">
-        <v>2.67</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="35">
@@ -2561,31 +2561,31 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.21</v>
+        <v>4.24</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.71</v>
+        <v>0.71</v>
       </c>
       <c r="G35" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="H35" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="I35" t="n">
-        <v>0.71</v>
+        <v>-0.47</v>
       </c>
       <c r="J35" t="n">
-        <v>4.22</v>
+        <v>4.32</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.02</v>
+        <v>0.1</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.47</v>
+        <v>2.37</v>
       </c>
       <c r="M35" t="n">
         <v>4.32</v>
@@ -2623,31 +2623,31 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.050000000000001</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.66</v>
+        <v>0.99</v>
       </c>
       <c r="G36" t="n">
-        <v>9.140000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="H36" t="n">
-        <v>0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="I36" t="n">
-        <v>0.99</v>
+        <v>-0.44</v>
       </c>
       <c r="J36" t="n">
-        <v>9.1</v>
+        <v>9.31</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.04</v>
+        <v>0.21</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.44</v>
+        <v>2.31</v>
       </c>
       <c r="M36" t="n">
         <v>9.31</v>
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>393.8</v>
+        <v>395.6</v>
       </c>
       <c r="E37" t="n">
-        <v>-3.6</v>
+        <v>1.8</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.91</v>
+        <v>0.46</v>
       </c>
       <c r="G37" t="n">
-        <v>395.6</v>
+        <v>388.6</v>
       </c>
       <c r="H37" t="n">
-        <v>1.8</v>
+        <v>-7</v>
       </c>
       <c r="I37" t="n">
-        <v>0.46</v>
+        <v>-1.77</v>
       </c>
       <c r="J37" t="n">
-        <v>388.6</v>
+        <v>388</v>
       </c>
       <c r="K37" t="n">
-        <v>-7</v>
+        <v>-0.6</v>
       </c>
       <c r="L37" t="n">
-        <v>-1.77</v>
+        <v>-0.15</v>
       </c>
       <c r="M37" t="n">
-        <v>388</v>
+        <v>391.2</v>
       </c>
       <c r="N37" t="n">
-        <v>-0.6</v>
+        <v>3.2</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.15</v>
+        <v>0.82</v>
       </c>
       <c r="P37" t="n">
-        <v>388</v>
+        <v>391.2</v>
       </c>
       <c r="Q37" t="n">
-        <v>-0.6</v>
+        <v>3.2</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.15</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.8</v>
+        <v>12.08</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.2</v>
+        <v>-0.72</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.54</v>
+        <v>-5.62</v>
       </c>
       <c r="G38" t="n">
-        <v>12.08</v>
+        <v>12.2</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.72</v>
+        <v>0.12</v>
       </c>
       <c r="I38" t="n">
-        <v>-5.62</v>
+        <v>0.99</v>
       </c>
       <c r="J38" t="n">
-        <v>12.2</v>
+        <v>12.24</v>
       </c>
       <c r="K38" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="L38" t="n">
-        <v>0.99</v>
+        <v>0.33</v>
       </c>
       <c r="M38" t="n">
-        <v>12.24</v>
+        <v>12.1</v>
       </c>
       <c r="N38" t="n">
-        <v>0.04</v>
+        <v>-0.14</v>
       </c>
       <c r="O38" t="n">
-        <v>0.33</v>
+        <v>-1.14</v>
       </c>
       <c r="P38" t="n">
-        <v>12.24</v>
+        <v>12.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.04</v>
+        <v>-0.14</v>
       </c>
       <c r="R38" t="n">
-        <v>0.33</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>516</v>
+        <v>501</v>
       </c>
       <c r="E39" t="n">
-        <v>-33</v>
+        <v>-15</v>
       </c>
       <c r="F39" t="n">
-        <v>-6.01</v>
+        <v>-2.91</v>
       </c>
       <c r="G39" t="n">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="H39" t="n">
-        <v>-15</v>
+        <v>6</v>
       </c>
       <c r="I39" t="n">
-        <v>-2.91</v>
+        <v>1.2</v>
       </c>
       <c r="J39" t="n">
         <v>507</v>
       </c>
       <c r="K39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>-0.59</v>
       </c>
       <c r="P39" t="n">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>40.38</v>
+        <v>40.42</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.64</v>
+        <v>0.04</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.9</v>
+        <v>0.1</v>
       </c>
       <c r="G40" t="n">
-        <v>40.42</v>
+        <v>41.18</v>
       </c>
       <c r="H40" t="n">
-        <v>0.04</v>
+        <v>0.76</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1</v>
+        <v>1.88</v>
       </c>
       <c r="J40" t="n">
-        <v>41.18</v>
+        <v>42.04</v>
       </c>
       <c r="K40" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="L40" t="n">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="M40" t="n">
-        <v>42.04</v>
+        <v>40.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0.86</v>
+        <v>-1.54</v>
       </c>
       <c r="O40" t="n">
-        <v>2.09</v>
+        <v>-3.66</v>
       </c>
       <c r="P40" t="n">
-        <v>42.04</v>
+        <v>40.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.86</v>
+        <v>-1.54</v>
       </c>
       <c r="R40" t="n">
-        <v>2.09</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="41">
@@ -2933,25 +2933,25 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31</v>
+        <v>31.18</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.85</v>
+        <v>0.18</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.67</v>
+        <v>0.58</v>
       </c>
       <c r="G41" t="n">
-        <v>31.18</v>
+        <v>31.28</v>
       </c>
       <c r="H41" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="I41" t="n">
-        <v>0.58</v>
+        <v>0.32</v>
       </c>
       <c r="J41" t="n">
-        <v>31.28</v>
+        <v>31.38</v>
       </c>
       <c r="K41" t="n">
         <v>0.1</v>
@@ -2960,22 +2960,22 @@
         <v>0.32</v>
       </c>
       <c r="M41" t="n">
-        <v>31.38</v>
+        <v>31.67</v>
       </c>
       <c r="N41" t="n">
-        <v>0.1</v>
+        <v>0.29</v>
       </c>
       <c r="O41" t="n">
-        <v>0.32</v>
+        <v>0.92</v>
       </c>
       <c r="P41" t="n">
-        <v>31.38</v>
+        <v>31.67</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.1</v>
+        <v>0.29</v>
       </c>
       <c r="R41" t="n">
-        <v>0.32</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>76.75</v>
+        <v>76.8</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.91</v>
+        <v>0.05</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.17</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G42" t="n">
-        <v>76.8</v>
+        <v>76.94</v>
       </c>
       <c r="H42" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="I42" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="J42" t="n">
-        <v>76.94</v>
+        <v>76.86</v>
       </c>
       <c r="K42" t="n">
-        <v>0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="L42" t="n">
-        <v>0.18</v>
+        <v>-0.1</v>
       </c>
       <c r="M42" t="n">
-        <v>76.86</v>
+        <v>77.36</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.08</v>
+        <v>0.5</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.1</v>
+        <v>0.65</v>
       </c>
       <c r="P42" t="n">
-        <v>76.86</v>
+        <v>77.36</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.08</v>
+        <v>0.5</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.1</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>41.33</v>
+        <v>41.21</v>
       </c>
       <c r="E43" t="n">
-        <v>-1</v>
+        <v>-0.12</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.36</v>
+        <v>-0.29</v>
       </c>
       <c r="G43" t="n">
-        <v>41.21</v>
+        <v>41.88</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.12</v>
+        <v>0.67</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.29</v>
+        <v>1.63</v>
       </c>
       <c r="J43" t="n">
-        <v>41.88</v>
+        <v>41.78</v>
       </c>
       <c r="K43" t="n">
-        <v>0.67</v>
+        <v>-0.1</v>
       </c>
       <c r="L43" t="n">
-        <v>1.63</v>
+        <v>-0.24</v>
       </c>
       <c r="M43" t="n">
-        <v>41.78</v>
+        <v>42.1</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.1</v>
+        <v>0.32</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.24</v>
+        <v>0.77</v>
       </c>
       <c r="P43" t="n">
-        <v>41.78</v>
+        <v>42.1</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.1</v>
+        <v>0.32</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.24</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="44">
@@ -3119,7 +3119,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6</v>
+        <v>5.95</v>
       </c>
       <c r="E44" t="n">
         <v>-0.05</v>
@@ -3128,40 +3128,40 @@
         <v>-0.83</v>
       </c>
       <c r="G44" t="n">
-        <v>5.95</v>
+        <v>5.93</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.83</v>
+        <v>-0.34</v>
       </c>
       <c r="J44" t="n">
-        <v>5.93</v>
+        <v>5.9</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.34</v>
+        <v>-0.51</v>
       </c>
       <c r="M44" t="n">
         <v>5.9</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>5.9</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="E45" t="n">
         <v>-0.01</v>
@@ -3190,40 +3190,40 @@
         <v>-0.47</v>
       </c>
       <c r="G45" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="H45" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="K45" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I45" t="n">
+      <c r="L45" t="n">
         <v>-0.47</v>
       </c>
-      <c r="J45" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0.95</v>
-      </c>
       <c r="M45" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.47</v>
+        <v>-3.3</v>
       </c>
       <c r="P45" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.47</v>
+        <v>-3.3</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.86</v>
+        <v>3.84</v>
       </c>
       <c r="E46" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="H46" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F46" t="n">
+      <c r="I46" t="n">
         <v>-0.26</v>
       </c>
-      <c r="G46" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="H46" t="n">
+      <c r="J46" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="K46" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I46" t="n">
+      <c r="L46" t="n">
         <v>-0.52</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="K46" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="L46" t="n">
-        <v>-0.26</v>
       </c>
       <c r="M46" t="n">
         <v>3.81</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
         <v>3.81</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.13</v>
+        <v>10.11</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.88</v>
+        <v>-0.2</v>
       </c>
       <c r="G47" t="n">
-        <v>10.11</v>
+        <v>10.19</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.2</v>
+        <v>0.79</v>
       </c>
       <c r="J47" t="n">
-        <v>10.19</v>
+        <v>10.43</v>
       </c>
       <c r="K47" t="n">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="L47" t="n">
-        <v>0.79</v>
+        <v>2.36</v>
       </c>
       <c r="M47" t="n">
-        <v>10.43</v>
+        <v>10.39</v>
       </c>
       <c r="N47" t="n">
-        <v>0.24</v>
+        <v>-0.04</v>
       </c>
       <c r="O47" t="n">
-        <v>2.36</v>
+        <v>-0.38</v>
       </c>
       <c r="P47" t="n">
-        <v>10.43</v>
+        <v>10.39</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.24</v>
+        <v>-0.04</v>
       </c>
       <c r="R47" t="n">
-        <v>2.36</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.315</v>
+        <v>0.31</v>
       </c>
       <c r="E48" t="n">
         <v>-0.005</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.56</v>
+        <v>-1.59</v>
       </c>
       <c r="G48" t="n">
-        <v>0.31</v>
+        <v>0.305</v>
       </c>
       <c r="H48" t="n">
         <v>-0.005</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.59</v>
+        <v>-1.61</v>
       </c>
       <c r="J48" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="M48" t="n">
         <v>0.305</v>
       </c>
-      <c r="K48" t="n">
+      <c r="N48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L48" t="n">
+      <c r="O48" t="n">
         <v>-1.61</v>
       </c>
-      <c r="M48" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="O48" t="n">
-        <v>1.64</v>
-      </c>
       <c r="P48" t="n">
-        <v>0.31</v>
+        <v>0.305</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>1.64</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.45</v>
+        <v>4.42</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.22</v>
+        <v>-0.67</v>
       </c>
       <c r="G49" t="n">
         <v>4.42</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.67</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>4.42</v>
+        <v>4.35</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>-1.58</v>
       </c>
       <c r="M49" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="O49" t="n">
-        <v>-1.58</v>
+        <v>-0.46</v>
       </c>
       <c r="P49" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="R49" t="n">
-        <v>-1.58</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="50">
@@ -3494,46 +3494,46 @@
         <v>1.12</v>
       </c>
       <c r="E50" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
       <c r="J50" t="n">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.89</v>
+        <v>-4.5</v>
       </c>
       <c r="M50" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="O50" t="n">
-        <v>-4.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P50" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="R50" t="n">
-        <v>-4.5</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.39</v>
+        <v>-0.79</v>
       </c>
       <c r="G51" t="n">
-        <v>5.05</v>
+        <v>5.14</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.79</v>
+        <v>1.78</v>
       </c>
       <c r="J51" t="n">
-        <v>5.14</v>
+        <v>5.17</v>
       </c>
       <c r="K51" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="L51" t="n">
-        <v>1.78</v>
+        <v>0.58</v>
       </c>
       <c r="M51" t="n">
-        <v>5.17</v>
+        <v>5.22</v>
       </c>
       <c r="N51" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="O51" t="n">
-        <v>0.58</v>
+        <v>0.97</v>
       </c>
       <c r="P51" t="n">
-        <v>5.17</v>
+        <v>5.22</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="R51" t="n">
-        <v>0.58</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.13</v>
+        <v>-0.1</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.15</v>
+        <v>-0.89</v>
       </c>
       <c r="G52" t="n">
-        <v>11.1</v>
+        <v>11.12</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.89</v>
+        <v>0.18</v>
       </c>
       <c r="J52" t="n">
-        <v>11.12</v>
+        <v>11.03</v>
       </c>
       <c r="K52" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="L52" t="n">
-        <v>0.18</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M52" t="n">
-        <v>11.03</v>
+        <v>11.07</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="P52" t="n">
-        <v>11.03</v>
+        <v>11.07</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J53" t="n">
         <v>8.050000000000001</v>
       </c>
-      <c r="E53" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-1.23</v>
-      </c>
-      <c r="G53" t="n">
-        <v>8.029999999999999</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I53" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="J53" t="n">
-        <v>8.140000000000001</v>
-      </c>
       <c r="K53" t="n">
-        <v>0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="L53" t="n">
-        <v>1.37</v>
+        <v>-1.11</v>
       </c>
       <c r="M53" t="n">
-        <v>8.050000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="O53" t="n">
-        <v>-1.11</v>
+        <v>0.5</v>
       </c>
       <c r="P53" t="n">
-        <v>8.050000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="R53" t="n">
-        <v>-1.11</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="54">
@@ -3739,22 +3739,22 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.445</v>
+        <v>0.44</v>
       </c>
       <c r="E54" t="n">
         <v>-0.005</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.11</v>
+        <v>-1.12</v>
       </c>
       <c r="G54" t="n">
         <v>0.44</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.12</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0.44</v>
@@ -3766,22 +3766,22 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>-2.27</v>
       </c>
       <c r="P54" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="55">
@@ -3810,40 +3810,40 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="J55" t="n">
         <v>0.615</v>
       </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.62</v>
-      </c>
       <c r="K55" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M55" t="n">
         <v>0.615</v>
       </c>
       <c r="N55" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
         <v>0.615</v>
       </c>
       <c r="Q55" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F56" t="n">
-        <v>-4.88</v>
+        <v>2.56</v>
       </c>
       <c r="G56" t="n">
-        <v>0.4</v>
+        <v>0.395</v>
       </c>
       <c r="H56" t="n">
-        <v>0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="I56" t="n">
-        <v>2.56</v>
+        <v>-1.25</v>
       </c>
       <c r="J56" t="n">
         <v>0.395</v>
       </c>
       <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="N56" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L56" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
       <c r="P56" t="n">
-        <v>0.395</v>
+        <v>0.39</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.54</v>
+        <v>0.27</v>
       </c>
       <c r="G57" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="H57" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I57" t="n">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="J57" t="n">
-        <v>3.73</v>
+        <v>3.68</v>
       </c>
       <c r="K57" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="L57" t="n">
-        <v>0.54</v>
+        <v>-1.34</v>
       </c>
       <c r="M57" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="O57" t="n">
-        <v>-1.34</v>
+        <v>-0.82</v>
       </c>
       <c r="P57" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="R57" t="n">
-        <v>-1.34</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.075</v>
+        <v>0.076</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.32</v>
+        <v>1.33</v>
       </c>
       <c r="G58" t="n">
         <v>0.076</v>
       </c>
       <c r="H58" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="M58" t="n">
         <v>0.076</v>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.074</v>
-      </c>
       <c r="N58" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="O58" t="n">
-        <v>-2.63</v>
+        <v>2.7</v>
       </c>
       <c r="P58" t="n">
-        <v>0.074</v>
+        <v>0.076</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="R58" t="n">
-        <v>-2.63</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22.53</v>
+        <v>22.38</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.38</v>
+        <v>-0.15</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.66</v>
+        <v>-0.67</v>
       </c>
       <c r="G59" t="n">
-        <v>22.38</v>
+        <v>22.27</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.15</v>
+        <v>-0.11</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.67</v>
+        <v>-0.49</v>
       </c>
       <c r="J59" t="n">
-        <v>22.27</v>
+        <v>22.2</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.49</v>
+        <v>-0.31</v>
       </c>
       <c r="M59" t="n">
-        <v>22.2</v>
+        <v>22.32</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.31</v>
+        <v>0.54</v>
       </c>
       <c r="P59" t="n">
-        <v>22.2</v>
+        <v>22.32</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="R59" t="n">
-        <v>-0.31</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="E60" t="n">
         <v>0.01</v>
@@ -4123,22 +4123,22 @@
         <v>3.12</v>
       </c>
       <c r="H60" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="M60" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="N60" t="n">
         <v>-0.01</v>
@@ -4147,7 +4147,7 @@
         <v>-0.32</v>
       </c>
       <c r="P60" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="Q60" t="n">
         <v>-0.01</v>
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="G61" t="n">
         <v>0.875</v>
       </c>
-      <c r="E61" t="n">
+      <c r="H61" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-1.69</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="N61" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F61" t="n">
-        <v>-1.13</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="I61" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="K61" t="n">
-        <v>-0.015</v>
-      </c>
-      <c r="L61" t="n">
-        <v>-1.69</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0.005</v>
-      </c>
       <c r="O61" t="n">
-        <v>0.57</v>
+        <v>-1.14</v>
       </c>
       <c r="P61" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.005</v>
+        <v>-0.01</v>
       </c>
       <c r="R61" t="n">
-        <v>0.57</v>
+        <v>-1.14</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-16 Close</t>
+          <t>2026-09-17 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-09-16 Change</t>
+          <t>2026-09-17 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-16 Change %</t>
+          <t>2026-09-17 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-09-17 Close</t>
+          <t>2026-09-18 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-09-17 Change</t>
+          <t>2026-09-18 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-09-17 Change %</t>
+          <t>2026-09-18 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-09-18 Close</t>
+          <t>2026-09-21 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-09-18 Change</t>
+          <t>2026-09-21 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-09-18 Change %</t>
+          <t>2026-09-21 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-09-21 Close</t>
+          <t>2026-09-22 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-09-21 Change</t>
+          <t>2026-09-22 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-09-21 Change %</t>
+          <t>2026-09-22 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-09-22 Close</t>
+          <t>2026-09-23 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-09-22 Change</t>
+          <t>2026-09-23 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-09-22 Change %</t>
+          <t>2026-09-23 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>160.9</v>
+        <v>159.8</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3</v>
+        <v>-1.1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.68</v>
       </c>
       <c r="G3" t="n">
-        <v>159.8</v>
+        <v>161.6</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.1</v>
+        <v>1.8</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.68</v>
+        <v>1.13</v>
       </c>
       <c r="J3" t="n">
-        <v>161.6</v>
+        <v>161.5</v>
       </c>
       <c r="K3" t="n">
-        <v>1.8</v>
+        <v>-0.1</v>
       </c>
       <c r="L3" t="n">
-        <v>1.13</v>
+        <v>-0.06</v>
       </c>
       <c r="M3" t="n">
-        <v>161.5</v>
+        <v>159.3</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1</v>
+        <v>-2.2</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.06</v>
+        <v>-1.36</v>
       </c>
       <c r="P3" t="n">
-        <v>161.5</v>
+        <v>159.3</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1</v>
+        <v>-2.2</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.06</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>244</v>
+        <v>243.4</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>-0.6</v>
       </c>
       <c r="F4" t="n">
-        <v>2.52</v>
+        <v>-0.25</v>
       </c>
       <c r="G4" t="n">
-        <v>243.4</v>
+        <v>245</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6</v>
+        <v>1.6</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.25</v>
+        <v>0.66</v>
       </c>
       <c r="J4" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
-        <v>0.66</v>
+        <v>0.41</v>
       </c>
       <c r="M4" t="n">
-        <v>246</v>
+        <v>239.4</v>
       </c>
       <c r="N4" t="n">
-        <v>1</v>
+        <v>-6.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0.41</v>
+        <v>-2.68</v>
       </c>
       <c r="P4" t="n">
-        <v>246</v>
+        <v>239.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>-6.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0.41</v>
+        <v>-2.68</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.36</v>
+        <v>6.32</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="F5" t="n">
-        <v>0.79</v>
+        <v>-0.63</v>
       </c>
       <c r="G5" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.63</v>
+        <v>-0.32</v>
       </c>
       <c r="J5" t="n">
-        <v>6.3</v>
+        <v>6.51</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.02</v>
+        <v>0.21</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.32</v>
+        <v>3.33</v>
       </c>
       <c r="M5" t="n">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0.21</v>
+        <v>-0.01</v>
       </c>
       <c r="O5" t="n">
-        <v>3.33</v>
+        <v>-0.15</v>
       </c>
       <c r="P5" t="n">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.21</v>
+        <v>-0.01</v>
       </c>
       <c r="R5" t="n">
-        <v>3.33</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.53</v>
+        <v>7.52</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="F6" t="n">
-        <v>0.53</v>
+        <v>-0.13</v>
       </c>
       <c r="G6" t="n">
-        <v>7.52</v>
+        <v>7.5</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.13</v>
+        <v>-0.27</v>
       </c>
       <c r="J6" t="n">
-        <v>7.5</v>
+        <v>7.58</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.27</v>
+        <v>1.07</v>
       </c>
       <c r="M6" t="n">
-        <v>7.58</v>
+        <v>7.54</v>
       </c>
       <c r="N6" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="O6" t="n">
-        <v>1.07</v>
+        <v>-0.53</v>
       </c>
       <c r="P6" t="n">
-        <v>7.58</v>
+        <v>7.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="R6" t="n">
-        <v>1.07</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.98</v>
+        <v>5.99</v>
       </c>
       <c r="E7" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="G7" t="n">
         <v>5.99</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>5.99</v>
+        <v>6.06</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M7" t="n">
-        <v>6.06</v>
+        <v>6.02</v>
       </c>
       <c r="N7" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="O7" t="n">
-        <v>1.17</v>
+        <v>-0.66</v>
       </c>
       <c r="P7" t="n">
-        <v>6.06</v>
+        <v>6.02</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="R7" t="n">
-        <v>1.17</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.640000000000001</v>
+        <v>9.68</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F8" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="G8" t="n">
-        <v>9.68</v>
+        <v>9.59</v>
       </c>
       <c r="H8" t="n">
-        <v>0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="I8" t="n">
-        <v>0.41</v>
+        <v>-0.93</v>
       </c>
       <c r="J8" t="n">
-        <v>9.59</v>
+        <v>9.76</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.09</v>
+        <v>0.17</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.93</v>
+        <v>1.77</v>
       </c>
       <c r="M8" t="n">
-        <v>9.76</v>
+        <v>9.74</v>
       </c>
       <c r="N8" t="n">
-        <v>0.17</v>
+        <v>-0.02</v>
       </c>
       <c r="O8" t="n">
-        <v>1.77</v>
+        <v>-0.2</v>
       </c>
       <c r="P8" t="n">
-        <v>9.76</v>
+        <v>9.74</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.17</v>
+        <v>-0.02</v>
       </c>
       <c r="R8" t="n">
-        <v>1.77</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.119999999999999</v>
+        <v>8.18</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="F9" t="n">
-        <v>1.25</v>
+        <v>0.74</v>
       </c>
       <c r="G9" t="n">
-        <v>8.18</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="I9" t="n">
-        <v>0.74</v>
+        <v>-0.49</v>
       </c>
       <c r="J9" t="n">
-        <v>8.140000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.04</v>
+        <v>0.12</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.49</v>
+        <v>1.47</v>
       </c>
       <c r="M9" t="n">
-        <v>8.26</v>
+        <v>8.24</v>
       </c>
       <c r="N9" t="n">
-        <v>0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="O9" t="n">
-        <v>1.47</v>
+        <v>-0.24</v>
       </c>
       <c r="P9" t="n">
-        <v>8.26</v>
+        <v>8.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.47</v>
+        <v>-0.24</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51.35</v>
+        <v>51.3</v>
       </c>
       <c r="E10" t="n">
-        <v>0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="F10" t="n">
-        <v>0.29</v>
+        <v>-0.1</v>
       </c>
       <c r="G10" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="J10" t="n">
-        <v>51.2</v>
+        <v>52.1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.19</v>
+        <v>1.76</v>
       </c>
       <c r="M10" t="n">
-        <v>52.1</v>
+        <v>51.65</v>
       </c>
       <c r="N10" t="n">
-        <v>0.9</v>
+        <v>-0.45</v>
       </c>
       <c r="O10" t="n">
-        <v>1.76</v>
+        <v>-0.86</v>
       </c>
       <c r="P10" t="n">
-        <v>52.1</v>
+        <v>51.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.9</v>
+        <v>-0.45</v>
       </c>
       <c r="R10" t="n">
-        <v>1.76</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.61</v>
+        <v>4.51</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.43</v>
+        <v>-2.17</v>
       </c>
       <c r="G11" t="n">
         <v>4.51</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.17</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>4.51</v>
+        <v>4.49</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="M11" t="n">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="N11" t="n">
         <v>-0.02</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
       <c r="P11" t="n">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.02</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.789999999999999</v>
+        <v>9.56</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.19</v>
+        <v>-0.23</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9</v>
+        <v>-2.35</v>
       </c>
       <c r="G12" t="n">
-        <v>9.56</v>
+        <v>9.49</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.23</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.35</v>
+        <v>-0.73</v>
       </c>
       <c r="J12" t="n">
-        <v>9.49</v>
+        <v>9.51</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.73</v>
+        <v>0.21</v>
       </c>
       <c r="M12" t="n">
-        <v>9.51</v>
+        <v>9.43</v>
       </c>
       <c r="N12" t="n">
-        <v>0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="O12" t="n">
-        <v>0.21</v>
+        <v>-0.84</v>
       </c>
       <c r="P12" t="n">
-        <v>9.51</v>
+        <v>9.43</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="R12" t="n">
-        <v>0.21</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24.36</v>
+        <v>23.88</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.12</v>
+        <v>-0.48</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.49</v>
+        <v>-1.97</v>
       </c>
       <c r="G13" t="n">
-        <v>23.88</v>
+        <v>23.6</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.48</v>
+        <v>-0.28</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.97</v>
+        <v>-1.17</v>
       </c>
       <c r="J13" t="n">
-        <v>23.6</v>
+        <v>23.94</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.28</v>
+        <v>0.34</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.17</v>
+        <v>1.44</v>
       </c>
       <c r="M13" t="n">
-        <v>23.94</v>
+        <v>23.68</v>
       </c>
       <c r="N13" t="n">
-        <v>0.34</v>
+        <v>-0.26</v>
       </c>
       <c r="O13" t="n">
-        <v>1.44</v>
+        <v>-1.09</v>
       </c>
       <c r="P13" t="n">
-        <v>23.94</v>
+        <v>23.68</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.34</v>
+        <v>-0.26</v>
       </c>
       <c r="R13" t="n">
-        <v>1.44</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="G14" t="n">
         <v>1.92</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-1.04</v>
       </c>
       <c r="M14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.04</v>
+        <v>-0.53</v>
       </c>
       <c r="P14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.04</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.11</v>
+        <v>5.07</v>
       </c>
       <c r="E15" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.78</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.19</v>
+      </c>
+      <c r="N15" t="n">
         <v>-0.06</v>
       </c>
-      <c r="F15" t="n">
-        <v>-1.16</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-0.78</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5.13</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L15" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.12</v>
-      </c>
       <c r="O15" t="n">
-        <v>2.34</v>
+        <v>-1.14</v>
       </c>
       <c r="P15" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="R15" t="n">
-        <v>2.34</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="16">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.44</v>
+        <v>4.45</v>
       </c>
       <c r="E16" t="n">
         <v>0.01</v>
@@ -1392,40 +1392,40 @@
         <v>0.23</v>
       </c>
       <c r="G16" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="H16" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="I16" t="n">
-        <v>0.23</v>
+        <v>-0.45</v>
       </c>
       <c r="J16" t="n">
         <v>4.43</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.43</v>
+        <v>4.39</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="P16" t="n">
-        <v>4.43</v>
+        <v>4.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="17">
@@ -1445,16 +1445,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.35</v>
+        <v>3.33</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="G17" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="H17" t="n">
         <v>-0.02</v>
@@ -1466,28 +1466,28 @@
         <v>3.31</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.91</v>
       </c>
       <c r="P17" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.09</v>
+        <v>3.02</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-2.27</v>
       </c>
       <c r="G18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="J18" t="n">
         <v>3.02</v>
       </c>
-      <c r="H18" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-2.27</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.98</v>
-      </c>
       <c r="K18" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.32</v>
+        <v>1.34</v>
       </c>
       <c r="M18" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="N18" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="O18" t="n">
-        <v>1.34</v>
+        <v>-1.66</v>
       </c>
       <c r="P18" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>52.8</v>
+        <v>52.85</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.25</v>
+        <v>0.05</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.47</v>
+        <v>0.09</v>
       </c>
       <c r="G19" t="n">
-        <v>52.85</v>
+        <v>53.2</v>
       </c>
       <c r="H19" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="I19" t="n">
-        <v>0.09</v>
+        <v>0.66</v>
       </c>
       <c r="J19" t="n">
-        <v>53.2</v>
+        <v>53.75</v>
       </c>
       <c r="K19" t="n">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="L19" t="n">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="M19" t="n">
-        <v>53.75</v>
+        <v>53.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.55</v>
+        <v>0.15</v>
       </c>
       <c r="O19" t="n">
-        <v>1.03</v>
+        <v>0.28</v>
       </c>
       <c r="P19" t="n">
-        <v>53.75</v>
+        <v>53.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.55</v>
+        <v>0.15</v>
       </c>
       <c r="R19" t="n">
-        <v>1.03</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.54</v>
+        <v>28.64</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.42</v>
+        <v>0.1</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.45</v>
+        <v>0.35</v>
       </c>
       <c r="G20" t="n">
-        <v>28.64</v>
+        <v>29.38</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1</v>
+        <v>0.74</v>
       </c>
       <c r="I20" t="n">
-        <v>0.35</v>
+        <v>2.58</v>
       </c>
       <c r="J20" t="n">
-        <v>29.38</v>
+        <v>29.08</v>
       </c>
       <c r="K20" t="n">
-        <v>0.74</v>
+        <v>-0.3</v>
       </c>
       <c r="L20" t="n">
-        <v>2.58</v>
+        <v>-1.02</v>
       </c>
       <c r="M20" t="n">
-        <v>29.08</v>
+        <v>29.7</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3</v>
+        <v>0.62</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.02</v>
+        <v>2.13</v>
       </c>
       <c r="P20" t="n">
-        <v>29.08</v>
+        <v>29.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.3</v>
+        <v>0.62</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.02</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.53</v>
+        <v>4.49</v>
       </c>
       <c r="E21" t="n">
-        <v>0.04</v>
+        <v>-0.04</v>
       </c>
       <c r="F21" t="n">
-        <v>0.89</v>
+        <v>-0.88</v>
       </c>
       <c r="G21" t="n">
-        <v>4.49</v>
+        <v>4.43</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.88</v>
+        <v>-1.34</v>
       </c>
       <c r="J21" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="M21" t="n">
         <v>4.43</v>
       </c>
-      <c r="K21" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="L21" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4.41</v>
-      </c>
       <c r="N21" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.45</v>
+        <v>0.45</v>
       </c>
       <c r="P21" t="n">
-        <v>4.41</v>
+        <v>4.43</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.45</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="22">
@@ -1755,16 +1755,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79.34999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3</v>
+        <v>-0.15</v>
       </c>
       <c r="F22" t="n">
-        <v>0.38</v>
+        <v>-0.19</v>
       </c>
       <c r="G22" t="n">
-        <v>79.2</v>
+        <v>79.05</v>
       </c>
       <c r="H22" t="n">
         <v>-0.15</v>
@@ -1773,31 +1773,31 @@
         <v>-0.19</v>
       </c>
       <c r="J22" t="n">
-        <v>79.05</v>
+        <v>79.2</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.19</v>
+        <v>0.19</v>
       </c>
       <c r="M22" t="n">
-        <v>79.2</v>
+        <v>78.95</v>
       </c>
       <c r="N22" t="n">
-        <v>0.15</v>
+        <v>-0.25</v>
       </c>
       <c r="O22" t="n">
-        <v>0.19</v>
+        <v>-0.32</v>
       </c>
       <c r="P22" t="n">
-        <v>79.2</v>
+        <v>78.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.15</v>
+        <v>-0.25</v>
       </c>
       <c r="R22" t="n">
-        <v>0.19</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22.62</v>
+        <v>22.44</v>
       </c>
       <c r="E23" t="n">
-        <v>0.16</v>
+        <v>-0.18</v>
       </c>
       <c r="F23" t="n">
-        <v>0.71</v>
+        <v>-0.8</v>
       </c>
       <c r="G23" t="n">
-        <v>22.44</v>
+        <v>22.84</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.18</v>
+        <v>0.4</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8</v>
+        <v>1.78</v>
       </c>
       <c r="J23" t="n">
-        <v>22.84</v>
+        <v>23.54</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="L23" t="n">
-        <v>1.78</v>
+        <v>3.06</v>
       </c>
       <c r="M23" t="n">
-        <v>23.54</v>
+        <v>23.24</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="O23" t="n">
-        <v>3.06</v>
+        <v>-1.27</v>
       </c>
       <c r="P23" t="n">
-        <v>23.54</v>
+        <v>23.24</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="R23" t="n">
-        <v>3.06</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.95</v>
+        <v>15.88</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.44</v>
+        <v>-0.44</v>
       </c>
       <c r="G24" t="n">
-        <v>15.88</v>
+        <v>16.42</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.44</v>
+        <v>3.4</v>
       </c>
       <c r="J24" t="n">
-        <v>16.42</v>
+        <v>16.21</v>
       </c>
       <c r="K24" t="n">
-        <v>0.54</v>
+        <v>-0.21</v>
       </c>
       <c r="L24" t="n">
-        <v>3.4</v>
+        <v>-1.28</v>
       </c>
       <c r="M24" t="n">
-        <v>16.21</v>
+        <v>15.86</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.21</v>
+        <v>-0.35</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.28</v>
+        <v>-2.16</v>
       </c>
       <c r="P24" t="n">
-        <v>16.21</v>
+        <v>15.86</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.21</v>
+        <v>-0.35</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.28</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.18</v>
+        <v>26.14</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.32</v>
+        <v>-0.04</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.21</v>
+        <v>-0.15</v>
       </c>
       <c r="G25" t="n">
-        <v>26.14</v>
+        <v>26.4</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.04</v>
+        <v>0.26</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.15</v>
+        <v>0.99</v>
       </c>
       <c r="J25" t="n">
-        <v>26.4</v>
+        <v>27.58</v>
       </c>
       <c r="K25" t="n">
-        <v>0.26</v>
+        <v>1.18</v>
       </c>
       <c r="L25" t="n">
-        <v>0.99</v>
+        <v>4.47</v>
       </c>
       <c r="M25" t="n">
-        <v>27.58</v>
+        <v>27.2</v>
       </c>
       <c r="N25" t="n">
-        <v>1.18</v>
+        <v>-0.38</v>
       </c>
       <c r="O25" t="n">
-        <v>4.47</v>
+        <v>-1.38</v>
       </c>
       <c r="P25" t="n">
-        <v>27.58</v>
+        <v>27.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.18</v>
+        <v>-0.38</v>
       </c>
       <c r="R25" t="n">
-        <v>4.47</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>32.88</v>
+        <v>33.86</v>
       </c>
       <c r="E26" t="n">
-        <v>0.82</v>
+        <v>0.98</v>
       </c>
       <c r="F26" t="n">
-        <v>2.56</v>
+        <v>2.98</v>
       </c>
       <c r="G26" t="n">
-        <v>33.86</v>
+        <v>37.94</v>
       </c>
       <c r="H26" t="n">
-        <v>0.98</v>
+        <v>4.08</v>
       </c>
       <c r="I26" t="n">
-        <v>2.98</v>
+        <v>12.05</v>
       </c>
       <c r="J26" t="n">
-        <v>37.94</v>
+        <v>42.58</v>
       </c>
       <c r="K26" t="n">
-        <v>4.08</v>
+        <v>4.64</v>
       </c>
       <c r="L26" t="n">
-        <v>12.05</v>
+        <v>12.23</v>
       </c>
       <c r="M26" t="n">
-        <v>42.58</v>
+        <v>42.9</v>
       </c>
       <c r="N26" t="n">
-        <v>4.64</v>
+        <v>0.32</v>
       </c>
       <c r="O26" t="n">
-        <v>12.23</v>
+        <v>0.75</v>
       </c>
       <c r="P26" t="n">
-        <v>42.58</v>
+        <v>42.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.64</v>
+        <v>0.32</v>
       </c>
       <c r="R26" t="n">
-        <v>12.23</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>433.4</v>
+        <v>426</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.4</v>
+        <v>-7.4</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.23</v>
+        <v>-1.71</v>
       </c>
       <c r="G27" t="n">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="H27" t="n">
-        <v>-7.4</v>
+        <v>-7</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.71</v>
+        <v>-1.64</v>
       </c>
       <c r="J27" t="n">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="K27" t="n">
-        <v>-7</v>
+        <v>11</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.64</v>
+        <v>2.63</v>
       </c>
       <c r="M27" t="n">
-        <v>430</v>
+        <v>451.6</v>
       </c>
       <c r="N27" t="n">
-        <v>11</v>
+        <v>21.6</v>
       </c>
       <c r="O27" t="n">
-        <v>2.63</v>
+        <v>5.02</v>
       </c>
       <c r="P27" t="n">
-        <v>430</v>
+        <v>451.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>11</v>
+        <v>21.6</v>
       </c>
       <c r="R27" t="n">
-        <v>2.63</v>
+        <v>5.02</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>106.2</v>
+        <v>105.1</v>
       </c>
       <c r="E28" t="n">
-        <v>-1</v>
+        <v>-1.1</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.93</v>
+        <v>-1.04</v>
       </c>
       <c r="G28" t="n">
-        <v>105.1</v>
+        <v>109.3</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.1</v>
+        <v>4.2</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.04</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
-        <v>109.3</v>
+        <v>112.6</v>
       </c>
       <c r="K28" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="L28" t="n">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="M28" t="n">
-        <v>112.6</v>
+        <v>114.8</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="O28" t="n">
-        <v>3.02</v>
+        <v>1.95</v>
       </c>
       <c r="P28" t="n">
-        <v>112.6</v>
+        <v>114.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="R28" t="n">
-        <v>3.02</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>105.9</v>
+        <v>105</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.38</v>
+        <v>-0.85</v>
       </c>
       <c r="G29" t="n">
         <v>105</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.85</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>105</v>
+        <v>105.4</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="M29" t="n">
-        <v>105.4</v>
+        <v>106.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="O29" t="n">
-        <v>0.38</v>
+        <v>1.04</v>
       </c>
       <c r="P29" t="n">
-        <v>105.4</v>
+        <v>106.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="R29" t="n">
-        <v>0.38</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>74.45</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.3</v>
+        <v>-1.55</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.4</v>
+        <v>-2.08</v>
       </c>
       <c r="G30" t="n">
-        <v>72.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.55</v>
+        <v>0.3</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.08</v>
+        <v>0.41</v>
       </c>
       <c r="J30" t="n">
+        <v>74</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="M30" t="n">
         <v>73.2</v>
       </c>
-      <c r="K30" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L30" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="M30" t="n">
-        <v>74</v>
-      </c>
       <c r="N30" t="n">
-        <v>0.8</v>
+        <v>-0.8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.09</v>
+        <v>-1.08</v>
       </c>
       <c r="P30" t="n">
-        <v>74</v>
+        <v>73.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.8</v>
+        <v>-0.8</v>
       </c>
       <c r="R30" t="n">
-        <v>1.09</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>88.05</v>
+        <v>87.34999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.85</v>
+        <v>-0.7</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.96</v>
+        <v>-0.8</v>
       </c>
       <c r="G31" t="n">
-        <v>87.34999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.7</v>
+        <v>-0.15</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.8</v>
+        <v>-0.17</v>
       </c>
       <c r="J31" t="n">
-        <v>87.2</v>
+        <v>89</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.15</v>
+        <v>1.8</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.17</v>
+        <v>2.06</v>
       </c>
       <c r="M31" t="n">
-        <v>89</v>
+        <v>89.5</v>
       </c>
       <c r="N31" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="O31" t="n">
-        <v>2.06</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P31" t="n">
-        <v>89</v>
+        <v>89.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="R31" t="n">
-        <v>2.06</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>63.65</v>
+        <v>62.4</v>
       </c>
       <c r="E32" t="n">
-        <v>2.9</v>
+        <v>-1.25</v>
       </c>
       <c r="F32" t="n">
-        <v>4.77</v>
+        <v>-1.96</v>
       </c>
       <c r="G32" t="n">
-        <v>62.4</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.25</v>
+        <v>2.75</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.96</v>
+        <v>4.41</v>
       </c>
       <c r="J32" t="n">
-        <v>65.15000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>2.75</v>
+        <v>0.45</v>
       </c>
       <c r="L32" t="n">
-        <v>4.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>65.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="N32" t="n">
-        <v>0.45</v>
+        <v>-1.3</v>
       </c>
       <c r="O32" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.98</v>
       </c>
       <c r="P32" t="n">
-        <v>65.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.45</v>
+        <v>-1.3</v>
       </c>
       <c r="R32" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.98</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>79.2</v>
+        <v>81.15000000000001</v>
       </c>
       <c r="E33" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="F33" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="G33" t="n">
+        <v>81.5</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J33" t="n">
+        <v>81.2</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="M33" t="n">
+        <v>81.34999999999999</v>
+      </c>
+      <c r="N33" t="n">
         <v>0.15</v>
       </c>
-      <c r="F33" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G33" t="n">
-        <v>81.15000000000001</v>
-      </c>
-      <c r="H33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="I33" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="J33" t="n">
-        <v>81.5</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="M33" t="n">
-        <v>81.2</v>
-      </c>
-      <c r="N33" t="n">
-        <v>-0.3</v>
-      </c>
       <c r="O33" t="n">
-        <v>-0.37</v>
+        <v>0.18</v>
       </c>
       <c r="P33" t="n">
-        <v>81.2</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.3</v>
+        <v>0.15</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.37</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>29.66</v>
+        <v>29.94</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.14</v>
+        <v>0.28</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.47</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G34" t="n">
-        <v>29.94</v>
+        <v>30.74</v>
       </c>
       <c r="H34" t="n">
-        <v>0.28</v>
+        <v>0.8</v>
       </c>
       <c r="I34" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.67</v>
       </c>
       <c r="J34" t="n">
-        <v>30.74</v>
+        <v>30.82</v>
       </c>
       <c r="K34" t="n">
-        <v>0.8</v>
+        <v>0.08</v>
       </c>
       <c r="L34" t="n">
-        <v>2.67</v>
+        <v>0.26</v>
       </c>
       <c r="M34" t="n">
-        <v>30.82</v>
+        <v>31.22</v>
       </c>
       <c r="N34" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="O34" t="n">
-        <v>0.26</v>
+        <v>1.3</v>
       </c>
       <c r="P34" t="n">
-        <v>30.82</v>
+        <v>31.22</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="R34" t="n">
-        <v>0.26</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.24</v>
+        <v>4.22</v>
       </c>
       <c r="E35" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="F35" t="n">
-        <v>0.71</v>
+        <v>-0.47</v>
       </c>
       <c r="G35" t="n">
-        <v>4.22</v>
+        <v>4.32</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.02</v>
+        <v>0.1</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.47</v>
+        <v>2.37</v>
       </c>
       <c r="J35" t="n">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="K35" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="L35" t="n">
-        <v>2.37</v>
+        <v>0.46</v>
       </c>
       <c r="M35" t="n">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="N35" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="O35" t="n">
-        <v>2.37</v>
+        <v>0.46</v>
       </c>
       <c r="P35" t="n">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="R35" t="n">
-        <v>2.37</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.140000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="E36" t="n">
-        <v>0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="F36" t="n">
-        <v>0.99</v>
+        <v>-0.44</v>
       </c>
       <c r="G36" t="n">
-        <v>9.1</v>
+        <v>9.31</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.04</v>
+        <v>0.21</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.44</v>
+        <v>2.31</v>
       </c>
       <c r="J36" t="n">
-        <v>9.31</v>
+        <v>9.34</v>
       </c>
       <c r="K36" t="n">
-        <v>0.21</v>
+        <v>0.03</v>
       </c>
       <c r="L36" t="n">
-        <v>2.31</v>
+        <v>0.32</v>
       </c>
       <c r="M36" t="n">
-        <v>9.31</v>
+        <v>9.34</v>
       </c>
       <c r="N36" t="n">
-        <v>0.21</v>
+        <v>0.03</v>
       </c>
       <c r="O36" t="n">
-        <v>2.31</v>
+        <v>0.32</v>
       </c>
       <c r="P36" t="n">
-        <v>9.31</v>
+        <v>9.34</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.21</v>
+        <v>0.03</v>
       </c>
       <c r="R36" t="n">
-        <v>2.31</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>395.6</v>
+        <v>388.6</v>
       </c>
       <c r="E37" t="n">
-        <v>1.8</v>
+        <v>-7</v>
       </c>
       <c r="F37" t="n">
-        <v>0.46</v>
+        <v>-1.77</v>
       </c>
       <c r="G37" t="n">
-        <v>388.6</v>
+        <v>388</v>
       </c>
       <c r="H37" t="n">
-        <v>-7</v>
+        <v>-0.6</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.77</v>
+        <v>-0.15</v>
       </c>
       <c r="J37" t="n">
-        <v>388</v>
+        <v>391.2</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.6</v>
+        <v>3.2</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.15</v>
+        <v>0.82</v>
       </c>
       <c r="M37" t="n">
-        <v>391.2</v>
+        <v>397.4</v>
       </c>
       <c r="N37" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="O37" t="n">
-        <v>0.82</v>
+        <v>1.58</v>
       </c>
       <c r="P37" t="n">
-        <v>391.2</v>
+        <v>397.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0.82</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.08</v>
+        <v>12.2</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.72</v>
+        <v>0.12</v>
       </c>
       <c r="F38" t="n">
-        <v>-5.62</v>
+        <v>0.99</v>
       </c>
       <c r="G38" t="n">
-        <v>12.2</v>
+        <v>12.24</v>
       </c>
       <c r="H38" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I38" t="n">
-        <v>0.99</v>
+        <v>0.33</v>
       </c>
       <c r="J38" t="n">
-        <v>12.24</v>
+        <v>12.1</v>
       </c>
       <c r="K38" t="n">
-        <v>0.04</v>
+        <v>-0.14</v>
       </c>
       <c r="L38" t="n">
-        <v>0.33</v>
+        <v>-1.14</v>
       </c>
       <c r="M38" t="n">
-        <v>12.1</v>
+        <v>12.16</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.14</v>
+        <v>0.06</v>
       </c>
       <c r="O38" t="n">
-        <v>-1.14</v>
+        <v>0.5</v>
       </c>
       <c r="P38" t="n">
-        <v>12.1</v>
+        <v>12.16</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.14</v>
+        <v>0.06</v>
       </c>
       <c r="R38" t="n">
-        <v>-1.14</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="E39" t="n">
-        <v>-15</v>
+        <v>6</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.91</v>
+        <v>1.2</v>
       </c>
       <c r="G39" t="n">
         <v>507</v>
       </c>
       <c r="H39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
+        <v>504</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="M39" t="n">
         <v>507</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" t="n">
-        <v>504</v>
-      </c>
       <c r="N39" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.59</v>
+        <v>0.6</v>
       </c>
       <c r="P39" t="n">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="Q39" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.59</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>40.42</v>
+        <v>41.18</v>
       </c>
       <c r="E40" t="n">
-        <v>0.04</v>
+        <v>0.76</v>
       </c>
       <c r="F40" t="n">
-        <v>0.1</v>
+        <v>1.88</v>
       </c>
       <c r="G40" t="n">
-        <v>41.18</v>
+        <v>42.04</v>
       </c>
       <c r="H40" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="I40" t="n">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="J40" t="n">
-        <v>42.04</v>
+        <v>40.5</v>
       </c>
       <c r="K40" t="n">
-        <v>0.86</v>
+        <v>-1.54</v>
       </c>
       <c r="L40" t="n">
-        <v>2.09</v>
+        <v>-3.66</v>
       </c>
       <c r="M40" t="n">
-        <v>40.5</v>
+        <v>40.74</v>
       </c>
       <c r="N40" t="n">
-        <v>-1.54</v>
+        <v>0.24</v>
       </c>
       <c r="O40" t="n">
-        <v>-3.66</v>
+        <v>0.59</v>
       </c>
       <c r="P40" t="n">
-        <v>40.5</v>
+        <v>40.74</v>
       </c>
       <c r="Q40" t="n">
-        <v>-1.54</v>
+        <v>0.24</v>
       </c>
       <c r="R40" t="n">
-        <v>-3.66</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="41">
@@ -2933,16 +2933,16 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.18</v>
+        <v>31.28</v>
       </c>
       <c r="E41" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
       <c r="F41" t="n">
-        <v>0.58</v>
+        <v>0.32</v>
       </c>
       <c r="G41" t="n">
-        <v>31.28</v>
+        <v>31.38</v>
       </c>
       <c r="H41" t="n">
         <v>0.1</v>
@@ -2951,31 +2951,31 @@
         <v>0.32</v>
       </c>
       <c r="J41" t="n">
-        <v>31.38</v>
+        <v>31.67</v>
       </c>
       <c r="K41" t="n">
-        <v>0.1</v>
+        <v>0.29</v>
       </c>
       <c r="L41" t="n">
-        <v>0.32</v>
+        <v>0.92</v>
       </c>
       <c r="M41" t="n">
-        <v>31.67</v>
+        <v>32.14</v>
       </c>
       <c r="N41" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="O41" t="n">
-        <v>0.92</v>
+        <v>1.48</v>
       </c>
       <c r="P41" t="n">
-        <v>31.67</v>
+        <v>32.14</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="R41" t="n">
-        <v>0.92</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>76.8</v>
+        <v>76.94</v>
       </c>
       <c r="E42" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="F42" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="G42" t="n">
-        <v>76.94</v>
+        <v>76.86</v>
       </c>
       <c r="H42" t="n">
-        <v>0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="I42" t="n">
-        <v>0.18</v>
+        <v>-0.1</v>
       </c>
       <c r="J42" t="n">
-        <v>76.86</v>
+        <v>77.36</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.08</v>
+        <v>0.5</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.1</v>
+        <v>0.65</v>
       </c>
       <c r="M42" t="n">
-        <v>77.36</v>
+        <v>77.8</v>
       </c>
       <c r="N42" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O42" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="P42" t="n">
-        <v>77.36</v>
+        <v>77.8</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="R42" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>41.21</v>
+        <v>41.88</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.12</v>
+        <v>0.67</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.29</v>
+        <v>1.63</v>
       </c>
       <c r="G43" t="n">
-        <v>41.88</v>
+        <v>41.78</v>
       </c>
       <c r="H43" t="n">
-        <v>0.67</v>
+        <v>-0.1</v>
       </c>
       <c r="I43" t="n">
-        <v>1.63</v>
+        <v>-0.24</v>
       </c>
       <c r="J43" t="n">
-        <v>41.78</v>
+        <v>42.1</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.1</v>
+        <v>0.32</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.24</v>
+        <v>0.77</v>
       </c>
       <c r="M43" t="n">
-        <v>42.1</v>
+        <v>42.8</v>
       </c>
       <c r="N43" t="n">
-        <v>0.32</v>
+        <v>0.7</v>
       </c>
       <c r="O43" t="n">
-        <v>0.77</v>
+        <v>1.66</v>
       </c>
       <c r="P43" t="n">
-        <v>42.1</v>
+        <v>42.8</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.32</v>
+        <v>0.7</v>
       </c>
       <c r="R43" t="n">
-        <v>0.77</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.95</v>
+        <v>5.93</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.83</v>
+        <v>-0.34</v>
       </c>
       <c r="G44" t="n">
-        <v>5.93</v>
+        <v>5.9</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.34</v>
+        <v>-0.51</v>
       </c>
       <c r="J44" t="n">
         <v>5.9</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>5.9</v>
+        <v>5.93</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
       <c r="P44" t="n">
-        <v>5.9</v>
+        <v>5.93</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="E45" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G45" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="H45" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F45" t="n">
+      <c r="I45" t="n">
         <v>-0.47</v>
       </c>
-      <c r="G45" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0.95</v>
-      </c>
       <c r="J45" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.47</v>
+        <v>-3.3</v>
       </c>
       <c r="M45" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="O45" t="n">
-        <v>-3.3</v>
+        <v>4.88</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="R45" t="n">
-        <v>-3.3</v>
+        <v>4.88</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.84</v>
+        <v>3.83</v>
       </c>
       <c r="E46" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="H46" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F46" t="n">
+      <c r="I46" t="n">
         <v>-0.52</v>
-      </c>
-      <c r="G46" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="I46" t="n">
-        <v>-0.26</v>
       </c>
       <c r="J46" t="n">
         <v>3.81</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="P46" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.11</v>
+        <v>10.19</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.2</v>
+        <v>0.79</v>
       </c>
       <c r="G47" t="n">
-        <v>10.19</v>
+        <v>10.43</v>
       </c>
       <c r="H47" t="n">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="I47" t="n">
-        <v>0.79</v>
+        <v>2.36</v>
       </c>
       <c r="J47" t="n">
-        <v>10.43</v>
+        <v>10.39</v>
       </c>
       <c r="K47" t="n">
-        <v>0.24</v>
+        <v>-0.04</v>
       </c>
       <c r="L47" t="n">
-        <v>2.36</v>
+        <v>-0.38</v>
       </c>
       <c r="M47" t="n">
-        <v>10.39</v>
+        <v>10.69</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.04</v>
+        <v>0.3</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.38</v>
+        <v>2.89</v>
       </c>
       <c r="P47" t="n">
-        <v>10.39</v>
+        <v>10.69</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.04</v>
+        <v>0.3</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.38</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.31</v>
+        <v>0.305</v>
       </c>
       <c r="E48" t="n">
         <v>-0.005</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.59</v>
+        <v>-1.61</v>
       </c>
       <c r="G48" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="J48" t="n">
         <v>0.305</v>
       </c>
-      <c r="H48" t="n">
+      <c r="K48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I48" t="n">
+      <c r="L48" t="n">
         <v>-1.61</v>
       </c>
-      <c r="J48" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1.64</v>
-      </c>
       <c r="M48" t="n">
-        <v>0.305</v>
+        <v>0.315</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.61</v>
+        <v>3.28</v>
       </c>
       <c r="P48" t="n">
-        <v>0.305</v>
+        <v>0.315</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="R48" t="n">
-        <v>-1.61</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="49">
@@ -3432,46 +3432,46 @@
         <v>4.42</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.67</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>4.42</v>
+        <v>4.35</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>-1.58</v>
       </c>
       <c r="J49" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="L49" t="n">
-        <v>-1.58</v>
+        <v>-0.46</v>
       </c>
       <c r="M49" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.46</v>
+        <v>-0.23</v>
       </c>
       <c r="P49" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.46</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
       <c r="G50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="M50" t="n">
         <v>1.11</v>
       </c>
-      <c r="H50" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="I50" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="K50" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="L50" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.07</v>
-      </c>
       <c r="N50" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.74</v>
       </c>
       <c r="P50" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="R50" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.05</v>
+        <v>5.14</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.04</v>
+        <v>0.09</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.79</v>
+        <v>1.78</v>
       </c>
       <c r="G51" t="n">
-        <v>5.14</v>
+        <v>5.17</v>
       </c>
       <c r="H51" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="I51" t="n">
-        <v>1.78</v>
+        <v>0.58</v>
       </c>
       <c r="J51" t="n">
-        <v>5.17</v>
+        <v>5.22</v>
       </c>
       <c r="K51" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="L51" t="n">
-        <v>0.58</v>
+        <v>0.97</v>
       </c>
       <c r="M51" t="n">
-        <v>5.22</v>
+        <v>5.26</v>
       </c>
       <c r="N51" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="O51" t="n">
-        <v>0.97</v>
+        <v>0.77</v>
       </c>
       <c r="P51" t="n">
-        <v>5.22</v>
+        <v>5.26</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="R51" t="n">
-        <v>0.97</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
+        <v>11.12</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G52" t="n">
+        <v>11.03</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+      <c r="J52" t="n">
+        <v>11.07</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="M52" t="n">
         <v>11.1</v>
       </c>
-      <c r="E52" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="G52" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="J52" t="n">
-        <v>11.03</v>
-      </c>
-      <c r="K52" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="L52" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="M52" t="n">
-        <v>11.07</v>
-      </c>
       <c r="N52" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="O52" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="P52" t="n">
-        <v>11.07</v>
+        <v>11.1</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="R52" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.029999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.02</v>
+        <v>0.11</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.25</v>
+        <v>1.37</v>
       </c>
       <c r="G53" t="n">
-        <v>8.140000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="I53" t="n">
-        <v>1.37</v>
+        <v>-1.11</v>
       </c>
       <c r="J53" t="n">
-        <v>8.050000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="L53" t="n">
-        <v>-1.11</v>
+        <v>0.5</v>
       </c>
       <c r="M53" t="n">
-        <v>8.09</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="O53" t="n">
-        <v>0.5</v>
+        <v>0.37</v>
       </c>
       <c r="P53" t="n">
-        <v>8.09</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="R53" t="n">
-        <v>0.5</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="54">
@@ -3742,10 +3742,10 @@
         <v>0.44</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.12</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>0.44</v>
@@ -3757,31 +3757,31 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>-2.27</v>
       </c>
       <c r="M54" t="n">
         <v>0.43</v>
       </c>
       <c r="N54" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>-2.27</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
         <v>0.43</v>
       </c>
       <c r="Q54" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>-2.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3801,49 +3801,49 @@
         </is>
       </c>
       <c r="D55" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="G55" t="n">
         <v>0.615</v>
       </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.62</v>
-      </c>
       <c r="H55" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J55" t="n">
         <v>0.615</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P55" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.4</v>
+        <v>0.395</v>
       </c>
       <c r="E56" t="n">
-        <v>0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="F56" t="n">
-        <v>2.56</v>
+        <v>-1.25</v>
       </c>
       <c r="G56" t="n">
         <v>0.395</v>
       </c>
       <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K56" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I56" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
       <c r="M56" t="n">
-        <v>0.39</v>
+        <v>0.385</v>
       </c>
       <c r="N56" t="n">
         <v>-0.005</v>
       </c>
       <c r="O56" t="n">
-        <v>-1.27</v>
+        <v>-1.28</v>
       </c>
       <c r="P56" t="n">
-        <v>0.39</v>
+        <v>0.385</v>
       </c>
       <c r="Q56" t="n">
         <v>-0.005</v>
       </c>
       <c r="R56" t="n">
-        <v>-1.27</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="E57" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="F57" t="n">
-        <v>0.27</v>
+        <v>0.54</v>
       </c>
       <c r="G57" t="n">
-        <v>3.73</v>
+        <v>3.68</v>
       </c>
       <c r="H57" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="I57" t="n">
-        <v>0.54</v>
+        <v>-1.34</v>
       </c>
       <c r="J57" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.34</v>
+        <v>-0.82</v>
       </c>
       <c r="M57" t="n">
         <v>3.65</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>-0.82</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
         <v>3.65</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>-0.82</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3990,46 +3990,46 @@
         <v>0.076</v>
       </c>
       <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="L58" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="N58" t="n">
         <v>0.001</v>
       </c>
-      <c r="F58" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.074</v>
-      </c>
-      <c r="K58" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="L58" t="n">
-        <v>-2.63</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.076</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0.002</v>
-      </c>
       <c r="O58" t="n">
-        <v>2.7</v>
+        <v>1.32</v>
       </c>
       <c r="P58" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="R58" t="n">
-        <v>2.7</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22.38</v>
+        <v>22.27</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.15</v>
+        <v>-0.11</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.67</v>
+        <v>-0.49</v>
       </c>
       <c r="G59" t="n">
-        <v>22.27</v>
+        <v>22.2</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.49</v>
+        <v>-0.31</v>
       </c>
       <c r="J59" t="n">
-        <v>22.2</v>
+        <v>22.32</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.31</v>
+        <v>0.54</v>
       </c>
       <c r="M59" t="n">
-        <v>22.32</v>
+        <v>22.96</v>
       </c>
       <c r="N59" t="n">
-        <v>0.12</v>
+        <v>0.64</v>
       </c>
       <c r="O59" t="n">
-        <v>0.54</v>
+        <v>2.87</v>
       </c>
       <c r="P59" t="n">
-        <v>22.32</v>
+        <v>22.96</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.12</v>
+        <v>0.64</v>
       </c>
       <c r="R59" t="n">
-        <v>0.54</v>
+        <v>2.87</v>
       </c>
     </row>
     <row r="60">
@@ -4114,22 +4114,22 @@
         <v>3.12</v>
       </c>
       <c r="E60" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="J60" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="K60" t="n">
         <v>-0.01</v>
@@ -4138,22 +4138,22 @@
         <v>-0.32</v>
       </c>
       <c r="M60" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="N60" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.32</v>
+        <v>0.97</v>
       </c>
       <c r="P60" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.32</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.89</v>
+        <v>0.875</v>
       </c>
       <c r="E61" t="n">
-        <v>0.015</v>
+        <v>-0.015</v>
       </c>
       <c r="F61" t="n">
-        <v>1.71</v>
+        <v>-1.69</v>
       </c>
       <c r="G61" t="n">
-        <v>0.875</v>
+        <v>0.88</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.015</v>
+        <v>0.005</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.69</v>
+        <v>0.57</v>
       </c>
       <c r="J61" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="K61" t="n">
-        <v>0.005</v>
+        <v>-0.01</v>
       </c>
       <c r="L61" t="n">
-        <v>0.57</v>
+        <v>-1.14</v>
       </c>
       <c r="M61" t="n">
-        <v>0.87</v>
+        <v>0.865</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="O61" t="n">
-        <v>-1.14</v>
+        <v>-0.57</v>
       </c>
       <c r="P61" t="n">
-        <v>0.87</v>
+        <v>0.865</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="R61" t="n">
-        <v>-1.14</v>
+        <v>-0.57</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-17 Close</t>
+          <t>2026-09-18 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-09-17 Change</t>
+          <t>2026-09-18 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-17 Change %</t>
+          <t>2026-09-18 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-09-18 Close</t>
+          <t>2026-09-21 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-09-18 Change</t>
+          <t>2026-09-21 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-09-18 Change %</t>
+          <t>2026-09-21 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-09-21 Close</t>
+          <t>2026-09-22 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-09-21 Change</t>
+          <t>2026-09-22 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-09-21 Change %</t>
+          <t>2026-09-22 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-09-22 Close</t>
+          <t>2026-09-23 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-09-22 Change</t>
+          <t>2026-09-23 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-09-22 Change %</t>
+          <t>2026-09-23 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-09-23 Close</t>
+          <t>2026-09-24 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-09-23 Change</t>
+          <t>2026-09-24 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-09-23 Change %</t>
+          <t>2026-09-24 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>159.8</v>
+        <v>161.6</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.1</v>
+        <v>1.8</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.68</v>
+        <v>1.13</v>
       </c>
       <c r="G3" t="n">
-        <v>161.6</v>
+        <v>161.5</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8</v>
+        <v>-0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>1.13</v>
+        <v>-0.06</v>
       </c>
       <c r="J3" t="n">
-        <v>161.5</v>
+        <v>159.3</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1</v>
+        <v>-2.2</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.06</v>
+        <v>-1.36</v>
       </c>
       <c r="M3" t="n">
-        <v>159.3</v>
+        <v>159.5</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.2</v>
+        <v>0.2</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.36</v>
+        <v>0.13</v>
       </c>
       <c r="P3" t="n">
-        <v>159.3</v>
+        <v>159.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2</v>
+        <v>0.2</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.36</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>243.4</v>
+        <v>245</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.25</v>
+        <v>0.66</v>
       </c>
       <c r="G4" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.66</v>
+        <v>0.41</v>
       </c>
       <c r="J4" t="n">
-        <v>246</v>
+        <v>239.4</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>-6.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.41</v>
+        <v>-2.68</v>
       </c>
       <c r="M4" t="n">
-        <v>239.4</v>
+        <v>240</v>
       </c>
       <c r="N4" t="n">
-        <v>-6.6</v>
+        <v>0.6</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.68</v>
+        <v>0.25</v>
       </c>
       <c r="P4" t="n">
-        <v>239.4</v>
+        <v>240</v>
       </c>
       <c r="Q4" t="n">
-        <v>-6.6</v>
+        <v>0.6</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.68</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="5">
@@ -701,34 +701,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.32</v>
+        <v>6.3</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.63</v>
+        <v>-0.32</v>
       </c>
       <c r="G5" t="n">
-        <v>6.3</v>
+        <v>6.51</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.02</v>
+        <v>0.21</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.32</v>
+        <v>3.33</v>
       </c>
       <c r="J5" t="n">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="K5" t="n">
-        <v>0.21</v>
+        <v>-0.01</v>
       </c>
       <c r="L5" t="n">
-        <v>3.33</v>
+        <v>-0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="N5" t="n">
         <v>-0.01</v>
@@ -737,7 +737,7 @@
         <v>-0.15</v>
       </c>
       <c r="P5" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.01</v>
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.52</v>
+        <v>7.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.13</v>
+        <v>-0.27</v>
       </c>
       <c r="G6" t="n">
-        <v>7.5</v>
+        <v>7.58</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.27</v>
+        <v>1.07</v>
       </c>
       <c r="J6" t="n">
-        <v>7.58</v>
+        <v>7.54</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="L6" t="n">
-        <v>1.07</v>
+        <v>-0.53</v>
       </c>
       <c r="M6" t="n">
         <v>7.54</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>7.54</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -828,46 +828,46 @@
         <v>5.99</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>5.99</v>
+        <v>6.06</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="J7" t="n">
-        <v>6.06</v>
+        <v>6.02</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="L7" t="n">
-        <v>1.17</v>
+        <v>-0.66</v>
       </c>
       <c r="M7" t="n">
-        <v>6.02</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.66</v>
+        <v>-0.33</v>
       </c>
       <c r="P7" t="n">
-        <v>6.02</v>
+        <v>6</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.66</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.68</v>
+        <v>9.59</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="F8" t="n">
-        <v>0.41</v>
+        <v>-0.93</v>
       </c>
       <c r="G8" t="n">
-        <v>9.59</v>
+        <v>9.76</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.09</v>
+        <v>0.17</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.93</v>
+        <v>1.77</v>
       </c>
       <c r="J8" t="n">
-        <v>9.76</v>
+        <v>9.74</v>
       </c>
       <c r="K8" t="n">
-        <v>0.17</v>
+        <v>-0.02</v>
       </c>
       <c r="L8" t="n">
-        <v>1.77</v>
+        <v>-0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>9.74</v>
+        <v>9.66</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2</v>
+        <v>-0.82</v>
       </c>
       <c r="P8" t="n">
-        <v>9.74</v>
+        <v>9.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.2</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.18</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="F9" t="n">
-        <v>0.74</v>
+        <v>-0.49</v>
       </c>
       <c r="G9" t="n">
-        <v>8.140000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.49</v>
+        <v>1.47</v>
       </c>
       <c r="J9" t="n">
-        <v>8.26</v>
+        <v>8.24</v>
       </c>
       <c r="K9" t="n">
-        <v>0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="L9" t="n">
-        <v>1.47</v>
+        <v>-0.24</v>
       </c>
       <c r="M9" t="n">
-        <v>8.24</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.24</v>
+        <v>-0.36</v>
       </c>
       <c r="P9" t="n">
-        <v>8.24</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.24</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51.3</v>
+        <v>51.2</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="G10" t="n">
-        <v>51.2</v>
+        <v>52.1</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1</v>
+        <v>0.9</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.19</v>
+        <v>1.76</v>
       </c>
       <c r="J10" t="n">
-        <v>52.1</v>
+        <v>51.65</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9</v>
+        <v>-0.45</v>
       </c>
       <c r="L10" t="n">
-        <v>1.76</v>
+        <v>-0.86</v>
       </c>
       <c r="M10" t="n">
-        <v>51.65</v>
+        <v>51.25</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.45</v>
+        <v>-0.4</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.86</v>
+        <v>-0.77</v>
       </c>
       <c r="P10" t="n">
-        <v>51.65</v>
+        <v>51.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.45</v>
+        <v>-0.4</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.86</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="11">
@@ -1076,31 +1076,31 @@
         <v>4.51</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.17</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>4.51</v>
+        <v>4.49</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="J11" t="n">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="K11" t="n">
         <v>-0.02</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
       <c r="M11" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="N11" t="n">
         <v>-0.02</v>
@@ -1109,7 +1109,7 @@
         <v>-0.45</v>
       </c>
       <c r="P11" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.02</v>
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.56</v>
+        <v>9.49</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.23</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.35</v>
+        <v>-0.73</v>
       </c>
       <c r="G12" t="n">
-        <v>9.49</v>
+        <v>9.51</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.73</v>
+        <v>0.21</v>
       </c>
       <c r="J12" t="n">
-        <v>9.51</v>
+        <v>9.43</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="L12" t="n">
-        <v>0.21</v>
+        <v>-0.84</v>
       </c>
       <c r="M12" t="n">
-        <v>9.43</v>
+        <v>9.35</v>
       </c>
       <c r="N12" t="n">
         <v>-0.08</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.84</v>
+        <v>-0.85</v>
       </c>
       <c r="P12" t="n">
-        <v>9.43</v>
+        <v>9.35</v>
       </c>
       <c r="Q12" t="n">
         <v>-0.08</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.84</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23.88</v>
+        <v>23.6</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.48</v>
+        <v>-0.28</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.97</v>
+        <v>-1.17</v>
       </c>
       <c r="G13" t="n">
-        <v>23.6</v>
+        <v>23.94</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.28</v>
+        <v>0.34</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.17</v>
+        <v>1.44</v>
       </c>
       <c r="J13" t="n">
-        <v>23.94</v>
+        <v>23.68</v>
       </c>
       <c r="K13" t="n">
-        <v>0.34</v>
+        <v>-0.26</v>
       </c>
       <c r="L13" t="n">
-        <v>1.44</v>
+        <v>-1.09</v>
       </c>
       <c r="M13" t="n">
-        <v>23.68</v>
+        <v>23.34</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.26</v>
+        <v>-0.34</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.09</v>
+        <v>-1.44</v>
       </c>
       <c r="P13" t="n">
-        <v>23.68</v>
+        <v>23.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.26</v>
+        <v>-0.34</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.09</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="14">
@@ -1262,46 +1262,46 @@
         <v>1.92</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.54</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-1.04</v>
       </c>
       <c r="J14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.04</v>
+        <v>-0.53</v>
       </c>
       <c r="M14" t="n">
         <v>1.89</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>1.89</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.07</v>
+        <v>5.13</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.04</v>
+        <v>0.06</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.78</v>
+        <v>1.18</v>
       </c>
       <c r="G15" t="n">
-        <v>5.13</v>
+        <v>5.25</v>
       </c>
       <c r="H15" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="I15" t="n">
-        <v>1.18</v>
+        <v>2.34</v>
       </c>
       <c r="J15" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="K15" t="n">
-        <v>0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="L15" t="n">
-        <v>2.34</v>
+        <v>-1.14</v>
       </c>
       <c r="M15" t="n">
-        <v>5.19</v>
+        <v>5.17</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.14</v>
+        <v>-0.39</v>
       </c>
       <c r="P15" t="n">
-        <v>5.19</v>
+        <v>5.17</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.14</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="E16" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F16" t="n">
-        <v>0.23</v>
+        <v>-0.45</v>
       </c>
       <c r="G16" t="n">
         <v>4.43</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>4.43</v>
+        <v>4.39</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="M16" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9</v>
+        <v>-1.14</v>
       </c>
       <c r="P16" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.9</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="17">
@@ -1445,7 +1445,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="E17" t="n">
         <v>-0.02</v>
@@ -1457,37 +1457,37 @@
         <v>3.31</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.91</v>
       </c>
       <c r="M17" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.91</v>
+        <v>-3.66</v>
       </c>
       <c r="P17" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.91</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="G18" t="n">
         <v>3.02</v>
       </c>
-      <c r="E18" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="F18" t="n">
-        <v>-2.27</v>
-      </c>
-      <c r="G18" t="n">
-        <v>2.98</v>
-      </c>
       <c r="H18" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.32</v>
+        <v>1.34</v>
       </c>
       <c r="J18" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="K18" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="L18" t="n">
-        <v>1.34</v>
+        <v>-1.66</v>
       </c>
       <c r="M18" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.66</v>
+        <v>-1.01</v>
       </c>
       <c r="P18" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="R18" t="n">
-        <v>-1.66</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>52.85</v>
+        <v>53.2</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05</v>
+        <v>0.35</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09</v>
+        <v>0.66</v>
       </c>
       <c r="G19" t="n">
-        <v>53.2</v>
+        <v>53.75</v>
       </c>
       <c r="H19" t="n">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="I19" t="n">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="J19" t="n">
-        <v>53.75</v>
+        <v>53.9</v>
       </c>
       <c r="K19" t="n">
-        <v>0.55</v>
+        <v>0.15</v>
       </c>
       <c r="L19" t="n">
-        <v>1.03</v>
+        <v>0.28</v>
       </c>
       <c r="M19" t="n">
-        <v>53.9</v>
+        <v>53.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="O19" t="n">
-        <v>0.28</v>
+        <v>-0.93</v>
       </c>
       <c r="P19" t="n">
-        <v>53.9</v>
+        <v>53.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="R19" t="n">
-        <v>0.28</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.64</v>
+        <v>29.38</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1</v>
+        <v>0.74</v>
       </c>
       <c r="F20" t="n">
-        <v>0.35</v>
+        <v>2.58</v>
       </c>
       <c r="G20" t="n">
-        <v>29.38</v>
+        <v>29.08</v>
       </c>
       <c r="H20" t="n">
-        <v>0.74</v>
+        <v>-0.3</v>
       </c>
       <c r="I20" t="n">
-        <v>2.58</v>
+        <v>-1.02</v>
       </c>
       <c r="J20" t="n">
-        <v>29.08</v>
+        <v>29.7</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.3</v>
+        <v>0.62</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.02</v>
+        <v>2.13</v>
       </c>
       <c r="M20" t="n">
         <v>29.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>29.7</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.49</v>
+        <v>4.43</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.88</v>
+        <v>-1.34</v>
       </c>
       <c r="G21" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="J21" t="n">
         <v>4.43</v>
       </c>
-      <c r="H21" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="I21" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="M21" t="n">
         <v>4.41</v>
       </c>
-      <c r="K21" t="n">
+      <c r="N21" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L21" t="n">
+      <c r="O21" t="n">
         <v>-0.45</v>
       </c>
-      <c r="M21" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0.45</v>
-      </c>
       <c r="P21" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="R21" t="n">
-        <v>0.45</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="22">
@@ -1755,7 +1755,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79.2</v>
+        <v>79.05</v>
       </c>
       <c r="E22" t="n">
         <v>-0.15</v>
@@ -1764,40 +1764,40 @@
         <v>-0.19</v>
       </c>
       <c r="G22" t="n">
-        <v>79.05</v>
+        <v>79.2</v>
       </c>
       <c r="H22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J22" t="n">
+        <v>78.95</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="L22" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="M22" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="N22" t="n">
         <v>-0.15</v>
       </c>
-      <c r="I22" t="n">
+      <c r="O22" t="n">
         <v>-0.19</v>
       </c>
-      <c r="J22" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="M22" t="n">
-        <v>78.95</v>
-      </c>
-      <c r="N22" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="O22" t="n">
-        <v>-0.32</v>
-      </c>
       <c r="P22" t="n">
-        <v>78.95</v>
+        <v>78.8</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.25</v>
+        <v>-0.15</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.32</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22.44</v>
+        <v>22.84</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.18</v>
+        <v>0.4</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8</v>
+        <v>1.78</v>
       </c>
       <c r="G23" t="n">
-        <v>22.84</v>
+        <v>23.54</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="I23" t="n">
-        <v>1.78</v>
+        <v>3.06</v>
       </c>
       <c r="J23" t="n">
-        <v>23.54</v>
+        <v>23.24</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="L23" t="n">
-        <v>3.06</v>
+        <v>-1.27</v>
       </c>
       <c r="M23" t="n">
-        <v>23.24</v>
+        <v>22.6</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.3</v>
+        <v>-0.64</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.27</v>
+        <v>-2.75</v>
       </c>
       <c r="P23" t="n">
-        <v>23.24</v>
+        <v>22.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.3</v>
+        <v>-0.64</v>
       </c>
       <c r="R23" t="n">
-        <v>-1.27</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.88</v>
+        <v>16.42</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.44</v>
+        <v>3.4</v>
       </c>
       <c r="G24" t="n">
-        <v>16.42</v>
+        <v>16.21</v>
       </c>
       <c r="H24" t="n">
-        <v>0.54</v>
+        <v>-0.21</v>
       </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>-1.28</v>
       </c>
       <c r="J24" t="n">
-        <v>16.21</v>
+        <v>15.86</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.21</v>
+        <v>-0.35</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.28</v>
+        <v>-2.16</v>
       </c>
       <c r="M24" t="n">
-        <v>15.86</v>
+        <v>15.25</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.35</v>
+        <v>-0.61</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.16</v>
+        <v>-3.85</v>
       </c>
       <c r="P24" t="n">
-        <v>15.86</v>
+        <v>15.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.35</v>
+        <v>-0.61</v>
       </c>
       <c r="R24" t="n">
-        <v>-2.16</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.14</v>
+        <v>26.4</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.04</v>
+        <v>0.26</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.15</v>
+        <v>0.99</v>
       </c>
       <c r="G25" t="n">
-        <v>26.4</v>
+        <v>27.58</v>
       </c>
       <c r="H25" t="n">
-        <v>0.26</v>
+        <v>1.18</v>
       </c>
       <c r="I25" t="n">
-        <v>0.99</v>
+        <v>4.47</v>
       </c>
       <c r="J25" t="n">
-        <v>27.58</v>
+        <v>27.2</v>
       </c>
       <c r="K25" t="n">
-        <v>1.18</v>
+        <v>-0.38</v>
       </c>
       <c r="L25" t="n">
-        <v>4.47</v>
+        <v>-1.38</v>
       </c>
       <c r="M25" t="n">
-        <v>27.2</v>
+        <v>26.18</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.38</v>
+        <v>-1.02</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.38</v>
+        <v>-3.75</v>
       </c>
       <c r="P25" t="n">
-        <v>27.2</v>
+        <v>26.18</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.38</v>
+        <v>-1.02</v>
       </c>
       <c r="R25" t="n">
-        <v>-1.38</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33.86</v>
+        <v>37.94</v>
       </c>
       <c r="E26" t="n">
-        <v>0.98</v>
+        <v>4.08</v>
       </c>
       <c r="F26" t="n">
-        <v>2.98</v>
+        <v>12.05</v>
       </c>
       <c r="G26" t="n">
-        <v>37.94</v>
+        <v>42.58</v>
       </c>
       <c r="H26" t="n">
-        <v>4.08</v>
+        <v>4.64</v>
       </c>
       <c r="I26" t="n">
-        <v>12.05</v>
+        <v>12.23</v>
       </c>
       <c r="J26" t="n">
-        <v>42.58</v>
+        <v>42.9</v>
       </c>
       <c r="K26" t="n">
-        <v>4.64</v>
+        <v>0.32</v>
       </c>
       <c r="L26" t="n">
-        <v>12.23</v>
+        <v>0.75</v>
       </c>
       <c r="M26" t="n">
-        <v>42.9</v>
+        <v>40.16</v>
       </c>
       <c r="N26" t="n">
-        <v>0.32</v>
+        <v>-2.74</v>
       </c>
       <c r="O26" t="n">
-        <v>0.75</v>
+        <v>-6.39</v>
       </c>
       <c r="P26" t="n">
-        <v>42.9</v>
+        <v>40.16</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.32</v>
+        <v>-2.74</v>
       </c>
       <c r="R26" t="n">
-        <v>0.75</v>
+        <v>-6.39</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>426</v>
+        <v>419</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.4</v>
+        <v>-7</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.71</v>
+        <v>-1.64</v>
       </c>
       <c r="G27" t="n">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="H27" t="n">
-        <v>-7</v>
+        <v>11</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.64</v>
+        <v>2.63</v>
       </c>
       <c r="J27" t="n">
-        <v>430</v>
+        <v>451.6</v>
       </c>
       <c r="K27" t="n">
-        <v>11</v>
+        <v>21.6</v>
       </c>
       <c r="L27" t="n">
-        <v>2.63</v>
+        <v>5.02</v>
       </c>
       <c r="M27" t="n">
-        <v>451.6</v>
+        <v>441</v>
       </c>
       <c r="N27" t="n">
-        <v>21.6</v>
+        <v>-10.6</v>
       </c>
       <c r="O27" t="n">
-        <v>5.02</v>
+        <v>-2.35</v>
       </c>
       <c r="P27" t="n">
-        <v>451.6</v>
+        <v>441</v>
       </c>
       <c r="Q27" t="n">
-        <v>21.6</v>
+        <v>-10.6</v>
       </c>
       <c r="R27" t="n">
-        <v>5.02</v>
+        <v>-2.35</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>105.1</v>
+        <v>109.3</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.1</v>
+        <v>4.2</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.04</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>109.3</v>
+        <v>112.6</v>
       </c>
       <c r="H28" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="J28" t="n">
-        <v>112.6</v>
+        <v>114.8</v>
       </c>
       <c r="K28" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="L28" t="n">
-        <v>3.02</v>
+        <v>1.95</v>
       </c>
       <c r="M28" t="n">
-        <v>114.8</v>
+        <v>109.8</v>
       </c>
       <c r="N28" t="n">
-        <v>2.2</v>
+        <v>-5</v>
       </c>
       <c r="O28" t="n">
-        <v>1.95</v>
+        <v>-4.36</v>
       </c>
       <c r="P28" t="n">
-        <v>114.8</v>
+        <v>109.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.2</v>
+        <v>-5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.95</v>
+        <v>-4.36</v>
       </c>
     </row>
     <row r="29">
@@ -2192,46 +2192,46 @@
         <v>105</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.85</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>105</v>
+        <v>105.4</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="J29" t="n">
-        <v>105.4</v>
+        <v>106.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.38</v>
+        <v>1.04</v>
       </c>
       <c r="M29" t="n">
-        <v>106.5</v>
+        <v>106.1</v>
       </c>
       <c r="N29" t="n">
-        <v>1.1</v>
+        <v>-0.4</v>
       </c>
       <c r="O29" t="n">
-        <v>1.04</v>
+        <v>-0.38</v>
       </c>
       <c r="P29" t="n">
-        <v>106.5</v>
+        <v>106.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.1</v>
+        <v>-0.4</v>
       </c>
       <c r="R29" t="n">
-        <v>1.04</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>72.90000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.55</v>
+        <v>0.3</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.08</v>
+        <v>0.41</v>
       </c>
       <c r="G30" t="n">
+        <v>74</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="J30" t="n">
         <v>73.2</v>
       </c>
-      <c r="H30" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="J30" t="n">
-        <v>74</v>
-      </c>
       <c r="K30" t="n">
-        <v>0.8</v>
+        <v>-0.8</v>
       </c>
       <c r="L30" t="n">
-        <v>1.09</v>
+        <v>-1.08</v>
       </c>
       <c r="M30" t="n">
-        <v>73.2</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.8</v>
+        <v>-0.35</v>
       </c>
       <c r="O30" t="n">
-        <v>-1.08</v>
+        <v>-0.48</v>
       </c>
       <c r="P30" t="n">
-        <v>73.2</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.8</v>
+        <v>-0.35</v>
       </c>
       <c r="R30" t="n">
-        <v>-1.08</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>87.34999999999999</v>
+        <v>87.2</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.7</v>
+        <v>-0.15</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.8</v>
+        <v>-0.17</v>
       </c>
       <c r="G31" t="n">
-        <v>87.2</v>
+        <v>89</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.15</v>
+        <v>1.8</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.17</v>
+        <v>2.06</v>
       </c>
       <c r="J31" t="n">
-        <v>89</v>
+        <v>89.5</v>
       </c>
       <c r="K31" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="L31" t="n">
-        <v>2.06</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>89.5</v>
+        <v>88.55</v>
       </c>
       <c r="N31" t="n">
-        <v>0.5</v>
+        <v>-0.95</v>
       </c>
       <c r="O31" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.06</v>
       </c>
       <c r="P31" t="n">
-        <v>89.5</v>
+        <v>88.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.5</v>
+        <v>-0.95</v>
       </c>
       <c r="R31" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>62.4</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.25</v>
+        <v>2.75</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.96</v>
+        <v>4.41</v>
       </c>
       <c r="G32" t="n">
-        <v>65.15000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>2.75</v>
+        <v>0.45</v>
       </c>
       <c r="I32" t="n">
-        <v>4.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>65.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="K32" t="n">
-        <v>0.45</v>
+        <v>-1.3</v>
       </c>
       <c r="L32" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.98</v>
       </c>
       <c r="M32" t="n">
-        <v>64.3</v>
+        <v>63.8</v>
       </c>
       <c r="N32" t="n">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="O32" t="n">
-        <v>-1.98</v>
+        <v>-0.78</v>
       </c>
       <c r="P32" t="n">
-        <v>64.3</v>
+        <v>63.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="R32" t="n">
-        <v>-1.98</v>
+        <v>-0.78</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>81.15000000000001</v>
+        <v>81.5</v>
       </c>
       <c r="E33" t="n">
-        <v>1.95</v>
+        <v>0.35</v>
       </c>
       <c r="F33" t="n">
-        <v>2.46</v>
+        <v>0.43</v>
       </c>
       <c r="G33" t="n">
-        <v>81.5</v>
+        <v>81.2</v>
       </c>
       <c r="H33" t="n">
-        <v>0.35</v>
+        <v>-0.3</v>
       </c>
       <c r="I33" t="n">
-        <v>0.43</v>
+        <v>-0.37</v>
       </c>
       <c r="J33" t="n">
-        <v>81.2</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.3</v>
+        <v>0.15</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.37</v>
+        <v>0.18</v>
       </c>
       <c r="M33" t="n">
-        <v>81.34999999999999</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>0.15</v>
+        <v>-1</v>
       </c>
       <c r="O33" t="n">
-        <v>0.18</v>
+        <v>-1.23</v>
       </c>
       <c r="P33" t="n">
-        <v>81.34999999999999</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.15</v>
+        <v>-1</v>
       </c>
       <c r="R33" t="n">
-        <v>0.18</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>29.94</v>
+        <v>30.74</v>
       </c>
       <c r="E34" t="n">
-        <v>0.28</v>
+        <v>0.8</v>
       </c>
       <c r="F34" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.67</v>
       </c>
       <c r="G34" t="n">
-        <v>30.74</v>
+        <v>30.82</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8</v>
+        <v>0.08</v>
       </c>
       <c r="I34" t="n">
-        <v>2.67</v>
+        <v>0.26</v>
       </c>
       <c r="J34" t="n">
-        <v>30.82</v>
+        <v>31.22</v>
       </c>
       <c r="K34" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="L34" t="n">
-        <v>0.26</v>
+        <v>1.3</v>
       </c>
       <c r="M34" t="n">
-        <v>31.22</v>
+        <v>30.78</v>
       </c>
       <c r="N34" t="n">
-        <v>0.4</v>
+        <v>-0.44</v>
       </c>
       <c r="O34" t="n">
-        <v>1.3</v>
+        <v>-1.41</v>
       </c>
       <c r="P34" t="n">
-        <v>31.22</v>
+        <v>30.78</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.4</v>
+        <v>-0.44</v>
       </c>
       <c r="R34" t="n">
-        <v>1.3</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.22</v>
+        <v>4.32</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.02</v>
+        <v>0.1</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.47</v>
+        <v>2.37</v>
       </c>
       <c r="G35" t="n">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="H35" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="I35" t="n">
-        <v>2.37</v>
+        <v>0.46</v>
       </c>
       <c r="J35" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="K35" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L35" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="M35" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="N35" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="O35" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="P35" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="R35" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.1</v>
+        <v>9.31</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.04</v>
+        <v>0.21</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.44</v>
+        <v>2.31</v>
       </c>
       <c r="G36" t="n">
-        <v>9.31</v>
+        <v>9.34</v>
       </c>
       <c r="H36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J36" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L36" t="n">
         <v>0.21</v>
       </c>
-      <c r="I36" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="J36" t="n">
-        <v>9.34</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.32</v>
-      </c>
       <c r="M36" t="n">
-        <v>9.34</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="O36" t="n">
-        <v>0.32</v>
+        <v>0.21</v>
       </c>
       <c r="P36" t="n">
-        <v>9.34</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="R36" t="n">
-        <v>0.32</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>388.6</v>
+        <v>388</v>
       </c>
       <c r="E37" t="n">
-        <v>-7</v>
+        <v>-0.6</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.77</v>
+        <v>-0.15</v>
       </c>
       <c r="G37" t="n">
-        <v>388</v>
+        <v>391.2</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.6</v>
+        <v>3.2</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.15</v>
+        <v>0.82</v>
       </c>
       <c r="J37" t="n">
-        <v>391.2</v>
+        <v>397.4</v>
       </c>
       <c r="K37" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="L37" t="n">
-        <v>0.82</v>
+        <v>1.58</v>
       </c>
       <c r="M37" t="n">
-        <v>397.4</v>
+        <v>395.8</v>
       </c>
       <c r="N37" t="n">
-        <v>6.2</v>
+        <v>-1.6</v>
       </c>
       <c r="O37" t="n">
-        <v>1.58</v>
+        <v>-0.4</v>
       </c>
       <c r="P37" t="n">
-        <v>397.4</v>
+        <v>395.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>6.2</v>
+        <v>-1.6</v>
       </c>
       <c r="R37" t="n">
-        <v>1.58</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.2</v>
+        <v>12.24</v>
       </c>
       <c r="E38" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F38" t="n">
-        <v>0.99</v>
+        <v>0.33</v>
       </c>
       <c r="G38" t="n">
-        <v>12.24</v>
+        <v>12.1</v>
       </c>
       <c r="H38" t="n">
-        <v>0.04</v>
+        <v>-0.14</v>
       </c>
       <c r="I38" t="n">
-        <v>0.33</v>
+        <v>-1.14</v>
       </c>
       <c r="J38" t="n">
-        <v>12.1</v>
+        <v>12.16</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.14</v>
+        <v>0.06</v>
       </c>
       <c r="L38" t="n">
-        <v>-1.14</v>
+        <v>0.5</v>
       </c>
       <c r="M38" t="n">
-        <v>12.16</v>
+        <v>12.07</v>
       </c>
       <c r="N38" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="O38" t="n">
-        <v>0.5</v>
+        <v>-0.74</v>
       </c>
       <c r="P38" t="n">
-        <v>12.16</v>
+        <v>12.07</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="R38" t="n">
-        <v>0.5</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="39">
@@ -2812,46 +2812,46 @@
         <v>507</v>
       </c>
       <c r="E39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
+        <v>504</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I39" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="J39" t="n">
         <v>507</v>
       </c>
-      <c r="H39" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
-      <c r="J39" t="n">
-        <v>504</v>
-      </c>
       <c r="K39" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.59</v>
+        <v>0.6</v>
       </c>
       <c r="M39" t="n">
-        <v>507</v>
+        <v>511.5</v>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="O39" t="n">
-        <v>0.6</v>
+        <v>0.89</v>
       </c>
       <c r="P39" t="n">
-        <v>507</v>
+        <v>511.5</v>
       </c>
       <c r="Q39" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="R39" t="n">
-        <v>0.6</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>41.18</v>
+        <v>42.04</v>
       </c>
       <c r="E40" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="F40" t="n">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="G40" t="n">
-        <v>42.04</v>
+        <v>40.5</v>
       </c>
       <c r="H40" t="n">
-        <v>0.86</v>
+        <v>-1.54</v>
       </c>
       <c r="I40" t="n">
-        <v>2.09</v>
+        <v>-3.66</v>
       </c>
       <c r="J40" t="n">
-        <v>40.5</v>
+        <v>40.74</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.54</v>
+        <v>0.24</v>
       </c>
       <c r="L40" t="n">
-        <v>-3.66</v>
+        <v>0.59</v>
       </c>
       <c r="M40" t="n">
-        <v>40.74</v>
+        <v>40.4</v>
       </c>
       <c r="N40" t="n">
-        <v>0.24</v>
+        <v>-0.34</v>
       </c>
       <c r="O40" t="n">
-        <v>0.59</v>
+        <v>-0.83</v>
       </c>
       <c r="P40" t="n">
-        <v>40.74</v>
+        <v>40.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.24</v>
+        <v>-0.34</v>
       </c>
       <c r="R40" t="n">
-        <v>0.59</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="41">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.28</v>
+        <v>31.38</v>
       </c>
       <c r="E41" t="n">
         <v>0.1</v>
@@ -2942,40 +2942,40 @@
         <v>0.32</v>
       </c>
       <c r="G41" t="n">
-        <v>31.38</v>
+        <v>31.67</v>
       </c>
       <c r="H41" t="n">
-        <v>0.1</v>
+        <v>0.29</v>
       </c>
       <c r="I41" t="n">
-        <v>0.32</v>
+        <v>0.92</v>
       </c>
       <c r="J41" t="n">
-        <v>31.67</v>
+        <v>32.14</v>
       </c>
       <c r="K41" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="L41" t="n">
-        <v>0.92</v>
+        <v>1.48</v>
       </c>
       <c r="M41" t="n">
-        <v>32.14</v>
+        <v>31.65</v>
       </c>
       <c r="N41" t="n">
-        <v>0.47</v>
+        <v>-0.49</v>
       </c>
       <c r="O41" t="n">
-        <v>1.48</v>
+        <v>-1.52</v>
       </c>
       <c r="P41" t="n">
-        <v>32.14</v>
+        <v>31.65</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.47</v>
+        <v>-0.49</v>
       </c>
       <c r="R41" t="n">
-        <v>1.48</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>76.94</v>
+        <v>76.86</v>
       </c>
       <c r="E42" t="n">
-        <v>0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="F42" t="n">
-        <v>0.18</v>
+        <v>-0.1</v>
       </c>
       <c r="G42" t="n">
-        <v>76.86</v>
+        <v>77.36</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.08</v>
+        <v>0.5</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.1</v>
+        <v>0.65</v>
       </c>
       <c r="J42" t="n">
-        <v>77.36</v>
+        <v>77.8</v>
       </c>
       <c r="K42" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="L42" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="M42" t="n">
-        <v>77.8</v>
+        <v>77.69</v>
       </c>
       <c r="N42" t="n">
-        <v>0.44</v>
+        <v>-0.11</v>
       </c>
       <c r="O42" t="n">
-        <v>0.57</v>
+        <v>-0.14</v>
       </c>
       <c r="P42" t="n">
-        <v>77.8</v>
+        <v>77.69</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.44</v>
+        <v>-0.11</v>
       </c>
       <c r="R42" t="n">
-        <v>0.57</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>41.88</v>
+        <v>41.78</v>
       </c>
       <c r="E43" t="n">
-        <v>0.67</v>
+        <v>-0.1</v>
       </c>
       <c r="F43" t="n">
-        <v>1.63</v>
+        <v>-0.24</v>
       </c>
       <c r="G43" t="n">
-        <v>41.78</v>
+        <v>42.1</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.1</v>
+        <v>0.32</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.24</v>
+        <v>0.77</v>
       </c>
       <c r="J43" t="n">
-        <v>42.1</v>
+        <v>42.8</v>
       </c>
       <c r="K43" t="n">
-        <v>0.32</v>
+        <v>0.7</v>
       </c>
       <c r="L43" t="n">
-        <v>0.77</v>
+        <v>1.66</v>
       </c>
       <c r="M43" t="n">
-        <v>42.8</v>
+        <v>42.84</v>
       </c>
       <c r="N43" t="n">
-        <v>0.7</v>
+        <v>0.04</v>
       </c>
       <c r="O43" t="n">
-        <v>1.66</v>
+        <v>0.09</v>
       </c>
       <c r="P43" t="n">
-        <v>42.8</v>
+        <v>42.84</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.7</v>
+        <v>0.04</v>
       </c>
       <c r="R43" t="n">
-        <v>1.66</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.93</v>
+        <v>5.9</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.34</v>
+        <v>-0.51</v>
       </c>
       <c r="G44" t="n">
         <v>5.9</v>
       </c>
       <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M44" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="N44" t="n">
         <v>-0.03</v>
       </c>
-      <c r="I44" t="n">
+      <c r="O44" t="n">
         <v>-0.51</v>
       </c>
-      <c r="J44" t="n">
+      <c r="P44" t="n">
         <v>5.9</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="P44" t="n">
-        <v>5.93</v>
-      </c>
       <c r="Q44" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="R44" t="n">
-        <v>0.51</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="E45" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F45" t="n">
-        <v>0.95</v>
+        <v>-0.47</v>
       </c>
       <c r="G45" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.47</v>
+        <v>-3.3</v>
       </c>
       <c r="J45" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="L45" t="n">
-        <v>-3.3</v>
+        <v>4.88</v>
       </c>
       <c r="M45" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="N45" t="n">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="O45" t="n">
-        <v>4.88</v>
+        <v>-2.33</v>
       </c>
       <c r="P45" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="R45" t="n">
-        <v>4.88</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.26</v>
+        <v>-0.52</v>
       </c>
       <c r="G46" t="n">
         <v>3.81</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="M46" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="N46" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="O46" t="n">
-        <v>0.52</v>
+        <v>-0.26</v>
       </c>
       <c r="P46" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="R46" t="n">
-        <v>0.52</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.19</v>
+        <v>10.43</v>
       </c>
       <c r="E47" t="n">
-        <v>0.08</v>
+        <v>0.24</v>
       </c>
       <c r="F47" t="n">
-        <v>0.79</v>
+        <v>2.36</v>
       </c>
       <c r="G47" t="n">
-        <v>10.43</v>
+        <v>10.39</v>
       </c>
       <c r="H47" t="n">
-        <v>0.24</v>
+        <v>-0.04</v>
       </c>
       <c r="I47" t="n">
-        <v>2.36</v>
+        <v>-0.38</v>
       </c>
       <c r="J47" t="n">
-        <v>10.39</v>
+        <v>10.69</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.04</v>
+        <v>0.3</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.38</v>
+        <v>2.89</v>
       </c>
       <c r="M47" t="n">
-        <v>10.69</v>
+        <v>10.81</v>
       </c>
       <c r="N47" t="n">
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="O47" t="n">
-        <v>2.89</v>
+        <v>1.12</v>
       </c>
       <c r="P47" t="n">
-        <v>10.69</v>
+        <v>10.81</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="R47" t="n">
-        <v>2.89</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.305</v>
       </c>
-      <c r="E48" t="n">
+      <c r="H48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F48" t="n">
+      <c r="I48" t="n">
         <v>-1.61</v>
       </c>
-      <c r="G48" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1.64</v>
-      </c>
       <c r="J48" t="n">
-        <v>0.305</v>
+        <v>0.315</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.61</v>
+        <v>3.28</v>
       </c>
       <c r="M48" t="n">
         <v>0.315</v>
       </c>
       <c r="N48" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0.315</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.42</v>
+        <v>4.35</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>-1.58</v>
       </c>
       <c r="G49" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.58</v>
+        <v>-0.46</v>
       </c>
       <c r="J49" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.46</v>
+        <v>-0.23</v>
       </c>
       <c r="M49" t="n">
-        <v>4.32</v>
+        <v>4.28</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.23</v>
+        <v>-0.93</v>
       </c>
       <c r="P49" t="n">
-        <v>4.32</v>
+        <v>4.28</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.23</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F50" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="J50" t="n">
         <v>1.11</v>
       </c>
-      <c r="E50" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-0.89</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I50" t="n">
-        <v>-4.5</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.07</v>
-      </c>
       <c r="K50" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="L50" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.74</v>
       </c>
       <c r="M50" t="n">
         <v>1.11</v>
       </c>
       <c r="N50" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
         <v>1.11</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.14</v>
+        <v>5.17</v>
       </c>
       <c r="E51" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="F51" t="n">
-        <v>1.78</v>
+        <v>0.58</v>
       </c>
       <c r="G51" t="n">
-        <v>5.17</v>
+        <v>5.22</v>
       </c>
       <c r="H51" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="I51" t="n">
-        <v>0.58</v>
+        <v>0.97</v>
       </c>
       <c r="J51" t="n">
-        <v>5.22</v>
+        <v>5.26</v>
       </c>
       <c r="K51" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="L51" t="n">
-        <v>0.97</v>
+        <v>0.77</v>
       </c>
       <c r="M51" t="n">
-        <v>5.26</v>
+        <v>5.18</v>
       </c>
       <c r="N51" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="O51" t="n">
-        <v>0.77</v>
+        <v>-1.52</v>
       </c>
       <c r="P51" t="n">
-        <v>5.26</v>
+        <v>5.18</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="R51" t="n">
-        <v>0.77</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.12</v>
+        <v>11.03</v>
       </c>
       <c r="E52" t="n">
-        <v>0.02</v>
+        <v>-0.09</v>
       </c>
       <c r="F52" t="n">
-        <v>0.18</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="G52" t="n">
-        <v>11.03</v>
+        <v>11.07</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="J52" t="n">
-        <v>11.07</v>
+        <v>11.1</v>
       </c>
       <c r="K52" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="L52" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="M52" t="n">
-        <v>11.1</v>
+        <v>11.21</v>
       </c>
       <c r="N52" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="O52" t="n">
-        <v>0.27</v>
+        <v>0.99</v>
       </c>
       <c r="P52" t="n">
-        <v>11.1</v>
+        <v>11.21</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="R52" t="n">
-        <v>0.27</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.140000000000001</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="F53" t="n">
-        <v>1.37</v>
+        <v>-1.11</v>
       </c>
       <c r="G53" t="n">
-        <v>8.050000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.11</v>
+        <v>0.5</v>
       </c>
       <c r="J53" t="n">
-        <v>8.09</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="L53" t="n">
-        <v>0.5</v>
+        <v>0.37</v>
       </c>
       <c r="M53" t="n">
-        <v>8.119999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="N53" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="O53" t="n">
-        <v>0.37</v>
+        <v>3.69</v>
       </c>
       <c r="P53" t="n">
-        <v>8.119999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="R53" t="n">
-        <v>0.37</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="54">
@@ -3748,40 +3748,40 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>-2.27</v>
       </c>
       <c r="J54" t="n">
         <v>0.43</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>-2.27</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.43</v>
+        <v>0.435</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="P54" t="n">
-        <v>0.43</v>
+        <v>0.435</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="55">
@@ -3801,49 +3801,49 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.62</v>
+        <v>0.615</v>
       </c>
       <c r="E55" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="G55" t="n">
         <v>0.615</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M55" t="n">
         <v>0.62</v>
       </c>
       <c r="N55" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
         <v>0.62</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3866,46 +3866,46 @@
         <v>0.395</v>
       </c>
       <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="H56" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F56" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.395</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
       <c r="J56" t="n">
-        <v>0.39</v>
+        <v>0.385</v>
       </c>
       <c r="K56" t="n">
         <v>-0.005</v>
       </c>
       <c r="L56" t="n">
-        <v>-1.27</v>
+        <v>-1.28</v>
       </c>
       <c r="M56" t="n">
         <v>0.385</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>-1.28</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
         <v>0.385</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>-1.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.73</v>
+        <v>3.68</v>
       </c>
       <c r="E57" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="F57" t="n">
-        <v>0.54</v>
+        <v>-1.34</v>
       </c>
       <c r="G57" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.34</v>
+        <v>-0.82</v>
       </c>
       <c r="J57" t="n">
         <v>3.65</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.82</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="P57" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-2.63</v>
+      </c>
+      <c r="G58" t="n">
         <v>0.076</v>
       </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.074</v>
-      </c>
       <c r="H58" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="I58" t="n">
-        <v>-2.63</v>
+        <v>2.7</v>
       </c>
       <c r="J58" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="K58" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="L58" t="n">
-        <v>2.7</v>
+        <v>1.32</v>
       </c>
       <c r="M58" t="n">
-        <v>0.077</v>
+        <v>0.08</v>
       </c>
       <c r="N58" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="O58" t="n">
-        <v>1.32</v>
+        <v>3.9</v>
       </c>
       <c r="P58" t="n">
-        <v>0.077</v>
+        <v>0.08</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="R58" t="n">
-        <v>1.32</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22.27</v>
+        <v>22.2</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.11</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.49</v>
+        <v>-0.31</v>
       </c>
       <c r="G59" t="n">
-        <v>22.2</v>
+        <v>22.32</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.31</v>
+        <v>0.54</v>
       </c>
       <c r="J59" t="n">
-        <v>22.32</v>
+        <v>22.96</v>
       </c>
       <c r="K59" t="n">
-        <v>0.12</v>
+        <v>0.64</v>
       </c>
       <c r="L59" t="n">
-        <v>0.54</v>
+        <v>2.87</v>
       </c>
       <c r="M59" t="n">
-        <v>22.96</v>
+        <v>22.74</v>
       </c>
       <c r="N59" t="n">
-        <v>0.64</v>
+        <v>-0.22</v>
       </c>
       <c r="O59" t="n">
-        <v>2.87</v>
+        <v>-0.96</v>
       </c>
       <c r="P59" t="n">
-        <v>22.96</v>
+        <v>22.74</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.64</v>
+        <v>-0.22</v>
       </c>
       <c r="R59" t="n">
-        <v>2.87</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="60">
@@ -4111,16 +4111,16 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="G60" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="H60" t="n">
         <v>-0.01</v>
@@ -4129,31 +4129,31 @@
         <v>-0.32</v>
       </c>
       <c r="J60" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.32</v>
+        <v>0.97</v>
       </c>
       <c r="M60" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="N60" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="O60" t="n">
-        <v>0.97</v>
+        <v>0.32</v>
       </c>
       <c r="P60" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="R60" t="n">
-        <v>0.97</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.875</v>
+        <v>0.88</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.015</v>
+        <v>0.005</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.69</v>
+        <v>0.57</v>
       </c>
       <c r="G61" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="H61" t="n">
-        <v>0.005</v>
+        <v>-0.01</v>
       </c>
       <c r="I61" t="n">
-        <v>0.57</v>
+        <v>-1.14</v>
       </c>
       <c r="J61" t="n">
-        <v>0.87</v>
+        <v>0.865</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="L61" t="n">
-        <v>-1.14</v>
+        <v>-0.57</v>
       </c>
       <c r="M61" t="n">
         <v>0.865</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>-0.57</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
         <v>0.865</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>-0.57</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-18 Close</t>
+          <t>2026-09-21 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-09-18 Change</t>
+          <t>2026-09-21 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-18 Change %</t>
+          <t>2026-09-21 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-09-21 Close</t>
+          <t>2026-09-22 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-09-21 Change</t>
+          <t>2026-09-22 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-09-21 Change %</t>
+          <t>2026-09-22 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-09-22 Close</t>
+          <t>2026-09-23 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-09-22 Change</t>
+          <t>2026-09-23 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-09-22 Change %</t>
+          <t>2026-09-23 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-09-23 Close</t>
+          <t>2026-09-24 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-09-23 Change</t>
+          <t>2026-09-24 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-09-23 Change %</t>
+          <t>2026-09-24 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-09-24 Close</t>
+          <t>2026-09-25 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-09-24 Change</t>
+          <t>2026-09-25 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-09-24 Change %</t>
+          <t>2026-09-25 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>161.6</v>
+        <v>161.5</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8</v>
+        <v>-0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>1.13</v>
+        <v>-0.06</v>
       </c>
       <c r="G3" t="n">
-        <v>161.5</v>
+        <v>159.3</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1</v>
+        <v>-2.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06</v>
+        <v>-1.36</v>
       </c>
       <c r="J3" t="n">
-        <v>159.3</v>
+        <v>159.5</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.2</v>
+        <v>0.2</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.36</v>
+        <v>0.13</v>
       </c>
       <c r="M3" t="n">
-        <v>159.5</v>
+        <v>156.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2</v>
+        <v>-2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>0.13</v>
+        <v>-1.63</v>
       </c>
       <c r="P3" t="n">
-        <v>159.5</v>
+        <v>156.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2</v>
+        <v>-2.6</v>
       </c>
       <c r="R3" t="n">
-        <v>0.13</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>0.66</v>
+        <v>0.41</v>
       </c>
       <c r="G4" t="n">
-        <v>246</v>
+        <v>239.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1</v>
+        <v>-6.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.41</v>
+        <v>-2.68</v>
       </c>
       <c r="J4" t="n">
-        <v>239.4</v>
+        <v>240</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.6</v>
+        <v>0.6</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.68</v>
+        <v>0.25</v>
       </c>
       <c r="M4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6</v>
+        <v>-4</v>
       </c>
       <c r="O4" t="n">
-        <v>0.25</v>
+        <v>-1.67</v>
       </c>
       <c r="P4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6</v>
+        <v>-4</v>
       </c>
       <c r="R4" t="n">
-        <v>0.25</v>
+        <v>-1.67</v>
       </c>
     </row>
     <row r="5">
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.3</v>
+        <v>6.51</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.02</v>
+        <v>0.21</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.32</v>
+        <v>3.33</v>
       </c>
       <c r="G5" t="n">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="H5" t="n">
-        <v>0.21</v>
+        <v>-0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>3.33</v>
+        <v>-0.15</v>
       </c>
       <c r="J5" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="K5" t="n">
         <v>-0.01</v>
@@ -728,22 +728,22 @@
         <v>-0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>6.49</v>
+        <v>6.61</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.01</v>
+        <v>0.12</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.15</v>
+        <v>1.85</v>
       </c>
       <c r="P5" t="n">
-        <v>6.49</v>
+        <v>6.61</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.01</v>
+        <v>0.12</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.15</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.5</v>
+        <v>7.58</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.27</v>
+        <v>1.07</v>
       </c>
       <c r="G6" t="n">
-        <v>7.58</v>
+        <v>7.54</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="I6" t="n">
-        <v>1.07</v>
+        <v>-0.53</v>
       </c>
       <c r="J6" t="n">
         <v>7.54</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>7.54</v>
+        <v>7.66</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="P6" t="n">
-        <v>7.54</v>
+        <v>7.66</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.99</v>
+        <v>6.06</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="G7" t="n">
-        <v>6.06</v>
+        <v>6.02</v>
       </c>
       <c r="H7" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="I7" t="n">
-        <v>1.17</v>
+        <v>-0.66</v>
       </c>
       <c r="J7" t="n">
-        <v>6.02</v>
+        <v>6</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.66</v>
+        <v>-0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>6.04</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.33</v>
+        <v>0.67</v>
       </c>
       <c r="P7" t="n">
-        <v>6</v>
+        <v>6.04</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.33</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.59</v>
+        <v>9.76</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.09</v>
+        <v>0.17</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.93</v>
+        <v>1.77</v>
       </c>
       <c r="G8" t="n">
-        <v>9.76</v>
+        <v>9.74</v>
       </c>
       <c r="H8" t="n">
-        <v>0.17</v>
+        <v>-0.02</v>
       </c>
       <c r="I8" t="n">
-        <v>1.77</v>
+        <v>-0.2</v>
       </c>
       <c r="J8" t="n">
-        <v>9.74</v>
+        <v>9.66</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.2</v>
+        <v>-0.82</v>
       </c>
       <c r="M8" t="n">
-        <v>9.66</v>
+        <v>9.68</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.82</v>
+        <v>0.21</v>
       </c>
       <c r="P8" t="n">
-        <v>9.66</v>
+        <v>9.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.82</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.140000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.49</v>
+        <v>1.47</v>
       </c>
       <c r="G9" t="n">
-        <v>8.26</v>
+        <v>8.24</v>
       </c>
       <c r="H9" t="n">
-        <v>0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="I9" t="n">
-        <v>1.47</v>
+        <v>-0.24</v>
       </c>
       <c r="J9" t="n">
-        <v>8.24</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.24</v>
+        <v>-0.36</v>
       </c>
       <c r="M9" t="n">
-        <v>8.210000000000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.36</v>
+        <v>0.85</v>
       </c>
       <c r="P9" t="n">
-        <v>8.210000000000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.36</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="G10" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="I10" t="n">
+        <v>-0.86</v>
+      </c>
+      <c r="J10" t="n">
+        <v>51.25</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-0.77</v>
+      </c>
+      <c r="M10" t="n">
         <v>51.2</v>
       </c>
-      <c r="E10" t="n">
+      <c r="N10" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O10" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F10" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="G10" t="n">
-        <v>52.1</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="I10" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="J10" t="n">
-        <v>51.65</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-0.86</v>
-      </c>
-      <c r="M10" t="n">
-        <v>51.25</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-0.4</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-0.77</v>
-      </c>
       <c r="P10" t="n">
-        <v>51.25</v>
+        <v>51.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.4</v>
+        <v>-0.05</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.77</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="11">
@@ -1073,25 +1073,25 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.51</v>
+        <v>4.49</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="G11" t="n">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="H11" t="n">
         <v>-0.02</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
       <c r="J11" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="K11" t="n">
         <v>-0.02</v>
@@ -1100,22 +1100,22 @@
         <v>-0.45</v>
       </c>
       <c r="M11" t="n">
-        <v>4.45</v>
+        <v>4.49</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.45</v>
+        <v>0.9</v>
       </c>
       <c r="P11" t="n">
-        <v>4.45</v>
+        <v>4.49</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="R11" t="n">
-        <v>-0.45</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.49</v>
+        <v>9.51</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.73</v>
+        <v>0.21</v>
       </c>
       <c r="G12" t="n">
-        <v>9.51</v>
+        <v>9.43</v>
       </c>
       <c r="H12" t="n">
-        <v>0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="I12" t="n">
-        <v>0.21</v>
+        <v>-0.84</v>
       </c>
       <c r="J12" t="n">
-        <v>9.43</v>
+        <v>9.35</v>
       </c>
       <c r="K12" t="n">
         <v>-0.08</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.84</v>
+        <v>-0.85</v>
       </c>
       <c r="M12" t="n">
-        <v>9.35</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.08</v>
+        <v>0.26</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.85</v>
+        <v>2.78</v>
       </c>
       <c r="P12" t="n">
-        <v>9.35</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.08</v>
+        <v>0.26</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.85</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23.6</v>
+        <v>23.94</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.28</v>
+        <v>0.34</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.17</v>
+        <v>1.44</v>
       </c>
       <c r="G13" t="n">
-        <v>23.94</v>
+        <v>23.68</v>
       </c>
       <c r="H13" t="n">
-        <v>0.34</v>
+        <v>-0.26</v>
       </c>
       <c r="I13" t="n">
-        <v>1.44</v>
+        <v>-1.09</v>
       </c>
       <c r="J13" t="n">
-        <v>23.68</v>
+        <v>23.34</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.26</v>
+        <v>-0.34</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.09</v>
+        <v>-1.44</v>
       </c>
       <c r="M13" t="n">
-        <v>23.34</v>
+        <v>23.84</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.34</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.44</v>
+        <v>2.14</v>
       </c>
       <c r="P13" t="n">
-        <v>23.34</v>
+        <v>23.84</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.34</v>
+        <v>0.5</v>
       </c>
       <c r="R13" t="n">
-        <v>-1.44</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-1.04</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.04</v>
+        <v>-0.53</v>
       </c>
       <c r="J14" t="n">
         <v>1.89</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.13</v>
+        <v>5.25</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="F15" t="n">
-        <v>1.18</v>
+        <v>2.34</v>
       </c>
       <c r="G15" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="H15" t="n">
-        <v>0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="I15" t="n">
-        <v>2.34</v>
+        <v>-1.14</v>
       </c>
       <c r="J15" t="n">
-        <v>5.19</v>
+        <v>5.17</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.14</v>
+        <v>-0.39</v>
       </c>
       <c r="M15" t="n">
-        <v>5.17</v>
+        <v>5.18</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.39</v>
+        <v>0.19</v>
       </c>
       <c r="P15" t="n">
-        <v>5.17</v>
+        <v>5.18</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.39</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="16">
@@ -1386,46 +1386,46 @@
         <v>4.43</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>4.43</v>
+        <v>4.39</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="J16" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="K16" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N16" t="n">
         <v>-0.04</v>
       </c>
-      <c r="L16" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="M16" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="O16" t="n">
-        <v>-1.14</v>
+        <v>-0.92</v>
       </c>
       <c r="P16" t="n">
-        <v>4.34</v>
+        <v>4.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.14</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="17">
@@ -1448,46 +1448,46 @@
         <v>3.31</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-0.91</v>
       </c>
       <c r="J17" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.91</v>
+        <v>-3.66</v>
       </c>
       <c r="M17" t="n">
         <v>3.16</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.66</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>3.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>-3.66</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.98</v>
+        <v>3.02</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.32</v>
+        <v>1.34</v>
       </c>
       <c r="G18" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="H18" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="I18" t="n">
-        <v>1.34</v>
+        <v>-1.66</v>
       </c>
       <c r="J18" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.66</v>
+        <v>-1.01</v>
       </c>
       <c r="M18" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.01</v>
+        <v>0.34</v>
       </c>
       <c r="P18" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="R18" t="n">
-        <v>-1.01</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>53.2</v>
+        <v>53.75</v>
       </c>
       <c r="E19" t="n">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="F19" t="n">
-        <v>0.66</v>
+        <v>1.03</v>
       </c>
       <c r="G19" t="n">
-        <v>53.75</v>
+        <v>53.9</v>
       </c>
       <c r="H19" t="n">
-        <v>0.55</v>
+        <v>0.15</v>
       </c>
       <c r="I19" t="n">
-        <v>1.03</v>
+        <v>0.28</v>
       </c>
       <c r="J19" t="n">
-        <v>53.9</v>
+        <v>53.4</v>
       </c>
       <c r="K19" t="n">
-        <v>0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="L19" t="n">
-        <v>0.28</v>
+        <v>-0.93</v>
       </c>
       <c r="M19" t="n">
-        <v>53.4</v>
+        <v>53.25</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.5</v>
+        <v>-0.15</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.93</v>
+        <v>-0.28</v>
       </c>
       <c r="P19" t="n">
-        <v>53.4</v>
+        <v>53.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.5</v>
+        <v>-0.15</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.93</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.38</v>
+        <v>29.08</v>
       </c>
       <c r="E20" t="n">
-        <v>0.74</v>
+        <v>-0.3</v>
       </c>
       <c r="F20" t="n">
-        <v>2.58</v>
+        <v>-1.02</v>
       </c>
       <c r="G20" t="n">
-        <v>29.08</v>
+        <v>29.7</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3</v>
+        <v>0.62</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.02</v>
+        <v>2.13</v>
       </c>
       <c r="J20" t="n">
         <v>29.7</v>
       </c>
       <c r="K20" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>29.7</v>
+        <v>29.44</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.88</v>
       </c>
       <c r="P20" t="n">
-        <v>29.7</v>
+        <v>29.44</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
+        <v>4.41</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="G21" t="n">
         <v>4.43</v>
       </c>
-      <c r="E21" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J21" t="n">
         <v>4.41</v>
       </c>
-      <c r="H21" t="n">
+      <c r="K21" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I21" t="n">
+      <c r="L21" t="n">
         <v>-0.45</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.45</v>
       </c>
       <c r="M21" t="n">
         <v>4.41</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>4.41</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79.05</v>
+        <v>79.2</v>
       </c>
       <c r="E22" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G22" t="n">
+        <v>78.95</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.32</v>
+      </c>
+      <c r="J22" t="n">
+        <v>78.8</v>
+      </c>
+      <c r="K22" t="n">
         <v>-0.15</v>
       </c>
-      <c r="F22" t="n">
+      <c r="L22" t="n">
         <v>-0.19</v>
       </c>
-      <c r="G22" t="n">
-        <v>79.2</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="J22" t="n">
-        <v>78.95</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-0.25</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-0.32</v>
-      </c>
       <c r="M22" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.15</v>
+        <v>0.1</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.19</v>
+        <v>0.13</v>
       </c>
       <c r="P22" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.15</v>
+        <v>0.1</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.19</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22.84</v>
+        <v>23.54</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F23" t="n">
-        <v>1.78</v>
+        <v>3.06</v>
       </c>
       <c r="G23" t="n">
-        <v>23.54</v>
+        <v>23.24</v>
       </c>
       <c r="H23" t="n">
-        <v>0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="I23" t="n">
-        <v>3.06</v>
+        <v>-1.27</v>
       </c>
       <c r="J23" t="n">
-        <v>23.24</v>
+        <v>22.6</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3</v>
+        <v>-0.64</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.27</v>
+        <v>-2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.64</v>
+        <v>0.1</v>
       </c>
       <c r="O23" t="n">
-        <v>-2.75</v>
+        <v>0.44</v>
       </c>
       <c r="P23" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.64</v>
+        <v>0.1</v>
       </c>
       <c r="R23" t="n">
-        <v>-2.75</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.42</v>
+        <v>16.21</v>
       </c>
       <c r="E24" t="n">
-        <v>0.54</v>
+        <v>-0.21</v>
       </c>
       <c r="F24" t="n">
-        <v>3.4</v>
+        <v>-1.28</v>
       </c>
       <c r="G24" t="n">
-        <v>16.21</v>
+        <v>15.86</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.21</v>
+        <v>-0.35</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.28</v>
+        <v>-2.16</v>
       </c>
       <c r="J24" t="n">
-        <v>15.86</v>
+        <v>15.25</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.35</v>
+        <v>-0.61</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.16</v>
+        <v>-3.85</v>
       </c>
       <c r="M24" t="n">
-        <v>15.25</v>
+        <v>15.09</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.61</v>
+        <v>-0.16</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.85</v>
+        <v>-1.05</v>
       </c>
       <c r="P24" t="n">
-        <v>15.25</v>
+        <v>15.09</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.61</v>
+        <v>-0.16</v>
       </c>
       <c r="R24" t="n">
-        <v>-3.85</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.4</v>
+        <v>27.58</v>
       </c>
       <c r="E25" t="n">
-        <v>0.26</v>
+        <v>1.18</v>
       </c>
       <c r="F25" t="n">
-        <v>0.99</v>
+        <v>4.47</v>
       </c>
       <c r="G25" t="n">
-        <v>27.58</v>
+        <v>27.2</v>
       </c>
       <c r="H25" t="n">
-        <v>1.18</v>
+        <v>-0.38</v>
       </c>
       <c r="I25" t="n">
-        <v>4.47</v>
+        <v>-1.38</v>
       </c>
       <c r="J25" t="n">
-        <v>27.2</v>
+        <v>26.18</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.38</v>
+        <v>-1.02</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.38</v>
+        <v>-3.75</v>
       </c>
       <c r="M25" t="n">
-        <v>26.18</v>
+        <v>26.58</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.02</v>
+        <v>0.4</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.75</v>
+        <v>1.53</v>
       </c>
       <c r="P25" t="n">
-        <v>26.18</v>
+        <v>26.58</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.02</v>
+        <v>0.4</v>
       </c>
       <c r="R25" t="n">
-        <v>-3.75</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>37.94</v>
+        <v>42.58</v>
       </c>
       <c r="E26" t="n">
-        <v>4.08</v>
+        <v>4.64</v>
       </c>
       <c r="F26" t="n">
-        <v>12.05</v>
+        <v>12.23</v>
       </c>
       <c r="G26" t="n">
-        <v>42.58</v>
+        <v>42.9</v>
       </c>
       <c r="H26" t="n">
-        <v>4.64</v>
+        <v>0.32</v>
       </c>
       <c r="I26" t="n">
-        <v>12.23</v>
+        <v>0.75</v>
       </c>
       <c r="J26" t="n">
-        <v>42.9</v>
+        <v>40.16</v>
       </c>
       <c r="K26" t="n">
-        <v>0.32</v>
+        <v>-2.74</v>
       </c>
       <c r="L26" t="n">
-        <v>0.75</v>
+        <v>-6.39</v>
       </c>
       <c r="M26" t="n">
-        <v>40.16</v>
+        <v>39.32</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.74</v>
+        <v>-0.84</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.39</v>
+        <v>-2.09</v>
       </c>
       <c r="P26" t="n">
-        <v>40.16</v>
+        <v>39.32</v>
       </c>
       <c r="Q26" t="n">
-        <v>-2.74</v>
+        <v>-0.84</v>
       </c>
       <c r="R26" t="n">
-        <v>-6.39</v>
+        <v>-2.09</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="E27" t="n">
-        <v>-7</v>
+        <v>11</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.64</v>
+        <v>2.63</v>
       </c>
       <c r="G27" t="n">
-        <v>430</v>
+        <v>451.6</v>
       </c>
       <c r="H27" t="n">
-        <v>11</v>
+        <v>21.6</v>
       </c>
       <c r="I27" t="n">
-        <v>2.63</v>
+        <v>5.02</v>
       </c>
       <c r="J27" t="n">
-        <v>451.6</v>
+        <v>441</v>
       </c>
       <c r="K27" t="n">
-        <v>21.6</v>
+        <v>-10.6</v>
       </c>
       <c r="L27" t="n">
-        <v>5.02</v>
+        <v>-2.35</v>
       </c>
       <c r="M27" t="n">
-        <v>441</v>
+        <v>438.4</v>
       </c>
       <c r="N27" t="n">
-        <v>-10.6</v>
+        <v>-2.6</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.35</v>
+        <v>-0.59</v>
       </c>
       <c r="P27" t="n">
-        <v>441</v>
+        <v>438.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>-10.6</v>
+        <v>-2.6</v>
       </c>
       <c r="R27" t="n">
-        <v>-2.35</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>109.3</v>
+        <v>112.6</v>
       </c>
       <c r="E28" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="F28" t="n">
-        <v>4</v>
+        <v>3.02</v>
       </c>
       <c r="G28" t="n">
-        <v>112.6</v>
+        <v>114.8</v>
       </c>
       <c r="H28" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="I28" t="n">
-        <v>3.02</v>
+        <v>1.95</v>
       </c>
       <c r="J28" t="n">
-        <v>114.8</v>
+        <v>109.8</v>
       </c>
       <c r="K28" t="n">
-        <v>2.2</v>
+        <v>-5</v>
       </c>
       <c r="L28" t="n">
-        <v>1.95</v>
+        <v>-4.36</v>
       </c>
       <c r="M28" t="n">
-        <v>109.8</v>
+        <v>110</v>
       </c>
       <c r="N28" t="n">
-        <v>-5</v>
+        <v>0.2</v>
       </c>
       <c r="O28" t="n">
-        <v>-4.36</v>
+        <v>0.18</v>
       </c>
       <c r="P28" t="n">
-        <v>109.8</v>
+        <v>110</v>
       </c>
       <c r="Q28" t="n">
-        <v>-5</v>
+        <v>0.2</v>
       </c>
       <c r="R28" t="n">
-        <v>-4.36</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>105</v>
+        <v>105.4</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="G29" t="n">
-        <v>105.4</v>
+        <v>106.5</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="I29" t="n">
-        <v>0.38</v>
+        <v>1.04</v>
       </c>
       <c r="J29" t="n">
-        <v>106.5</v>
+        <v>106.1</v>
       </c>
       <c r="K29" t="n">
-        <v>1.1</v>
+        <v>-0.4</v>
       </c>
       <c r="L29" t="n">
-        <v>1.04</v>
+        <v>-0.38</v>
       </c>
       <c r="M29" t="n">
-        <v>106.1</v>
+        <v>105.6</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.38</v>
+        <v>-0.47</v>
       </c>
       <c r="P29" t="n">
-        <v>106.1</v>
+        <v>105.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.38</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
+        <v>74</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="G30" t="n">
         <v>73.2</v>
       </c>
-      <c r="E30" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="G30" t="n">
-        <v>74</v>
-      </c>
       <c r="H30" t="n">
-        <v>0.8</v>
+        <v>-0.8</v>
       </c>
       <c r="I30" t="n">
-        <v>1.09</v>
+        <v>-1.08</v>
       </c>
       <c r="J30" t="n">
-        <v>73.2</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.8</v>
+        <v>-0.35</v>
       </c>
       <c r="L30" t="n">
-        <v>-1.08</v>
+        <v>-0.48</v>
       </c>
       <c r="M30" t="n">
-        <v>72.84999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.35</v>
+        <v>-0.6</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.48</v>
+        <v>-0.82</v>
       </c>
       <c r="P30" t="n">
-        <v>72.84999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.35</v>
+        <v>-0.6</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.48</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>87.2</v>
+        <v>89</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.15</v>
+        <v>1.8</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.17</v>
+        <v>2.06</v>
       </c>
       <c r="G31" t="n">
-        <v>89</v>
+        <v>89.5</v>
       </c>
       <c r="H31" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="I31" t="n">
-        <v>2.06</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>89.5</v>
+        <v>88.55</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5</v>
+        <v>-0.95</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.06</v>
       </c>
       <c r="M31" t="n">
-        <v>88.55</v>
+        <v>86.3</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.95</v>
+        <v>-2.25</v>
       </c>
       <c r="O31" t="n">
-        <v>-1.06</v>
+        <v>-2.54</v>
       </c>
       <c r="P31" t="n">
-        <v>88.55</v>
+        <v>86.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.95</v>
+        <v>-2.25</v>
       </c>
       <c r="R31" t="n">
-        <v>-1.06</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>65.15000000000001</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>2.75</v>
+        <v>0.45</v>
       </c>
       <c r="F32" t="n">
-        <v>4.41</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G32" t="n">
-        <v>65.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="H32" t="n">
-        <v>0.45</v>
+        <v>-1.3</v>
       </c>
       <c r="I32" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.98</v>
       </c>
       <c r="J32" t="n">
-        <v>64.3</v>
+        <v>63.8</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="L32" t="n">
-        <v>-1.98</v>
+        <v>-0.78</v>
       </c>
       <c r="M32" t="n">
         <v>63.8</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.78</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>63.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>81.5</v>
+        <v>81.2</v>
       </c>
       <c r="E33" t="n">
-        <v>0.35</v>
+        <v>-0.3</v>
       </c>
       <c r="F33" t="n">
-        <v>0.43</v>
+        <v>-0.37</v>
       </c>
       <c r="G33" t="n">
-        <v>81.2</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3</v>
+        <v>0.15</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.37</v>
+        <v>0.18</v>
       </c>
       <c r="J33" t="n">
-        <v>81.34999999999999</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>0.15</v>
+        <v>-1</v>
       </c>
       <c r="L33" t="n">
-        <v>0.18</v>
+        <v>-1.23</v>
       </c>
       <c r="M33" t="n">
-        <v>80.34999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="N33" t="n">
-        <v>-1</v>
+        <v>-0.85</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.23</v>
+        <v>-1.06</v>
       </c>
       <c r="P33" t="n">
-        <v>80.34999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>-1</v>
+        <v>-0.85</v>
       </c>
       <c r="R33" t="n">
-        <v>-1.23</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>30.74</v>
+        <v>30.82</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8</v>
+        <v>0.08</v>
       </c>
       <c r="F34" t="n">
-        <v>2.67</v>
+        <v>0.26</v>
       </c>
       <c r="G34" t="n">
-        <v>30.82</v>
+        <v>31.22</v>
       </c>
       <c r="H34" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="I34" t="n">
-        <v>0.26</v>
+        <v>1.3</v>
       </c>
       <c r="J34" t="n">
-        <v>31.22</v>
+        <v>30.78</v>
       </c>
       <c r="K34" t="n">
-        <v>0.4</v>
+        <v>-0.44</v>
       </c>
       <c r="L34" t="n">
-        <v>1.3</v>
+        <v>-1.41</v>
       </c>
       <c r="M34" t="n">
-        <v>30.78</v>
+        <v>30.5</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.44</v>
+        <v>-0.28</v>
       </c>
       <c r="O34" t="n">
-        <v>-1.41</v>
+        <v>-0.91</v>
       </c>
       <c r="P34" t="n">
-        <v>30.78</v>
+        <v>30.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.44</v>
+        <v>-0.28</v>
       </c>
       <c r="R34" t="n">
-        <v>-1.41</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="F35" t="n">
-        <v>2.37</v>
+        <v>0.46</v>
       </c>
       <c r="G35" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="H35" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I35" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="J35" t="n">
-        <v>4.35</v>
+        <v>4.28</v>
       </c>
       <c r="K35" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>0.23</v>
+        <v>-1.61</v>
       </c>
       <c r="M35" t="n">
-        <v>4.35</v>
+        <v>4.28</v>
       </c>
       <c r="N35" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>0.23</v>
+        <v>-1.61</v>
       </c>
       <c r="P35" t="n">
-        <v>4.35</v>
+        <v>4.28</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R35" t="n">
-        <v>0.23</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.31</v>
+        <v>9.34</v>
       </c>
       <c r="E36" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G36" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I36" t="n">
         <v>0.21</v>
       </c>
-      <c r="F36" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="G36" t="n">
-        <v>9.34</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.32</v>
-      </c>
       <c r="J36" t="n">
-        <v>9.359999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="K36" t="n">
-        <v>0.02</v>
+        <v>-0.13</v>
       </c>
       <c r="L36" t="n">
-        <v>0.21</v>
+        <v>-1.39</v>
       </c>
       <c r="M36" t="n">
-        <v>9.359999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="N36" t="n">
-        <v>0.02</v>
+        <v>-0.13</v>
       </c>
       <c r="O36" t="n">
-        <v>0.21</v>
+        <v>-1.39</v>
       </c>
       <c r="P36" t="n">
-        <v>9.359999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.02</v>
+        <v>-0.13</v>
       </c>
       <c r="R36" t="n">
-        <v>0.21</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>388</v>
+        <v>391.2</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.6</v>
+        <v>3.2</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.15</v>
+        <v>0.82</v>
       </c>
       <c r="G37" t="n">
-        <v>391.2</v>
+        <v>397.4</v>
       </c>
       <c r="H37" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="I37" t="n">
-        <v>0.82</v>
+        <v>1.58</v>
       </c>
       <c r="J37" t="n">
-        <v>397.4</v>
+        <v>395.8</v>
       </c>
       <c r="K37" t="n">
-        <v>6.2</v>
+        <v>-1.6</v>
       </c>
       <c r="L37" t="n">
-        <v>1.58</v>
+        <v>-0.4</v>
       </c>
       <c r="M37" t="n">
-        <v>395.8</v>
+        <v>393.4</v>
       </c>
       <c r="N37" t="n">
-        <v>-1.6</v>
+        <v>-2.4</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.4</v>
+        <v>-0.61</v>
       </c>
       <c r="P37" t="n">
-        <v>395.8</v>
+        <v>393.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>-1.6</v>
+        <v>-2.4</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.4</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.24</v>
+        <v>12.1</v>
       </c>
       <c r="E38" t="n">
-        <v>0.04</v>
+        <v>-0.14</v>
       </c>
       <c r="F38" t="n">
-        <v>0.33</v>
+        <v>-1.14</v>
       </c>
       <c r="G38" t="n">
-        <v>12.1</v>
+        <v>12.16</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.14</v>
+        <v>0.06</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.14</v>
+        <v>0.5</v>
       </c>
       <c r="J38" t="n">
-        <v>12.16</v>
+        <v>12.07</v>
       </c>
       <c r="K38" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="L38" t="n">
-        <v>0.5</v>
+        <v>-0.74</v>
       </c>
       <c r="M38" t="n">
-        <v>12.07</v>
+        <v>12.04</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.09</v>
+        <v>-0.03</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.74</v>
+        <v>-0.25</v>
       </c>
       <c r="P38" t="n">
-        <v>12.07</v>
+        <v>12.04</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.09</v>
+        <v>-0.03</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.74</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
+        <v>504</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>-0.59</v>
+      </c>
+      <c r="G39" t="n">
         <v>507</v>
       </c>
-      <c r="E39" t="n">
-        <v>0</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" t="n">
-        <v>504</v>
-      </c>
       <c r="H39" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.59</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
-        <v>507</v>
+        <v>511.5</v>
       </c>
       <c r="K39" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="L39" t="n">
-        <v>0.6</v>
+        <v>0.89</v>
       </c>
       <c r="M39" t="n">
-        <v>511.5</v>
+        <v>492.8</v>
       </c>
       <c r="N39" t="n">
-        <v>4.5</v>
+        <v>-18.7</v>
       </c>
       <c r="O39" t="n">
-        <v>0.89</v>
+        <v>-3.66</v>
       </c>
       <c r="P39" t="n">
-        <v>511.5</v>
+        <v>492.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>4.5</v>
+        <v>-18.7</v>
       </c>
       <c r="R39" t="n">
-        <v>0.89</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>42.04</v>
+        <v>40.5</v>
       </c>
       <c r="E40" t="n">
-        <v>0.86</v>
+        <v>-1.54</v>
       </c>
       <c r="F40" t="n">
-        <v>2.09</v>
+        <v>-3.66</v>
       </c>
       <c r="G40" t="n">
-        <v>40.5</v>
+        <v>40.74</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.54</v>
+        <v>0.24</v>
       </c>
       <c r="I40" t="n">
-        <v>-3.66</v>
+        <v>0.59</v>
       </c>
       <c r="J40" t="n">
-        <v>40.74</v>
+        <v>40.4</v>
       </c>
       <c r="K40" t="n">
-        <v>0.24</v>
+        <v>-0.34</v>
       </c>
       <c r="L40" t="n">
-        <v>0.59</v>
+        <v>-0.83</v>
       </c>
       <c r="M40" t="n">
-        <v>40.4</v>
+        <v>40.22</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.34</v>
+        <v>-0.18</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.83</v>
+        <v>-0.45</v>
       </c>
       <c r="P40" t="n">
-        <v>40.4</v>
+        <v>40.22</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.34</v>
+        <v>-0.18</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.83</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.38</v>
+        <v>31.67</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1</v>
+        <v>0.29</v>
       </c>
       <c r="F41" t="n">
-        <v>0.32</v>
+        <v>0.92</v>
       </c>
       <c r="G41" t="n">
-        <v>31.67</v>
+        <v>32.14</v>
       </c>
       <c r="H41" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="I41" t="n">
-        <v>0.92</v>
+        <v>1.48</v>
       </c>
       <c r="J41" t="n">
-        <v>32.14</v>
+        <v>31.65</v>
       </c>
       <c r="K41" t="n">
-        <v>0.47</v>
+        <v>-0.49</v>
       </c>
       <c r="L41" t="n">
-        <v>1.48</v>
+        <v>-1.52</v>
       </c>
       <c r="M41" t="n">
-        <v>31.65</v>
+        <v>31.59</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.49</v>
+        <v>-0.06</v>
       </c>
       <c r="O41" t="n">
-        <v>-1.52</v>
+        <v>-0.19</v>
       </c>
       <c r="P41" t="n">
-        <v>31.65</v>
+        <v>31.59</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.49</v>
+        <v>-0.06</v>
       </c>
       <c r="R41" t="n">
-        <v>-1.52</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>76.86</v>
+        <v>77.36</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.08</v>
+        <v>0.5</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.1</v>
+        <v>0.65</v>
       </c>
       <c r="G42" t="n">
-        <v>77.36</v>
+        <v>77.8</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="I42" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="J42" t="n">
-        <v>77.8</v>
+        <v>77.69</v>
       </c>
       <c r="K42" t="n">
-        <v>0.44</v>
+        <v>-0.11</v>
       </c>
       <c r="L42" t="n">
-        <v>0.57</v>
+        <v>-0.14</v>
       </c>
       <c r="M42" t="n">
-        <v>77.69</v>
+        <v>77.48</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.11</v>
+        <v>-0.21</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.14</v>
+        <v>-0.27</v>
       </c>
       <c r="P42" t="n">
-        <v>77.69</v>
+        <v>77.48</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.11</v>
+        <v>-0.21</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.14</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>41.78</v>
+        <v>42.1</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.1</v>
+        <v>0.32</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.24</v>
+        <v>0.77</v>
       </c>
       <c r="G43" t="n">
-        <v>42.1</v>
+        <v>42.8</v>
       </c>
       <c r="H43" t="n">
-        <v>0.32</v>
+        <v>0.7</v>
       </c>
       <c r="I43" t="n">
-        <v>0.77</v>
+        <v>1.66</v>
       </c>
       <c r="J43" t="n">
-        <v>42.8</v>
+        <v>42.84</v>
       </c>
       <c r="K43" t="n">
-        <v>0.7</v>
+        <v>0.04</v>
       </c>
       <c r="L43" t="n">
-        <v>1.66</v>
+        <v>0.09</v>
       </c>
       <c r="M43" t="n">
-        <v>42.84</v>
+        <v>42.5</v>
       </c>
       <c r="N43" t="n">
-        <v>0.04</v>
+        <v>-0.34</v>
       </c>
       <c r="O43" t="n">
-        <v>0.09</v>
+        <v>-0.79</v>
       </c>
       <c r="P43" t="n">
-        <v>42.84</v>
+        <v>42.5</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.04</v>
+        <v>-0.34</v>
       </c>
       <c r="R43" t="n">
-        <v>0.09</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="44">
@@ -3122,46 +3122,46 @@
         <v>5.9</v>
       </c>
       <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="K44" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F44" t="n">
+      <c r="L44" t="n">
         <v>-0.51</v>
       </c>
-      <c r="G44" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>5.93</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.51</v>
-      </c>
       <c r="M44" t="n">
-        <v>5.9</v>
+        <v>5.85</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.51</v>
+        <v>-0.85</v>
       </c>
       <c r="P44" t="n">
-        <v>5.9</v>
+        <v>5.85</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.51</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.47</v>
+        <v>-3.3</v>
       </c>
       <c r="G45" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="I45" t="n">
-        <v>-3.3</v>
+        <v>4.88</v>
       </c>
       <c r="J45" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="K45" t="n">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="L45" t="n">
-        <v>4.88</v>
+        <v>-2.33</v>
       </c>
       <c r="M45" t="n">
         <v>2.1</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>-2.33</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
         <v>2.1</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>-2.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3246,31 +3246,31 @@
         <v>3.81</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.52</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="K46" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="M46" t="n">
         <v>3.81</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.82</v>
       </c>
       <c r="N46" t="n">
         <v>-0.01</v>
@@ -3279,7 +3279,7 @@
         <v>-0.26</v>
       </c>
       <c r="P46" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="Q46" t="n">
         <v>-0.01</v>
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.43</v>
+        <v>10.39</v>
       </c>
       <c r="E47" t="n">
-        <v>0.24</v>
+        <v>-0.04</v>
       </c>
       <c r="F47" t="n">
-        <v>2.36</v>
+        <v>-0.38</v>
       </c>
       <c r="G47" t="n">
-        <v>10.39</v>
+        <v>10.69</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.04</v>
+        <v>0.3</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.38</v>
+        <v>2.89</v>
       </c>
       <c r="J47" t="n">
-        <v>10.69</v>
+        <v>10.81</v>
       </c>
       <c r="K47" t="n">
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="L47" t="n">
-        <v>2.89</v>
+        <v>1.12</v>
       </c>
       <c r="M47" t="n">
-        <v>10.81</v>
+        <v>10.86</v>
       </c>
       <c r="N47" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="O47" t="n">
-        <v>1.12</v>
+        <v>0.46</v>
       </c>
       <c r="P47" t="n">
-        <v>10.81</v>
+        <v>10.86</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="R47" t="n">
-        <v>1.12</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="48">
@@ -3367,31 +3367,31 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.31</v>
+        <v>0.305</v>
       </c>
       <c r="E48" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="F48" t="n">
-        <v>1.64</v>
+        <v>-1.61</v>
       </c>
       <c r="G48" t="n">
-        <v>0.305</v>
+        <v>0.315</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.61</v>
+        <v>3.28</v>
       </c>
       <c r="J48" t="n">
         <v>0.315</v>
       </c>
       <c r="K48" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0.315</v>
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.58</v>
+        <v>-0.46</v>
       </c>
       <c r="G49" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.46</v>
+        <v>-0.23</v>
       </c>
       <c r="J49" t="n">
-        <v>4.32</v>
+        <v>4.28</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.23</v>
+        <v>-0.93</v>
       </c>
       <c r="M49" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.93</v>
+        <v>-0.7</v>
       </c>
       <c r="P49" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.04</v>
+        <v>-0.03</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.93</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>-4.5</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G50" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="H50" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="I50" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.74</v>
       </c>
       <c r="J50" t="n">
         <v>1.11</v>
       </c>
       <c r="K50" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P50" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5.18</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="M51" t="n">
         <v>5.17</v>
       </c>
-      <c r="E51" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="G51" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="J51" t="n">
-        <v>5.26</v>
-      </c>
-      <c r="K51" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L51" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="M51" t="n">
-        <v>5.18</v>
-      </c>
       <c r="N51" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="O51" t="n">
-        <v>-1.52</v>
+        <v>-0.19</v>
       </c>
       <c r="P51" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="R51" t="n">
-        <v>-1.52</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.03</v>
+        <v>11.07</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="G52" t="n">
-        <v>11.07</v>
+        <v>11.1</v>
       </c>
       <c r="H52" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I52" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="J52" t="n">
-        <v>11.1</v>
+        <v>11.21</v>
       </c>
       <c r="K52" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="L52" t="n">
-        <v>0.27</v>
+        <v>0.99</v>
       </c>
       <c r="M52" t="n">
-        <v>11.21</v>
+        <v>11.29</v>
       </c>
       <c r="N52" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="O52" t="n">
-        <v>0.99</v>
+        <v>0.71</v>
       </c>
       <c r="P52" t="n">
-        <v>11.21</v>
+        <v>11.29</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="R52" t="n">
-        <v>0.99</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.050000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.09</v>
+        <v>0.04</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.11</v>
+        <v>0.5</v>
       </c>
       <c r="G53" t="n">
-        <v>8.09</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="H53" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5</v>
+        <v>0.37</v>
       </c>
       <c r="J53" t="n">
-        <v>8.119999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="K53" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="L53" t="n">
-        <v>0.37</v>
+        <v>3.69</v>
       </c>
       <c r="M53" t="n">
-        <v>8.42</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="O53" t="n">
-        <v>3.69</v>
+        <v>-2.38</v>
       </c>
       <c r="P53" t="n">
-        <v>8.42</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="R53" t="n">
-        <v>3.69</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="54">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>-2.27</v>
       </c>
       <c r="G54" t="n">
         <v>0.43</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>-2.27</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0.43</v>
+        <v>0.435</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="M54" t="n">
         <v>0.435</v>
       </c>
       <c r="N54" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
         <v>0.435</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3804,28 +3804,28 @@
         <v>0.615</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J55" t="n">
         <v>0.62</v>
       </c>
       <c r="K55" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0.62</v>
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.395</v>
+        <v>0.39</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
       <c r="G56" t="n">
-        <v>0.39</v>
+        <v>0.385</v>
       </c>
       <c r="H56" t="n">
         <v>-0.005</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.27</v>
+        <v>-1.28</v>
       </c>
       <c r="J56" t="n">
         <v>0.385</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>-1.28</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.385</v>
+        <v>0.39</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P56" t="n">
-        <v>0.385</v>
+        <v>0.39</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.68</v>
+        <v>3.65</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.34</v>
+        <v>-0.82</v>
       </c>
       <c r="G57" t="n">
         <v>3.65</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.82</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="M57" t="n">
         <v>3.65</v>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.67</v>
-      </c>
       <c r="N57" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="O57" t="n">
-        <v>0.55</v>
+        <v>-0.54</v>
       </c>
       <c r="P57" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="R57" t="n">
-        <v>0.55</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.074</v>
+        <v>0.076</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.002</v>
+        <v>0.002</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.63</v>
+        <v>2.7</v>
       </c>
       <c r="G58" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="H58" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="I58" t="n">
-        <v>2.7</v>
+        <v>1.32</v>
       </c>
       <c r="J58" t="n">
-        <v>0.077</v>
+        <v>0.08</v>
       </c>
       <c r="K58" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="L58" t="n">
-        <v>1.32</v>
+        <v>3.9</v>
       </c>
       <c r="M58" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="N58" t="n">
-        <v>0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="O58" t="n">
-        <v>3.9</v>
+        <v>-1.25</v>
       </c>
       <c r="P58" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="R58" t="n">
-        <v>3.9</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22.2</v>
+        <v>22.32</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.31</v>
+        <v>0.54</v>
       </c>
       <c r="G59" t="n">
-        <v>22.32</v>
+        <v>22.96</v>
       </c>
       <c r="H59" t="n">
-        <v>0.12</v>
+        <v>0.64</v>
       </c>
       <c r="I59" t="n">
-        <v>0.54</v>
+        <v>2.87</v>
       </c>
       <c r="J59" t="n">
-        <v>22.96</v>
+        <v>22.74</v>
       </c>
       <c r="K59" t="n">
-        <v>0.64</v>
+        <v>-0.22</v>
       </c>
       <c r="L59" t="n">
-        <v>2.87</v>
+        <v>-0.96</v>
       </c>
       <c r="M59" t="n">
-        <v>22.74</v>
+        <v>22.42</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.22</v>
+        <v>-0.32</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.96</v>
+        <v>-1.41</v>
       </c>
       <c r="P59" t="n">
-        <v>22.74</v>
+        <v>22.42</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.22</v>
+        <v>-0.32</v>
       </c>
       <c r="R59" t="n">
-        <v>-0.96</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="60">
@@ -4111,7 +4111,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="E60" t="n">
         <v>-0.01</v>
@@ -4120,40 +4120,40 @@
         <v>-0.32</v>
       </c>
       <c r="G60" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.32</v>
+        <v>0.97</v>
       </c>
       <c r="J60" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="K60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="N60" t="n">
         <v>0.03</v>
       </c>
-      <c r="L60" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0.01</v>
-      </c>
       <c r="O60" t="n">
-        <v>0.32</v>
+        <v>0.96</v>
       </c>
       <c r="P60" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="R60" t="n">
-        <v>0.32</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="E61" t="n">
-        <v>0.005</v>
+        <v>-0.01</v>
       </c>
       <c r="F61" t="n">
-        <v>0.57</v>
+        <v>-1.14</v>
       </c>
       <c r="G61" t="n">
-        <v>0.87</v>
+        <v>0.865</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.14</v>
+        <v>-0.57</v>
       </c>
       <c r="J61" t="n">
         <v>0.865</v>
       </c>
       <c r="K61" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="N61" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L61" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0</v>
-      </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>-0.58</v>
       </c>
       <c r="P61" t="n">
-        <v>0.865</v>
+        <v>0.86</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-21 Close</t>
+          <t>2026-09-22 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-09-21 Change</t>
+          <t>2026-09-22 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-21 Change %</t>
+          <t>2026-09-22 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-09-22 Close</t>
+          <t>2026-09-23 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-09-22 Change</t>
+          <t>2026-09-23 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-09-22 Change %</t>
+          <t>2026-09-23 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-09-23 Close</t>
+          <t>2026-09-24 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-09-23 Change</t>
+          <t>2026-09-24 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-09-23 Change %</t>
+          <t>2026-09-24 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-09-24 Close</t>
+          <t>2026-09-25 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-09-24 Change</t>
+          <t>2026-09-25 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-09-24 Change %</t>
+          <t>2026-09-25 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-09-25 Close</t>
+          <t>2026-09-28 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-09-25 Change</t>
+          <t>2026-09-28 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-09-25 Change %</t>
+          <t>2026-09-28 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>161.5</v>
+        <v>159.3</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1</v>
+        <v>-2.2</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.06</v>
+        <v>-1.36</v>
       </c>
       <c r="G3" t="n">
-        <v>159.3</v>
+        <v>159.5</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.2</v>
+        <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.36</v>
+        <v>0.13</v>
       </c>
       <c r="J3" t="n">
-        <v>159.5</v>
+        <v>156.9</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2</v>
+        <v>-2.6</v>
       </c>
       <c r="L3" t="n">
-        <v>0.13</v>
+        <v>-1.63</v>
       </c>
       <c r="M3" t="n">
-        <v>156.9</v>
+        <v>157.6</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.6</v>
+        <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.63</v>
+        <v>0.45</v>
       </c>
       <c r="P3" t="n">
-        <v>156.9</v>
+        <v>158.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.6</v>
+        <v>1.3</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.63</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>246</v>
+        <v>239.4</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>-6.6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.41</v>
+        <v>-2.68</v>
       </c>
       <c r="G4" t="n">
-        <v>239.4</v>
+        <v>240</v>
       </c>
       <c r="H4" t="n">
-        <v>-6.6</v>
+        <v>0.6</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.68</v>
+        <v>0.25</v>
       </c>
       <c r="J4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6</v>
+        <v>-4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.25</v>
+        <v>-1.67</v>
       </c>
       <c r="M4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N4" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.67</v>
+        <v>0.85</v>
       </c>
       <c r="P4" t="n">
-        <v>236</v>
+        <v>242.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>-4</v>
+        <v>4.6</v>
       </c>
       <c r="R4" t="n">
-        <v>-1.67</v>
+        <v>1.93</v>
       </c>
     </row>
     <row r="5">
@@ -701,16 +701,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.21</v>
+        <v>-0.01</v>
       </c>
       <c r="F5" t="n">
-        <v>3.33</v>
+        <v>-0.15</v>
       </c>
       <c r="G5" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="H5" t="n">
         <v>-0.01</v>
@@ -719,31 +719,31 @@
         <v>-0.15</v>
       </c>
       <c r="J5" t="n">
-        <v>6.49</v>
+        <v>6.61</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.01</v>
+        <v>0.12</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.15</v>
+        <v>1.85</v>
       </c>
       <c r="M5" t="n">
-        <v>6.61</v>
+        <v>6.51</v>
       </c>
       <c r="N5" t="n">
-        <v>0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.85</v>
+        <v>-1.51</v>
       </c>
       <c r="P5" t="n">
-        <v>6.61</v>
+        <v>6.55</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="R5" t="n">
-        <v>1.85</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.58</v>
+        <v>7.54</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="F6" t="n">
-        <v>1.07</v>
+        <v>-0.53</v>
       </c>
       <c r="G6" t="n">
         <v>7.54</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>7.54</v>
+        <v>7.66</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M6" t="n">
-        <v>7.66</v>
+        <v>7.51</v>
       </c>
       <c r="N6" t="n">
-        <v>0.12</v>
+        <v>-0.15</v>
       </c>
       <c r="O6" t="n">
-        <v>1.59</v>
+        <v>-1.96</v>
       </c>
       <c r="P6" t="n">
-        <v>7.66</v>
+        <v>7.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.12</v>
+        <v>0.19</v>
       </c>
       <c r="R6" t="n">
-        <v>1.59</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.06</v>
+        <v>6.02</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="F7" t="n">
-        <v>1.17</v>
+        <v>-0.66</v>
       </c>
       <c r="G7" t="n">
-        <v>6.02</v>
+        <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.66</v>
+        <v>-0.33</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>6.04</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.33</v>
+        <v>0.67</v>
       </c>
       <c r="M7" t="n">
-        <v>6.04</v>
+        <v>5.98</v>
       </c>
       <c r="N7" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="O7" t="n">
-        <v>0.67</v>
+        <v>-0.99</v>
       </c>
       <c r="P7" t="n">
-        <v>6.04</v>
+        <v>6.07</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="R7" t="n">
-        <v>0.67</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.76</v>
+        <v>9.74</v>
       </c>
       <c r="E8" t="n">
-        <v>0.17</v>
+        <v>-0.02</v>
       </c>
       <c r="F8" t="n">
-        <v>1.77</v>
+        <v>-0.2</v>
       </c>
       <c r="G8" t="n">
-        <v>9.74</v>
+        <v>9.66</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2</v>
+        <v>-0.82</v>
       </c>
       <c r="J8" t="n">
-        <v>9.66</v>
+        <v>9.68</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.82</v>
+        <v>0.21</v>
       </c>
       <c r="M8" t="n">
-        <v>9.68</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.02</v>
+        <v>-0.15</v>
       </c>
       <c r="O8" t="n">
-        <v>0.21</v>
+        <v>-1.55</v>
       </c>
       <c r="P8" t="n">
         <v>9.68</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02</v>
+        <v>0.15</v>
       </c>
       <c r="R8" t="n">
-        <v>0.21</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.26</v>
+        <v>8.24</v>
       </c>
       <c r="E9" t="n">
-        <v>0.12</v>
+        <v>-0.02</v>
       </c>
       <c r="F9" t="n">
-        <v>1.47</v>
+        <v>-0.24</v>
       </c>
       <c r="G9" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I9" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="P9" t="n">
         <v>8.24</v>
       </c>
-      <c r="H9" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="M9" t="n">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="P9" t="n">
-        <v>8.279999999999999</v>
-      </c>
       <c r="Q9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="R9" t="n">
-        <v>0.85</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>52.1</v>
+        <v>51.65</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9</v>
+        <v>-0.45</v>
       </c>
       <c r="F10" t="n">
-        <v>1.76</v>
+        <v>-0.86</v>
       </c>
       <c r="G10" t="n">
-        <v>51.65</v>
+        <v>51.25</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.45</v>
+        <v>-0.4</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.86</v>
+        <v>-0.77</v>
       </c>
       <c r="J10" t="n">
-        <v>51.25</v>
+        <v>51.2</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4</v>
+        <v>-0.05</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.77</v>
+        <v>-0.1</v>
       </c>
       <c r="M10" t="n">
-        <v>51.2</v>
+        <v>50.5</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.05</v>
+        <v>-0.7</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1</v>
+        <v>-1.37</v>
       </c>
       <c r="P10" t="n">
-        <v>51.2</v>
+        <v>51.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.05</v>
+        <v>0.6</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.1</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="11">
@@ -1073,16 +1073,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.49</v>
+        <v>4.47</v>
       </c>
       <c r="E11" t="n">
         <v>-0.02</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
       <c r="G11" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="H11" t="n">
         <v>-0.02</v>
@@ -1091,31 +1091,31 @@
         <v>-0.45</v>
       </c>
       <c r="J11" t="n">
-        <v>4.45</v>
+        <v>4.49</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.45</v>
+        <v>0.9</v>
       </c>
       <c r="M11" t="n">
-        <v>4.49</v>
+        <v>4.43</v>
       </c>
       <c r="N11" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9</v>
+        <v>-1.34</v>
       </c>
       <c r="P11" t="n">
-        <v>4.49</v>
+        <v>4.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.51</v>
+        <v>9.43</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="F12" t="n">
-        <v>0.21</v>
+        <v>-0.84</v>
       </c>
       <c r="G12" t="n">
-        <v>9.43</v>
+        <v>9.35</v>
       </c>
       <c r="H12" t="n">
         <v>-0.08</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.84</v>
+        <v>-0.85</v>
       </c>
       <c r="J12" t="n">
-        <v>9.35</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.08</v>
+        <v>0.26</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.85</v>
+        <v>2.78</v>
       </c>
       <c r="M12" t="n">
-        <v>9.609999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="N12" t="n">
-        <v>0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="O12" t="n">
-        <v>2.78</v>
+        <v>-2.08</v>
       </c>
       <c r="P12" t="n">
-        <v>9.609999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="R12" t="n">
-        <v>2.78</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23.94</v>
+        <v>23.68</v>
       </c>
       <c r="E13" t="n">
-        <v>0.34</v>
+        <v>-0.26</v>
       </c>
       <c r="F13" t="n">
-        <v>1.44</v>
+        <v>-1.09</v>
       </c>
       <c r="G13" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="J13" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="M13" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="O13" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="P13" t="n">
         <v>23.68</v>
       </c>
-      <c r="H13" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="J13" t="n">
-        <v>23.34</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="M13" t="n">
-        <v>23.84</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="O13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="P13" t="n">
-        <v>23.84</v>
-      </c>
       <c r="Q13" t="n">
-        <v>0.5</v>
+        <v>0.28</v>
       </c>
       <c r="R13" t="n">
-        <v>2.14</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="14">
@@ -1259,43 +1259,43 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.04</v>
+        <v>-0.53</v>
       </c>
       <c r="G14" t="n">
         <v>1.89</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="O14" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="P14" t="n">
         <v>1.89</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.9</v>
       </c>
       <c r="Q14" t="n">
         <v>0.01</v>
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="E15" t="n">
-        <v>0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="F15" t="n">
-        <v>2.34</v>
+        <v>-1.14</v>
       </c>
       <c r="G15" t="n">
-        <v>5.19</v>
+        <v>5.17</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.14</v>
+        <v>-0.39</v>
       </c>
       <c r="J15" t="n">
-        <v>5.17</v>
+        <v>5.18</v>
       </c>
       <c r="K15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="N15" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L15" t="n">
+      <c r="O15" t="n">
         <v>-0.39</v>
       </c>
-      <c r="M15" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.19</v>
-      </c>
       <c r="P15" t="n">
-        <v>5.18</v>
+        <v>5.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.01</v>
+        <v>0.2</v>
       </c>
       <c r="R15" t="n">
-        <v>0.19</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.43</v>
+        <v>4.39</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="G16" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="H16" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K16" t="n">
         <v>-0.04</v>
       </c>
-      <c r="I16" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="L16" t="n">
-        <v>-1.14</v>
+        <v>-0.92</v>
       </c>
       <c r="M16" t="n">
         <v>4.3</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.92</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.92</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-0.91</v>
       </c>
       <c r="G17" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.91</v>
+        <v>-3.66</v>
       </c>
       <c r="J17" t="n">
         <v>3.16</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.66</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="P17" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="E18" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="F18" t="n">
-        <v>1.34</v>
+        <v>-1.66</v>
       </c>
       <c r="G18" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.66</v>
+        <v>-1.01</v>
       </c>
       <c r="J18" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.01</v>
+        <v>0.34</v>
       </c>
       <c r="M18" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="N18" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="O18" t="n">
-        <v>0.34</v>
+        <v>-1.36</v>
       </c>
       <c r="P18" t="n">
-        <v>2.95</v>
+        <v>2.98</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.01</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>0.34</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>53.75</v>
+        <v>53.9</v>
       </c>
       <c r="E19" t="n">
-        <v>0.55</v>
+        <v>0.15</v>
       </c>
       <c r="F19" t="n">
-        <v>1.03</v>
+        <v>0.28</v>
       </c>
       <c r="G19" t="n">
-        <v>53.9</v>
+        <v>53.4</v>
       </c>
       <c r="H19" t="n">
-        <v>0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="I19" t="n">
-        <v>0.28</v>
+        <v>-0.93</v>
       </c>
       <c r="J19" t="n">
-        <v>53.4</v>
+        <v>53.25</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.5</v>
+        <v>-0.15</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.93</v>
+        <v>-0.28</v>
       </c>
       <c r="M19" t="n">
-        <v>53.25</v>
+        <v>52.7</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.15</v>
+        <v>-0.55</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.28</v>
+        <v>-1.03</v>
       </c>
       <c r="P19" t="n">
-        <v>53.25</v>
+        <v>52.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.28</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.08</v>
+        <v>29.7</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3</v>
+        <v>0.62</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.02</v>
+        <v>2.13</v>
       </c>
       <c r="G20" t="n">
         <v>29.7</v>
       </c>
       <c r="H20" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>29.7</v>
+        <v>29.44</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>-0.88</v>
       </c>
       <c r="M20" t="n">
-        <v>29.44</v>
+        <v>28.58</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.26</v>
+        <v>-0.86</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.88</v>
+        <v>-2.92</v>
       </c>
       <c r="P20" t="n">
-        <v>29.44</v>
+        <v>28.08</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.26</v>
+        <v>-0.5</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.88</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="G21" t="n">
         <v>4.41</v>
       </c>
-      <c r="E21" t="n">
+      <c r="H21" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F21" t="n">
+      <c r="I21" t="n">
         <v>-0.45</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.45</v>
       </c>
       <c r="J21" t="n">
         <v>4.41</v>
       </c>
       <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="N21" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L21" t="n">
+      <c r="O21" t="n">
         <v>-0.45</v>
       </c>
-      <c r="M21" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
       <c r="P21" t="n">
-        <v>4.41</v>
+        <v>4.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79.2</v>
+        <v>78.95</v>
       </c>
       <c r="E22" t="n">
-        <v>0.15</v>
+        <v>-0.25</v>
       </c>
       <c r="F22" t="n">
-        <v>0.19</v>
+        <v>-0.32</v>
       </c>
       <c r="G22" t="n">
-        <v>78.95</v>
+        <v>78.8</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.25</v>
+        <v>-0.15</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.32</v>
+        <v>-0.19</v>
       </c>
       <c r="J22" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.15</v>
+        <v>0.1</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.19</v>
+        <v>0.13</v>
       </c>
       <c r="M22" t="n">
-        <v>78.90000000000001</v>
+        <v>78.45</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1</v>
+        <v>-0.45</v>
       </c>
       <c r="O22" t="n">
-        <v>0.13</v>
+        <v>-0.57</v>
       </c>
       <c r="P22" t="n">
-        <v>78.90000000000001</v>
+        <v>79.25</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="R22" t="n">
-        <v>0.13</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>23.54</v>
+        <v>23.24</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="F23" t="n">
-        <v>3.06</v>
+        <v>-1.27</v>
       </c>
       <c r="G23" t="n">
-        <v>23.24</v>
+        <v>22.6</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.3</v>
+        <v>-0.64</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.27</v>
+        <v>-2.75</v>
       </c>
       <c r="J23" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.64</v>
+        <v>0.1</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.75</v>
+        <v>0.44</v>
       </c>
       <c r="M23" t="n">
-        <v>22.7</v>
+        <v>22.44</v>
       </c>
       <c r="N23" t="n">
-        <v>0.1</v>
+        <v>-0.26</v>
       </c>
       <c r="O23" t="n">
-        <v>0.44</v>
+        <v>-1.15</v>
       </c>
       <c r="P23" t="n">
-        <v>22.7</v>
+        <v>22.08</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.1</v>
+        <v>-0.36</v>
       </c>
       <c r="R23" t="n">
-        <v>0.44</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.21</v>
+        <v>15.86</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.21</v>
+        <v>-0.35</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.28</v>
+        <v>-2.16</v>
       </c>
       <c r="G24" t="n">
-        <v>15.86</v>
+        <v>15.25</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.35</v>
+        <v>-0.61</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.16</v>
+        <v>-3.85</v>
       </c>
       <c r="J24" t="n">
-        <v>15.25</v>
+        <v>15.09</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.61</v>
+        <v>-0.16</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.85</v>
+        <v>-1.05</v>
       </c>
       <c r="M24" t="n">
-        <v>15.09</v>
+        <v>15.08</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.16</v>
+        <v>-0.01</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>15.09</v>
+        <v>14.41</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.16</v>
+        <v>-0.67</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.05</v>
+        <v>-4.44</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>27.58</v>
+        <v>27.2</v>
       </c>
       <c r="E25" t="n">
-        <v>1.18</v>
+        <v>-0.38</v>
       </c>
       <c r="F25" t="n">
-        <v>4.47</v>
+        <v>-1.38</v>
       </c>
       <c r="G25" t="n">
-        <v>27.2</v>
+        <v>26.18</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.38</v>
+        <v>-1.02</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.38</v>
+        <v>-3.75</v>
       </c>
       <c r="J25" t="n">
-        <v>26.18</v>
+        <v>26.58</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.02</v>
+        <v>0.4</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.75</v>
+        <v>1.53</v>
       </c>
       <c r="M25" t="n">
-        <v>26.58</v>
+        <v>25.9</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4</v>
+        <v>-0.68</v>
       </c>
       <c r="O25" t="n">
-        <v>1.53</v>
+        <v>-2.56</v>
       </c>
       <c r="P25" t="n">
-        <v>26.58</v>
+        <v>25.86</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.4</v>
+        <v>-0.04</v>
       </c>
       <c r="R25" t="n">
-        <v>1.53</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>42.58</v>
+        <v>42.9</v>
       </c>
       <c r="E26" t="n">
-        <v>4.64</v>
+        <v>0.32</v>
       </c>
       <c r="F26" t="n">
-        <v>12.23</v>
+        <v>0.75</v>
       </c>
       <c r="G26" t="n">
-        <v>42.9</v>
+        <v>40.16</v>
       </c>
       <c r="H26" t="n">
-        <v>0.32</v>
+        <v>-2.74</v>
       </c>
       <c r="I26" t="n">
-        <v>0.75</v>
+        <v>-6.39</v>
       </c>
       <c r="J26" t="n">
-        <v>40.16</v>
+        <v>39.32</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.74</v>
+        <v>-0.84</v>
       </c>
       <c r="L26" t="n">
-        <v>-6.39</v>
+        <v>-2.09</v>
       </c>
       <c r="M26" t="n">
-        <v>39.32</v>
+        <v>38.16</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.84</v>
+        <v>-1.16</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.09</v>
+        <v>-2.95</v>
       </c>
       <c r="P26" t="n">
-        <v>39.32</v>
+        <v>35.04</v>
       </c>
       <c r="Q26" t="n">
-        <v>-0.84</v>
+        <v>-3.12</v>
       </c>
       <c r="R26" t="n">
-        <v>-2.09</v>
+        <v>-8.18</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>430</v>
+        <v>451.6</v>
       </c>
       <c r="E27" t="n">
-        <v>11</v>
+        <v>21.6</v>
       </c>
       <c r="F27" t="n">
-        <v>2.63</v>
+        <v>5.02</v>
       </c>
       <c r="G27" t="n">
-        <v>451.6</v>
+        <v>441</v>
       </c>
       <c r="H27" t="n">
-        <v>21.6</v>
+        <v>-10.6</v>
       </c>
       <c r="I27" t="n">
-        <v>5.02</v>
+        <v>-2.35</v>
       </c>
       <c r="J27" t="n">
-        <v>441</v>
+        <v>438.4</v>
       </c>
       <c r="K27" t="n">
-        <v>-10.6</v>
+        <v>-2.6</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.35</v>
+        <v>-0.59</v>
       </c>
       <c r="M27" t="n">
-        <v>438.4</v>
+        <v>436.6</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.6</v>
+        <v>-1.8</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.59</v>
+        <v>-0.41</v>
       </c>
       <c r="P27" t="n">
-        <v>438.4</v>
+        <v>439.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>-2.6</v>
+        <v>3.2</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.59</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>112.6</v>
+        <v>114.8</v>
       </c>
       <c r="E28" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="F28" t="n">
-        <v>3.02</v>
+        <v>1.95</v>
       </c>
       <c r="G28" t="n">
-        <v>114.8</v>
+        <v>109.8</v>
       </c>
       <c r="H28" t="n">
-        <v>2.2</v>
+        <v>-5</v>
       </c>
       <c r="I28" t="n">
-        <v>1.95</v>
+        <v>-4.36</v>
       </c>
       <c r="J28" t="n">
-        <v>109.8</v>
+        <v>110</v>
       </c>
       <c r="K28" t="n">
-        <v>-5</v>
+        <v>0.2</v>
       </c>
       <c r="L28" t="n">
-        <v>-4.36</v>
+        <v>0.18</v>
       </c>
       <c r="M28" t="n">
-        <v>110</v>
+        <v>108.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0.2</v>
+        <v>-1.6</v>
       </c>
       <c r="O28" t="n">
-        <v>0.18</v>
+        <v>-1.45</v>
       </c>
       <c r="P28" t="n">
-        <v>110</v>
+        <v>107.7</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.2</v>
+        <v>-0.7</v>
       </c>
       <c r="R28" t="n">
-        <v>0.18</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>105.4</v>
+        <v>106.5</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="F29" t="n">
-        <v>0.38</v>
+        <v>1.04</v>
       </c>
       <c r="G29" t="n">
-        <v>106.5</v>
+        <v>106.1</v>
       </c>
       <c r="H29" t="n">
-        <v>1.1</v>
+        <v>-0.4</v>
       </c>
       <c r="I29" t="n">
-        <v>1.04</v>
+        <v>-0.38</v>
       </c>
       <c r="J29" t="n">
-        <v>106.1</v>
+        <v>105.6</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.38</v>
+        <v>-0.47</v>
       </c>
       <c r="M29" t="n">
-        <v>105.6</v>
+        <v>103.7</v>
       </c>
       <c r="N29" t="n">
-        <v>-0.5</v>
+        <v>-1.9</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.47</v>
+        <v>-1.8</v>
       </c>
       <c r="P29" t="n">
-        <v>105.6</v>
+        <v>104.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.5</v>
+        <v>0.8</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.47</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>74</v>
+        <v>73.2</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8</v>
+        <v>-0.8</v>
       </c>
       <c r="F30" t="n">
-        <v>1.09</v>
+        <v>-1.08</v>
       </c>
       <c r="G30" t="n">
-        <v>73.2</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.8</v>
+        <v>-0.35</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.08</v>
+        <v>-0.48</v>
       </c>
       <c r="J30" t="n">
-        <v>72.84999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.35</v>
+        <v>-0.6</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.48</v>
+        <v>-0.82</v>
       </c>
       <c r="M30" t="n">
-        <v>72.25</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="N30" t="n">
         <v>-0.6</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.82</v>
+        <v>-0.83</v>
       </c>
       <c r="P30" t="n">
-        <v>72.25</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.6</v>
+        <v>0.25</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.82</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>89</v>
+        <v>89.5</v>
       </c>
       <c r="E31" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="F31" t="n">
-        <v>2.06</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G31" t="n">
-        <v>89.5</v>
+        <v>88.55</v>
       </c>
       <c r="H31" t="n">
-        <v>0.5</v>
+        <v>-0.95</v>
       </c>
       <c r="I31" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.06</v>
       </c>
       <c r="J31" t="n">
-        <v>88.55</v>
+        <v>86.3</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.95</v>
+        <v>-2.25</v>
       </c>
       <c r="L31" t="n">
-        <v>-1.06</v>
+        <v>-2.54</v>
       </c>
       <c r="M31" t="n">
-        <v>86.3</v>
+        <v>85.3</v>
       </c>
       <c r="N31" t="n">
-        <v>-2.25</v>
+        <v>-1</v>
       </c>
       <c r="O31" t="n">
-        <v>-2.54</v>
+        <v>-1.16</v>
       </c>
       <c r="P31" t="n">
-        <v>86.3</v>
+        <v>85.55</v>
       </c>
       <c r="Q31" t="n">
-        <v>-2.25</v>
+        <v>0.25</v>
       </c>
       <c r="R31" t="n">
-        <v>-2.54</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>65.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="E32" t="n">
-        <v>0.45</v>
+        <v>-1.3</v>
       </c>
       <c r="F32" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.98</v>
       </c>
       <c r="G32" t="n">
-        <v>64.3</v>
+        <v>63.8</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.98</v>
+        <v>-0.78</v>
       </c>
       <c r="J32" t="n">
         <v>63.8</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.78</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>63.8</v>
+        <v>63.35</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="P32" t="n">
-        <v>63.8</v>
+        <v>61.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>-2.3</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>-3.63</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>81.2</v>
+        <v>81.34999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3</v>
+        <v>0.15</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.37</v>
+        <v>0.18</v>
       </c>
       <c r="G33" t="n">
-        <v>81.34999999999999</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>0.15</v>
+        <v>-1</v>
       </c>
       <c r="I33" t="n">
-        <v>0.18</v>
+        <v>-1.23</v>
       </c>
       <c r="J33" t="n">
-        <v>80.34999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="K33" t="n">
-        <v>-1</v>
+        <v>-0.85</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.23</v>
+        <v>-1.06</v>
       </c>
       <c r="M33" t="n">
-        <v>79.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.85</v>
+        <v>-1.4</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.06</v>
+        <v>-1.76</v>
       </c>
       <c r="P33" t="n">
-        <v>79.5</v>
+        <v>77.7</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.85</v>
+        <v>-0.4</v>
       </c>
       <c r="R33" t="n">
-        <v>-1.06</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>30.82</v>
+        <v>31.22</v>
       </c>
       <c r="E34" t="n">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="F34" t="n">
-        <v>0.26</v>
+        <v>1.3</v>
       </c>
       <c r="G34" t="n">
-        <v>31.22</v>
+        <v>30.78</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4</v>
+        <v>-0.44</v>
       </c>
       <c r="I34" t="n">
-        <v>1.3</v>
+        <v>-1.41</v>
       </c>
       <c r="J34" t="n">
-        <v>30.78</v>
+        <v>30.5</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.44</v>
+        <v>-0.28</v>
       </c>
       <c r="L34" t="n">
-        <v>-1.41</v>
+        <v>-0.91</v>
       </c>
       <c r="M34" t="n">
-        <v>30.5</v>
+        <v>30.02</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.28</v>
+        <v>-0.48</v>
       </c>
       <c r="O34" t="n">
-        <v>-0.91</v>
+        <v>-1.57</v>
       </c>
       <c r="P34" t="n">
-        <v>30.5</v>
+        <v>30.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.28</v>
+        <v>0.68</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.91</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="E35" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F35" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="G35" t="n">
-        <v>4.35</v>
+        <v>4.28</v>
       </c>
       <c r="H35" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>0.23</v>
+        <v>-1.61</v>
       </c>
       <c r="J35" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="L35" t="n">
-        <v>-1.61</v>
+        <v>-0.23</v>
       </c>
       <c r="M35" t="n">
-        <v>4.28</v>
+        <v>4.24</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="O35" t="n">
-        <v>-1.61</v>
+        <v>-0.7</v>
       </c>
       <c r="P35" t="n">
-        <v>4.28</v>
+        <v>4.24</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="R35" t="n">
-        <v>-1.61</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.34</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F36" t="n">
-        <v>0.32</v>
+        <v>0.21</v>
       </c>
       <c r="G36" t="n">
-        <v>9.359999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="H36" t="n">
-        <v>0.02</v>
+        <v>-0.13</v>
       </c>
       <c r="I36" t="n">
-        <v>0.21</v>
+        <v>-1.39</v>
       </c>
       <c r="J36" t="n">
-        <v>9.23</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.13</v>
+        <v>-0.01</v>
       </c>
       <c r="L36" t="n">
-        <v>-1.39</v>
+        <v>-0.11</v>
       </c>
       <c r="M36" t="n">
-        <v>9.23</v>
+        <v>9.09</v>
       </c>
       <c r="N36" t="n">
         <v>-0.13</v>
       </c>
       <c r="O36" t="n">
-        <v>-1.39</v>
+        <v>-1.41</v>
       </c>
       <c r="P36" t="n">
-        <v>9.23</v>
+        <v>9.09</v>
       </c>
       <c r="Q36" t="n">
         <v>-0.13</v>
       </c>
       <c r="R36" t="n">
-        <v>-1.39</v>
+        <v>-1.41</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>391.2</v>
+        <v>397.4</v>
       </c>
       <c r="E37" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="F37" t="n">
-        <v>0.82</v>
+        <v>1.58</v>
       </c>
       <c r="G37" t="n">
-        <v>397.4</v>
+        <v>395.8</v>
       </c>
       <c r="H37" t="n">
-        <v>6.2</v>
+        <v>-1.6</v>
       </c>
       <c r="I37" t="n">
-        <v>1.58</v>
+        <v>-0.4</v>
       </c>
       <c r="J37" t="n">
-        <v>395.8</v>
+        <v>393.4</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.6</v>
+        <v>-2.4</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.4</v>
+        <v>-0.61</v>
       </c>
       <c r="M37" t="n">
-        <v>393.4</v>
+        <v>388.4</v>
       </c>
       <c r="N37" t="n">
-        <v>-2.4</v>
+        <v>-5</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.61</v>
+        <v>-1.27</v>
       </c>
       <c r="P37" t="n">
-        <v>393.4</v>
+        <v>388.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>-2.4</v>
+        <v>0.2</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.61</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.1</v>
+        <v>12.16</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.14</v>
+        <v>0.06</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.14</v>
+        <v>0.5</v>
       </c>
       <c r="G38" t="n">
-        <v>12.16</v>
+        <v>12.07</v>
       </c>
       <c r="H38" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5</v>
+        <v>-0.74</v>
       </c>
       <c r="J38" t="n">
-        <v>12.07</v>
+        <v>12.04</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.09</v>
+        <v>-0.03</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.74</v>
+        <v>-0.25</v>
       </c>
       <c r="M38" t="n">
-        <v>12.04</v>
+        <v>11.91</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.25</v>
+        <v>-1.08</v>
       </c>
       <c r="P38" t="n">
-        <v>12.04</v>
+        <v>11.93</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="R38" t="n">
-        <v>-0.25</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="E39" t="n">
-        <v>-3</v>
+        <v>3</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.59</v>
+        <v>0.6</v>
       </c>
       <c r="G39" t="n">
-        <v>507</v>
+        <v>511.5</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>0.89</v>
       </c>
       <c r="J39" t="n">
-        <v>511.5</v>
+        <v>492.8</v>
       </c>
       <c r="K39" t="n">
-        <v>4.5</v>
+        <v>-18.7</v>
       </c>
       <c r="L39" t="n">
-        <v>0.89</v>
+        <v>-3.66</v>
       </c>
       <c r="M39" t="n">
-        <v>492.8</v>
+        <v>489.4</v>
       </c>
       <c r="N39" t="n">
-        <v>-18.7</v>
+        <v>-3.4</v>
       </c>
       <c r="O39" t="n">
-        <v>-3.66</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="P39" t="n">
-        <v>492.8</v>
+        <v>484.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>-18.7</v>
+        <v>-4.8</v>
       </c>
       <c r="R39" t="n">
-        <v>-3.66</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>40.5</v>
+        <v>40.74</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.54</v>
+        <v>0.24</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.66</v>
+        <v>0.59</v>
       </c>
       <c r="G40" t="n">
-        <v>40.74</v>
+        <v>40.4</v>
       </c>
       <c r="H40" t="n">
-        <v>0.24</v>
+        <v>-0.34</v>
       </c>
       <c r="I40" t="n">
-        <v>0.59</v>
+        <v>-0.83</v>
       </c>
       <c r="J40" t="n">
-        <v>40.4</v>
+        <v>40.22</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.34</v>
+        <v>-0.18</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.83</v>
+        <v>-0.45</v>
       </c>
       <c r="M40" t="n">
-        <v>40.22</v>
+        <v>39.46</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.18</v>
+        <v>-0.76</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.45</v>
+        <v>-1.89</v>
       </c>
       <c r="P40" t="n">
-        <v>40.22</v>
+        <v>39.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.18</v>
+        <v>-0.36</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.45</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.67</v>
+        <v>32.14</v>
       </c>
       <c r="E41" t="n">
-        <v>0.29</v>
+        <v>0.47</v>
       </c>
       <c r="F41" t="n">
-        <v>0.92</v>
+        <v>1.48</v>
       </c>
       <c r="G41" t="n">
-        <v>32.14</v>
+        <v>31.65</v>
       </c>
       <c r="H41" t="n">
-        <v>0.47</v>
+        <v>-0.49</v>
       </c>
       <c r="I41" t="n">
-        <v>1.48</v>
+        <v>-1.52</v>
       </c>
       <c r="J41" t="n">
-        <v>31.65</v>
+        <v>31.59</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.49</v>
+        <v>-0.06</v>
       </c>
       <c r="L41" t="n">
-        <v>-1.52</v>
+        <v>-0.19</v>
       </c>
       <c r="M41" t="n">
-        <v>31.59</v>
+        <v>32.01</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.06</v>
+        <v>0.42</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.19</v>
+        <v>1.33</v>
       </c>
       <c r="P41" t="n">
-        <v>31.59</v>
+        <v>32.22</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.06</v>
+        <v>0.21</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.19</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>77.36</v>
+        <v>77.8</v>
       </c>
       <c r="E42" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="F42" t="n">
-        <v>0.65</v>
+        <v>0.57</v>
       </c>
       <c r="G42" t="n">
-        <v>77.8</v>
+        <v>77.69</v>
       </c>
       <c r="H42" t="n">
-        <v>0.44</v>
+        <v>-0.11</v>
       </c>
       <c r="I42" t="n">
-        <v>0.57</v>
+        <v>-0.14</v>
       </c>
       <c r="J42" t="n">
-        <v>77.69</v>
+        <v>77.48</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.11</v>
+        <v>-0.21</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.14</v>
+        <v>-0.27</v>
       </c>
       <c r="M42" t="n">
-        <v>77.48</v>
+        <v>78</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.21</v>
+        <v>0.52</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.27</v>
+        <v>0.67</v>
       </c>
       <c r="P42" t="n">
-        <v>77.48</v>
+        <v>78.11</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.21</v>
+        <v>0.11</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.27</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>42.1</v>
+        <v>42.8</v>
       </c>
       <c r="E43" t="n">
-        <v>0.32</v>
+        <v>0.7</v>
       </c>
       <c r="F43" t="n">
-        <v>0.77</v>
+        <v>1.66</v>
       </c>
       <c r="G43" t="n">
-        <v>42.8</v>
+        <v>42.84</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7</v>
+        <v>0.04</v>
       </c>
       <c r="I43" t="n">
-        <v>1.66</v>
+        <v>0.09</v>
       </c>
       <c r="J43" t="n">
-        <v>42.84</v>
+        <v>42.5</v>
       </c>
       <c r="K43" t="n">
-        <v>0.04</v>
+        <v>-0.34</v>
       </c>
       <c r="L43" t="n">
-        <v>0.09</v>
+        <v>-0.79</v>
       </c>
       <c r="M43" t="n">
-        <v>42.5</v>
+        <v>42.57</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.34</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.79</v>
+        <v>0.16</v>
       </c>
       <c r="P43" t="n">
-        <v>42.5</v>
+        <v>43.29</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.34</v>
+        <v>0.72</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.79</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
+        <v>5.93</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="G44" t="n">
         <v>5.9</v>
       </c>
-      <c r="E44" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" t="n">
-        <v>5.93</v>
-      </c>
       <c r="H44" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.51</v>
+        <v>-0.51</v>
       </c>
       <c r="J44" t="n">
-        <v>5.9</v>
+        <v>5.85</v>
       </c>
       <c r="K44" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="M44" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="P44" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="Q44" t="n">
         <v>-0.03</v>
       </c>
-      <c r="L44" t="n">
+      <c r="R44" t="n">
         <v>-0.51</v>
-      </c>
-      <c r="M44" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="N44" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="O44" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="P44" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="R44" t="n">
-        <v>-0.85</v>
       </c>
     </row>
     <row r="45">
@@ -3181,31 +3181,31 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="F45" t="n">
-        <v>-3.3</v>
+        <v>4.88</v>
       </c>
       <c r="G45" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="I45" t="n">
-        <v>4.88</v>
+        <v>-2.33</v>
       </c>
       <c r="J45" t="n">
         <v>2.1</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>-2.33</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>2.1</v>
@@ -3217,13 +3217,13 @@
         <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="46">
@@ -3243,25 +3243,25 @@
         </is>
       </c>
       <c r="D46" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="J46" t="n">
         <v>3.81</v>
-      </c>
-      <c r="E46" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.82</v>
       </c>
       <c r="K46" t="n">
         <v>-0.01</v>
@@ -3270,22 +3270,22 @@
         <v>-0.26</v>
       </c>
       <c r="M46" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="O46" t="n">
-        <v>-0.26</v>
+        <v>0.52</v>
       </c>
       <c r="P46" t="n">
-        <v>3.81</v>
+        <v>3.88</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.26</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.39</v>
+        <v>10.69</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.04</v>
+        <v>0.3</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.38</v>
+        <v>2.89</v>
       </c>
       <c r="G47" t="n">
-        <v>10.69</v>
+        <v>10.81</v>
       </c>
       <c r="H47" t="n">
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="I47" t="n">
-        <v>2.89</v>
+        <v>1.12</v>
       </c>
       <c r="J47" t="n">
-        <v>10.81</v>
+        <v>10.86</v>
       </c>
       <c r="K47" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="L47" t="n">
-        <v>1.12</v>
+        <v>0.46</v>
       </c>
       <c r="M47" t="n">
-        <v>10.86</v>
+        <v>10.87</v>
       </c>
       <c r="N47" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="O47" t="n">
-        <v>0.46</v>
+        <v>0.09</v>
       </c>
       <c r="P47" t="n">
-        <v>10.86</v>
+        <v>10.87</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>0.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3367,22 +3367,22 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.305</v>
+        <v>0.315</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.61</v>
+        <v>3.28</v>
       </c>
       <c r="G48" t="n">
         <v>0.315</v>
       </c>
       <c r="H48" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
         <v>0.315</v>
@@ -3403,13 +3403,13 @@
         <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>0.315</v>
+        <v>0.31</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.33</v>
+        <v>4.32</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.46</v>
+        <v>-0.23</v>
       </c>
       <c r="G49" t="n">
-        <v>4.32</v>
+        <v>4.28</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.23</v>
+        <v>-0.93</v>
       </c>
       <c r="J49" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="M49" t="n">
         <v>4.28</v>
       </c>
-      <c r="K49" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="L49" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="M49" t="n">
-        <v>4.25</v>
-      </c>
       <c r="N49" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.7</v>
+        <v>0.71</v>
       </c>
       <c r="P49" t="n">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.7</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="E50" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9399999999999999</v>
+        <v>3.74</v>
       </c>
       <c r="G50" t="n">
         <v>1.11</v>
       </c>
       <c r="H50" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M50" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="N50" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="O50" t="n">
-        <v>2.7</v>
+        <v>-1.75</v>
       </c>
       <c r="P50" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="R50" t="n">
-        <v>2.7</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.22</v>
+        <v>5.26</v>
       </c>
       <c r="E51" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F51" t="n">
-        <v>0.97</v>
+        <v>0.77</v>
       </c>
       <c r="G51" t="n">
-        <v>5.26</v>
+        <v>5.18</v>
       </c>
       <c r="H51" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="I51" t="n">
-        <v>0.77</v>
+        <v>-1.52</v>
       </c>
       <c r="J51" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="L51" t="n">
-        <v>-1.52</v>
+        <v>-0.19</v>
       </c>
       <c r="M51" t="n">
-        <v>5.17</v>
+        <v>5.19</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.19</v>
+        <v>0.39</v>
       </c>
       <c r="P51" t="n">
-        <v>5.17</v>
+        <v>5.16</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="R51" t="n">
-        <v>-0.19</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="52">
@@ -3615,43 +3615,43 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.07</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F52" t="n">
-        <v>0.36</v>
+        <v>0.27</v>
       </c>
       <c r="G52" t="n">
-        <v>11.1</v>
+        <v>11.21</v>
       </c>
       <c r="H52" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="I52" t="n">
-        <v>0.27</v>
+        <v>0.99</v>
       </c>
       <c r="J52" t="n">
-        <v>11.21</v>
+        <v>11.29</v>
       </c>
       <c r="K52" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="L52" t="n">
-        <v>0.99</v>
+        <v>0.71</v>
       </c>
       <c r="M52" t="n">
-        <v>11.29</v>
+        <v>11.3</v>
       </c>
       <c r="N52" t="n">
-        <v>0.08</v>
+        <v>0.01</v>
       </c>
       <c r="O52" t="n">
-        <v>0.71</v>
+        <v>0.09</v>
       </c>
       <c r="P52" t="n">
-        <v>11.29</v>
+        <v>11.38</v>
       </c>
       <c r="Q52" t="n">
         <v>0.08</v>
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.09</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="E53" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I53" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="J53" t="n">
+        <v>8.220000000000001</v>
+      </c>
+      <c r="K53" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-2.38</v>
+      </c>
+      <c r="M53" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="N53" t="n">
         <v>0.04</v>
       </c>
-      <c r="F53" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="G53" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="J53" t="n">
-        <v>8.42</v>
-      </c>
-      <c r="K53" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L53" t="n">
-        <v>3.69</v>
-      </c>
-      <c r="M53" t="n">
-        <v>8.220000000000001</v>
-      </c>
-      <c r="N53" t="n">
-        <v>-0.2</v>
-      </c>
       <c r="O53" t="n">
-        <v>-2.38</v>
+        <v>0.49</v>
       </c>
       <c r="P53" t="n">
-        <v>8.220000000000001</v>
+        <v>7.59</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.2</v>
+        <v>-0.67</v>
       </c>
       <c r="R53" t="n">
-        <v>-2.38</v>
+        <v>-8.109999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -3742,46 +3742,46 @@
         <v>0.43</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.27</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.43</v>
+        <v>0.435</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="J54" t="n">
         <v>0.435</v>
       </c>
       <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="N54" t="n">
         <v>0.005</v>
       </c>
-      <c r="L54" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P54" t="n">
         <v>0.435</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="55">
@@ -3801,22 +3801,22 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G55" t="n">
         <v>0.62</v>
       </c>
       <c r="H55" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0.62</v>
@@ -3828,22 +3828,22 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.62</v>
+        <v>0.615</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P55" t="n">
-        <v>0.62</v>
+        <v>0.625</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="56">
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.39</v>
+        <v>0.385</v>
       </c>
       <c r="E56" t="n">
         <v>-0.005</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.27</v>
+        <v>-1.28</v>
       </c>
       <c r="G56" t="n">
         <v>0.385</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.28</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.385</v>
+        <v>0.39</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M56" t="n">
         <v>0.39</v>
       </c>
       <c r="N56" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
         <v>0.39</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3928,46 +3928,46 @@
         <v>3.65</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.82</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="J57" t="n">
         <v>3.65</v>
       </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3.67</v>
-      </c>
       <c r="K57" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="L57" t="n">
-        <v>0.55</v>
+        <v>-0.54</v>
       </c>
       <c r="M57" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="O57" t="n">
-        <v>-0.54</v>
+        <v>0.82</v>
       </c>
       <c r="P57" t="n">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R57" t="n">
-        <v>-0.54</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.076</v>
+        <v>0.077</v>
       </c>
       <c r="E58" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="F58" t="n">
-        <v>2.7</v>
+        <v>1.32</v>
       </c>
       <c r="G58" t="n">
-        <v>0.077</v>
+        <v>0.08</v>
       </c>
       <c r="H58" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="I58" t="n">
-        <v>1.32</v>
+        <v>3.9</v>
       </c>
       <c r="J58" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="K58" t="n">
-        <v>0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="L58" t="n">
-        <v>3.9</v>
+        <v>-1.25</v>
       </c>
       <c r="M58" t="n">
         <v>0.079</v>
       </c>
       <c r="N58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
         <v>0.079</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22.32</v>
+        <v>22.96</v>
       </c>
       <c r="E59" t="n">
-        <v>0.12</v>
+        <v>0.64</v>
       </c>
       <c r="F59" t="n">
-        <v>0.54</v>
+        <v>2.87</v>
       </c>
       <c r="G59" t="n">
-        <v>22.96</v>
+        <v>22.74</v>
       </c>
       <c r="H59" t="n">
-        <v>0.64</v>
+        <v>-0.22</v>
       </c>
       <c r="I59" t="n">
-        <v>2.87</v>
+        <v>-0.96</v>
       </c>
       <c r="J59" t="n">
-        <v>22.74</v>
+        <v>22.42</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.22</v>
+        <v>-0.32</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.96</v>
+        <v>-1.41</v>
       </c>
       <c r="M59" t="n">
-        <v>22.42</v>
+        <v>22.4</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.32</v>
+        <v>-0.02</v>
       </c>
       <c r="O59" t="n">
-        <v>-1.41</v>
+        <v>-0.09</v>
       </c>
       <c r="P59" t="n">
-        <v>22.42</v>
+        <v>22.47</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.32</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R59" t="n">
-        <v>-1.41</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="E60" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.97</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="P60" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Q60" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F60" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="G60" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I60" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="N60" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="O60" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="P60" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0.03</v>
-      </c>
       <c r="R60" t="n">
-        <v>0.96</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.87</v>
+        <v>0.865</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.14</v>
+        <v>-0.57</v>
       </c>
       <c r="G61" t="n">
         <v>0.865</v>
       </c>
       <c r="H61" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="K61" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I61" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>-0.58</v>
       </c>
       <c r="M61" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="O61" t="n">
-        <v>-0.58</v>
+        <v>1.16</v>
       </c>
       <c r="P61" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.005</v>
+        <v>-0.02</v>
       </c>
       <c r="R61" t="n">
-        <v>-0.58</v>
+        <v>-2.3</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-22 Close</t>
+          <t>2026-09-23 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-09-22 Change</t>
+          <t>2026-09-23 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-22 Change %</t>
+          <t>2026-09-23 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-09-23 Close</t>
+          <t>2026-09-24 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-09-23 Change</t>
+          <t>2026-09-24 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-09-23 Change %</t>
+          <t>2026-09-24 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-09-24 Close</t>
+          <t>2026-09-25 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-09-24 Change</t>
+          <t>2026-09-25 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-09-24 Change %</t>
+          <t>2026-09-25 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-09-25 Close</t>
+          <t>2026-09-28 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-09-25 Change</t>
+          <t>2026-09-28 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-09-25 Change %</t>
+          <t>2026-09-28 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-09-28 Close</t>
+          <t>2026-09-29 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-09-28 Change</t>
+          <t>2026-09-29 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-09-28 Change %</t>
+          <t>2026-09-29 Change %</t>
         </is>
       </c>
     </row>
@@ -577,40 +577,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>159.3</v>
+        <v>159.5</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.2</v>
+        <v>0.2</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.36</v>
+        <v>0.13</v>
       </c>
       <c r="G3" t="n">
-        <v>159.5</v>
+        <v>156.9</v>
       </c>
       <c r="H3" t="n">
-        <v>0.2</v>
+        <v>-2.6</v>
       </c>
       <c r="I3" t="n">
-        <v>0.13</v>
+        <v>-1.63</v>
       </c>
       <c r="J3" t="n">
-        <v>156.9</v>
+        <v>157.6</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.6</v>
+        <v>0.7</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.63</v>
+        <v>0.45</v>
       </c>
       <c r="M3" t="n">
-        <v>157.6</v>
+        <v>158.9</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0.45</v>
+        <v>0.82</v>
       </c>
       <c r="P3" t="n">
         <v>158.9</v>
@@ -639,40 +639,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>239.4</v>
+        <v>240</v>
       </c>
       <c r="E4" t="n">
-        <v>-6.6</v>
+        <v>0.6</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.68</v>
+        <v>0.25</v>
       </c>
       <c r="G4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6</v>
+        <v>-4</v>
       </c>
       <c r="I4" t="n">
-        <v>0.25</v>
+        <v>-1.67</v>
       </c>
       <c r="J4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="K4" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.67</v>
+        <v>0.85</v>
       </c>
       <c r="M4" t="n">
-        <v>238</v>
+        <v>242.6</v>
       </c>
       <c r="N4" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0.85</v>
+        <v>1.93</v>
       </c>
       <c r="P4" t="n">
         <v>242.6</v>
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="E5" t="n">
         <v>-0.01</v>
@@ -710,31 +710,31 @@
         <v>-0.15</v>
       </c>
       <c r="G5" t="n">
-        <v>6.49</v>
+        <v>6.61</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.01</v>
+        <v>0.12</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.15</v>
+        <v>1.85</v>
       </c>
       <c r="J5" t="n">
-        <v>6.61</v>
+        <v>6.51</v>
       </c>
       <c r="K5" t="n">
-        <v>0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="L5" t="n">
-        <v>1.85</v>
+        <v>-1.51</v>
       </c>
       <c r="M5" t="n">
-        <v>6.51</v>
+        <v>6.55</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1</v>
+        <v>0.04</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.51</v>
+        <v>0.61</v>
       </c>
       <c r="P5" t="n">
         <v>6.55</v>
@@ -766,37 +766,37 @@
         <v>7.54</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>7.54</v>
+        <v>7.66</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="J6" t="n">
-        <v>7.66</v>
+        <v>7.51</v>
       </c>
       <c r="K6" t="n">
-        <v>0.12</v>
+        <v>-0.15</v>
       </c>
       <c r="L6" t="n">
-        <v>1.59</v>
+        <v>-1.96</v>
       </c>
       <c r="M6" t="n">
-        <v>7.51</v>
+        <v>7.7</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.15</v>
+        <v>0.19</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.96</v>
+        <v>2.53</v>
       </c>
       <c r="P6" t="n">
         <v>7.7</v>
@@ -825,40 +825,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.02</v>
+        <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.66</v>
+        <v>-0.33</v>
       </c>
       <c r="G7" t="n">
-        <v>6</v>
+        <v>6.04</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.33</v>
+        <v>0.67</v>
       </c>
       <c r="J7" t="n">
-        <v>6.04</v>
+        <v>5.98</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="L7" t="n">
-        <v>0.67</v>
+        <v>-0.99</v>
       </c>
       <c r="M7" t="n">
-        <v>5.98</v>
+        <v>6.07</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.06</v>
+        <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.99</v>
+        <v>1.51</v>
       </c>
       <c r="P7" t="n">
         <v>6.07</v>
@@ -887,40 +887,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.74</v>
+        <v>9.66</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2</v>
+        <v>-0.82</v>
       </c>
       <c r="G8" t="n">
-        <v>9.66</v>
+        <v>9.68</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.82</v>
+        <v>0.21</v>
       </c>
       <c r="J8" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="M8" t="n">
         <v>9.68</v>
       </c>
-      <c r="K8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="M8" t="n">
-        <v>9.529999999999999</v>
-      </c>
       <c r="N8" t="n">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.55</v>
+        <v>1.57</v>
       </c>
       <c r="P8" t="n">
         <v>9.68</v>
@@ -949,40 +949,40 @@
         </is>
       </c>
       <c r="D9" t="n">
+        <v>8.210000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="L9" t="n">
+        <v>-1.09</v>
+      </c>
+      <c r="M9" t="n">
         <v>8.24</v>
       </c>
-      <c r="E9" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-0.24</v>
-      </c>
-      <c r="G9" t="n">
-        <v>8.210000000000001</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8.279999999999999</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="M9" t="n">
-        <v>8.19</v>
-      </c>
       <c r="N9" t="n">
-        <v>-0.09</v>
+        <v>0.05</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.09</v>
+        <v>0.61</v>
       </c>
       <c r="P9" t="n">
         <v>8.24</v>
@@ -1011,40 +1011,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51.65</v>
+        <v>51.25</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.45</v>
+        <v>-0.4</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.86</v>
+        <v>-0.77</v>
       </c>
       <c r="G10" t="n">
-        <v>51.25</v>
+        <v>51.2</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4</v>
+        <v>-0.05</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.77</v>
+        <v>-0.1</v>
       </c>
       <c r="J10" t="n">
-        <v>51.2</v>
+        <v>50.5</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.05</v>
+        <v>-0.7</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1</v>
+        <v>-1.37</v>
       </c>
       <c r="M10" t="n">
-        <v>50.5</v>
+        <v>51.1</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7</v>
+        <v>0.6</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.37</v>
+        <v>1.19</v>
       </c>
       <c r="P10" t="n">
         <v>51.1</v>
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="E11" t="n">
         <v>-0.02</v>
@@ -1082,31 +1082,31 @@
         <v>-0.45</v>
       </c>
       <c r="G11" t="n">
-        <v>4.45</v>
+        <v>4.49</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.45</v>
+        <v>0.9</v>
       </c>
       <c r="J11" t="n">
-        <v>4.49</v>
+        <v>4.43</v>
       </c>
       <c r="K11" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9</v>
+        <v>-1.34</v>
       </c>
       <c r="M11" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.34</v>
+        <v>1.58</v>
       </c>
       <c r="P11" t="n">
         <v>4.5</v>
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.43</v>
+        <v>9.35</v>
       </c>
       <c r="E12" t="n">
         <v>-0.08</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.84</v>
+        <v>-0.85</v>
       </c>
       <c r="G12" t="n">
-        <v>9.35</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.08</v>
+        <v>0.26</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.85</v>
+        <v>2.78</v>
       </c>
       <c r="J12" t="n">
-        <v>9.609999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="K12" t="n">
-        <v>0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="L12" t="n">
-        <v>2.78</v>
+        <v>-2.08</v>
       </c>
       <c r="M12" t="n">
-        <v>9.41</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.2</v>
+        <v>0.29</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.08</v>
+        <v>3.08</v>
       </c>
       <c r="P12" t="n">
         <v>9.699999999999999</v>
@@ -1197,40 +1197,40 @@
         </is>
       </c>
       <c r="D13" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.34</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-1.44</v>
+      </c>
+      <c r="G13" t="n">
+        <v>23.84</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="J13" t="n">
+        <v>23.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1.85</v>
+      </c>
+      <c r="M13" t="n">
         <v>23.68</v>
       </c>
-      <c r="E13" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-1.09</v>
-      </c>
-      <c r="G13" t="n">
-        <v>23.34</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.34</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-1.44</v>
-      </c>
-      <c r="J13" t="n">
-        <v>23.84</v>
-      </c>
-      <c r="K13" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L13" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="M13" t="n">
-        <v>23.4</v>
-      </c>
       <c r="N13" t="n">
-        <v>-0.44</v>
+        <v>0.28</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.85</v>
+        <v>1.2</v>
       </c>
       <c r="P13" t="n">
         <v>23.68</v>
@@ -1262,37 +1262,37 @@
         <v>1.89</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="K14" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="M14" t="n">
         <v>1.89</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K14" t="n">
+      <c r="N14" t="n">
         <v>0.01</v>
       </c>
-      <c r="L14" t="n">
+      <c r="O14" t="n">
         <v>0.53</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O14" t="n">
-        <v>-1.05</v>
       </c>
       <c r="P14" t="n">
         <v>1.89</v>
@@ -1321,40 +1321,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.19</v>
+        <v>5.17</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.14</v>
+        <v>-0.39</v>
       </c>
       <c r="G15" t="n">
-        <v>5.17</v>
+        <v>5.18</v>
       </c>
       <c r="H15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="K15" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I15" t="n">
+      <c r="L15" t="n">
         <v>-0.39</v>
       </c>
-      <c r="J15" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.19</v>
-      </c>
       <c r="M15" t="n">
-        <v>5.16</v>
+        <v>5.36</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.02</v>
+        <v>0.2</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.39</v>
+        <v>3.88</v>
       </c>
       <c r="P15" t="n">
         <v>5.36</v>
@@ -1383,40 +1383,40 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.39</v>
+        <v>4.34</v>
       </c>
       <c r="E16" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="H16" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F16" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="G16" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.05</v>
-      </c>
       <c r="I16" t="n">
-        <v>-1.14</v>
+        <v>-0.92</v>
       </c>
       <c r="J16" t="n">
         <v>4.3</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.92</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
       <c r="P16" t="n">
         <v>4.25</v>
@@ -1445,40 +1445,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.28</v>
+        <v>3.16</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.91</v>
+        <v>-3.66</v>
       </c>
       <c r="G17" t="n">
         <v>3.16</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.66</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="M17" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="O17" t="n">
-        <v>0.95</v>
+        <v>-1.25</v>
       </c>
       <c r="P17" t="n">
         <v>3.15</v>
@@ -1507,40 +1507,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.97</v>
+        <v>2.94</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.66</v>
+        <v>-1.01</v>
       </c>
       <c r="G18" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.01</v>
+        <v>0.34</v>
       </c>
       <c r="J18" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="L18" t="n">
-        <v>0.34</v>
+        <v>-1.36</v>
       </c>
       <c r="M18" t="n">
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.36</v>
+        <v>2.41</v>
       </c>
       <c r="P18" t="n">
         <v>2.98</v>
@@ -1569,40 +1569,40 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>53.9</v>
+        <v>53.4</v>
       </c>
       <c r="E19" t="n">
-        <v>0.15</v>
+        <v>-0.5</v>
       </c>
       <c r="F19" t="n">
-        <v>0.28</v>
+        <v>-0.93</v>
       </c>
       <c r="G19" t="n">
-        <v>53.4</v>
+        <v>53.25</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5</v>
+        <v>-0.15</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.93</v>
+        <v>-0.28</v>
       </c>
       <c r="J19" t="n">
-        <v>53.25</v>
+        <v>52.7</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.15</v>
+        <v>-0.55</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.28</v>
+        <v>-1.03</v>
       </c>
       <c r="M19" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.55</v>
+        <v>-0.1</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.03</v>
+        <v>-0.19</v>
       </c>
       <c r="P19" t="n">
         <v>52.6</v>
@@ -1634,37 +1634,37 @@
         <v>29.7</v>
       </c>
       <c r="E20" t="n">
-        <v>0.62</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>29.7</v>
+        <v>29.44</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-0.88</v>
       </c>
       <c r="J20" t="n">
-        <v>29.44</v>
+        <v>28.58</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.26</v>
+        <v>-0.86</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.88</v>
+        <v>-2.92</v>
       </c>
       <c r="M20" t="n">
-        <v>28.58</v>
+        <v>28.08</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.86</v>
+        <v>-0.5</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.92</v>
+        <v>-1.75</v>
       </c>
       <c r="P20" t="n">
         <v>28.08</v>
@@ -1693,40 +1693,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.43</v>
+        <v>4.41</v>
       </c>
       <c r="E21" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="F21" t="n">
-        <v>0.45</v>
+        <v>-0.45</v>
       </c>
       <c r="G21" t="n">
         <v>4.41</v>
       </c>
       <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="K21" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I21" t="n">
+      <c r="L21" t="n">
         <v>-0.45</v>
       </c>
-      <c r="J21" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
       <c r="M21" t="n">
-        <v>4.39</v>
+        <v>4.49</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.02</v>
+        <v>0.1</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.45</v>
+        <v>2.28</v>
       </c>
       <c r="P21" t="n">
         <v>4.49</v>
@@ -1755,40 +1755,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>78.95</v>
+        <v>78.8</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.25</v>
+        <v>-0.15</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.32</v>
+        <v>-0.19</v>
       </c>
       <c r="G22" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.15</v>
+        <v>0.1</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.19</v>
+        <v>0.13</v>
       </c>
       <c r="J22" t="n">
-        <v>78.90000000000001</v>
+        <v>78.45</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1</v>
+        <v>-0.45</v>
       </c>
       <c r="L22" t="n">
-        <v>0.13</v>
+        <v>-0.57</v>
       </c>
       <c r="M22" t="n">
-        <v>78.45</v>
+        <v>79.25</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.45</v>
+        <v>0.8</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.57</v>
+        <v>1.02</v>
       </c>
       <c r="P22" t="n">
         <v>79.25</v>
@@ -1817,40 +1817,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>23.24</v>
+        <v>22.6</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.3</v>
+        <v>-0.64</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.27</v>
+        <v>-2.75</v>
       </c>
       <c r="G23" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.64</v>
+        <v>0.1</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.75</v>
+        <v>0.44</v>
       </c>
       <c r="J23" t="n">
-        <v>22.7</v>
+        <v>22.44</v>
       </c>
       <c r="K23" t="n">
-        <v>0.1</v>
+        <v>-0.26</v>
       </c>
       <c r="L23" t="n">
-        <v>0.44</v>
+        <v>-1.15</v>
       </c>
       <c r="M23" t="n">
-        <v>22.44</v>
+        <v>22.08</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.26</v>
+        <v>-0.36</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.15</v>
+        <v>-1.6</v>
       </c>
       <c r="P23" t="n">
         <v>22.08</v>
@@ -1879,40 +1879,40 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.86</v>
+        <v>15.25</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.35</v>
+        <v>-0.61</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.16</v>
+        <v>-3.85</v>
       </c>
       <c r="G24" t="n">
-        <v>15.25</v>
+        <v>15.09</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.61</v>
+        <v>-0.16</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.85</v>
+        <v>-1.05</v>
       </c>
       <c r="J24" t="n">
-        <v>15.09</v>
+        <v>15.08</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.16</v>
+        <v>-0.01</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>15.08</v>
+        <v>14.41</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.01</v>
+        <v>-0.67</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-4.44</v>
       </c>
       <c r="P24" t="n">
         <v>14.41</v>
@@ -1941,40 +1941,40 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>27.2</v>
+        <v>26.18</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.38</v>
+        <v>-1.02</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.38</v>
+        <v>-3.75</v>
       </c>
       <c r="G25" t="n">
-        <v>26.18</v>
+        <v>26.58</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.02</v>
+        <v>0.4</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.75</v>
+        <v>1.53</v>
       </c>
       <c r="J25" t="n">
-        <v>26.58</v>
+        <v>25.9</v>
       </c>
       <c r="K25" t="n">
-        <v>0.4</v>
+        <v>-0.68</v>
       </c>
       <c r="L25" t="n">
-        <v>1.53</v>
+        <v>-2.56</v>
       </c>
       <c r="M25" t="n">
-        <v>25.9</v>
+        <v>25.86</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.68</v>
+        <v>-0.04</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.56</v>
+        <v>-0.15</v>
       </c>
       <c r="P25" t="n">
         <v>25.86</v>
@@ -2003,40 +2003,40 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>42.9</v>
+        <v>40.16</v>
       </c>
       <c r="E26" t="n">
-        <v>0.32</v>
+        <v>-2.74</v>
       </c>
       <c r="F26" t="n">
-        <v>0.75</v>
+        <v>-6.39</v>
       </c>
       <c r="G26" t="n">
-        <v>40.16</v>
+        <v>39.32</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.74</v>
+        <v>-0.84</v>
       </c>
       <c r="I26" t="n">
-        <v>-6.39</v>
+        <v>-2.09</v>
       </c>
       <c r="J26" t="n">
-        <v>39.32</v>
+        <v>38.16</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.84</v>
+        <v>-1.16</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.09</v>
+        <v>-2.95</v>
       </c>
       <c r="M26" t="n">
-        <v>38.16</v>
+        <v>35.04</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.16</v>
+        <v>-3.12</v>
       </c>
       <c r="O26" t="n">
-        <v>-2.95</v>
+        <v>-8.18</v>
       </c>
       <c r="P26" t="n">
         <v>35.04</v>
@@ -2065,40 +2065,40 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>451.6</v>
+        <v>441</v>
       </c>
       <c r="E27" t="n">
-        <v>21.6</v>
+        <v>-10.6</v>
       </c>
       <c r="F27" t="n">
-        <v>5.02</v>
+        <v>-2.35</v>
       </c>
       <c r="G27" t="n">
-        <v>441</v>
+        <v>438.4</v>
       </c>
       <c r="H27" t="n">
-        <v>-10.6</v>
+        <v>-2.6</v>
       </c>
       <c r="I27" t="n">
-        <v>-2.35</v>
+        <v>-0.59</v>
       </c>
       <c r="J27" t="n">
-        <v>438.4</v>
+        <v>436.6</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.6</v>
+        <v>-1.8</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.59</v>
+        <v>-0.41</v>
       </c>
       <c r="M27" t="n">
-        <v>436.6</v>
+        <v>439.8</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.8</v>
+        <v>3.2</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.41</v>
+        <v>0.73</v>
       </c>
       <c r="P27" t="n">
         <v>439.8</v>
@@ -2127,40 +2127,40 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>114.8</v>
+        <v>109.8</v>
       </c>
       <c r="E28" t="n">
-        <v>2.2</v>
+        <v>-5</v>
       </c>
       <c r="F28" t="n">
-        <v>1.95</v>
+        <v>-4.36</v>
       </c>
       <c r="G28" t="n">
-        <v>109.8</v>
+        <v>110</v>
       </c>
       <c r="H28" t="n">
-        <v>-5</v>
+        <v>0.2</v>
       </c>
       <c r="I28" t="n">
-        <v>-4.36</v>
+        <v>0.18</v>
       </c>
       <c r="J28" t="n">
-        <v>110</v>
+        <v>108.4</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2</v>
+        <v>-1.6</v>
       </c>
       <c r="L28" t="n">
-        <v>0.18</v>
+        <v>-1.45</v>
       </c>
       <c r="M28" t="n">
-        <v>108.4</v>
+        <v>107.7</v>
       </c>
       <c r="N28" t="n">
-        <v>-1.6</v>
+        <v>-0.7</v>
       </c>
       <c r="O28" t="n">
-        <v>-1.45</v>
+        <v>-0.65</v>
       </c>
       <c r="P28" t="n">
         <v>107.7</v>
@@ -2189,40 +2189,40 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>106.5</v>
+        <v>106.1</v>
       </c>
       <c r="E29" t="n">
-        <v>1.1</v>
+        <v>-0.4</v>
       </c>
       <c r="F29" t="n">
-        <v>1.04</v>
+        <v>-0.38</v>
       </c>
       <c r="G29" t="n">
-        <v>106.1</v>
+        <v>105.6</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.38</v>
+        <v>-0.47</v>
       </c>
       <c r="J29" t="n">
-        <v>105.6</v>
+        <v>103.7</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.5</v>
+        <v>-1.9</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.47</v>
+        <v>-1.8</v>
       </c>
       <c r="M29" t="n">
-        <v>103.7</v>
+        <v>104.5</v>
       </c>
       <c r="N29" t="n">
-        <v>-1.9</v>
+        <v>0.8</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.8</v>
+        <v>0.77</v>
       </c>
       <c r="P29" t="n">
         <v>104.5</v>
@@ -2251,40 +2251,40 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>73.2</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.8</v>
+        <v>-0.35</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.08</v>
+        <v>-0.48</v>
       </c>
       <c r="G30" t="n">
-        <v>72.84999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.35</v>
+        <v>-0.6</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.48</v>
+        <v>-0.82</v>
       </c>
       <c r="J30" t="n">
-        <v>72.25</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="K30" t="n">
         <v>-0.6</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.82</v>
+        <v>-0.83</v>
       </c>
       <c r="M30" t="n">
-        <v>71.65000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.6</v>
+        <v>0.25</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.83</v>
+        <v>0.35</v>
       </c>
       <c r="P30" t="n">
         <v>71.90000000000001</v>
@@ -2313,40 +2313,40 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>89.5</v>
+        <v>88.55</v>
       </c>
       <c r="E31" t="n">
-        <v>0.5</v>
+        <v>-0.95</v>
       </c>
       <c r="F31" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.06</v>
       </c>
       <c r="G31" t="n">
-        <v>88.55</v>
+        <v>86.3</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.95</v>
+        <v>-2.25</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.06</v>
+        <v>-2.54</v>
       </c>
       <c r="J31" t="n">
-        <v>86.3</v>
+        <v>85.3</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.25</v>
+        <v>-1</v>
       </c>
       <c r="L31" t="n">
-        <v>-2.54</v>
+        <v>-1.16</v>
       </c>
       <c r="M31" t="n">
-        <v>85.3</v>
+        <v>85.55</v>
       </c>
       <c r="N31" t="n">
-        <v>-1</v>
+        <v>0.25</v>
       </c>
       <c r="O31" t="n">
-        <v>-1.16</v>
+        <v>0.29</v>
       </c>
       <c r="P31" t="n">
         <v>85.55</v>
@@ -2375,40 +2375,40 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>64.3</v>
+        <v>63.8</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.3</v>
+        <v>-0.5</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.98</v>
+        <v>-0.78</v>
       </c>
       <c r="G32" t="n">
         <v>63.8</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.78</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>63.8</v>
+        <v>63.35</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="M32" t="n">
-        <v>63.35</v>
+        <v>61.05</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.45</v>
+        <v>-2.3</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.71</v>
+        <v>-3.63</v>
       </c>
       <c r="P32" t="n">
         <v>61.05</v>
@@ -2437,40 +2437,40 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>81.34999999999999</v>
+        <v>80.34999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>0.15</v>
+        <v>-1</v>
       </c>
       <c r="F33" t="n">
-        <v>0.18</v>
+        <v>-1.23</v>
       </c>
       <c r="G33" t="n">
-        <v>80.34999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="H33" t="n">
-        <v>-1</v>
+        <v>-0.85</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.23</v>
+        <v>-1.06</v>
       </c>
       <c r="J33" t="n">
-        <v>79.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.85</v>
+        <v>-1.4</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.06</v>
+        <v>-1.76</v>
       </c>
       <c r="M33" t="n">
-        <v>78.09999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="N33" t="n">
-        <v>-1.4</v>
+        <v>-0.4</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.76</v>
+        <v>-0.51</v>
       </c>
       <c r="P33" t="n">
         <v>77.7</v>
@@ -2499,40 +2499,40 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>31.22</v>
+        <v>30.78</v>
       </c>
       <c r="E34" t="n">
-        <v>0.4</v>
+        <v>-0.44</v>
       </c>
       <c r="F34" t="n">
-        <v>1.3</v>
+        <v>-1.41</v>
       </c>
       <c r="G34" t="n">
-        <v>30.78</v>
+        <v>30.5</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.44</v>
+        <v>-0.28</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.41</v>
+        <v>-0.91</v>
       </c>
       <c r="J34" t="n">
-        <v>30.5</v>
+        <v>30.02</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.28</v>
+        <v>-0.48</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.91</v>
+        <v>-1.57</v>
       </c>
       <c r="M34" t="n">
-        <v>30.02</v>
+        <v>30.7</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.48</v>
+        <v>0.68</v>
       </c>
       <c r="O34" t="n">
-        <v>-1.57</v>
+        <v>2.27</v>
       </c>
       <c r="P34" t="n">
         <v>30.7</v>
@@ -2561,31 +2561,31 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.35</v>
+        <v>4.28</v>
       </c>
       <c r="E35" t="n">
-        <v>0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>0.23</v>
+        <v>-1.61</v>
       </c>
       <c r="G35" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.61</v>
+        <v>-0.23</v>
       </c>
       <c r="J35" t="n">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.23</v>
+        <v>-0.7</v>
       </c>
       <c r="M35" t="n">
         <v>4.24</v>
@@ -2623,31 +2623,31 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.359999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="E36" t="n">
-        <v>0.02</v>
+        <v>-0.13</v>
       </c>
       <c r="F36" t="n">
-        <v>0.21</v>
+        <v>-1.39</v>
       </c>
       <c r="G36" t="n">
-        <v>9.23</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="H36" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="J36" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="K36" t="n">
         <v>-0.13</v>
       </c>
-      <c r="I36" t="n">
-        <v>-1.39</v>
-      </c>
-      <c r="J36" t="n">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="K36" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="L36" t="n">
-        <v>-0.11</v>
+        <v>-1.41</v>
       </c>
       <c r="M36" t="n">
         <v>9.09</v>
@@ -2685,40 +2685,40 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>397.4</v>
+        <v>395.8</v>
       </c>
       <c r="E37" t="n">
-        <v>6.2</v>
+        <v>-1.6</v>
       </c>
       <c r="F37" t="n">
-        <v>1.58</v>
+        <v>-0.4</v>
       </c>
       <c r="G37" t="n">
-        <v>395.8</v>
+        <v>393.4</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.6</v>
+        <v>-2.4</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.4</v>
+        <v>-0.61</v>
       </c>
       <c r="J37" t="n">
-        <v>393.4</v>
+        <v>388.4</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.4</v>
+        <v>-5</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.61</v>
+        <v>-1.27</v>
       </c>
       <c r="M37" t="n">
-        <v>388.4</v>
+        <v>388.6</v>
       </c>
       <c r="N37" t="n">
-        <v>-5</v>
+        <v>0.2</v>
       </c>
       <c r="O37" t="n">
-        <v>-1.27</v>
+        <v>0.05</v>
       </c>
       <c r="P37" t="n">
         <v>388.6</v>
@@ -2747,40 +2747,40 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.16</v>
+        <v>12.07</v>
       </c>
       <c r="E38" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="F38" t="n">
-        <v>0.5</v>
+        <v>-0.74</v>
       </c>
       <c r="G38" t="n">
-        <v>12.07</v>
+        <v>12.04</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.09</v>
+        <v>-0.03</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.74</v>
+        <v>-0.25</v>
       </c>
       <c r="J38" t="n">
-        <v>12.04</v>
+        <v>11.91</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.25</v>
+        <v>-1.08</v>
       </c>
       <c r="M38" t="n">
-        <v>11.91</v>
+        <v>11.93</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.13</v>
+        <v>0.02</v>
       </c>
       <c r="O38" t="n">
-        <v>-1.08</v>
+        <v>0.17</v>
       </c>
       <c r="P38" t="n">
         <v>11.93</v>
@@ -2809,40 +2809,40 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>507</v>
+        <v>511.5</v>
       </c>
       <c r="E39" t="n">
-        <v>3</v>
+        <v>4.5</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6</v>
+        <v>0.89</v>
       </c>
       <c r="G39" t="n">
-        <v>511.5</v>
+        <v>492.8</v>
       </c>
       <c r="H39" t="n">
-        <v>4.5</v>
+        <v>-18.7</v>
       </c>
       <c r="I39" t="n">
-        <v>0.89</v>
+        <v>-3.66</v>
       </c>
       <c r="J39" t="n">
-        <v>492.8</v>
+        <v>489.4</v>
       </c>
       <c r="K39" t="n">
-        <v>-18.7</v>
+        <v>-3.4</v>
       </c>
       <c r="L39" t="n">
-        <v>-3.66</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>489.4</v>
+        <v>484.6</v>
       </c>
       <c r="N39" t="n">
-        <v>-3.4</v>
+        <v>-4.8</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.98</v>
       </c>
       <c r="P39" t="n">
         <v>484.6</v>
@@ -2871,40 +2871,40 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>40.74</v>
+        <v>40.4</v>
       </c>
       <c r="E40" t="n">
-        <v>0.24</v>
+        <v>-0.34</v>
       </c>
       <c r="F40" t="n">
-        <v>0.59</v>
+        <v>-0.83</v>
       </c>
       <c r="G40" t="n">
-        <v>40.4</v>
+        <v>40.22</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.34</v>
+        <v>-0.18</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.83</v>
+        <v>-0.45</v>
       </c>
       <c r="J40" t="n">
-        <v>40.22</v>
+        <v>39.46</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.18</v>
+        <v>-0.76</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.45</v>
+        <v>-1.89</v>
       </c>
       <c r="M40" t="n">
-        <v>39.46</v>
+        <v>39.1</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.76</v>
+        <v>-0.36</v>
       </c>
       <c r="O40" t="n">
-        <v>-1.89</v>
+        <v>-0.91</v>
       </c>
       <c r="P40" t="n">
         <v>39.1</v>
@@ -2933,40 +2933,40 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>32.14</v>
+        <v>31.65</v>
       </c>
       <c r="E41" t="n">
-        <v>0.47</v>
+        <v>-0.49</v>
       </c>
       <c r="F41" t="n">
-        <v>1.48</v>
+        <v>-1.52</v>
       </c>
       <c r="G41" t="n">
-        <v>31.65</v>
+        <v>31.59</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.49</v>
+        <v>-0.06</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.52</v>
+        <v>-0.19</v>
       </c>
       <c r="J41" t="n">
-        <v>31.59</v>
+        <v>32.01</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.06</v>
+        <v>0.42</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.19</v>
+        <v>1.33</v>
       </c>
       <c r="M41" t="n">
-        <v>32.01</v>
+        <v>32.22</v>
       </c>
       <c r="N41" t="n">
-        <v>0.42</v>
+        <v>0.21</v>
       </c>
       <c r="O41" t="n">
-        <v>1.33</v>
+        <v>0.66</v>
       </c>
       <c r="P41" t="n">
         <v>32.22</v>
@@ -2995,40 +2995,40 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>77.8</v>
+        <v>77.69</v>
       </c>
       <c r="E42" t="n">
-        <v>0.44</v>
+        <v>-0.11</v>
       </c>
       <c r="F42" t="n">
-        <v>0.57</v>
+        <v>-0.14</v>
       </c>
       <c r="G42" t="n">
-        <v>77.69</v>
+        <v>77.48</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.11</v>
+        <v>-0.21</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.14</v>
+        <v>-0.27</v>
       </c>
       <c r="J42" t="n">
-        <v>77.48</v>
+        <v>78</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.21</v>
+        <v>0.52</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.27</v>
+        <v>0.67</v>
       </c>
       <c r="M42" t="n">
-        <v>78</v>
+        <v>78.11</v>
       </c>
       <c r="N42" t="n">
-        <v>0.52</v>
+        <v>0.11</v>
       </c>
       <c r="O42" t="n">
-        <v>0.67</v>
+        <v>0.14</v>
       </c>
       <c r="P42" t="n">
         <v>78.11</v>
@@ -3057,40 +3057,40 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>42.8</v>
+        <v>42.84</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7</v>
+        <v>0.04</v>
       </c>
       <c r="F43" t="n">
-        <v>1.66</v>
+        <v>0.09</v>
       </c>
       <c r="G43" t="n">
-        <v>42.84</v>
+        <v>42.5</v>
       </c>
       <c r="H43" t="n">
-        <v>0.04</v>
+        <v>-0.34</v>
       </c>
       <c r="I43" t="n">
-        <v>0.09</v>
+        <v>-0.79</v>
       </c>
       <c r="J43" t="n">
-        <v>42.5</v>
+        <v>42.57</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.34</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.79</v>
+        <v>0.16</v>
       </c>
       <c r="M43" t="n">
-        <v>42.57</v>
+        <v>43.29</v>
       </c>
       <c r="N43" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="O43" t="n">
-        <v>0.16</v>
+        <v>1.69</v>
       </c>
       <c r="P43" t="n">
         <v>43.29</v>
@@ -3119,40 +3119,40 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.93</v>
+        <v>5.9</v>
       </c>
       <c r="E44" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="F44" t="n">
-        <v>0.51</v>
+        <v>-0.51</v>
       </c>
       <c r="G44" t="n">
-        <v>5.9</v>
+        <v>5.85</v>
       </c>
       <c r="H44" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I44" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M44" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="N44" t="n">
         <v>-0.03</v>
       </c>
-      <c r="I44" t="n">
+      <c r="O44" t="n">
         <v>-0.51</v>
-      </c>
-      <c r="J44" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="K44" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="L44" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="M44" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0.34</v>
       </c>
       <c r="P44" t="n">
         <v>5.84</v>
@@ -3181,22 +3181,22 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="F45" t="n">
-        <v>4.88</v>
+        <v>-2.33</v>
       </c>
       <c r="G45" t="n">
         <v>2.1</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>-2.33</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>2.1</v>
@@ -3208,13 +3208,13 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>-1.43</v>
       </c>
       <c r="P45" t="n">
         <v>2.07</v>
@@ -3243,16 +3243,16 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="E46" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F46" t="n">
-        <v>0.52</v>
+        <v>-0.26</v>
       </c>
       <c r="G46" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="H46" t="n">
         <v>-0.01</v>
@@ -3261,22 +3261,22 @@
         <v>-0.26</v>
       </c>
       <c r="J46" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.26</v>
+        <v>0.52</v>
       </c>
       <c r="M46" t="n">
-        <v>3.83</v>
+        <v>3.88</v>
       </c>
       <c r="N46" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="O46" t="n">
-        <v>0.52</v>
+        <v>1.31</v>
       </c>
       <c r="P46" t="n">
         <v>3.88</v>
@@ -3305,40 +3305,40 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.69</v>
+        <v>10.81</v>
       </c>
       <c r="E47" t="n">
-        <v>0.3</v>
+        <v>0.12</v>
       </c>
       <c r="F47" t="n">
-        <v>2.89</v>
+        <v>1.12</v>
       </c>
       <c r="G47" t="n">
-        <v>10.81</v>
+        <v>10.86</v>
       </c>
       <c r="H47" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="I47" t="n">
-        <v>1.12</v>
+        <v>0.46</v>
       </c>
       <c r="J47" t="n">
-        <v>10.86</v>
+        <v>10.87</v>
       </c>
       <c r="K47" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="L47" t="n">
-        <v>0.46</v>
+        <v>0.09</v>
       </c>
       <c r="M47" t="n">
         <v>10.87</v>
       </c>
       <c r="N47" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="P47" t="n">
         <v>10.87</v>
@@ -3370,10 +3370,10 @@
         <v>0.315</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
         <v>0.315</v>
@@ -3394,13 +3394,13 @@
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.315</v>
+        <v>0.31</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>-1.59</v>
       </c>
       <c r="P48" t="n">
         <v>0.31</v>
@@ -3429,40 +3429,40 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.32</v>
+        <v>4.28</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.23</v>
+        <v>-0.93</v>
       </c>
       <c r="G49" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="J49" t="n">
         <v>4.28</v>
       </c>
-      <c r="H49" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I49" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="J49" t="n">
-        <v>4.25</v>
-      </c>
       <c r="K49" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.7</v>
+        <v>0.71</v>
       </c>
       <c r="M49" t="n">
-        <v>4.28</v>
+        <v>4.29</v>
       </c>
       <c r="N49" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="O49" t="n">
-        <v>0.71</v>
+        <v>0.23</v>
       </c>
       <c r="P49" t="n">
         <v>4.29</v>
@@ -3494,37 +3494,37 @@
         <v>1.11</v>
       </c>
       <c r="E50" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J50" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="K50" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="L50" t="n">
-        <v>2.7</v>
+        <v>-1.75</v>
       </c>
       <c r="M50" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="O50" t="n">
-        <v>-1.75</v>
+        <v>0.89</v>
       </c>
       <c r="P50" t="n">
         <v>1.13</v>
@@ -3553,40 +3553,40 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.26</v>
+        <v>5.18</v>
       </c>
       <c r="E51" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="F51" t="n">
-        <v>0.77</v>
+        <v>-1.52</v>
       </c>
       <c r="G51" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.52</v>
+        <v>-0.19</v>
       </c>
       <c r="J51" t="n">
-        <v>5.17</v>
+        <v>5.19</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.19</v>
+        <v>0.39</v>
       </c>
       <c r="M51" t="n">
-        <v>5.19</v>
+        <v>5.16</v>
       </c>
       <c r="N51" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="O51" t="n">
-        <v>0.39</v>
+        <v>-0.58</v>
       </c>
       <c r="P51" t="n">
         <v>5.16</v>
@@ -3615,40 +3615,40 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.21</v>
       </c>
       <c r="E52" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="F52" t="n">
-        <v>0.27</v>
+        <v>0.99</v>
       </c>
       <c r="G52" t="n">
-        <v>11.21</v>
+        <v>11.29</v>
       </c>
       <c r="H52" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="I52" t="n">
-        <v>0.99</v>
+        <v>0.71</v>
       </c>
       <c r="J52" t="n">
-        <v>11.29</v>
+        <v>11.3</v>
       </c>
       <c r="K52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M52" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="N52" t="n">
         <v>0.08</v>
       </c>
-      <c r="L52" t="n">
+      <c r="O52" t="n">
         <v>0.71</v>
-      </c>
-      <c r="M52" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0.09</v>
       </c>
       <c r="P52" t="n">
         <v>11.38</v>
@@ -3677,40 +3677,40 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.119999999999999</v>
+        <v>8.42</v>
       </c>
       <c r="E53" t="n">
-        <v>0.03</v>
+        <v>0.3</v>
       </c>
       <c r="F53" t="n">
-        <v>0.37</v>
+        <v>3.69</v>
       </c>
       <c r="G53" t="n">
-        <v>8.42</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="I53" t="n">
-        <v>3.69</v>
+        <v>-2.38</v>
       </c>
       <c r="J53" t="n">
-        <v>8.220000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.2</v>
+        <v>0.04</v>
       </c>
       <c r="L53" t="n">
-        <v>-2.38</v>
+        <v>0.49</v>
       </c>
       <c r="M53" t="n">
-        <v>8.26</v>
+        <v>7.59</v>
       </c>
       <c r="N53" t="n">
-        <v>0.04</v>
+        <v>-0.67</v>
       </c>
       <c r="O53" t="n">
-        <v>0.49</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="P53" t="n">
         <v>7.59</v>
@@ -3739,40 +3739,40 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.43</v>
+        <v>0.435</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="G54" t="n">
         <v>0.435</v>
       </c>
       <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K54" t="n">
         <v>0.005</v>
       </c>
-      <c r="I54" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="M54" t="n">
         <v>0.435</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0.44</v>
-      </c>
       <c r="N54" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="O54" t="n">
-        <v>1.15</v>
+        <v>-1.14</v>
       </c>
       <c r="P54" t="n">
         <v>0.435</v>
@@ -3804,10 +3804,10 @@
         <v>0.62</v>
       </c>
       <c r="E55" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0.62</v>
@@ -3819,22 +3819,22 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.62</v>
+        <v>0.615</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>0.615</v>
+        <v>0.625</v>
       </c>
       <c r="N55" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>1.63</v>
       </c>
       <c r="P55" t="n">
         <v>0.625</v>
@@ -3866,28 +3866,28 @@
         <v>0.385</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.28</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.385</v>
+        <v>0.39</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="J56" t="n">
         <v>0.39</v>
       </c>
       <c r="K56" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
         <v>0.39</v>
@@ -3925,40 +3925,40 @@
         </is>
       </c>
       <c r="D57" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="G57" t="n">
         <v>3.65</v>
       </c>
-      <c r="E57" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>3.67</v>
-      </c>
       <c r="H57" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="I57" t="n">
-        <v>0.55</v>
+        <v>-0.54</v>
       </c>
       <c r="J57" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.54</v>
+        <v>0.82</v>
       </c>
       <c r="M57" t="n">
-        <v>3.68</v>
+        <v>3.61</v>
       </c>
       <c r="N57" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>0.82</v>
+        <v>-1.9</v>
       </c>
       <c r="P57" t="n">
         <v>3.61</v>
@@ -3987,31 +3987,31 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.077</v>
+        <v>0.08</v>
       </c>
       <c r="E58" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="F58" t="n">
-        <v>1.32</v>
+        <v>3.9</v>
       </c>
       <c r="G58" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="H58" t="n">
-        <v>0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="I58" t="n">
-        <v>3.9</v>
+        <v>-1.25</v>
       </c>
       <c r="J58" t="n">
         <v>0.079</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0.079</v>
@@ -4049,40 +4049,40 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22.96</v>
+        <v>22.74</v>
       </c>
       <c r="E59" t="n">
-        <v>0.64</v>
+        <v>-0.22</v>
       </c>
       <c r="F59" t="n">
-        <v>2.87</v>
+        <v>-0.96</v>
       </c>
       <c r="G59" t="n">
-        <v>22.74</v>
+        <v>22.42</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.22</v>
+        <v>-0.32</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.96</v>
+        <v>-1.41</v>
       </c>
       <c r="J59" t="n">
-        <v>22.42</v>
+        <v>22.4</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.32</v>
+        <v>-0.02</v>
       </c>
       <c r="L59" t="n">
-        <v>-1.41</v>
+        <v>-0.09</v>
       </c>
       <c r="M59" t="n">
-        <v>22.4</v>
+        <v>22.47</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.09</v>
+        <v>0.31</v>
       </c>
       <c r="P59" t="n">
         <v>22.47</v>
@@ -4111,40 +4111,40 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="E60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="H60" t="n">
         <v>0.03</v>
       </c>
-      <c r="F60" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="G60" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.01</v>
-      </c>
       <c r="I60" t="n">
-        <v>0.32</v>
+        <v>0.96</v>
       </c>
       <c r="J60" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="K60" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="L60" t="n">
-        <v>0.96</v>
+        <v>0.63</v>
       </c>
       <c r="M60" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="N60" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="O60" t="n">
-        <v>0.63</v>
+        <v>-0.31</v>
       </c>
       <c r="P60" t="n">
         <v>3.18</v>
@@ -4176,37 +4176,37 @@
         <v>0.865</v>
       </c>
       <c r="E61" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H61" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F61" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0</v>
-      </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>-0.58</v>
       </c>
       <c r="J61" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="L61" t="n">
-        <v>-0.58</v>
+        <v>1.16</v>
       </c>
       <c r="M61" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="N61" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="O61" t="n">
-        <v>1.16</v>
+        <v>-2.3</v>
       </c>
       <c r="P61" t="n">
         <v>0.85</v>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-23 Close</t>
+          <t>2026-09-24 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-09-23 Change</t>
+          <t>2026-09-24 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-23 Change %</t>
+          <t>2026-09-24 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-09-24 Close</t>
+          <t>2026-09-25 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-09-24 Change</t>
+          <t>2026-09-25 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-09-24 Change %</t>
+          <t>2026-09-25 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-09-25 Close</t>
+          <t>2026-09-28 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-09-25 Change</t>
+          <t>2026-09-28 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-09-25 Change %</t>
+          <t>2026-09-28 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-09-28 Close</t>
+          <t>2026-09-29 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-09-28 Change</t>
+          <t>2026-09-29 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-09-28 Change %</t>
+          <t>2026-09-29 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-09-29 Close</t>
+          <t>2026-09-30 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-09-29 Change</t>
+          <t>2026-09-30 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-09-29 Change %</t>
+          <t>2026-09-30 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>159.5</v>
+        <v>156.9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2</v>
+        <v>-2.6</v>
       </c>
       <c r="F3" t="n">
-        <v>0.13</v>
+        <v>-1.63</v>
       </c>
       <c r="G3" t="n">
-        <v>156.9</v>
+        <v>157.6</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.6</v>
+        <v>0.7</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.63</v>
+        <v>0.45</v>
       </c>
       <c r="J3" t="n">
-        <v>157.6</v>
+        <v>158.9</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="L3" t="n">
-        <v>0.45</v>
+        <v>0.82</v>
       </c>
       <c r="M3" t="n">
-        <v>158.9</v>
+        <v>159</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.82</v>
+        <v>0.06</v>
       </c>
       <c r="P3" t="n">
-        <v>158.9</v>
+        <v>159</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.82</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6</v>
+        <v>-4</v>
       </c>
       <c r="F4" t="n">
-        <v>0.25</v>
+        <v>-1.67</v>
       </c>
       <c r="G4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H4" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.67</v>
+        <v>0.85</v>
       </c>
       <c r="J4" t="n">
-        <v>238</v>
+        <v>242.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.85</v>
+        <v>1.93</v>
       </c>
       <c r="M4" t="n">
-        <v>242.6</v>
+        <v>242.8</v>
       </c>
       <c r="N4" t="n">
-        <v>4.6</v>
+        <v>0.2</v>
       </c>
       <c r="O4" t="n">
-        <v>1.93</v>
+        <v>0.08</v>
       </c>
       <c r="P4" t="n">
-        <v>242.6</v>
+        <v>242.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.6</v>
+        <v>0.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.93</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="5">
@@ -701,34 +701,34 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.49</v>
+        <v>6.61</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.01</v>
+        <v>0.12</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.15</v>
+        <v>1.85</v>
       </c>
       <c r="G5" t="n">
-        <v>6.61</v>
+        <v>6.51</v>
       </c>
       <c r="H5" t="n">
-        <v>0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="I5" t="n">
-        <v>1.85</v>
+        <v>-1.51</v>
       </c>
       <c r="J5" t="n">
-        <v>6.51</v>
+        <v>6.55</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1</v>
+        <v>0.04</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.51</v>
+        <v>0.61</v>
       </c>
       <c r="M5" t="n">
-        <v>6.55</v>
+        <v>6.59</v>
       </c>
       <c r="N5" t="n">
         <v>0.04</v>
@@ -737,7 +737,7 @@
         <v>0.61</v>
       </c>
       <c r="P5" t="n">
-        <v>6.55</v>
+        <v>6.59</v>
       </c>
       <c r="Q5" t="n">
         <v>0.04</v>
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.54</v>
+        <v>7.66</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="G6" t="n">
-        <v>7.66</v>
+        <v>7.51</v>
       </c>
       <c r="H6" t="n">
-        <v>0.12</v>
+        <v>-0.15</v>
       </c>
       <c r="I6" t="n">
-        <v>1.59</v>
+        <v>-1.96</v>
       </c>
       <c r="J6" t="n">
-        <v>7.51</v>
+        <v>7.7</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.15</v>
+        <v>0.19</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.96</v>
+        <v>2.53</v>
       </c>
       <c r="M6" t="n">
-        <v>7.7</v>
+        <v>7.65</v>
       </c>
       <c r="N6" t="n">
-        <v>0.19</v>
+        <v>-0.05</v>
       </c>
       <c r="O6" t="n">
-        <v>2.53</v>
+        <v>-0.65</v>
       </c>
       <c r="P6" t="n">
-        <v>7.7</v>
+        <v>7.65</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.19</v>
+        <v>-0.05</v>
       </c>
       <c r="R6" t="n">
-        <v>2.53</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>6.04</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.33</v>
+        <v>0.67</v>
       </c>
       <c r="G7" t="n">
-        <v>6.04</v>
+        <v>5.98</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="I7" t="n">
-        <v>0.67</v>
+        <v>-0.99</v>
       </c>
       <c r="J7" t="n">
-        <v>5.98</v>
+        <v>6.07</v>
       </c>
       <c r="K7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="N7" t="n">
         <v>-0.06</v>
       </c>
-      <c r="L7" t="n">
+      <c r="O7" t="n">
         <v>-0.99</v>
       </c>
-      <c r="M7" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1.51</v>
-      </c>
       <c r="P7" t="n">
-        <v>6.07</v>
+        <v>6.01</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.09</v>
+        <v>-0.06</v>
       </c>
       <c r="R7" t="n">
-        <v>1.51</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.66</v>
+        <v>9.68</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.08</v>
+        <v>0.02</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.82</v>
+        <v>0.21</v>
       </c>
       <c r="G8" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="I8" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="J8" t="n">
         <v>9.68</v>
       </c>
-      <c r="H8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="J8" t="n">
-        <v>9.529999999999999</v>
-      </c>
       <c r="K8" t="n">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.55</v>
+        <v>1.57</v>
       </c>
       <c r="M8" t="n">
-        <v>9.68</v>
+        <v>9.69</v>
       </c>
       <c r="N8" t="n">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="O8" t="n">
-        <v>1.57</v>
+        <v>0.1</v>
       </c>
       <c r="P8" t="n">
-        <v>9.68</v>
+        <v>9.69</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="R8" t="n">
-        <v>1.57</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.210000000000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.36</v>
+        <v>0.85</v>
       </c>
       <c r="G9" t="n">
-        <v>8.279999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="I9" t="n">
-        <v>0.85</v>
+        <v>-1.09</v>
       </c>
       <c r="J9" t="n">
-        <v>8.19</v>
+        <v>8.24</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.09</v>
+        <v>0.05</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.09</v>
+        <v>0.61</v>
       </c>
       <c r="M9" t="n">
         <v>8.24</v>
       </c>
       <c r="N9" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>8.24</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51.25</v>
+        <v>51.2</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.4</v>
+        <v>-0.05</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.77</v>
+        <v>-0.1</v>
       </c>
       <c r="G10" t="n">
-        <v>51.2</v>
+        <v>50.5</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.05</v>
+        <v>-0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1</v>
+        <v>-1.37</v>
       </c>
       <c r="J10" t="n">
-        <v>50.5</v>
+        <v>51.1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7</v>
+        <v>0.6</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.37</v>
+        <v>1.19</v>
       </c>
       <c r="M10" t="n">
         <v>51.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>51.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.45</v>
+        <v>4.49</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.45</v>
+        <v>0.9</v>
       </c>
       <c r="G11" t="n">
-        <v>4.49</v>
+        <v>4.43</v>
       </c>
       <c r="H11" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9</v>
+        <v>-1.34</v>
       </c>
       <c r="J11" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.34</v>
+        <v>1.58</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="N11" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="O11" t="n">
-        <v>1.58</v>
+        <v>-2</v>
       </c>
       <c r="P11" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="R11" t="n">
-        <v>1.58</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.35</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.08</v>
+        <v>0.26</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.85</v>
+        <v>2.78</v>
       </c>
       <c r="G12" t="n">
-        <v>9.609999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="H12" t="n">
-        <v>0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="I12" t="n">
-        <v>2.78</v>
+        <v>-2.08</v>
       </c>
       <c r="J12" t="n">
-        <v>9.41</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2</v>
+        <v>0.29</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.08</v>
+        <v>3.08</v>
       </c>
       <c r="M12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>0.29</v>
+        <v>0.01</v>
       </c>
       <c r="O12" t="n">
-        <v>3.08</v>
+        <v>0.1</v>
       </c>
       <c r="P12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.29</v>
+        <v>0.01</v>
       </c>
       <c r="R12" t="n">
-        <v>3.08</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23.34</v>
+        <v>23.84</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.34</v>
+        <v>0.5</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.44</v>
+        <v>2.14</v>
       </c>
       <c r="G13" t="n">
-        <v>23.84</v>
+        <v>23.4</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5</v>
+        <v>-0.44</v>
       </c>
       <c r="I13" t="n">
-        <v>2.14</v>
+        <v>-1.85</v>
       </c>
       <c r="J13" t="n">
-        <v>23.4</v>
+        <v>23.68</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.44</v>
+        <v>0.28</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.85</v>
+        <v>1.2</v>
       </c>
       <c r="M13" t="n">
-        <v>23.68</v>
+        <v>23.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0.28</v>
+        <v>0.02</v>
       </c>
       <c r="O13" t="n">
-        <v>1.2</v>
+        <v>0.08</v>
       </c>
       <c r="P13" t="n">
-        <v>23.68</v>
+        <v>23.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.28</v>
+        <v>0.02</v>
       </c>
       <c r="R13" t="n">
-        <v>1.2</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="J14" t="n">
         <v>1.89</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="K14" t="n">
         <v>0.01</v>
       </c>
-      <c r="I14" t="n">
+      <c r="L14" t="n">
         <v>0.53</v>
       </c>
-      <c r="J14" t="n">
+      <c r="M14" t="n">
         <v>1.88</v>
       </c>
-      <c r="K14" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L14" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.89</v>
-      </c>
       <c r="N14" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="O14" t="n">
-        <v>0.53</v>
+        <v>-0.53</v>
       </c>
       <c r="P14" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="R14" t="n">
-        <v>0.53</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.17</v>
+        <v>5.18</v>
       </c>
       <c r="E15" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="H15" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F15" t="n">
+      <c r="I15" t="n">
         <v>-0.39</v>
       </c>
-      <c r="G15" t="n">
-        <v>5.18</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0.19</v>
-      </c>
       <c r="J15" t="n">
-        <v>5.16</v>
+        <v>5.36</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.02</v>
+        <v>0.2</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.39</v>
+        <v>3.88</v>
       </c>
       <c r="M15" t="n">
-        <v>5.36</v>
+        <v>5.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2</v>
+        <v>-0.06</v>
       </c>
       <c r="O15" t="n">
-        <v>3.88</v>
+        <v>-1.12</v>
       </c>
       <c r="P15" t="n">
-        <v>5.36</v>
+        <v>5.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2</v>
+        <v>-0.06</v>
       </c>
       <c r="R15" t="n">
-        <v>3.88</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.34</v>
+        <v>4.3</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.14</v>
+        <v>-0.92</v>
       </c>
       <c r="G16" t="n">
         <v>4.3</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.92</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
       <c r="M16" t="n">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.16</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.16</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1448,46 +1448,46 @@
         <v>3.16</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.66</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="M17" t="n">
         <v>3.16</v>
       </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.15</v>
-      </c>
       <c r="N17" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.25</v>
+        <v>0.32</v>
       </c>
       <c r="P17" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="R17" t="n">
-        <v>-1.25</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.01</v>
+        <v>0.34</v>
       </c>
       <c r="G18" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="H18" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N18" t="n">
         <v>0.01</v>
       </c>
-      <c r="I18" t="n">
+      <c r="O18" t="n">
         <v>0.34</v>
       </c>
-      <c r="J18" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="L18" t="n">
-        <v>-1.36</v>
-      </c>
-      <c r="M18" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="O18" t="n">
-        <v>2.41</v>
-      </c>
       <c r="P18" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="R18" t="n">
-        <v>2.41</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>53.4</v>
+        <v>53.25</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5</v>
+        <v>-0.15</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.93</v>
+        <v>-0.28</v>
       </c>
       <c r="G19" t="n">
-        <v>53.25</v>
+        <v>52.7</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.15</v>
+        <v>-0.55</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.28</v>
+        <v>-1.03</v>
       </c>
       <c r="J19" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.55</v>
+        <v>-0.1</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.03</v>
+        <v>-0.19</v>
       </c>
       <c r="M19" t="n">
-        <v>52.6</v>
+        <v>52.9</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.19</v>
+        <v>0.57</v>
       </c>
       <c r="P19" t="n">
-        <v>52.6</v>
+        <v>52.9</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.19</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.7</v>
+        <v>29.44</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>-0.26</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>-0.88</v>
       </c>
       <c r="G20" t="n">
-        <v>29.44</v>
+        <v>28.58</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.26</v>
+        <v>-0.86</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.88</v>
+        <v>-2.92</v>
       </c>
       <c r="J20" t="n">
-        <v>28.58</v>
+        <v>28.08</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.86</v>
+        <v>-0.5</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.92</v>
+        <v>-1.75</v>
       </c>
       <c r="M20" t="n">
-        <v>28.08</v>
+        <v>28.8</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5</v>
+        <v>0.72</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.75</v>
+        <v>2.56</v>
       </c>
       <c r="P20" t="n">
-        <v>28.08</v>
+        <v>28.8</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.5</v>
+        <v>0.72</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.75</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="21">
@@ -1696,46 +1696,46 @@
         <v>4.41</v>
       </c>
       <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="H21" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F21" t="n">
+      <c r="I21" t="n">
         <v>-0.45</v>
       </c>
-      <c r="G21" t="n">
-        <v>4.41</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
       <c r="J21" t="n">
-        <v>4.39</v>
+        <v>4.49</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.02</v>
+        <v>0.1</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.45</v>
+        <v>2.28</v>
       </c>
       <c r="M21" t="n">
         <v>4.49</v>
       </c>
       <c r="N21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>4.49</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.15</v>
+        <v>0.1</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.19</v>
+        <v>0.13</v>
       </c>
       <c r="G22" t="n">
-        <v>78.90000000000001</v>
+        <v>78.45</v>
       </c>
       <c r="H22" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="J22" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="M22" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="N22" t="n">
         <v>0.1</v>
       </c>
-      <c r="I22" t="n">
+      <c r="O22" t="n">
         <v>0.13</v>
       </c>
-      <c r="J22" t="n">
-        <v>78.45</v>
-      </c>
-      <c r="K22" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="M22" t="n">
-        <v>79.25</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="O22" t="n">
-        <v>1.02</v>
-      </c>
       <c r="P22" t="n">
-        <v>79.25</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.02</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.64</v>
+        <v>0.1</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.75</v>
+        <v>0.44</v>
       </c>
       <c r="G23" t="n">
-        <v>22.7</v>
+        <v>22.44</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1</v>
+        <v>-0.26</v>
       </c>
       <c r="I23" t="n">
-        <v>0.44</v>
+        <v>-1.15</v>
       </c>
       <c r="J23" t="n">
-        <v>22.44</v>
+        <v>22.08</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.26</v>
+        <v>-0.36</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.15</v>
+        <v>-1.6</v>
       </c>
       <c r="M23" t="n">
-        <v>22.08</v>
+        <v>21.72</v>
       </c>
       <c r="N23" t="n">
         <v>-0.36</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.6</v>
+        <v>-1.63</v>
       </c>
       <c r="P23" t="n">
-        <v>22.08</v>
+        <v>21.72</v>
       </c>
       <c r="Q23" t="n">
         <v>-0.36</v>
       </c>
       <c r="R23" t="n">
-        <v>-1.6</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.25</v>
+        <v>15.09</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.61</v>
+        <v>-0.16</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.85</v>
+        <v>-1.05</v>
       </c>
       <c r="G24" t="n">
-        <v>15.09</v>
+        <v>15.08</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.16</v>
+        <v>-0.01</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>15.08</v>
+        <v>14.41</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.01</v>
+        <v>-0.67</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-4.44</v>
       </c>
       <c r="M24" t="n">
-        <v>14.41</v>
+        <v>14.58</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.67</v>
+        <v>0.17</v>
       </c>
       <c r="O24" t="n">
-        <v>-4.44</v>
+        <v>1.18</v>
       </c>
       <c r="P24" t="n">
-        <v>14.41</v>
+        <v>14.58</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.67</v>
+        <v>0.17</v>
       </c>
       <c r="R24" t="n">
-        <v>-4.44</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.18</v>
+        <v>26.58</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.02</v>
+        <v>0.4</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.75</v>
+        <v>1.53</v>
       </c>
       <c r="G25" t="n">
-        <v>26.58</v>
+        <v>25.9</v>
       </c>
       <c r="H25" t="n">
-        <v>0.4</v>
+        <v>-0.68</v>
       </c>
       <c r="I25" t="n">
-        <v>1.53</v>
+        <v>-2.56</v>
       </c>
       <c r="J25" t="n">
-        <v>25.9</v>
+        <v>25.86</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.68</v>
+        <v>-0.04</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.56</v>
+        <v>-0.15</v>
       </c>
       <c r="M25" t="n">
-        <v>25.86</v>
+        <v>25.2</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.04</v>
+        <v>-0.66</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.15</v>
+        <v>-2.55</v>
       </c>
       <c r="P25" t="n">
-        <v>25.86</v>
+        <v>25.2</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.04</v>
+        <v>-0.66</v>
       </c>
       <c r="R25" t="n">
-        <v>-0.15</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>40.16</v>
+        <v>39.32</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.74</v>
+        <v>-0.84</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.39</v>
+        <v>-2.09</v>
       </c>
       <c r="G26" t="n">
-        <v>39.32</v>
+        <v>38.16</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.84</v>
+        <v>-1.16</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.09</v>
+        <v>-2.95</v>
       </c>
       <c r="J26" t="n">
-        <v>38.16</v>
+        <v>35.04</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.16</v>
+        <v>-3.12</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.95</v>
+        <v>-8.18</v>
       </c>
       <c r="M26" t="n">
-        <v>35.04</v>
+        <v>37.36</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.12</v>
+        <v>2.32</v>
       </c>
       <c r="O26" t="n">
-        <v>-8.18</v>
+        <v>6.62</v>
       </c>
       <c r="P26" t="n">
-        <v>35.04</v>
+        <v>37.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.12</v>
+        <v>2.32</v>
       </c>
       <c r="R26" t="n">
-        <v>-8.18</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>441</v>
+        <v>438.4</v>
       </c>
       <c r="E27" t="n">
-        <v>-10.6</v>
+        <v>-2.6</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.35</v>
+        <v>-0.59</v>
       </c>
       <c r="G27" t="n">
-        <v>438.4</v>
+        <v>436.6</v>
       </c>
       <c r="H27" t="n">
-        <v>-2.6</v>
+        <v>-1.8</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.59</v>
+        <v>-0.41</v>
       </c>
       <c r="J27" t="n">
-        <v>436.6</v>
+        <v>439.8</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.8</v>
+        <v>3.2</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.41</v>
+        <v>0.73</v>
       </c>
       <c r="M27" t="n">
-        <v>439.8</v>
+        <v>432</v>
       </c>
       <c r="N27" t="n">
-        <v>3.2</v>
+        <v>-7.8</v>
       </c>
       <c r="O27" t="n">
-        <v>0.73</v>
+        <v>-1.77</v>
       </c>
       <c r="P27" t="n">
-        <v>439.8</v>
+        <v>432</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>-7.8</v>
       </c>
       <c r="R27" t="n">
-        <v>0.73</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>109.8</v>
+        <v>110</v>
       </c>
       <c r="E28" t="n">
-        <v>-5</v>
+        <v>0.2</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.36</v>
+        <v>0.18</v>
       </c>
       <c r="G28" t="n">
-        <v>110</v>
+        <v>108.4</v>
       </c>
       <c r="H28" t="n">
-        <v>0.2</v>
+        <v>-1.6</v>
       </c>
       <c r="I28" t="n">
-        <v>0.18</v>
+        <v>-1.45</v>
       </c>
       <c r="J28" t="n">
-        <v>108.4</v>
+        <v>107.7</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.6</v>
+        <v>-0.7</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.45</v>
+        <v>-0.65</v>
       </c>
       <c r="M28" t="n">
-        <v>107.7</v>
+        <v>106.2</v>
       </c>
       <c r="N28" t="n">
-        <v>-0.7</v>
+        <v>-1.5</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.65</v>
+        <v>-1.39</v>
       </c>
       <c r="P28" t="n">
-        <v>107.7</v>
+        <v>106.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.7</v>
+        <v>-1.5</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.65</v>
+        <v>-1.39</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>106.1</v>
+        <v>105.6</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.38</v>
+        <v>-0.47</v>
       </c>
       <c r="G29" t="n">
-        <v>105.6</v>
+        <v>103.7</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5</v>
+        <v>-1.9</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.47</v>
+        <v>-1.8</v>
       </c>
       <c r="J29" t="n">
-        <v>103.7</v>
+        <v>104.5</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.9</v>
+        <v>0.8</v>
       </c>
       <c r="L29" t="n">
-        <v>-1.8</v>
+        <v>0.77</v>
       </c>
       <c r="M29" t="n">
-        <v>104.5</v>
+        <v>103.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.8</v>
+        <v>-1.4</v>
       </c>
       <c r="O29" t="n">
-        <v>0.77</v>
+        <v>-1.34</v>
       </c>
       <c r="P29" t="n">
-        <v>104.5</v>
+        <v>103.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8</v>
+        <v>-1.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0.77</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>72.84999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.35</v>
+        <v>-0.6</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.48</v>
+        <v>-0.82</v>
       </c>
       <c r="G30" t="n">
-        <v>72.25</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="H30" t="n">
         <v>-0.6</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.82</v>
+        <v>-0.83</v>
       </c>
       <c r="J30" t="n">
-        <v>71.65000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.6</v>
+        <v>0.25</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.83</v>
+        <v>0.35</v>
       </c>
       <c r="M30" t="n">
-        <v>71.90000000000001</v>
+        <v>70.45</v>
       </c>
       <c r="N30" t="n">
-        <v>0.25</v>
+        <v>-1.45</v>
       </c>
       <c r="O30" t="n">
-        <v>0.35</v>
+        <v>-2.02</v>
       </c>
       <c r="P30" t="n">
-        <v>71.90000000000001</v>
+        <v>70.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.25</v>
+        <v>-1.45</v>
       </c>
       <c r="R30" t="n">
-        <v>0.35</v>
+        <v>-2.02</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>88.55</v>
+        <v>86.3</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.95</v>
+        <v>-2.25</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.06</v>
+        <v>-2.54</v>
       </c>
       <c r="G31" t="n">
-        <v>86.3</v>
+        <v>85.3</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.25</v>
+        <v>-1</v>
       </c>
       <c r="I31" t="n">
-        <v>-2.54</v>
+        <v>-1.16</v>
       </c>
       <c r="J31" t="n">
-        <v>85.3</v>
+        <v>85.55</v>
       </c>
       <c r="K31" t="n">
-        <v>-1</v>
+        <v>0.25</v>
       </c>
       <c r="L31" t="n">
-        <v>-1.16</v>
+        <v>0.29</v>
       </c>
       <c r="M31" t="n">
-        <v>85.55</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>0.25</v>
+        <v>-0.65</v>
       </c>
       <c r="O31" t="n">
-        <v>0.29</v>
+        <v>-0.76</v>
       </c>
       <c r="P31" t="n">
-        <v>85.55</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.25</v>
+        <v>-0.65</v>
       </c>
       <c r="R31" t="n">
-        <v>0.29</v>
+        <v>-0.76</v>
       </c>
     </row>
     <row r="32">
@@ -2378,46 +2378,46 @@
         <v>63.8</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.78</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>63.8</v>
+        <v>63.35</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="J32" t="n">
-        <v>63.35</v>
+        <v>61.05</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.45</v>
+        <v>-2.3</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.71</v>
+        <v>-3.63</v>
       </c>
       <c r="M32" t="n">
         <v>61.05</v>
       </c>
       <c r="N32" t="n">
-        <v>-2.3</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>-3.63</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>61.05</v>
       </c>
       <c r="Q32" t="n">
-        <v>-2.3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>-3.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>80.34999999999999</v>
+        <v>79.5</v>
       </c>
       <c r="E33" t="n">
-        <v>-1</v>
+        <v>-0.85</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.23</v>
+        <v>-1.06</v>
       </c>
       <c r="G33" t="n">
-        <v>79.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.85</v>
+        <v>-1.4</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.06</v>
+        <v>-1.76</v>
       </c>
       <c r="J33" t="n">
-        <v>78.09999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.4</v>
+        <v>-0.4</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.76</v>
+        <v>-0.51</v>
       </c>
       <c r="M33" t="n">
-        <v>77.7</v>
+        <v>75.75</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.4</v>
+        <v>-1.95</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.51</v>
+        <v>-2.51</v>
       </c>
       <c r="P33" t="n">
-        <v>77.7</v>
+        <v>75.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.4</v>
+        <v>-1.95</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.51</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>30.78</v>
+        <v>30.5</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.44</v>
+        <v>-0.28</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.41</v>
+        <v>-0.91</v>
       </c>
       <c r="G34" t="n">
-        <v>30.5</v>
+        <v>30.02</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.28</v>
+        <v>-0.48</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.91</v>
+        <v>-1.57</v>
       </c>
       <c r="J34" t="n">
-        <v>30.02</v>
+        <v>30.7</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.48</v>
+        <v>0.68</v>
       </c>
       <c r="L34" t="n">
-        <v>-1.57</v>
+        <v>2.27</v>
       </c>
       <c r="M34" t="n">
-        <v>30.7</v>
+        <v>30.24</v>
       </c>
       <c r="N34" t="n">
-        <v>0.68</v>
+        <v>-0.46</v>
       </c>
       <c r="O34" t="n">
-        <v>2.27</v>
+        <v>-1.5</v>
       </c>
       <c r="P34" t="n">
-        <v>30.7</v>
+        <v>30.24</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.68</v>
+        <v>-0.46</v>
       </c>
       <c r="R34" t="n">
-        <v>2.27</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.61</v>
+        <v>-0.23</v>
       </c>
       <c r="G35" t="n">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.23</v>
+        <v>-0.7</v>
       </c>
       <c r="J35" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.7</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.7</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="P35" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.7</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.23</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="E36" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="G36" t="n">
+        <v>9.09</v>
+      </c>
+      <c r="H36" t="n">
         <v>-0.13</v>
       </c>
-      <c r="F36" t="n">
-        <v>-1.39</v>
-      </c>
-      <c r="G36" t="n">
-        <v>9.220000000000001</v>
-      </c>
-      <c r="H36" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="I36" t="n">
-        <v>-0.11</v>
+        <v>-1.41</v>
       </c>
       <c r="J36" t="n">
         <v>9.09</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
-        <v>-1.41</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
         <v>9.09</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>-1.41</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
         <v>9.09</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>-1.41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>395.8</v>
+        <v>393.4</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.6</v>
+        <v>-2.4</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.4</v>
+        <v>-0.61</v>
       </c>
       <c r="G37" t="n">
-        <v>393.4</v>
+        <v>388.4</v>
       </c>
       <c r="H37" t="n">
-        <v>-2.4</v>
+        <v>-5</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.61</v>
+        <v>-1.27</v>
       </c>
       <c r="J37" t="n">
-        <v>388.4</v>
+        <v>388.6</v>
       </c>
       <c r="K37" t="n">
-        <v>-5</v>
+        <v>0.2</v>
       </c>
       <c r="L37" t="n">
-        <v>-1.27</v>
+        <v>0.05</v>
       </c>
       <c r="M37" t="n">
-        <v>388.6</v>
+        <v>386.8</v>
       </c>
       <c r="N37" t="n">
-        <v>0.2</v>
+        <v>-1.8</v>
       </c>
       <c r="O37" t="n">
-        <v>0.05</v>
+        <v>-0.46</v>
       </c>
       <c r="P37" t="n">
-        <v>388.6</v>
+        <v>386.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.2</v>
+        <v>-1.8</v>
       </c>
       <c r="R37" t="n">
-        <v>0.05</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.07</v>
+        <v>12.04</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.09</v>
+        <v>-0.03</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.74</v>
+        <v>-0.25</v>
       </c>
       <c r="G38" t="n">
-        <v>12.04</v>
+        <v>11.91</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.25</v>
+        <v>-1.08</v>
       </c>
       <c r="J38" t="n">
-        <v>11.91</v>
+        <v>11.93</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.13</v>
+        <v>0.02</v>
       </c>
       <c r="L38" t="n">
-        <v>-1.08</v>
+        <v>0.17</v>
       </c>
       <c r="M38" t="n">
-        <v>11.93</v>
+        <v>11.79</v>
       </c>
       <c r="N38" t="n">
-        <v>0.02</v>
+        <v>-0.14</v>
       </c>
       <c r="O38" t="n">
-        <v>0.17</v>
+        <v>-1.17</v>
       </c>
       <c r="P38" t="n">
-        <v>11.93</v>
+        <v>11.79</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.02</v>
+        <v>-0.14</v>
       </c>
       <c r="R38" t="n">
-        <v>0.17</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>511.5</v>
+        <v>492.8</v>
       </c>
       <c r="E39" t="n">
-        <v>4.5</v>
+        <v>-18.7</v>
       </c>
       <c r="F39" t="n">
-        <v>0.89</v>
+        <v>-3.66</v>
       </c>
       <c r="G39" t="n">
-        <v>492.8</v>
+        <v>489.4</v>
       </c>
       <c r="H39" t="n">
-        <v>-18.7</v>
+        <v>-3.4</v>
       </c>
       <c r="I39" t="n">
-        <v>-3.66</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>489.4</v>
+        <v>484.6</v>
       </c>
       <c r="K39" t="n">
-        <v>-3.4</v>
+        <v>-4.8</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.98</v>
       </c>
       <c r="M39" t="n">
-        <v>484.6</v>
+        <v>482.2</v>
       </c>
       <c r="N39" t="n">
-        <v>-4.8</v>
+        <v>-2.4</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.98</v>
+        <v>-0.5</v>
       </c>
       <c r="P39" t="n">
-        <v>484.6</v>
+        <v>482.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>-4.8</v>
+        <v>-2.4</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.98</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>40.4</v>
+        <v>40.22</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.34</v>
+        <v>-0.18</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.83</v>
+        <v>-0.45</v>
       </c>
       <c r="G40" t="n">
-        <v>40.22</v>
+        <v>39.46</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.18</v>
+        <v>-0.76</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.45</v>
+        <v>-1.89</v>
       </c>
       <c r="J40" t="n">
-        <v>39.46</v>
+        <v>39.1</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.76</v>
+        <v>-0.36</v>
       </c>
       <c r="L40" t="n">
-        <v>-1.89</v>
+        <v>-0.91</v>
       </c>
       <c r="M40" t="n">
-        <v>39.1</v>
+        <v>37.5</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.36</v>
+        <v>-1.6</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.91</v>
+        <v>-4.09</v>
       </c>
       <c r="P40" t="n">
-        <v>39.1</v>
+        <v>37.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.36</v>
+        <v>-1.6</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.91</v>
+        <v>-4.09</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.65</v>
+        <v>31.59</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.49</v>
+        <v>-0.06</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.52</v>
+        <v>-0.19</v>
       </c>
       <c r="G41" t="n">
-        <v>31.59</v>
+        <v>32.01</v>
       </c>
       <c r="H41" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J41" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="M41" t="n">
+        <v>32.16</v>
+      </c>
+      <c r="N41" t="n">
         <v>-0.06</v>
       </c>
-      <c r="I41" t="n">
+      <c r="O41" t="n">
         <v>-0.19</v>
       </c>
-      <c r="J41" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="L41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="M41" t="n">
-        <v>32.22</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0.66</v>
-      </c>
       <c r="P41" t="n">
-        <v>32.22</v>
+        <v>32.16</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.21</v>
+        <v>-0.06</v>
       </c>
       <c r="R41" t="n">
-        <v>0.66</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>77.69</v>
+        <v>77.48</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.11</v>
+        <v>-0.21</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.14</v>
+        <v>-0.27</v>
       </c>
       <c r="G42" t="n">
-        <v>77.48</v>
+        <v>78</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.21</v>
+        <v>0.52</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.27</v>
+        <v>0.67</v>
       </c>
       <c r="J42" t="n">
-        <v>78</v>
+        <v>78.11</v>
       </c>
       <c r="K42" t="n">
-        <v>0.52</v>
+        <v>0.11</v>
       </c>
       <c r="L42" t="n">
-        <v>0.67</v>
+        <v>0.14</v>
       </c>
       <c r="M42" t="n">
-        <v>78.11</v>
+        <v>78.38</v>
       </c>
       <c r="N42" t="n">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="O42" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
       <c r="P42" t="n">
-        <v>78.11</v>
+        <v>78.38</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="R42" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>42.84</v>
+        <v>42.5</v>
       </c>
       <c r="E43" t="n">
-        <v>0.04</v>
+        <v>-0.34</v>
       </c>
       <c r="F43" t="n">
-        <v>0.09</v>
+        <v>-0.79</v>
       </c>
       <c r="G43" t="n">
-        <v>42.5</v>
+        <v>42.57</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.34</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.79</v>
+        <v>0.16</v>
       </c>
       <c r="J43" t="n">
-        <v>42.57</v>
+        <v>43.29</v>
       </c>
       <c r="K43" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M43" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O43" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="L43" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="M43" t="n">
-        <v>43.29</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="O43" t="n">
-        <v>1.69</v>
-      </c>
       <c r="P43" t="n">
-        <v>43.29</v>
+        <v>43.32</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.72</v>
+        <v>0.03</v>
       </c>
       <c r="R43" t="n">
-        <v>1.69</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.9</v>
+        <v>5.85</v>
       </c>
       <c r="E44" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5.87</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="K44" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F44" t="n">
+      <c r="L44" t="n">
         <v>-0.51</v>
       </c>
-      <c r="G44" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I44" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="J44" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.34</v>
-      </c>
       <c r="M44" t="n">
-        <v>5.84</v>
+        <v>5.8</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.51</v>
+        <v>-0.68</v>
       </c>
       <c r="P44" t="n">
-        <v>5.84</v>
+        <v>5.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.51</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="45">
@@ -3184,10 +3184,10 @@
         <v>2.1</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.33</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>2.1</v>
@@ -3199,31 +3199,31 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>-1.43</v>
       </c>
       <c r="M45" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="O45" t="n">
-        <v>-1.43</v>
+        <v>0.48</v>
       </c>
       <c r="P45" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="R45" t="n">
-        <v>-1.43</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="46">
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="E46" t="n">
         <v>-0.01</v>
@@ -3252,40 +3252,40 @@
         <v>-0.26</v>
       </c>
       <c r="G46" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="H46" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="N46" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I46" t="n">
+      <c r="O46" t="n">
         <v>-0.26</v>
       </c>
-      <c r="J46" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="O46" t="n">
-        <v>1.31</v>
-      </c>
       <c r="P46" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="R46" t="n">
-        <v>1.31</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.81</v>
+        <v>10.86</v>
       </c>
       <c r="E47" t="n">
-        <v>0.12</v>
+        <v>0.05</v>
       </c>
       <c r="F47" t="n">
-        <v>1.12</v>
+        <v>0.46</v>
       </c>
       <c r="G47" t="n">
-        <v>10.86</v>
+        <v>10.87</v>
       </c>
       <c r="H47" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I47" t="n">
-        <v>0.46</v>
+        <v>0.09</v>
       </c>
       <c r="J47" t="n">
         <v>10.87</v>
       </c>
       <c r="K47" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>10.87</v>
+        <v>10.85</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="P47" t="n">
-        <v>10.87</v>
+        <v>10.85</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="48">
@@ -3385,31 +3385,31 @@
         <v>0</v>
       </c>
       <c r="J48" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="L48" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="M48" t="n">
         <v>0.315</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.31</v>
-      </c>
       <c r="N48" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.59</v>
+        <v>1.61</v>
       </c>
       <c r="P48" t="n">
-        <v>0.31</v>
+        <v>0.315</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>-1.59</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="G49" t="n">
         <v>4.28</v>
       </c>
-      <c r="E49" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="G49" t="n">
-        <v>4.25</v>
-      </c>
       <c r="H49" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.7</v>
+        <v>0.71</v>
       </c>
       <c r="J49" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M49" t="n">
         <v>4.28</v>
       </c>
-      <c r="K49" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="M49" t="n">
-        <v>4.29</v>
-      </c>
       <c r="N49" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="O49" t="n">
-        <v>0.23</v>
+        <v>-0.23</v>
       </c>
       <c r="P49" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="R49" t="n">
-        <v>0.23</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="G50" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="H50" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="I50" t="n">
-        <v>2.7</v>
+        <v>-1.75</v>
       </c>
       <c r="J50" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="M50" t="n">
         <v>1.12</v>
       </c>
-      <c r="K50" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L50" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.13</v>
-      </c>
       <c r="N50" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="O50" t="n">
-        <v>0.89</v>
+        <v>-0.88</v>
       </c>
       <c r="P50" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="R50" t="n">
-        <v>0.89</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.18</v>
+        <v>5.17</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.52</v>
+        <v>-0.19</v>
       </c>
       <c r="G51" t="n">
-        <v>5.17</v>
+        <v>5.19</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.19</v>
+        <v>0.39</v>
       </c>
       <c r="J51" t="n">
-        <v>5.19</v>
+        <v>5.16</v>
       </c>
       <c r="K51" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="L51" t="n">
-        <v>0.39</v>
+        <v>-0.58</v>
       </c>
       <c r="M51" t="n">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.58</v>
+        <v>-0.39</v>
       </c>
       <c r="P51" t="n">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="R51" t="n">
-        <v>-0.58</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.21</v>
+        <v>11.29</v>
       </c>
       <c r="E52" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="F52" t="n">
-        <v>0.99</v>
+        <v>0.71</v>
       </c>
       <c r="G52" t="n">
-        <v>11.29</v>
+        <v>11.3</v>
       </c>
       <c r="H52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J52" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="K52" t="n">
         <v>0.08</v>
       </c>
-      <c r="I52" t="n">
+      <c r="L52" t="n">
         <v>0.71</v>
       </c>
-      <c r="J52" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L52" t="n">
+      <c r="M52" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="N52" t="n">
         <v>0.09</v>
       </c>
-      <c r="M52" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0.08</v>
-      </c>
       <c r="O52" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="P52" t="n">
-        <v>11.38</v>
+        <v>11.47</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="R52" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.42</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="F53" t="n">
-        <v>3.69</v>
+        <v>-2.38</v>
       </c>
       <c r="G53" t="n">
-        <v>8.220000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.2</v>
+        <v>0.04</v>
       </c>
       <c r="I53" t="n">
-        <v>-2.38</v>
+        <v>0.49</v>
       </c>
       <c r="J53" t="n">
-        <v>8.26</v>
+        <v>7.59</v>
       </c>
       <c r="K53" t="n">
-        <v>0.04</v>
+        <v>-0.67</v>
       </c>
       <c r="L53" t="n">
-        <v>0.49</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>7.59</v>
+        <v>7.43</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.67</v>
+        <v>-0.16</v>
       </c>
       <c r="O53" t="n">
-        <v>-8.109999999999999</v>
+        <v>-2.11</v>
       </c>
       <c r="P53" t="n">
-        <v>7.59</v>
+        <v>7.43</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.67</v>
+        <v>-0.16</v>
       </c>
       <c r="R53" t="n">
-        <v>-8.109999999999999</v>
+        <v>-2.11</v>
       </c>
     </row>
     <row r="54">
@@ -3742,46 +3742,46 @@
         <v>0.435</v>
       </c>
       <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H54" t="n">
         <v>0.005</v>
       </c>
-      <c r="F54" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="G54" t="n">
+      <c r="I54" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="J54" t="n">
         <v>0.435</v>
       </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.44</v>
-      </c>
       <c r="K54" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="L54" t="n">
-        <v>1.15</v>
+        <v>-1.14</v>
       </c>
       <c r="M54" t="n">
         <v>0.435</v>
       </c>
       <c r="N54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
         <v>0.435</v>
       </c>
       <c r="Q54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>-1.14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3810,40 +3810,40 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.62</v>
+        <v>0.615</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J55" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L55" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M55" t="n">
         <v>0.615</v>
       </c>
-      <c r="K55" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="L55" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="M55" t="n">
-        <v>0.625</v>
-      </c>
       <c r="N55" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="O55" t="n">
-        <v>1.63</v>
+        <v>-1.6</v>
       </c>
       <c r="P55" t="n">
-        <v>0.625</v>
+        <v>0.615</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="R55" t="n">
-        <v>1.63</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="56">
@@ -3863,22 +3863,22 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.385</v>
+        <v>0.39</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="G56" t="n">
         <v>0.39</v>
       </c>
       <c r="H56" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="I56" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="J56" t="n">
         <v>0.39</v>
@@ -3890,22 +3890,22 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.39</v>
+        <v>0.375</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>-3.85</v>
       </c>
       <c r="P56" t="n">
-        <v>0.39</v>
+        <v>0.375</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>-3.85</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="E57" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="F57" t="n">
-        <v>0.55</v>
+        <v>-0.54</v>
       </c>
       <c r="G57" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.54</v>
+        <v>0.82</v>
       </c>
       <c r="J57" t="n">
-        <v>3.68</v>
+        <v>3.61</v>
       </c>
       <c r="K57" t="n">
-        <v>0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>0.82</v>
+        <v>-1.9</v>
       </c>
       <c r="M57" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="O57" t="n">
-        <v>-1.9</v>
+        <v>-0.83</v>
       </c>
       <c r="P57" t="n">
-        <v>3.61</v>
+        <v>3.58</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="R57" t="n">
-        <v>-1.9</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="58">
@@ -3987,22 +3987,22 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.08</v>
+        <v>0.079</v>
       </c>
       <c r="E58" t="n">
-        <v>0.003</v>
+        <v>-0.001</v>
       </c>
       <c r="F58" t="n">
-        <v>3.9</v>
+        <v>-1.25</v>
       </c>
       <c r="G58" t="n">
         <v>0.079</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0.079</v>
@@ -4014,22 +4014,22 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="P58" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22.74</v>
+        <v>22.42</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.22</v>
+        <v>-0.32</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.96</v>
+        <v>-1.41</v>
       </c>
       <c r="G59" t="n">
-        <v>22.42</v>
+        <v>22.4</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.32</v>
+        <v>-0.02</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.41</v>
+        <v>-0.09</v>
       </c>
       <c r="J59" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M59" t="n">
         <v>22.4</v>
       </c>
-      <c r="K59" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L59" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="M59" t="n">
-        <v>22.47</v>
-      </c>
       <c r="N59" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O59" t="n">
-        <v>0.31</v>
+        <v>-0.31</v>
       </c>
       <c r="P59" t="n">
-        <v>22.47</v>
+        <v>22.4</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R59" t="n">
-        <v>0.31</v>
+        <v>-0.31</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.14</v>
+        <v>3.17</v>
       </c>
       <c r="E60" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="F60" t="n">
-        <v>0.32</v>
+        <v>0.96</v>
       </c>
       <c r="G60" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="H60" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="I60" t="n">
-        <v>0.96</v>
+        <v>0.63</v>
       </c>
       <c r="J60" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="K60" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="L60" t="n">
-        <v>0.63</v>
+        <v>-0.31</v>
       </c>
       <c r="M60" t="n">
         <v>3.18</v>
       </c>
       <c r="N60" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.31</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
         <v>3.18</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.31</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.865</v>
+        <v>0.86</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>-0.58</v>
       </c>
       <c r="G61" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.58</v>
+        <v>1.16</v>
       </c>
       <c r="J61" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="K61" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="L61" t="n">
-        <v>1.16</v>
+        <v>-2.3</v>
       </c>
       <c r="M61" t="n">
-        <v>0.85</v>
+        <v>0.855</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.02</v>
+        <v>0.005</v>
       </c>
       <c r="O61" t="n">
-        <v>-2.3</v>
+        <v>0.59</v>
       </c>
       <c r="P61" t="n">
-        <v>0.85</v>
+        <v>0.855</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.02</v>
+        <v>0.005</v>
       </c>
       <c r="R61" t="n">
-        <v>-2.3</v>
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-24 Close</t>
+          <t>2026-09-25 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-09-24 Change</t>
+          <t>2026-09-25 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-24 Change %</t>
+          <t>2026-09-25 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-09-25 Close</t>
+          <t>2026-09-28 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-09-25 Change</t>
+          <t>2026-09-28 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-09-25 Change %</t>
+          <t>2026-09-28 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-09-28 Close</t>
+          <t>2026-09-29 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-09-28 Change</t>
+          <t>2026-09-29 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-09-28 Change %</t>
+          <t>2026-09-29 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-09-29 Close</t>
+          <t>2026-09-30 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-09-29 Change</t>
+          <t>2026-09-30 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-09-29 Change %</t>
+          <t>2026-09-30 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-09-30 Close</t>
+          <t>2026-10-01 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-09-30 Change</t>
+          <t>2026-10-01 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-09-30 Change %</t>
+          <t>2026-10-01 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>156.9</v>
+        <v>157.6</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.6</v>
+        <v>0.7</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.63</v>
+        <v>0.45</v>
       </c>
       <c r="G3" t="n">
-        <v>157.6</v>
+        <v>158.9</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="I3" t="n">
-        <v>0.45</v>
+        <v>0.82</v>
       </c>
       <c r="J3" t="n">
-        <v>158.9</v>
+        <v>159</v>
       </c>
       <c r="K3" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.82</v>
+        <v>0.06</v>
       </c>
       <c r="M3" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06</v>
+        <v>-0.63</v>
       </c>
       <c r="P3" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.06</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E4" t="n">
-        <v>-4</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.67</v>
+        <v>0.85</v>
       </c>
       <c r="G4" t="n">
-        <v>238</v>
+        <v>242.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.85</v>
+        <v>1.93</v>
       </c>
       <c r="J4" t="n">
-        <v>242.6</v>
+        <v>242.8</v>
       </c>
       <c r="K4" t="n">
-        <v>4.6</v>
+        <v>0.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.93</v>
+        <v>0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>242.8</v>
+        <v>244.4</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08</v>
+        <v>0.66</v>
       </c>
       <c r="P4" t="n">
-        <v>242.8</v>
+        <v>244.4</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="R4" t="n">
-        <v>0.08</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="5">
@@ -701,25 +701,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.61</v>
+        <v>6.51</v>
       </c>
       <c r="E5" t="n">
-        <v>0.12</v>
+        <v>-0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>1.85</v>
+        <v>-1.51</v>
       </c>
       <c r="G5" t="n">
-        <v>6.51</v>
+        <v>6.55</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1</v>
+        <v>0.04</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.51</v>
+        <v>0.61</v>
       </c>
       <c r="J5" t="n">
-        <v>6.55</v>
+        <v>6.59</v>
       </c>
       <c r="K5" t="n">
         <v>0.04</v>
@@ -728,7 +728,7 @@
         <v>0.61</v>
       </c>
       <c r="M5" t="n">
-        <v>6.59</v>
+        <v>6.63</v>
       </c>
       <c r="N5" t="n">
         <v>0.04</v>
@@ -737,7 +737,7 @@
         <v>0.61</v>
       </c>
       <c r="P5" t="n">
-        <v>6.59</v>
+        <v>6.63</v>
       </c>
       <c r="Q5" t="n">
         <v>0.04</v>
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.66</v>
+        <v>7.51</v>
       </c>
       <c r="E6" t="n">
-        <v>0.12</v>
+        <v>-0.15</v>
       </c>
       <c r="F6" t="n">
-        <v>1.59</v>
+        <v>-1.96</v>
       </c>
       <c r="G6" t="n">
-        <v>7.51</v>
+        <v>7.7</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.96</v>
+        <v>2.53</v>
       </c>
       <c r="J6" t="n">
-        <v>7.7</v>
+        <v>7.65</v>
       </c>
       <c r="K6" t="n">
-        <v>0.19</v>
+        <v>-0.05</v>
       </c>
       <c r="L6" t="n">
-        <v>2.53</v>
+        <v>-0.65</v>
       </c>
       <c r="M6" t="n">
-        <v>7.65</v>
+        <v>7.71</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.65</v>
+        <v>0.78</v>
       </c>
       <c r="P6" t="n">
-        <v>7.65</v>
+        <v>7.71</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.65</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.04</v>
+        <v>5.98</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="F7" t="n">
-        <v>0.67</v>
+        <v>-0.99</v>
       </c>
       <c r="G7" t="n">
-        <v>5.98</v>
+        <v>6.07</v>
       </c>
       <c r="H7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="K7" t="n">
         <v>-0.06</v>
       </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
         <v>-0.99</v>
       </c>
-      <c r="J7" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1.51</v>
-      </c>
       <c r="M7" t="n">
-        <v>6.01</v>
+        <v>6.09</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.06</v>
+        <v>0.08</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.99</v>
+        <v>1.33</v>
       </c>
       <c r="P7" t="n">
-        <v>6.01</v>
+        <v>6.09</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.06</v>
+        <v>0.08</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.99</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="F8" t="n">
+        <v>-1.55</v>
+      </c>
+      <c r="G8" t="n">
         <v>9.68</v>
       </c>
-      <c r="E8" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="G8" t="n">
-        <v>9.529999999999999</v>
-      </c>
       <c r="H8" t="n">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.55</v>
+        <v>1.57</v>
       </c>
       <c r="J8" t="n">
-        <v>9.68</v>
+        <v>9.69</v>
       </c>
       <c r="K8" t="n">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="L8" t="n">
-        <v>1.57</v>
+        <v>0.1</v>
       </c>
       <c r="M8" t="n">
-        <v>9.69</v>
+        <v>9.82</v>
       </c>
       <c r="N8" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1</v>
+        <v>1.34</v>
       </c>
       <c r="P8" t="n">
-        <v>9.69</v>
+        <v>9.82</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="R8" t="n">
-        <v>0.1</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.279999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="E9" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="F9" t="n">
-        <v>0.85</v>
+        <v>-1.09</v>
       </c>
       <c r="G9" t="n">
-        <v>8.19</v>
+        <v>8.24</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.09</v>
+        <v>0.05</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.09</v>
+        <v>0.61</v>
       </c>
       <c r="J9" t="n">
         <v>8.24</v>
       </c>
       <c r="K9" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>8.24</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="P9" t="n">
-        <v>8.24</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51.2</v>
+        <v>50.5</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.05</v>
+        <v>-0.7</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1</v>
+        <v>-1.37</v>
       </c>
       <c r="G10" t="n">
-        <v>50.5</v>
+        <v>51.1</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.7</v>
+        <v>0.6</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.37</v>
+        <v>1.19</v>
       </c>
       <c r="J10" t="n">
         <v>51.1</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="P10" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.49</v>
+        <v>4.43</v>
       </c>
       <c r="E11" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9</v>
+        <v>-1.34</v>
       </c>
       <c r="G11" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.34</v>
+        <v>1.58</v>
       </c>
       <c r="J11" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="K11" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="L11" t="n">
-        <v>1.58</v>
+        <v>-2</v>
       </c>
       <c r="M11" t="n">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.09</v>
+        <v>0.01</v>
       </c>
       <c r="O11" t="n">
-        <v>-2</v>
+        <v>0.23</v>
       </c>
       <c r="P11" t="n">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.09</v>
+        <v>0.01</v>
       </c>
       <c r="R11" t="n">
-        <v>-2</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.609999999999999</v>
+        <v>9.41</v>
       </c>
       <c r="E12" t="n">
-        <v>0.26</v>
+        <v>-0.2</v>
       </c>
       <c r="F12" t="n">
-        <v>2.78</v>
+        <v>-2.08</v>
       </c>
       <c r="G12" t="n">
-        <v>9.41</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.2</v>
+        <v>0.29</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.08</v>
+        <v>3.08</v>
       </c>
       <c r="J12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>0.29</v>
+        <v>0.01</v>
       </c>
       <c r="L12" t="n">
-        <v>3.08</v>
+        <v>0.1</v>
       </c>
       <c r="M12" t="n">
-        <v>9.710000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="N12" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="O12" t="n">
-        <v>0.1</v>
+        <v>-0.51</v>
       </c>
       <c r="P12" t="n">
-        <v>9.710000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23.84</v>
+        <v>23.4</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5</v>
+        <v>-0.44</v>
       </c>
       <c r="F13" t="n">
-        <v>2.14</v>
+        <v>-1.85</v>
       </c>
       <c r="G13" t="n">
-        <v>23.4</v>
+        <v>23.68</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.44</v>
+        <v>0.28</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.85</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
-        <v>23.68</v>
+        <v>23.7</v>
       </c>
       <c r="K13" t="n">
-        <v>0.28</v>
+        <v>0.02</v>
       </c>
       <c r="L13" t="n">
-        <v>1.2</v>
+        <v>0.08</v>
       </c>
       <c r="M13" t="n">
-        <v>23.7</v>
+        <v>23.96</v>
       </c>
       <c r="N13" t="n">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="O13" t="n">
-        <v>0.08</v>
+        <v>1.1</v>
       </c>
       <c r="P13" t="n">
-        <v>23.7</v>
+        <v>23.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="R13" t="n">
-        <v>0.08</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.9</v>
+        <v>1.88</v>
       </c>
       <c r="E14" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H14" t="n">
         <v>0.01</v>
       </c>
-      <c r="F14" t="n">
+      <c r="I14" t="n">
         <v>0.53</v>
       </c>
-      <c r="G14" t="n">
+      <c r="J14" t="n">
         <v>1.88</v>
       </c>
-      <c r="H14" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I14" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.89</v>
-      </c>
       <c r="K14" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="L14" t="n">
-        <v>0.53</v>
+        <v>-0.53</v>
       </c>
       <c r="M14" t="n">
         <v>1.88</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>1.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.18</v>
+        <v>5.16</v>
       </c>
       <c r="E15" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F15" t="n">
-        <v>0.19</v>
+        <v>-0.39</v>
       </c>
       <c r="G15" t="n">
-        <v>5.16</v>
+        <v>5.36</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.02</v>
+        <v>0.2</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.39</v>
+        <v>3.88</v>
       </c>
       <c r="J15" t="n">
-        <v>5.36</v>
+        <v>5.3</v>
       </c>
       <c r="K15" t="n">
-        <v>0.2</v>
+        <v>-0.06</v>
       </c>
       <c r="L15" t="n">
-        <v>3.88</v>
+        <v>-1.12</v>
       </c>
       <c r="M15" t="n">
-        <v>5.3</v>
+        <v>5.33</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.12</v>
+        <v>0.57</v>
       </c>
       <c r="P15" t="n">
-        <v>5.3</v>
+        <v>5.33</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.12</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="16">
@@ -1386,46 +1386,46 @@
         <v>4.3</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.92</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
       <c r="J16" t="n">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.16</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>4.29</v>
+        <v>4.36</v>
       </c>
       <c r="N16" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.63</v>
       </c>
       <c r="P16" t="n">
-        <v>4.29</v>
+        <v>4.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H17" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I17" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="J17" t="n">
         <v>3.16</v>
       </c>
-      <c r="E17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K17" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.25</v>
+        <v>0.32</v>
       </c>
       <c r="M17" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="N17" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="O17" t="n">
-        <v>0.32</v>
+        <v>1.9</v>
       </c>
       <c r="P17" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="R17" t="n">
-        <v>0.32</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="E18" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K18" t="n">
         <v>0.01</v>
       </c>
-      <c r="F18" t="n">
+      <c r="L18" t="n">
         <v>0.34</v>
       </c>
-      <c r="G18" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I18" t="n">
-        <v>-1.36</v>
-      </c>
-      <c r="J18" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="L18" t="n">
-        <v>2.41</v>
-      </c>
       <c r="M18" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
         <v>0.01</v>
       </c>
       <c r="O18" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="P18" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="Q18" t="n">
         <v>0.01</v>
       </c>
       <c r="R18" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>53.25</v>
+        <v>52.7</v>
       </c>
       <c r="E19" t="n">
+        <v>-0.55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-1.03</v>
+      </c>
+      <c r="G19" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="J19" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M19" t="n">
+        <v>52.75</v>
+      </c>
+      <c r="N19" t="n">
         <v>-0.15</v>
       </c>
-      <c r="F19" t="n">
+      <c r="O19" t="n">
         <v>-0.28</v>
       </c>
-      <c r="G19" t="n">
-        <v>52.7</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-0.55</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="J19" t="n">
-        <v>52.6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="M19" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.57</v>
-      </c>
       <c r="P19" t="n">
-        <v>52.9</v>
+        <v>52.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.3</v>
+        <v>-0.15</v>
       </c>
       <c r="R19" t="n">
-        <v>0.57</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>29.44</v>
+        <v>28.58</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.26</v>
+        <v>-0.86</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.88</v>
+        <v>-2.92</v>
       </c>
       <c r="G20" t="n">
-        <v>28.58</v>
+        <v>28.08</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.86</v>
+        <v>-0.5</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.92</v>
+        <v>-1.75</v>
       </c>
       <c r="J20" t="n">
-        <v>28.08</v>
+        <v>28.8</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5</v>
+        <v>0.72</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.75</v>
+        <v>2.56</v>
       </c>
       <c r="M20" t="n">
-        <v>28.8</v>
+        <v>28.12</v>
       </c>
       <c r="N20" t="n">
-        <v>0.72</v>
+        <v>-0.68</v>
       </c>
       <c r="O20" t="n">
-        <v>2.56</v>
+        <v>-2.36</v>
       </c>
       <c r="P20" t="n">
-        <v>28.8</v>
+        <v>28.12</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.72</v>
+        <v>-0.68</v>
       </c>
       <c r="R20" t="n">
-        <v>2.56</v>
+        <v>-2.36</v>
       </c>
     </row>
     <row r="21">
@@ -1693,31 +1693,31 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="G21" t="n">
-        <v>4.39</v>
+        <v>4.49</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.02</v>
+        <v>0.1</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.45</v>
+        <v>2.28</v>
       </c>
       <c r="J21" t="n">
         <v>4.49</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
         <v>4.49</v>
@@ -1755,34 +1755,34 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>78.90000000000001</v>
+        <v>78.45</v>
       </c>
       <c r="E22" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="G22" t="n">
+        <v>79.25</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="J22" t="n">
+        <v>79.34999999999999</v>
+      </c>
+      <c r="K22" t="n">
         <v>0.1</v>
       </c>
-      <c r="F22" t="n">
+      <c r="L22" t="n">
         <v>0.13</v>
       </c>
-      <c r="G22" t="n">
-        <v>78.45</v>
-      </c>
-      <c r="H22" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="J22" t="n">
-        <v>79.25</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="L22" t="n">
-        <v>1.02</v>
-      </c>
       <c r="M22" t="n">
-        <v>79.34999999999999</v>
+        <v>79.45</v>
       </c>
       <c r="N22" t="n">
         <v>0.1</v>
@@ -1791,7 +1791,7 @@
         <v>0.13</v>
       </c>
       <c r="P22" t="n">
-        <v>79.34999999999999</v>
+        <v>79.45</v>
       </c>
       <c r="Q22" t="n">
         <v>0.1</v>
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22.7</v>
+        <v>22.44</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1</v>
+        <v>-0.26</v>
       </c>
       <c r="F23" t="n">
-        <v>0.44</v>
+        <v>-1.15</v>
       </c>
       <c r="G23" t="n">
-        <v>22.44</v>
+        <v>22.08</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.26</v>
+        <v>-0.36</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.15</v>
+        <v>-1.6</v>
       </c>
       <c r="J23" t="n">
-        <v>22.08</v>
+        <v>21.72</v>
       </c>
       <c r="K23" t="n">
         <v>-0.36</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.6</v>
+        <v>-1.63</v>
       </c>
       <c r="M23" t="n">
-        <v>21.72</v>
+        <v>21.86</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.36</v>
+        <v>0.14</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.63</v>
+        <v>0.64</v>
       </c>
       <c r="P23" t="n">
-        <v>21.72</v>
+        <v>21.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.36</v>
+        <v>0.14</v>
       </c>
       <c r="R23" t="n">
-        <v>-1.63</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.09</v>
+        <v>15.08</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.16</v>
+        <v>-0.01</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>15.08</v>
+        <v>14.41</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.01</v>
+        <v>-0.67</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-4.44</v>
       </c>
       <c r="J24" t="n">
-        <v>14.41</v>
+        <v>14.58</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.67</v>
+        <v>0.17</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.44</v>
+        <v>1.18</v>
       </c>
       <c r="M24" t="n">
-        <v>14.58</v>
+        <v>14.38</v>
       </c>
       <c r="N24" t="n">
-        <v>0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="O24" t="n">
-        <v>1.18</v>
+        <v>-1.37</v>
       </c>
       <c r="P24" t="n">
-        <v>14.58</v>
+        <v>14.38</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.18</v>
+        <v>-1.37</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.58</v>
+        <v>25.9</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4</v>
+        <v>-0.68</v>
       </c>
       <c r="F25" t="n">
-        <v>1.53</v>
+        <v>-2.56</v>
       </c>
       <c r="G25" t="n">
-        <v>25.9</v>
+        <v>25.86</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.68</v>
+        <v>-0.04</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.56</v>
+        <v>-0.15</v>
       </c>
       <c r="J25" t="n">
-        <v>25.86</v>
+        <v>25.2</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.04</v>
+        <v>-0.66</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.15</v>
+        <v>-2.55</v>
       </c>
       <c r="M25" t="n">
-        <v>25.2</v>
+        <v>25.24</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.66</v>
+        <v>0.04</v>
       </c>
       <c r="O25" t="n">
-        <v>-2.55</v>
+        <v>0.16</v>
       </c>
       <c r="P25" t="n">
-        <v>25.2</v>
+        <v>25.24</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.66</v>
+        <v>0.04</v>
       </c>
       <c r="R25" t="n">
-        <v>-2.55</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>39.32</v>
+        <v>38.16</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.84</v>
+        <v>-1.16</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.09</v>
+        <v>-2.95</v>
       </c>
       <c r="G26" t="n">
-        <v>38.16</v>
+        <v>35.04</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.16</v>
+        <v>-3.12</v>
       </c>
       <c r="I26" t="n">
-        <v>-2.95</v>
+        <v>-8.18</v>
       </c>
       <c r="J26" t="n">
-        <v>35.04</v>
+        <v>37.36</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.12</v>
+        <v>2.32</v>
       </c>
       <c r="L26" t="n">
-        <v>-8.18</v>
+        <v>6.62</v>
       </c>
       <c r="M26" t="n">
-        <v>37.36</v>
+        <v>37.38</v>
       </c>
       <c r="N26" t="n">
-        <v>2.32</v>
+        <v>0.02</v>
       </c>
       <c r="O26" t="n">
-        <v>6.62</v>
+        <v>0.05</v>
       </c>
       <c r="P26" t="n">
-        <v>37.36</v>
+        <v>37.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.32</v>
+        <v>0.02</v>
       </c>
       <c r="R26" t="n">
-        <v>6.62</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>438.4</v>
+        <v>436.6</v>
       </c>
       <c r="E27" t="n">
-        <v>-2.6</v>
+        <v>-1.8</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.59</v>
+        <v>-0.41</v>
       </c>
       <c r="G27" t="n">
-        <v>436.6</v>
+        <v>439.8</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.8</v>
+        <v>3.2</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.41</v>
+        <v>0.73</v>
       </c>
       <c r="J27" t="n">
-        <v>439.8</v>
+        <v>432</v>
       </c>
       <c r="K27" t="n">
-        <v>3.2</v>
+        <v>-7.8</v>
       </c>
       <c r="L27" t="n">
-        <v>0.73</v>
+        <v>-1.77</v>
       </c>
       <c r="M27" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="N27" t="n">
-        <v>-7.8</v>
+        <v>-1</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.77</v>
+        <v>-0.23</v>
       </c>
       <c r="P27" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="Q27" t="n">
-        <v>-7.8</v>
+        <v>-1</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.77</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>110</v>
+        <v>108.4</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2</v>
+        <v>-1.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0.18</v>
+        <v>-1.45</v>
       </c>
       <c r="G28" t="n">
-        <v>108.4</v>
+        <v>107.7</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.6</v>
+        <v>-0.7</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.45</v>
+        <v>-0.65</v>
       </c>
       <c r="J28" t="n">
-        <v>107.7</v>
+        <v>106.2</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.7</v>
+        <v>-1.5</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.65</v>
+        <v>-1.39</v>
       </c>
       <c r="M28" t="n">
-        <v>106.2</v>
+        <v>106.6</v>
       </c>
       <c r="N28" t="n">
-        <v>-1.5</v>
+        <v>0.4</v>
       </c>
       <c r="O28" t="n">
-        <v>-1.39</v>
+        <v>0.38</v>
       </c>
       <c r="P28" t="n">
-        <v>106.2</v>
+        <v>106.6</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1.5</v>
+        <v>0.4</v>
       </c>
       <c r="R28" t="n">
-        <v>-1.39</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>105.6</v>
+        <v>103.7</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5</v>
+        <v>-1.9</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.47</v>
+        <v>-1.8</v>
       </c>
       <c r="G29" t="n">
-        <v>103.7</v>
+        <v>104.5</v>
       </c>
       <c r="H29" t="n">
-        <v>-1.9</v>
+        <v>0.8</v>
       </c>
       <c r="I29" t="n">
-        <v>-1.8</v>
+        <v>0.77</v>
       </c>
       <c r="J29" t="n">
-        <v>104.5</v>
+        <v>103.1</v>
       </c>
       <c r="K29" t="n">
-        <v>0.8</v>
+        <v>-1.4</v>
       </c>
       <c r="L29" t="n">
-        <v>0.77</v>
+        <v>-1.34</v>
       </c>
       <c r="M29" t="n">
-        <v>103.1</v>
+        <v>104.3</v>
       </c>
       <c r="N29" t="n">
-        <v>-1.4</v>
+        <v>1.2</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.34</v>
+        <v>1.16</v>
       </c>
       <c r="P29" t="n">
-        <v>103.1</v>
+        <v>104.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1.4</v>
+        <v>1.2</v>
       </c>
       <c r="R29" t="n">
-        <v>-1.34</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>72.25</v>
+        <v>71.65000000000001</v>
       </c>
       <c r="E30" t="n">
         <v>-0.6</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.82</v>
+        <v>-0.83</v>
       </c>
       <c r="G30" t="n">
-        <v>71.65000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.6</v>
+        <v>0.25</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.83</v>
+        <v>0.35</v>
       </c>
       <c r="J30" t="n">
-        <v>71.90000000000001</v>
+        <v>70.45</v>
       </c>
       <c r="K30" t="n">
-        <v>0.25</v>
+        <v>-1.45</v>
       </c>
       <c r="L30" t="n">
-        <v>0.35</v>
+        <v>-2.02</v>
       </c>
       <c r="M30" t="n">
-        <v>70.45</v>
+        <v>71.7</v>
       </c>
       <c r="N30" t="n">
-        <v>-1.45</v>
+        <v>1.25</v>
       </c>
       <c r="O30" t="n">
-        <v>-2.02</v>
+        <v>1.77</v>
       </c>
       <c r="P30" t="n">
-        <v>70.45</v>
+        <v>71.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>-1.45</v>
+        <v>1.25</v>
       </c>
       <c r="R30" t="n">
-        <v>-2.02</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>86.3</v>
+        <v>85.3</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.25</v>
+        <v>-1</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.54</v>
+        <v>-1.16</v>
       </c>
       <c r="G31" t="n">
-        <v>85.3</v>
+        <v>85.55</v>
       </c>
       <c r="H31" t="n">
-        <v>-1</v>
+        <v>0.25</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.16</v>
+        <v>0.29</v>
       </c>
       <c r="J31" t="n">
-        <v>85.55</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.25</v>
+        <v>-0.65</v>
       </c>
       <c r="L31" t="n">
-        <v>0.29</v>
+        <v>-0.76</v>
       </c>
       <c r="M31" t="n">
-        <v>84.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.65</v>
+        <v>0.9</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.76</v>
+        <v>1.06</v>
       </c>
       <c r="P31" t="n">
-        <v>84.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.65</v>
+        <v>0.9</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.76</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>63.8</v>
+        <v>63.35</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>-0.45</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>-0.71</v>
       </c>
       <c r="G32" t="n">
-        <v>63.35</v>
+        <v>61.05</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.45</v>
+        <v>-2.3</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.71</v>
+        <v>-3.63</v>
       </c>
       <c r="J32" t="n">
         <v>61.05</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.3</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>-3.63</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>61.05</v>
+        <v>60.65</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>-0.66</v>
       </c>
       <c r="P32" t="n">
-        <v>61.05</v>
+        <v>60.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>79.5</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.85</v>
+        <v>-1.4</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.06</v>
+        <v>-1.76</v>
       </c>
       <c r="G33" t="n">
-        <v>78.09999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.4</v>
+        <v>-0.4</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.76</v>
+        <v>-0.51</v>
       </c>
       <c r="J33" t="n">
-        <v>77.7</v>
+        <v>75.75</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.4</v>
+        <v>-1.95</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.51</v>
+        <v>-2.51</v>
       </c>
       <c r="M33" t="n">
-        <v>75.75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>-1.95</v>
+        <v>-0.15</v>
       </c>
       <c r="O33" t="n">
-        <v>-2.51</v>
+        <v>-0.2</v>
       </c>
       <c r="P33" t="n">
-        <v>75.75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>-1.95</v>
+        <v>-0.15</v>
       </c>
       <c r="R33" t="n">
-        <v>-2.51</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>30.5</v>
+        <v>30.02</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.28</v>
+        <v>-0.48</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.91</v>
+        <v>-1.57</v>
       </c>
       <c r="G34" t="n">
-        <v>30.02</v>
+        <v>30.7</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.48</v>
+        <v>0.68</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.57</v>
+        <v>2.27</v>
       </c>
       <c r="J34" t="n">
-        <v>30.7</v>
+        <v>30.24</v>
       </c>
       <c r="K34" t="n">
-        <v>0.68</v>
+        <v>-0.46</v>
       </c>
       <c r="L34" t="n">
-        <v>2.27</v>
+        <v>-1.5</v>
       </c>
       <c r="M34" t="n">
-        <v>30.24</v>
+        <v>30.94</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.46</v>
+        <v>0.7</v>
       </c>
       <c r="O34" t="n">
-        <v>-1.5</v>
+        <v>2.31</v>
       </c>
       <c r="P34" t="n">
-        <v>30.24</v>
+        <v>30.94</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.46</v>
+        <v>0.7</v>
       </c>
       <c r="R34" t="n">
-        <v>-1.5</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.27</v>
+        <v>4.24</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.23</v>
+        <v>-0.7</v>
       </c>
       <c r="G35" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.19</v>
       </c>
       <c r="M35" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.19</v>
       </c>
       <c r="P35" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.220000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.01</v>
+        <v>-0.13</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.11</v>
+        <v>-1.41</v>
       </c>
       <c r="G36" t="n">
         <v>9.09</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.41</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>9.09</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>-1.32</v>
       </c>
       <c r="M36" t="n">
-        <v>9.09</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>-1.32</v>
       </c>
       <c r="P36" t="n">
-        <v>9.09</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>393.4</v>
+        <v>388.4</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.4</v>
+        <v>-5</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.61</v>
+        <v>-1.27</v>
       </c>
       <c r="G37" t="n">
-        <v>388.4</v>
+        <v>388.6</v>
       </c>
       <c r="H37" t="n">
-        <v>-5</v>
+        <v>0.2</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.27</v>
+        <v>0.05</v>
       </c>
       <c r="J37" t="n">
-        <v>388.6</v>
+        <v>386.8</v>
       </c>
       <c r="K37" t="n">
-        <v>0.2</v>
+        <v>-1.8</v>
       </c>
       <c r="L37" t="n">
-        <v>0.05</v>
+        <v>-0.46</v>
       </c>
       <c r="M37" t="n">
-        <v>386.8</v>
+        <v>387.8</v>
       </c>
       <c r="N37" t="n">
-        <v>-1.8</v>
+        <v>1</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.46</v>
+        <v>0.26</v>
       </c>
       <c r="P37" t="n">
-        <v>386.8</v>
+        <v>387.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>-1.8</v>
+        <v>1</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.46</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.04</v>
+        <v>11.91</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.03</v>
+        <v>-0.13</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.25</v>
+        <v>-1.08</v>
       </c>
       <c r="G38" t="n">
-        <v>11.91</v>
+        <v>11.93</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.13</v>
+        <v>0.02</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.08</v>
+        <v>0.17</v>
       </c>
       <c r="J38" t="n">
-        <v>11.93</v>
+        <v>11.79</v>
       </c>
       <c r="K38" t="n">
-        <v>0.02</v>
+        <v>-0.14</v>
       </c>
       <c r="L38" t="n">
-        <v>0.17</v>
+        <v>-1.17</v>
       </c>
       <c r="M38" t="n">
-        <v>11.79</v>
+        <v>11.85</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.14</v>
+        <v>0.06</v>
       </c>
       <c r="O38" t="n">
-        <v>-1.17</v>
+        <v>0.51</v>
       </c>
       <c r="P38" t="n">
-        <v>11.79</v>
+        <v>11.85</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.14</v>
+        <v>0.06</v>
       </c>
       <c r="R38" t="n">
-        <v>-1.17</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>492.8</v>
+        <v>489.4</v>
       </c>
       <c r="E39" t="n">
-        <v>-18.7</v>
+        <v>-3.4</v>
       </c>
       <c r="F39" t="n">
-        <v>-3.66</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>489.4</v>
+        <v>484.6</v>
       </c>
       <c r="H39" t="n">
-        <v>-3.4</v>
+        <v>-4.8</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.98</v>
       </c>
       <c r="J39" t="n">
-        <v>484.6</v>
+        <v>482.2</v>
       </c>
       <c r="K39" t="n">
-        <v>-4.8</v>
+        <v>-2.4</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.98</v>
+        <v>-0.5</v>
       </c>
       <c r="M39" t="n">
-        <v>482.2</v>
+        <v>484.2</v>
       </c>
       <c r="N39" t="n">
-        <v>-2.4</v>
+        <v>2</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.5</v>
+        <v>0.41</v>
       </c>
       <c r="P39" t="n">
-        <v>482.2</v>
+        <v>484.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>-2.4</v>
+        <v>2</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.5</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>40.22</v>
+        <v>39.46</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.18</v>
+        <v>-0.76</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.45</v>
+        <v>-1.89</v>
       </c>
       <c r="G40" t="n">
-        <v>39.46</v>
+        <v>39.1</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.76</v>
+        <v>-0.36</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.89</v>
+        <v>-0.91</v>
       </c>
       <c r="J40" t="n">
-        <v>39.1</v>
+        <v>37.5</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.36</v>
+        <v>-1.6</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.91</v>
+        <v>-4.09</v>
       </c>
       <c r="M40" t="n">
-        <v>37.5</v>
+        <v>37.86</v>
       </c>
       <c r="N40" t="n">
-        <v>-1.6</v>
+        <v>0.36</v>
       </c>
       <c r="O40" t="n">
-        <v>-4.09</v>
+        <v>0.96</v>
       </c>
       <c r="P40" t="n">
-        <v>37.5</v>
+        <v>37.86</v>
       </c>
       <c r="Q40" t="n">
-        <v>-1.6</v>
+        <v>0.36</v>
       </c>
       <c r="R40" t="n">
-        <v>-4.09</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.59</v>
+        <v>32.01</v>
       </c>
       <c r="E41" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G41" t="n">
+        <v>32.22</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J41" t="n">
+        <v>32.16</v>
+      </c>
+      <c r="K41" t="n">
         <v>-0.06</v>
       </c>
-      <c r="F41" t="n">
+      <c r="L41" t="n">
         <v>-0.19</v>
       </c>
-      <c r="G41" t="n">
-        <v>32.01</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="I41" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="J41" t="n">
-        <v>32.22</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0.66</v>
-      </c>
       <c r="M41" t="n">
-        <v>32.16</v>
+        <v>31.99</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.06</v>
+        <v>-0.17</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.19</v>
+        <v>-0.53</v>
       </c>
       <c r="P41" t="n">
-        <v>32.16</v>
+        <v>31.99</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.06</v>
+        <v>-0.17</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.19</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>77.48</v>
+        <v>78</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.21</v>
+        <v>0.52</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.27</v>
+        <v>0.67</v>
       </c>
       <c r="G42" t="n">
-        <v>78</v>
+        <v>78.11</v>
       </c>
       <c r="H42" t="n">
-        <v>0.52</v>
+        <v>0.11</v>
       </c>
       <c r="I42" t="n">
-        <v>0.67</v>
+        <v>0.14</v>
       </c>
       <c r="J42" t="n">
-        <v>78.11</v>
+        <v>78.38</v>
       </c>
       <c r="K42" t="n">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="L42" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
       <c r="M42" t="n">
-        <v>78.38</v>
+        <v>77.5</v>
       </c>
       <c r="N42" t="n">
-        <v>0.27</v>
+        <v>-0.88</v>
       </c>
       <c r="O42" t="n">
-        <v>0.35</v>
+        <v>-1.12</v>
       </c>
       <c r="P42" t="n">
-        <v>78.38</v>
+        <v>77.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.27</v>
+        <v>-0.88</v>
       </c>
       <c r="R42" t="n">
-        <v>0.35</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>42.5</v>
+        <v>42.57</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.34</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.79</v>
+        <v>0.16</v>
       </c>
       <c r="G43" t="n">
-        <v>42.57</v>
+        <v>43.29</v>
       </c>
       <c r="H43" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="J43" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L43" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="I43" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="J43" t="n">
-        <v>43.29</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="L43" t="n">
-        <v>1.69</v>
-      </c>
       <c r="M43" t="n">
-        <v>43.32</v>
+        <v>42.84</v>
       </c>
       <c r="N43" t="n">
-        <v>0.03</v>
+        <v>-0.48</v>
       </c>
       <c r="O43" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.11</v>
       </c>
       <c r="P43" t="n">
-        <v>43.32</v>
+        <v>42.84</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.03</v>
+        <v>-0.48</v>
       </c>
       <c r="R43" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.11</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.85</v>
+        <v>5.87</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.85</v>
+        <v>0.34</v>
       </c>
       <c r="G44" t="n">
-        <v>5.87</v>
+        <v>5.84</v>
       </c>
       <c r="H44" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="I44" t="n">
-        <v>0.34</v>
+        <v>-0.51</v>
       </c>
       <c r="J44" t="n">
-        <v>5.84</v>
+        <v>5.8</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.51</v>
+        <v>-0.68</v>
       </c>
       <c r="M44" t="n">
-        <v>5.8</v>
+        <v>5.79</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.68</v>
+        <v>-0.17</v>
       </c>
       <c r="P44" t="n">
-        <v>5.8</v>
+        <v>5.79</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.68</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="45">
@@ -3190,40 +3190,40 @@
         <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>-1.43</v>
       </c>
       <c r="J45" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="K45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="N45" t="n">
         <v>-0.03</v>
       </c>
-      <c r="L45" t="n">
-        <v>-1.43</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0.01</v>
-      </c>
       <c r="O45" t="n">
-        <v>0.48</v>
+        <v>-1.44</v>
       </c>
       <c r="P45" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="R45" t="n">
-        <v>0.48</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="E46" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="K46" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F46" t="n">
+      <c r="L46" t="n">
         <v>-0.26</v>
       </c>
-      <c r="G46" t="n">
+      <c r="M46" t="n">
         <v>3.83</v>
       </c>
-      <c r="H46" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="L46" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.87</v>
-      </c>
       <c r="N46" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="O46" t="n">
-        <v>-0.26</v>
+        <v>-1.03</v>
       </c>
       <c r="P46" t="n">
-        <v>3.87</v>
+        <v>3.83</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.26</v>
+        <v>-1.03</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.86</v>
+        <v>10.87</v>
       </c>
       <c r="E47" t="n">
-        <v>0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F47" t="n">
-        <v>0.46</v>
+        <v>0.09</v>
       </c>
       <c r="G47" t="n">
         <v>10.87</v>
       </c>
       <c r="H47" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>10.87</v>
+        <v>10.85</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="M47" t="n">
-        <v>10.85</v>
+        <v>10.92</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.18</v>
+        <v>0.65</v>
       </c>
       <c r="P47" t="n">
-        <v>10.85</v>
+        <v>10.92</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.18</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="48">
@@ -3376,40 +3376,40 @@
         <v>0</v>
       </c>
       <c r="G48" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="I48" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="J48" t="n">
         <v>0.315</v>
       </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.31</v>
-      </c>
       <c r="K48" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.59</v>
+        <v>1.61</v>
       </c>
       <c r="M48" t="n">
-        <v>0.315</v>
+        <v>0.3</v>
       </c>
       <c r="N48" t="n">
-        <v>0.005</v>
+        <v>-0.015</v>
       </c>
       <c r="O48" t="n">
-        <v>1.61</v>
+        <v>-4.76</v>
       </c>
       <c r="P48" t="n">
-        <v>0.315</v>
+        <v>0.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.005</v>
+        <v>-0.015</v>
       </c>
       <c r="R48" t="n">
-        <v>1.61</v>
+        <v>-4.76</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G49" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="J49" t="n">
+        <v>4.28</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="M49" t="n">
         <v>4.25</v>
       </c>
-      <c r="E49" t="n">
+      <c r="N49" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F49" t="n">
+      <c r="O49" t="n">
         <v>-0.7</v>
       </c>
-      <c r="G49" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="J49" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="M49" t="n">
-        <v>4.28</v>
-      </c>
-      <c r="N49" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="O49" t="n">
-        <v>-0.23</v>
-      </c>
       <c r="P49" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.23</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="E50" t="n">
-        <v>0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="F50" t="n">
-        <v>2.7</v>
+        <v>-1.75</v>
       </c>
       <c r="G50" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="J50" t="n">
         <v>1.12</v>
       </c>
-      <c r="H50" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I50" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.13</v>
-      </c>
       <c r="K50" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="L50" t="n">
-        <v>0.89</v>
+        <v>-0.88</v>
       </c>
       <c r="M50" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="N50" t="n">
         <v>-0.01</v>
       </c>
       <c r="O50" t="n">
-        <v>-0.88</v>
+        <v>-0.89</v>
       </c>
       <c r="P50" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="Q50" t="n">
         <v>-0.01</v>
       </c>
       <c r="R50" t="n">
-        <v>-0.88</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.17</v>
+        <v>5.19</v>
       </c>
       <c r="E51" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5.16</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5.14</v>
+      </c>
+      <c r="K51" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L51" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="M51" t="n">
+        <v>5.13</v>
+      </c>
+      <c r="N51" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F51" t="n">
+      <c r="O51" t="n">
         <v>-0.19</v>
       </c>
-      <c r="G51" t="n">
-        <v>5.19</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="J51" t="n">
-        <v>5.16</v>
-      </c>
-      <c r="K51" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="L51" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="M51" t="n">
-        <v>5.14</v>
-      </c>
-      <c r="N51" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="O51" t="n">
-        <v>-0.39</v>
-      </c>
       <c r="P51" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="R51" t="n">
-        <v>-0.39</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.29</v>
+        <v>11.3</v>
       </c>
       <c r="E52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G52" t="n">
+        <v>11.38</v>
+      </c>
+      <c r="H52" t="n">
         <v>0.08</v>
       </c>
-      <c r="F52" t="n">
+      <c r="I52" t="n">
         <v>0.71</v>
       </c>
-      <c r="G52" t="n">
-        <v>11.3</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I52" t="n">
+      <c r="J52" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="K52" t="n">
         <v>0.09</v>
       </c>
-      <c r="J52" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0.08</v>
-      </c>
       <c r="L52" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="M52" t="n">
-        <v>11.47</v>
+        <v>11.28</v>
       </c>
       <c r="N52" t="n">
-        <v>0.09</v>
+        <v>-0.19</v>
       </c>
       <c r="O52" t="n">
-        <v>0.79</v>
+        <v>-1.66</v>
       </c>
       <c r="P52" t="n">
-        <v>11.47</v>
+        <v>11.28</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.09</v>
+        <v>-0.19</v>
       </c>
       <c r="R52" t="n">
-        <v>0.79</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.220000000000001</v>
+        <v>8.26</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.2</v>
+        <v>0.04</v>
       </c>
       <c r="F53" t="n">
-        <v>-2.38</v>
+        <v>0.49</v>
       </c>
       <c r="G53" t="n">
-        <v>8.26</v>
+        <v>7.59</v>
       </c>
       <c r="H53" t="n">
-        <v>0.04</v>
+        <v>-0.67</v>
       </c>
       <c r="I53" t="n">
-        <v>0.49</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="J53" t="n">
-        <v>7.59</v>
+        <v>7.43</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.67</v>
+        <v>-0.16</v>
       </c>
       <c r="L53" t="n">
-        <v>-8.109999999999999</v>
+        <v>-2.11</v>
       </c>
       <c r="M53" t="n">
-        <v>7.43</v>
+        <v>7.39</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.16</v>
+        <v>-0.04</v>
       </c>
       <c r="O53" t="n">
-        <v>-2.11</v>
+        <v>-0.54</v>
       </c>
       <c r="P53" t="n">
-        <v>7.43</v>
+        <v>7.39</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.16</v>
+        <v>-0.04</v>
       </c>
       <c r="R53" t="n">
-        <v>-2.11</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="54">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="D54" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F54" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="G54" t="n">
         <v>0.435</v>
       </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" t="n">
-        <v>0.44</v>
-      </c>
       <c r="H54" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="I54" t="n">
-        <v>1.15</v>
+        <v>-1.14</v>
       </c>
       <c r="J54" t="n">
         <v>0.435</v>
       </c>
       <c r="K54" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="N54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L54" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>-1.15</v>
       </c>
       <c r="P54" t="n">
-        <v>0.435</v>
+        <v>0.43</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="55">
@@ -3801,49 +3801,49 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.62</v>
+        <v>0.615</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="G55" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I55" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J55" t="n">
         <v>0.615</v>
       </c>
-      <c r="H55" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="I55" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0.625</v>
-      </c>
       <c r="K55" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="L55" t="n">
-        <v>1.63</v>
+        <v>-1.6</v>
       </c>
       <c r="M55" t="n">
         <v>0.615</v>
       </c>
       <c r="N55" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
         <v>0.615</v>
       </c>
       <c r="Q55" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3866,10 +3866,10 @@
         <v>0.39</v>
       </c>
       <c r="E56" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="G56" t="n">
         <v>0.39</v>
@@ -3881,31 +3881,31 @@
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>0.39</v>
+        <v>0.375</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>-3.85</v>
       </c>
       <c r="M56" t="n">
         <v>0.375</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>-3.85</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
         <v>0.375</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>-3.85</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.65</v>
+        <v>3.68</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.54</v>
+        <v>0.82</v>
       </c>
       <c r="G57" t="n">
-        <v>3.68</v>
+        <v>3.61</v>
       </c>
       <c r="H57" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="K57" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="L57" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="N57" t="n">
         <v>0.03</v>
       </c>
-      <c r="I57" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="J57" t="n">
+      <c r="O57" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="P57" t="n">
         <v>3.61</v>
       </c>
-      <c r="K57" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="L57" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="N57" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="O57" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="P57" t="n">
-        <v>3.58</v>
-      </c>
       <c r="Q57" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="R57" t="n">
-        <v>-0.83</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="58">
@@ -3990,10 +3990,10 @@
         <v>0.079</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>0.079</v>
@@ -4005,31 +4005,31 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M58" t="n">
         <v>0.081</v>
       </c>
       <c r="N58" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
         <v>0.081</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22.42</v>
+        <v>22.4</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.32</v>
+        <v>-0.02</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.41</v>
+        <v>-0.09</v>
       </c>
       <c r="G59" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J59" t="n">
         <v>22.4</v>
       </c>
-      <c r="H59" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I59" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="J59" t="n">
-        <v>22.47</v>
-      </c>
       <c r="K59" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>0.31</v>
+        <v>-0.31</v>
       </c>
       <c r="M59" t="n">
-        <v>22.4</v>
+        <v>22.61</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.31</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P59" t="n">
-        <v>22.4</v>
+        <v>22.61</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="R59" t="n">
-        <v>-0.31</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="E60" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="F60" t="n">
-        <v>0.96</v>
+        <v>0.63</v>
       </c>
       <c r="G60" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="H60" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I60" t="n">
-        <v>0.63</v>
+        <v>-0.31</v>
       </c>
       <c r="J60" t="n">
         <v>3.18</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.31</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>-1.26</v>
       </c>
       <c r="P60" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>-1.26</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="E61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F61" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-2.3</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="N61" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F61" t="n">
+      <c r="O61" t="n">
         <v>-0.58</v>
       </c>
-      <c r="G61" t="n">
-        <v>0.87</v>
-      </c>
-      <c r="H61" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I61" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="J61" t="n">
+      <c r="P61" t="n">
         <v>0.85</v>
       </c>
-      <c r="K61" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L61" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="M61" t="n">
-        <v>0.855</v>
-      </c>
-      <c r="N61" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="O61" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="P61" t="n">
-        <v>0.855</v>
-      </c>
       <c r="Q61" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="R61" t="n">
-        <v>0.59</v>
+        <v>-0.58</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-25 Close</t>
+          <t>2026-09-28 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-09-25 Change</t>
+          <t>2026-09-28 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-25 Change %</t>
+          <t>2026-09-28 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-09-28 Close</t>
+          <t>2026-09-29 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-09-28 Change</t>
+          <t>2026-09-29 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-09-28 Change %</t>
+          <t>2026-09-29 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-09-29 Close</t>
+          <t>2026-09-30 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-09-29 Change</t>
+          <t>2026-09-30 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-09-29 Change %</t>
+          <t>2026-09-30 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-09-30 Close</t>
+          <t>2026-10-01 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-09-30 Change</t>
+          <t>2026-10-01 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-09-30 Change %</t>
+          <t>2026-10-01 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-10-01 Close</t>
+          <t>2026-10-02 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-10-01 Change</t>
+          <t>2026-10-02 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-10-01 Change %</t>
+          <t>2026-10-02 Change %</t>
         </is>
       </c>
     </row>
@@ -577,31 +577,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>157.6</v>
+        <v>158.9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="F3" t="n">
-        <v>0.45</v>
+        <v>0.82</v>
       </c>
       <c r="G3" t="n">
-        <v>158.9</v>
+        <v>159</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3</v>
+        <v>0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.82</v>
+        <v>0.06</v>
       </c>
       <c r="J3" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06</v>
+        <v>-0.63</v>
       </c>
       <c r="M3" t="n">
         <v>158</v>
@@ -639,31 +639,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>238</v>
+        <v>242.6</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>4.6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.85</v>
+        <v>1.93</v>
       </c>
       <c r="G4" t="n">
-        <v>242.6</v>
+        <v>242.8</v>
       </c>
       <c r="H4" t="n">
-        <v>4.6</v>
+        <v>0.2</v>
       </c>
       <c r="I4" t="n">
-        <v>1.93</v>
+        <v>0.08</v>
       </c>
       <c r="J4" t="n">
-        <v>242.8</v>
+        <v>244.4</v>
       </c>
       <c r="K4" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.08</v>
+        <v>0.66</v>
       </c>
       <c r="M4" t="n">
         <v>244.4</v>
@@ -701,16 +701,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.51</v>
+        <v>6.55</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1</v>
+        <v>0.04</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.51</v>
+        <v>0.61</v>
       </c>
       <c r="G5" t="n">
-        <v>6.55</v>
+        <v>6.59</v>
       </c>
       <c r="H5" t="n">
         <v>0.04</v>
@@ -719,7 +719,7 @@
         <v>0.61</v>
       </c>
       <c r="J5" t="n">
-        <v>6.59</v>
+        <v>6.63</v>
       </c>
       <c r="K5" t="n">
         <v>0.04</v>
@@ -763,31 +763,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.51</v>
+        <v>7.7</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.15</v>
+        <v>0.19</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.96</v>
+        <v>2.53</v>
       </c>
       <c r="G6" t="n">
-        <v>7.7</v>
+        <v>7.65</v>
       </c>
       <c r="H6" t="n">
-        <v>0.19</v>
+        <v>-0.05</v>
       </c>
       <c r="I6" t="n">
-        <v>2.53</v>
+        <v>-0.65</v>
       </c>
       <c r="J6" t="n">
-        <v>7.65</v>
+        <v>7.71</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.65</v>
+        <v>0.78</v>
       </c>
       <c r="M6" t="n">
         <v>7.71</v>
@@ -825,31 +825,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.98</v>
+        <v>6.07</v>
       </c>
       <c r="E7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.01</v>
+      </c>
+      <c r="H7" t="n">
         <v>-0.06</v>
       </c>
-      <c r="F7" t="n">
+      <c r="I7" t="n">
         <v>-0.99</v>
       </c>
-      <c r="G7" t="n">
-        <v>6.07</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I7" t="n">
-        <v>1.51</v>
-      </c>
       <c r="J7" t="n">
-        <v>6.01</v>
+        <v>6.09</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.06</v>
+        <v>0.08</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.99</v>
+        <v>1.33</v>
       </c>
       <c r="M7" t="n">
         <v>6.09</v>
@@ -887,31 +887,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.529999999999999</v>
+        <v>9.68</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.15</v>
+        <v>0.15</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.55</v>
+        <v>1.57</v>
       </c>
       <c r="G8" t="n">
-        <v>9.68</v>
+        <v>9.69</v>
       </c>
       <c r="H8" t="n">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="I8" t="n">
-        <v>1.57</v>
+        <v>0.1</v>
       </c>
       <c r="J8" t="n">
-        <v>9.69</v>
+        <v>9.82</v>
       </c>
       <c r="K8" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1</v>
+        <v>1.34</v>
       </c>
       <c r="M8" t="n">
         <v>9.82</v>
@@ -949,31 +949,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.19</v>
+        <v>8.24</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.09</v>
+        <v>0.05</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.09</v>
+        <v>0.61</v>
       </c>
       <c r="G9" t="n">
         <v>8.24</v>
       </c>
       <c r="H9" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.61</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>8.24</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="M9" t="n">
         <v>8.359999999999999</v>
@@ -1011,31 +1011,31 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50.5</v>
+        <v>51.1</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.37</v>
+        <v>1.19</v>
       </c>
       <c r="G10" t="n">
         <v>51.1</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="M10" t="n">
         <v>51.5</v>
@@ -1073,31 +1073,31 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.34</v>
+        <v>1.58</v>
       </c>
       <c r="G11" t="n">
-        <v>4.5</v>
+        <v>4.41</v>
       </c>
       <c r="H11" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.09</v>
       </c>
       <c r="I11" t="n">
-        <v>1.58</v>
+        <v>-2</v>
       </c>
       <c r="J11" t="n">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.09</v>
+        <v>0.01</v>
       </c>
       <c r="L11" t="n">
-        <v>-2</v>
+        <v>0.23</v>
       </c>
       <c r="M11" t="n">
         <v>4.42</v>
@@ -1135,31 +1135,31 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.41</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2</v>
+        <v>0.29</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.08</v>
+        <v>3.08</v>
       </c>
       <c r="G12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.29</v>
+        <v>0.01</v>
       </c>
       <c r="I12" t="n">
-        <v>3.08</v>
+        <v>0.1</v>
       </c>
       <c r="J12" t="n">
-        <v>9.710000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="K12" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="L12" t="n">
-        <v>0.1</v>
+        <v>-0.51</v>
       </c>
       <c r="M12" t="n">
         <v>9.66</v>
@@ -1197,31 +1197,31 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23.4</v>
+        <v>23.68</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.44</v>
+        <v>0.28</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.85</v>
+        <v>1.2</v>
       </c>
       <c r="G13" t="n">
-        <v>23.68</v>
+        <v>23.7</v>
       </c>
       <c r="H13" t="n">
-        <v>0.28</v>
+        <v>0.02</v>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>23.7</v>
+        <v>23.96</v>
       </c>
       <c r="K13" t="n">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="L13" t="n">
-        <v>0.08</v>
+        <v>1.1</v>
       </c>
       <c r="M13" t="n">
         <v>23.96</v>
@@ -1259,31 +1259,31 @@
         </is>
       </c>
       <c r="D14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G14" t="n">
         <v>1.88</v>
       </c>
-      <c r="E14" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-1.05</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.89</v>
-      </c>
       <c r="H14" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.53</v>
+        <v>-0.53</v>
       </c>
       <c r="J14" t="n">
         <v>1.88</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>1.88</v>
@@ -1321,31 +1321,31 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.16</v>
+        <v>5.36</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.02</v>
+        <v>0.2</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.39</v>
+        <v>3.88</v>
       </c>
       <c r="G15" t="n">
-        <v>5.36</v>
+        <v>5.3</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2</v>
+        <v>-0.06</v>
       </c>
       <c r="I15" t="n">
-        <v>3.88</v>
+        <v>-1.12</v>
       </c>
       <c r="J15" t="n">
-        <v>5.3</v>
+        <v>5.33</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.12</v>
+        <v>0.57</v>
       </c>
       <c r="M15" t="n">
         <v>5.33</v>
@@ -1383,31 +1383,31 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
       <c r="G16" t="n">
-        <v>4.25</v>
+        <v>4.29</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.16</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>4.29</v>
+        <v>4.36</v>
       </c>
       <c r="K16" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.63</v>
       </c>
       <c r="M16" t="n">
         <v>4.36</v>
@@ -1445,31 +1445,31 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.19</v>
+        <v>3.15</v>
       </c>
       <c r="E17" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F17" t="n">
-        <v>0.95</v>
+        <v>-1.25</v>
       </c>
       <c r="G17" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.25</v>
+        <v>0.32</v>
       </c>
       <c r="J17" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01</v>
+        <v>0.06</v>
       </c>
       <c r="L17" t="n">
-        <v>0.32</v>
+        <v>1.9</v>
       </c>
       <c r="M17" t="n">
         <v>3.22</v>
@@ -1507,31 +1507,31 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.91</v>
+        <v>2.98</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.36</v>
+        <v>2.41</v>
       </c>
       <c r="G18" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="H18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>2.41</v>
+        <v>0.34</v>
       </c>
       <c r="J18" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
         <v>0.01</v>
       </c>
       <c r="L18" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="M18" t="n">
         <v>3</v>
@@ -1569,31 +1569,31 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>52.7</v>
+        <v>52.6</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.55</v>
+        <v>-0.1</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.03</v>
+        <v>-0.19</v>
       </c>
       <c r="G19" t="n">
-        <v>52.6</v>
+        <v>52.9</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.19</v>
+        <v>0.57</v>
       </c>
       <c r="J19" t="n">
-        <v>52.9</v>
+        <v>52.75</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3</v>
+        <v>-0.15</v>
       </c>
       <c r="L19" t="n">
-        <v>0.57</v>
+        <v>-0.28</v>
       </c>
       <c r="M19" t="n">
         <v>52.75</v>
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.58</v>
+        <v>28.08</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.86</v>
+        <v>-0.5</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.92</v>
+        <v>-1.75</v>
       </c>
       <c r="G20" t="n">
-        <v>28.08</v>
+        <v>28.8</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5</v>
+        <v>0.72</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.75</v>
+        <v>2.56</v>
       </c>
       <c r="J20" t="n">
-        <v>28.8</v>
+        <v>28.12</v>
       </c>
       <c r="K20" t="n">
-        <v>0.72</v>
+        <v>-0.68</v>
       </c>
       <c r="L20" t="n">
-        <v>2.56</v>
+        <v>-2.36</v>
       </c>
       <c r="M20" t="n">
         <v>28.12</v>
@@ -1693,22 +1693,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.39</v>
+        <v>4.49</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.02</v>
+        <v>0.1</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.45</v>
+        <v>2.28</v>
       </c>
       <c r="G21" t="n">
         <v>4.49</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>4.49</v>
@@ -1755,25 +1755,25 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>78.45</v>
+        <v>79.25</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.45</v>
+        <v>0.8</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.57</v>
+        <v>1.02</v>
       </c>
       <c r="G22" t="n">
-        <v>79.25</v>
+        <v>79.34999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="I22" t="n">
-        <v>1.02</v>
+        <v>0.13</v>
       </c>
       <c r="J22" t="n">
-        <v>79.34999999999999</v>
+        <v>79.45</v>
       </c>
       <c r="K22" t="n">
         <v>0.1</v>
@@ -1817,31 +1817,31 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22.44</v>
+        <v>22.08</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.26</v>
+        <v>-0.36</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.15</v>
+        <v>-1.6</v>
       </c>
       <c r="G23" t="n">
-        <v>22.08</v>
+        <v>21.72</v>
       </c>
       <c r="H23" t="n">
         <v>-0.36</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.6</v>
+        <v>-1.63</v>
       </c>
       <c r="J23" t="n">
-        <v>21.72</v>
+        <v>21.86</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.36</v>
+        <v>0.14</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.63</v>
+        <v>0.64</v>
       </c>
       <c r="M23" t="n">
         <v>21.86</v>
@@ -1879,31 +1879,31 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.08</v>
+        <v>14.41</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.01</v>
+        <v>-0.67</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-4.44</v>
       </c>
       <c r="G24" t="n">
-        <v>14.41</v>
+        <v>14.58</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.67</v>
+        <v>0.17</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.44</v>
+        <v>1.18</v>
       </c>
       <c r="J24" t="n">
-        <v>14.58</v>
+        <v>14.38</v>
       </c>
       <c r="K24" t="n">
-        <v>0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="L24" t="n">
-        <v>1.18</v>
+        <v>-1.37</v>
       </c>
       <c r="M24" t="n">
         <v>14.38</v>
@@ -1941,31 +1941,31 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.9</v>
+        <v>25.86</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.68</v>
+        <v>-0.04</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.56</v>
+        <v>-0.15</v>
       </c>
       <c r="G25" t="n">
-        <v>25.86</v>
+        <v>25.2</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.04</v>
+        <v>-0.66</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.15</v>
+        <v>-2.55</v>
       </c>
       <c r="J25" t="n">
-        <v>25.2</v>
+        <v>25.24</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.66</v>
+        <v>0.04</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.55</v>
+        <v>0.16</v>
       </c>
       <c r="M25" t="n">
         <v>25.24</v>
@@ -2003,31 +2003,31 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>38.16</v>
+        <v>35.04</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.16</v>
+        <v>-3.12</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.95</v>
+        <v>-8.18</v>
       </c>
       <c r="G26" t="n">
-        <v>35.04</v>
+        <v>37.36</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.12</v>
+        <v>2.32</v>
       </c>
       <c r="I26" t="n">
-        <v>-8.18</v>
+        <v>6.62</v>
       </c>
       <c r="J26" t="n">
-        <v>37.36</v>
+        <v>37.38</v>
       </c>
       <c r="K26" t="n">
-        <v>2.32</v>
+        <v>0.02</v>
       </c>
       <c r="L26" t="n">
-        <v>6.62</v>
+        <v>0.05</v>
       </c>
       <c r="M26" t="n">
         <v>37.38</v>
@@ -2065,31 +2065,31 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>436.6</v>
+        <v>439.8</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.8</v>
+        <v>3.2</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.41</v>
+        <v>0.73</v>
       </c>
       <c r="G27" t="n">
-        <v>439.8</v>
+        <v>432</v>
       </c>
       <c r="H27" t="n">
-        <v>3.2</v>
+        <v>-7.8</v>
       </c>
       <c r="I27" t="n">
-        <v>0.73</v>
+        <v>-1.77</v>
       </c>
       <c r="J27" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.8</v>
+        <v>-1</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.77</v>
+        <v>-0.23</v>
       </c>
       <c r="M27" t="n">
         <v>431</v>
@@ -2127,31 +2127,31 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>108.4</v>
+        <v>107.7</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.6</v>
+        <v>-0.7</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.45</v>
+        <v>-0.65</v>
       </c>
       <c r="G28" t="n">
-        <v>107.7</v>
+        <v>106.2</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.7</v>
+        <v>-1.5</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.65</v>
+        <v>-1.39</v>
       </c>
       <c r="J28" t="n">
-        <v>106.2</v>
+        <v>106.6</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.5</v>
+        <v>0.4</v>
       </c>
       <c r="L28" t="n">
-        <v>-1.39</v>
+        <v>0.38</v>
       </c>
       <c r="M28" t="n">
         <v>106.6</v>
@@ -2189,31 +2189,31 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>103.7</v>
+        <v>104.5</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.9</v>
+        <v>0.8</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.8</v>
+        <v>0.77</v>
       </c>
       <c r="G29" t="n">
-        <v>104.5</v>
+        <v>103.1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.8</v>
+        <v>-1.4</v>
       </c>
       <c r="I29" t="n">
-        <v>0.77</v>
+        <v>-1.34</v>
       </c>
       <c r="J29" t="n">
-        <v>103.1</v>
+        <v>104.3</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.4</v>
+        <v>1.2</v>
       </c>
       <c r="L29" t="n">
-        <v>-1.34</v>
+        <v>1.16</v>
       </c>
       <c r="M29" t="n">
         <v>104.3</v>
@@ -2251,31 +2251,31 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>71.65000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6</v>
+        <v>0.25</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.83</v>
+        <v>0.35</v>
       </c>
       <c r="G30" t="n">
-        <v>71.90000000000001</v>
+        <v>70.45</v>
       </c>
       <c r="H30" t="n">
-        <v>0.25</v>
+        <v>-1.45</v>
       </c>
       <c r="I30" t="n">
-        <v>0.35</v>
+        <v>-2.02</v>
       </c>
       <c r="J30" t="n">
-        <v>70.45</v>
+        <v>71.7</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.45</v>
+        <v>1.25</v>
       </c>
       <c r="L30" t="n">
-        <v>-2.02</v>
+        <v>1.77</v>
       </c>
       <c r="M30" t="n">
         <v>71.7</v>
@@ -2313,31 +2313,31 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>85.3</v>
+        <v>85.55</v>
       </c>
       <c r="E31" t="n">
-        <v>-1</v>
+        <v>0.25</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.16</v>
+        <v>0.29</v>
       </c>
       <c r="G31" t="n">
-        <v>85.55</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>0.25</v>
+        <v>-0.65</v>
       </c>
       <c r="I31" t="n">
-        <v>0.29</v>
+        <v>-0.76</v>
       </c>
       <c r="J31" t="n">
-        <v>84.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.65</v>
+        <v>0.9</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.76</v>
+        <v>1.06</v>
       </c>
       <c r="M31" t="n">
         <v>85.8</v>
@@ -2375,31 +2375,31 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>63.35</v>
+        <v>61.05</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.45</v>
+        <v>-2.3</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.71</v>
+        <v>-3.63</v>
       </c>
       <c r="G32" t="n">
         <v>61.05</v>
       </c>
       <c r="H32" t="n">
-        <v>-2.3</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>-3.63</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>61.05</v>
+        <v>60.65</v>
       </c>
       <c r="K32" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>-0.66</v>
       </c>
       <c r="M32" t="n">
         <v>60.65</v>
@@ -2437,31 +2437,31 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>78.09999999999999</v>
+        <v>77.7</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.4</v>
+        <v>-0.4</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.76</v>
+        <v>-0.51</v>
       </c>
       <c r="G33" t="n">
-        <v>77.7</v>
+        <v>75.75</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4</v>
+        <v>-1.95</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.51</v>
+        <v>-2.51</v>
       </c>
       <c r="J33" t="n">
-        <v>75.75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.95</v>
+        <v>-0.15</v>
       </c>
       <c r="L33" t="n">
-        <v>-2.51</v>
+        <v>-0.2</v>
       </c>
       <c r="M33" t="n">
         <v>75.59999999999999</v>
@@ -2499,31 +2499,31 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>30.02</v>
+        <v>30.7</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.48</v>
+        <v>0.68</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.57</v>
+        <v>2.27</v>
       </c>
       <c r="G34" t="n">
-        <v>30.7</v>
+        <v>30.24</v>
       </c>
       <c r="H34" t="n">
-        <v>0.68</v>
+        <v>-0.46</v>
       </c>
       <c r="I34" t="n">
-        <v>2.27</v>
+        <v>-1.5</v>
       </c>
       <c r="J34" t="n">
-        <v>30.24</v>
+        <v>30.94</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.46</v>
+        <v>0.7</v>
       </c>
       <c r="L34" t="n">
-        <v>-1.5</v>
+        <v>2.31</v>
       </c>
       <c r="M34" t="n">
         <v>30.94</v>
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>4.2</v>
+        <v>4.15</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.19</v>
       </c>
       <c r="J35" t="n">
-        <v>4.15</v>
+        <v>4.17</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="L35" t="n">
-        <v>-1.19</v>
+        <v>0.48</v>
       </c>
       <c r="M35" t="n">
-        <v>4.15</v>
+        <v>4.17</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="O35" t="n">
-        <v>-1.19</v>
+        <v>0.48</v>
       </c>
       <c r="P35" t="n">
-        <v>4.15</v>
+        <v>4.07</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="R35" t="n">
-        <v>-1.19</v>
+        <v>-2.4</v>
       </c>
     </row>
     <row r="36">
@@ -2626,46 +2626,46 @@
         <v>9.09</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.13</v>
+        <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.41</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>9.09</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>-0.12</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>-1.32</v>
       </c>
       <c r="J36" t="n">
-        <v>8.970000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.12</v>
+        <v>0.01</v>
       </c>
       <c r="L36" t="n">
-        <v>-1.32</v>
+        <v>0.11</v>
       </c>
       <c r="M36" t="n">
-        <v>8.970000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.12</v>
+        <v>0.01</v>
       </c>
       <c r="O36" t="n">
-        <v>-1.32</v>
+        <v>0.11</v>
       </c>
       <c r="P36" t="n">
-        <v>8.970000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.12</v>
+        <v>-0.23</v>
       </c>
       <c r="R36" t="n">
-        <v>-1.32</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="37">
@@ -2685,31 +2685,31 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>388.4</v>
+        <v>388.6</v>
       </c>
       <c r="E37" t="n">
-        <v>-5</v>
+        <v>0.2</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.27</v>
+        <v>0.05</v>
       </c>
       <c r="G37" t="n">
-        <v>388.6</v>
+        <v>386.8</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2</v>
+        <v>-1.8</v>
       </c>
       <c r="I37" t="n">
-        <v>0.05</v>
+        <v>-0.46</v>
       </c>
       <c r="J37" t="n">
-        <v>386.8</v>
+        <v>387.8</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.8</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.46</v>
+        <v>0.26</v>
       </c>
       <c r="M37" t="n">
         <v>387.8</v>
@@ -2747,31 +2747,31 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.91</v>
+        <v>11.93</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.13</v>
+        <v>0.02</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.08</v>
+        <v>0.17</v>
       </c>
       <c r="G38" t="n">
-        <v>11.93</v>
+        <v>11.79</v>
       </c>
       <c r="H38" t="n">
-        <v>0.02</v>
+        <v>-0.14</v>
       </c>
       <c r="I38" t="n">
-        <v>0.17</v>
+        <v>-1.17</v>
       </c>
       <c r="J38" t="n">
-        <v>11.79</v>
+        <v>11.85</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.14</v>
+        <v>0.06</v>
       </c>
       <c r="L38" t="n">
-        <v>-1.17</v>
+        <v>0.51</v>
       </c>
       <c r="M38" t="n">
         <v>11.85</v>
@@ -2809,31 +2809,31 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>489.4</v>
+        <v>484.6</v>
       </c>
       <c r="E39" t="n">
-        <v>-3.4</v>
+        <v>-4.8</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.98</v>
       </c>
       <c r="G39" t="n">
-        <v>484.6</v>
+        <v>482.2</v>
       </c>
       <c r="H39" t="n">
-        <v>-4.8</v>
+        <v>-2.4</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.98</v>
+        <v>-0.5</v>
       </c>
       <c r="J39" t="n">
-        <v>482.2</v>
+        <v>484.2</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.4</v>
+        <v>2</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.5</v>
+        <v>0.41</v>
       </c>
       <c r="M39" t="n">
         <v>484.2</v>
@@ -2871,31 +2871,31 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>39.46</v>
+        <v>39.1</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.76</v>
+        <v>-0.36</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.89</v>
+        <v>-0.91</v>
       </c>
       <c r="G40" t="n">
-        <v>39.1</v>
+        <v>37.5</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.36</v>
+        <v>-1.6</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.91</v>
+        <v>-4.09</v>
       </c>
       <c r="J40" t="n">
-        <v>37.5</v>
+        <v>37.86</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.6</v>
+        <v>0.36</v>
       </c>
       <c r="L40" t="n">
-        <v>-4.09</v>
+        <v>0.96</v>
       </c>
       <c r="M40" t="n">
         <v>37.86</v>
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>32.01</v>
+        <v>32.22</v>
       </c>
       <c r="E41" t="n">
-        <v>0.42</v>
+        <v>0.21</v>
       </c>
       <c r="F41" t="n">
-        <v>1.33</v>
+        <v>0.66</v>
       </c>
       <c r="G41" t="n">
-        <v>32.22</v>
+        <v>32.16</v>
       </c>
       <c r="H41" t="n">
-        <v>0.21</v>
+        <v>-0.06</v>
       </c>
       <c r="I41" t="n">
-        <v>0.66</v>
+        <v>-0.19</v>
       </c>
       <c r="J41" t="n">
-        <v>32.16</v>
+        <v>31.99</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.06</v>
+        <v>-0.17</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.19</v>
+        <v>-0.53</v>
       </c>
       <c r="M41" t="n">
-        <v>31.99</v>
+        <v>31.55</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.17</v>
+        <v>-0.44</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.53</v>
+        <v>-1.38</v>
       </c>
       <c r="P41" t="n">
-        <v>31.99</v>
+        <v>31.55</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.17</v>
+        <v>-0.44</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.53</v>
+        <v>-1.38</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>78</v>
+        <v>78.11</v>
       </c>
       <c r="E42" t="n">
-        <v>0.52</v>
+        <v>0.11</v>
       </c>
       <c r="F42" t="n">
-        <v>0.67</v>
+        <v>0.14</v>
       </c>
       <c r="G42" t="n">
-        <v>78.11</v>
+        <v>78.38</v>
       </c>
       <c r="H42" t="n">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="I42" t="n">
-        <v>0.14</v>
+        <v>0.35</v>
       </c>
       <c r="J42" t="n">
-        <v>78.38</v>
+        <v>77.5</v>
       </c>
       <c r="K42" t="n">
-        <v>0.27</v>
+        <v>-0.88</v>
       </c>
       <c r="L42" t="n">
-        <v>0.35</v>
+        <v>-1.12</v>
       </c>
       <c r="M42" t="n">
-        <v>77.5</v>
+        <v>77.36</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.88</v>
+        <v>-0.14</v>
       </c>
       <c r="O42" t="n">
-        <v>-1.12</v>
+        <v>-0.18</v>
       </c>
       <c r="P42" t="n">
-        <v>77.5</v>
+        <v>77.36</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.88</v>
+        <v>-0.14</v>
       </c>
       <c r="R42" t="n">
-        <v>-1.12</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>42.57</v>
+        <v>43.29</v>
       </c>
       <c r="E43" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="G43" t="n">
+        <v>43.32</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I43" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="F43" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="G43" t="n">
-        <v>43.29</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="I43" t="n">
-        <v>1.69</v>
-      </c>
       <c r="J43" t="n">
-        <v>43.32</v>
+        <v>42.84</v>
       </c>
       <c r="K43" t="n">
-        <v>0.03</v>
+        <v>-0.48</v>
       </c>
       <c r="L43" t="n">
-        <v>0.07000000000000001</v>
+        <v>-1.11</v>
       </c>
       <c r="M43" t="n">
-        <v>42.84</v>
+        <v>43.34</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.48</v>
+        <v>0.5</v>
       </c>
       <c r="O43" t="n">
-        <v>-1.11</v>
+        <v>1.17</v>
       </c>
       <c r="P43" t="n">
-        <v>42.84</v>
+        <v>43.34</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.48</v>
+        <v>0.5</v>
       </c>
       <c r="R43" t="n">
-        <v>-1.11</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.87</v>
+        <v>5.84</v>
       </c>
       <c r="E44" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="F44" t="n">
-        <v>0.34</v>
+        <v>-0.51</v>
       </c>
       <c r="G44" t="n">
-        <v>5.84</v>
+        <v>5.8</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.51</v>
+        <v>-0.68</v>
       </c>
       <c r="J44" t="n">
-        <v>5.8</v>
+        <v>5.79</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.68</v>
+        <v>-0.17</v>
       </c>
       <c r="M44" t="n">
-        <v>5.79</v>
+        <v>5.88</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.17</v>
+        <v>1.55</v>
       </c>
       <c r="P44" t="n">
-        <v>5.79</v>
+        <v>5.88</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.17</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-1.43</v>
       </c>
       <c r="G45" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="H45" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="K45" t="n">
         <v>-0.03</v>
       </c>
-      <c r="I45" t="n">
-        <v>-1.43</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0.01</v>
-      </c>
       <c r="L45" t="n">
-        <v>0.48</v>
+        <v>-1.44</v>
       </c>
       <c r="M45" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="O45" t="n">
-        <v>-1.44</v>
+        <v>-0.49</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="R45" t="n">
-        <v>-1.44</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="J46" t="n">
         <v>3.83</v>
       </c>
-      <c r="E46" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="G46" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I46" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.87</v>
-      </c>
       <c r="K46" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.26</v>
+        <v>-1.03</v>
       </c>
       <c r="M46" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="O46" t="n">
-        <v>-1.03</v>
+        <v>-1.31</v>
       </c>
       <c r="P46" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="R46" t="n">
-        <v>-1.03</v>
+        <v>-1.31</v>
       </c>
     </row>
     <row r="47">
@@ -3308,46 +3308,46 @@
         <v>10.87</v>
       </c>
       <c r="E47" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.09</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>10.87</v>
+        <v>10.85</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="J47" t="n">
-        <v>10.85</v>
+        <v>10.92</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.18</v>
+        <v>0.65</v>
       </c>
       <c r="M47" t="n">
-        <v>10.92</v>
+        <v>11</v>
       </c>
       <c r="N47" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="O47" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="P47" t="n">
-        <v>10.92</v>
+        <v>11</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="R47" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.315</v>
       </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.31</v>
-      </c>
       <c r="H48" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.59</v>
+        <v>1.61</v>
       </c>
       <c r="J48" t="n">
-        <v>0.315</v>
+        <v>0.3</v>
       </c>
       <c r="K48" t="n">
-        <v>0.005</v>
+        <v>-0.015</v>
       </c>
       <c r="L48" t="n">
-        <v>1.61</v>
+        <v>-4.76</v>
       </c>
       <c r="M48" t="n">
         <v>0.3</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>-4.76</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0.3</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>-4.76</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G49" t="n">
         <v>4.28</v>
       </c>
-      <c r="E49" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F49" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="G49" t="n">
-        <v>4.29</v>
-      </c>
       <c r="H49" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="I49" t="n">
-        <v>0.23</v>
+        <v>-0.23</v>
       </c>
       <c r="J49" t="n">
-        <v>4.28</v>
+        <v>4.25</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.23</v>
+        <v>-0.7</v>
       </c>
       <c r="M49" t="n">
-        <v>4.25</v>
+        <v>4.27</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.7</v>
+        <v>0.47</v>
       </c>
       <c r="P49" t="n">
-        <v>4.25</v>
+        <v>4.27</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.7</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="G50" t="n">
         <v>1.12</v>
       </c>
-      <c r="E50" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F50" t="n">
-        <v>-1.75</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1.13</v>
-      </c>
       <c r="H50" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="I50" t="n">
-        <v>0.89</v>
+        <v>-0.88</v>
       </c>
       <c r="J50" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="K50" t="n">
         <v>-0.01</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.88</v>
+        <v>-0.89</v>
       </c>
       <c r="M50" t="n">
         <v>1.11</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>-0.89</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
         <v>1.11</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>-0.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.19</v>
+        <v>5.16</v>
       </c>
       <c r="E51" t="n">
-        <v>0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="F51" t="n">
-        <v>0.39</v>
+        <v>-0.58</v>
       </c>
       <c r="G51" t="n">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.58</v>
+        <v>-0.39</v>
       </c>
       <c r="J51" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.39</v>
+        <v>-0.19</v>
       </c>
       <c r="M51" t="n">
-        <v>5.13</v>
+        <v>5.07</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.19</v>
+        <v>-1.17</v>
       </c>
       <c r="P51" t="n">
-        <v>5.13</v>
+        <v>5.07</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="R51" t="n">
-        <v>-0.19</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.3</v>
+        <v>11.38</v>
       </c>
       <c r="E52" t="n">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="F52" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="G52" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="H52" t="n">
         <v>0.09</v>
       </c>
-      <c r="G52" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.08</v>
-      </c>
       <c r="I52" t="n">
-        <v>0.71</v>
+        <v>0.79</v>
       </c>
       <c r="J52" t="n">
-        <v>11.47</v>
+        <v>11.28</v>
       </c>
       <c r="K52" t="n">
-        <v>0.09</v>
+        <v>-0.19</v>
       </c>
       <c r="L52" t="n">
-        <v>0.79</v>
+        <v>-1.66</v>
       </c>
       <c r="M52" t="n">
-        <v>11.28</v>
+        <v>11.18</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.19</v>
+        <v>-0.1</v>
       </c>
       <c r="O52" t="n">
-        <v>-1.66</v>
+        <v>-0.89</v>
       </c>
       <c r="P52" t="n">
-        <v>11.28</v>
+        <v>11.18</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.19</v>
+        <v>-0.1</v>
       </c>
       <c r="R52" t="n">
-        <v>-1.66</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>8.26</v>
+        <v>7.59</v>
       </c>
       <c r="E53" t="n">
-        <v>0.04</v>
+        <v>-0.67</v>
       </c>
       <c r="F53" t="n">
-        <v>0.49</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="G53" t="n">
-        <v>7.59</v>
+        <v>7.43</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.67</v>
+        <v>-0.16</v>
       </c>
       <c r="I53" t="n">
-        <v>-8.109999999999999</v>
+        <v>-2.11</v>
       </c>
       <c r="J53" t="n">
-        <v>7.43</v>
+        <v>7.39</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.16</v>
+        <v>-0.04</v>
       </c>
       <c r="L53" t="n">
-        <v>-2.11</v>
+        <v>-0.54</v>
       </c>
       <c r="M53" t="n">
-        <v>7.39</v>
+        <v>7.12</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.04</v>
+        <v>-0.27</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.54</v>
+        <v>-3.65</v>
       </c>
       <c r="P53" t="n">
-        <v>7.39</v>
+        <v>7.12</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.04</v>
+        <v>-0.27</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.54</v>
+        <v>-3.65</v>
       </c>
     </row>
     <row r="54">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.44</v>
+        <v>0.435</v>
       </c>
       <c r="E54" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="F54" t="n">
-        <v>1.15</v>
+        <v>-1.14</v>
       </c>
       <c r="G54" t="n">
         <v>0.435</v>
       </c>
       <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="K54" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I54" t="n">
-        <v>-1.14</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>-1.15</v>
       </c>
       <c r="M54" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="N54" t="n">
         <v>-0.005</v>
       </c>
       <c r="O54" t="n">
-        <v>-1.15</v>
+        <v>-1.16</v>
       </c>
       <c r="P54" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="Q54" t="n">
         <v>-0.005</v>
       </c>
       <c r="R54" t="n">
-        <v>-1.15</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="55">
@@ -3801,31 +3801,31 @@
         </is>
       </c>
       <c r="D55" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F55" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="G55" t="n">
         <v>0.615</v>
       </c>
-      <c r="E55" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-0.8100000000000001</v>
-      </c>
-      <c r="G55" t="n">
-        <v>0.625</v>
-      </c>
       <c r="H55" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="I55" t="n">
-        <v>1.63</v>
+        <v>-1.6</v>
       </c>
       <c r="J55" t="n">
         <v>0.615</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0.615</v>
@@ -3872,40 +3872,40 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.39</v>
+        <v>0.375</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>-3.85</v>
       </c>
       <c r="J56" t="n">
         <v>0.375</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>-3.85</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.375</v>
+        <v>0.38</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P56" t="n">
-        <v>0.375</v>
+        <v>0.38</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.68</v>
+        <v>3.61</v>
       </c>
       <c r="E57" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.61</v>
+      </c>
+      <c r="K57" t="n">
         <v>0.03</v>
       </c>
-      <c r="F57" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="G57" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="I57" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="K57" t="n">
-        <v>-0.03</v>
-      </c>
       <c r="L57" t="n">
-        <v>-0.83</v>
+        <v>0.84</v>
       </c>
       <c r="M57" t="n">
-        <v>3.61</v>
+        <v>3.51</v>
       </c>
       <c r="N57" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="O57" t="n">
-        <v>0.84</v>
+        <v>-2.77</v>
       </c>
       <c r="P57" t="n">
-        <v>3.61</v>
+        <v>3.51</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="R57" t="n">
-        <v>0.84</v>
+        <v>-2.77</v>
       </c>
     </row>
     <row r="58">
@@ -3996,22 +3996,22 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>0.002</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="J58" t="n">
         <v>0.081</v>
       </c>
       <c r="K58" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0.081</v>
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
+        <v>22.47</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="G59" t="n">
         <v>22.4</v>
       </c>
-      <c r="E59" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F59" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="G59" t="n">
-        <v>22.47</v>
-      </c>
       <c r="H59" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>0.31</v>
+        <v>-0.31</v>
       </c>
       <c r="J59" t="n">
-        <v>22.4</v>
+        <v>22.61</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.31</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M59" t="n">
         <v>22.61</v>
       </c>
       <c r="N59" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="P59" t="n">
         <v>22.61</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="E60" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>0.63</v>
+        <v>-0.31</v>
       </c>
       <c r="G60" t="n">
         <v>3.18</v>
       </c>
       <c r="H60" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="K60" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L60" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="M60" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="N60" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I60" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="N60" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="O60" t="n">
-        <v>-1.26</v>
+        <v>-0.32</v>
       </c>
       <c r="P60" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="R60" t="n">
-        <v>-1.26</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.87</v>
+        <v>0.85</v>
       </c>
       <c r="E61" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F61" t="n">
-        <v>1.16</v>
+        <v>-2.3</v>
       </c>
       <c r="G61" t="n">
+        <v>0.855</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J61" t="n">
         <v>0.85</v>
       </c>
-      <c r="H61" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I61" t="n">
-        <v>-2.3</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.855</v>
-      </c>
       <c r="K61" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="L61" t="n">
-        <v>0.59</v>
+        <v>-0.58</v>
       </c>
       <c r="M61" t="n">
-        <v>0.85</v>
+        <v>0.835</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.005</v>
+        <v>-0.015</v>
       </c>
       <c r="O61" t="n">
-        <v>-0.58</v>
+        <v>-1.76</v>
       </c>
       <c r="P61" t="n">
-        <v>0.85</v>
+        <v>0.835</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.005</v>
+        <v>-0.015</v>
       </c>
       <c r="R61" t="n">
-        <v>-0.58</v>
+        <v>-1.76</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-28 Close</t>
+          <t>2026-09-30 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-09-28 Change</t>
+          <t>2026-09-30 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-28 Change %</t>
+          <t>2026-09-30 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-09-29 Close</t>
+          <t>2026-10-01 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-09-29 Change</t>
+          <t>2026-10-01 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-09-29 Change %</t>
+          <t>2026-10-01 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-09-30 Close</t>
+          <t>2026-10-02 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-09-30 Change</t>
+          <t>2026-10-02 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-09-30 Change %</t>
+          <t>2026-10-02 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-10-01 Close</t>
+          <t>2026-10-05 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-10-01 Change</t>
+          <t>2026-10-05 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-10-01 Change %</t>
+          <t>2026-10-05 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-10-02 Close</t>
+          <t>2026-10-06 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-10-02 Change</t>
+          <t>2026-10-06 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-10-02 Change %</t>
+          <t>2026-10-06 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>158.9</v>
+        <v>158</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3</v>
+        <v>-1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.82</v>
+        <v>-0.63</v>
       </c>
       <c r="G3" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1</v>
+        <v>-1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06</v>
+        <v>-0.63</v>
       </c>
       <c r="J3" t="n">
-        <v>158</v>
+        <v>149.5</v>
       </c>
       <c r="K3" t="n">
-        <v>-1</v>
+        <v>-8.5</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.63</v>
+        <v>-5.38</v>
       </c>
       <c r="M3" t="n">
-        <v>158</v>
+        <v>149.9</v>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.63</v>
+        <v>0.27</v>
       </c>
       <c r="P3" t="n">
-        <v>158</v>
+        <v>149.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.63</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>242.6</v>
+        <v>244.4</v>
       </c>
       <c r="E4" t="n">
-        <v>4.6</v>
+        <v>1.6</v>
       </c>
       <c r="F4" t="n">
-        <v>1.93</v>
+        <v>0.66</v>
       </c>
       <c r="G4" t="n">
-        <v>242.8</v>
+        <v>244.4</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2</v>
+        <v>1.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08</v>
+        <v>0.66</v>
       </c>
       <c r="J4" t="n">
-        <v>244.4</v>
+        <v>229.8</v>
       </c>
       <c r="K4" t="n">
-        <v>1.6</v>
+        <v>-14.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.66</v>
+        <v>-5.97</v>
       </c>
       <c r="M4" t="n">
-        <v>244.4</v>
+        <v>228.6</v>
       </c>
       <c r="N4" t="n">
-        <v>1.6</v>
+        <v>-1.2</v>
       </c>
       <c r="O4" t="n">
-        <v>0.66</v>
+        <v>-0.52</v>
       </c>
       <c r="P4" t="n">
-        <v>244.4</v>
+        <v>228.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.6</v>
+        <v>-1.2</v>
       </c>
       <c r="R4" t="n">
-        <v>0.66</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="5">
@@ -701,7 +701,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.55</v>
+        <v>6.63</v>
       </c>
       <c r="E5" t="n">
         <v>0.04</v>
@@ -710,7 +710,7 @@
         <v>0.61</v>
       </c>
       <c r="G5" t="n">
-        <v>6.59</v>
+        <v>6.63</v>
       </c>
       <c r="H5" t="n">
         <v>0.04</v>
@@ -719,31 +719,31 @@
         <v>0.61</v>
       </c>
       <c r="J5" t="n">
-        <v>6.63</v>
+        <v>6.46</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04</v>
+        <v>-0.17</v>
       </c>
       <c r="L5" t="n">
-        <v>0.61</v>
+        <v>-2.56</v>
       </c>
       <c r="M5" t="n">
-        <v>6.63</v>
+        <v>6.49</v>
       </c>
       <c r="N5" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="O5" t="n">
-        <v>0.61</v>
+        <v>0.46</v>
       </c>
       <c r="P5" t="n">
-        <v>6.63</v>
+        <v>6.49</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="R5" t="n">
-        <v>0.61</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.7</v>
+        <v>7.71</v>
       </c>
       <c r="E6" t="n">
-        <v>0.19</v>
+        <v>0.06</v>
       </c>
       <c r="F6" t="n">
-        <v>2.53</v>
+        <v>0.78</v>
       </c>
       <c r="G6" t="n">
-        <v>7.65</v>
+        <v>7.71</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.65</v>
+        <v>0.78</v>
       </c>
       <c r="J6" t="n">
-        <v>7.71</v>
+        <v>7.45</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06</v>
+        <v>-0.26</v>
       </c>
       <c r="L6" t="n">
-        <v>0.78</v>
+        <v>-3.37</v>
       </c>
       <c r="M6" t="n">
-        <v>7.71</v>
+        <v>7.45</v>
       </c>
       <c r="N6" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>7.71</v>
+        <v>7.45</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.07</v>
+        <v>6.09</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="G7" t="n">
-        <v>6.01</v>
+        <v>6.09</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.06</v>
+        <v>0.08</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.99</v>
+        <v>1.33</v>
       </c>
       <c r="J7" t="n">
-        <v>6.09</v>
+        <v>5.92</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08</v>
+        <v>-0.17</v>
       </c>
       <c r="L7" t="n">
-        <v>1.33</v>
+        <v>-2.79</v>
       </c>
       <c r="M7" t="n">
-        <v>6.09</v>
+        <v>5.92</v>
       </c>
       <c r="N7" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>6.09</v>
+        <v>5.92</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.68</v>
+        <v>9.82</v>
       </c>
       <c r="E8" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="F8" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="G8" t="n">
-        <v>9.69</v>
+        <v>9.82</v>
       </c>
       <c r="H8" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1</v>
+        <v>1.34</v>
       </c>
       <c r="J8" t="n">
-        <v>9.82</v>
+        <v>9.56</v>
       </c>
       <c r="K8" t="n">
-        <v>0.13</v>
+        <v>-0.26</v>
       </c>
       <c r="L8" t="n">
-        <v>1.34</v>
+        <v>-2.65</v>
       </c>
       <c r="M8" t="n">
-        <v>9.82</v>
+        <v>9.51</v>
       </c>
       <c r="N8" t="n">
-        <v>0.13</v>
+        <v>-0.05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.34</v>
+        <v>-0.52</v>
       </c>
       <c r="P8" t="n">
-        <v>9.82</v>
+        <v>9.51</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.13</v>
+        <v>-0.05</v>
       </c>
       <c r="R8" t="n">
-        <v>1.34</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.24</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05</v>
+        <v>0.12</v>
       </c>
       <c r="F9" t="n">
-        <v>0.61</v>
+        <v>1.46</v>
       </c>
       <c r="G9" t="n">
-        <v>8.24</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="J9" t="n">
-        <v>8.359999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="L9" t="n">
-        <v>1.46</v>
+        <v>-1.67</v>
       </c>
       <c r="M9" t="n">
-        <v>8.359999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="N9" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="O9" t="n">
-        <v>1.46</v>
+        <v>-0.36</v>
       </c>
       <c r="P9" t="n">
-        <v>8.359999999999999</v>
+        <v>8.19</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.12</v>
+        <v>-0.03</v>
       </c>
       <c r="R9" t="n">
-        <v>1.46</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="F10" t="n">
-        <v>1.19</v>
+        <v>0.78</v>
       </c>
       <c r="G10" t="n">
-        <v>51.1</v>
+        <v>51.5</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.78</v>
       </c>
       <c r="J10" t="n">
-        <v>51.5</v>
+        <v>50.6</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="L10" t="n">
-        <v>0.78</v>
+        <v>-1.75</v>
       </c>
       <c r="M10" t="n">
-        <v>51.5</v>
+        <v>50.7</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="O10" t="n">
-        <v>0.78</v>
+        <v>0.2</v>
       </c>
       <c r="P10" t="n">
-        <v>51.5</v>
+        <v>50.7</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="R10" t="n">
-        <v>0.78</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.5</v>
+        <v>4.42</v>
       </c>
       <c r="E11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="F11" t="n">
-        <v>1.58</v>
+        <v>0.23</v>
       </c>
       <c r="G11" t="n">
-        <v>4.41</v>
+        <v>4.42</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.09</v>
+        <v>0.01</v>
       </c>
       <c r="I11" t="n">
-        <v>-2</v>
+        <v>0.23</v>
       </c>
       <c r="J11" t="n">
-        <v>4.42</v>
+        <v>4.36</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="L11" t="n">
-        <v>0.23</v>
+        <v>-1.36</v>
       </c>
       <c r="M11" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="N11" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="O11" t="n">
-        <v>0.23</v>
+        <v>0.46</v>
       </c>
       <c r="P11" t="n">
-        <v>4.42</v>
+        <v>4.38</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="R11" t="n">
-        <v>0.23</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.699999999999999</v>
+        <v>9.66</v>
       </c>
       <c r="E12" t="n">
-        <v>0.29</v>
+        <v>-0.05</v>
       </c>
       <c r="F12" t="n">
-        <v>3.08</v>
+        <v>-0.51</v>
       </c>
       <c r="G12" t="n">
-        <v>9.710000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="H12" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1</v>
+        <v>-0.51</v>
       </c>
       <c r="J12" t="n">
-        <v>9.66</v>
+        <v>9.52</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.05</v>
+        <v>-0.14</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.51</v>
+        <v>-1.45</v>
       </c>
       <c r="M12" t="n">
-        <v>9.66</v>
+        <v>9.56</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.51</v>
+        <v>0.42</v>
       </c>
       <c r="P12" t="n">
-        <v>9.66</v>
+        <v>9.56</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.51</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23.68</v>
+        <v>23.96</v>
       </c>
       <c r="E13" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="G13" t="n">
-        <v>23.7</v>
+        <v>23.96</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02</v>
+        <v>0.26</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08</v>
+        <v>1.1</v>
       </c>
       <c r="J13" t="n">
-        <v>23.96</v>
+        <v>23.52</v>
       </c>
       <c r="K13" t="n">
-        <v>0.26</v>
+        <v>-0.44</v>
       </c>
       <c r="L13" t="n">
-        <v>1.1</v>
+        <v>-1.84</v>
       </c>
       <c r="M13" t="n">
-        <v>23.96</v>
+        <v>23.42</v>
       </c>
       <c r="N13" t="n">
-        <v>0.26</v>
+        <v>-0.1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.1</v>
+        <v>-0.43</v>
       </c>
       <c r="P13" t="n">
-        <v>23.96</v>
+        <v>23.42</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.26</v>
+        <v>-0.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.1</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="14">
@@ -1259,34 +1259,34 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.53</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
         <v>1.88</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.53</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="M14" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -1295,7 +1295,7 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.36</v>
+        <v>5.33</v>
       </c>
       <c r="E15" t="n">
-        <v>0.2</v>
+        <v>0.03</v>
       </c>
       <c r="F15" t="n">
-        <v>3.88</v>
+        <v>0.57</v>
       </c>
       <c r="G15" t="n">
-        <v>5.3</v>
+        <v>5.33</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.12</v>
+        <v>0.57</v>
       </c>
       <c r="J15" t="n">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="K15" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="L15" t="n">
-        <v>0.57</v>
+        <v>-1.5</v>
       </c>
       <c r="M15" t="n">
-        <v>5.33</v>
+        <v>5.24</v>
       </c>
       <c r="N15" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="O15" t="n">
-        <v>0.57</v>
+        <v>-0.19</v>
       </c>
       <c r="P15" t="n">
-        <v>5.33</v>
+        <v>5.24</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="R15" t="n">
-        <v>0.57</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.25</v>
+        <v>4.36</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.16</v>
+        <v>1.63</v>
       </c>
       <c r="G16" t="n">
-        <v>4.29</v>
+        <v>4.36</v>
       </c>
       <c r="H16" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.63</v>
       </c>
       <c r="J16" t="n">
-        <v>4.36</v>
+        <v>4.3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="L16" t="n">
-        <v>1.63</v>
+        <v>-1.38</v>
       </c>
       <c r="M16" t="n">
-        <v>4.36</v>
+        <v>4.3</v>
       </c>
       <c r="N16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>4.36</v>
+        <v>4.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.15</v>
+        <v>3.22</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.04</v>
+        <v>0.06</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.25</v>
+        <v>1.9</v>
       </c>
       <c r="G17" t="n">
-        <v>3.16</v>
+        <v>3.22</v>
       </c>
       <c r="H17" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.93</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N17" t="n">
         <v>0.01</v>
       </c>
-      <c r="I17" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="M17" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.06</v>
-      </c>
       <c r="O17" t="n">
-        <v>1.9</v>
+        <v>0.31</v>
       </c>
       <c r="P17" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="R17" t="n">
-        <v>1.9</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="F18" t="n">
-        <v>2.41</v>
+        <v>0.33</v>
       </c>
       <c r="G18" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="H18" t="n">
         <v>0.01</v>
       </c>
       <c r="I18" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="J18" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="L18" t="n">
-        <v>0.33</v>
+        <v>-1</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N18" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="O18" t="n">
-        <v>0.33</v>
+        <v>-0.67</v>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="R18" t="n">
-        <v>0.33</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>52.6</v>
+        <v>52.75</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1</v>
+        <v>-0.15</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.19</v>
+        <v>-0.28</v>
       </c>
       <c r="G19" t="n">
-        <v>52.9</v>
+        <v>52.75</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3</v>
+        <v>-0.15</v>
       </c>
       <c r="I19" t="n">
-        <v>0.57</v>
+        <v>-0.28</v>
       </c>
       <c r="J19" t="n">
-        <v>52.75</v>
+        <v>52</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.28</v>
+        <v>-1.42</v>
       </c>
       <c r="M19" t="n">
-        <v>52.75</v>
+        <v>51.75</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.15</v>
+        <v>-0.25</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.28</v>
+        <v>-0.48</v>
       </c>
       <c r="P19" t="n">
-        <v>52.75</v>
+        <v>51.75</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.15</v>
+        <v>-0.25</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.28</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.08</v>
+        <v>28.12</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5</v>
+        <v>-0.68</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.75</v>
+        <v>-2.36</v>
       </c>
       <c r="G20" t="n">
-        <v>28.8</v>
+        <v>28.12</v>
       </c>
       <c r="H20" t="n">
-        <v>0.72</v>
+        <v>-0.68</v>
       </c>
       <c r="I20" t="n">
-        <v>2.56</v>
+        <v>-2.36</v>
       </c>
       <c r="J20" t="n">
-        <v>28.12</v>
+        <v>27.5</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.68</v>
+        <v>-0.62</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.36</v>
+        <v>-2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>28.12</v>
+        <v>27.56</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.68</v>
+        <v>0.06</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.36</v>
+        <v>0.22</v>
       </c>
       <c r="P20" t="n">
-        <v>28.12</v>
+        <v>27.56</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.68</v>
+        <v>0.06</v>
       </c>
       <c r="R20" t="n">
-        <v>-2.36</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="21">
@@ -1696,10 +1696,10 @@
         <v>4.49</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>4.49</v>
@@ -1711,31 +1711,31 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>4.49</v>
+        <v>4.45</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
       <c r="M21" t="n">
-        <v>4.49</v>
+        <v>4.46</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="P21" t="n">
-        <v>4.49</v>
+        <v>4.46</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="22">
@@ -1755,16 +1755,16 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79.25</v>
+        <v>79.45</v>
       </c>
       <c r="E22" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="F22" t="n">
-        <v>1.02</v>
+        <v>0.13</v>
       </c>
       <c r="G22" t="n">
-        <v>79.34999999999999</v>
+        <v>79.45</v>
       </c>
       <c r="H22" t="n">
         <v>0.1</v>
@@ -1773,31 +1773,31 @@
         <v>0.13</v>
       </c>
       <c r="J22" t="n">
-        <v>79.45</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="L22" t="n">
-        <v>0.13</v>
+        <v>-0.76</v>
       </c>
       <c r="M22" t="n">
-        <v>79.45</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="O22" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="P22" t="n">
-        <v>79.45</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="R22" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>22.08</v>
+        <v>21.86</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.36</v>
+        <v>0.14</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.6</v>
+        <v>0.64</v>
       </c>
       <c r="G23" t="n">
-        <v>21.72</v>
+        <v>21.86</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.36</v>
+        <v>0.14</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.63</v>
+        <v>0.64</v>
       </c>
       <c r="J23" t="n">
-        <v>21.86</v>
+        <v>21.66</v>
       </c>
       <c r="K23" t="n">
-        <v>0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="L23" t="n">
-        <v>0.64</v>
+        <v>-0.91</v>
       </c>
       <c r="M23" t="n">
-        <v>21.86</v>
+        <v>21.62</v>
       </c>
       <c r="N23" t="n">
-        <v>0.14</v>
+        <v>-0.04</v>
       </c>
       <c r="O23" t="n">
-        <v>0.64</v>
+        <v>-0.18</v>
       </c>
       <c r="P23" t="n">
-        <v>21.86</v>
+        <v>21.62</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.14</v>
+        <v>-0.04</v>
       </c>
       <c r="R23" t="n">
-        <v>0.64</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.41</v>
+        <v>14.38</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.67</v>
+        <v>-0.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.44</v>
+        <v>-1.37</v>
       </c>
       <c r="G24" t="n">
-        <v>14.58</v>
+        <v>14.38</v>
       </c>
       <c r="H24" t="n">
-        <v>0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="I24" t="n">
-        <v>1.18</v>
+        <v>-1.37</v>
       </c>
       <c r="J24" t="n">
-        <v>14.38</v>
+        <v>14.9</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.2</v>
+        <v>0.52</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.37</v>
+        <v>3.62</v>
       </c>
       <c r="M24" t="n">
-        <v>14.38</v>
+        <v>14.75</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2</v>
+        <v>-0.15</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.37</v>
+        <v>-1.01</v>
       </c>
       <c r="P24" t="n">
-        <v>14.38</v>
+        <v>14.75</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.2</v>
+        <v>-0.15</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.37</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.86</v>
+        <v>25.24</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.04</v>
+        <v>0.04</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.15</v>
+        <v>0.16</v>
       </c>
       <c r="G25" t="n">
-        <v>25.2</v>
+        <v>25.24</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.66</v>
+        <v>0.04</v>
       </c>
       <c r="I25" t="n">
-        <v>-2.55</v>
+        <v>0.16</v>
       </c>
       <c r="J25" t="n">
-        <v>25.24</v>
+        <v>24.24</v>
       </c>
       <c r="K25" t="n">
-        <v>0.04</v>
+        <v>-1</v>
       </c>
       <c r="L25" t="n">
-        <v>0.16</v>
+        <v>-3.96</v>
       </c>
       <c r="M25" t="n">
-        <v>25.24</v>
+        <v>23.88</v>
       </c>
       <c r="N25" t="n">
-        <v>0.04</v>
+        <v>-0.36</v>
       </c>
       <c r="O25" t="n">
-        <v>0.16</v>
+        <v>-1.49</v>
       </c>
       <c r="P25" t="n">
-        <v>25.24</v>
+        <v>23.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.04</v>
+        <v>-0.36</v>
       </c>
       <c r="R25" t="n">
-        <v>0.16</v>
+        <v>-1.49</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>35.04</v>
+        <v>37.38</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.12</v>
+        <v>0.02</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.18</v>
+        <v>0.05</v>
       </c>
       <c r="G26" t="n">
-        <v>37.36</v>
+        <v>37.38</v>
       </c>
       <c r="H26" t="n">
-        <v>2.32</v>
+        <v>0.02</v>
       </c>
       <c r="I26" t="n">
-        <v>6.62</v>
+        <v>0.05</v>
       </c>
       <c r="J26" t="n">
-        <v>37.38</v>
+        <v>35.9</v>
       </c>
       <c r="K26" t="n">
-        <v>0.02</v>
+        <v>-1.48</v>
       </c>
       <c r="L26" t="n">
-        <v>0.05</v>
+        <v>-3.96</v>
       </c>
       <c r="M26" t="n">
-        <v>37.38</v>
+        <v>36.82</v>
       </c>
       <c r="N26" t="n">
-        <v>0.02</v>
+        <v>0.92</v>
       </c>
       <c r="O26" t="n">
-        <v>0.05</v>
+        <v>2.56</v>
       </c>
       <c r="P26" t="n">
-        <v>37.38</v>
+        <v>36.82</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.02</v>
+        <v>0.92</v>
       </c>
       <c r="R26" t="n">
-        <v>0.05</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>439.8</v>
+        <v>431</v>
       </c>
       <c r="E27" t="n">
-        <v>3.2</v>
+        <v>-1</v>
       </c>
       <c r="F27" t="n">
-        <v>0.73</v>
+        <v>-0.23</v>
       </c>
       <c r="G27" t="n">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H27" t="n">
-        <v>-7.8</v>
+        <v>-1</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.77</v>
+        <v>-0.23</v>
       </c>
       <c r="J27" t="n">
-        <v>431</v>
+        <v>421.2</v>
       </c>
       <c r="K27" t="n">
-        <v>-1</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.23</v>
+        <v>-2.27</v>
       </c>
       <c r="M27" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="N27" t="n">
-        <v>-1</v>
+        <v>1.8</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.23</v>
+        <v>0.43</v>
       </c>
       <c r="P27" t="n">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="Q27" t="n">
-        <v>-1</v>
+        <v>1.8</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.23</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>107.7</v>
+        <v>106.6</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.65</v>
+        <v>0.38</v>
       </c>
       <c r="G28" t="n">
-        <v>106.2</v>
+        <v>106.6</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.5</v>
+        <v>0.4</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.39</v>
+        <v>0.38</v>
       </c>
       <c r="J28" t="n">
-        <v>106.6</v>
+        <v>104.4</v>
       </c>
       <c r="K28" t="n">
-        <v>0.4</v>
+        <v>-2.2</v>
       </c>
       <c r="L28" t="n">
-        <v>0.38</v>
+        <v>-2.06</v>
       </c>
       <c r="M28" t="n">
-        <v>106.6</v>
+        <v>105.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="O28" t="n">
-        <v>0.38</v>
+        <v>0.96</v>
       </c>
       <c r="P28" t="n">
-        <v>106.6</v>
+        <v>105.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>0.38</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>104.5</v>
+        <v>104.3</v>
       </c>
       <c r="E29" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="F29" t="n">
-        <v>0.77</v>
+        <v>1.16</v>
       </c>
       <c r="G29" t="n">
-        <v>103.1</v>
+        <v>104.3</v>
       </c>
       <c r="H29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="J29" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="K29" t="n">
         <v>-1.4</v>
       </c>
-      <c r="I29" t="n">
+      <c r="L29" t="n">
         <v>-1.34</v>
       </c>
-      <c r="J29" t="n">
-        <v>104.3</v>
-      </c>
-      <c r="K29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="L29" t="n">
-        <v>1.16</v>
-      </c>
       <c r="M29" t="n">
-        <v>104.3</v>
+        <v>102.4</v>
       </c>
       <c r="N29" t="n">
-        <v>1.2</v>
+        <v>-0.5</v>
       </c>
       <c r="O29" t="n">
-        <v>1.16</v>
+        <v>-0.49</v>
       </c>
       <c r="P29" t="n">
-        <v>104.3</v>
+        <v>102.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.2</v>
+        <v>-0.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.16</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>71.90000000000001</v>
+        <v>71.7</v>
       </c>
       <c r="E30" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="F30" t="n">
-        <v>0.35</v>
+        <v>1.77</v>
       </c>
       <c r="G30" t="n">
-        <v>70.45</v>
+        <v>71.7</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.45</v>
+        <v>1.25</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.02</v>
+        <v>1.77</v>
       </c>
       <c r="J30" t="n">
-        <v>71.7</v>
+        <v>70.2</v>
       </c>
       <c r="K30" t="n">
-        <v>1.25</v>
+        <v>-1.5</v>
       </c>
       <c r="L30" t="n">
-        <v>1.77</v>
+        <v>-2.09</v>
       </c>
       <c r="M30" t="n">
-        <v>71.7</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>1.25</v>
+        <v>0.45</v>
       </c>
       <c r="O30" t="n">
-        <v>1.77</v>
+        <v>0.64</v>
       </c>
       <c r="P30" t="n">
-        <v>71.7</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.25</v>
+        <v>0.45</v>
       </c>
       <c r="R30" t="n">
-        <v>1.77</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>85.55</v>
+        <v>85.8</v>
       </c>
       <c r="E31" t="n">
-        <v>0.25</v>
+        <v>0.9</v>
       </c>
       <c r="F31" t="n">
-        <v>0.29</v>
+        <v>1.06</v>
       </c>
       <c r="G31" t="n">
-        <v>84.90000000000001</v>
+        <v>85.8</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.65</v>
+        <v>0.9</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.76</v>
+        <v>1.06</v>
       </c>
       <c r="J31" t="n">
-        <v>85.8</v>
+        <v>83.2</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9</v>
+        <v>-2.6</v>
       </c>
       <c r="L31" t="n">
-        <v>1.06</v>
+        <v>-3.03</v>
       </c>
       <c r="M31" t="n">
-        <v>85.8</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="O31" t="n">
-        <v>1.06</v>
+        <v>0.24</v>
       </c>
       <c r="P31" t="n">
-        <v>85.8</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.06</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="32">
@@ -2375,25 +2375,25 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>61.05</v>
+        <v>60.65</v>
       </c>
       <c r="E32" t="n">
-        <v>-2.3</v>
+        <v>-0.4</v>
       </c>
       <c r="F32" t="n">
-        <v>-3.63</v>
+        <v>-0.66</v>
       </c>
       <c r="G32" t="n">
-        <v>61.05</v>
+        <v>60.65</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>-0.66</v>
       </c>
       <c r="J32" t="n">
-        <v>60.65</v>
+        <v>60.25</v>
       </c>
       <c r="K32" t="n">
         <v>-0.4</v>
@@ -2402,22 +2402,22 @@
         <v>-0.66</v>
       </c>
       <c r="M32" t="n">
-        <v>60.65</v>
+        <v>61.3</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.4</v>
+        <v>1.05</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.66</v>
+        <v>1.74</v>
       </c>
       <c r="P32" t="n">
-        <v>60.65</v>
+        <v>61.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.4</v>
+        <v>1.05</v>
       </c>
       <c r="R32" t="n">
-        <v>-0.66</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>77.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4</v>
+        <v>-0.15</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.51</v>
+        <v>-0.2</v>
       </c>
       <c r="G33" t="n">
-        <v>75.75</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.95</v>
+        <v>-0.15</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.51</v>
+        <v>-0.2</v>
       </c>
       <c r="J33" t="n">
-        <v>75.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.15</v>
+        <v>-1.7</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.2</v>
+        <v>-2.25</v>
       </c>
       <c r="M33" t="n">
-        <v>75.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.15</v>
+        <v>0.2</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.2</v>
+        <v>0.27</v>
       </c>
       <c r="P33" t="n">
-        <v>75.59999999999999</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.15</v>
+        <v>0.2</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.2</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>30.7</v>
+        <v>30.94</v>
       </c>
       <c r="E34" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="F34" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="G34" t="n">
-        <v>30.24</v>
+        <v>30.94</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.46</v>
+        <v>0.7</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.5</v>
+        <v>2.31</v>
       </c>
       <c r="J34" t="n">
-        <v>30.94</v>
+        <v>29.58</v>
       </c>
       <c r="K34" t="n">
-        <v>0.7</v>
+        <v>-1.36</v>
       </c>
       <c r="L34" t="n">
-        <v>2.31</v>
+        <v>-4.4</v>
       </c>
       <c r="M34" t="n">
-        <v>30.94</v>
+        <v>29.5</v>
       </c>
       <c r="N34" t="n">
-        <v>0.7</v>
+        <v>-0.08</v>
       </c>
       <c r="O34" t="n">
-        <v>2.31</v>
+        <v>-0.27</v>
       </c>
       <c r="P34" t="n">
-        <v>30.94</v>
+        <v>29.5</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.7</v>
+        <v>-0.08</v>
       </c>
       <c r="R34" t="n">
-        <v>2.31</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="35">
@@ -2561,40 +2561,40 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.2</v>
+        <v>4.17</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="G35" t="n">
-        <v>4.15</v>
+        <v>4.17</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.19</v>
+        <v>0.48</v>
       </c>
       <c r="J35" t="n">
-        <v>4.17</v>
+        <v>4.07</v>
       </c>
       <c r="K35" t="n">
-        <v>0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="L35" t="n">
-        <v>0.48</v>
+        <v>-2.4</v>
       </c>
       <c r="M35" t="n">
-        <v>4.17</v>
+        <v>4.07</v>
       </c>
       <c r="N35" t="n">
-        <v>0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="O35" t="n">
-        <v>0.48</v>
+        <v>-2.4</v>
       </c>
       <c r="P35" t="n">
         <v>4.07</v>
@@ -2623,40 +2623,40 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>9.09</v>
+        <v>8.98</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="G36" t="n">
-        <v>8.970000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.12</v>
+        <v>0.01</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.32</v>
+        <v>0.11</v>
       </c>
       <c r="J36" t="n">
-        <v>8.98</v>
+        <v>8.75</v>
       </c>
       <c r="K36" t="n">
-        <v>0.01</v>
+        <v>-0.23</v>
       </c>
       <c r="L36" t="n">
-        <v>0.11</v>
+        <v>-2.56</v>
       </c>
       <c r="M36" t="n">
-        <v>8.98</v>
+        <v>8.75</v>
       </c>
       <c r="N36" t="n">
-        <v>0.01</v>
+        <v>-0.23</v>
       </c>
       <c r="O36" t="n">
-        <v>0.11</v>
+        <v>-2.56</v>
       </c>
       <c r="P36" t="n">
         <v>8.75</v>
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>388.6</v>
+        <v>387.8</v>
       </c>
       <c r="E37" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
-        <v>0.05</v>
+        <v>0.26</v>
       </c>
       <c r="G37" t="n">
-        <v>386.8</v>
+        <v>387.8</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.8</v>
+        <v>1</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.46</v>
+        <v>0.26</v>
       </c>
       <c r="J37" t="n">
-        <v>387.8</v>
+        <v>375.8</v>
       </c>
       <c r="K37" t="n">
-        <v>1</v>
+        <v>-12</v>
       </c>
       <c r="L37" t="n">
-        <v>0.26</v>
+        <v>-3.09</v>
       </c>
       <c r="M37" t="n">
-        <v>387.8</v>
+        <v>378</v>
       </c>
       <c r="N37" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="O37" t="n">
-        <v>0.26</v>
+        <v>0.59</v>
       </c>
       <c r="P37" t="n">
-        <v>387.8</v>
+        <v>378</v>
       </c>
       <c r="Q37" t="n">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0.26</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.93</v>
+        <v>11.85</v>
       </c>
       <c r="E38" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="F38" t="n">
-        <v>0.17</v>
+        <v>0.51</v>
       </c>
       <c r="G38" t="n">
-        <v>11.79</v>
+        <v>11.85</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.14</v>
+        <v>0.06</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.17</v>
+        <v>0.51</v>
       </c>
       <c r="J38" t="n">
-        <v>11.85</v>
+        <v>11.38</v>
       </c>
       <c r="K38" t="n">
-        <v>0.06</v>
+        <v>-0.47</v>
       </c>
       <c r="L38" t="n">
-        <v>0.51</v>
+        <v>-3.97</v>
       </c>
       <c r="M38" t="n">
-        <v>11.85</v>
+        <v>11.53</v>
       </c>
       <c r="N38" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="O38" t="n">
-        <v>0.51</v>
+        <v>1.32</v>
       </c>
       <c r="P38" t="n">
-        <v>11.85</v>
+        <v>11.53</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.06</v>
+        <v>0.15</v>
       </c>
       <c r="R38" t="n">
-        <v>0.51</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>484.6</v>
+        <v>484.2</v>
       </c>
       <c r="E39" t="n">
-        <v>-4.8</v>
+        <v>2</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.98</v>
+        <v>0.41</v>
       </c>
       <c r="G39" t="n">
-        <v>482.2</v>
+        <v>484.2</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.4</v>
+        <v>2</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.5</v>
+        <v>0.41</v>
       </c>
       <c r="J39" t="n">
-        <v>484.2</v>
+        <v>476.8</v>
       </c>
       <c r="K39" t="n">
-        <v>2</v>
+        <v>-7.4</v>
       </c>
       <c r="L39" t="n">
-        <v>0.41</v>
+        <v>-1.53</v>
       </c>
       <c r="M39" t="n">
-        <v>484.2</v>
+        <v>483.4</v>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="O39" t="n">
-        <v>0.41</v>
+        <v>1.38</v>
       </c>
       <c r="P39" t="n">
-        <v>484.2</v>
+        <v>483.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>2</v>
+        <v>6.6</v>
       </c>
       <c r="R39" t="n">
-        <v>0.41</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>39.1</v>
+        <v>37.86</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.36</v>
+        <v>0.36</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.91</v>
+        <v>0.96</v>
       </c>
       <c r="G40" t="n">
-        <v>37.5</v>
+        <v>37.86</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.6</v>
+        <v>0.36</v>
       </c>
       <c r="I40" t="n">
-        <v>-4.09</v>
+        <v>0.96</v>
       </c>
       <c r="J40" t="n">
-        <v>37.86</v>
+        <v>36.36</v>
       </c>
       <c r="K40" t="n">
-        <v>0.36</v>
+        <v>-1.5</v>
       </c>
       <c r="L40" t="n">
-        <v>0.96</v>
+        <v>-3.96</v>
       </c>
       <c r="M40" t="n">
-        <v>37.86</v>
+        <v>36.28</v>
       </c>
       <c r="N40" t="n">
-        <v>0.36</v>
+        <v>-0.08</v>
       </c>
       <c r="O40" t="n">
-        <v>0.96</v>
+        <v>-0.22</v>
       </c>
       <c r="P40" t="n">
-        <v>37.86</v>
+        <v>36.28</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.36</v>
+        <v>-0.08</v>
       </c>
       <c r="R40" t="n">
-        <v>0.96</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>32.22</v>
+        <v>31.99</v>
       </c>
       <c r="E41" t="n">
-        <v>0.21</v>
+        <v>-0.17</v>
       </c>
       <c r="F41" t="n">
-        <v>0.66</v>
+        <v>-0.53</v>
       </c>
       <c r="G41" t="n">
-        <v>32.16</v>
+        <v>31.55</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.06</v>
+        <v>-0.44</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.19</v>
+        <v>-1.38</v>
       </c>
       <c r="J41" t="n">
-        <v>31.99</v>
+        <v>31.66</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.17</v>
+        <v>0.11</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.53</v>
+        <v>0.35</v>
       </c>
       <c r="M41" t="n">
-        <v>31.55</v>
+        <v>31.88</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.44</v>
+        <v>0.22</v>
       </c>
       <c r="O41" t="n">
-        <v>-1.38</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P41" t="n">
-        <v>31.55</v>
+        <v>31.88</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.44</v>
+        <v>0.22</v>
       </c>
       <c r="R41" t="n">
-        <v>-1.38</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>78.11</v>
+        <v>77.5</v>
       </c>
       <c r="E42" t="n">
-        <v>0.11</v>
+        <v>-0.88</v>
       </c>
       <c r="F42" t="n">
-        <v>0.14</v>
+        <v>-1.12</v>
       </c>
       <c r="G42" t="n">
-        <v>78.38</v>
+        <v>77.36</v>
       </c>
       <c r="H42" t="n">
-        <v>0.27</v>
+        <v>-0.14</v>
       </c>
       <c r="I42" t="n">
-        <v>0.35</v>
+        <v>-0.18</v>
       </c>
       <c r="J42" t="n">
-        <v>77.5</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.88</v>
+        <v>-0.15</v>
       </c>
       <c r="L42" t="n">
-        <v>-1.12</v>
+        <v>-0.19</v>
       </c>
       <c r="M42" t="n">
-        <v>77.36</v>
+        <v>77.83</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.14</v>
+        <v>0.62</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.18</v>
+        <v>0.8</v>
       </c>
       <c r="P42" t="n">
-        <v>77.36</v>
+        <v>77.83</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.14</v>
+        <v>0.62</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.18</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>43.29</v>
+        <v>42.84</v>
       </c>
       <c r="E43" t="n">
-        <v>0.72</v>
+        <v>-0.48</v>
       </c>
       <c r="F43" t="n">
-        <v>1.69</v>
+        <v>-1.11</v>
       </c>
       <c r="G43" t="n">
-        <v>43.32</v>
+        <v>43.34</v>
       </c>
       <c r="H43" t="n">
-        <v>0.03</v>
+        <v>0.5</v>
       </c>
       <c r="I43" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.17</v>
       </c>
       <c r="J43" t="n">
-        <v>42.84</v>
+        <v>43.11</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.48</v>
+        <v>-0.23</v>
       </c>
       <c r="L43" t="n">
-        <v>-1.11</v>
+        <v>-0.53</v>
       </c>
       <c r="M43" t="n">
-        <v>43.34</v>
+        <v>43.06</v>
       </c>
       <c r="N43" t="n">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
       <c r="O43" t="n">
-        <v>1.17</v>
+        <v>-0.12</v>
       </c>
       <c r="P43" t="n">
-        <v>43.34</v>
+        <v>43.06</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
       <c r="R43" t="n">
-        <v>1.17</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5.88</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J44" t="n">
         <v>5.84</v>
       </c>
-      <c r="E44" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="F44" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="G44" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="H44" t="n">
+      <c r="K44" t="n">
         <v>-0.04</v>
       </c>
-      <c r="I44" t="n">
+      <c r="L44" t="n">
         <v>-0.68</v>
       </c>
-      <c r="J44" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="K44" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="L44" t="n">
-        <v>-0.17</v>
-      </c>
       <c r="M44" t="n">
-        <v>5.88</v>
+        <v>5.92</v>
       </c>
       <c r="N44" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="O44" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="P44" t="n">
-        <v>5.88</v>
+        <v>5.92</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="R44" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="E45" t="n">
         <v>-0.03</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.43</v>
+        <v>-1.44</v>
       </c>
       <c r="G45" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H45" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="I45" t="n">
-        <v>0.48</v>
+        <v>-0.49</v>
       </c>
       <c r="J45" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="L45" t="n">
-        <v>-1.44</v>
+        <v>-0.49</v>
       </c>
       <c r="M45" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.49</v>
+        <v>-1.97</v>
       </c>
       <c r="P45" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.01</v>
+        <v>-0.04</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.49</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.88</v>
+        <v>3.83</v>
       </c>
       <c r="E46" t="n">
-        <v>0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="F46" t="n">
-        <v>1.31</v>
+        <v>-1.03</v>
       </c>
       <c r="G46" t="n">
-        <v>3.87</v>
+        <v>3.78</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.26</v>
+        <v>-1.31</v>
       </c>
       <c r="J46" t="n">
-        <v>3.83</v>
+        <v>3.73</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="L46" t="n">
-        <v>-1.03</v>
+        <v>-1.32</v>
       </c>
       <c r="M46" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="O46" t="n">
-        <v>-1.31</v>
+        <v>0.27</v>
       </c>
       <c r="P46" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="R46" t="n">
-        <v>-1.31</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.87</v>
+        <v>10.92</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>0.65</v>
       </c>
       <c r="G47" t="n">
-        <v>10.85</v>
+        <v>11</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.02</v>
+        <v>0.08</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.18</v>
+        <v>0.73</v>
       </c>
       <c r="J47" t="n">
-        <v>10.92</v>
+        <v>10.97</v>
       </c>
       <c r="K47" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="L47" t="n">
-        <v>0.65</v>
+        <v>-0.27</v>
       </c>
       <c r="M47" t="n">
-        <v>11</v>
+        <v>11.23</v>
       </c>
       <c r="N47" t="n">
-        <v>0.08</v>
+        <v>0.26</v>
       </c>
       <c r="O47" t="n">
-        <v>0.73</v>
+        <v>2.37</v>
       </c>
       <c r="P47" t="n">
-        <v>11</v>
+        <v>11.23</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.08</v>
+        <v>0.26</v>
       </c>
       <c r="R47" t="n">
-        <v>0.73</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="E48" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="F48" t="n">
+        <v>-4.76</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F48" t="n">
-        <v>-1.59</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="I48" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K48" t="n">
-        <v>-0.015</v>
-      </c>
       <c r="L48" t="n">
-        <v>-4.76</v>
+        <v>-1.67</v>
       </c>
       <c r="M48" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>-1.69</v>
       </c>
       <c r="P48" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="49">
@@ -3429,31 +3429,31 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.29</v>
+        <v>4.25</v>
       </c>
       <c r="E49" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F49" t="n">
-        <v>0.23</v>
+        <v>-0.7</v>
       </c>
       <c r="G49" t="n">
-        <v>4.28</v>
+        <v>4.27</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.23</v>
+        <v>0.47</v>
       </c>
       <c r="J49" t="n">
         <v>4.25</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.7</v>
+        <v>-0.47</v>
       </c>
       <c r="M49" t="n">
         <v>4.27</v>
@@ -3491,31 +3491,31 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="E50" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>0.89</v>
+        <v>-0.89</v>
       </c>
       <c r="G50" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.88</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
         <v>1.11</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.89</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
         <v>1.11</v>
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.16</v>
+        <v>5.13</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.58</v>
+        <v>-0.19</v>
       </c>
       <c r="G51" t="n">
-        <v>5.14</v>
+        <v>5.07</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.39</v>
+        <v>-1.17</v>
       </c>
       <c r="J51" t="n">
-        <v>5.13</v>
+        <v>5.02</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.19</v>
+        <v>-0.99</v>
       </c>
       <c r="M51" t="n">
-        <v>5.07</v>
+        <v>5.08</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
       <c r="O51" t="n">
-        <v>-1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P51" t="n">
-        <v>5.07</v>
+        <v>5.08</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
       <c r="R51" t="n">
-        <v>-1.17</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.38</v>
+        <v>11.28</v>
       </c>
       <c r="E52" t="n">
-        <v>0.08</v>
+        <v>-0.19</v>
       </c>
       <c r="F52" t="n">
-        <v>0.71</v>
+        <v>-1.66</v>
       </c>
       <c r="G52" t="n">
-        <v>11.47</v>
+        <v>11.18</v>
       </c>
       <c r="H52" t="n">
-        <v>0.09</v>
+        <v>-0.1</v>
       </c>
       <c r="I52" t="n">
-        <v>0.79</v>
+        <v>-0.89</v>
       </c>
       <c r="J52" t="n">
-        <v>11.28</v>
+        <v>11.04</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.19</v>
+        <v>-0.14</v>
       </c>
       <c r="L52" t="n">
-        <v>-1.66</v>
+        <v>-1.25</v>
       </c>
       <c r="M52" t="n">
-        <v>11.18</v>
+        <v>11.11</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.89</v>
+        <v>0.63</v>
       </c>
       <c r="P52" t="n">
-        <v>11.18</v>
+        <v>11.11</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.89</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7.59</v>
+        <v>7.39</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.67</v>
+        <v>-0.04</v>
       </c>
       <c r="F53" t="n">
-        <v>-8.109999999999999</v>
+        <v>-0.54</v>
       </c>
       <c r="G53" t="n">
-        <v>7.43</v>
+        <v>7.12</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.16</v>
+        <v>-0.27</v>
       </c>
       <c r="I53" t="n">
-        <v>-2.11</v>
+        <v>-3.65</v>
       </c>
       <c r="J53" t="n">
-        <v>7.39</v>
+        <v>7.04</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.54</v>
+        <v>-1.12</v>
       </c>
       <c r="M53" t="n">
-        <v>7.12</v>
+        <v>7.02</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.27</v>
+        <v>-0.02</v>
       </c>
       <c r="O53" t="n">
-        <v>-3.65</v>
+        <v>-0.28</v>
       </c>
       <c r="P53" t="n">
-        <v>7.12</v>
+        <v>7.02</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.27</v>
+        <v>-0.02</v>
       </c>
       <c r="R53" t="n">
-        <v>-3.65</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="54">
@@ -3739,49 +3739,49 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.435</v>
+        <v>0.43</v>
       </c>
       <c r="E54" t="n">
         <v>-0.005</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.14</v>
+        <v>-1.15</v>
       </c>
       <c r="G54" t="n">
-        <v>0.435</v>
+        <v>0.425</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
       <c r="J54" t="n">
         <v>0.43</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.15</v>
+        <v>1.18</v>
       </c>
       <c r="M54" t="n">
-        <v>0.425</v>
+        <v>0.43</v>
       </c>
       <c r="N54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>-1.16</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0.425</v>
+        <v>0.43</v>
       </c>
       <c r="Q54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>-1.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3801,22 +3801,22 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.625</v>
+        <v>0.615</v>
       </c>
       <c r="E55" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0.615</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0.615</v>
@@ -3828,22 +3828,22 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P55" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.39</v>
+        <v>0.375</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -3872,40 +3872,40 @@
         <v>0</v>
       </c>
       <c r="G56" t="n">
-        <v>0.375</v>
+        <v>0.38</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.015</v>
+        <v>0.005</v>
       </c>
       <c r="I56" t="n">
-        <v>-3.85</v>
+        <v>1.33</v>
       </c>
       <c r="J56" t="n">
         <v>0.375</v>
       </c>
       <c r="K56" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>-1.32</v>
       </c>
       <c r="M56" t="n">
-        <v>0.38</v>
+        <v>0.375</v>
       </c>
       <c r="N56" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>0.38</v>
+        <v>0.375</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3928,46 +3928,46 @@
         <v>3.61</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.9</v>
+        <v>0.84</v>
       </c>
       <c r="G57" t="n">
-        <v>3.58</v>
+        <v>3.51</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="I57" t="n">
-        <v>-0.83</v>
+        <v>-2.77</v>
       </c>
       <c r="J57" t="n">
-        <v>3.61</v>
+        <v>3.47</v>
       </c>
       <c r="K57" t="n">
-        <v>0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="L57" t="n">
-        <v>0.84</v>
+        <v>-1.14</v>
       </c>
       <c r="M57" t="n">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="O57" t="n">
-        <v>-2.77</v>
+        <v>0.29</v>
       </c>
       <c r="P57" t="n">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.1</v>
+        <v>0.01</v>
       </c>
       <c r="R57" t="n">
-        <v>-2.77</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="58">
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.079</v>
+        <v>0.081</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -3999,37 +3999,37 @@
         <v>0.081</v>
       </c>
       <c r="H58" t="n">
-        <v>0.002</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0.081</v>
+        <v>0.079</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>-2.47</v>
       </c>
       <c r="M58" t="n">
-        <v>0.081</v>
+        <v>0.078</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
       <c r="P58" t="n">
-        <v>0.081</v>
+        <v>0.078</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22.47</v>
+        <v>22.61</v>
       </c>
       <c r="E59" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.21</v>
       </c>
       <c r="F59" t="n">
-        <v>0.31</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G59" t="n">
-        <v>22.4</v>
+        <v>22.61</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.31</v>
+        <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>22.61</v>
+        <v>20.99</v>
       </c>
       <c r="K59" t="n">
-        <v>0.21</v>
+        <v>-1.62</v>
       </c>
       <c r="L59" t="n">
-        <v>0.9399999999999999</v>
+        <v>-7.16</v>
       </c>
       <c r="M59" t="n">
-        <v>22.61</v>
+        <v>20.75</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="O59" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
       <c r="P59" t="n">
-        <v>22.61</v>
+        <v>20.75</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>-0.24</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.18</v>
+        <v>3.14</v>
       </c>
       <c r="E60" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-1.26</v>
+      </c>
+      <c r="G60" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="H60" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F60" t="n">
-        <v>-0.31</v>
-      </c>
-      <c r="G60" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0</v>
-      </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>-0.32</v>
       </c>
       <c r="J60" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
       <c r="L60" t="n">
-        <v>-1.26</v>
+        <v>0.64</v>
       </c>
       <c r="M60" t="n">
         <v>3.13</v>
       </c>
       <c r="N60" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.32</v>
+        <v>-0.63</v>
       </c>
       <c r="P60" t="n">
         <v>3.13</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.32</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="61">
@@ -4176,46 +4176,46 @@
         <v>0.85</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.02</v>
+        <v>-0.005</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.3</v>
+        <v>-0.58</v>
       </c>
       <c r="G61" t="n">
-        <v>0.855</v>
+        <v>0.835</v>
       </c>
       <c r="H61" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="I61" t="n">
+        <v>-1.76</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K61" t="n">
         <v>0.005</v>
       </c>
-      <c r="I61" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="J61" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="K61" t="n">
-        <v>-0.005</v>
-      </c>
       <c r="L61" t="n">
-        <v>-0.58</v>
+        <v>0.6</v>
       </c>
       <c r="M61" t="n">
-        <v>0.835</v>
+        <v>0.84</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>-1.76</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>0.835</v>
+        <v>0.84</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>-1.76</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-09-30 Close</t>
+          <t>2026-10-01 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-09-30 Change</t>
+          <t>2026-10-01 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-09-30 Change %</t>
+          <t>2026-10-01 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-10-01 Close</t>
+          <t>2026-10-02 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-10-01 Change</t>
+          <t>2026-10-02 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-10-01 Change %</t>
+          <t>2026-10-02 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-10-02 Close</t>
+          <t>2026-10-05 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-10-02 Change</t>
+          <t>2026-10-05 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-10-02 Change %</t>
+          <t>2026-10-05 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-10-05 Close</t>
+          <t>2026-10-06 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-10-05 Change</t>
+          <t>2026-10-06 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-10-05 Change %</t>
+          <t>2026-10-06 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-10-06 Close</t>
+          <t>2026-10-07 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-10-06 Change</t>
+          <t>2026-10-07 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-10-06 Change %</t>
+          <t>2026-10-07 Change %</t>
         </is>
       </c>
     </row>
@@ -586,40 +586,40 @@
         <v>-0.63</v>
       </c>
       <c r="G3" t="n">
-        <v>158</v>
+        <v>149.5</v>
       </c>
       <c r="H3" t="n">
-        <v>-1</v>
+        <v>-8.5</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.63</v>
+        <v>-5.38</v>
       </c>
       <c r="J3" t="n">
-        <v>149.5</v>
+        <v>149.9</v>
       </c>
       <c r="K3" t="n">
-        <v>-8.5</v>
+        <v>0.4</v>
       </c>
       <c r="L3" t="n">
-        <v>-5.38</v>
+        <v>0.27</v>
       </c>
       <c r="M3" t="n">
-        <v>149.9</v>
+        <v>152.8</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="O3" t="n">
-        <v>0.27</v>
+        <v>1.93</v>
       </c>
       <c r="P3" t="n">
         <v>149.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4</v>
+        <v>-2.9</v>
       </c>
       <c r="R3" t="n">
-        <v>0.27</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="4">
@@ -648,40 +648,40 @@
         <v>0.66</v>
       </c>
       <c r="G4" t="n">
-        <v>244.4</v>
+        <v>229.8</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6</v>
+        <v>-14.6</v>
       </c>
       <c r="I4" t="n">
-        <v>0.66</v>
+        <v>-5.97</v>
       </c>
       <c r="J4" t="n">
-        <v>229.8</v>
+        <v>228.6</v>
       </c>
       <c r="K4" t="n">
-        <v>-14.6</v>
+        <v>-1.2</v>
       </c>
       <c r="L4" t="n">
-        <v>-5.97</v>
+        <v>-0.52</v>
       </c>
       <c r="M4" t="n">
-        <v>228.6</v>
+        <v>236.4</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2</v>
+        <v>7.8</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.52</v>
+        <v>3.41</v>
       </c>
       <c r="P4" t="n">
-        <v>228.6</v>
+        <v>230</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.2</v>
+        <v>-6.4</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.52</v>
+        <v>-2.71</v>
       </c>
     </row>
     <row r="5">
@@ -710,40 +710,40 @@
         <v>0.61</v>
       </c>
       <c r="G5" t="n">
-        <v>6.63</v>
+        <v>6.46</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04</v>
+        <v>-0.17</v>
       </c>
       <c r="I5" t="n">
-        <v>0.61</v>
+        <v>-2.56</v>
       </c>
       <c r="J5" t="n">
-        <v>6.46</v>
+        <v>6.49</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.17</v>
+        <v>0.03</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.56</v>
+        <v>0.46</v>
       </c>
       <c r="M5" t="n">
-        <v>6.49</v>
+        <v>6.55</v>
       </c>
       <c r="N5" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="O5" t="n">
-        <v>0.46</v>
+        <v>0.92</v>
       </c>
       <c r="P5" t="n">
-        <v>6.49</v>
+        <v>6.57</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="R5" t="n">
-        <v>0.46</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="6">
@@ -772,34 +772,34 @@
         <v>0.78</v>
       </c>
       <c r="G6" t="n">
-        <v>7.71</v>
+        <v>7.45</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06</v>
+        <v>-0.26</v>
       </c>
       <c r="I6" t="n">
-        <v>0.78</v>
+        <v>-3.37</v>
       </c>
       <c r="J6" t="n">
         <v>7.45</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.26</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.37</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>7.45</v>
+        <v>7.58</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="P6" t="n">
-        <v>7.45</v>
+        <v>7.58</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -834,40 +834,40 @@
         <v>1.33</v>
       </c>
       <c r="G7" t="n">
-        <v>6.09</v>
+        <v>5.92</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08</v>
+        <v>-0.17</v>
       </c>
       <c r="I7" t="n">
-        <v>1.33</v>
+        <v>-2.79</v>
       </c>
       <c r="J7" t="n">
         <v>5.92</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.79</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>5.92</v>
+        <v>6.01</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="P7" t="n">
-        <v>5.92</v>
+        <v>5.99</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="8">
@@ -896,40 +896,40 @@
         <v>1.34</v>
       </c>
       <c r="G8" t="n">
-        <v>9.82</v>
+        <v>9.56</v>
       </c>
       <c r="H8" t="n">
-        <v>0.13</v>
+        <v>-0.26</v>
       </c>
       <c r="I8" t="n">
-        <v>1.34</v>
+        <v>-2.65</v>
       </c>
       <c r="J8" t="n">
-        <v>9.56</v>
+        <v>9.51</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.26</v>
+        <v>-0.05</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.65</v>
+        <v>-0.52</v>
       </c>
       <c r="M8" t="n">
-        <v>9.51</v>
+        <v>9.65</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.05</v>
+        <v>0.14</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.52</v>
+        <v>1.47</v>
       </c>
       <c r="P8" t="n">
-        <v>9.51</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.52</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="9">
@@ -958,34 +958,34 @@
         <v>1.46</v>
       </c>
       <c r="G9" t="n">
-        <v>8.359999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="I9" t="n">
-        <v>1.46</v>
+        <v>-1.67</v>
       </c>
       <c r="J9" t="n">
-        <v>8.220000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.14</v>
+        <v>-0.03</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.67</v>
+        <v>-0.36</v>
       </c>
       <c r="M9" t="n">
-        <v>8.19</v>
+        <v>8.23</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.36</v>
+        <v>0.49</v>
       </c>
       <c r="P9" t="n">
-        <v>8.19</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.03</v>
@@ -1020,40 +1020,40 @@
         <v>0.78</v>
       </c>
       <c r="G10" t="n">
-        <v>51.5</v>
+        <v>50.6</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="I10" t="n">
-        <v>0.78</v>
+        <v>-1.75</v>
       </c>
       <c r="J10" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9</v>
+        <v>0.1</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.75</v>
+        <v>0.2</v>
       </c>
       <c r="M10" t="n">
-        <v>50.7</v>
+        <v>51</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="O10" t="n">
-        <v>0.2</v>
+        <v>0.59</v>
       </c>
       <c r="P10" t="n">
-        <v>50.7</v>
+        <v>50.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="11">
@@ -1082,40 +1082,40 @@
         <v>0.23</v>
       </c>
       <c r="G11" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M11" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="P11" t="n">
         <v>4.42</v>
       </c>
-      <c r="H11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-1.36</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="P11" t="n">
-        <v>4.38</v>
-      </c>
       <c r="Q11" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="R11" t="n">
-        <v>0.46</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="12">
@@ -1144,40 +1144,40 @@
         <v>-0.51</v>
       </c>
       <c r="G12" t="n">
-        <v>9.66</v>
+        <v>9.52</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.05</v>
+        <v>-0.14</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.51</v>
+        <v>-1.45</v>
       </c>
       <c r="J12" t="n">
-        <v>9.52</v>
+        <v>9.56</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.14</v>
+        <v>0.04</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.45</v>
+        <v>0.42</v>
       </c>
       <c r="M12" t="n">
-        <v>9.56</v>
+        <v>9.67</v>
       </c>
       <c r="N12" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="O12" t="n">
-        <v>0.42</v>
+        <v>1.15</v>
       </c>
       <c r="P12" t="n">
-        <v>9.56</v>
+        <v>9.59</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="R12" t="n">
-        <v>0.42</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="13">
@@ -1206,40 +1206,40 @@
         <v>1.1</v>
       </c>
       <c r="G13" t="n">
-        <v>23.96</v>
+        <v>23.52</v>
       </c>
       <c r="H13" t="n">
-        <v>0.26</v>
+        <v>-0.44</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1</v>
+        <v>-1.84</v>
       </c>
       <c r="J13" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="K13" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="M13" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="P13" t="n">
         <v>23.52</v>
       </c>
-      <c r="K13" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-1.84</v>
-      </c>
-      <c r="M13" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="O13" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="P13" t="n">
-        <v>23.42</v>
-      </c>
       <c r="Q13" t="n">
-        <v>-0.1</v>
+        <v>0.08</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.43</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="14">
@@ -1268,40 +1268,40 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="J14" t="n">
         <v>1.85</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.54</v>
       </c>
       <c r="P14" t="n">
         <v>1.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>-0.54</v>
       </c>
     </row>
     <row r="15">
@@ -1330,40 +1330,40 @@
         <v>0.57</v>
       </c>
       <c r="G15" t="n">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="H15" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="I15" t="n">
-        <v>0.57</v>
+        <v>-1.5</v>
       </c>
       <c r="J15" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.5</v>
+        <v>-0.19</v>
       </c>
       <c r="M15" t="n">
         <v>5.24</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>5.24</v>
+        <v>5.29</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.01</v>
+        <v>0.05</v>
       </c>
       <c r="R15" t="n">
-        <v>-0.19</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="16">
@@ -1392,40 +1392,40 @@
         <v>1.63</v>
       </c>
       <c r="G16" t="n">
-        <v>4.36</v>
+        <v>4.3</v>
       </c>
       <c r="H16" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="I16" t="n">
-        <v>1.63</v>
+        <v>-1.38</v>
       </c>
       <c r="J16" t="n">
         <v>4.3</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.38</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="P16" t="n">
-        <v>4.3</v>
+        <v>4.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="17">
@@ -1454,40 +1454,40 @@
         <v>1.9</v>
       </c>
       <c r="G17" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="H17" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="I17" t="n">
-        <v>1.9</v>
+        <v>-0.93</v>
       </c>
       <c r="J17" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.93</v>
+        <v>0.31</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="N17" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="O17" t="n">
-        <v>0.31</v>
+        <v>1.25</v>
       </c>
       <c r="P17" t="n">
-        <v>3.2</v>
+        <v>3.28</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="R17" t="n">
-        <v>0.31</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="18">
@@ -1516,40 +1516,40 @@
         <v>0.33</v>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="H18" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="I18" t="n">
-        <v>0.33</v>
+        <v>-1</v>
       </c>
       <c r="J18" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="L18" t="n">
-        <v>-1</v>
+        <v>-0.67</v>
       </c>
       <c r="M18" t="n">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.67</v>
+        <v>2.03</v>
       </c>
       <c r="P18" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="Q18" t="n">
         <v>-0.02</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.67</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="19">
@@ -1578,40 +1578,40 @@
         <v>-0.28</v>
       </c>
       <c r="G19" t="n">
-        <v>52.75</v>
+        <v>52</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.28</v>
+        <v>-1.42</v>
       </c>
       <c r="J19" t="n">
-        <v>52</v>
+        <v>51.75</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.75</v>
+        <v>-0.25</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.42</v>
+        <v>-0.48</v>
       </c>
       <c r="M19" t="n">
-        <v>51.75</v>
+        <v>51.55</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.48</v>
+        <v>-0.39</v>
       </c>
       <c r="P19" t="n">
-        <v>51.75</v>
+        <v>51.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.25</v>
+        <v>-0.05</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.48</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="20">
@@ -1640,40 +1640,40 @@
         <v>-2.36</v>
       </c>
       <c r="G20" t="n">
-        <v>28.12</v>
+        <v>27.5</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.68</v>
+        <v>-0.62</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.36</v>
+        <v>-2.2</v>
       </c>
       <c r="J20" t="n">
-        <v>27.5</v>
+        <v>27.56</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.62</v>
+        <v>0.06</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.2</v>
+        <v>0.22</v>
       </c>
       <c r="M20" t="n">
-        <v>27.56</v>
+        <v>27.3</v>
       </c>
       <c r="N20" t="n">
-        <v>0.06</v>
+        <v>-0.26</v>
       </c>
       <c r="O20" t="n">
-        <v>0.22</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>27.56</v>
+        <v>27.26</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="R20" t="n">
-        <v>0.22</v>
+        <v>-0.15</v>
       </c>
     </row>
     <row r="21">
@@ -1702,40 +1702,40 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>4.49</v>
+        <v>4.45</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
       <c r="J21" t="n">
-        <v>4.45</v>
+        <v>4.46</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.89</v>
+        <v>0.22</v>
       </c>
       <c r="M21" t="n">
-        <v>4.46</v>
+        <v>4.51</v>
       </c>
       <c r="N21" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="O21" t="n">
-        <v>0.22</v>
+        <v>1.12</v>
       </c>
       <c r="P21" t="n">
-        <v>4.46</v>
+        <v>4.53</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="R21" t="n">
-        <v>0.22</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="22">
@@ -1764,40 +1764,40 @@
         <v>0.13</v>
       </c>
       <c r="G22" t="n">
-        <v>79.45</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="I22" t="n">
-        <v>0.13</v>
+        <v>-0.76</v>
       </c>
       <c r="J22" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M22" t="n">
         <v>78.84999999999999</v>
       </c>
-      <c r="K22" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="L22" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="M22" t="n">
-        <v>78.90000000000001</v>
-      </c>
       <c r="N22" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="O22" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="P22" t="n">
-        <v>78.90000000000001</v>
+        <v>79.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.05</v>
+        <v>0.2</v>
       </c>
       <c r="R22" t="n">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="23">
@@ -1826,40 +1826,40 @@
         <v>0.64</v>
       </c>
       <c r="G23" t="n">
-        <v>21.86</v>
+        <v>21.66</v>
       </c>
       <c r="H23" t="n">
-        <v>0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="I23" t="n">
-        <v>0.64</v>
+        <v>-0.91</v>
       </c>
       <c r="J23" t="n">
-        <v>21.66</v>
+        <v>21.62</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.2</v>
+        <v>-0.04</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.91</v>
+        <v>-0.18</v>
       </c>
       <c r="M23" t="n">
-        <v>21.62</v>
+        <v>21.8</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.04</v>
+        <v>0.18</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.18</v>
+        <v>0.83</v>
       </c>
       <c r="P23" t="n">
-        <v>21.62</v>
+        <v>21.72</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.04</v>
+        <v>-0.08</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.18</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="24">
@@ -1888,40 +1888,40 @@
         <v>-1.37</v>
       </c>
       <c r="G24" t="n">
-        <v>14.38</v>
+        <v>14.9</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2</v>
+        <v>0.52</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.37</v>
+        <v>3.62</v>
       </c>
       <c r="J24" t="n">
-        <v>14.9</v>
+        <v>14.75</v>
       </c>
       <c r="K24" t="n">
-        <v>0.52</v>
+        <v>-0.15</v>
       </c>
       <c r="L24" t="n">
-        <v>3.62</v>
+        <v>-1.01</v>
       </c>
       <c r="M24" t="n">
-        <v>14.75</v>
+        <v>14.94</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.15</v>
+        <v>0.19</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.01</v>
+        <v>1.29</v>
       </c>
       <c r="P24" t="n">
-        <v>14.75</v>
+        <v>14.46</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.15</v>
+        <v>-0.48</v>
       </c>
       <c r="R24" t="n">
-        <v>-1.01</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="25">
@@ -1950,40 +1950,40 @@
         <v>0.16</v>
       </c>
       <c r="G25" t="n">
-        <v>25.24</v>
+        <v>24.24</v>
       </c>
       <c r="H25" t="n">
-        <v>0.04</v>
+        <v>-1</v>
       </c>
       <c r="I25" t="n">
-        <v>0.16</v>
+        <v>-3.96</v>
       </c>
       <c r="J25" t="n">
-        <v>24.24</v>
+        <v>23.88</v>
       </c>
       <c r="K25" t="n">
-        <v>-1</v>
+        <v>-0.36</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.96</v>
+        <v>-1.49</v>
       </c>
       <c r="M25" t="n">
-        <v>23.88</v>
+        <v>24.26</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.36</v>
+        <v>0.38</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.49</v>
+        <v>1.59</v>
       </c>
       <c r="P25" t="n">
-        <v>23.88</v>
+        <v>23.94</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.36</v>
+        <v>-0.32</v>
       </c>
       <c r="R25" t="n">
-        <v>-1.49</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="26">
@@ -2012,40 +2012,40 @@
         <v>0.05</v>
       </c>
       <c r="G26" t="n">
-        <v>37.38</v>
+        <v>35.9</v>
       </c>
       <c r="H26" t="n">
-        <v>0.02</v>
+        <v>-1.48</v>
       </c>
       <c r="I26" t="n">
-        <v>0.05</v>
+        <v>-3.96</v>
       </c>
       <c r="J26" t="n">
-        <v>35.9</v>
+        <v>36.82</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.48</v>
+        <v>0.92</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.96</v>
+        <v>2.56</v>
       </c>
       <c r="M26" t="n">
-        <v>36.82</v>
+        <v>35.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.92</v>
+        <v>-1.22</v>
       </c>
       <c r="O26" t="n">
-        <v>2.56</v>
+        <v>-3.31</v>
       </c>
       <c r="P26" t="n">
-        <v>36.82</v>
+        <v>34.44</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.92</v>
+        <v>-1.16</v>
       </c>
       <c r="R26" t="n">
-        <v>2.56</v>
+        <v>-3.26</v>
       </c>
     </row>
     <row r="27">
@@ -2074,40 +2074,40 @@
         <v>-0.23</v>
       </c>
       <c r="G27" t="n">
-        <v>431</v>
+        <v>421.2</v>
       </c>
       <c r="H27" t="n">
-        <v>-1</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.23</v>
+        <v>-2.27</v>
       </c>
       <c r="J27" t="n">
-        <v>421.2</v>
+        <v>423</v>
       </c>
       <c r="K27" t="n">
-        <v>-9.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.27</v>
+        <v>0.43</v>
       </c>
       <c r="M27" t="n">
-        <v>423</v>
+        <v>428.2</v>
       </c>
       <c r="N27" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="O27" t="n">
-        <v>0.43</v>
+        <v>1.23</v>
       </c>
       <c r="P27" t="n">
-        <v>423</v>
+        <v>420.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.8</v>
+        <v>-7.6</v>
       </c>
       <c r="R27" t="n">
-        <v>0.43</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="28">
@@ -2136,40 +2136,40 @@
         <v>0.38</v>
       </c>
       <c r="G28" t="n">
-        <v>106.6</v>
+        <v>104.4</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4</v>
+        <v>-2.2</v>
       </c>
       <c r="I28" t="n">
-        <v>0.38</v>
+        <v>-2.06</v>
       </c>
       <c r="J28" t="n">
-        <v>104.4</v>
+        <v>105.4</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.2</v>
+        <v>1</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.06</v>
+        <v>0.96</v>
       </c>
       <c r="M28" t="n">
-        <v>105.4</v>
+        <v>108.2</v>
       </c>
       <c r="N28" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
-        <v>0.96</v>
+        <v>2.66</v>
       </c>
       <c r="P28" t="n">
         <v>105.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>1</v>
+        <v>-2.8</v>
       </c>
       <c r="R28" t="n">
-        <v>0.96</v>
+        <v>-2.59</v>
       </c>
     </row>
     <row r="29">
@@ -2198,40 +2198,40 @@
         <v>1.16</v>
       </c>
       <c r="G29" t="n">
-        <v>104.3</v>
+        <v>102.9</v>
       </c>
       <c r="H29" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="J29" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="K29" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="M29" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="N29" t="n">
         <v>1.2</v>
       </c>
-      <c r="I29" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="J29" t="n">
-        <v>102.9</v>
-      </c>
-      <c r="K29" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="L29" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="M29" t="n">
-        <v>102.4</v>
-      </c>
-      <c r="N29" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="O29" t="n">
-        <v>-0.49</v>
+        <v>1.17</v>
       </c>
       <c r="P29" t="n">
-        <v>102.4</v>
+        <v>104.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.5</v>
+        <v>1.3</v>
       </c>
       <c r="R29" t="n">
-        <v>-0.49</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="30">
@@ -2260,40 +2260,40 @@
         <v>1.77</v>
       </c>
       <c r="G30" t="n">
-        <v>71.7</v>
+        <v>70.2</v>
       </c>
       <c r="H30" t="n">
-        <v>1.25</v>
+        <v>-1.5</v>
       </c>
       <c r="I30" t="n">
-        <v>1.77</v>
+        <v>-2.09</v>
       </c>
       <c r="J30" t="n">
-        <v>70.2</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.5</v>
+        <v>0.45</v>
       </c>
       <c r="L30" t="n">
-        <v>-2.09</v>
+        <v>0.64</v>
       </c>
       <c r="M30" t="n">
-        <v>70.65000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="N30" t="n">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="O30" t="n">
-        <v>0.64</v>
+        <v>0.21</v>
       </c>
       <c r="P30" t="n">
-        <v>70.65000000000001</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.45</v>
+        <v>-0.65</v>
       </c>
       <c r="R30" t="n">
-        <v>0.64</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="31">
@@ -2322,40 +2322,40 @@
         <v>1.06</v>
       </c>
       <c r="G31" t="n">
-        <v>85.8</v>
+        <v>83.2</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9</v>
+        <v>-2.6</v>
       </c>
       <c r="I31" t="n">
-        <v>1.06</v>
+        <v>-3.03</v>
       </c>
       <c r="J31" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.6</v>
+        <v>0.2</v>
       </c>
       <c r="L31" t="n">
-        <v>-3.03</v>
+        <v>0.24</v>
       </c>
       <c r="M31" t="n">
-        <v>83.40000000000001</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>0.2</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
-        <v>0.24</v>
+        <v>3.3</v>
       </c>
       <c r="P31" t="n">
-        <v>83.40000000000001</v>
+        <v>84.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.2</v>
+        <v>-1.4</v>
       </c>
       <c r="R31" t="n">
-        <v>0.24</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="32">
@@ -2384,7 +2384,7 @@
         <v>-0.66</v>
       </c>
       <c r="G32" t="n">
-        <v>60.65</v>
+        <v>60.25</v>
       </c>
       <c r="H32" t="n">
         <v>-0.4</v>
@@ -2393,31 +2393,31 @@
         <v>-0.66</v>
       </c>
       <c r="J32" t="n">
-        <v>60.25</v>
+        <v>61.3</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.4</v>
+        <v>1.05</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.66</v>
+        <v>1.74</v>
       </c>
       <c r="M32" t="n">
-        <v>61.3</v>
+        <v>61.55</v>
       </c>
       <c r="N32" t="n">
-        <v>1.05</v>
+        <v>0.25</v>
       </c>
       <c r="O32" t="n">
-        <v>1.74</v>
+        <v>0.41</v>
       </c>
       <c r="P32" t="n">
-        <v>61.3</v>
+        <v>60.9</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.05</v>
+        <v>-0.65</v>
       </c>
       <c r="R32" t="n">
-        <v>1.74</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="33">
@@ -2446,40 +2446,40 @@
         <v>-0.2</v>
       </c>
       <c r="G33" t="n">
-        <v>75.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.15</v>
+        <v>-1.7</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.2</v>
+        <v>-2.25</v>
       </c>
       <c r="J33" t="n">
-        <v>73.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.7</v>
+        <v>0.2</v>
       </c>
       <c r="L33" t="n">
-        <v>-2.25</v>
+        <v>0.27</v>
       </c>
       <c r="M33" t="n">
-        <v>74.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="N33" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="O33" t="n">
-        <v>0.27</v>
+        <v>1.21</v>
       </c>
       <c r="P33" t="n">
-        <v>74.09999999999999</v>
+        <v>74.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.2</v>
+        <v>-0.45</v>
       </c>
       <c r="R33" t="n">
-        <v>0.27</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="34">
@@ -2508,40 +2508,40 @@
         <v>2.31</v>
       </c>
       <c r="G34" t="n">
-        <v>30.94</v>
+        <v>29.58</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7</v>
+        <v>-1.36</v>
       </c>
       <c r="I34" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="J34" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="K34" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="M34" t="n">
+        <v>30.18</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="O34" t="n">
         <v>2.31</v>
       </c>
-      <c r="J34" t="n">
-        <v>29.58</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-1.36</v>
-      </c>
-      <c r="L34" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="M34" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="N34" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="O34" t="n">
-        <v>-0.27</v>
-      </c>
       <c r="P34" t="n">
-        <v>29.5</v>
+        <v>29.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.08</v>
+        <v>-0.48</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.27</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="35">
@@ -2570,40 +2570,40 @@
         <v>0.48</v>
       </c>
       <c r="G35" t="n">
-        <v>4.17</v>
+        <v>4.07</v>
       </c>
       <c r="H35" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I35" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="J35" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="K35" t="n">
         <v>0.02</v>
       </c>
-      <c r="I35" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="J35" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="K35" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="L35" t="n">
-        <v>-2.4</v>
+        <v>0.49</v>
       </c>
       <c r="M35" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="O35" t="n">
-        <v>-2.4</v>
+        <v>0.49</v>
       </c>
       <c r="P35" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="R35" t="n">
-        <v>-2.4</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="36">
@@ -2632,40 +2632,40 @@
         <v>0.11</v>
       </c>
       <c r="G36" t="n">
-        <v>8.98</v>
+        <v>8.75</v>
       </c>
       <c r="H36" t="n">
-        <v>0.01</v>
+        <v>-0.23</v>
       </c>
       <c r="I36" t="n">
-        <v>0.11</v>
+        <v>-2.56</v>
       </c>
       <c r="J36" t="n">
-        <v>8.75</v>
+        <v>8.81</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.23</v>
+        <v>0.06</v>
       </c>
       <c r="L36" t="n">
-        <v>-2.56</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>8.75</v>
+        <v>8.81</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.23</v>
+        <v>0.06</v>
       </c>
       <c r="O36" t="n">
-        <v>-2.56</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P36" t="n">
-        <v>8.75</v>
+        <v>8.81</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.23</v>
+        <v>0.06</v>
       </c>
       <c r="R36" t="n">
-        <v>-2.56</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2694,40 +2694,40 @@
         <v>0.26</v>
       </c>
       <c r="G37" t="n">
-        <v>387.8</v>
+        <v>375.8</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>-12</v>
       </c>
       <c r="I37" t="n">
-        <v>0.26</v>
+        <v>-3.09</v>
       </c>
       <c r="J37" t="n">
-        <v>375.8</v>
+        <v>378</v>
       </c>
       <c r="K37" t="n">
-        <v>-12</v>
+        <v>2.2</v>
       </c>
       <c r="L37" t="n">
-        <v>-3.09</v>
+        <v>0.59</v>
       </c>
       <c r="M37" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="N37" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O37" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="P37" t="n">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.2</v>
+        <v>-1</v>
       </c>
       <c r="R37" t="n">
-        <v>0.59</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="38">
@@ -2756,40 +2756,40 @@
         <v>0.51</v>
       </c>
       <c r="G38" t="n">
-        <v>11.85</v>
+        <v>11.38</v>
       </c>
       <c r="H38" t="n">
-        <v>0.06</v>
+        <v>-0.47</v>
       </c>
       <c r="I38" t="n">
-        <v>0.51</v>
+        <v>-3.97</v>
       </c>
       <c r="J38" t="n">
-        <v>11.38</v>
+        <v>11.53</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.47</v>
+        <v>0.15</v>
       </c>
       <c r="L38" t="n">
-        <v>-3.97</v>
+        <v>1.32</v>
       </c>
       <c r="M38" t="n">
-        <v>11.53</v>
+        <v>11.43</v>
       </c>
       <c r="N38" t="n">
-        <v>0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="O38" t="n">
-        <v>1.32</v>
+        <v>-0.87</v>
       </c>
       <c r="P38" t="n">
-        <v>11.53</v>
+        <v>11.27</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.15</v>
+        <v>-0.16</v>
       </c>
       <c r="R38" t="n">
-        <v>1.32</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="39">
@@ -2818,40 +2818,40 @@
         <v>0.41</v>
       </c>
       <c r="G39" t="n">
-        <v>484.2</v>
+        <v>476.8</v>
       </c>
       <c r="H39" t="n">
-        <v>2</v>
+        <v>-7.4</v>
       </c>
       <c r="I39" t="n">
-        <v>0.41</v>
+        <v>-1.53</v>
       </c>
       <c r="J39" t="n">
-        <v>476.8</v>
+        <v>483.4</v>
       </c>
       <c r="K39" t="n">
-        <v>-7.4</v>
+        <v>6.6</v>
       </c>
       <c r="L39" t="n">
-        <v>-1.53</v>
+        <v>1.38</v>
       </c>
       <c r="M39" t="n">
-        <v>483.4</v>
+        <v>488.6</v>
       </c>
       <c r="N39" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="O39" t="n">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="P39" t="n">
-        <v>483.4</v>
+        <v>486.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>6.6</v>
+        <v>-2.2</v>
       </c>
       <c r="R39" t="n">
-        <v>1.38</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="40">
@@ -2880,40 +2880,40 @@
         <v>0.96</v>
       </c>
       <c r="G40" t="n">
-        <v>37.86</v>
+        <v>36.36</v>
       </c>
       <c r="H40" t="n">
-        <v>0.36</v>
+        <v>-1.5</v>
       </c>
       <c r="I40" t="n">
-        <v>0.96</v>
+        <v>-3.96</v>
       </c>
       <c r="J40" t="n">
-        <v>36.36</v>
+        <v>36.28</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.5</v>
+        <v>-0.08</v>
       </c>
       <c r="L40" t="n">
-        <v>-3.96</v>
+        <v>-0.22</v>
       </c>
       <c r="M40" t="n">
-        <v>36.28</v>
+        <v>37.2</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.08</v>
+        <v>0.92</v>
       </c>
       <c r="O40" t="n">
-        <v>-0.22</v>
+        <v>2.54</v>
       </c>
       <c r="P40" t="n">
-        <v>36.28</v>
+        <v>38</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.08</v>
+        <v>0.8</v>
       </c>
       <c r="R40" t="n">
-        <v>-0.22</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.99</v>
+        <v>31.55</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.17</v>
+        <v>-0.44</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.53</v>
+        <v>-1.38</v>
       </c>
       <c r="G41" t="n">
-        <v>31.55</v>
+        <v>31.66</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.44</v>
+        <v>0.11</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.38</v>
+        <v>0.35</v>
       </c>
       <c r="J41" t="n">
-        <v>31.66</v>
+        <v>31.88</v>
       </c>
       <c r="K41" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="L41" t="n">
-        <v>0.35</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>31.88</v>
+        <v>32.2</v>
       </c>
       <c r="N41" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="O41" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="P41" t="n">
-        <v>31.88</v>
+        <v>30.3</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.22</v>
+        <v>-1.9</v>
       </c>
       <c r="R41" t="n">
-        <v>0.6899999999999999</v>
+        <v>-5.9</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>77.5</v>
+        <v>77.36</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.88</v>
+        <v>-0.14</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.12</v>
+        <v>-0.18</v>
       </c>
       <c r="G42" t="n">
-        <v>77.36</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="J42" t="n">
-        <v>77.20999999999999</v>
+        <v>77.83</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.15</v>
+        <v>0.62</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.19</v>
+        <v>0.8</v>
       </c>
       <c r="M42" t="n">
-        <v>77.83</v>
+        <v>78.56</v>
       </c>
       <c r="N42" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="O42" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="P42" t="n">
-        <v>77.83</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.62</v>
+        <v>-1.07</v>
       </c>
       <c r="R42" t="n">
-        <v>0.8</v>
+        <v>-1.36</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>42.84</v>
+        <v>43.34</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.48</v>
+        <v>0.5</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.11</v>
+        <v>1.17</v>
       </c>
       <c r="G43" t="n">
-        <v>43.34</v>
+        <v>43.11</v>
       </c>
       <c r="H43" t="n">
-        <v>0.5</v>
+        <v>-0.23</v>
       </c>
       <c r="I43" t="n">
-        <v>1.17</v>
+        <v>-0.53</v>
       </c>
       <c r="J43" t="n">
-        <v>43.11</v>
+        <v>43.06</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.23</v>
+        <v>-0.05</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.53</v>
+        <v>-0.12</v>
       </c>
       <c r="M43" t="n">
-        <v>43.06</v>
+        <v>43.72</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.05</v>
+        <v>0.66</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.12</v>
+        <v>1.53</v>
       </c>
       <c r="P43" t="n">
-        <v>43.06</v>
+        <v>42.44</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.05</v>
+        <v>-1.28</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.12</v>
+        <v>-2.93</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.79</v>
+        <v>5.88</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.17</v>
+        <v>1.55</v>
       </c>
       <c r="G44" t="n">
-        <v>5.88</v>
+        <v>5.84</v>
       </c>
       <c r="H44" t="n">
-        <v>0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="I44" t="n">
-        <v>1.55</v>
+        <v>-0.68</v>
       </c>
       <c r="J44" t="n">
-        <v>5.84</v>
+        <v>5.92</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.04</v>
+        <v>0.08</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.68</v>
+        <v>1.37</v>
       </c>
       <c r="M44" t="n">
-        <v>5.92</v>
+        <v>5.87</v>
       </c>
       <c r="N44" t="n">
-        <v>0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="O44" t="n">
-        <v>1.37</v>
+        <v>-0.84</v>
       </c>
       <c r="P44" t="n">
-        <v>5.92</v>
+        <v>5.91</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="R44" t="n">
-        <v>1.37</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="45">
@@ -3181,16 +3181,16 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.44</v>
+        <v>-0.49</v>
       </c>
       <c r="G45" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="H45" t="n">
         <v>-0.01</v>
@@ -3199,31 +3199,31 @@
         <v>-0.49</v>
       </c>
       <c r="J45" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="K45" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="L45" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="N45" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L45" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="M45" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="N45" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="O45" t="n">
-        <v>-1.97</v>
+        <v>-0.5</v>
       </c>
       <c r="P45" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.04</v>
+        <v>0.03</v>
       </c>
       <c r="R45" t="n">
-        <v>-1.97</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="46">
@@ -3243,43 +3243,43 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.03</v>
+        <v>-1.31</v>
       </c>
       <c r="G46" t="n">
-        <v>3.78</v>
+        <v>3.73</v>
       </c>
       <c r="H46" t="n">
         <v>-0.05</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.31</v>
+        <v>-1.32</v>
       </c>
       <c r="J46" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="L46" t="n">
-        <v>-1.32</v>
+        <v>0.27</v>
       </c>
       <c r="M46" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="N46" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="O46" t="n">
-        <v>0.27</v>
+        <v>0.53</v>
       </c>
       <c r="P46" t="n">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="Q46" t="n">
         <v>0.01</v>
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.92</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="F47" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
       <c r="G47" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="J47" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="L47" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="M47" t="n">
         <v>11</v>
       </c>
-      <c r="H47" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="J47" t="n">
-        <v>10.97</v>
-      </c>
-      <c r="K47" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="L47" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="M47" t="n">
-        <v>11.23</v>
-      </c>
       <c r="N47" t="n">
-        <v>0.26</v>
+        <v>-0.23</v>
       </c>
       <c r="O47" t="n">
-        <v>2.37</v>
+        <v>-2.05</v>
       </c>
       <c r="P47" t="n">
-        <v>11.23</v>
+        <v>11.03</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.26</v>
+        <v>0.03</v>
       </c>
       <c r="R47" t="n">
-        <v>2.37</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="48">
@@ -3370,46 +3370,46 @@
         <v>0.3</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.015</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>-4.76</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>0.3</v>
+        <v>0.295</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>-1.67</v>
       </c>
       <c r="J48" t="n">
-        <v>0.295</v>
+        <v>0.29</v>
       </c>
       <c r="K48" t="n">
         <v>-0.005</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.67</v>
+        <v>-1.69</v>
       </c>
       <c r="M48" t="n">
-        <v>0.29</v>
+        <v>0.285</v>
       </c>
       <c r="N48" t="n">
         <v>-0.005</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.69</v>
+        <v>-1.72</v>
       </c>
       <c r="P48" t="n">
-        <v>0.29</v>
+        <v>0.295</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="R48" t="n">
-        <v>-1.69</v>
+        <v>3.51</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G49" t="n">
         <v>4.25</v>
       </c>
-      <c r="E49" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="J49" t="n">
         <v>4.27</v>
       </c>
-      <c r="H49" t="n">
+      <c r="K49" t="n">
         <v>0.02</v>
       </c>
-      <c r="I49" t="n">
+      <c r="L49" t="n">
         <v>0.47</v>
       </c>
-      <c r="J49" t="n">
+      <c r="M49" t="n">
         <v>4.25</v>
       </c>
-      <c r="K49" t="n">
+      <c r="N49" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L49" t="n">
+      <c r="O49" t="n">
         <v>-0.47</v>
       </c>
-      <c r="M49" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0.47</v>
-      </c>
       <c r="P49" t="n">
-        <v>4.27</v>
+        <v>4.3</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="R49" t="n">
-        <v>0.47</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="50">
@@ -3494,10 +3494,10 @@
         <v>1.11</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.89</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
         <v>1.11</v>
@@ -3518,16 +3518,16 @@
         <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="P50" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.13</v>
+        <v>5.07</v>
       </c>
       <c r="E51" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-1.17</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L51" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="M51" t="n">
+        <v>5.07</v>
+      </c>
+      <c r="N51" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F51" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="G51" t="n">
+      <c r="O51" t="n">
+        <v>-0.2</v>
+      </c>
+      <c r="P51" t="n">
         <v>5.07</v>
       </c>
-      <c r="H51" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="I51" t="n">
-        <v>-1.17</v>
-      </c>
-      <c r="J51" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="K51" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="L51" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="M51" t="n">
-        <v>5.08</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="O51" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="P51" t="n">
-        <v>5.08</v>
-      </c>
       <c r="Q51" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.28</v>
+        <v>11.18</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.19</v>
+        <v>-0.1</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.66</v>
+        <v>-0.89</v>
       </c>
       <c r="G52" t="n">
-        <v>11.18</v>
+        <v>11.04</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.1</v>
+        <v>-0.14</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.89</v>
+        <v>-1.25</v>
       </c>
       <c r="J52" t="n">
-        <v>11.04</v>
+        <v>11.11</v>
       </c>
       <c r="K52" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="M52" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="N52" t="n">
         <v>-0.14</v>
       </c>
-      <c r="L52" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="M52" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="O52" t="n">
-        <v>0.63</v>
+        <v>-1.26</v>
       </c>
       <c r="P52" t="n">
-        <v>11.11</v>
+        <v>11.02</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="R52" t="n">
-        <v>0.63</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7.39</v>
+        <v>7.12</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.04</v>
+        <v>-0.27</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.54</v>
+        <v>-3.65</v>
       </c>
       <c r="G53" t="n">
-        <v>7.12</v>
+        <v>7.04</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.27</v>
+        <v>-0.08</v>
       </c>
       <c r="I53" t="n">
-        <v>-3.65</v>
+        <v>-1.12</v>
       </c>
       <c r="J53" t="n">
-        <v>7.04</v>
+        <v>7.02</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="L53" t="n">
-        <v>-1.12</v>
+        <v>-0.28</v>
       </c>
       <c r="M53" t="n">
-        <v>7.02</v>
+        <v>6.99</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.28</v>
+        <v>-0.43</v>
       </c>
       <c r="P53" t="n">
-        <v>7.02</v>
+        <v>7.17</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.02</v>
+        <v>0.18</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.28</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="54">
@@ -3739,31 +3739,31 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="E54" t="n">
         <v>-0.005</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.15</v>
+        <v>-1.16</v>
       </c>
       <c r="G54" t="n">
-        <v>0.425</v>
+        <v>0.43</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.16</v>
+        <v>1.18</v>
       </c>
       <c r="J54" t="n">
         <v>0.43</v>
       </c>
       <c r="K54" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>0.43</v>
@@ -3819,16 +3819,16 @@
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="K55" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>0.62</v>
+        <v>0.625</v>
       </c>
       <c r="N55" t="n">
         <v>0.005</v>
@@ -3840,10 +3840,10 @@
         <v>0.62</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="56">
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F56" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="G56" t="n">
         <v>0.375</v>
       </c>
-      <c r="E56" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.38</v>
-      </c>
       <c r="H56" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="I56" t="n">
-        <v>1.33</v>
+        <v>-1.32</v>
       </c>
       <c r="J56" t="n">
         <v>0.375</v>
       </c>
       <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="N56" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L56" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0</v>
-      </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>-1.33</v>
       </c>
       <c r="P56" t="n">
-        <v>0.375</v>
+        <v>0.355</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>-4.05</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.61</v>
+        <v>3.51</v>
       </c>
       <c r="E57" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="F57" t="n">
-        <v>0.84</v>
+        <v>-2.77</v>
       </c>
       <c r="G57" t="n">
-        <v>3.51</v>
+        <v>3.47</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="I57" t="n">
-        <v>-2.77</v>
+        <v>-1.14</v>
       </c>
       <c r="J57" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.14</v>
+        <v>0.29</v>
       </c>
       <c r="M57" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="N57" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="O57" t="n">
-        <v>0.29</v>
+        <v>3.45</v>
       </c>
       <c r="P57" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3996,31 +3996,31 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.081</v>
+        <v>0.079</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>-2.47</v>
       </c>
       <c r="J58" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="K58" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="L58" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="M58" t="n">
         <v>0.079</v>
       </c>
-      <c r="K58" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="L58" t="n">
-        <v>-2.47</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.078</v>
-      </c>
       <c r="N58" t="n">
-        <v>-0.001</v>
+        <v>0.001</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P58" t="n">
         <v>0.078</v>
@@ -4052,46 +4052,46 @@
         <v>22.61</v>
       </c>
       <c r="E59" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9399999999999999</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
-        <v>22.61</v>
+        <v>20.99</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>-1.62</v>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>-7.16</v>
       </c>
       <c r="J59" t="n">
-        <v>20.99</v>
+        <v>20.75</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.62</v>
+        <v>-0.24</v>
       </c>
       <c r="L59" t="n">
-        <v>-7.16</v>
+        <v>-1.14</v>
       </c>
       <c r="M59" t="n">
-        <v>20.75</v>
+        <v>21.04</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.24</v>
+        <v>0.29</v>
       </c>
       <c r="O59" t="n">
-        <v>-1.14</v>
+        <v>1.4</v>
       </c>
       <c r="P59" t="n">
-        <v>20.75</v>
+        <v>21.29</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.24</v>
+        <v>0.25</v>
       </c>
       <c r="R59" t="n">
-        <v>-1.14</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.26</v>
+        <v>-0.32</v>
       </c>
       <c r="G60" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="J60" t="n">
         <v>3.13</v>
       </c>
-      <c r="H60" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="I60" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="J60" t="n">
-        <v>3.15</v>
-      </c>
       <c r="K60" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="L60" t="n">
-        <v>0.64</v>
+        <v>-0.63</v>
       </c>
       <c r="M60" t="n">
         <v>3.13</v>
       </c>
       <c r="N60" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="R60" t="n">
-        <v>-0.63</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="61">
@@ -4173,31 +4173,31 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.85</v>
+        <v>0.835</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.005</v>
+        <v>-0.015</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.58</v>
+        <v>-1.76</v>
       </c>
       <c r="G61" t="n">
-        <v>0.835</v>
+        <v>0.84</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.015</v>
+        <v>0.005</v>
       </c>
       <c r="I61" t="n">
-        <v>-1.76</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0.84</v>
       </c>
       <c r="K61" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
         <v>0.84</v>
@@ -4209,13 +4209,13 @@
         <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>0.84</v>
+        <v>0.855</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-10-01 Close</t>
+          <t>2026-10-02 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-10-01 Change</t>
+          <t>2026-10-02 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-10-01 Change %</t>
+          <t>2026-10-02 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-10-02 Close</t>
+          <t>2026-10-05 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-10-02 Change</t>
+          <t>2026-10-05 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-10-02 Change %</t>
+          <t>2026-10-05 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-10-05 Close</t>
+          <t>2026-10-06 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-10-05 Change</t>
+          <t>2026-10-06 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-10-05 Change %</t>
+          <t>2026-10-06 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-10-06 Close</t>
+          <t>2026-10-07 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-10-06 Change</t>
+          <t>2026-10-07 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-10-06 Change %</t>
+          <t>2026-10-07 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-10-07 Close</t>
+          <t>2026-10-08 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-10-07 Change</t>
+          <t>2026-10-08 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-10-07 Change %</t>
+          <t>2026-10-08 Change %</t>
         </is>
       </c>
     </row>
@@ -577,40 +577,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>158</v>
+        <v>149.5</v>
       </c>
       <c r="E3" t="n">
-        <v>-1</v>
+        <v>-8.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.63</v>
+        <v>-5.38</v>
       </c>
       <c r="G3" t="n">
-        <v>149.5</v>
+        <v>149.9</v>
       </c>
       <c r="H3" t="n">
-        <v>-8.5</v>
+        <v>0.4</v>
       </c>
       <c r="I3" t="n">
-        <v>-5.38</v>
+        <v>0.27</v>
       </c>
       <c r="J3" t="n">
+        <v>152.8</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="M3" t="n">
         <v>149.9</v>
       </c>
-      <c r="K3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="M3" t="n">
-        <v>152.8</v>
-      </c>
       <c r="N3" t="n">
-        <v>2.9</v>
+        <v>-2.9</v>
       </c>
       <c r="O3" t="n">
-        <v>1.93</v>
+        <v>-1.9</v>
       </c>
       <c r="P3" t="n">
         <v>149.9</v>
@@ -639,40 +639,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>244.4</v>
+        <v>229.8</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6</v>
+        <v>-14.6</v>
       </c>
       <c r="F4" t="n">
-        <v>0.66</v>
+        <v>-5.97</v>
       </c>
       <c r="G4" t="n">
-        <v>229.8</v>
+        <v>228.6</v>
       </c>
       <c r="H4" t="n">
-        <v>-14.6</v>
+        <v>-1.2</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.97</v>
+        <v>-0.52</v>
       </c>
       <c r="J4" t="n">
-        <v>228.6</v>
+        <v>236.4</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2</v>
+        <v>7.8</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.52</v>
+        <v>3.41</v>
       </c>
       <c r="M4" t="n">
-        <v>236.4</v>
+        <v>230</v>
       </c>
       <c r="N4" t="n">
-        <v>7.8</v>
+        <v>-6.4</v>
       </c>
       <c r="O4" t="n">
-        <v>3.41</v>
+        <v>-2.71</v>
       </c>
       <c r="P4" t="n">
         <v>230</v>
@@ -701,40 +701,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.63</v>
+        <v>6.46</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04</v>
+        <v>-0.17</v>
       </c>
       <c r="F5" t="n">
-        <v>0.61</v>
+        <v>-2.56</v>
       </c>
       <c r="G5" t="n">
-        <v>6.46</v>
+        <v>6.49</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.17</v>
+        <v>0.03</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.56</v>
+        <v>0.46</v>
       </c>
       <c r="J5" t="n">
-        <v>6.49</v>
+        <v>6.55</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="L5" t="n">
-        <v>0.46</v>
+        <v>0.92</v>
       </c>
       <c r="M5" t="n">
-        <v>6.55</v>
+        <v>6.57</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="O5" t="n">
-        <v>0.92</v>
+        <v>0.31</v>
       </c>
       <c r="P5" t="n">
         <v>6.57</v>
@@ -763,40 +763,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.71</v>
+        <v>7.45</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06</v>
+        <v>-0.26</v>
       </c>
       <c r="F6" t="n">
-        <v>0.78</v>
+        <v>-3.37</v>
       </c>
       <c r="G6" t="n">
         <v>7.45</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.26</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-3.37</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>7.45</v>
+        <v>7.58</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M6" t="n">
         <v>7.58</v>
       </c>
       <c r="N6" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>7.58</v>
@@ -825,40 +825,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.09</v>
+        <v>5.92</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08</v>
+        <v>-0.17</v>
       </c>
       <c r="F7" t="n">
-        <v>1.33</v>
+        <v>-2.79</v>
       </c>
       <c r="G7" t="n">
         <v>5.92</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.79</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>5.92</v>
+        <v>6.01</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M7" t="n">
-        <v>6.01</v>
+        <v>5.99</v>
       </c>
       <c r="N7" t="n">
-        <v>0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="O7" t="n">
-        <v>1.52</v>
+        <v>-0.33</v>
       </c>
       <c r="P7" t="n">
         <v>5.99</v>
@@ -887,40 +887,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.82</v>
+        <v>9.56</v>
       </c>
       <c r="E8" t="n">
-        <v>0.13</v>
+        <v>-0.26</v>
       </c>
       <c r="F8" t="n">
-        <v>1.34</v>
+        <v>-2.65</v>
       </c>
       <c r="G8" t="n">
-        <v>9.56</v>
+        <v>9.51</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.26</v>
+        <v>-0.05</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.65</v>
+        <v>-0.52</v>
       </c>
       <c r="J8" t="n">
-        <v>9.51</v>
+        <v>9.65</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.05</v>
+        <v>0.14</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.52</v>
+        <v>1.47</v>
       </c>
       <c r="M8" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.14</v>
+        <v>-0.02</v>
       </c>
       <c r="O8" t="n">
-        <v>1.47</v>
+        <v>-0.21</v>
       </c>
       <c r="P8" t="n">
         <v>9.630000000000001</v>
@@ -949,40 +949,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.359999999999999</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.12</v>
+        <v>-0.14</v>
       </c>
       <c r="F9" t="n">
-        <v>1.46</v>
+        <v>-1.67</v>
       </c>
       <c r="G9" t="n">
-        <v>8.220000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.14</v>
+        <v>-0.03</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.67</v>
+        <v>-0.36</v>
       </c>
       <c r="J9" t="n">
-        <v>8.19</v>
+        <v>8.23</v>
       </c>
       <c r="K9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="N9" t="n">
         <v>-0.03</v>
       </c>
-      <c r="L9" t="n">
+      <c r="O9" t="n">
         <v>-0.36</v>
-      </c>
-      <c r="M9" t="n">
-        <v>8.23</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.49</v>
       </c>
       <c r="P9" t="n">
         <v>8.199999999999999</v>
@@ -1011,40 +1011,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51.5</v>
+        <v>50.6</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4</v>
+        <v>-0.9</v>
       </c>
       <c r="F10" t="n">
-        <v>0.78</v>
+        <v>-1.75</v>
       </c>
       <c r="G10" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9</v>
+        <v>0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.75</v>
+        <v>0.2</v>
       </c>
       <c r="J10" t="n">
-        <v>50.7</v>
+        <v>51</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2</v>
+        <v>0.59</v>
       </c>
       <c r="M10" t="n">
-        <v>51</v>
+        <v>50.95</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3</v>
+        <v>-0.05</v>
       </c>
       <c r="O10" t="n">
-        <v>0.59</v>
+        <v>-0.1</v>
       </c>
       <c r="P10" t="n">
         <v>50.95</v>
@@ -1073,40 +1073,40 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-1.36</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.38</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="M11" t="n">
         <v>4.42</v>
       </c>
-      <c r="E11" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4.36</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="I11" t="n">
-        <v>-1.36</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.39</v>
-      </c>
       <c r="N11" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="O11" t="n">
-        <v>0.23</v>
+        <v>0.68</v>
       </c>
       <c r="P11" t="n">
         <v>4.42</v>
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.66</v>
+        <v>9.52</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.05</v>
+        <v>-0.14</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.51</v>
+        <v>-1.45</v>
       </c>
       <c r="G12" t="n">
-        <v>9.52</v>
+        <v>9.56</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.14</v>
+        <v>0.04</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.45</v>
+        <v>0.42</v>
       </c>
       <c r="J12" t="n">
-        <v>9.56</v>
+        <v>9.67</v>
       </c>
       <c r="K12" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="L12" t="n">
-        <v>0.42</v>
+        <v>1.15</v>
       </c>
       <c r="M12" t="n">
-        <v>9.67</v>
+        <v>9.59</v>
       </c>
       <c r="N12" t="n">
-        <v>0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="O12" t="n">
-        <v>1.15</v>
+        <v>-0.83</v>
       </c>
       <c r="P12" t="n">
         <v>9.59</v>
@@ -1197,40 +1197,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23.96</v>
+        <v>23.52</v>
       </c>
       <c r="E13" t="n">
-        <v>0.26</v>
+        <v>-0.44</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1</v>
+        <v>-1.84</v>
       </c>
       <c r="G13" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="J13" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="M13" t="n">
         <v>23.52</v>
       </c>
-      <c r="H13" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-1.84</v>
-      </c>
-      <c r="J13" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="K13" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="M13" t="n">
-        <v>23.44</v>
-      </c>
       <c r="N13" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="O13" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="P13" t="n">
         <v>23.52</v>
@@ -1259,40 +1259,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="G14" t="n">
         <v>1.85</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M14" t="n">
         <v>1.85</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.86</v>
-      </c>
       <c r="N14" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="O14" t="n">
-        <v>0.54</v>
+        <v>-0.54</v>
       </c>
       <c r="P14" t="n">
         <v>1.85</v>
@@ -1321,40 +1321,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.33</v>
+        <v>5.25</v>
       </c>
       <c r="E15" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="F15" t="n">
-        <v>0.57</v>
+        <v>-1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.5</v>
+        <v>-0.19</v>
       </c>
       <c r="J15" t="n">
         <v>5.24</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>5.24</v>
+        <v>5.29</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="P15" t="n">
         <v>5.29</v>
@@ -1383,40 +1383,40 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.36</v>
+        <v>4.3</v>
       </c>
       <c r="E16" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="F16" t="n">
-        <v>1.63</v>
+        <v>-1.38</v>
       </c>
       <c r="G16" t="n">
         <v>4.3</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.38</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="M16" t="n">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="N16" t="n">
         <v>0.02</v>
       </c>
       <c r="O16" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="P16" t="n">
         <v>4.34</v>
@@ -1445,40 +1445,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="E17" t="n">
-        <v>0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="F17" t="n">
-        <v>1.9</v>
+        <v>-0.93</v>
       </c>
       <c r="G17" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.93</v>
+        <v>0.31</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="L17" t="n">
-        <v>0.31</v>
+        <v>1.25</v>
       </c>
       <c r="M17" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="N17" t="n">
         <v>0.04</v>
       </c>
       <c r="O17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P17" t="n">
         <v>3.28</v>
@@ -1507,40 +1507,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="E18" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F18" t="n">
-        <v>0.33</v>
+        <v>-1</v>
       </c>
       <c r="G18" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="I18" t="n">
-        <v>-1</v>
+        <v>-0.67</v>
       </c>
       <c r="J18" t="n">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="K18" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="N18" t="n">
         <v>-0.02</v>
       </c>
-      <c r="L18" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0.06</v>
-      </c>
       <c r="O18" t="n">
-        <v>2.03</v>
+        <v>-0.66</v>
       </c>
       <c r="P18" t="n">
         <v>2.99</v>
@@ -1569,40 +1569,40 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>52.75</v>
+        <v>52</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.15</v>
+        <v>-0.75</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.28</v>
+        <v>-1.42</v>
       </c>
       <c r="G19" t="n">
-        <v>52</v>
+        <v>51.75</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.75</v>
+        <v>-0.25</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.42</v>
+        <v>-0.48</v>
       </c>
       <c r="J19" t="n">
-        <v>51.75</v>
+        <v>51.55</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.48</v>
+        <v>-0.39</v>
       </c>
       <c r="M19" t="n">
-        <v>51.55</v>
+        <v>51.5</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2</v>
+        <v>-0.05</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.39</v>
+        <v>-0.1</v>
       </c>
       <c r="P19" t="n">
         <v>51.5</v>
@@ -1631,40 +1631,40 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>28.12</v>
+        <v>27.5</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.68</v>
+        <v>-0.62</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.36</v>
+        <v>-2.2</v>
       </c>
       <c r="G20" t="n">
-        <v>27.5</v>
+        <v>27.56</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.62</v>
+        <v>0.06</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.2</v>
+        <v>0.22</v>
       </c>
       <c r="J20" t="n">
-        <v>27.56</v>
+        <v>27.3</v>
       </c>
       <c r="K20" t="n">
-        <v>0.06</v>
+        <v>-0.26</v>
       </c>
       <c r="L20" t="n">
-        <v>0.22</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>27.3</v>
+        <v>27.26</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.26</v>
+        <v>-0.04</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.15</v>
       </c>
       <c r="P20" t="n">
         <v>27.26</v>
@@ -1693,40 +1693,40 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.49</v>
+        <v>4.45</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
       <c r="G21" t="n">
-        <v>4.45</v>
+        <v>4.46</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.89</v>
+        <v>0.22</v>
       </c>
       <c r="J21" t="n">
-        <v>4.46</v>
+        <v>4.51</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="L21" t="n">
-        <v>0.22</v>
+        <v>1.12</v>
       </c>
       <c r="M21" t="n">
-        <v>4.51</v>
+        <v>4.53</v>
       </c>
       <c r="N21" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="O21" t="n">
-        <v>1.12</v>
+        <v>0.44</v>
       </c>
       <c r="P21" t="n">
         <v>4.53</v>
@@ -1755,40 +1755,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79.45</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
       <c r="F22" t="n">
-        <v>0.13</v>
+        <v>-0.76</v>
       </c>
       <c r="G22" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="J22" t="n">
         <v>78.84999999999999</v>
       </c>
-      <c r="H22" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="I22" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="J22" t="n">
-        <v>78.90000000000001</v>
-      </c>
       <c r="K22" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="M22" t="n">
-        <v>78.84999999999999</v>
+        <v>79.05</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.05</v>
+        <v>0.2</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.06</v>
+        <v>0.25</v>
       </c>
       <c r="P22" t="n">
         <v>79.05</v>
@@ -1817,40 +1817,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>21.86</v>
+        <v>21.66</v>
       </c>
       <c r="E23" t="n">
-        <v>0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="F23" t="n">
-        <v>0.64</v>
+        <v>-0.91</v>
       </c>
       <c r="G23" t="n">
-        <v>21.66</v>
+        <v>21.62</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.2</v>
+        <v>-0.04</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.91</v>
+        <v>-0.18</v>
       </c>
       <c r="J23" t="n">
-        <v>21.62</v>
+        <v>21.8</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.04</v>
+        <v>0.18</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.18</v>
+        <v>0.83</v>
       </c>
       <c r="M23" t="n">
-        <v>21.8</v>
+        <v>21.72</v>
       </c>
       <c r="N23" t="n">
-        <v>0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="O23" t="n">
-        <v>0.83</v>
+        <v>-0.37</v>
       </c>
       <c r="P23" t="n">
         <v>21.72</v>
@@ -1879,40 +1879,40 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.38</v>
+        <v>14.9</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.2</v>
+        <v>0.52</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.37</v>
+        <v>3.62</v>
       </c>
       <c r="G24" t="n">
-        <v>14.9</v>
+        <v>14.75</v>
       </c>
       <c r="H24" t="n">
-        <v>0.52</v>
+        <v>-0.15</v>
       </c>
       <c r="I24" t="n">
-        <v>3.62</v>
+        <v>-1.01</v>
       </c>
       <c r="J24" t="n">
-        <v>14.75</v>
+        <v>14.94</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.15</v>
+        <v>0.19</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M24" t="n">
-        <v>14.94</v>
+        <v>14.46</v>
       </c>
       <c r="N24" t="n">
-        <v>0.19</v>
+        <v>-0.48</v>
       </c>
       <c r="O24" t="n">
-        <v>1.29</v>
+        <v>-3.21</v>
       </c>
       <c r="P24" t="n">
         <v>14.46</v>
@@ -1941,40 +1941,40 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.24</v>
+        <v>24.24</v>
       </c>
       <c r="E25" t="n">
-        <v>0.04</v>
+        <v>-1</v>
       </c>
       <c r="F25" t="n">
-        <v>0.16</v>
+        <v>-3.96</v>
       </c>
       <c r="G25" t="n">
-        <v>24.24</v>
+        <v>23.88</v>
       </c>
       <c r="H25" t="n">
-        <v>-1</v>
+        <v>-0.36</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.96</v>
+        <v>-1.49</v>
       </c>
       <c r="J25" t="n">
-        <v>23.88</v>
+        <v>24.26</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.36</v>
+        <v>0.38</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.49</v>
+        <v>1.59</v>
       </c>
       <c r="M25" t="n">
-        <v>24.26</v>
+        <v>23.94</v>
       </c>
       <c r="N25" t="n">
-        <v>0.38</v>
+        <v>-0.32</v>
       </c>
       <c r="O25" t="n">
-        <v>1.59</v>
+        <v>-1.32</v>
       </c>
       <c r="P25" t="n">
         <v>23.94</v>
@@ -2003,40 +2003,40 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>37.38</v>
+        <v>35.9</v>
       </c>
       <c r="E26" t="n">
-        <v>0.02</v>
+        <v>-1.48</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05</v>
+        <v>-3.96</v>
       </c>
       <c r="G26" t="n">
-        <v>35.9</v>
+        <v>36.82</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.48</v>
+        <v>0.92</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.96</v>
+        <v>2.56</v>
       </c>
       <c r="J26" t="n">
-        <v>36.82</v>
+        <v>35.6</v>
       </c>
       <c r="K26" t="n">
-        <v>0.92</v>
+        <v>-1.22</v>
       </c>
       <c r="L26" t="n">
-        <v>2.56</v>
+        <v>-3.31</v>
       </c>
       <c r="M26" t="n">
-        <v>35.6</v>
+        <v>34.44</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.22</v>
+        <v>-1.16</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.31</v>
+        <v>-3.26</v>
       </c>
       <c r="P26" t="n">
         <v>34.44</v>
@@ -2065,40 +2065,40 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>431</v>
+        <v>421.2</v>
       </c>
       <c r="E27" t="n">
-        <v>-1</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.23</v>
+        <v>-2.27</v>
       </c>
       <c r="G27" t="n">
-        <v>421.2</v>
+        <v>423</v>
       </c>
       <c r="H27" t="n">
-        <v>-9.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="I27" t="n">
-        <v>-2.27</v>
+        <v>0.43</v>
       </c>
       <c r="J27" t="n">
-        <v>423</v>
+        <v>428.2</v>
       </c>
       <c r="K27" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="L27" t="n">
-        <v>0.43</v>
+        <v>1.23</v>
       </c>
       <c r="M27" t="n">
-        <v>428.2</v>
+        <v>420.6</v>
       </c>
       <c r="N27" t="n">
-        <v>5.2</v>
+        <v>-7.6</v>
       </c>
       <c r="O27" t="n">
-        <v>1.23</v>
+        <v>-1.77</v>
       </c>
       <c r="P27" t="n">
         <v>420.6</v>
@@ -2127,40 +2127,40 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>106.6</v>
+        <v>104.4</v>
       </c>
       <c r="E28" t="n">
-        <v>0.4</v>
+        <v>-2.2</v>
       </c>
       <c r="F28" t="n">
-        <v>0.38</v>
+        <v>-2.06</v>
       </c>
       <c r="G28" t="n">
-        <v>104.4</v>
+        <v>105.4</v>
       </c>
       <c r="H28" t="n">
-        <v>-2.2</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>-2.06</v>
+        <v>0.96</v>
       </c>
       <c r="J28" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="M28" t="n">
         <v>105.4</v>
       </c>
-      <c r="K28" t="n">
-        <v>1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="M28" t="n">
-        <v>108.2</v>
-      </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>-2.8</v>
       </c>
       <c r="O28" t="n">
-        <v>2.66</v>
+        <v>-2.59</v>
       </c>
       <c r="P28" t="n">
         <v>105.4</v>
@@ -2189,40 +2189,40 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>104.3</v>
+        <v>102.9</v>
       </c>
       <c r="E29" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-1.34</v>
+      </c>
+      <c r="G29" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-0.49</v>
+      </c>
+      <c r="J29" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="K29" t="n">
         <v>1.2</v>
       </c>
-      <c r="F29" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="G29" t="n">
-        <v>102.9</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-1.4</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-1.34</v>
-      </c>
-      <c r="J29" t="n">
-        <v>102.4</v>
-      </c>
-      <c r="K29" t="n">
-        <v>-0.5</v>
-      </c>
       <c r="L29" t="n">
-        <v>-0.49</v>
+        <v>1.17</v>
       </c>
       <c r="M29" t="n">
-        <v>103.6</v>
+        <v>104.9</v>
       </c>
       <c r="N29" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="P29" t="n">
         <v>104.9</v>
@@ -2251,40 +2251,40 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>71.7</v>
+        <v>70.2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.25</v>
+        <v>-1.5</v>
       </c>
       <c r="F30" t="n">
-        <v>1.77</v>
+        <v>-2.09</v>
       </c>
       <c r="G30" t="n">
-        <v>70.2</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.5</v>
+        <v>0.45</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.09</v>
+        <v>0.64</v>
       </c>
       <c r="J30" t="n">
-        <v>70.65000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="K30" t="n">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="L30" t="n">
-        <v>0.64</v>
+        <v>0.21</v>
       </c>
       <c r="M30" t="n">
-        <v>70.8</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>0.15</v>
+        <v>-0.65</v>
       </c>
       <c r="O30" t="n">
-        <v>0.21</v>
+        <v>-0.92</v>
       </c>
       <c r="P30" t="n">
         <v>70.15000000000001</v>
@@ -2313,40 +2313,40 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>85.8</v>
+        <v>83.2</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9</v>
+        <v>-2.6</v>
       </c>
       <c r="F31" t="n">
-        <v>1.06</v>
+        <v>-3.03</v>
       </c>
       <c r="G31" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.6</v>
+        <v>0.2</v>
       </c>
       <c r="I31" t="n">
-        <v>-3.03</v>
+        <v>0.24</v>
       </c>
       <c r="J31" t="n">
-        <v>83.40000000000001</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>0.2</v>
+        <v>2.75</v>
       </c>
       <c r="L31" t="n">
-        <v>0.24</v>
+        <v>3.3</v>
       </c>
       <c r="M31" t="n">
-        <v>86.15000000000001</v>
+        <v>84.75</v>
       </c>
       <c r="N31" t="n">
-        <v>2.75</v>
+        <v>-1.4</v>
       </c>
       <c r="O31" t="n">
-        <v>3.3</v>
+        <v>-1.63</v>
       </c>
       <c r="P31" t="n">
         <v>84.75</v>
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>60.65</v>
+        <v>60.25</v>
       </c>
       <c r="E32" t="n">
         <v>-0.4</v>
@@ -2384,31 +2384,31 @@
         <v>-0.66</v>
       </c>
       <c r="G32" t="n">
-        <v>60.25</v>
+        <v>61.3</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.4</v>
+        <v>1.05</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.66</v>
+        <v>1.74</v>
       </c>
       <c r="J32" t="n">
-        <v>61.3</v>
+        <v>61.55</v>
       </c>
       <c r="K32" t="n">
-        <v>1.05</v>
+        <v>0.25</v>
       </c>
       <c r="L32" t="n">
-        <v>1.74</v>
+        <v>0.41</v>
       </c>
       <c r="M32" t="n">
-        <v>61.55</v>
+        <v>60.9</v>
       </c>
       <c r="N32" t="n">
-        <v>0.25</v>
+        <v>-0.65</v>
       </c>
       <c r="O32" t="n">
-        <v>0.41</v>
+        <v>-1.06</v>
       </c>
       <c r="P32" t="n">
         <v>60.9</v>
@@ -2437,40 +2437,40 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>75.59999999999999</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.15</v>
+        <v>-1.7</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.2</v>
+        <v>-2.25</v>
       </c>
       <c r="G33" t="n">
-        <v>73.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.7</v>
+        <v>0.2</v>
       </c>
       <c r="I33" t="n">
-        <v>-2.25</v>
+        <v>0.27</v>
       </c>
       <c r="J33" t="n">
-        <v>74.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="K33" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="L33" t="n">
-        <v>0.27</v>
+        <v>1.21</v>
       </c>
       <c r="M33" t="n">
-        <v>75</v>
+        <v>74.55</v>
       </c>
       <c r="N33" t="n">
-        <v>0.9</v>
+        <v>-0.45</v>
       </c>
       <c r="O33" t="n">
-        <v>1.21</v>
+        <v>-0.6</v>
       </c>
       <c r="P33" t="n">
         <v>74.55</v>
@@ -2499,40 +2499,40 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>30.94</v>
+        <v>29.58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.7</v>
+        <v>-1.36</v>
       </c>
       <c r="F34" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="G34" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="H34" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="I34" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="J34" t="n">
+        <v>30.18</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="L34" t="n">
         <v>2.31</v>
       </c>
-      <c r="G34" t="n">
-        <v>29.58</v>
-      </c>
-      <c r="H34" t="n">
-        <v>-1.36</v>
-      </c>
-      <c r="I34" t="n">
-        <v>-4.4</v>
-      </c>
-      <c r="J34" t="n">
-        <v>29.5</v>
-      </c>
-      <c r="K34" t="n">
-        <v>-0.08</v>
-      </c>
-      <c r="L34" t="n">
-        <v>-0.27</v>
-      </c>
       <c r="M34" t="n">
-        <v>30.18</v>
+        <v>29.7</v>
       </c>
       <c r="N34" t="n">
-        <v>0.68</v>
+        <v>-0.48</v>
       </c>
       <c r="O34" t="n">
-        <v>2.31</v>
+        <v>-1.59</v>
       </c>
       <c r="P34" t="n">
         <v>29.7</v>
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.17</v>
+        <v>4.07</v>
       </c>
       <c r="E35" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F35" t="n">
+        <v>-2.4</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="H35" t="n">
         <v>0.02</v>
       </c>
-      <c r="F35" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="G35" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="H35" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="I35" t="n">
-        <v>-2.4</v>
+        <v>0.49</v>
       </c>
       <c r="J35" t="n">
-        <v>4.09</v>
+        <v>4.14</v>
       </c>
       <c r="K35" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="L35" t="n">
-        <v>0.49</v>
+        <v>1.22</v>
       </c>
       <c r="M35" t="n">
-        <v>4.09</v>
+        <v>4.14</v>
       </c>
       <c r="N35" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="O35" t="n">
-        <v>0.49</v>
+        <v>1.22</v>
       </c>
       <c r="P35" t="n">
-        <v>4.09</v>
+        <v>4.14</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="R35" t="n">
-        <v>0.49</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8.98</v>
+        <v>8.75</v>
       </c>
       <c r="E36" t="n">
-        <v>0.01</v>
+        <v>-0.23</v>
       </c>
       <c r="F36" t="n">
-        <v>0.11</v>
+        <v>-2.56</v>
       </c>
       <c r="G36" t="n">
-        <v>8.75</v>
+        <v>8.81</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.23</v>
+        <v>0.06</v>
       </c>
       <c r="I36" t="n">
-        <v>-2.56</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>8.81</v>
+        <v>8.9</v>
       </c>
       <c r="K36" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="L36" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="M36" t="n">
-        <v>8.81</v>
+        <v>8.9</v>
       </c>
       <c r="N36" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="O36" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="P36" t="n">
-        <v>8.81</v>
+        <v>8.9</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="R36" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="37">
@@ -2685,40 +2685,40 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>387.8</v>
+        <v>375.8</v>
       </c>
       <c r="E37" t="n">
-        <v>1</v>
+        <v>-12</v>
       </c>
       <c r="F37" t="n">
-        <v>0.26</v>
+        <v>-3.09</v>
       </c>
       <c r="G37" t="n">
-        <v>375.8</v>
+        <v>378</v>
       </c>
       <c r="H37" t="n">
-        <v>-12</v>
+        <v>2.2</v>
       </c>
       <c r="I37" t="n">
-        <v>-3.09</v>
+        <v>0.59</v>
       </c>
       <c r="J37" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K37" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="L37" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="M37" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="N37" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="O37" t="n">
-        <v>0.53</v>
+        <v>-0.26</v>
       </c>
       <c r="P37" t="n">
         <v>379</v>
@@ -2747,40 +2747,40 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.85</v>
+        <v>11.38</v>
       </c>
       <c r="E38" t="n">
-        <v>0.06</v>
+        <v>-0.47</v>
       </c>
       <c r="F38" t="n">
-        <v>0.51</v>
+        <v>-3.97</v>
       </c>
       <c r="G38" t="n">
-        <v>11.38</v>
+        <v>11.53</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.47</v>
+        <v>0.15</v>
       </c>
       <c r="I38" t="n">
-        <v>-3.97</v>
+        <v>1.32</v>
       </c>
       <c r="J38" t="n">
-        <v>11.53</v>
+        <v>11.43</v>
       </c>
       <c r="K38" t="n">
-        <v>0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="L38" t="n">
-        <v>1.32</v>
+        <v>-0.87</v>
       </c>
       <c r="M38" t="n">
-        <v>11.43</v>
+        <v>11.27</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.1</v>
+        <v>-0.16</v>
       </c>
       <c r="O38" t="n">
-        <v>-0.87</v>
+        <v>-1.4</v>
       </c>
       <c r="P38" t="n">
         <v>11.27</v>
@@ -2809,40 +2809,40 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>484.2</v>
+        <v>476.8</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>-7.4</v>
       </c>
       <c r="F39" t="n">
-        <v>0.41</v>
+        <v>-1.53</v>
       </c>
       <c r="G39" t="n">
-        <v>476.8</v>
+        <v>483.4</v>
       </c>
       <c r="H39" t="n">
-        <v>-7.4</v>
+        <v>6.6</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.53</v>
+        <v>1.38</v>
       </c>
       <c r="J39" t="n">
-        <v>483.4</v>
+        <v>488.6</v>
       </c>
       <c r="K39" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="L39" t="n">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="M39" t="n">
-        <v>488.6</v>
+        <v>486.4</v>
       </c>
       <c r="N39" t="n">
-        <v>5.2</v>
+        <v>-2.2</v>
       </c>
       <c r="O39" t="n">
-        <v>1.08</v>
+        <v>-0.45</v>
       </c>
       <c r="P39" t="n">
         <v>486.4</v>
@@ -2871,40 +2871,40 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>37.86</v>
+        <v>36.36</v>
       </c>
       <c r="E40" t="n">
-        <v>0.36</v>
+        <v>-1.5</v>
       </c>
       <c r="F40" t="n">
-        <v>0.96</v>
+        <v>-3.96</v>
       </c>
       <c r="G40" t="n">
-        <v>36.36</v>
+        <v>36.28</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.5</v>
+        <v>-0.08</v>
       </c>
       <c r="I40" t="n">
-        <v>-3.96</v>
+        <v>-0.22</v>
       </c>
       <c r="J40" t="n">
-        <v>36.28</v>
+        <v>37.2</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.08</v>
+        <v>0.92</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.22</v>
+        <v>2.54</v>
       </c>
       <c r="M40" t="n">
-        <v>37.2</v>
+        <v>38</v>
       </c>
       <c r="N40" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="O40" t="n">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="P40" t="n">
         <v>38</v>
@@ -2933,40 +2933,40 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.55</v>
+        <v>31.66</v>
       </c>
       <c r="E41" t="n">
-        <v>-0.44</v>
+        <v>0.11</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.38</v>
+        <v>0.35</v>
       </c>
       <c r="G41" t="n">
-        <v>31.66</v>
+        <v>31.88</v>
       </c>
       <c r="H41" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="I41" t="n">
-        <v>0.35</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>31.88</v>
+        <v>32.2</v>
       </c>
       <c r="K41" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="L41" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="M41" t="n">
-        <v>32.2</v>
+        <v>30.3</v>
       </c>
       <c r="N41" t="n">
-        <v>0.32</v>
+        <v>-1.9</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>-5.9</v>
       </c>
       <c r="P41" t="n">
         <v>30.3</v>
@@ -2995,40 +2995,40 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>77.36</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.14</v>
+        <v>-0.15</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="G42" t="n">
-        <v>77.20999999999999</v>
+        <v>77.83</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.15</v>
+        <v>0.62</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.19</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
-        <v>77.83</v>
+        <v>78.56</v>
       </c>
       <c r="K42" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="L42" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>78.56</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>0.73</v>
+        <v>-1.07</v>
       </c>
       <c r="O42" t="n">
-        <v>0.9399999999999999</v>
+        <v>-1.36</v>
       </c>
       <c r="P42" t="n">
         <v>77.48999999999999</v>
@@ -3057,40 +3057,40 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>43.34</v>
+        <v>43.11</v>
       </c>
       <c r="E43" t="n">
-        <v>0.5</v>
+        <v>-0.23</v>
       </c>
       <c r="F43" t="n">
-        <v>1.17</v>
+        <v>-0.53</v>
       </c>
       <c r="G43" t="n">
-        <v>43.11</v>
+        <v>43.06</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.23</v>
+        <v>-0.05</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.53</v>
+        <v>-0.12</v>
       </c>
       <c r="J43" t="n">
-        <v>43.06</v>
+        <v>43.72</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.05</v>
+        <v>0.66</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.12</v>
+        <v>1.53</v>
       </c>
       <c r="M43" t="n">
-        <v>43.72</v>
+        <v>42.44</v>
       </c>
       <c r="N43" t="n">
-        <v>0.66</v>
+        <v>-1.28</v>
       </c>
       <c r="O43" t="n">
-        <v>1.53</v>
+        <v>-2.93</v>
       </c>
       <c r="P43" t="n">
         <v>42.44</v>
@@ -3119,40 +3119,40 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.88</v>
+        <v>5.84</v>
       </c>
       <c r="E44" t="n">
-        <v>0.09</v>
+        <v>-0.04</v>
       </c>
       <c r="F44" t="n">
-        <v>1.55</v>
+        <v>-0.68</v>
       </c>
       <c r="G44" t="n">
-        <v>5.84</v>
+        <v>5.92</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.04</v>
+        <v>0.08</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.68</v>
+        <v>1.37</v>
       </c>
       <c r="J44" t="n">
-        <v>5.92</v>
+        <v>5.87</v>
       </c>
       <c r="K44" t="n">
-        <v>0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="L44" t="n">
-        <v>1.37</v>
+        <v>-0.84</v>
       </c>
       <c r="M44" t="n">
-        <v>5.87</v>
+        <v>5.91</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.84</v>
+        <v>0.68</v>
       </c>
       <c r="P44" t="n">
         <v>5.91</v>
@@ -3181,7 +3181,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="E45" t="n">
         <v>-0.01</v>
@@ -3190,31 +3190,31 @@
         <v>-0.49</v>
       </c>
       <c r="G45" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="H45" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="K45" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I45" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="K45" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="L45" t="n">
-        <v>-1.97</v>
+        <v>-0.5</v>
       </c>
       <c r="M45" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.5</v>
+        <v>1.52</v>
       </c>
       <c r="P45" t="n">
         <v>2.01</v>
@@ -3243,40 +3243,40 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.78</v>
+        <v>3.73</v>
       </c>
       <c r="E46" t="n">
         <v>-0.05</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.31</v>
+        <v>-1.32</v>
       </c>
       <c r="G46" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.32</v>
+        <v>0.27</v>
       </c>
       <c r="J46" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="K46" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="N46" t="n">
         <v>0.01</v>
       </c>
-      <c r="L46" t="n">
+      <c r="O46" t="n">
         <v>0.27</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0.53</v>
       </c>
       <c r="P46" t="n">
         <v>3.77</v>
@@ -3305,40 +3305,40 @@
         </is>
       </c>
       <c r="D47" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="G47" t="n">
+        <v>11.23</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="I47" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="J47" t="n">
         <v>11</v>
       </c>
-      <c r="E47" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="G47" t="n">
-        <v>10.97</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="I47" t="n">
-        <v>-0.27</v>
-      </c>
-      <c r="J47" t="n">
-        <v>11.23</v>
-      </c>
       <c r="K47" t="n">
-        <v>0.26</v>
+        <v>-0.23</v>
       </c>
       <c r="L47" t="n">
-        <v>2.37</v>
+        <v>-2.05</v>
       </c>
       <c r="M47" t="n">
-        <v>11</v>
+        <v>11.03</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.23</v>
+        <v>0.03</v>
       </c>
       <c r="O47" t="n">
-        <v>-2.05</v>
+        <v>0.27</v>
       </c>
       <c r="P47" t="n">
         <v>11.03</v>
@@ -3367,40 +3367,40 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.3</v>
+        <v>0.295</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>-1.67</v>
       </c>
       <c r="G48" t="n">
-        <v>0.295</v>
+        <v>0.29</v>
       </c>
       <c r="H48" t="n">
         <v>-0.005</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.67</v>
+        <v>-1.69</v>
       </c>
       <c r="J48" t="n">
-        <v>0.29</v>
+        <v>0.285</v>
       </c>
       <c r="K48" t="n">
         <v>-0.005</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.69</v>
+        <v>-1.72</v>
       </c>
       <c r="M48" t="n">
-        <v>0.285</v>
+        <v>0.295</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.005</v>
+        <v>0.01</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.72</v>
+        <v>3.51</v>
       </c>
       <c r="P48" t="n">
         <v>0.295</v>
@@ -3429,40 +3429,40 @@
         </is>
       </c>
       <c r="D49" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="G49" t="n">
         <v>4.27</v>
       </c>
-      <c r="E49" t="n">
+      <c r="H49" t="n">
         <v>0.02</v>
       </c>
-      <c r="F49" t="n">
+      <c r="I49" t="n">
         <v>0.47</v>
       </c>
-      <c r="G49" t="n">
+      <c r="J49" t="n">
         <v>4.25</v>
       </c>
-      <c r="H49" t="n">
+      <c r="K49" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I49" t="n">
+      <c r="L49" t="n">
         <v>-0.47</v>
       </c>
-      <c r="J49" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="K49" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0.47</v>
-      </c>
       <c r="M49" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.47</v>
+        <v>1.18</v>
       </c>
       <c r="P49" t="n">
         <v>4.3</v>
@@ -3509,22 +3509,22 @@
         <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="M50" t="n">
         <v>1.12</v>
       </c>
       <c r="N50" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
         <v>1.12</v>
@@ -3553,40 +3553,40 @@
         </is>
       </c>
       <c r="D51" t="n">
+        <v>5.02</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I51" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J51" t="n">
         <v>5.07</v>
       </c>
-      <c r="E51" t="n">
-        <v>-0.06</v>
-      </c>
-      <c r="F51" t="n">
-        <v>-1.17</v>
-      </c>
-      <c r="G51" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I51" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="J51" t="n">
-        <v>5.08</v>
-      </c>
       <c r="K51" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="L51" t="n">
-        <v>1.2</v>
+        <v>-0.2</v>
       </c>
       <c r="M51" t="n">
         <v>5.07</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="P51" t="n">
         <v>5.07</v>
@@ -3615,40 +3615,40 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.18</v>
+        <v>11.04</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.1</v>
+        <v>-0.14</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.89</v>
+        <v>-1.25</v>
       </c>
       <c r="G52" t="n">
-        <v>11.04</v>
+        <v>11.11</v>
       </c>
       <c r="H52" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="J52" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="K52" t="n">
         <v>-0.14</v>
       </c>
-      <c r="I52" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="J52" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="L52" t="n">
-        <v>0.63</v>
+        <v>-1.26</v>
       </c>
       <c r="M52" t="n">
-        <v>10.97</v>
+        <v>11.02</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.14</v>
+        <v>0.05</v>
       </c>
       <c r="O52" t="n">
-        <v>-1.26</v>
+        <v>0.46</v>
       </c>
       <c r="P52" t="n">
         <v>11.02</v>
@@ -3677,40 +3677,40 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7.12</v>
+        <v>7.04</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.27</v>
+        <v>-0.08</v>
       </c>
       <c r="F53" t="n">
-        <v>-3.65</v>
+        <v>-1.12</v>
       </c>
       <c r="G53" t="n">
-        <v>7.04</v>
+        <v>7.02</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.12</v>
+        <v>-0.28</v>
       </c>
       <c r="J53" t="n">
-        <v>7.02</v>
+        <v>6.99</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.28</v>
+        <v>-0.43</v>
       </c>
       <c r="M53" t="n">
-        <v>6.99</v>
+        <v>7.17</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.03</v>
+        <v>0.18</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.43</v>
+        <v>2.58</v>
       </c>
       <c r="P53" t="n">
         <v>7.17</v>
@@ -3739,22 +3739,22 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.425</v>
+        <v>0.43</v>
       </c>
       <c r="E54" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.16</v>
+        <v>1.18</v>
       </c>
       <c r="G54" t="n">
         <v>0.43</v>
       </c>
       <c r="H54" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0.43</v>
@@ -3810,16 +3810,16 @@
         <v>0</v>
       </c>
       <c r="G55" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>0.62</v>
+        <v>0.625</v>
       </c>
       <c r="K55" t="n">
         <v>0.005</v>
@@ -3828,13 +3828,13 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>0.625</v>
+        <v>0.62</v>
       </c>
       <c r="N55" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.8</v>
       </c>
       <c r="P55" t="n">
         <v>0.62</v>
@@ -3863,40 +3863,40 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.38</v>
+        <v>0.375</v>
       </c>
       <c r="E56" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="F56" t="n">
-        <v>1.33</v>
+        <v>-1.32</v>
       </c>
       <c r="G56" t="n">
         <v>0.375</v>
       </c>
       <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="K56" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I56" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>-1.33</v>
       </c>
       <c r="M56" t="n">
-        <v>0.37</v>
+        <v>0.355</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.005</v>
+        <v>-0.015</v>
       </c>
       <c r="O56" t="n">
-        <v>-1.33</v>
+        <v>-4.05</v>
       </c>
       <c r="P56" t="n">
         <v>0.355</v>
@@ -3925,40 +3925,40 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.51</v>
+        <v>3.47</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.1</v>
+        <v>-0.04</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.77</v>
+        <v>-1.14</v>
       </c>
       <c r="G57" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="H57" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="I57" t="n">
-        <v>-1.14</v>
+        <v>0.29</v>
       </c>
       <c r="J57" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="K57" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="L57" t="n">
-        <v>0.29</v>
+        <v>3.45</v>
       </c>
       <c r="M57" t="n">
         <v>3.6</v>
       </c>
       <c r="N57" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P57" t="n">
         <v>3.6</v>
@@ -3987,40 +3987,40 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.081</v>
+        <v>0.079</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>-0.002</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>-2.47</v>
       </c>
       <c r="G58" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="I58" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="J58" t="n">
         <v>0.079</v>
       </c>
-      <c r="H58" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="I58" t="n">
-        <v>-2.47</v>
-      </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="L58" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M58" t="n">
         <v>0.078</v>
       </c>
-      <c r="K58" t="n">
+      <c r="N58" t="n">
         <v>-0.001</v>
       </c>
-      <c r="L58" t="n">
+      <c r="O58" t="n">
         <v>-1.27</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="O58" t="n">
-        <v>1.28</v>
       </c>
       <c r="P58" t="n">
         <v>0.078</v>
@@ -4049,40 +4049,40 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>22.61</v>
+        <v>20.99</v>
       </c>
       <c r="E59" t="n">
-        <v>0</v>
+        <v>-1.62</v>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>-7.16</v>
       </c>
       <c r="G59" t="n">
-        <v>20.99</v>
+        <v>20.75</v>
       </c>
       <c r="H59" t="n">
-        <v>-1.62</v>
+        <v>-0.24</v>
       </c>
       <c r="I59" t="n">
-        <v>-7.16</v>
+        <v>-1.14</v>
       </c>
       <c r="J59" t="n">
-        <v>20.75</v>
+        <v>21.04</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.24</v>
+        <v>0.29</v>
       </c>
       <c r="L59" t="n">
-        <v>-1.14</v>
+        <v>1.4</v>
       </c>
       <c r="M59" t="n">
-        <v>21.04</v>
+        <v>21.29</v>
       </c>
       <c r="N59" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="O59" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="P59" t="n">
         <v>21.29</v>
@@ -4111,40 +4111,40 @@
         </is>
       </c>
       <c r="D60" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="G60" t="n">
         <v>3.13</v>
       </c>
-      <c r="E60" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="G60" t="n">
-        <v>3.15</v>
-      </c>
       <c r="H60" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="I60" t="n">
-        <v>0.64</v>
+        <v>-0.63</v>
       </c>
       <c r="J60" t="n">
         <v>3.13</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="P60" t="n">
         <v>3.16</v>
@@ -4173,22 +4173,22 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.835</v>
+        <v>0.84</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.015</v>
+        <v>0.005</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.76</v>
+        <v>0.6</v>
       </c>
       <c r="G61" t="n">
         <v>0.84</v>
       </c>
       <c r="H61" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
         <v>0.84</v>
@@ -4200,13 +4200,13 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0.84</v>
+        <v>0.855</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P61" t="n">
         <v>0.855</v>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-10-02 Close</t>
+          <t>2026-10-05 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-10-02 Change</t>
+          <t>2026-10-05 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-10-02 Change %</t>
+          <t>2026-10-05 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-10-05 Close</t>
+          <t>2026-10-06 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-10-05 Change</t>
+          <t>2026-10-06 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-10-05 Change %</t>
+          <t>2026-10-06 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-10-06 Close</t>
+          <t>2026-10-07 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-10-06 Change</t>
+          <t>2026-10-07 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-10-06 Change %</t>
+          <t>2026-10-07 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-10-07 Close</t>
+          <t>2026-10-08 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-10-07 Change</t>
+          <t>2026-10-08 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-10-07 Change %</t>
+          <t>2026-10-08 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-10-08 Close</t>
+          <t>2026-10-09 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-10-08 Change</t>
+          <t>2026-10-09 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-10-08 Change %</t>
+          <t>2026-10-09 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>149.5</v>
+        <v>149.9</v>
       </c>
       <c r="E3" t="n">
-        <v>-8.5</v>
+        <v>0.4</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.38</v>
+        <v>0.27</v>
       </c>
       <c r="G3" t="n">
+        <v>152.8</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="J3" t="n">
         <v>149.9</v>
       </c>
-      <c r="H3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="J3" t="n">
-        <v>152.8</v>
-      </c>
       <c r="K3" t="n">
-        <v>2.9</v>
+        <v>-2.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.93</v>
+        <v>-1.9</v>
       </c>
       <c r="M3" t="n">
-        <v>149.9</v>
+        <v>142.6</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.9</v>
+        <v>-7.3</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.9</v>
+        <v>-4.87</v>
       </c>
       <c r="P3" t="n">
-        <v>149.9</v>
+        <v>142.6</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9</v>
+        <v>-7.3</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.9</v>
+        <v>-4.87</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>229.8</v>
+        <v>228.6</v>
       </c>
       <c r="E4" t="n">
-        <v>-14.6</v>
+        <v>-1.2</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.97</v>
+        <v>-0.52</v>
       </c>
       <c r="G4" t="n">
-        <v>228.6</v>
+        <v>236.4</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2</v>
+        <v>7.8</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.52</v>
+        <v>3.41</v>
       </c>
       <c r="J4" t="n">
-        <v>236.4</v>
+        <v>230</v>
       </c>
       <c r="K4" t="n">
-        <v>7.8</v>
+        <v>-6.4</v>
       </c>
       <c r="L4" t="n">
-        <v>3.41</v>
+        <v>-2.71</v>
       </c>
       <c r="M4" t="n">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="N4" t="n">
-        <v>-6.4</v>
+        <v>-12</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.71</v>
+        <v>-5.22</v>
       </c>
       <c r="P4" t="n">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="Q4" t="n">
-        <v>-6.4</v>
+        <v>-12</v>
       </c>
       <c r="R4" t="n">
-        <v>-2.71</v>
+        <v>-5.22</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.46</v>
+        <v>6.49</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.17</v>
+        <v>0.03</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.56</v>
+        <v>0.46</v>
       </c>
       <c r="G5" t="n">
-        <v>6.49</v>
+        <v>6.55</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="I5" t="n">
-        <v>0.46</v>
+        <v>0.92</v>
       </c>
       <c r="J5" t="n">
-        <v>6.55</v>
+        <v>6.57</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="L5" t="n">
-        <v>0.92</v>
+        <v>0.31</v>
       </c>
       <c r="M5" t="n">
-        <v>6.57</v>
+        <v>6.59</v>
       </c>
       <c r="N5" t="n">
         <v>0.02</v>
       </c>
       <c r="O5" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="P5" t="n">
-        <v>6.57</v>
+        <v>6.59</v>
       </c>
       <c r="Q5" t="n">
         <v>0.02</v>
       </c>
       <c r="R5" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
@@ -766,46 +766,46 @@
         <v>7.45</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.26</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.37</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>7.45</v>
+        <v>7.58</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="J6" t="n">
         <v>7.58</v>
       </c>
       <c r="K6" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>7.58</v>
+        <v>7.57</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="P6" t="n">
-        <v>7.58</v>
+        <v>7.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="7">
@@ -828,46 +828,46 @@
         <v>5.92</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.17</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.79</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>5.92</v>
+        <v>6.01</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="J7" t="n">
-        <v>6.01</v>
+        <v>5.99</v>
       </c>
       <c r="K7" t="n">
-        <v>0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="L7" t="n">
-        <v>1.52</v>
+        <v>-0.33</v>
       </c>
       <c r="M7" t="n">
-        <v>5.99</v>
+        <v>6.03</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.33</v>
+        <v>0.67</v>
       </c>
       <c r="P7" t="n">
-        <v>5.99</v>
+        <v>6.03</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.33</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.56</v>
+        <v>9.51</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.26</v>
+        <v>-0.05</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.65</v>
+        <v>-0.52</v>
       </c>
       <c r="G8" t="n">
-        <v>9.51</v>
+        <v>9.65</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.05</v>
+        <v>0.14</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.52</v>
+        <v>1.47</v>
       </c>
       <c r="J8" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.14</v>
+        <v>-0.02</v>
       </c>
       <c r="L8" t="n">
-        <v>1.47</v>
+        <v>-0.21</v>
       </c>
       <c r="M8" t="n">
-        <v>9.630000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.21</v>
+        <v>0.31</v>
       </c>
       <c r="P8" t="n">
-        <v>9.630000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="R8" t="n">
-        <v>-0.21</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.220000000000001</v>
+        <v>8.19</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.14</v>
+        <v>-0.03</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.67</v>
+        <v>-0.36</v>
       </c>
       <c r="G9" t="n">
-        <v>8.19</v>
+        <v>8.23</v>
       </c>
       <c r="H9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="K9" t="n">
         <v>-0.03</v>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
         <v>-0.36</v>
       </c>
-      <c r="J9" t="n">
-        <v>8.23</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.49</v>
-      </c>
       <c r="M9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.03</v>
+        <v>0.15</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.36</v>
+        <v>1.83</v>
       </c>
       <c r="P9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.03</v>
+        <v>0.15</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.36</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50.6</v>
+        <v>50.7</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9</v>
+        <v>0.1</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.75</v>
+        <v>0.2</v>
       </c>
       <c r="G10" t="n">
-        <v>50.7</v>
+        <v>51</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2</v>
+        <v>0.59</v>
       </c>
       <c r="J10" t="n">
-        <v>51</v>
+        <v>50.95</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3</v>
+        <v>-0.05</v>
       </c>
       <c r="L10" t="n">
-        <v>0.59</v>
+        <v>-0.1</v>
       </c>
       <c r="M10" t="n">
-        <v>50.95</v>
+        <v>51.65</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.05</v>
+        <v>0.7</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1</v>
+        <v>1.37</v>
       </c>
       <c r="P10" t="n">
-        <v>50.95</v>
+        <v>51.65</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.05</v>
+        <v>0.7</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.1</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.36</v>
+        <v>4.38</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.06</v>
+        <v>0.02</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.36</v>
+        <v>0.46</v>
       </c>
       <c r="G11" t="n">
-        <v>4.38</v>
+        <v>4.39</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I11" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="J11" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="L11" t="n">
-        <v>0.23</v>
+        <v>0.68</v>
       </c>
       <c r="M11" t="n">
-        <v>4.42</v>
+        <v>4.53</v>
       </c>
       <c r="N11" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="O11" t="n">
-        <v>0.68</v>
+        <v>2.49</v>
       </c>
       <c r="P11" t="n">
-        <v>4.42</v>
+        <v>4.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="R11" t="n">
-        <v>0.68</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.52</v>
+        <v>9.56</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.14</v>
+        <v>0.04</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.45</v>
+        <v>0.42</v>
       </c>
       <c r="G12" t="n">
-        <v>9.56</v>
+        <v>9.67</v>
       </c>
       <c r="H12" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="I12" t="n">
-        <v>0.42</v>
+        <v>1.15</v>
       </c>
       <c r="J12" t="n">
-        <v>9.67</v>
+        <v>9.59</v>
       </c>
       <c r="K12" t="n">
-        <v>0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="L12" t="n">
-        <v>1.15</v>
+        <v>-0.83</v>
       </c>
       <c r="M12" t="n">
-        <v>9.59</v>
+        <v>9.83</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.08</v>
+        <v>0.24</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.83</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>9.59</v>
+        <v>9.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.08</v>
+        <v>0.24</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.83</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="G13" t="n">
+        <v>23.44</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="J13" t="n">
         <v>23.52</v>
       </c>
-      <c r="E13" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="F13" t="n">
-        <v>-1.84</v>
-      </c>
-      <c r="G13" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="I13" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="J13" t="n">
-        <v>23.44</v>
-      </c>
       <c r="K13" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="L13" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="M13" t="n">
-        <v>23.52</v>
+        <v>24.04</v>
       </c>
       <c r="N13" t="n">
-        <v>0.08</v>
+        <v>0.52</v>
       </c>
       <c r="O13" t="n">
-        <v>0.34</v>
+        <v>2.21</v>
       </c>
       <c r="P13" t="n">
-        <v>23.52</v>
+        <v>24.04</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.08</v>
+        <v>0.52</v>
       </c>
       <c r="R13" t="n">
-        <v>0.34</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="14">
@@ -1262,46 +1262,46 @@
         <v>1.85</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J14" t="n">
         <v>1.85</v>
       </c>
-      <c r="H14" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.86</v>
-      </c>
       <c r="K14" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="L14" t="n">
-        <v>0.54</v>
+        <v>-0.54</v>
       </c>
       <c r="M14" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.54</v>
+        <v>1.62</v>
       </c>
       <c r="P14" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.54</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.08</v>
+        <v>-0.01</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.5</v>
+        <v>-0.19</v>
       </c>
       <c r="G15" t="n">
         <v>5.24</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>5.24</v>
+        <v>5.29</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="M15" t="n">
-        <v>5.29</v>
+        <v>5.22</v>
       </c>
       <c r="N15" t="n">
-        <v>0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>0.95</v>
+        <v>-1.32</v>
       </c>
       <c r="P15" t="n">
-        <v>5.29</v>
+        <v>5.22</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R15" t="n">
-        <v>0.95</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="16">
@@ -1386,46 +1386,46 @@
         <v>4.3</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.38</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="J16" t="n">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="K16" t="n">
         <v>0.02</v>
       </c>
       <c r="L16" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="M16" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="N16" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="O16" t="n">
-        <v>0.46</v>
+        <v>-0.23</v>
       </c>
       <c r="P16" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="R16" t="n">
-        <v>0.46</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.93</v>
+        <v>0.31</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="I17" t="n">
-        <v>0.31</v>
+        <v>1.25</v>
       </c>
       <c r="J17" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="K17" t="n">
         <v>0.04</v>
       </c>
       <c r="L17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="M17" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="N17" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="O17" t="n">
-        <v>1.23</v>
+        <v>-1.52</v>
       </c>
       <c r="P17" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="R17" t="n">
-        <v>1.23</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="F18" t="n">
-        <v>-1</v>
+        <v>-0.67</v>
       </c>
       <c r="G18" t="n">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="H18" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="K18" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I18" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0.06</v>
-      </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>-0.66</v>
       </c>
       <c r="M18" t="n">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.66</v>
+        <v>1.34</v>
       </c>
       <c r="P18" t="n">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.66</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>52</v>
+        <v>51.75</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.75</v>
+        <v>-0.25</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.42</v>
+        <v>-0.48</v>
       </c>
       <c r="G19" t="n">
-        <v>51.75</v>
+        <v>51.55</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.48</v>
+        <v>-0.39</v>
       </c>
       <c r="J19" t="n">
-        <v>51.55</v>
+        <v>51.5</v>
       </c>
       <c r="K19" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="M19" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="N19" t="n">
         <v>-0.2</v>
       </c>
-      <c r="L19" t="n">
+      <c r="O19" t="n">
         <v>-0.39</v>
       </c>
-      <c r="M19" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="O19" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="P19" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.1</v>
+        <v>-0.39</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27.5</v>
+        <v>27.56</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.62</v>
+        <v>0.06</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2</v>
+        <v>0.22</v>
       </c>
       <c r="G20" t="n">
-        <v>27.56</v>
+        <v>27.3</v>
       </c>
       <c r="H20" t="n">
-        <v>0.06</v>
+        <v>-0.26</v>
       </c>
       <c r="I20" t="n">
-        <v>0.22</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>27.3</v>
+        <v>27.26</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.26</v>
+        <v>-0.04</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.15</v>
       </c>
       <c r="M20" t="n">
-        <v>27.26</v>
+        <v>26.76</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.04</v>
+        <v>-0.5</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.15</v>
+        <v>-1.83</v>
       </c>
       <c r="P20" t="n">
-        <v>27.26</v>
+        <v>26.76</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.04</v>
+        <v>-0.5</v>
       </c>
       <c r="R20" t="n">
-        <v>-0.15</v>
+        <v>-1.83</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.45</v>
+        <v>4.46</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.89</v>
+        <v>0.22</v>
       </c>
       <c r="G21" t="n">
-        <v>4.46</v>
+        <v>4.51</v>
       </c>
       <c r="H21" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I21" t="n">
-        <v>0.22</v>
+        <v>1.12</v>
       </c>
       <c r="J21" t="n">
-        <v>4.51</v>
+        <v>4.53</v>
       </c>
       <c r="K21" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="L21" t="n">
-        <v>1.12</v>
+        <v>0.44</v>
       </c>
       <c r="M21" t="n">
         <v>4.53</v>
       </c>
       <c r="N21" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>4.53</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
+        <v>78.90000000000001</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G22" t="n">
         <v>78.84999999999999</v>
       </c>
-      <c r="E22" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-0.76</v>
-      </c>
-      <c r="G22" t="n">
-        <v>78.90000000000001</v>
-      </c>
       <c r="H22" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="I22" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="J22" t="n">
-        <v>78.84999999999999</v>
+        <v>79.05</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.05</v>
+        <v>0.2</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.06</v>
+        <v>0.25</v>
       </c>
       <c r="M22" t="n">
-        <v>79.05</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="P22" t="n">
-        <v>79.05</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="R22" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>21.66</v>
+        <v>21.62</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.2</v>
+        <v>-0.04</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.91</v>
+        <v>-0.18</v>
       </c>
       <c r="G23" t="n">
-        <v>21.62</v>
+        <v>21.8</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.04</v>
+        <v>0.18</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.18</v>
+        <v>0.83</v>
       </c>
       <c r="J23" t="n">
-        <v>21.8</v>
+        <v>21.72</v>
       </c>
       <c r="K23" t="n">
-        <v>0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="L23" t="n">
-        <v>0.83</v>
+        <v>-0.37</v>
       </c>
       <c r="M23" t="n">
-        <v>21.72</v>
+        <v>20.7</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.08</v>
+        <v>-1.02</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.37</v>
+        <v>-4.7</v>
       </c>
       <c r="P23" t="n">
-        <v>21.72</v>
+        <v>20.7</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.08</v>
+        <v>-1.02</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.37</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.9</v>
+        <v>14.75</v>
       </c>
       <c r="E24" t="n">
-        <v>0.52</v>
+        <v>-0.15</v>
       </c>
       <c r="F24" t="n">
-        <v>3.62</v>
+        <v>-1.01</v>
       </c>
       <c r="G24" t="n">
-        <v>14.75</v>
+        <v>14.94</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.15</v>
+        <v>0.19</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.01</v>
+        <v>1.29</v>
       </c>
       <c r="J24" t="n">
-        <v>14.94</v>
+        <v>14.46</v>
       </c>
       <c r="K24" t="n">
-        <v>0.19</v>
+        <v>-0.48</v>
       </c>
       <c r="L24" t="n">
-        <v>1.29</v>
+        <v>-3.21</v>
       </c>
       <c r="M24" t="n">
-        <v>14.46</v>
+        <v>13.91</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.48</v>
+        <v>-0.55</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.21</v>
+        <v>-3.8</v>
       </c>
       <c r="P24" t="n">
-        <v>14.46</v>
+        <v>13.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.48</v>
+        <v>-0.55</v>
       </c>
       <c r="R24" t="n">
-        <v>-3.21</v>
+        <v>-3.8</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>24.24</v>
+        <v>23.88</v>
       </c>
       <c r="E25" t="n">
-        <v>-1</v>
+        <v>-0.36</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.96</v>
+        <v>-1.49</v>
       </c>
       <c r="G25" t="n">
-        <v>23.88</v>
+        <v>24.26</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.36</v>
+        <v>0.38</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.49</v>
+        <v>1.59</v>
       </c>
       <c r="J25" t="n">
-        <v>24.26</v>
+        <v>23.94</v>
       </c>
       <c r="K25" t="n">
-        <v>0.38</v>
+        <v>-0.32</v>
       </c>
       <c r="L25" t="n">
-        <v>1.59</v>
+        <v>-1.32</v>
       </c>
       <c r="M25" t="n">
-        <v>23.94</v>
+        <v>23.66</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.32</v>
+        <v>-1.17</v>
       </c>
       <c r="P25" t="n">
-        <v>23.94</v>
+        <v>23.66</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="R25" t="n">
-        <v>-1.32</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>35.9</v>
+        <v>36.82</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.48</v>
+        <v>0.92</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.96</v>
+        <v>2.56</v>
       </c>
       <c r="G26" t="n">
-        <v>36.82</v>
+        <v>35.6</v>
       </c>
       <c r="H26" t="n">
-        <v>0.92</v>
+        <v>-1.22</v>
       </c>
       <c r="I26" t="n">
-        <v>2.56</v>
+        <v>-3.31</v>
       </c>
       <c r="J26" t="n">
-        <v>35.6</v>
+        <v>34.44</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.22</v>
+        <v>-1.16</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.31</v>
+        <v>-3.26</v>
       </c>
       <c r="M26" t="n">
-        <v>34.44</v>
+        <v>30.36</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.16</v>
+        <v>-4.08</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.26</v>
+        <v>-11.85</v>
       </c>
       <c r="P26" t="n">
-        <v>34.44</v>
+        <v>30.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.16</v>
+        <v>-4.08</v>
       </c>
       <c r="R26" t="n">
-        <v>-3.26</v>
+        <v>-11.85</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>421.2</v>
+        <v>423</v>
       </c>
       <c r="E27" t="n">
-        <v>-9.800000000000001</v>
+        <v>1.8</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.27</v>
+        <v>0.43</v>
       </c>
       <c r="G27" t="n">
-        <v>423</v>
+        <v>428.2</v>
       </c>
       <c r="H27" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="I27" t="n">
-        <v>0.43</v>
+        <v>1.23</v>
       </c>
       <c r="J27" t="n">
-        <v>428.2</v>
+        <v>420.6</v>
       </c>
       <c r="K27" t="n">
-        <v>5.2</v>
+        <v>-7.6</v>
       </c>
       <c r="L27" t="n">
-        <v>1.23</v>
+        <v>-1.77</v>
       </c>
       <c r="M27" t="n">
-        <v>420.6</v>
+        <v>411.4</v>
       </c>
       <c r="N27" t="n">
-        <v>-7.6</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.77</v>
+        <v>-2.19</v>
       </c>
       <c r="P27" t="n">
-        <v>420.6</v>
+        <v>411.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>-7.6</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.77</v>
+        <v>-2.19</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>104.4</v>
+        <v>105.4</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.2</v>
+        <v>1</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.06</v>
+        <v>0.96</v>
       </c>
       <c r="G28" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="I28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J28" t="n">
         <v>105.4</v>
       </c>
-      <c r="H28" t="n">
-        <v>1</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="J28" t="n">
-        <v>108.2</v>
-      </c>
       <c r="K28" t="n">
-        <v>2.8</v>
+        <v>-2.8</v>
       </c>
       <c r="L28" t="n">
-        <v>2.66</v>
+        <v>-2.59</v>
       </c>
       <c r="M28" t="n">
-        <v>105.4</v>
+        <v>104.3</v>
       </c>
       <c r="N28" t="n">
-        <v>-2.8</v>
+        <v>-1.1</v>
       </c>
       <c r="O28" t="n">
-        <v>-2.59</v>
+        <v>-1.04</v>
       </c>
       <c r="P28" t="n">
-        <v>105.4</v>
+        <v>104.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>-2.8</v>
+        <v>-1.1</v>
       </c>
       <c r="R28" t="n">
-        <v>-2.59</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>102.9</v>
+        <v>102.4</v>
       </c>
       <c r="E29" t="n">
-        <v>-1.4</v>
+        <v>-0.5</v>
       </c>
       <c r="F29" t="n">
-        <v>-1.34</v>
+        <v>-0.49</v>
       </c>
       <c r="G29" t="n">
-        <v>102.4</v>
+        <v>103.6</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.5</v>
+        <v>1.2</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.49</v>
+        <v>1.17</v>
       </c>
       <c r="J29" t="n">
-        <v>103.6</v>
+        <v>104.9</v>
       </c>
       <c r="K29" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="M29" t="n">
-        <v>104.9</v>
+        <v>105.2</v>
       </c>
       <c r="N29" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="O29" t="n">
-        <v>1.25</v>
+        <v>0.29</v>
       </c>
       <c r="P29" t="n">
-        <v>104.9</v>
+        <v>105.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>70.2</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.5</v>
+        <v>0.45</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.09</v>
+        <v>0.64</v>
       </c>
       <c r="G30" t="n">
-        <v>70.65000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="H30" t="n">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="I30" t="n">
-        <v>0.64</v>
+        <v>0.21</v>
       </c>
       <c r="J30" t="n">
-        <v>70.8</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>0.15</v>
+        <v>-0.65</v>
       </c>
       <c r="L30" t="n">
-        <v>0.21</v>
+        <v>-0.92</v>
       </c>
       <c r="M30" t="n">
-        <v>70.15000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.65</v>
+        <v>-0.75</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.92</v>
+        <v>-1.07</v>
       </c>
       <c r="P30" t="n">
-        <v>70.15000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.65</v>
+        <v>-0.75</v>
       </c>
       <c r="R30" t="n">
-        <v>-0.92</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>83.2</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="E31" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="G31" t="n">
+        <v>86.15000000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="K31" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-1.63</v>
+      </c>
+      <c r="M31" t="n">
+        <v>82.15000000000001</v>
+      </c>
+      <c r="N31" t="n">
         <v>-2.6</v>
       </c>
-      <c r="F31" t="n">
-        <v>-3.03</v>
-      </c>
-      <c r="G31" t="n">
-        <v>83.40000000000001</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="J31" t="n">
-        <v>86.15000000000001</v>
-      </c>
-      <c r="K31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M31" t="n">
-        <v>84.75</v>
-      </c>
-      <c r="N31" t="n">
-        <v>-1.4</v>
-      </c>
       <c r="O31" t="n">
-        <v>-1.63</v>
+        <v>-3.07</v>
       </c>
       <c r="P31" t="n">
-        <v>84.75</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>-1.4</v>
+        <v>-2.6</v>
       </c>
       <c r="R31" t="n">
-        <v>-1.63</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>60.25</v>
+        <v>61.3</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.4</v>
+        <v>1.05</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.66</v>
+        <v>1.74</v>
       </c>
       <c r="G32" t="n">
-        <v>61.3</v>
+        <v>61.55</v>
       </c>
       <c r="H32" t="n">
-        <v>1.05</v>
+        <v>0.25</v>
       </c>
       <c r="I32" t="n">
-        <v>1.74</v>
+        <v>0.41</v>
       </c>
       <c r="J32" t="n">
-        <v>61.55</v>
+        <v>60.9</v>
       </c>
       <c r="K32" t="n">
-        <v>0.25</v>
+        <v>-0.65</v>
       </c>
       <c r="L32" t="n">
-        <v>0.41</v>
+        <v>-1.06</v>
       </c>
       <c r="M32" t="n">
-        <v>60.9</v>
+        <v>56.8</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.65</v>
+        <v>-4.1</v>
       </c>
       <c r="O32" t="n">
-        <v>-1.06</v>
+        <v>-6.73</v>
       </c>
       <c r="P32" t="n">
-        <v>60.9</v>
+        <v>56.8</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.65</v>
+        <v>-4.1</v>
       </c>
       <c r="R32" t="n">
-        <v>-1.06</v>
+        <v>-6.73</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>73.90000000000001</v>
+        <v>74.09999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.7</v>
+        <v>0.2</v>
       </c>
       <c r="F33" t="n">
-        <v>-2.25</v>
+        <v>0.27</v>
       </c>
       <c r="G33" t="n">
-        <v>74.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="H33" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="I33" t="n">
-        <v>0.27</v>
+        <v>1.21</v>
       </c>
       <c r="J33" t="n">
-        <v>75</v>
+        <v>74.55</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9</v>
+        <v>-0.45</v>
       </c>
       <c r="L33" t="n">
-        <v>1.21</v>
+        <v>-0.6</v>
       </c>
       <c r="M33" t="n">
-        <v>74.55</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.45</v>
+        <v>-1.65</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.6</v>
+        <v>-2.21</v>
       </c>
       <c r="P33" t="n">
-        <v>74.55</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.45</v>
+        <v>-1.65</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.6</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>29.58</v>
+        <v>29.5</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.36</v>
+        <v>-0.08</v>
       </c>
       <c r="F34" t="n">
-        <v>-4.4</v>
+        <v>-0.27</v>
       </c>
       <c r="G34" t="n">
-        <v>29.5</v>
+        <v>30.18</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.08</v>
+        <v>0.68</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.27</v>
+        <v>2.31</v>
       </c>
       <c r="J34" t="n">
-        <v>30.18</v>
+        <v>29.7</v>
       </c>
       <c r="K34" t="n">
-        <v>0.68</v>
+        <v>-0.48</v>
       </c>
       <c r="L34" t="n">
-        <v>2.31</v>
+        <v>-1.59</v>
       </c>
       <c r="M34" t="n">
-        <v>29.7</v>
+        <v>28.54</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.48</v>
+        <v>-1.16</v>
       </c>
       <c r="O34" t="n">
-        <v>-1.59</v>
+        <v>-3.91</v>
       </c>
       <c r="P34" t="n">
-        <v>29.7</v>
+        <v>28.54</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.48</v>
+        <v>-1.16</v>
       </c>
       <c r="R34" t="n">
-        <v>-1.59</v>
+        <v>-3.91</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.07</v>
+        <v>4.09</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="F35" t="n">
-        <v>-2.4</v>
+        <v>0.49</v>
       </c>
       <c r="G35" t="n">
-        <v>4.09</v>
+        <v>4.14</v>
       </c>
       <c r="H35" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="I35" t="n">
-        <v>0.49</v>
+        <v>1.22</v>
       </c>
       <c r="J35" t="n">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="K35" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="L35" t="n">
-        <v>1.22</v>
+        <v>-0.72</v>
       </c>
       <c r="M35" t="n">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="N35" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="O35" t="n">
-        <v>1.22</v>
+        <v>-0.72</v>
       </c>
       <c r="P35" t="n">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="R35" t="n">
-        <v>1.22</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8.75</v>
+        <v>8.81</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.23</v>
+        <v>0.06</v>
       </c>
       <c r="F36" t="n">
-        <v>-2.56</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>8.81</v>
+        <v>8.9</v>
       </c>
       <c r="H36" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="J36" t="n">
-        <v>8.9</v>
+        <v>8.85</v>
       </c>
       <c r="K36" t="n">
-        <v>0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="L36" t="n">
-        <v>1.02</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>8.9</v>
+        <v>8.85</v>
       </c>
       <c r="N36" t="n">
-        <v>0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="O36" t="n">
-        <v>1.02</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="P36" t="n">
-        <v>8.9</v>
+        <v>8.85</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="R36" t="n">
-        <v>1.02</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>375.8</v>
+        <v>378</v>
       </c>
       <c r="E37" t="n">
-        <v>-12</v>
+        <v>2.2</v>
       </c>
       <c r="F37" t="n">
-        <v>-3.09</v>
+        <v>0.59</v>
       </c>
       <c r="G37" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="H37" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="I37" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="J37" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L37" t="n">
-        <v>0.53</v>
+        <v>-0.26</v>
       </c>
       <c r="M37" t="n">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="N37" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.26</v>
+        <v>-1.06</v>
       </c>
       <c r="P37" t="n">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="Q37" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.26</v>
+        <v>-1.06</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.38</v>
+        <v>11.53</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.47</v>
+        <v>0.15</v>
       </c>
       <c r="F38" t="n">
-        <v>-3.97</v>
+        <v>1.32</v>
       </c>
       <c r="G38" t="n">
-        <v>11.53</v>
+        <v>11.43</v>
       </c>
       <c r="H38" t="n">
-        <v>0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="I38" t="n">
-        <v>1.32</v>
+        <v>-0.87</v>
       </c>
       <c r="J38" t="n">
-        <v>11.43</v>
+        <v>11.27</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.1</v>
+        <v>-0.16</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.87</v>
+        <v>-1.4</v>
       </c>
       <c r="M38" t="n">
-        <v>11.27</v>
+        <v>11.02</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.16</v>
+        <v>-0.25</v>
       </c>
       <c r="O38" t="n">
-        <v>-1.4</v>
+        <v>-2.22</v>
       </c>
       <c r="P38" t="n">
-        <v>11.27</v>
+        <v>11.02</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.16</v>
+        <v>-0.25</v>
       </c>
       <c r="R38" t="n">
-        <v>-1.4</v>
+        <v>-2.22</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
+        <v>483.4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="G39" t="n">
+        <v>488.6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="J39" t="n">
+        <v>486.4</v>
+      </c>
+      <c r="K39" t="n">
+        <v>-2.2</v>
+      </c>
+      <c r="L39" t="n">
+        <v>-0.45</v>
+      </c>
+      <c r="M39" t="n">
         <v>476.8</v>
       </c>
-      <c r="E39" t="n">
-        <v>-7.4</v>
-      </c>
-      <c r="F39" t="n">
-        <v>-1.53</v>
-      </c>
-      <c r="G39" t="n">
-        <v>483.4</v>
-      </c>
-      <c r="H39" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="I39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="J39" t="n">
-        <v>488.6</v>
-      </c>
-      <c r="K39" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="L39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="M39" t="n">
-        <v>486.4</v>
-      </c>
       <c r="N39" t="n">
-        <v>-2.2</v>
+        <v>-9.6</v>
       </c>
       <c r="O39" t="n">
-        <v>-0.45</v>
+        <v>-1.97</v>
       </c>
       <c r="P39" t="n">
-        <v>486.4</v>
+        <v>476.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>-2.2</v>
+        <v>-9.6</v>
       </c>
       <c r="R39" t="n">
-        <v>-0.45</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>36.36</v>
+        <v>36.28</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.5</v>
+        <v>-0.08</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.96</v>
+        <v>-0.22</v>
       </c>
       <c r="G40" t="n">
-        <v>36.28</v>
+        <v>37.2</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.08</v>
+        <v>0.92</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.22</v>
+        <v>2.54</v>
       </c>
       <c r="J40" t="n">
-        <v>37.2</v>
+        <v>38</v>
       </c>
       <c r="K40" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="L40" t="n">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="M40" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="O40" t="n">
-        <v>2.15</v>
+        <v>-1.32</v>
       </c>
       <c r="P40" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="R40" t="n">
-        <v>2.15</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.66</v>
+        <v>31.88</v>
       </c>
       <c r="E41" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="F41" t="n">
-        <v>0.35</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G41" t="n">
-        <v>31.88</v>
+        <v>32.2</v>
       </c>
       <c r="H41" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="I41" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="J41" t="n">
-        <v>32.2</v>
+        <v>30.3</v>
       </c>
       <c r="K41" t="n">
-        <v>0.32</v>
+        <v>-1.9</v>
       </c>
       <c r="L41" t="n">
-        <v>1</v>
+        <v>-5.9</v>
       </c>
       <c r="M41" t="n">
-        <v>30.3</v>
+        <v>29</v>
       </c>
       <c r="N41" t="n">
-        <v>-1.9</v>
+        <v>-1.3</v>
       </c>
       <c r="O41" t="n">
-        <v>-5.9</v>
+        <v>-4.29</v>
       </c>
       <c r="P41" t="n">
-        <v>30.3</v>
+        <v>29</v>
       </c>
       <c r="Q41" t="n">
-        <v>-1.9</v>
+        <v>-1.3</v>
       </c>
       <c r="R41" t="n">
-        <v>-5.9</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>77.20999999999999</v>
+        <v>77.83</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.15</v>
+        <v>0.62</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.19</v>
+        <v>0.8</v>
       </c>
       <c r="G42" t="n">
-        <v>77.83</v>
+        <v>78.56</v>
       </c>
       <c r="H42" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="I42" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>78.56</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>0.73</v>
+        <v>-1.07</v>
       </c>
       <c r="L42" t="n">
-        <v>0.9399999999999999</v>
+        <v>-1.36</v>
       </c>
       <c r="M42" t="n">
-        <v>77.48999999999999</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>-1.07</v>
+        <v>-3.64</v>
       </c>
       <c r="O42" t="n">
-        <v>-1.36</v>
+        <v>-4.7</v>
       </c>
       <c r="P42" t="n">
-        <v>77.48999999999999</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="Q42" t="n">
-        <v>-1.07</v>
+        <v>-3.64</v>
       </c>
       <c r="R42" t="n">
-        <v>-1.36</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>43.11</v>
+        <v>43.06</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.23</v>
+        <v>-0.05</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.53</v>
+        <v>-0.12</v>
       </c>
       <c r="G43" t="n">
-        <v>43.06</v>
+        <v>43.72</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.05</v>
+        <v>0.66</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.12</v>
+        <v>1.53</v>
       </c>
       <c r="J43" t="n">
-        <v>43.72</v>
+        <v>42.44</v>
       </c>
       <c r="K43" t="n">
-        <v>0.66</v>
+        <v>-1.28</v>
       </c>
       <c r="L43" t="n">
-        <v>1.53</v>
+        <v>-2.93</v>
       </c>
       <c r="M43" t="n">
-        <v>42.44</v>
+        <v>40.25</v>
       </c>
       <c r="N43" t="n">
-        <v>-1.28</v>
+        <v>-2.19</v>
       </c>
       <c r="O43" t="n">
-        <v>-2.93</v>
+        <v>-5.16</v>
       </c>
       <c r="P43" t="n">
-        <v>42.44</v>
+        <v>40.25</v>
       </c>
       <c r="Q43" t="n">
-        <v>-1.28</v>
+        <v>-2.19</v>
       </c>
       <c r="R43" t="n">
-        <v>-2.93</v>
+        <v>-5.16</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.84</v>
+        <v>5.92</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.04</v>
+        <v>0.08</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.68</v>
+        <v>1.37</v>
       </c>
       <c r="G44" t="n">
-        <v>5.92</v>
+        <v>5.87</v>
       </c>
       <c r="H44" t="n">
-        <v>0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="I44" t="n">
-        <v>1.37</v>
+        <v>-0.84</v>
       </c>
       <c r="J44" t="n">
-        <v>5.87</v>
+        <v>5.91</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.84</v>
+        <v>0.68</v>
       </c>
       <c r="M44" t="n">
-        <v>5.91</v>
+        <v>5.82</v>
       </c>
       <c r="N44" t="n">
-        <v>0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="O44" t="n">
-        <v>0.68</v>
+        <v>-1.52</v>
       </c>
       <c r="P44" t="n">
-        <v>5.91</v>
+        <v>5.82</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="R44" t="n">
-        <v>0.68</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="E45" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="F45" t="n">
+        <v>-1.97</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="H45" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F45" t="n">
-        <v>-0.49</v>
-      </c>
-      <c r="G45" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-0.04</v>
-      </c>
       <c r="I45" t="n">
-        <v>-1.97</v>
+        <v>-0.5</v>
       </c>
       <c r="J45" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.5</v>
+        <v>1.52</v>
       </c>
       <c r="M45" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="N45" t="n">
-        <v>0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="O45" t="n">
-        <v>1.52</v>
+        <v>-2.49</v>
       </c>
       <c r="P45" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="R45" t="n">
-        <v>1.52</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="E46" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="N46" t="n">
         <v>-0.05</v>
       </c>
-      <c r="F46" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="G46" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="M46" t="n">
-        <v>3.77</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0.01</v>
-      </c>
       <c r="O46" t="n">
-        <v>0.27</v>
+        <v>-1.33</v>
       </c>
       <c r="P46" t="n">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="R46" t="n">
-        <v>0.27</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.97</v>
+        <v>11.23</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.03</v>
+        <v>0.26</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.27</v>
+        <v>2.37</v>
       </c>
       <c r="G47" t="n">
-        <v>11.23</v>
+        <v>11</v>
       </c>
       <c r="H47" t="n">
-        <v>0.26</v>
+        <v>-0.23</v>
       </c>
       <c r="I47" t="n">
-        <v>2.37</v>
+        <v>-2.05</v>
       </c>
       <c r="J47" t="n">
-        <v>11</v>
+        <v>11.03</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.23</v>
+        <v>0.03</v>
       </c>
       <c r="L47" t="n">
-        <v>-2.05</v>
+        <v>0.27</v>
       </c>
       <c r="M47" t="n">
-        <v>11.03</v>
+        <v>10.51</v>
       </c>
       <c r="N47" t="n">
-        <v>0.03</v>
+        <v>-0.52</v>
       </c>
       <c r="O47" t="n">
-        <v>0.27</v>
+        <v>-4.71</v>
       </c>
       <c r="P47" t="n">
-        <v>11.03</v>
+        <v>10.51</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.03</v>
+        <v>-0.52</v>
       </c>
       <c r="R47" t="n">
-        <v>0.27</v>
+        <v>-4.71</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.295</v>
+        <v>0.29</v>
       </c>
       <c r="E48" t="n">
         <v>-0.005</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.67</v>
+        <v>-1.69</v>
       </c>
       <c r="G48" t="n">
-        <v>0.29</v>
+        <v>0.285</v>
       </c>
       <c r="H48" t="n">
         <v>-0.005</v>
       </c>
       <c r="I48" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="L48" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N48" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="O48" t="n">
         <v>-1.69</v>
       </c>
-      <c r="J48" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="K48" t="n">
+      <c r="P48" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="Q48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L48" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="O48" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0.01</v>
-      </c>
       <c r="R48" t="n">
-        <v>3.51</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G49" t="n">
         <v>4.25</v>
       </c>
-      <c r="E49" t="n">
+      <c r="H49" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F49" t="n">
+      <c r="I49" t="n">
         <v>-0.47</v>
       </c>
-      <c r="G49" t="n">
-        <v>4.27</v>
-      </c>
-      <c r="H49" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I49" t="n">
-        <v>0.47</v>
-      </c>
       <c r="J49" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.47</v>
+        <v>1.18</v>
       </c>
       <c r="M49" t="n">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
       <c r="N49" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="O49" t="n">
-        <v>1.18</v>
+        <v>-1.4</v>
       </c>
       <c r="P49" t="n">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="R49" t="n">
-        <v>1.18</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="50">
@@ -3500,40 +3500,40 @@
         <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="J50" t="n">
         <v>1.12</v>
       </c>
       <c r="K50" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>-1.79</v>
       </c>
       <c r="P50" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.02</v>
+        <v>5.08</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.99</v>
+        <v>1.2</v>
       </c>
       <c r="G51" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="H51" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="I51" t="n">
-        <v>1.2</v>
+        <v>-0.2</v>
       </c>
       <c r="J51" t="n">
         <v>5.07</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>5.07</v>
+        <v>4.94</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>-2.56</v>
       </c>
       <c r="P51" t="n">
-        <v>5.07</v>
+        <v>4.94</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.04</v>
+        <v>11.11</v>
       </c>
       <c r="E52" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G52" t="n">
+        <v>10.97</v>
+      </c>
+      <c r="H52" t="n">
         <v>-0.14</v>
       </c>
-      <c r="F52" t="n">
-        <v>-1.25</v>
-      </c>
-      <c r="G52" t="n">
-        <v>11.11</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.07000000000000001</v>
-      </c>
       <c r="I52" t="n">
-        <v>0.63</v>
+        <v>-1.26</v>
       </c>
       <c r="J52" t="n">
-        <v>10.97</v>
+        <v>11.02</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.14</v>
+        <v>0.05</v>
       </c>
       <c r="L52" t="n">
-        <v>-1.26</v>
+        <v>0.46</v>
       </c>
       <c r="M52" t="n">
-        <v>11.02</v>
+        <v>10.49</v>
       </c>
       <c r="N52" t="n">
-        <v>0.05</v>
+        <v>-0.53</v>
       </c>
       <c r="O52" t="n">
-        <v>0.46</v>
+        <v>-4.81</v>
       </c>
       <c r="P52" t="n">
-        <v>11.02</v>
+        <v>10.49</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.05</v>
+        <v>-0.53</v>
       </c>
       <c r="R52" t="n">
-        <v>0.46</v>
+        <v>-4.81</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7.04</v>
+        <v>7.02</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.08</v>
+        <v>-0.02</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.12</v>
+        <v>-0.28</v>
       </c>
       <c r="G53" t="n">
-        <v>7.02</v>
+        <v>6.99</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.28</v>
+        <v>-0.43</v>
       </c>
       <c r="J53" t="n">
-        <v>6.99</v>
+        <v>7.17</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.03</v>
+        <v>0.18</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.43</v>
+        <v>2.58</v>
       </c>
       <c r="M53" t="n">
-        <v>7.17</v>
+        <v>7.1</v>
       </c>
       <c r="N53" t="n">
-        <v>0.18</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O53" t="n">
-        <v>2.58</v>
+        <v>-0.98</v>
       </c>
       <c r="P53" t="n">
-        <v>7.17</v>
+        <v>7.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.18</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R53" t="n">
-        <v>2.58</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="54">
@@ -3742,10 +3742,10 @@
         <v>0.43</v>
       </c>
       <c r="E54" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="G54" t="n">
         <v>0.43</v>
@@ -3801,16 +3801,16 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.615</v>
+        <v>0.62</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>0.62</v>
+        <v>0.625</v>
       </c>
       <c r="H55" t="n">
         <v>0.005</v>
@@ -3819,31 +3819,31 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>0.625</v>
+        <v>0.62</v>
       </c>
       <c r="K55" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.8</v>
       </c>
       <c r="M55" t="n">
-        <v>0.62</v>
+        <v>0.615</v>
       </c>
       <c r="N55" t="n">
         <v>-0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.8</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P55" t="n">
-        <v>0.62</v>
+        <v>0.615</v>
       </c>
       <c r="Q55" t="n">
         <v>-0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.8</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -3866,46 +3866,46 @@
         <v>0.375</v>
       </c>
       <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="H56" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F56" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>-1.33</v>
       </c>
       <c r="J56" t="n">
-        <v>0.37</v>
+        <v>0.355</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.005</v>
+        <v>-0.015</v>
       </c>
       <c r="L56" t="n">
-        <v>-1.33</v>
+        <v>-4.05</v>
       </c>
       <c r="M56" t="n">
-        <v>0.355</v>
+        <v>0.345</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.015</v>
+        <v>-0.01</v>
       </c>
       <c r="O56" t="n">
-        <v>-4.05</v>
+        <v>-2.82</v>
       </c>
       <c r="P56" t="n">
-        <v>0.355</v>
+        <v>0.345</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.015</v>
+        <v>-0.01</v>
       </c>
       <c r="R56" t="n">
-        <v>-4.05</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.04</v>
+        <v>0.01</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.14</v>
+        <v>0.29</v>
       </c>
       <c r="G57" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="H57" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="I57" t="n">
-        <v>0.29</v>
+        <v>3.45</v>
       </c>
       <c r="J57" t="n">
         <v>3.6</v>
       </c>
       <c r="K57" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="L57" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>0</v>
+        <v>-1.94</v>
       </c>
       <c r="P57" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-0.001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-1.27</v>
+      </c>
+      <c r="G58" t="n">
         <v>0.079</v>
       </c>
-      <c r="E58" t="n">
-        <v>-0.002</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-2.47</v>
-      </c>
-      <c r="G58" t="n">
+      <c r="H58" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I58" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J58" t="n">
         <v>0.078</v>
       </c>
-      <c r="H58" t="n">
+      <c r="K58" t="n">
         <v>-0.001</v>
       </c>
-      <c r="I58" t="n">
+      <c r="L58" t="n">
         <v>-1.27</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="L58" t="n">
-        <v>1.28</v>
       </c>
       <c r="M58" t="n">
         <v>0.078</v>
       </c>
       <c r="N58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
         <v>0.078</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>20.99</v>
+        <v>20.75</v>
       </c>
       <c r="E59" t="n">
-        <v>-1.62</v>
+        <v>-0.24</v>
       </c>
       <c r="F59" t="n">
-        <v>-7.16</v>
+        <v>-1.14</v>
       </c>
       <c r="G59" t="n">
-        <v>20.75</v>
+        <v>21.04</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.24</v>
+        <v>0.29</v>
       </c>
       <c r="I59" t="n">
-        <v>-1.14</v>
+        <v>1.4</v>
       </c>
       <c r="J59" t="n">
-        <v>21.04</v>
+        <v>21.29</v>
       </c>
       <c r="K59" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="L59" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="M59" t="n">
-        <v>21.29</v>
+        <v>20.64</v>
       </c>
       <c r="N59" t="n">
-        <v>0.25</v>
+        <v>-0.65</v>
       </c>
       <c r="O59" t="n">
-        <v>1.19</v>
+        <v>-3.05</v>
       </c>
       <c r="P59" t="n">
-        <v>21.29</v>
+        <v>20.64</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.25</v>
+        <v>-0.65</v>
       </c>
       <c r="R59" t="n">
-        <v>1.19</v>
+        <v>-3.05</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="E60" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="F60" t="n">
-        <v>0.64</v>
+        <v>-0.63</v>
       </c>
       <c r="G60" t="n">
         <v>3.13</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="M60" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="N60" t="n">
-        <v>0.03</v>
+        <v>-0.11</v>
       </c>
       <c r="O60" t="n">
-        <v>0.96</v>
+        <v>-3.48</v>
       </c>
       <c r="P60" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.03</v>
+        <v>-0.11</v>
       </c>
       <c r="R60" t="n">
-        <v>0.96</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="61">
@@ -4176,10 +4176,10 @@
         <v>0.84</v>
       </c>
       <c r="E61" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
         <v>0.84</v>
@@ -4191,31 +4191,31 @@
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0.84</v>
+        <v>0.855</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="M61" t="n">
-        <v>0.855</v>
+        <v>0.83</v>
       </c>
       <c r="N61" t="n">
-        <v>0.015</v>
+        <v>-0.025</v>
       </c>
       <c r="O61" t="n">
-        <v>1.79</v>
+        <v>-2.92</v>
       </c>
       <c r="P61" t="n">
-        <v>0.855</v>
+        <v>0.83</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.015</v>
+        <v>-0.025</v>
       </c>
       <c r="R61" t="n">
-        <v>1.79</v>
+        <v>-2.92</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-10-05 Close</t>
+          <t>2026-10-06 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-10-05 Change</t>
+          <t>2026-10-06 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-10-05 Change %</t>
+          <t>2026-10-06 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-10-06 Close</t>
+          <t>2026-10-07 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-10-06 Change</t>
+          <t>2026-10-07 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-10-06 Change %</t>
+          <t>2026-10-07 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-10-07 Close</t>
+          <t>2026-10-08 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-10-07 Change</t>
+          <t>2026-10-08 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-10-07 Change %</t>
+          <t>2026-10-08 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-10-08 Close</t>
+          <t>2026-10-09 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-10-08 Change</t>
+          <t>2026-10-09 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-10-08 Change %</t>
+          <t>2026-10-09 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-10-09 Close</t>
+          <t>2026-10-12 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-10-09 Change</t>
+          <t>2026-10-12 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-10-09 Change %</t>
+          <t>2026-10-12 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
+        <v>152.8</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="G3" t="n">
         <v>149.9</v>
       </c>
-      <c r="E3" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="G3" t="n">
-        <v>152.8</v>
-      </c>
       <c r="H3" t="n">
-        <v>2.9</v>
+        <v>-2.9</v>
       </c>
       <c r="I3" t="n">
-        <v>1.93</v>
+        <v>-1.9</v>
       </c>
       <c r="J3" t="n">
-        <v>149.9</v>
+        <v>142.6</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.9</v>
+        <v>-7.3</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.9</v>
+        <v>-4.87</v>
       </c>
       <c r="M3" t="n">
-        <v>142.6</v>
+        <v>145.2</v>
       </c>
       <c r="N3" t="n">
-        <v>-7.3</v>
+        <v>2.6</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.87</v>
+        <v>1.82</v>
       </c>
       <c r="P3" t="n">
-        <v>142.6</v>
+        <v>145.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>-7.3</v>
+        <v>2.6</v>
       </c>
       <c r="R3" t="n">
-        <v>-4.87</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>228.6</v>
+        <v>236.4</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2</v>
+        <v>7.8</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.52</v>
+        <v>3.41</v>
       </c>
       <c r="G4" t="n">
-        <v>236.4</v>
+        <v>230</v>
       </c>
       <c r="H4" t="n">
-        <v>7.8</v>
+        <v>-6.4</v>
       </c>
       <c r="I4" t="n">
-        <v>3.41</v>
+        <v>-2.71</v>
       </c>
       <c r="J4" t="n">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.4</v>
+        <v>-12</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.71</v>
+        <v>-5.22</v>
       </c>
       <c r="M4" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="N4" t="n">
-        <v>-12</v>
+        <v>3</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.22</v>
+        <v>1.38</v>
       </c>
       <c r="P4" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="Q4" t="n">
-        <v>-12</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>-5.22</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.49</v>
+        <v>6.55</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="F5" t="n">
-        <v>0.46</v>
+        <v>0.92</v>
       </c>
       <c r="G5" t="n">
-        <v>6.55</v>
+        <v>6.57</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="I5" t="n">
-        <v>0.92</v>
+        <v>0.31</v>
       </c>
       <c r="J5" t="n">
-        <v>6.57</v>
+        <v>6.59</v>
       </c>
       <c r="K5" t="n">
         <v>0.02</v>
       </c>
       <c r="L5" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="M5" t="n">
-        <v>6.59</v>
+        <v>6.49</v>
       </c>
       <c r="N5" t="n">
-        <v>0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3</v>
+        <v>-1.52</v>
       </c>
       <c r="P5" t="n">
-        <v>6.59</v>
+        <v>6.49</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3</v>
+        <v>-1.52</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.45</v>
+        <v>7.58</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="G6" t="n">
         <v>7.58</v>
       </c>
       <c r="H6" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>7.58</v>
+        <v>7.57</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>7.57</v>
+        <v>7.5</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.13</v>
+        <v>-0.92</v>
       </c>
       <c r="P6" t="n">
-        <v>7.57</v>
+        <v>7.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.13</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.92</v>
+        <v>6.01</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="G7" t="n">
-        <v>6.01</v>
+        <v>5.99</v>
       </c>
       <c r="H7" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I7" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="M7" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="N7" t="n">
         <v>0.09</v>
       </c>
-      <c r="I7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="J7" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L7" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="M7" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.04</v>
-      </c>
       <c r="O7" t="n">
-        <v>0.67</v>
+        <v>1.49</v>
       </c>
       <c r="P7" t="n">
-        <v>6.03</v>
+        <v>6.12</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="R7" t="n">
-        <v>0.67</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.51</v>
+        <v>9.65</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.05</v>
+        <v>0.14</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.52</v>
+        <v>1.47</v>
       </c>
       <c r="G8" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.14</v>
+        <v>-0.02</v>
       </c>
       <c r="I8" t="n">
-        <v>1.47</v>
+        <v>-0.21</v>
       </c>
       <c r="J8" t="n">
-        <v>9.630000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.21</v>
+        <v>0.31</v>
       </c>
       <c r="M8" t="n">
-        <v>9.66</v>
+        <v>9.73</v>
       </c>
       <c r="N8" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>0.31</v>
+        <v>0.72</v>
       </c>
       <c r="P8" t="n">
-        <v>9.66</v>
+        <v>9.73</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>0.31</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.19</v>
+        <v>8.23</v>
       </c>
       <c r="E9" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H9" t="n">
         <v>-0.03</v>
       </c>
-      <c r="F9" t="n">
+      <c r="I9" t="n">
         <v>-0.36</v>
       </c>
-      <c r="G9" t="n">
-        <v>8.23</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="N9" t="n">
         <v>0.04</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="K9" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="L9" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="M9" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.15</v>
-      </c>
       <c r="O9" t="n">
-        <v>1.83</v>
+        <v>0.48</v>
       </c>
       <c r="P9" t="n">
-        <v>8.35</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="R9" t="n">
-        <v>1.83</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50.7</v>
+        <v>51</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2</v>
+        <v>0.59</v>
       </c>
       <c r="G10" t="n">
-        <v>51</v>
+        <v>50.95</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3</v>
+        <v>-0.05</v>
       </c>
       <c r="I10" t="n">
-        <v>0.59</v>
+        <v>-0.1</v>
       </c>
       <c r="J10" t="n">
-        <v>50.95</v>
+        <v>51.65</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.05</v>
+        <v>0.7</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1</v>
+        <v>1.37</v>
       </c>
       <c r="M10" t="n">
-        <v>51.65</v>
+        <v>52.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="O10" t="n">
-        <v>1.37</v>
+        <v>1.06</v>
       </c>
       <c r="P10" t="n">
-        <v>51.65</v>
+        <v>52.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="R10" t="n">
-        <v>1.37</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.38</v>
+        <v>4.39</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F11" t="n">
-        <v>0.46</v>
+        <v>0.23</v>
       </c>
       <c r="G11" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="H11" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="I11" t="n">
-        <v>0.23</v>
+        <v>0.68</v>
       </c>
       <c r="J11" t="n">
-        <v>4.42</v>
+        <v>4.53</v>
       </c>
       <c r="K11" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="L11" t="n">
-        <v>0.68</v>
+        <v>2.49</v>
       </c>
       <c r="M11" t="n">
         <v>4.53</v>
       </c>
       <c r="N11" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>4.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.56</v>
+        <v>9.67</v>
       </c>
       <c r="E12" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="F12" t="n">
-        <v>0.42</v>
+        <v>1.15</v>
       </c>
       <c r="G12" t="n">
-        <v>9.67</v>
+        <v>9.59</v>
       </c>
       <c r="H12" t="n">
-        <v>0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="I12" t="n">
-        <v>1.15</v>
+        <v>-0.83</v>
       </c>
       <c r="J12" t="n">
-        <v>9.59</v>
+        <v>9.83</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.08</v>
+        <v>0.24</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.83</v>
+        <v>2.5</v>
       </c>
       <c r="M12" t="n">
         <v>9.83</v>
       </c>
       <c r="N12" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>9.83</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23.42</v>
+        <v>23.44</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.43</v>
+        <v>0.09</v>
       </c>
       <c r="G13" t="n">
-        <v>23.44</v>
+        <v>23.52</v>
       </c>
       <c r="H13" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="J13" t="n">
-        <v>23.52</v>
+        <v>24.04</v>
       </c>
       <c r="K13" t="n">
-        <v>0.08</v>
+        <v>0.52</v>
       </c>
       <c r="L13" t="n">
-        <v>0.34</v>
+        <v>2.21</v>
       </c>
       <c r="M13" t="n">
-        <v>24.04</v>
+        <v>23.9</v>
       </c>
       <c r="N13" t="n">
-        <v>0.52</v>
+        <v>-0.14</v>
       </c>
       <c r="O13" t="n">
-        <v>2.21</v>
+        <v>-0.58</v>
       </c>
       <c r="P13" t="n">
-        <v>24.04</v>
+        <v>23.9</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.52</v>
+        <v>-0.14</v>
       </c>
       <c r="R13" t="n">
-        <v>2.21</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="G14" t="n">
         <v>1.85</v>
       </c>
-      <c r="E14" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.86</v>
-      </c>
       <c r="H14" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="I14" t="n">
-        <v>0.54</v>
+        <v>-0.54</v>
       </c>
       <c r="J14" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.54</v>
+        <v>1.62</v>
       </c>
       <c r="M14" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="N14" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="O14" t="n">
-        <v>1.62</v>
+        <v>1.06</v>
       </c>
       <c r="P14" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="R14" t="n">
-        <v>1.62</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="15">
@@ -1324,46 +1324,46 @@
         <v>5.24</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.19</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>5.24</v>
+        <v>5.29</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="J15" t="n">
-        <v>5.29</v>
+        <v>5.22</v>
       </c>
       <c r="K15" t="n">
-        <v>0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.95</v>
+        <v>-1.32</v>
       </c>
       <c r="M15" t="n">
-        <v>5.22</v>
+        <v>5.34</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.32</v>
+        <v>2.3</v>
       </c>
       <c r="P15" t="n">
-        <v>5.22</v>
+        <v>5.34</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.32</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="16">
@@ -1383,49 +1383,49 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.3</v>
+        <v>4.32</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.47</v>
       </c>
       <c r="G16" t="n">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="H16" t="n">
         <v>0.02</v>
       </c>
       <c r="I16" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="J16" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="K16" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="L16" t="n">
-        <v>0.46</v>
+        <v>-0.23</v>
       </c>
       <c r="M16" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.23</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="R16" t="n">
-        <v>-0.23</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F17" t="n">
-        <v>0.31</v>
+        <v>1.25</v>
       </c>
       <c r="G17" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="H17" t="n">
         <v>0.04</v>
       </c>
       <c r="I17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="J17" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="K17" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="L17" t="n">
-        <v>1.23</v>
+        <v>-1.52</v>
       </c>
       <c r="M17" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.52</v>
+        <v>-0.62</v>
       </c>
       <c r="P17" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="R17" t="n">
-        <v>-1.52</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="E18" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="G18" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="H18" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F18" t="n">
-        <v>-0.67</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.06</v>
-      </c>
       <c r="I18" t="n">
-        <v>2.03</v>
+        <v>-0.66</v>
       </c>
       <c r="J18" t="n">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.66</v>
+        <v>1.34</v>
       </c>
       <c r="M18" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="N18" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="O18" t="n">
-        <v>1.34</v>
+        <v>-0.33</v>
       </c>
       <c r="P18" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="R18" t="n">
-        <v>1.34</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>51.75</v>
+        <v>51.55</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.25</v>
+        <v>-0.2</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.48</v>
+        <v>-0.39</v>
       </c>
       <c r="G19" t="n">
-        <v>51.55</v>
+        <v>51.5</v>
       </c>
       <c r="H19" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="J19" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="K19" t="n">
         <v>-0.2</v>
       </c>
-      <c r="I19" t="n">
+      <c r="L19" t="n">
         <v>-0.39</v>
       </c>
-      <c r="J19" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="M19" t="n">
-        <v>51.3</v>
+        <v>51.85</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2</v>
+        <v>0.55</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.39</v>
+        <v>1.07</v>
       </c>
       <c r="P19" t="n">
-        <v>51.3</v>
+        <v>51.85</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2</v>
+        <v>0.55</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.39</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27.56</v>
+        <v>27.3</v>
       </c>
       <c r="E20" t="n">
-        <v>0.06</v>
+        <v>-0.26</v>
       </c>
       <c r="F20" t="n">
-        <v>0.22</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>27.3</v>
+        <v>27.26</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.26</v>
+        <v>-0.04</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.15</v>
       </c>
       <c r="J20" t="n">
-        <v>27.26</v>
+        <v>26.76</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.04</v>
+        <v>-0.5</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.15</v>
+        <v>-1.83</v>
       </c>
       <c r="M20" t="n">
-        <v>26.76</v>
+        <v>26.16</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.83</v>
+        <v>-2.24</v>
       </c>
       <c r="P20" t="n">
-        <v>26.76</v>
+        <v>26.16</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="R20" t="n">
-        <v>-1.83</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.46</v>
+        <v>4.51</v>
       </c>
       <c r="E21" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="F21" t="n">
-        <v>0.22</v>
+        <v>1.12</v>
       </c>
       <c r="G21" t="n">
-        <v>4.51</v>
+        <v>4.53</v>
       </c>
       <c r="H21" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="I21" t="n">
-        <v>1.12</v>
+        <v>0.44</v>
       </c>
       <c r="J21" t="n">
         <v>4.53</v>
       </c>
       <c r="K21" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L21" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.53</v>
+        <v>4.68</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P21" t="n">
-        <v>4.53</v>
+        <v>4.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>78.90000000000001</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="F22" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="G22" t="n">
-        <v>78.84999999999999</v>
+        <v>79.05</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.05</v>
+        <v>0.2</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.06</v>
+        <v>0.25</v>
       </c>
       <c r="J22" t="n">
-        <v>79.05</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="L22" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="M22" t="n">
-        <v>79.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="O22" t="n">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="P22" t="n">
-        <v>79.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="R22" t="n">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>21.62</v>
+        <v>21.8</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.04</v>
+        <v>0.18</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.18</v>
+        <v>0.83</v>
       </c>
       <c r="G23" t="n">
-        <v>21.8</v>
+        <v>21.72</v>
       </c>
       <c r="H23" t="n">
-        <v>0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="I23" t="n">
-        <v>0.83</v>
+        <v>-0.37</v>
       </c>
       <c r="J23" t="n">
-        <v>21.72</v>
+        <v>20.7</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.08</v>
+        <v>-1.02</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.37</v>
+        <v>-4.7</v>
       </c>
       <c r="M23" t="n">
-        <v>20.7</v>
+        <v>20.76</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.02</v>
+        <v>0.06</v>
       </c>
       <c r="O23" t="n">
-        <v>-4.7</v>
+        <v>0.29</v>
       </c>
       <c r="P23" t="n">
-        <v>20.7</v>
+        <v>20.76</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.02</v>
+        <v>0.06</v>
       </c>
       <c r="R23" t="n">
-        <v>-4.7</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.75</v>
+        <v>14.94</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.15</v>
+        <v>0.19</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.01</v>
+        <v>1.29</v>
       </c>
       <c r="G24" t="n">
-        <v>14.94</v>
+        <v>14.46</v>
       </c>
       <c r="H24" t="n">
-        <v>0.19</v>
+        <v>-0.48</v>
       </c>
       <c r="I24" t="n">
-        <v>1.29</v>
+        <v>-3.21</v>
       </c>
       <c r="J24" t="n">
-        <v>14.46</v>
+        <v>13.91</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.48</v>
+        <v>-0.55</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.21</v>
+        <v>-3.8</v>
       </c>
       <c r="M24" t="n">
-        <v>13.91</v>
+        <v>13.86</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.55</v>
+        <v>-0.05</v>
       </c>
       <c r="O24" t="n">
-        <v>-3.8</v>
+        <v>-0.36</v>
       </c>
       <c r="P24" t="n">
-        <v>13.91</v>
+        <v>13.86</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.55</v>
+        <v>-0.05</v>
       </c>
       <c r="R24" t="n">
-        <v>-3.8</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>23.88</v>
+        <v>24.26</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.36</v>
+        <v>0.38</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.49</v>
+        <v>1.59</v>
       </c>
       <c r="G25" t="n">
-        <v>24.26</v>
+        <v>23.94</v>
       </c>
       <c r="H25" t="n">
-        <v>0.38</v>
+        <v>-0.32</v>
       </c>
       <c r="I25" t="n">
-        <v>1.59</v>
+        <v>-1.32</v>
       </c>
       <c r="J25" t="n">
-        <v>23.94</v>
+        <v>23.66</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.32</v>
+        <v>-1.17</v>
       </c>
       <c r="M25" t="n">
-        <v>23.66</v>
+        <v>25.96</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.28</v>
+        <v>2.3</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.17</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>23.66</v>
+        <v>25.96</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.28</v>
+        <v>2.3</v>
       </c>
       <c r="R25" t="n">
-        <v>-1.17</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>36.82</v>
+        <v>35.6</v>
       </c>
       <c r="E26" t="n">
-        <v>0.92</v>
+        <v>-1.22</v>
       </c>
       <c r="F26" t="n">
-        <v>2.56</v>
+        <v>-3.31</v>
       </c>
       <c r="G26" t="n">
-        <v>35.6</v>
+        <v>34.44</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.22</v>
+        <v>-1.16</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.31</v>
+        <v>-3.26</v>
       </c>
       <c r="J26" t="n">
-        <v>34.44</v>
+        <v>30.36</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.16</v>
+        <v>-4.08</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.26</v>
+        <v>-11.85</v>
       </c>
       <c r="M26" t="n">
-        <v>30.36</v>
+        <v>31</v>
       </c>
       <c r="N26" t="n">
-        <v>-4.08</v>
+        <v>0.64</v>
       </c>
       <c r="O26" t="n">
-        <v>-11.85</v>
+        <v>2.11</v>
       </c>
       <c r="P26" t="n">
-        <v>30.36</v>
+        <v>31</v>
       </c>
       <c r="Q26" t="n">
-        <v>-4.08</v>
+        <v>0.64</v>
       </c>
       <c r="R26" t="n">
-        <v>-11.85</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>423</v>
+        <v>428.2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.8</v>
+        <v>5.2</v>
       </c>
       <c r="F27" t="n">
-        <v>0.43</v>
+        <v>1.23</v>
       </c>
       <c r="G27" t="n">
-        <v>428.2</v>
+        <v>420.6</v>
       </c>
       <c r="H27" t="n">
-        <v>5.2</v>
+        <v>-7.6</v>
       </c>
       <c r="I27" t="n">
-        <v>1.23</v>
+        <v>-1.77</v>
       </c>
       <c r="J27" t="n">
-        <v>420.6</v>
+        <v>411.4</v>
       </c>
       <c r="K27" t="n">
-        <v>-7.6</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.77</v>
+        <v>-2.19</v>
       </c>
       <c r="M27" t="n">
-        <v>411.4</v>
+        <v>424.8</v>
       </c>
       <c r="N27" t="n">
-        <v>-9.199999999999999</v>
+        <v>13.4</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.19</v>
+        <v>3.26</v>
       </c>
       <c r="P27" t="n">
-        <v>411.4</v>
+        <v>424.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>-9.199999999999999</v>
+        <v>13.4</v>
       </c>
       <c r="R27" t="n">
-        <v>-2.19</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
+        <v>108.2</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="G28" t="n">
         <v>105.4</v>
       </c>
-      <c r="E28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="G28" t="n">
-        <v>108.2</v>
-      </c>
       <c r="H28" t="n">
-        <v>2.8</v>
+        <v>-2.8</v>
       </c>
       <c r="I28" t="n">
-        <v>2.66</v>
+        <v>-2.59</v>
       </c>
       <c r="J28" t="n">
-        <v>105.4</v>
+        <v>104.3</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.8</v>
+        <v>-1.1</v>
       </c>
       <c r="L28" t="n">
-        <v>-2.59</v>
+        <v>-1.04</v>
       </c>
       <c r="M28" t="n">
-        <v>104.3</v>
+        <v>107</v>
       </c>
       <c r="N28" t="n">
-        <v>-1.1</v>
+        <v>2.7</v>
       </c>
       <c r="O28" t="n">
-        <v>-1.04</v>
+        <v>2.59</v>
       </c>
       <c r="P28" t="n">
-        <v>104.3</v>
+        <v>107</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1.1</v>
+        <v>2.7</v>
       </c>
       <c r="R28" t="n">
-        <v>-1.04</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>102.4</v>
+        <v>103.6</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5</v>
+        <v>1.2</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.49</v>
+        <v>1.17</v>
       </c>
       <c r="G29" t="n">
-        <v>103.6</v>
+        <v>104.9</v>
       </c>
       <c r="H29" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="I29" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="J29" t="n">
-        <v>104.9</v>
+        <v>105.2</v>
       </c>
       <c r="K29" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="L29" t="n">
-        <v>1.25</v>
+        <v>0.29</v>
       </c>
       <c r="M29" t="n">
-        <v>105.2</v>
+        <v>105.6</v>
       </c>
       <c r="N29" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="O29" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="P29" t="n">
-        <v>105.2</v>
+        <v>105.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="R29" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>70.65000000000001</v>
+        <v>70.8</v>
       </c>
       <c r="E30" t="n">
-        <v>0.45</v>
+        <v>0.15</v>
       </c>
       <c r="F30" t="n">
-        <v>0.64</v>
+        <v>0.21</v>
       </c>
       <c r="G30" t="n">
-        <v>70.8</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>0.15</v>
+        <v>-0.65</v>
       </c>
       <c r="I30" t="n">
-        <v>0.21</v>
+        <v>-0.92</v>
       </c>
       <c r="J30" t="n">
-        <v>70.15000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.65</v>
+        <v>-0.75</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.92</v>
+        <v>-1.07</v>
       </c>
       <c r="M30" t="n">
-        <v>69.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.75</v>
+        <v>2.1</v>
       </c>
       <c r="O30" t="n">
-        <v>-1.07</v>
+        <v>3.03</v>
       </c>
       <c r="P30" t="n">
-        <v>69.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>-0.75</v>
+        <v>2.1</v>
       </c>
       <c r="R30" t="n">
-        <v>-1.07</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>83.40000000000001</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>0.2</v>
+        <v>2.75</v>
       </c>
       <c r="F31" t="n">
-        <v>0.24</v>
+        <v>3.3</v>
       </c>
       <c r="G31" t="n">
-        <v>86.15000000000001</v>
+        <v>84.75</v>
       </c>
       <c r="H31" t="n">
-        <v>2.75</v>
+        <v>-1.4</v>
       </c>
       <c r="I31" t="n">
-        <v>3.3</v>
+        <v>-1.63</v>
       </c>
       <c r="J31" t="n">
-        <v>84.75</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.4</v>
+        <v>-2.6</v>
       </c>
       <c r="L31" t="n">
-        <v>-1.63</v>
+        <v>-3.07</v>
       </c>
       <c r="M31" t="n">
-        <v>82.15000000000001</v>
+        <v>83</v>
       </c>
       <c r="N31" t="n">
-        <v>-2.6</v>
+        <v>0.85</v>
       </c>
       <c r="O31" t="n">
-        <v>-3.07</v>
+        <v>1.03</v>
       </c>
       <c r="P31" t="n">
-        <v>82.15000000000001</v>
+        <v>83</v>
       </c>
       <c r="Q31" t="n">
-        <v>-2.6</v>
+        <v>0.85</v>
       </c>
       <c r="R31" t="n">
-        <v>-3.07</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>61.3</v>
+        <v>61.55</v>
       </c>
       <c r="E32" t="n">
-        <v>1.05</v>
+        <v>0.25</v>
       </c>
       <c r="F32" t="n">
-        <v>1.74</v>
+        <v>0.41</v>
       </c>
       <c r="G32" t="n">
-        <v>61.55</v>
+        <v>60.9</v>
       </c>
       <c r="H32" t="n">
-        <v>0.25</v>
+        <v>-0.65</v>
       </c>
       <c r="I32" t="n">
-        <v>0.41</v>
+        <v>-1.06</v>
       </c>
       <c r="J32" t="n">
-        <v>60.9</v>
+        <v>56.8</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.65</v>
+        <v>-4.1</v>
       </c>
       <c r="L32" t="n">
-        <v>-1.06</v>
+        <v>-6.73</v>
       </c>
       <c r="M32" t="n">
-        <v>56.8</v>
+        <v>57.65</v>
       </c>
       <c r="N32" t="n">
-        <v>-4.1</v>
+        <v>0.85</v>
       </c>
       <c r="O32" t="n">
-        <v>-6.73</v>
+        <v>1.5</v>
       </c>
       <c r="P32" t="n">
-        <v>56.8</v>
+        <v>57.65</v>
       </c>
       <c r="Q32" t="n">
-        <v>-4.1</v>
+        <v>0.85</v>
       </c>
       <c r="R32" t="n">
-        <v>-6.73</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>74.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="F33" t="n">
-        <v>0.27</v>
+        <v>1.21</v>
       </c>
       <c r="G33" t="n">
-        <v>75</v>
+        <v>74.55</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9</v>
+        <v>-0.45</v>
       </c>
       <c r="I33" t="n">
-        <v>1.21</v>
+        <v>-0.6</v>
       </c>
       <c r="J33" t="n">
-        <v>74.55</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.45</v>
+        <v>-1.65</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.6</v>
+        <v>-2.21</v>
       </c>
       <c r="M33" t="n">
-        <v>72.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>-1.65</v>
+        <v>2.7</v>
       </c>
       <c r="O33" t="n">
-        <v>-2.21</v>
+        <v>3.7</v>
       </c>
       <c r="P33" t="n">
-        <v>72.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>-1.65</v>
+        <v>2.7</v>
       </c>
       <c r="R33" t="n">
-        <v>-2.21</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>29.5</v>
+        <v>30.18</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.08</v>
+        <v>0.68</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.27</v>
+        <v>2.31</v>
       </c>
       <c r="G34" t="n">
-        <v>30.18</v>
+        <v>29.7</v>
       </c>
       <c r="H34" t="n">
-        <v>0.68</v>
+        <v>-0.48</v>
       </c>
       <c r="I34" t="n">
-        <v>2.31</v>
+        <v>-1.59</v>
       </c>
       <c r="J34" t="n">
-        <v>29.7</v>
+        <v>28.54</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.48</v>
+        <v>-1.16</v>
       </c>
       <c r="L34" t="n">
-        <v>-1.59</v>
+        <v>-3.91</v>
       </c>
       <c r="M34" t="n">
-        <v>28.54</v>
+        <v>30.1</v>
       </c>
       <c r="N34" t="n">
-        <v>-1.16</v>
+        <v>1.56</v>
       </c>
       <c r="O34" t="n">
-        <v>-3.91</v>
+        <v>5.47</v>
       </c>
       <c r="P34" t="n">
-        <v>28.54</v>
+        <v>30.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>-1.16</v>
+        <v>1.56</v>
       </c>
       <c r="R34" t="n">
-        <v>-3.91</v>
+        <v>5.47</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.09</v>
+        <v>4.14</v>
       </c>
       <c r="E35" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="F35" t="n">
-        <v>0.49</v>
+        <v>1.22</v>
       </c>
       <c r="G35" t="n">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="H35" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="I35" t="n">
-        <v>1.22</v>
+        <v>-0.72</v>
       </c>
       <c r="J35" t="n">
-        <v>4.11</v>
+        <v>3.99</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.72</v>
+        <v>-2.92</v>
       </c>
       <c r="M35" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.03</v>
+        <v>0.11</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.72</v>
+        <v>2.76</v>
       </c>
       <c r="P35" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.03</v>
+        <v>0.11</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.72</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8.81</v>
+        <v>8.9</v>
       </c>
       <c r="E36" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="G36" t="n">
-        <v>8.9</v>
+        <v>8.85</v>
       </c>
       <c r="H36" t="n">
-        <v>0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="I36" t="n">
-        <v>1.02</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>8.85</v>
+        <v>8.59</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.05</v>
+        <v>-0.26</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-2.94</v>
       </c>
       <c r="M36" t="n">
-        <v>8.85</v>
+        <v>8.84</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.05</v>
+        <v>0.25</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.5600000000000001</v>
+        <v>2.91</v>
       </c>
       <c r="P36" t="n">
-        <v>8.85</v>
+        <v>8.84</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.05</v>
+        <v>0.25</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.5600000000000001</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E37" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="F37" t="n">
-        <v>0.59</v>
+        <v>0.53</v>
       </c>
       <c r="G37" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H37" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="I37" t="n">
-        <v>0.53</v>
+        <v>-0.26</v>
       </c>
       <c r="J37" t="n">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="K37" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.26</v>
+        <v>-1.06</v>
       </c>
       <c r="M37" t="n">
-        <v>375</v>
+        <v>377.8</v>
       </c>
       <c r="N37" t="n">
-        <v>-4</v>
+        <v>2.8</v>
       </c>
       <c r="O37" t="n">
-        <v>-1.06</v>
+        <v>0.75</v>
       </c>
       <c r="P37" t="n">
-        <v>375</v>
+        <v>377.8</v>
       </c>
       <c r="Q37" t="n">
-        <v>-4</v>
+        <v>2.8</v>
       </c>
       <c r="R37" t="n">
-        <v>-1.06</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.53</v>
+        <v>11.43</v>
       </c>
       <c r="E38" t="n">
-        <v>0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="F38" t="n">
-        <v>1.32</v>
+        <v>-0.87</v>
       </c>
       <c r="G38" t="n">
-        <v>11.43</v>
+        <v>11.27</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.1</v>
+        <v>-0.16</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.87</v>
+        <v>-1.4</v>
       </c>
       <c r="J38" t="n">
-        <v>11.27</v>
+        <v>11.02</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.16</v>
+        <v>-0.25</v>
       </c>
       <c r="L38" t="n">
-        <v>-1.4</v>
+        <v>-2.22</v>
       </c>
       <c r="M38" t="n">
-        <v>11.02</v>
+        <v>11.46</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.25</v>
+        <v>0.44</v>
       </c>
       <c r="O38" t="n">
-        <v>-2.22</v>
+        <v>3.99</v>
       </c>
       <c r="P38" t="n">
-        <v>11.02</v>
+        <v>11.46</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.25</v>
+        <v>0.44</v>
       </c>
       <c r="R38" t="n">
-        <v>-2.22</v>
+        <v>3.99</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>483.4</v>
+        <v>488.6</v>
       </c>
       <c r="E39" t="n">
-        <v>6.6</v>
+        <v>5.2</v>
       </c>
       <c r="F39" t="n">
-        <v>1.38</v>
+        <v>1.08</v>
       </c>
       <c r="G39" t="n">
-        <v>488.6</v>
+        <v>486.4</v>
       </c>
       <c r="H39" t="n">
-        <v>5.2</v>
+        <v>-2.2</v>
       </c>
       <c r="I39" t="n">
-        <v>1.08</v>
+        <v>-0.45</v>
       </c>
       <c r="J39" t="n">
-        <v>486.4</v>
+        <v>476.8</v>
       </c>
       <c r="K39" t="n">
-        <v>-2.2</v>
+        <v>-9.6</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.45</v>
+        <v>-1.97</v>
       </c>
       <c r="M39" t="n">
-        <v>476.8</v>
+        <v>491.4</v>
       </c>
       <c r="N39" t="n">
-        <v>-9.6</v>
+        <v>14.6</v>
       </c>
       <c r="O39" t="n">
-        <v>-1.97</v>
+        <v>3.06</v>
       </c>
       <c r="P39" t="n">
-        <v>476.8</v>
+        <v>491.4</v>
       </c>
       <c r="Q39" t="n">
-        <v>-9.6</v>
+        <v>14.6</v>
       </c>
       <c r="R39" t="n">
-        <v>-1.97</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>36.28</v>
+        <v>37.2</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.08</v>
+        <v>0.92</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.22</v>
+        <v>2.54</v>
       </c>
       <c r="G40" t="n">
-        <v>37.2</v>
+        <v>38</v>
       </c>
       <c r="H40" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="I40" t="n">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="J40" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="K40" t="n">
-        <v>0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="L40" t="n">
-        <v>2.15</v>
+        <v>-1.32</v>
       </c>
       <c r="M40" t="n">
-        <v>37.5</v>
+        <v>38.34</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.5</v>
+        <v>0.84</v>
       </c>
       <c r="O40" t="n">
-        <v>-1.32</v>
+        <v>2.24</v>
       </c>
       <c r="P40" t="n">
-        <v>37.5</v>
+        <v>38.34</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.5</v>
+        <v>0.84</v>
       </c>
       <c r="R40" t="n">
-        <v>-1.32</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>31.88</v>
+        <v>32.2</v>
       </c>
       <c r="E41" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6899999999999999</v>
+        <v>1</v>
       </c>
       <c r="G41" t="n">
-        <v>32.2</v>
+        <v>30.3</v>
       </c>
       <c r="H41" t="n">
-        <v>0.32</v>
+        <v>-1.9</v>
       </c>
       <c r="I41" t="n">
-        <v>1</v>
+        <v>-5.9</v>
       </c>
       <c r="J41" t="n">
-        <v>30.3</v>
+        <v>29</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.9</v>
+        <v>-1.3</v>
       </c>
       <c r="L41" t="n">
-        <v>-5.9</v>
+        <v>-4.29</v>
       </c>
       <c r="M41" t="n">
         <v>29</v>
       </c>
       <c r="N41" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
-        <v>-4.29</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
         <v>29</v>
       </c>
       <c r="Q41" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>-4.29</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>77.83</v>
+        <v>78.56</v>
       </c>
       <c r="E42" t="n">
-        <v>0.62</v>
+        <v>0.73</v>
       </c>
       <c r="F42" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="G42" t="n">
-        <v>78.56</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>0.73</v>
+        <v>-1.07</v>
       </c>
       <c r="I42" t="n">
-        <v>0.9399999999999999</v>
+        <v>-1.36</v>
       </c>
       <c r="J42" t="n">
-        <v>77.48999999999999</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>-1.07</v>
+        <v>-3.64</v>
       </c>
       <c r="L42" t="n">
-        <v>-1.36</v>
+        <v>-4.7</v>
       </c>
       <c r="M42" t="n">
-        <v>73.84999999999999</v>
+        <v>73.36</v>
       </c>
       <c r="N42" t="n">
-        <v>-3.64</v>
+        <v>-0.49</v>
       </c>
       <c r="O42" t="n">
-        <v>-4.7</v>
+        <v>-0.66</v>
       </c>
       <c r="P42" t="n">
-        <v>73.84999999999999</v>
+        <v>73.36</v>
       </c>
       <c r="Q42" t="n">
-        <v>-3.64</v>
+        <v>-0.49</v>
       </c>
       <c r="R42" t="n">
-        <v>-4.7</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>43.06</v>
+        <v>43.72</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.05</v>
+        <v>0.66</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.12</v>
+        <v>1.53</v>
       </c>
       <c r="G43" t="n">
-        <v>43.72</v>
+        <v>42.44</v>
       </c>
       <c r="H43" t="n">
-        <v>0.66</v>
+        <v>-1.28</v>
       </c>
       <c r="I43" t="n">
-        <v>1.53</v>
+        <v>-2.93</v>
       </c>
       <c r="J43" t="n">
-        <v>42.44</v>
+        <v>40.25</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.28</v>
+        <v>-2.19</v>
       </c>
       <c r="L43" t="n">
-        <v>-2.93</v>
+        <v>-5.16</v>
       </c>
       <c r="M43" t="n">
-        <v>40.25</v>
+        <v>39.96</v>
       </c>
       <c r="N43" t="n">
-        <v>-2.19</v>
+        <v>-0.29</v>
       </c>
       <c r="O43" t="n">
-        <v>-5.16</v>
+        <v>-0.72</v>
       </c>
       <c r="P43" t="n">
-        <v>40.25</v>
+        <v>39.96</v>
       </c>
       <c r="Q43" t="n">
-        <v>-2.19</v>
+        <v>-0.29</v>
       </c>
       <c r="R43" t="n">
-        <v>-5.16</v>
+        <v>-0.72</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.92</v>
+        <v>5.87</v>
       </c>
       <c r="E44" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F44" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="G44" t="n">
+        <v>5.91</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="J44" t="n">
+        <v>5.82</v>
+      </c>
+      <c r="K44" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="L44" t="n">
+        <v>-1.52</v>
+      </c>
+      <c r="M44" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="N44" t="n">
         <v>0.08</v>
       </c>
-      <c r="F44" t="n">
+      <c r="O44" t="n">
         <v>1.37</v>
       </c>
-      <c r="G44" t="n">
-        <v>5.87</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I44" t="n">
-        <v>-0.84</v>
-      </c>
-      <c r="J44" t="n">
-        <v>5.91</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="M44" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="N44" t="n">
-        <v>-0.09</v>
-      </c>
-      <c r="O44" t="n">
-        <v>-1.52</v>
-      </c>
       <c r="P44" t="n">
-        <v>5.82</v>
+        <v>5.9</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.09</v>
+        <v>0.08</v>
       </c>
       <c r="R44" t="n">
-        <v>-1.52</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.97</v>
+        <v>-0.5</v>
       </c>
       <c r="G45" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5</v>
+        <v>1.52</v>
       </c>
       <c r="J45" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="K45" t="n">
-        <v>0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="L45" t="n">
-        <v>1.52</v>
+        <v>-2.49</v>
       </c>
       <c r="M45" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="O45" t="n">
-        <v>-2.49</v>
+        <v>2.04</v>
       </c>
       <c r="P45" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="R45" t="n">
-        <v>-2.49</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="E46" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="H46" t="n">
         <v>0.01</v>
       </c>
-      <c r="F46" t="n">
+      <c r="I46" t="n">
         <v>0.27</v>
       </c>
-      <c r="G46" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0.53</v>
-      </c>
       <c r="J46" t="n">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="K46" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="L46" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="N46" t="n">
         <v>0.01</v>
       </c>
-      <c r="L46" t="n">
+      <c r="O46" t="n">
         <v>0.27</v>
       </c>
-      <c r="M46" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="N46" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="O46" t="n">
-        <v>-1.33</v>
-      </c>
       <c r="P46" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="R46" t="n">
-        <v>-1.33</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.23</v>
+        <v>11</v>
       </c>
       <c r="E47" t="n">
-        <v>0.26</v>
+        <v>-0.23</v>
       </c>
       <c r="F47" t="n">
-        <v>2.37</v>
+        <v>-2.05</v>
       </c>
       <c r="G47" t="n">
-        <v>11</v>
+        <v>11.03</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.23</v>
+        <v>0.03</v>
       </c>
       <c r="I47" t="n">
-        <v>-2.05</v>
+        <v>0.27</v>
       </c>
       <c r="J47" t="n">
-        <v>11.03</v>
+        <v>10.51</v>
       </c>
       <c r="K47" t="n">
-        <v>0.03</v>
+        <v>-0.52</v>
       </c>
       <c r="L47" t="n">
-        <v>0.27</v>
+        <v>-4.71</v>
       </c>
       <c r="M47" t="n">
-        <v>10.51</v>
+        <v>10.42</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.52</v>
+        <v>-0.09</v>
       </c>
       <c r="O47" t="n">
-        <v>-4.71</v>
+        <v>-0.86</v>
       </c>
       <c r="P47" t="n">
-        <v>10.51</v>
+        <v>10.42</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.52</v>
+        <v>-0.09</v>
       </c>
       <c r="R47" t="n">
-        <v>-4.71</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.29</v>
+        <v>0.285</v>
       </c>
       <c r="E48" t="n">
         <v>-0.005</v>
       </c>
       <c r="F48" t="n">
+        <v>-1.72</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I48" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K48" t="n">
+        <v>-0.005</v>
+      </c>
+      <c r="L48" t="n">
         <v>-1.69</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-0.005</v>
-      </c>
-      <c r="I48" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L48" t="n">
-        <v>3.51</v>
       </c>
       <c r="M48" t="n">
         <v>0.29</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.69</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0.29</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>-1.69</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="E49" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="F49" t="n">
-        <v>0.47</v>
+        <v>-0.47</v>
       </c>
       <c r="G49" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.47</v>
+        <v>1.18</v>
       </c>
       <c r="J49" t="n">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
       <c r="K49" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="L49" t="n">
-        <v>1.18</v>
+        <v>-1.4</v>
       </c>
       <c r="M49" t="n">
         <v>4.24</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>4.24</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="G50" t="n">
         <v>1.12</v>
       </c>
       <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L50" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N50" t="n">
         <v>0.01</v>
       </c>
-      <c r="I50" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N50" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="O50" t="n">
-        <v>-1.79</v>
+        <v>0.91</v>
       </c>
       <c r="P50" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="R50" t="n">
-        <v>-1.79</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.08</v>
+        <v>5.07</v>
       </c>
       <c r="E51" t="n">
-        <v>0.06</v>
+        <v>-0.01</v>
       </c>
       <c r="F51" t="n">
-        <v>1.2</v>
+        <v>-0.2</v>
       </c>
       <c r="G51" t="n">
         <v>5.07</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>5.07</v>
+        <v>4.94</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>-2.56</v>
       </c>
       <c r="M51" t="n">
-        <v>4.94</v>
+        <v>5.1</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.13</v>
+        <v>0.16</v>
       </c>
       <c r="O51" t="n">
-        <v>-2.56</v>
+        <v>3.24</v>
       </c>
       <c r="P51" t="n">
-        <v>4.94</v>
+        <v>5.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.13</v>
+        <v>0.16</v>
       </c>
       <c r="R51" t="n">
-        <v>-2.56</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.11</v>
+        <v>10.97</v>
       </c>
       <c r="E52" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.14</v>
       </c>
       <c r="F52" t="n">
-        <v>0.63</v>
+        <v>-1.26</v>
       </c>
       <c r="G52" t="n">
-        <v>10.97</v>
+        <v>11.02</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.14</v>
+        <v>0.05</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.26</v>
+        <v>0.46</v>
       </c>
       <c r="J52" t="n">
-        <v>11.02</v>
+        <v>10.49</v>
       </c>
       <c r="K52" t="n">
-        <v>0.05</v>
+        <v>-0.53</v>
       </c>
       <c r="L52" t="n">
-        <v>0.46</v>
+        <v>-4.81</v>
       </c>
       <c r="M52" t="n">
-        <v>10.49</v>
+        <v>10.52</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.53</v>
+        <v>0.03</v>
       </c>
       <c r="O52" t="n">
-        <v>-4.81</v>
+        <v>0.29</v>
       </c>
       <c r="P52" t="n">
-        <v>10.49</v>
+        <v>10.52</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.53</v>
+        <v>0.03</v>
       </c>
       <c r="R52" t="n">
-        <v>-4.81</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7.02</v>
+        <v>6.99</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.28</v>
+        <v>-0.43</v>
       </c>
       <c r="G53" t="n">
-        <v>6.99</v>
+        <v>7.17</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.03</v>
+        <v>0.18</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.43</v>
+        <v>2.58</v>
       </c>
       <c r="J53" t="n">
-        <v>7.17</v>
+        <v>7.1</v>
       </c>
       <c r="K53" t="n">
-        <v>0.18</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>2.58</v>
+        <v>-0.98</v>
       </c>
       <c r="M53" t="n">
         <v>7.1</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
         <v>7.1</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3801,7 +3801,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.62</v>
+        <v>0.625</v>
       </c>
       <c r="E55" t="n">
         <v>0.005</v>
@@ -3810,40 +3810,40 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>0.625</v>
+        <v>0.62</v>
       </c>
       <c r="H55" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.8</v>
       </c>
       <c r="J55" t="n">
-        <v>0.62</v>
+        <v>0.615</v>
       </c>
       <c r="K55" t="n">
         <v>-0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.8</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="M55" t="n">
         <v>0.615</v>
       </c>
       <c r="N55" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
         <v>0.615</v>
       </c>
       <c r="Q55" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.375</v>
+        <v>0.37</v>
       </c>
       <c r="E56" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>-1.33</v>
       </c>
       <c r="G56" t="n">
-        <v>0.37</v>
+        <v>0.355</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.005</v>
+        <v>-0.015</v>
       </c>
       <c r="I56" t="n">
-        <v>-1.33</v>
+        <v>-4.05</v>
       </c>
       <c r="J56" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="M56" t="n">
         <v>0.355</v>
       </c>
-      <c r="K56" t="n">
-        <v>-0.015</v>
-      </c>
-      <c r="L56" t="n">
-        <v>-4.05</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.345</v>
-      </c>
       <c r="N56" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="O56" t="n">
-        <v>-2.82</v>
+        <v>2.9</v>
       </c>
       <c r="P56" t="n">
-        <v>0.345</v>
+        <v>0.355</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="R56" t="n">
-        <v>-2.82</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="E57" t="n">
-        <v>0.01</v>
+        <v>0.12</v>
       </c>
       <c r="F57" t="n">
-        <v>0.29</v>
+        <v>3.45</v>
       </c>
       <c r="G57" t="n">
         <v>3.6</v>
       </c>
       <c r="H57" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="K57" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>-1.94</v>
       </c>
       <c r="M57" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="O57" t="n">
-        <v>-1.94</v>
+        <v>0.57</v>
       </c>
       <c r="P57" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="R57" t="n">
-        <v>-1.94</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="58">
@@ -3987,31 +3987,31 @@
         </is>
       </c>
       <c r="D58" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="G58" t="n">
         <v>0.078</v>
       </c>
-      <c r="E58" t="n">
+      <c r="H58" t="n">
         <v>-0.001</v>
       </c>
-      <c r="F58" t="n">
+      <c r="I58" t="n">
         <v>-1.27</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="I58" t="n">
-        <v>1.28</v>
       </c>
       <c r="J58" t="n">
         <v>0.078</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0.078</v>
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>20.75</v>
+        <v>21.04</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.24</v>
+        <v>0.29</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.14</v>
+        <v>1.4</v>
       </c>
       <c r="G59" t="n">
-        <v>21.04</v>
+        <v>21.29</v>
       </c>
       <c r="H59" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="I59" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="J59" t="n">
-        <v>21.29</v>
+        <v>20.64</v>
       </c>
       <c r="K59" t="n">
-        <v>0.25</v>
+        <v>-0.65</v>
       </c>
       <c r="L59" t="n">
-        <v>1.19</v>
+        <v>-3.05</v>
       </c>
       <c r="M59" t="n">
-        <v>20.64</v>
+        <v>20.73</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.65</v>
+        <v>0.09</v>
       </c>
       <c r="O59" t="n">
-        <v>-3.05</v>
+        <v>0.44</v>
       </c>
       <c r="P59" t="n">
-        <v>20.64</v>
+        <v>20.73</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.65</v>
+        <v>0.09</v>
       </c>
       <c r="R59" t="n">
-        <v>-3.05</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="60">
@@ -4114,46 +4114,46 @@
         <v>3.13</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>-0.63</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="J60" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="K60" t="n">
-        <v>0.03</v>
+        <v>-0.11</v>
       </c>
       <c r="L60" t="n">
-        <v>0.96</v>
+        <v>-3.48</v>
       </c>
       <c r="M60" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N60" t="n">
-        <v>-0.11</v>
+        <v>0.05</v>
       </c>
       <c r="O60" t="n">
-        <v>-3.48</v>
+        <v>1.64</v>
       </c>
       <c r="P60" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.11</v>
+        <v>0.05</v>
       </c>
       <c r="R60" t="n">
-        <v>-3.48</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="61">
@@ -4182,40 +4182,40 @@
         <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.84</v>
+        <v>0.855</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="J61" t="n">
-        <v>0.855</v>
+        <v>0.83</v>
       </c>
       <c r="K61" t="n">
-        <v>0.015</v>
+        <v>-0.025</v>
       </c>
       <c r="L61" t="n">
-        <v>1.79</v>
+        <v>-2.92</v>
       </c>
       <c r="M61" t="n">
-        <v>0.83</v>
+        <v>0.835</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.025</v>
+        <v>0.005</v>
       </c>
       <c r="O61" t="n">
-        <v>-2.92</v>
+        <v>0.6</v>
       </c>
       <c r="P61" t="n">
-        <v>0.83</v>
+        <v>0.835</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.025</v>
+        <v>0.005</v>
       </c>
       <c r="R61" t="n">
-        <v>-2.92</v>
+        <v>0.6</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-10-06 Close</t>
+          <t>2026-10-07 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-10-06 Change</t>
+          <t>2026-10-07 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-10-06 Change %</t>
+          <t>2026-10-07 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-10-07 Close</t>
+          <t>2026-10-08 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-10-07 Change</t>
+          <t>2026-10-08 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-10-07 Change %</t>
+          <t>2026-10-08 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-10-08 Close</t>
+          <t>2026-10-09 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-10-08 Change</t>
+          <t>2026-10-09 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-10-08 Change %</t>
+          <t>2026-10-09 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-10-09 Close</t>
+          <t>2026-10-12 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-10-09 Change</t>
+          <t>2026-10-12 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-10-09 Change %</t>
+          <t>2026-10-12 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-10-12 Close</t>
+          <t>2026-10-13 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-10-12 Change</t>
+          <t>2026-10-13 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-10-12 Change %</t>
+          <t>2026-10-13 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>152.8</v>
+        <v>149.9</v>
       </c>
       <c r="E3" t="n">
+        <v>-2.9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="G3" t="n">
+        <v>142.6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-7.3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-4.87</v>
+      </c>
+      <c r="J3" t="n">
+        <v>145.2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="M3" t="n">
+        <v>148.1</v>
+      </c>
+      <c r="N3" t="n">
         <v>2.9</v>
       </c>
-      <c r="F3" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="G3" t="n">
-        <v>149.9</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-1.9</v>
-      </c>
-      <c r="J3" t="n">
-        <v>142.6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>-7.3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-4.87</v>
-      </c>
-      <c r="M3" t="n">
-        <v>145.2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.6</v>
-      </c>
       <c r="O3" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>145.2</v>
+        <v>150.7</v>
       </c>
       <c r="Q3" t="n">
         <v>2.6</v>
       </c>
       <c r="R3" t="n">
-        <v>1.82</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>236.4</v>
+        <v>230</v>
       </c>
       <c r="E4" t="n">
-        <v>7.8</v>
+        <v>-6.4</v>
       </c>
       <c r="F4" t="n">
-        <v>3.41</v>
+        <v>-2.71</v>
       </c>
       <c r="G4" t="n">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="H4" t="n">
-        <v>-6.4</v>
+        <v>-12</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.71</v>
+        <v>-5.22</v>
       </c>
       <c r="J4" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="K4" t="n">
-        <v>-12</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
-        <v>-5.22</v>
+        <v>1.38</v>
       </c>
       <c r="M4" t="n">
-        <v>221</v>
+        <v>224.4</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="P4" t="n">
-        <v>221</v>
+        <v>229.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>5.4</v>
       </c>
       <c r="R4" t="n">
-        <v>1.38</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.55</v>
+        <v>6.57</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="F5" t="n">
-        <v>0.92</v>
+        <v>0.31</v>
       </c>
       <c r="G5" t="n">
-        <v>6.57</v>
+        <v>6.59</v>
       </c>
       <c r="H5" t="n">
         <v>0.02</v>
       </c>
       <c r="I5" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="J5" t="n">
-        <v>6.59</v>
+        <v>6.49</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3</v>
+        <v>-1.52</v>
       </c>
       <c r="M5" t="n">
-        <v>6.49</v>
+        <v>6.66</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1</v>
+        <v>0.17</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.52</v>
+        <v>2.62</v>
       </c>
       <c r="P5" t="n">
-        <v>6.49</v>
+        <v>6.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.1</v>
+        <v>0.06</v>
       </c>
       <c r="R5" t="n">
-        <v>-1.52</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -766,46 +766,46 @@
         <v>7.58</v>
       </c>
       <c r="E6" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>7.58</v>
+        <v>7.57</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="J6" t="n">
-        <v>7.57</v>
+        <v>7.5</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.13</v>
+        <v>-0.92</v>
       </c>
       <c r="M6" t="n">
-        <v>7.5</v>
+        <v>7.62</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.92</v>
+        <v>1.6</v>
       </c>
       <c r="P6" t="n">
-        <v>7.5</v>
+        <v>7.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.92</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.01</v>
+        <v>5.99</v>
       </c>
       <c r="E7" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F7" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="G7" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J7" t="n">
+        <v>6.12</v>
+      </c>
+      <c r="K7" t="n">
         <v>0.09</v>
       </c>
-      <c r="F7" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5.99</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I7" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="J7" t="n">
-        <v>6.03</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0.04</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.67</v>
+        <v>1.49</v>
       </c>
       <c r="M7" t="n">
-        <v>6.12</v>
+        <v>6.25</v>
       </c>
       <c r="N7" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="O7" t="n">
-        <v>1.49</v>
+        <v>2.12</v>
       </c>
       <c r="P7" t="n">
-        <v>6.12</v>
+        <v>6.26</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.09</v>
+        <v>0.01</v>
       </c>
       <c r="R7" t="n">
-        <v>1.49</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.65</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.14</v>
+        <v>-0.02</v>
       </c>
       <c r="F8" t="n">
-        <v>1.47</v>
+        <v>-0.21</v>
       </c>
       <c r="G8" t="n">
-        <v>9.630000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.21</v>
+        <v>0.31</v>
       </c>
       <c r="J8" t="n">
-        <v>9.66</v>
+        <v>9.73</v>
       </c>
       <c r="K8" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0.31</v>
+        <v>0.72</v>
       </c>
       <c r="M8" t="n">
-        <v>9.73</v>
+        <v>9.91</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="O8" t="n">
-        <v>0.72</v>
+        <v>1.85</v>
       </c>
       <c r="P8" t="n">
-        <v>9.73</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.05</v>
       </c>
       <c r="R8" t="n">
-        <v>0.72</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.23</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="E9" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="F9" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="K9" t="n">
         <v>0.04</v>
       </c>
-      <c r="F9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="G9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="I9" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.15</v>
-      </c>
       <c r="L9" t="n">
-        <v>1.83</v>
+        <v>0.48</v>
       </c>
       <c r="M9" t="n">
-        <v>8.390000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04</v>
+        <v>0.2</v>
       </c>
       <c r="O9" t="n">
-        <v>0.48</v>
+        <v>2.38</v>
       </c>
       <c r="P9" t="n">
-        <v>8.390000000000001</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="Q9" t="n">
         <v>0.04</v>
       </c>
       <c r="R9" t="n">
-        <v>0.48</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51</v>
+        <v>50.95</v>
       </c>
       <c r="E10" t="n">
-        <v>0.3</v>
+        <v>-0.05</v>
       </c>
       <c r="F10" t="n">
-        <v>0.59</v>
+        <v>-0.1</v>
       </c>
       <c r="G10" t="n">
-        <v>50.95</v>
+        <v>51.65</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.05</v>
+        <v>0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1</v>
+        <v>1.37</v>
       </c>
       <c r="J10" t="n">
-        <v>51.65</v>
+        <v>52.2</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="L10" t="n">
-        <v>1.37</v>
+        <v>1.06</v>
       </c>
       <c r="M10" t="n">
-        <v>52.2</v>
+        <v>53.8</v>
       </c>
       <c r="N10" t="n">
-        <v>0.55</v>
+        <v>1.6</v>
       </c>
       <c r="O10" t="n">
-        <v>1.06</v>
+        <v>3.07</v>
       </c>
       <c r="P10" t="n">
-        <v>52.2</v>
+        <v>53.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.55</v>
+        <v>0.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.06</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.39</v>
+        <v>4.42</v>
       </c>
       <c r="E11" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="F11" t="n">
-        <v>0.23</v>
+        <v>0.68</v>
       </c>
       <c r="G11" t="n">
-        <v>4.42</v>
+        <v>4.53</v>
       </c>
       <c r="H11" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="I11" t="n">
-        <v>0.68</v>
+        <v>2.49</v>
       </c>
       <c r="J11" t="n">
         <v>4.53</v>
       </c>
       <c r="K11" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.53</v>
+        <v>4.51</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0.44</v>
       </c>
       <c r="P11" t="n">
         <v>4.53</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.67</v>
+        <v>9.59</v>
       </c>
       <c r="E12" t="n">
-        <v>0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="F12" t="n">
-        <v>1.15</v>
+        <v>-0.83</v>
       </c>
       <c r="G12" t="n">
-        <v>9.59</v>
+        <v>9.83</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.08</v>
+        <v>0.24</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.83</v>
+        <v>2.5</v>
       </c>
       <c r="J12" t="n">
         <v>9.83</v>
       </c>
       <c r="K12" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="P12" t="n">
-        <v>9.83</v>
+        <v>10.22</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.37</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23.44</v>
+        <v>23.52</v>
       </c>
       <c r="E13" t="n">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="F13" t="n">
-        <v>0.09</v>
+        <v>0.34</v>
       </c>
       <c r="G13" t="n">
-        <v>23.52</v>
+        <v>24.04</v>
       </c>
       <c r="H13" t="n">
-        <v>0.08</v>
+        <v>0.52</v>
       </c>
       <c r="I13" t="n">
-        <v>0.34</v>
+        <v>2.21</v>
       </c>
       <c r="J13" t="n">
-        <v>24.04</v>
+        <v>23.9</v>
       </c>
       <c r="K13" t="n">
-        <v>0.52</v>
+        <v>-0.14</v>
       </c>
       <c r="L13" t="n">
-        <v>2.21</v>
+        <v>-0.58</v>
       </c>
       <c r="M13" t="n">
-        <v>23.9</v>
+        <v>24.14</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.14</v>
+        <v>0.24</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.58</v>
+        <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>23.9</v>
+        <v>24.28</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.14</v>
+        <v>0.14</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.58</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="14">
@@ -1259,49 +1259,49 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="F14" t="n">
-        <v>0.54</v>
+        <v>-0.54</v>
       </c>
       <c r="G14" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="H14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="M14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="N14" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I14" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="J14" t="n">
+      <c r="O14" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="P14" t="n">
         <v>1.88</v>
       </c>
-      <c r="K14" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.9</v>
-      </c>
       <c r="Q14" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="R14" t="n">
-        <v>1.06</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.24</v>
+        <v>5.29</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="G15" t="n">
-        <v>5.29</v>
+        <v>5.22</v>
       </c>
       <c r="H15" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="L15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="P15" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="Q15" t="n">
         <v>0.05</v>
       </c>
-      <c r="I15" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="P15" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.12</v>
-      </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="16">
@@ -1383,34 +1383,34 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="E16" t="n">
         <v>0.02</v>
       </c>
       <c r="F16" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="G16" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="H16" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I16" t="n">
-        <v>0.46</v>
+        <v>-0.23</v>
       </c>
       <c r="J16" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.23</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="N16" t="n">
         <v>0.03</v>
@@ -1419,13 +1419,13 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="E17" t="n">
         <v>0.04</v>
       </c>
       <c r="F17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="G17" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="I17" t="n">
-        <v>1.23</v>
+        <v>-1.52</v>
       </c>
       <c r="J17" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.52</v>
+        <v>-0.62</v>
       </c>
       <c r="M17" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.62</v>
+        <v>0.31</v>
       </c>
       <c r="P17" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="R17" t="n">
-        <v>-0.62</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.01</v>
+        <v>2.99</v>
       </c>
       <c r="E18" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="F18" t="n">
-        <v>2.03</v>
+        <v>-0.66</v>
       </c>
       <c r="G18" t="n">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.66</v>
+        <v>1.34</v>
       </c>
       <c r="J18" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="K18" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="M18" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="N18" t="n">
         <v>0.04</v>
       </c>
-      <c r="L18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="M18" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="O18" t="n">
-        <v>-0.33</v>
+        <v>1.32</v>
       </c>
       <c r="P18" t="n">
-        <v>3.02</v>
+        <v>3.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.01</v>
+        <v>0.11</v>
       </c>
       <c r="R18" t="n">
-        <v>-0.33</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>51.55</v>
+        <v>51.5</v>
       </c>
       <c r="E19" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="G19" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="H19" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F19" t="n">
+      <c r="I19" t="n">
         <v>-0.39</v>
       </c>
-      <c r="G19" t="n">
-        <v>51.5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-0.1</v>
-      </c>
       <c r="J19" t="n">
-        <v>51.3</v>
+        <v>51.85</v>
       </c>
       <c r="K19" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="L19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="M19" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="N19" t="n">
         <v>-0.2</v>
       </c>
-      <c r="L19" t="n">
+      <c r="O19" t="n">
         <v>-0.39</v>
       </c>
-      <c r="M19" t="n">
-        <v>51.85</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1.07</v>
-      </c>
       <c r="P19" t="n">
-        <v>51.85</v>
+        <v>51.35</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.55</v>
+        <v>-0.3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.07</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27.3</v>
+        <v>27.26</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.26</v>
+        <v>-0.04</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.15</v>
       </c>
       <c r="G20" t="n">
-        <v>27.26</v>
+        <v>26.76</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.04</v>
+        <v>-0.5</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.15</v>
+        <v>-1.83</v>
       </c>
       <c r="J20" t="n">
-        <v>26.76</v>
+        <v>26.16</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.83</v>
+        <v>-2.24</v>
       </c>
       <c r="M20" t="n">
-        <v>26.16</v>
+        <v>26.26</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6</v>
+        <v>0.1</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.24</v>
+        <v>0.38</v>
       </c>
       <c r="P20" t="n">
-        <v>26.16</v>
+        <v>25.62</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.6</v>
+        <v>-0.64</v>
       </c>
       <c r="R20" t="n">
-        <v>-2.24</v>
+        <v>-2.44</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.51</v>
+        <v>4.53</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="F21" t="n">
-        <v>1.12</v>
+        <v>0.44</v>
       </c>
       <c r="G21" t="n">
         <v>4.53</v>
       </c>
       <c r="H21" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>4.53</v>
+        <v>4.68</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="M21" t="n">
-        <v>4.68</v>
+        <v>4.66</v>
       </c>
       <c r="N21" t="n">
-        <v>0.15</v>
+        <v>-0.02</v>
       </c>
       <c r="O21" t="n">
-        <v>3.31</v>
+        <v>-0.43</v>
       </c>
       <c r="P21" t="n">
         <v>4.68</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.15</v>
+        <v>0.02</v>
       </c>
       <c r="R21" t="n">
-        <v>3.31</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>78.84999999999999</v>
+        <v>79.05</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.05</v>
+        <v>0.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.06</v>
+        <v>0.25</v>
       </c>
       <c r="G22" t="n">
-        <v>79.05</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="I22" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="J22" t="n">
-        <v>79.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="L22" t="n">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="M22" t="n">
-        <v>80.09999999999999</v>
+        <v>79.95</v>
       </c>
       <c r="N22" t="n">
-        <v>0.7</v>
+        <v>-0.15</v>
       </c>
       <c r="O22" t="n">
-        <v>0.88</v>
+        <v>-0.19</v>
       </c>
       <c r="P22" t="n">
-        <v>80.09999999999999</v>
+        <v>80.45</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="R22" t="n">
-        <v>0.88</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>21.8</v>
+        <v>21.72</v>
       </c>
       <c r="E23" t="n">
-        <v>0.18</v>
+        <v>-0.08</v>
       </c>
       <c r="F23" t="n">
-        <v>0.83</v>
+        <v>-0.37</v>
       </c>
       <c r="G23" t="n">
-        <v>21.72</v>
+        <v>20.7</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.08</v>
+        <v>-1.02</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.37</v>
+        <v>-4.7</v>
       </c>
       <c r="J23" t="n">
-        <v>20.7</v>
+        <v>20.76</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.02</v>
+        <v>0.06</v>
       </c>
       <c r="L23" t="n">
-        <v>-4.7</v>
+        <v>0.29</v>
       </c>
       <c r="M23" t="n">
-        <v>20.76</v>
+        <v>20.36</v>
       </c>
       <c r="N23" t="n">
-        <v>0.06</v>
+        <v>-0.4</v>
       </c>
       <c r="O23" t="n">
-        <v>0.29</v>
+        <v>-1.93</v>
       </c>
       <c r="P23" t="n">
-        <v>20.76</v>
+        <v>20.12</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.06</v>
+        <v>-0.24</v>
       </c>
       <c r="R23" t="n">
-        <v>0.29</v>
+        <v>-1.18</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.94</v>
+        <v>14.46</v>
       </c>
       <c r="E24" t="n">
-        <v>0.19</v>
+        <v>-0.48</v>
       </c>
       <c r="F24" t="n">
-        <v>1.29</v>
+        <v>-3.21</v>
       </c>
       <c r="G24" t="n">
-        <v>14.46</v>
+        <v>13.91</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.48</v>
+        <v>-0.55</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.21</v>
+        <v>-3.8</v>
       </c>
       <c r="J24" t="n">
-        <v>13.91</v>
+        <v>13.86</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.55</v>
+        <v>-0.05</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.8</v>
+        <v>-0.36</v>
       </c>
       <c r="M24" t="n">
-        <v>13.86</v>
+        <v>13.48</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.05</v>
+        <v>-0.38</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.36</v>
+        <v>-2.74</v>
       </c>
       <c r="P24" t="n">
-        <v>13.86</v>
+        <v>12.89</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.05</v>
+        <v>-0.59</v>
       </c>
       <c r="R24" t="n">
-        <v>-0.36</v>
+        <v>-4.38</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>24.26</v>
+        <v>23.94</v>
       </c>
       <c r="E25" t="n">
-        <v>0.38</v>
+        <v>-0.32</v>
       </c>
       <c r="F25" t="n">
-        <v>1.59</v>
+        <v>-1.32</v>
       </c>
       <c r="G25" t="n">
-        <v>23.94</v>
+        <v>23.66</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.32</v>
+        <v>-1.17</v>
       </c>
       <c r="J25" t="n">
-        <v>23.66</v>
+        <v>25.96</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.28</v>
+        <v>2.3</v>
       </c>
       <c r="L25" t="n">
-        <v>-1.17</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>25.96</v>
+        <v>24.52</v>
       </c>
       <c r="N25" t="n">
-        <v>2.3</v>
+        <v>-1.44</v>
       </c>
       <c r="O25" t="n">
-        <v>9.720000000000001</v>
+        <v>-5.55</v>
       </c>
       <c r="P25" t="n">
-        <v>25.96</v>
+        <v>25.04</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.3</v>
+        <v>0.52</v>
       </c>
       <c r="R25" t="n">
-        <v>9.720000000000001</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>35.6</v>
+        <v>34.44</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.22</v>
+        <v>-1.16</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.31</v>
+        <v>-3.26</v>
       </c>
       <c r="G26" t="n">
-        <v>34.44</v>
+        <v>30.36</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.16</v>
+        <v>-4.08</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.26</v>
+        <v>-11.85</v>
       </c>
       <c r="J26" t="n">
-        <v>30.36</v>
+        <v>31</v>
       </c>
       <c r="K26" t="n">
-        <v>-4.08</v>
+        <v>0.64</v>
       </c>
       <c r="L26" t="n">
-        <v>-11.85</v>
+        <v>2.11</v>
       </c>
       <c r="M26" t="n">
-        <v>31</v>
+        <v>29.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.64</v>
+        <v>-1.1</v>
       </c>
       <c r="O26" t="n">
-        <v>2.11</v>
+        <v>-3.55</v>
       </c>
       <c r="P26" t="n">
-        <v>31</v>
+        <v>28.24</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.64</v>
+        <v>-1.66</v>
       </c>
       <c r="R26" t="n">
-        <v>2.11</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>428.2</v>
+        <v>420.6</v>
       </c>
       <c r="E27" t="n">
-        <v>5.2</v>
+        <v>-7.6</v>
       </c>
       <c r="F27" t="n">
-        <v>1.23</v>
+        <v>-1.77</v>
       </c>
       <c r="G27" t="n">
-        <v>420.6</v>
+        <v>411.4</v>
       </c>
       <c r="H27" t="n">
-        <v>-7.6</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.77</v>
+        <v>-2.19</v>
       </c>
       <c r="J27" t="n">
-        <v>411.4</v>
+        <v>424.8</v>
       </c>
       <c r="K27" t="n">
-        <v>-9.199999999999999</v>
+        <v>13.4</v>
       </c>
       <c r="L27" t="n">
-        <v>-2.19</v>
+        <v>3.26</v>
       </c>
       <c r="M27" t="n">
-        <v>424.8</v>
+        <v>425.8</v>
       </c>
       <c r="N27" t="n">
-        <v>13.4</v>
+        <v>1</v>
       </c>
       <c r="O27" t="n">
-        <v>3.26</v>
+        <v>0.24</v>
       </c>
       <c r="P27" t="n">
-        <v>424.8</v>
+        <v>425.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>13.4</v>
+        <v>-0.6</v>
       </c>
       <c r="R27" t="n">
-        <v>3.26</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
+        <v>105.4</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-2.8</v>
+      </c>
+      <c r="F28" t="n">
+        <v>-2.59</v>
+      </c>
+      <c r="G28" t="n">
+        <v>104.3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>-1.04</v>
+      </c>
+      <c r="J28" t="n">
+        <v>107</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L28" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="M28" t="n">
         <v>108.2</v>
       </c>
-      <c r="E28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F28" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="G28" t="n">
-        <v>105.4</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-2.8</v>
-      </c>
-      <c r="I28" t="n">
-        <v>-2.59</v>
-      </c>
-      <c r="J28" t="n">
-        <v>104.3</v>
-      </c>
-      <c r="K28" t="n">
-        <v>-1.1</v>
-      </c>
-      <c r="L28" t="n">
-        <v>-1.04</v>
-      </c>
-      <c r="M28" t="n">
-        <v>107</v>
-      </c>
       <c r="N28" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="O28" t="n">
-        <v>2.59</v>
+        <v>1.12</v>
       </c>
       <c r="P28" t="n">
-        <v>107</v>
+        <v>107.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.7</v>
+        <v>-1</v>
       </c>
       <c r="R28" t="n">
-        <v>2.59</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>103.6</v>
+        <v>104.9</v>
       </c>
       <c r="E29" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="F29" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="G29" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="J29" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M29" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="P29" t="n">
         <v>104.9</v>
       </c>
-      <c r="H29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="I29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="J29" t="n">
-        <v>105.2</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="M29" t="n">
-        <v>105.6</v>
-      </c>
-      <c r="N29" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="P29" t="n">
-        <v>105.6</v>
-      </c>
       <c r="Q29" t="n">
-        <v>0.4</v>
+        <v>-3.6</v>
       </c>
       <c r="R29" t="n">
-        <v>0.38</v>
+        <v>-3.32</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>70.8</v>
+        <v>70.15000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>0.15</v>
+        <v>-0.65</v>
       </c>
       <c r="F30" t="n">
-        <v>0.21</v>
+        <v>-0.92</v>
       </c>
       <c r="G30" t="n">
-        <v>70.15000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.65</v>
+        <v>-0.75</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.92</v>
+        <v>-1.07</v>
       </c>
       <c r="J30" t="n">
-        <v>69.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.75</v>
+        <v>2.1</v>
       </c>
       <c r="L30" t="n">
-        <v>-1.07</v>
+        <v>3.03</v>
       </c>
       <c r="M30" t="n">
-        <v>71.5</v>
+        <v>71.8</v>
       </c>
       <c r="N30" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="O30" t="n">
-        <v>3.03</v>
+        <v>0.42</v>
       </c>
       <c r="P30" t="n">
-        <v>71.5</v>
+        <v>72.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="R30" t="n">
-        <v>3.03</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>86.15000000000001</v>
+        <v>84.75</v>
       </c>
       <c r="E31" t="n">
-        <v>2.75</v>
+        <v>-1.4</v>
       </c>
       <c r="F31" t="n">
-        <v>3.3</v>
+        <v>-1.63</v>
       </c>
       <c r="G31" t="n">
-        <v>84.75</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.4</v>
+        <v>-2.6</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.63</v>
+        <v>-3.07</v>
       </c>
       <c r="J31" t="n">
-        <v>82.15000000000001</v>
+        <v>83</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.6</v>
+        <v>0.85</v>
       </c>
       <c r="L31" t="n">
-        <v>-3.07</v>
+        <v>1.03</v>
       </c>
       <c r="M31" t="n">
-        <v>83</v>
+        <v>81.8</v>
       </c>
       <c r="N31" t="n">
-        <v>0.85</v>
+        <v>-1.2</v>
       </c>
       <c r="O31" t="n">
-        <v>1.03</v>
+        <v>-1.45</v>
       </c>
       <c r="P31" t="n">
-        <v>83</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.85</v>
+        <v>-0.15</v>
       </c>
       <c r="R31" t="n">
-        <v>1.03</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>61.55</v>
+        <v>60.9</v>
       </c>
       <c r="E32" t="n">
-        <v>0.25</v>
+        <v>-0.65</v>
       </c>
       <c r="F32" t="n">
-        <v>0.41</v>
+        <v>-1.06</v>
       </c>
       <c r="G32" t="n">
-        <v>60.9</v>
+        <v>56.8</v>
       </c>
       <c r="H32" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>-6.73</v>
+      </c>
+      <c r="J32" t="n">
+        <v>57.65</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="L32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M32" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="P32" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="Q32" t="n">
         <v>-0.65</v>
       </c>
-      <c r="I32" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="J32" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="K32" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="L32" t="n">
-        <v>-6.73</v>
-      </c>
-      <c r="M32" t="n">
-        <v>57.65</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="O32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P32" t="n">
-        <v>57.65</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0.85</v>
-      </c>
       <c r="R32" t="n">
-        <v>1.5</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>75</v>
+        <v>74.55</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9</v>
+        <v>-0.45</v>
       </c>
       <c r="F33" t="n">
-        <v>1.21</v>
+        <v>-0.6</v>
       </c>
       <c r="G33" t="n">
-        <v>74.55</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.45</v>
+        <v>-1.65</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.6</v>
+        <v>-2.21</v>
       </c>
       <c r="J33" t="n">
-        <v>72.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="K33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M33" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="O33" t="n">
         <v>-1.65</v>
       </c>
-      <c r="L33" t="n">
-        <v>-2.21</v>
-      </c>
-      <c r="M33" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O33" t="n">
-        <v>3.7</v>
-      </c>
       <c r="P33" t="n">
-        <v>75.59999999999999</v>
+        <v>73.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.7</v>
+        <v>-1.1</v>
       </c>
       <c r="R33" t="n">
-        <v>3.7</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>30.18</v>
+        <v>29.7</v>
       </c>
       <c r="E34" t="n">
-        <v>0.68</v>
+        <v>-0.48</v>
       </c>
       <c r="F34" t="n">
-        <v>2.31</v>
+        <v>-1.59</v>
       </c>
       <c r="G34" t="n">
-        <v>29.7</v>
+        <v>28.54</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.48</v>
+        <v>-1.16</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.59</v>
+        <v>-3.91</v>
       </c>
       <c r="J34" t="n">
-        <v>28.54</v>
+        <v>30.1</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.16</v>
+        <v>1.56</v>
       </c>
       <c r="L34" t="n">
-        <v>-3.91</v>
+        <v>5.47</v>
       </c>
       <c r="M34" t="n">
-        <v>30.1</v>
+        <v>29.26</v>
       </c>
       <c r="N34" t="n">
-        <v>1.56</v>
+        <v>-0.84</v>
       </c>
       <c r="O34" t="n">
-        <v>5.47</v>
+        <v>-2.79</v>
       </c>
       <c r="P34" t="n">
-        <v>30.1</v>
+        <v>29.16</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.56</v>
+        <v>-0.1</v>
       </c>
       <c r="R34" t="n">
-        <v>5.47</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="35">
@@ -2561,31 +2561,31 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.14</v>
+        <v>4.11</v>
       </c>
       <c r="E35" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="F35" t="n">
-        <v>1.22</v>
+        <v>-0.72</v>
       </c>
       <c r="G35" t="n">
-        <v>4.11</v>
+        <v>3.99</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.72</v>
+        <v>-2.92</v>
       </c>
       <c r="J35" t="n">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.12</v>
+        <v>0.11</v>
       </c>
       <c r="L35" t="n">
-        <v>-2.92</v>
+        <v>2.76</v>
       </c>
       <c r="M35" t="n">
         <v>4.1</v>
@@ -2623,31 +2623,31 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8.9</v>
+        <v>8.85</v>
       </c>
       <c r="E36" t="n">
-        <v>0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="F36" t="n">
-        <v>1.02</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>8.85</v>
+        <v>8.59</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.05</v>
+        <v>-0.26</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-2.94</v>
       </c>
       <c r="J36" t="n">
-        <v>8.59</v>
+        <v>8.84</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.26</v>
+        <v>0.25</v>
       </c>
       <c r="L36" t="n">
-        <v>-2.94</v>
+        <v>2.91</v>
       </c>
       <c r="M36" t="n">
         <v>8.84</v>
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="F37" t="n">
-        <v>0.53</v>
+        <v>-0.26</v>
       </c>
       <c r="G37" t="n">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="H37" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.26</v>
+        <v>-1.06</v>
       </c>
       <c r="J37" t="n">
-        <v>375</v>
+        <v>377.8</v>
       </c>
       <c r="K37" t="n">
-        <v>-4</v>
+        <v>2.8</v>
       </c>
       <c r="L37" t="n">
-        <v>-1.06</v>
+        <v>0.75</v>
       </c>
       <c r="M37" t="n">
-        <v>377.8</v>
+        <v>375.4</v>
       </c>
       <c r="N37" t="n">
-        <v>2.8</v>
+        <v>-2.4</v>
       </c>
       <c r="O37" t="n">
-        <v>0.75</v>
+        <v>-0.64</v>
       </c>
       <c r="P37" t="n">
-        <v>377.8</v>
+        <v>379.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.8</v>
+        <v>4.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0.75</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.43</v>
+        <v>11.27</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.1</v>
+        <v>-0.16</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.87</v>
+        <v>-1.4</v>
       </c>
       <c r="G38" t="n">
-        <v>11.27</v>
+        <v>11.02</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.16</v>
+        <v>-0.25</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.4</v>
+        <v>-2.22</v>
       </c>
       <c r="J38" t="n">
-        <v>11.02</v>
+        <v>11.46</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.25</v>
+        <v>0.44</v>
       </c>
       <c r="L38" t="n">
-        <v>-2.22</v>
+        <v>3.99</v>
       </c>
       <c r="M38" t="n">
-        <v>11.46</v>
+        <v>11.05</v>
       </c>
       <c r="N38" t="n">
-        <v>0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="O38" t="n">
-        <v>3.99</v>
+        <v>-3.58</v>
       </c>
       <c r="P38" t="n">
-        <v>11.46</v>
+        <v>11.42</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.44</v>
+        <v>0.37</v>
       </c>
       <c r="R38" t="n">
-        <v>3.99</v>
+        <v>3.35</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>488.6</v>
+        <v>486.4</v>
       </c>
       <c r="E39" t="n">
-        <v>5.2</v>
+        <v>-2.2</v>
       </c>
       <c r="F39" t="n">
-        <v>1.08</v>
+        <v>-0.45</v>
       </c>
       <c r="G39" t="n">
-        <v>486.4</v>
+        <v>476.8</v>
       </c>
       <c r="H39" t="n">
-        <v>-2.2</v>
+        <v>-9.6</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.45</v>
+        <v>-1.97</v>
       </c>
       <c r="J39" t="n">
-        <v>476.8</v>
+        <v>491.4</v>
       </c>
       <c r="K39" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="L39" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="M39" t="n">
+        <v>494.8</v>
+      </c>
+      <c r="N39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="P39" t="n">
+        <v>485.2</v>
+      </c>
+      <c r="Q39" t="n">
         <v>-9.6</v>
       </c>
-      <c r="L39" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="M39" t="n">
-        <v>491.4</v>
-      </c>
-      <c r="N39" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="O39" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="P39" t="n">
-        <v>491.4</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>14.6</v>
-      </c>
       <c r="R39" t="n">
-        <v>3.06</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>37.2</v>
+        <v>38</v>
       </c>
       <c r="E40" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="F40" t="n">
-        <v>2.54</v>
+        <v>2.15</v>
       </c>
       <c r="G40" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="H40" t="n">
-        <v>0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="I40" t="n">
-        <v>2.15</v>
+        <v>-1.32</v>
       </c>
       <c r="J40" t="n">
-        <v>37.5</v>
+        <v>38.34</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.5</v>
+        <v>0.84</v>
       </c>
       <c r="L40" t="n">
-        <v>-1.32</v>
+        <v>2.24</v>
       </c>
       <c r="M40" t="n">
-        <v>38.34</v>
+        <v>38.48</v>
       </c>
       <c r="N40" t="n">
-        <v>0.84</v>
+        <v>0.14</v>
       </c>
       <c r="O40" t="n">
-        <v>2.24</v>
+        <v>0.37</v>
       </c>
       <c r="P40" t="n">
-        <v>38.34</v>
+        <v>37.84</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.84</v>
+        <v>-0.64</v>
       </c>
       <c r="R40" t="n">
-        <v>2.24</v>
+        <v>-1.66</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>32.2</v>
+        <v>30.3</v>
       </c>
       <c r="E41" t="n">
-        <v>0.32</v>
+        <v>-1.9</v>
       </c>
       <c r="F41" t="n">
-        <v>1</v>
+        <v>-5.9</v>
       </c>
       <c r="G41" t="n">
-        <v>30.3</v>
+        <v>29</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.9</v>
+        <v>-1.3</v>
       </c>
       <c r="I41" t="n">
-        <v>-5.9</v>
+        <v>-4.29</v>
       </c>
       <c r="J41" t="n">
         <v>29</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>-4.29</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>29</v>
+        <v>29.06</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="P41" t="n">
-        <v>29</v>
+        <v>29.2</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>78.56</v>
+        <v>77.48999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>0.73</v>
+        <v>-1.07</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9399999999999999</v>
+        <v>-1.36</v>
       </c>
       <c r="G42" t="n">
-        <v>77.48999999999999</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>-1.07</v>
+        <v>-3.64</v>
       </c>
       <c r="I42" t="n">
-        <v>-1.36</v>
+        <v>-4.7</v>
       </c>
       <c r="J42" t="n">
-        <v>73.84999999999999</v>
+        <v>73.36</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.64</v>
+        <v>-0.49</v>
       </c>
       <c r="L42" t="n">
-        <v>-4.7</v>
+        <v>-0.66</v>
       </c>
       <c r="M42" t="n">
-        <v>73.36</v>
+        <v>73.94</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.49</v>
+        <v>0.58</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.66</v>
+        <v>0.79</v>
       </c>
       <c r="P42" t="n">
-        <v>73.36</v>
+        <v>74.47</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.49</v>
+        <v>0.53</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.66</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>43.72</v>
+        <v>42.44</v>
       </c>
       <c r="E43" t="n">
-        <v>0.66</v>
+        <v>-1.28</v>
       </c>
       <c r="F43" t="n">
-        <v>1.53</v>
+        <v>-2.93</v>
       </c>
       <c r="G43" t="n">
-        <v>42.44</v>
+        <v>40.25</v>
       </c>
       <c r="H43" t="n">
-        <v>-1.28</v>
+        <v>-2.19</v>
       </c>
       <c r="I43" t="n">
-        <v>-2.93</v>
+        <v>-5.16</v>
       </c>
       <c r="J43" t="n">
-        <v>40.25</v>
+        <v>39.96</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.19</v>
+        <v>-0.29</v>
       </c>
       <c r="L43" t="n">
-        <v>-5.16</v>
+        <v>-0.72</v>
       </c>
       <c r="M43" t="n">
-        <v>39.96</v>
+        <v>40.5</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.29</v>
+        <v>0.54</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.72</v>
+        <v>1.35</v>
       </c>
       <c r="P43" t="n">
-        <v>39.96</v>
+        <v>40.93</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.29</v>
+        <v>0.43</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.72</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.87</v>
+        <v>5.91</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.84</v>
+        <v>0.68</v>
       </c>
       <c r="G44" t="n">
-        <v>5.91</v>
+        <v>5.82</v>
       </c>
       <c r="H44" t="n">
-        <v>0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="I44" t="n">
-        <v>0.68</v>
+        <v>-1.52</v>
       </c>
       <c r="J44" t="n">
-        <v>5.82</v>
+        <v>5.9</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.09</v>
+        <v>0.08</v>
       </c>
       <c r="L44" t="n">
-        <v>-1.52</v>
+        <v>1.37</v>
       </c>
       <c r="M44" t="n">
-        <v>5.9</v>
+        <v>6.01</v>
       </c>
       <c r="N44" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="O44" t="n">
-        <v>1.37</v>
+        <v>1.86</v>
       </c>
       <c r="P44" t="n">
-        <v>5.9</v>
+        <v>6.08</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="R44" t="n">
-        <v>1.37</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1.98</v>
+        <v>2.01</v>
       </c>
       <c r="E45" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F45" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I45" t="n">
+        <v>-2.49</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="L45" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="M45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="N45" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="O45" t="n">
+        <v>-2.5</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="Q45" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F45" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I45" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="J45" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="K45" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="L45" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="O45" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="P45" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0.04</v>
-      </c>
       <c r="R45" t="n">
-        <v>2.04</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="E46" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F46" t="n">
-        <v>0.53</v>
+        <v>0.27</v>
       </c>
       <c r="G46" t="n">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="H46" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="I46" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="K46" t="n">
         <v>0.01</v>
       </c>
-      <c r="I46" t="n">
+      <c r="L46" t="n">
         <v>0.27</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="K46" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="L46" t="n">
-        <v>-1.33</v>
       </c>
       <c r="M46" t="n">
         <v>3.73</v>
       </c>
       <c r="N46" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="R46" t="n">
-        <v>0.27</v>
+        <v>-1.61</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11</v>
+        <v>11.03</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.23</v>
+        <v>0.03</v>
       </c>
       <c r="F47" t="n">
-        <v>-2.05</v>
+        <v>0.27</v>
       </c>
       <c r="G47" t="n">
-        <v>11.03</v>
+        <v>10.51</v>
       </c>
       <c r="H47" t="n">
-        <v>0.03</v>
+        <v>-0.52</v>
       </c>
       <c r="I47" t="n">
-        <v>0.27</v>
+        <v>-4.71</v>
       </c>
       <c r="J47" t="n">
-        <v>10.51</v>
+        <v>10.42</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.52</v>
+        <v>-0.09</v>
       </c>
       <c r="L47" t="n">
-        <v>-4.71</v>
+        <v>-0.86</v>
       </c>
       <c r="M47" t="n">
-        <v>10.42</v>
+        <v>10.4</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.86</v>
+        <v>-0.19</v>
       </c>
       <c r="P47" t="n">
-        <v>10.42</v>
+        <v>10.35</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.09</v>
+        <v>-0.05</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.86</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="48">
@@ -3367,43 +3367,43 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.285</v>
+        <v>0.295</v>
       </c>
       <c r="E48" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F48" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F48" t="n">
-        <v>-1.72</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0.01</v>
-      </c>
       <c r="I48" t="n">
-        <v>3.51</v>
+        <v>-1.69</v>
       </c>
       <c r="J48" t="n">
         <v>0.29</v>
       </c>
       <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="N48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L48" t="n">
-        <v>-1.69</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0</v>
-      </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>-1.72</v>
       </c>
       <c r="P48" t="n">
-        <v>0.29</v>
+        <v>0.285</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.25</v>
+        <v>4.3</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.47</v>
+        <v>1.18</v>
       </c>
       <c r="G49" t="n">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
       <c r="H49" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="I49" t="n">
-        <v>1.18</v>
+        <v>-1.4</v>
       </c>
       <c r="J49" t="n">
         <v>4.24</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="P49" t="n">
-        <v>4.24</v>
+        <v>4.16</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>-0.95</v>
       </c>
     </row>
     <row r="50">
@@ -3494,46 +3494,46 @@
         <v>1.12</v>
       </c>
       <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H50" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I50" t="n">
+        <v>-1.79</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K50" t="n">
         <v>0.01</v>
       </c>
-      <c r="F50" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="L50" t="n">
-        <v>-1.79</v>
+        <v>0.91</v>
       </c>
       <c r="M50" t="n">
         <v>1.11</v>
       </c>
       <c r="N50" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="R50" t="n">
-        <v>0.91</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="51">
@@ -3556,46 +3556,46 @@
         <v>5.07</v>
       </c>
       <c r="E51" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>4.94</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-0.13</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-2.56</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="M51" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="N51" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F51" t="n">
+      <c r="O51" t="n">
         <v>-0.2</v>
       </c>
-      <c r="G51" t="n">
-        <v>5.07</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>4.94</v>
-      </c>
-      <c r="K51" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="L51" t="n">
-        <v>-2.56</v>
-      </c>
-      <c r="M51" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="N51" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="O51" t="n">
-        <v>3.24</v>
-      </c>
       <c r="P51" t="n">
-        <v>5.1</v>
+        <v>5.06</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.16</v>
+        <v>-0.03</v>
       </c>
       <c r="R51" t="n">
-        <v>3.24</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.97</v>
+        <v>11.02</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.14</v>
+        <v>0.05</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.26</v>
+        <v>0.46</v>
       </c>
       <c r="G52" t="n">
-        <v>11.02</v>
+        <v>10.49</v>
       </c>
       <c r="H52" t="n">
-        <v>0.05</v>
+        <v>-0.53</v>
       </c>
       <c r="I52" t="n">
-        <v>0.46</v>
+        <v>-4.81</v>
       </c>
       <c r="J52" t="n">
-        <v>10.49</v>
+        <v>10.52</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.53</v>
+        <v>0.03</v>
       </c>
       <c r="L52" t="n">
-        <v>-4.81</v>
+        <v>0.29</v>
       </c>
       <c r="M52" t="n">
-        <v>10.52</v>
+        <v>10.43</v>
       </c>
       <c r="N52" t="n">
-        <v>0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="O52" t="n">
-        <v>0.29</v>
+        <v>-0.86</v>
       </c>
       <c r="P52" t="n">
-        <v>10.52</v>
+        <v>10.42</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="R52" t="n">
-        <v>0.29</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>6.99</v>
+        <v>7.17</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.03</v>
+        <v>0.18</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.43</v>
+        <v>2.58</v>
       </c>
       <c r="G53" t="n">
-        <v>7.17</v>
+        <v>7.1</v>
       </c>
       <c r="H53" t="n">
-        <v>0.18</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>2.58</v>
+        <v>-0.98</v>
       </c>
       <c r="J53" t="n">
         <v>7.1</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>7.1</v>
+        <v>7.05</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="P53" t="n">
-        <v>7.1</v>
+        <v>7.15</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="54">
@@ -3801,49 +3801,49 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.625</v>
+        <v>0.62</v>
       </c>
       <c r="E55" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>0.8100000000000001</v>
+        <v>-0.8</v>
       </c>
       <c r="G55" t="n">
-        <v>0.62</v>
+        <v>0.615</v>
       </c>
       <c r="H55" t="n">
         <v>-0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.8</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="J55" t="n">
         <v>0.615</v>
       </c>
       <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="N55" t="n">
         <v>-0.005</v>
       </c>
-      <c r="L55" t="n">
+      <c r="O55" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="M55" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="N55" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
       <c r="P55" t="n">
-        <v>0.615</v>
+        <v>0.605</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="56">
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.37</v>
+        <v>0.355</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.005</v>
+        <v>-0.015</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.33</v>
+        <v>-4.05</v>
       </c>
       <c r="G56" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="J56" t="n">
         <v>0.355</v>
       </c>
-      <c r="H56" t="n">
-        <v>-0.015</v>
-      </c>
-      <c r="I56" t="n">
-        <v>-4.05</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.345</v>
-      </c>
       <c r="K56" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="L56" t="n">
-        <v>-2.82</v>
+        <v>2.9</v>
       </c>
       <c r="M56" t="n">
-        <v>0.355</v>
+        <v>0.335</v>
       </c>
       <c r="N56" t="n">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="O56" t="n">
-        <v>2.9</v>
+        <v>-5.63</v>
       </c>
       <c r="P56" t="n">
         <v>0.355</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="R56" t="n">
-        <v>2.9</v>
+        <v>5.97</v>
       </c>
     </row>
     <row r="57">
@@ -3928,46 +3928,46 @@
         <v>3.6</v>
       </c>
       <c r="E57" t="n">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="G57" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>0</v>
+        <v>-1.94</v>
       </c>
       <c r="J57" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="K57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M57" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="N57" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="L57" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N57" t="n">
-        <v>0.02</v>
-      </c>
       <c r="O57" t="n">
-        <v>0.57</v>
+        <v>-1.97</v>
       </c>
       <c r="P57" t="n">
-        <v>3.55</v>
+        <v>3.46</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="R57" t="n">
-        <v>0.57</v>
+        <v>-0.57</v>
       </c>
     </row>
     <row r="58">
@@ -3987,22 +3987,22 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.079</v>
+        <v>0.078</v>
       </c>
       <c r="E58" t="n">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="F58" t="n">
-        <v>1.28</v>
+        <v>-1.27</v>
       </c>
       <c r="G58" t="n">
         <v>0.078</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
         <v>0.078</v>
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.04</v>
+        <v>21.29</v>
       </c>
       <c r="E59" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F59" t="n">
-        <v>1.4</v>
+        <v>1.19</v>
       </c>
       <c r="G59" t="n">
-        <v>21.29</v>
+        <v>20.64</v>
       </c>
       <c r="H59" t="n">
-        <v>0.25</v>
+        <v>-0.65</v>
       </c>
       <c r="I59" t="n">
-        <v>1.19</v>
+        <v>-3.05</v>
       </c>
       <c r="J59" t="n">
-        <v>20.64</v>
+        <v>20.73</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.65</v>
+        <v>0.09</v>
       </c>
       <c r="L59" t="n">
-        <v>-3.05</v>
+        <v>0.44</v>
       </c>
       <c r="M59" t="n">
-        <v>20.73</v>
+        <v>21.35</v>
       </c>
       <c r="N59" t="n">
-        <v>0.09</v>
+        <v>0.62</v>
       </c>
       <c r="O59" t="n">
-        <v>0.44</v>
+        <v>2.99</v>
       </c>
       <c r="P59" t="n">
-        <v>20.73</v>
+        <v>21.14</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.09</v>
+        <v>-0.21</v>
       </c>
       <c r="R59" t="n">
-        <v>0.44</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>0.96</v>
       </c>
       <c r="G60" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="H60" t="n">
-        <v>0.03</v>
+        <v>-0.11</v>
       </c>
       <c r="I60" t="n">
-        <v>0.96</v>
+        <v>-3.48</v>
       </c>
       <c r="J60" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.11</v>
+        <v>0.05</v>
       </c>
       <c r="L60" t="n">
-        <v>-3.48</v>
+        <v>1.64</v>
       </c>
       <c r="M60" t="n">
         <v>3.1</v>
       </c>
       <c r="N60" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="P60" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="R60" t="n">
-        <v>1.64</v>
+        <v>-1.94</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.84</v>
+        <v>0.855</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>0.015</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="G61" t="n">
-        <v>0.855</v>
+        <v>0.83</v>
       </c>
       <c r="H61" t="n">
-        <v>0.015</v>
+        <v>-0.025</v>
       </c>
       <c r="I61" t="n">
-        <v>1.79</v>
+        <v>-2.92</v>
       </c>
       <c r="J61" t="n">
-        <v>0.83</v>
+        <v>0.835</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.025</v>
+        <v>0.005</v>
       </c>
       <c r="L61" t="n">
-        <v>-2.92</v>
+        <v>0.6</v>
       </c>
       <c r="M61" t="n">
         <v>0.835</v>
       </c>
       <c r="N61" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
-        <v>0.835</v>
+        <v>0.795</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.005</v>
+        <v>-0.04</v>
       </c>
       <c r="R61" t="n">
-        <v>0.6</v>
+        <v>-4.79</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-10-07 Close</t>
+          <t>2026-10-08 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-10-07 Change</t>
+          <t>2026-10-08 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-10-07 Change %</t>
+          <t>2026-10-08 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-10-08 Close</t>
+          <t>2026-10-09 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-10-08 Change</t>
+          <t>2026-10-09 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-10-08 Change %</t>
+          <t>2026-10-09 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-10-09 Close</t>
+          <t>2026-10-12 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-10-09 Change</t>
+          <t>2026-10-12 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-10-09 Change %</t>
+          <t>2026-10-12 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-10-12 Close</t>
+          <t>2026-10-13 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-10-12 Change</t>
+          <t>2026-10-13 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-10-12 Change %</t>
+          <t>2026-10-13 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-10-13 Close</t>
+          <t>2026-10-14 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-10-13 Change</t>
+          <t>2026-10-14 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-10-13 Change %</t>
+          <t>2026-10-14 Change %</t>
         </is>
       </c>
     </row>
@@ -577,40 +577,40 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>149.9</v>
+        <v>142.6</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.9</v>
+        <v>-7.3</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.9</v>
+        <v>-4.87</v>
       </c>
       <c r="G3" t="n">
-        <v>142.6</v>
+        <v>145.2</v>
       </c>
       <c r="H3" t="n">
-        <v>-7.3</v>
+        <v>2.6</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.87</v>
+        <v>1.82</v>
       </c>
       <c r="J3" t="n">
-        <v>145.2</v>
+        <v>148.1</v>
       </c>
       <c r="K3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2</v>
+      </c>
+      <c r="M3" t="n">
+        <v>150.7</v>
+      </c>
+      <c r="N3" t="n">
         <v>2.6</v>
       </c>
-      <c r="L3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="M3" t="n">
-        <v>148.1</v>
-      </c>
-      <c r="N3" t="n">
-        <v>2.9</v>
-      </c>
       <c r="O3" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="P3" t="n">
         <v>150.7</v>
@@ -639,40 +639,40 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="E4" t="n">
-        <v>-6.4</v>
+        <v>-12</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.71</v>
+        <v>-5.22</v>
       </c>
       <c r="G4" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="H4" t="n">
-        <v>-12</v>
+        <v>3</v>
       </c>
       <c r="I4" t="n">
-        <v>-5.22</v>
+        <v>1.38</v>
       </c>
       <c r="J4" t="n">
-        <v>221</v>
+        <v>224.4</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="M4" t="n">
-        <v>224.4</v>
+        <v>229.8</v>
       </c>
       <c r="N4" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="O4" t="n">
-        <v>1.54</v>
+        <v>2.41</v>
       </c>
       <c r="P4" t="n">
         <v>229.8</v>
@@ -701,40 +701,40 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.57</v>
+        <v>6.59</v>
       </c>
       <c r="E5" t="n">
         <v>0.02</v>
       </c>
       <c r="F5" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="G5" t="n">
-        <v>6.59</v>
+        <v>6.49</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="I5" t="n">
-        <v>0.3</v>
+        <v>-1.52</v>
       </c>
       <c r="J5" t="n">
-        <v>6.49</v>
+        <v>6.66</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1</v>
+        <v>0.17</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.52</v>
+        <v>2.62</v>
       </c>
       <c r="M5" t="n">
-        <v>6.66</v>
+        <v>6.72</v>
       </c>
       <c r="N5" t="n">
-        <v>0.17</v>
+        <v>0.06</v>
       </c>
       <c r="O5" t="n">
-        <v>2.62</v>
+        <v>0.9</v>
       </c>
       <c r="P5" t="n">
         <v>6.72</v>
@@ -763,40 +763,40 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.58</v>
+        <v>7.57</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="G6" t="n">
-        <v>7.57</v>
+        <v>7.5</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.13</v>
+        <v>-0.92</v>
       </c>
       <c r="J6" t="n">
-        <v>7.5</v>
+        <v>7.62</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.92</v>
+        <v>1.6</v>
       </c>
       <c r="M6" t="n">
-        <v>7.62</v>
+        <v>7.64</v>
       </c>
       <c r="N6" t="n">
-        <v>0.12</v>
+        <v>0.02</v>
       </c>
       <c r="O6" t="n">
-        <v>1.6</v>
+        <v>0.26</v>
       </c>
       <c r="P6" t="n">
         <v>7.64</v>
@@ -825,40 +825,40 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5.99</v>
+        <v>6.03</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.33</v>
+        <v>0.67</v>
       </c>
       <c r="G7" t="n">
-        <v>6.03</v>
+        <v>6.12</v>
       </c>
       <c r="H7" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="I7" t="n">
-        <v>0.67</v>
+        <v>1.49</v>
       </c>
       <c r="J7" t="n">
-        <v>6.12</v>
+        <v>6.25</v>
       </c>
       <c r="K7" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="L7" t="n">
-        <v>1.49</v>
+        <v>2.12</v>
       </c>
       <c r="M7" t="n">
-        <v>6.25</v>
+        <v>6.26</v>
       </c>
       <c r="N7" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="O7" t="n">
-        <v>2.12</v>
+        <v>0.16</v>
       </c>
       <c r="P7" t="n">
         <v>6.26</v>
@@ -887,40 +887,40 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.630000000000001</v>
+        <v>9.66</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.02</v>
+        <v>0.03</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.21</v>
+        <v>0.31</v>
       </c>
       <c r="G8" t="n">
-        <v>9.66</v>
+        <v>9.73</v>
       </c>
       <c r="H8" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>0.31</v>
+        <v>0.72</v>
       </c>
       <c r="J8" t="n">
-        <v>9.73</v>
+        <v>9.91</v>
       </c>
       <c r="K8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="L8" t="n">
-        <v>0.72</v>
+        <v>1.85</v>
       </c>
       <c r="M8" t="n">
-        <v>9.91</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
       <c r="O8" t="n">
-        <v>1.85</v>
+        <v>0.5</v>
       </c>
       <c r="P8" t="n">
         <v>9.960000000000001</v>
@@ -949,40 +949,40 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.35</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.03</v>
+        <v>0.15</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.36</v>
+        <v>1.83</v>
       </c>
       <c r="G9" t="n">
-        <v>8.35</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="I9" t="n">
-        <v>1.83</v>
+        <v>0.48</v>
       </c>
       <c r="J9" t="n">
-        <v>8.390000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="K9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="M9" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="N9" t="n">
         <v>0.04</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="M9" t="n">
-        <v>8.59</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.2</v>
-      </c>
       <c r="O9" t="n">
-        <v>2.38</v>
+        <v>0.47</v>
       </c>
       <c r="P9" t="n">
         <v>8.630000000000001</v>
@@ -1011,40 +1011,40 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>50.95</v>
+        <v>51.65</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.05</v>
+        <v>0.7</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1</v>
+        <v>1.37</v>
       </c>
       <c r="G10" t="n">
-        <v>51.65</v>
+        <v>52.2</v>
       </c>
       <c r="H10" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="I10" t="n">
-        <v>1.37</v>
+        <v>1.06</v>
       </c>
       <c r="J10" t="n">
-        <v>52.2</v>
+        <v>53.8</v>
       </c>
       <c r="K10" t="n">
-        <v>0.55</v>
+        <v>1.6</v>
       </c>
       <c r="L10" t="n">
-        <v>1.06</v>
+        <v>3.07</v>
       </c>
       <c r="M10" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="N10" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="O10" t="n">
-        <v>3.07</v>
+        <v>0.19</v>
       </c>
       <c r="P10" t="n">
         <v>53.9</v>
@@ -1073,40 +1073,40 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.42</v>
+        <v>4.53</v>
       </c>
       <c r="E11" t="n">
-        <v>0.03</v>
+        <v>0.11</v>
       </c>
       <c r="F11" t="n">
-        <v>0.68</v>
+        <v>2.49</v>
       </c>
       <c r="G11" t="n">
         <v>4.53</v>
       </c>
       <c r="H11" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="M11" t="n">
         <v>4.53</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
-        <v>4.51</v>
-      </c>
       <c r="N11" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.44</v>
+        <v>0.44</v>
       </c>
       <c r="P11" t="n">
         <v>4.53</v>
@@ -1135,40 +1135,40 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.59</v>
+        <v>9.83</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.08</v>
+        <v>0.24</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.83</v>
+        <v>2.5</v>
       </c>
       <c r="G12" t="n">
         <v>9.83</v>
       </c>
       <c r="H12" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="M12" t="n">
-        <v>9.85</v>
+        <v>10.22</v>
       </c>
       <c r="N12" t="n">
-        <v>0.02</v>
+        <v>0.37</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2</v>
+        <v>3.76</v>
       </c>
       <c r="P12" t="n">
         <v>10.22</v>
@@ -1197,40 +1197,40 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23.52</v>
+        <v>24.04</v>
       </c>
       <c r="E13" t="n">
-        <v>0.08</v>
+        <v>0.52</v>
       </c>
       <c r="F13" t="n">
-        <v>0.34</v>
+        <v>2.21</v>
       </c>
       <c r="G13" t="n">
-        <v>24.04</v>
+        <v>23.9</v>
       </c>
       <c r="H13" t="n">
-        <v>0.52</v>
+        <v>-0.14</v>
       </c>
       <c r="I13" t="n">
-        <v>2.21</v>
+        <v>-0.58</v>
       </c>
       <c r="J13" t="n">
-        <v>23.9</v>
+        <v>24.14</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.14</v>
+        <v>0.24</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.58</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>24.14</v>
+        <v>24.28</v>
       </c>
       <c r="N13" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
       <c r="O13" t="n">
-        <v>1</v>
+        <v>0.58</v>
       </c>
       <c r="P13" t="n">
         <v>24.28</v>
@@ -1259,34 +1259,34 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="E14" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="K14" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F14" t="n">
-        <v>-0.54</v>
-      </c>
-      <c r="G14" t="n">
+      <c r="L14" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="M14" t="n">
         <v>1.88</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="K14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="M14" t="n">
-        <v>1.89</v>
       </c>
       <c r="N14" t="n">
         <v>-0.01</v>
@@ -1321,40 +1321,40 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.29</v>
+        <v>5.22</v>
       </c>
       <c r="E15" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-1.32</v>
+      </c>
+      <c r="G15" t="n">
+        <v>5.34</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J15" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="M15" t="n">
+        <v>5.41</v>
+      </c>
+      <c r="N15" t="n">
         <v>0.05</v>
       </c>
-      <c r="F15" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="G15" t="n">
-        <v>5.22</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-1.32</v>
-      </c>
-      <c r="J15" t="n">
-        <v>5.34</v>
-      </c>
-      <c r="K15" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L15" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="M15" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.02</v>
-      </c>
       <c r="O15" t="n">
-        <v>0.37</v>
+        <v>0.93</v>
       </c>
       <c r="P15" t="n">
         <v>5.41</v>
@@ -1383,25 +1383,25 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.34</v>
+        <v>4.33</v>
       </c>
       <c r="E16" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F16" t="n">
-        <v>0.46</v>
+        <v>-0.23</v>
       </c>
       <c r="G16" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.23</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="K16" t="n">
         <v>0.03</v>
@@ -1413,10 +1413,10 @@
         <v>4.39</v>
       </c>
       <c r="N16" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>4.39</v>
@@ -1445,40 +1445,40 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.28</v>
+        <v>3.23</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="F17" t="n">
-        <v>1.23</v>
+        <v>-1.52</v>
       </c>
       <c r="G17" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.52</v>
+        <v>-0.62</v>
       </c>
       <c r="J17" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.62</v>
+        <v>0.31</v>
       </c>
       <c r="M17" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="N17" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="O17" t="n">
-        <v>0.31</v>
+        <v>1.55</v>
       </c>
       <c r="P17" t="n">
         <v>3.27</v>
@@ -1507,40 +1507,40 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2.99</v>
+        <v>3.03</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.02</v>
+        <v>0.04</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.66</v>
+        <v>1.34</v>
       </c>
       <c r="G18" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="H18" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I18" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="K18" t="n">
         <v>0.04</v>
       </c>
-      <c r="I18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="L18" t="n">
-        <v>-0.33</v>
+        <v>1.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.06</v>
+        <v>3.17</v>
       </c>
       <c r="N18" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="O18" t="n">
-        <v>1.32</v>
+        <v>3.59</v>
       </c>
       <c r="P18" t="n">
         <v>3.17</v>
@@ -1569,40 +1569,40 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>51.5</v>
+        <v>51.3</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.05</v>
+        <v>-0.2</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1</v>
+        <v>-0.39</v>
       </c>
       <c r="G19" t="n">
-        <v>51.3</v>
+        <v>51.85</v>
       </c>
       <c r="H19" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="J19" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="K19" t="n">
         <v>-0.2</v>
       </c>
-      <c r="I19" t="n">
+      <c r="L19" t="n">
         <v>-0.39</v>
       </c>
-      <c r="J19" t="n">
-        <v>51.85</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="L19" t="n">
-        <v>1.07</v>
-      </c>
       <c r="M19" t="n">
-        <v>51.65</v>
+        <v>51.35</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.39</v>
+        <v>-0.58</v>
       </c>
       <c r="P19" t="n">
         <v>51.35</v>
@@ -1631,40 +1631,40 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>27.26</v>
+        <v>26.76</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.04</v>
+        <v>-0.5</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.15</v>
+        <v>-1.83</v>
       </c>
       <c r="G20" t="n">
-        <v>26.76</v>
+        <v>26.16</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.83</v>
+        <v>-2.24</v>
       </c>
       <c r="J20" t="n">
-        <v>26.16</v>
+        <v>26.26</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6</v>
+        <v>0.1</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.24</v>
+        <v>0.38</v>
       </c>
       <c r="M20" t="n">
-        <v>26.26</v>
+        <v>25.62</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1</v>
+        <v>-0.64</v>
       </c>
       <c r="O20" t="n">
-        <v>0.38</v>
+        <v>-2.44</v>
       </c>
       <c r="P20" t="n">
         <v>25.62</v>
@@ -1696,37 +1696,37 @@
         <v>4.53</v>
       </c>
       <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="N21" t="n">
         <v>0.02</v>
       </c>
-      <c r="F21" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.53</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="L21" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-0.02</v>
-      </c>
       <c r="O21" t="n">
-        <v>-0.43</v>
+        <v>0.43</v>
       </c>
       <c r="P21" t="n">
         <v>4.68</v>
@@ -1755,40 +1755,40 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79.05</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="F22" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="G22" t="n">
-        <v>79.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="I22" t="n">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="J22" t="n">
-        <v>80.09999999999999</v>
+        <v>79.95</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7</v>
+        <v>-0.15</v>
       </c>
       <c r="L22" t="n">
-        <v>0.88</v>
+        <v>-0.19</v>
       </c>
       <c r="M22" t="n">
-        <v>79.95</v>
+        <v>80.45</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.15</v>
+        <v>0.5</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.19</v>
+        <v>0.63</v>
       </c>
       <c r="P22" t="n">
         <v>80.45</v>
@@ -1817,40 +1817,40 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>21.72</v>
+        <v>20.7</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.08</v>
+        <v>-1.02</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.37</v>
+        <v>-4.7</v>
       </c>
       <c r="G23" t="n">
-        <v>20.7</v>
+        <v>20.76</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.02</v>
+        <v>0.06</v>
       </c>
       <c r="I23" t="n">
-        <v>-4.7</v>
+        <v>0.29</v>
       </c>
       <c r="J23" t="n">
-        <v>20.76</v>
+        <v>20.36</v>
       </c>
       <c r="K23" t="n">
-        <v>0.06</v>
+        <v>-0.4</v>
       </c>
       <c r="L23" t="n">
-        <v>0.29</v>
+        <v>-1.93</v>
       </c>
       <c r="M23" t="n">
-        <v>20.36</v>
+        <v>20.12</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4</v>
+        <v>-0.24</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.93</v>
+        <v>-1.18</v>
       </c>
       <c r="P23" t="n">
         <v>20.12</v>
@@ -1879,40 +1879,40 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.46</v>
+        <v>13.91</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.48</v>
+        <v>-0.55</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.21</v>
+        <v>-3.8</v>
       </c>
       <c r="G24" t="n">
-        <v>13.91</v>
+        <v>13.86</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.55</v>
+        <v>-0.05</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.8</v>
+        <v>-0.36</v>
       </c>
       <c r="J24" t="n">
-        <v>13.86</v>
+        <v>13.48</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.05</v>
+        <v>-0.38</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.36</v>
+        <v>-2.74</v>
       </c>
       <c r="M24" t="n">
-        <v>13.48</v>
+        <v>12.89</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.38</v>
+        <v>-0.59</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.74</v>
+        <v>-4.38</v>
       </c>
       <c r="P24" t="n">
         <v>12.89</v>
@@ -1941,40 +1941,40 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>23.94</v>
+        <v>23.66</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.32</v>
+        <v>-0.28</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.32</v>
+        <v>-1.17</v>
       </c>
       <c r="G25" t="n">
-        <v>23.66</v>
+        <v>25.96</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.28</v>
+        <v>2.3</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.17</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>25.96</v>
+        <v>24.52</v>
       </c>
       <c r="K25" t="n">
-        <v>2.3</v>
+        <v>-1.44</v>
       </c>
       <c r="L25" t="n">
-        <v>9.720000000000001</v>
+        <v>-5.55</v>
       </c>
       <c r="M25" t="n">
-        <v>24.52</v>
+        <v>25.04</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.44</v>
+        <v>0.52</v>
       </c>
       <c r="O25" t="n">
-        <v>-5.55</v>
+        <v>2.12</v>
       </c>
       <c r="P25" t="n">
         <v>25.04</v>
@@ -2003,40 +2003,40 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>34.44</v>
+        <v>30.36</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.16</v>
+        <v>-4.08</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.26</v>
+        <v>-11.85</v>
       </c>
       <c r="G26" t="n">
-        <v>30.36</v>
+        <v>31</v>
       </c>
       <c r="H26" t="n">
-        <v>-4.08</v>
+        <v>0.64</v>
       </c>
       <c r="I26" t="n">
-        <v>-11.85</v>
+        <v>2.11</v>
       </c>
       <c r="J26" t="n">
-        <v>31</v>
+        <v>29.9</v>
       </c>
       <c r="K26" t="n">
-        <v>0.64</v>
+        <v>-1.1</v>
       </c>
       <c r="L26" t="n">
-        <v>2.11</v>
+        <v>-3.55</v>
       </c>
       <c r="M26" t="n">
-        <v>29.9</v>
+        <v>28.24</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.1</v>
+        <v>-1.66</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.55</v>
+        <v>-5.55</v>
       </c>
       <c r="P26" t="n">
         <v>28.24</v>
@@ -2065,40 +2065,40 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>420.6</v>
+        <v>411.4</v>
       </c>
       <c r="E27" t="n">
-        <v>-7.6</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-1.77</v>
+        <v>-2.19</v>
       </c>
       <c r="G27" t="n">
-        <v>411.4</v>
+        <v>424.8</v>
       </c>
       <c r="H27" t="n">
-        <v>-9.199999999999999</v>
+        <v>13.4</v>
       </c>
       <c r="I27" t="n">
-        <v>-2.19</v>
+        <v>3.26</v>
       </c>
       <c r="J27" t="n">
-        <v>424.8</v>
+        <v>425.8</v>
       </c>
       <c r="K27" t="n">
-        <v>13.4</v>
+        <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>3.26</v>
+        <v>0.24</v>
       </c>
       <c r="M27" t="n">
-        <v>425.8</v>
+        <v>425.2</v>
       </c>
       <c r="N27" t="n">
-        <v>1</v>
+        <v>-0.6</v>
       </c>
       <c r="O27" t="n">
-        <v>0.24</v>
+        <v>-0.14</v>
       </c>
       <c r="P27" t="n">
         <v>425.2</v>
@@ -2127,40 +2127,40 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>105.4</v>
+        <v>104.3</v>
       </c>
       <c r="E28" t="n">
-        <v>-2.8</v>
+        <v>-1.1</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.59</v>
+        <v>-1.04</v>
       </c>
       <c r="G28" t="n">
-        <v>104.3</v>
+        <v>107</v>
       </c>
       <c r="H28" t="n">
-        <v>-1.1</v>
+        <v>2.7</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.04</v>
+        <v>2.59</v>
       </c>
       <c r="J28" t="n">
-        <v>107</v>
+        <v>108.2</v>
       </c>
       <c r="K28" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="L28" t="n">
-        <v>2.59</v>
+        <v>1.12</v>
       </c>
       <c r="M28" t="n">
-        <v>108.2</v>
+        <v>107.2</v>
       </c>
       <c r="N28" t="n">
-        <v>1.2</v>
+        <v>-1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.12</v>
+        <v>-0.92</v>
       </c>
       <c r="P28" t="n">
         <v>107.2</v>
@@ -2189,40 +2189,40 @@
         </is>
       </c>
       <c r="D29" t="n">
+        <v>105.2</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="G29" t="n">
+        <v>105.6</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="J29" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M29" t="n">
         <v>104.9</v>
       </c>
-      <c r="E29" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="F29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="G29" t="n">
-        <v>105.2</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="J29" t="n">
-        <v>105.6</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L29" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="M29" t="n">
-        <v>108.5</v>
-      </c>
       <c r="N29" t="n">
-        <v>2.9</v>
+        <v>-3.6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.75</v>
+        <v>-3.32</v>
       </c>
       <c r="P29" t="n">
         <v>104.9</v>
@@ -2251,40 +2251,40 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>70.15000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.65</v>
+        <v>-0.75</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.92</v>
+        <v>-1.07</v>
       </c>
       <c r="G30" t="n">
-        <v>69.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.75</v>
+        <v>2.1</v>
       </c>
       <c r="I30" t="n">
-        <v>-1.07</v>
+        <v>3.03</v>
       </c>
       <c r="J30" t="n">
-        <v>71.5</v>
+        <v>71.8</v>
       </c>
       <c r="K30" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="L30" t="n">
-        <v>3.03</v>
+        <v>0.42</v>
       </c>
       <c r="M30" t="n">
-        <v>71.8</v>
+        <v>72.3</v>
       </c>
       <c r="N30" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="O30" t="n">
-        <v>0.42</v>
+        <v>0.7</v>
       </c>
       <c r="P30" t="n">
         <v>72.3</v>
@@ -2313,40 +2313,40 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>84.75</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.4</v>
+        <v>-2.6</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.63</v>
+        <v>-3.07</v>
       </c>
       <c r="G31" t="n">
-        <v>82.15000000000001</v>
+        <v>83</v>
       </c>
       <c r="H31" t="n">
-        <v>-2.6</v>
+        <v>0.85</v>
       </c>
       <c r="I31" t="n">
-        <v>-3.07</v>
+        <v>1.03</v>
       </c>
       <c r="J31" t="n">
-        <v>83</v>
+        <v>81.8</v>
       </c>
       <c r="K31" t="n">
-        <v>0.85</v>
+        <v>-1.2</v>
       </c>
       <c r="L31" t="n">
-        <v>1.03</v>
+        <v>-1.45</v>
       </c>
       <c r="M31" t="n">
-        <v>81.8</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>-1.2</v>
+        <v>-0.15</v>
       </c>
       <c r="O31" t="n">
-        <v>-1.45</v>
+        <v>-0.18</v>
       </c>
       <c r="P31" t="n">
         <v>81.65000000000001</v>
@@ -2375,40 +2375,40 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>60.9</v>
+        <v>56.8</v>
       </c>
       <c r="E32" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="F32" t="n">
+        <v>-6.73</v>
+      </c>
+      <c r="G32" t="n">
+        <v>57.65</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J32" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="L32" t="n">
+        <v>-2.52</v>
+      </c>
+      <c r="M32" t="n">
+        <v>55.55</v>
+      </c>
+      <c r="N32" t="n">
         <v>-0.65</v>
       </c>
-      <c r="F32" t="n">
-        <v>-1.06</v>
-      </c>
-      <c r="G32" t="n">
-        <v>56.8</v>
-      </c>
-      <c r="H32" t="n">
-        <v>-4.1</v>
-      </c>
-      <c r="I32" t="n">
-        <v>-6.73</v>
-      </c>
-      <c r="J32" t="n">
-        <v>57.65</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="L32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="M32" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="N32" t="n">
-        <v>-1.45</v>
-      </c>
       <c r="O32" t="n">
-        <v>-2.52</v>
+        <v>-1.16</v>
       </c>
       <c r="P32" t="n">
         <v>55.55</v>
@@ -2437,40 +2437,40 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>74.55</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.45</v>
+        <v>-1.65</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.6</v>
+        <v>-2.21</v>
       </c>
       <c r="G33" t="n">
-        <v>72.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="I33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J33" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="L33" t="n">
         <v>-1.65</v>
       </c>
-      <c r="I33" t="n">
-        <v>-2.21</v>
-      </c>
-      <c r="J33" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="K33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="L33" t="n">
-        <v>3.7</v>
-      </c>
       <c r="M33" t="n">
-        <v>74.34999999999999</v>
+        <v>73.25</v>
       </c>
       <c r="N33" t="n">
-        <v>-1.25</v>
+        <v>-1.1</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.65</v>
+        <v>-1.48</v>
       </c>
       <c r="P33" t="n">
         <v>73.25</v>
@@ -2499,40 +2499,40 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>29.7</v>
+        <v>28.54</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.48</v>
+        <v>-1.16</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.59</v>
+        <v>-3.91</v>
       </c>
       <c r="G34" t="n">
-        <v>28.54</v>
+        <v>30.1</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.16</v>
+        <v>1.56</v>
       </c>
       <c r="I34" t="n">
-        <v>-3.91</v>
+        <v>5.47</v>
       </c>
       <c r="J34" t="n">
-        <v>30.1</v>
+        <v>29.26</v>
       </c>
       <c r="K34" t="n">
-        <v>1.56</v>
+        <v>-0.84</v>
       </c>
       <c r="L34" t="n">
-        <v>5.47</v>
+        <v>-2.79</v>
       </c>
       <c r="M34" t="n">
-        <v>29.26</v>
+        <v>29.16</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.84</v>
+        <v>-0.1</v>
       </c>
       <c r="O34" t="n">
-        <v>-2.79</v>
+        <v>-0.34</v>
       </c>
       <c r="P34" t="n">
         <v>29.16</v>
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.11</v>
+        <v>3.99</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.72</v>
+        <v>-2.92</v>
       </c>
       <c r="G35" t="n">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.12</v>
+        <v>0.11</v>
       </c>
       <c r="I35" t="n">
-        <v>-2.92</v>
+        <v>2.76</v>
       </c>
       <c r="J35" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="K35" t="n">
-        <v>0.11</v>
+        <v>-0.02</v>
       </c>
       <c r="L35" t="n">
-        <v>2.76</v>
+        <v>-0.49</v>
       </c>
       <c r="M35" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="N35" t="n">
-        <v>0.11</v>
+        <v>-0.02</v>
       </c>
       <c r="O35" t="n">
-        <v>2.76</v>
+        <v>-0.49</v>
       </c>
       <c r="P35" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.11</v>
+        <v>-0.02</v>
       </c>
       <c r="R35" t="n">
-        <v>2.76</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8.85</v>
+        <v>8.59</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.05</v>
+        <v>-0.26</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-2.94</v>
       </c>
       <c r="G36" t="n">
-        <v>8.59</v>
+        <v>8.84</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.26</v>
+        <v>0.25</v>
       </c>
       <c r="I36" t="n">
-        <v>-2.94</v>
+        <v>2.91</v>
       </c>
       <c r="J36" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>0.25</v>
+        <v>-0.04</v>
       </c>
       <c r="L36" t="n">
-        <v>2.91</v>
+        <v>-0.45</v>
       </c>
       <c r="M36" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>0.25</v>
+        <v>-0.04</v>
       </c>
       <c r="O36" t="n">
-        <v>2.91</v>
+        <v>-0.45</v>
       </c>
       <c r="P36" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.25</v>
+        <v>-0.04</v>
       </c>
       <c r="R36" t="n">
-        <v>2.91</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="37">
@@ -2685,40 +2685,40 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E37" t="n">
-        <v>-1</v>
+        <v>-4</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.26</v>
+        <v>-1.06</v>
       </c>
       <c r="G37" t="n">
-        <v>375</v>
+        <v>377.8</v>
       </c>
       <c r="H37" t="n">
-        <v>-4</v>
+        <v>2.8</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.06</v>
+        <v>0.75</v>
       </c>
       <c r="J37" t="n">
-        <v>377.8</v>
+        <v>375.4</v>
       </c>
       <c r="K37" t="n">
-        <v>2.8</v>
+        <v>-2.4</v>
       </c>
       <c r="L37" t="n">
-        <v>0.75</v>
+        <v>-0.64</v>
       </c>
       <c r="M37" t="n">
-        <v>375.4</v>
+        <v>379.6</v>
       </c>
       <c r="N37" t="n">
-        <v>-2.4</v>
+        <v>4.2</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.64</v>
+        <v>1.12</v>
       </c>
       <c r="P37" t="n">
         <v>379.6</v>
@@ -2747,40 +2747,40 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.27</v>
+        <v>11.02</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.16</v>
+        <v>-0.25</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.4</v>
+        <v>-2.22</v>
       </c>
       <c r="G38" t="n">
-        <v>11.02</v>
+        <v>11.46</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.25</v>
+        <v>0.44</v>
       </c>
       <c r="I38" t="n">
-        <v>-2.22</v>
+        <v>3.99</v>
       </c>
       <c r="J38" t="n">
-        <v>11.46</v>
+        <v>11.05</v>
       </c>
       <c r="K38" t="n">
-        <v>0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="L38" t="n">
-        <v>3.99</v>
+        <v>-3.58</v>
       </c>
       <c r="M38" t="n">
-        <v>11.05</v>
+        <v>11.42</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.41</v>
+        <v>0.37</v>
       </c>
       <c r="O38" t="n">
-        <v>-3.58</v>
+        <v>3.35</v>
       </c>
       <c r="P38" t="n">
         <v>11.42</v>
@@ -2809,40 +2809,40 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>486.4</v>
+        <v>476.8</v>
       </c>
       <c r="E39" t="n">
-        <v>-2.2</v>
+        <v>-9.6</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.45</v>
+        <v>-1.97</v>
       </c>
       <c r="G39" t="n">
-        <v>476.8</v>
+        <v>491.4</v>
       </c>
       <c r="H39" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="J39" t="n">
+        <v>494.8</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="M39" t="n">
+        <v>485.2</v>
+      </c>
+      <c r="N39" t="n">
         <v>-9.6</v>
       </c>
-      <c r="I39" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="J39" t="n">
-        <v>491.4</v>
-      </c>
-      <c r="K39" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="L39" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="M39" t="n">
-        <v>494.8</v>
-      </c>
-      <c r="N39" t="n">
-        <v>3.4</v>
-      </c>
       <c r="O39" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.94</v>
       </c>
       <c r="P39" t="n">
         <v>485.2</v>
@@ -2871,40 +2871,40 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>38</v>
+        <v>37.5</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8</v>
+        <v>-0.5</v>
       </c>
       <c r="F40" t="n">
-        <v>2.15</v>
+        <v>-1.32</v>
       </c>
       <c r="G40" t="n">
-        <v>37.5</v>
+        <v>38.34</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.5</v>
+        <v>0.84</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.32</v>
+        <v>2.24</v>
       </c>
       <c r="J40" t="n">
-        <v>38.34</v>
+        <v>38.48</v>
       </c>
       <c r="K40" t="n">
-        <v>0.84</v>
+        <v>0.14</v>
       </c>
       <c r="L40" t="n">
-        <v>2.24</v>
+        <v>0.37</v>
       </c>
       <c r="M40" t="n">
-        <v>38.48</v>
+        <v>37.84</v>
       </c>
       <c r="N40" t="n">
-        <v>0.14</v>
+        <v>-0.64</v>
       </c>
       <c r="O40" t="n">
-        <v>0.37</v>
+        <v>-1.66</v>
       </c>
       <c r="P40" t="n">
         <v>37.84</v>
@@ -2933,40 +2933,40 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>30.3</v>
+        <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.9</v>
+        <v>-1.3</v>
       </c>
       <c r="F41" t="n">
-        <v>-5.9</v>
+        <v>-4.29</v>
       </c>
       <c r="G41" t="n">
         <v>29</v>
       </c>
       <c r="H41" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>-4.29</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>29</v>
+        <v>29.06</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="M41" t="n">
-        <v>29.06</v>
+        <v>29.2</v>
       </c>
       <c r="N41" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="O41" t="n">
-        <v>0.21</v>
+        <v>0.48</v>
       </c>
       <c r="P41" t="n">
         <v>29.2</v>
@@ -2995,40 +2995,40 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>77.48999999999999</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>-1.07</v>
+        <v>-3.64</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.36</v>
+        <v>-4.7</v>
       </c>
       <c r="G42" t="n">
-        <v>73.84999999999999</v>
+        <v>73.36</v>
       </c>
       <c r="H42" t="n">
-        <v>-3.64</v>
+        <v>-0.49</v>
       </c>
       <c r="I42" t="n">
-        <v>-4.7</v>
+        <v>-0.66</v>
       </c>
       <c r="J42" t="n">
-        <v>73.36</v>
+        <v>73.94</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.49</v>
+        <v>0.58</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.66</v>
+        <v>0.79</v>
       </c>
       <c r="M42" t="n">
-        <v>73.94</v>
+        <v>74.47</v>
       </c>
       <c r="N42" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="O42" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="P42" t="n">
         <v>74.47</v>
@@ -3057,40 +3057,40 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>42.44</v>
+        <v>40.25</v>
       </c>
       <c r="E43" t="n">
-        <v>-1.28</v>
+        <v>-2.19</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.93</v>
+        <v>-5.16</v>
       </c>
       <c r="G43" t="n">
-        <v>40.25</v>
+        <v>39.96</v>
       </c>
       <c r="H43" t="n">
-        <v>-2.19</v>
+        <v>-0.29</v>
       </c>
       <c r="I43" t="n">
-        <v>-5.16</v>
+        <v>-0.72</v>
       </c>
       <c r="J43" t="n">
-        <v>39.96</v>
+        <v>40.5</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.29</v>
+        <v>0.54</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.72</v>
+        <v>1.35</v>
       </c>
       <c r="M43" t="n">
-        <v>40.5</v>
+        <v>40.93</v>
       </c>
       <c r="N43" t="n">
-        <v>0.54</v>
+        <v>0.43</v>
       </c>
       <c r="O43" t="n">
-        <v>1.35</v>
+        <v>1.06</v>
       </c>
       <c r="P43" t="n">
         <v>40.93</v>
@@ -3119,40 +3119,40 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.91</v>
+        <v>5.82</v>
       </c>
       <c r="E44" t="n">
-        <v>0.04</v>
+        <v>-0.09</v>
       </c>
       <c r="F44" t="n">
-        <v>0.68</v>
+        <v>-1.52</v>
       </c>
       <c r="G44" t="n">
-        <v>5.82</v>
+        <v>5.9</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.09</v>
+        <v>0.08</v>
       </c>
       <c r="I44" t="n">
-        <v>-1.52</v>
+        <v>1.37</v>
       </c>
       <c r="J44" t="n">
-        <v>5.9</v>
+        <v>6.01</v>
       </c>
       <c r="K44" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="L44" t="n">
-        <v>1.37</v>
+        <v>1.86</v>
       </c>
       <c r="M44" t="n">
-        <v>6.01</v>
+        <v>6.08</v>
       </c>
       <c r="N44" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>1.86</v>
+        <v>1.16</v>
       </c>
       <c r="P44" t="n">
         <v>6.08</v>
@@ -3181,40 +3181,40 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2.01</v>
+        <v>1.96</v>
       </c>
       <c r="E45" t="n">
-        <v>0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="F45" t="n">
-        <v>1.52</v>
+        <v>-2.49</v>
       </c>
       <c r="G45" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="J45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="K45" t="n">
         <v>-0.05</v>
       </c>
-      <c r="I45" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="J45" t="n">
-        <v>2</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0.04</v>
-      </c>
       <c r="L45" t="n">
-        <v>2.04</v>
+        <v>-2.5</v>
       </c>
       <c r="M45" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="O45" t="n">
-        <v>-2.5</v>
+        <v>-0.51</v>
       </c>
       <c r="P45" t="n">
         <v>1.94</v>
@@ -3243,40 +3243,40 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.77</v>
+        <v>3.72</v>
       </c>
       <c r="E46" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F46" t="n">
+        <v>-1.33</v>
+      </c>
+      <c r="G46" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="H46" t="n">
         <v>0.01</v>
       </c>
-      <c r="F46" t="n">
+      <c r="I46" t="n">
         <v>0.27</v>
-      </c>
-      <c r="G46" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I46" t="n">
-        <v>-1.33</v>
       </c>
       <c r="J46" t="n">
         <v>3.73</v>
       </c>
       <c r="K46" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>-1.61</v>
       </c>
       <c r="P46" t="n">
         <v>3.67</v>
@@ -3305,40 +3305,40 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.03</v>
+        <v>10.51</v>
       </c>
       <c r="E47" t="n">
-        <v>0.03</v>
+        <v>-0.52</v>
       </c>
       <c r="F47" t="n">
-        <v>0.27</v>
+        <v>-4.71</v>
       </c>
       <c r="G47" t="n">
-        <v>10.51</v>
+        <v>10.42</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.52</v>
+        <v>-0.09</v>
       </c>
       <c r="I47" t="n">
-        <v>-4.71</v>
+        <v>-0.86</v>
       </c>
       <c r="J47" t="n">
-        <v>10.42</v>
+        <v>10.4</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.86</v>
+        <v>-0.19</v>
       </c>
       <c r="M47" t="n">
-        <v>10.4</v>
+        <v>10.35</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.19</v>
+        <v>-0.48</v>
       </c>
       <c r="P47" t="n">
         <v>10.35</v>
@@ -3367,40 +3367,40 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.295</v>
+        <v>0.29</v>
       </c>
       <c r="E48" t="n">
-        <v>0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="F48" t="n">
-        <v>3.51</v>
+        <v>-1.69</v>
       </c>
       <c r="G48" t="n">
         <v>0.29</v>
       </c>
       <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="K48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I48" t="n">
-        <v>-1.69</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>-1.72</v>
       </c>
       <c r="M48" t="n">
         <v>0.285</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.72</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0.285</v>
@@ -3429,40 +3429,40 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.3</v>
+        <v>4.24</v>
       </c>
       <c r="E49" t="n">
-        <v>0.05</v>
+        <v>-0.06</v>
       </c>
       <c r="F49" t="n">
-        <v>1.18</v>
+        <v>-1.4</v>
       </c>
       <c r="G49" t="n">
         <v>4.24</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="N49" t="n">
         <v>-0.04</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.95</v>
       </c>
       <c r="P49" t="n">
         <v>4.16</v>
@@ -3491,40 +3491,40 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>-1.79</v>
       </c>
       <c r="G50" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.79</v>
+        <v>0.91</v>
       </c>
       <c r="J50" t="n">
         <v>1.11</v>
       </c>
       <c r="K50" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="P50" t="n">
         <v>1.1</v>
@@ -3553,40 +3553,40 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.07</v>
+        <v>4.94</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>-0.13</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>-2.56</v>
       </c>
       <c r="G51" t="n">
-        <v>4.94</v>
+        <v>5.1</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.13</v>
+        <v>0.16</v>
       </c>
       <c r="I51" t="n">
-        <v>-2.56</v>
+        <v>3.24</v>
       </c>
       <c r="J51" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="K51" t="n">
-        <v>0.16</v>
+        <v>-0.01</v>
       </c>
       <c r="L51" t="n">
-        <v>3.24</v>
+        <v>-0.2</v>
       </c>
       <c r="M51" t="n">
-        <v>5.09</v>
+        <v>5.06</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.2</v>
+        <v>-0.59</v>
       </c>
       <c r="P51" t="n">
         <v>5.06</v>
@@ -3615,40 +3615,40 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.02</v>
+        <v>10.49</v>
       </c>
       <c r="E52" t="n">
-        <v>0.05</v>
+        <v>-0.53</v>
       </c>
       <c r="F52" t="n">
-        <v>0.46</v>
+        <v>-4.81</v>
       </c>
       <c r="G52" t="n">
-        <v>10.49</v>
+        <v>10.52</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.53</v>
+        <v>0.03</v>
       </c>
       <c r="I52" t="n">
-        <v>-4.81</v>
+        <v>0.29</v>
       </c>
       <c r="J52" t="n">
-        <v>10.52</v>
+        <v>10.43</v>
       </c>
       <c r="K52" t="n">
-        <v>0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="L52" t="n">
-        <v>0.29</v>
+        <v>-0.86</v>
       </c>
       <c r="M52" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.86</v>
+        <v>-0.1</v>
       </c>
       <c r="P52" t="n">
         <v>10.42</v>
@@ -3677,40 +3677,40 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7.17</v>
+        <v>7.1</v>
       </c>
       <c r="E53" t="n">
-        <v>0.18</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>2.58</v>
+        <v>-0.98</v>
       </c>
       <c r="G53" t="n">
         <v>7.1</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>7.1</v>
+        <v>7.05</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="M53" t="n">
-        <v>7.05</v>
+        <v>7.15</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.05</v>
+        <v>0.1</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.7</v>
+        <v>1.42</v>
       </c>
       <c r="P53" t="n">
         <v>7.15</v>
@@ -3801,40 +3801,40 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.62</v>
+        <v>0.615</v>
       </c>
       <c r="E55" t="n">
         <v>-0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.8</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="G55" t="n">
         <v>0.615</v>
       </c>
       <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K55" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I55" t="n">
+      <c r="L55" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="J55" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" t="n">
-        <v>0</v>
-      </c>
       <c r="M55" t="n">
-        <v>0.61</v>
+        <v>0.605</v>
       </c>
       <c r="N55" t="n">
         <v>-0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.82</v>
       </c>
       <c r="P55" t="n">
         <v>0.605</v>
@@ -3863,40 +3863,40 @@
         </is>
       </c>
       <c r="D56" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="G56" t="n">
         <v>0.355</v>
       </c>
-      <c r="E56" t="n">
-        <v>-0.015</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-4.05</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.345</v>
-      </c>
       <c r="H56" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="I56" t="n">
-        <v>-2.82</v>
+        <v>2.9</v>
       </c>
       <c r="J56" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="K56" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L56" t="n">
+        <v>-5.63</v>
+      </c>
+      <c r="M56" t="n">
         <v>0.355</v>
       </c>
-      <c r="K56" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="L56" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.335</v>
-      </c>
       <c r="N56" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="O56" t="n">
-        <v>-5.63</v>
+        <v>5.97</v>
       </c>
       <c r="P56" t="n">
         <v>0.355</v>
@@ -3925,40 +3925,40 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.6</v>
+        <v>3.53</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>-1.94</v>
       </c>
       <c r="G57" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="H57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="K57" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="I57" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K57" t="n">
-        <v>0.02</v>
-      </c>
       <c r="L57" t="n">
-        <v>0.57</v>
+        <v>-1.97</v>
       </c>
       <c r="M57" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="O57" t="n">
-        <v>-1.97</v>
+        <v>-0.57</v>
       </c>
       <c r="P57" t="n">
         <v>3.46</v>
@@ -3990,10 +3990,10 @@
         <v>0.078</v>
       </c>
       <c r="E58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.27</v>
+        <v>0</v>
       </c>
       <c r="G58" t="n">
         <v>0.078</v>
@@ -4049,40 +4049,40 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.29</v>
+        <v>20.64</v>
       </c>
       <c r="E59" t="n">
-        <v>0.25</v>
+        <v>-0.65</v>
       </c>
       <c r="F59" t="n">
-        <v>1.19</v>
+        <v>-3.05</v>
       </c>
       <c r="G59" t="n">
-        <v>20.64</v>
+        <v>20.73</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.65</v>
+        <v>0.09</v>
       </c>
       <c r="I59" t="n">
-        <v>-3.05</v>
+        <v>0.44</v>
       </c>
       <c r="J59" t="n">
-        <v>20.73</v>
+        <v>21.35</v>
       </c>
       <c r="K59" t="n">
-        <v>0.09</v>
+        <v>0.62</v>
       </c>
       <c r="L59" t="n">
-        <v>0.44</v>
+        <v>2.99</v>
       </c>
       <c r="M59" t="n">
-        <v>21.35</v>
+        <v>21.14</v>
       </c>
       <c r="N59" t="n">
-        <v>0.62</v>
+        <v>-0.21</v>
       </c>
       <c r="O59" t="n">
-        <v>2.99</v>
+        <v>-0.98</v>
       </c>
       <c r="P59" t="n">
         <v>21.14</v>
@@ -4111,40 +4111,40 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="E60" t="n">
-        <v>0.03</v>
+        <v>-0.11</v>
       </c>
       <c r="F60" t="n">
-        <v>0.96</v>
+        <v>-3.48</v>
       </c>
       <c r="G60" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.11</v>
+        <v>0.05</v>
       </c>
       <c r="I60" t="n">
-        <v>-3.48</v>
+        <v>1.64</v>
       </c>
       <c r="J60" t="n">
         <v>3.1</v>
       </c>
       <c r="K60" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="L60" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="O60" t="n">
-        <v>0</v>
+        <v>-1.94</v>
       </c>
       <c r="P60" t="n">
         <v>3.04</v>
@@ -4173,40 +4173,40 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.855</v>
+        <v>0.83</v>
       </c>
       <c r="E61" t="n">
-        <v>0.015</v>
+        <v>-0.025</v>
       </c>
       <c r="F61" t="n">
-        <v>1.79</v>
+        <v>-2.92</v>
       </c>
       <c r="G61" t="n">
-        <v>0.83</v>
+        <v>0.835</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.025</v>
+        <v>0.005</v>
       </c>
       <c r="I61" t="n">
-        <v>-2.92</v>
+        <v>0.6</v>
       </c>
       <c r="J61" t="n">
         <v>0.835</v>
       </c>
       <c r="K61" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0.835</v>
+        <v>0.795</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>-4.79</v>
       </c>
       <c r="P61" t="n">
         <v>0.795</v>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-10-08 Close</t>
+          <t>2026-10-09 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-10-08 Change</t>
+          <t>2026-10-09 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-10-08 Change %</t>
+          <t>2026-10-09 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-10-09 Close</t>
+          <t>2026-10-12 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-10-09 Change</t>
+          <t>2026-10-12 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-10-09 Change %</t>
+          <t>2026-10-12 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-10-12 Close</t>
+          <t>2026-10-13 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-10-12 Change</t>
+          <t>2026-10-13 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-10-12 Change %</t>
+          <t>2026-10-13 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-10-13 Close</t>
+          <t>2026-10-14 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-10-13 Change</t>
+          <t>2026-10-14 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-10-13 Change %</t>
+          <t>2026-10-14 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-10-14 Close</t>
+          <t>2026-10-15 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-10-14 Change</t>
+          <t>2026-10-15 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-10-14 Change %</t>
+          <t>2026-10-15 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>142.6</v>
+        <v>145.2</v>
       </c>
       <c r="E3" t="n">
-        <v>-7.3</v>
+        <v>2.6</v>
       </c>
       <c r="F3" t="n">
-        <v>-4.87</v>
+        <v>1.82</v>
       </c>
       <c r="G3" t="n">
-        <v>145.2</v>
+        <v>148.1</v>
       </c>
       <c r="H3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" t="n">
+        <v>150.7</v>
+      </c>
+      <c r="K3" t="n">
         <v>2.6</v>
       </c>
-      <c r="I3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="J3" t="n">
-        <v>148.1</v>
-      </c>
-      <c r="K3" t="n">
-        <v>2.9</v>
-      </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="M3" t="n">
-        <v>150.7</v>
+        <v>148</v>
       </c>
       <c r="N3" t="n">
-        <v>2.6</v>
+        <v>-2.7</v>
       </c>
       <c r="O3" t="n">
-        <v>1.76</v>
+        <v>-1.79</v>
       </c>
       <c r="P3" t="n">
-        <v>150.7</v>
+        <v>148</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.6</v>
+        <v>-2.7</v>
       </c>
       <c r="R3" t="n">
-        <v>1.76</v>
+        <v>-1.79</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E4" t="n">
-        <v>-12</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>-5.22</v>
+        <v>1.38</v>
       </c>
       <c r="G4" t="n">
-        <v>221</v>
+        <v>224.4</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="I4" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="J4" t="n">
-        <v>224.4</v>
+        <v>229.8</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="L4" t="n">
-        <v>1.54</v>
+        <v>2.41</v>
       </c>
       <c r="M4" t="n">
-        <v>229.8</v>
+        <v>221.8</v>
       </c>
       <c r="N4" t="n">
-        <v>5.4</v>
+        <v>-8</v>
       </c>
       <c r="O4" t="n">
-        <v>2.41</v>
+        <v>-3.48</v>
       </c>
       <c r="P4" t="n">
-        <v>229.8</v>
+        <v>221.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.4</v>
+        <v>-8</v>
       </c>
       <c r="R4" t="n">
-        <v>2.41</v>
+        <v>-3.48</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.59</v>
+        <v>6.49</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02</v>
+        <v>-0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3</v>
+        <v>-1.52</v>
       </c>
       <c r="G5" t="n">
-        <v>6.49</v>
+        <v>6.66</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1</v>
+        <v>0.17</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.52</v>
+        <v>2.62</v>
       </c>
       <c r="J5" t="n">
-        <v>6.66</v>
+        <v>6.72</v>
       </c>
       <c r="K5" t="n">
-        <v>0.17</v>
+        <v>0.06</v>
       </c>
       <c r="L5" t="n">
-        <v>2.62</v>
+        <v>0.9</v>
       </c>
       <c r="M5" t="n">
-        <v>6.72</v>
+        <v>6.57</v>
       </c>
       <c r="N5" t="n">
-        <v>0.06</v>
+        <v>-0.15</v>
       </c>
       <c r="O5" t="n">
-        <v>0.9</v>
+        <v>-2.23</v>
       </c>
       <c r="P5" t="n">
-        <v>6.72</v>
+        <v>6.57</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.06</v>
+        <v>-0.15</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9</v>
+        <v>-2.23</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7.62</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M6" t="n">
         <v>7.57</v>
       </c>
-      <c r="E6" t="n">
-        <v>-0.01</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-0.13</v>
-      </c>
-      <c r="G6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="N6" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="I6" t="n">
+      <c r="O6" t="n">
         <v>-0.92</v>
       </c>
-      <c r="J6" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="M6" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.26</v>
-      </c>
       <c r="P6" t="n">
-        <v>7.64</v>
+        <v>7.57</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>0.26</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.03</v>
+        <v>6.12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.04</v>
+        <v>0.09</v>
       </c>
       <c r="F7" t="n">
-        <v>0.67</v>
+        <v>1.49</v>
       </c>
       <c r="G7" t="n">
-        <v>6.12</v>
+        <v>6.25</v>
       </c>
       <c r="H7" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="I7" t="n">
-        <v>1.49</v>
+        <v>2.12</v>
       </c>
       <c r="J7" t="n">
-        <v>6.25</v>
+        <v>6.26</v>
       </c>
       <c r="K7" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="L7" t="n">
-        <v>2.12</v>
+        <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>6.26</v>
+        <v>6.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="O7" t="n">
-        <v>0.16</v>
+        <v>-0.96</v>
       </c>
       <c r="P7" t="n">
-        <v>6.26</v>
+        <v>6.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="R7" t="n">
-        <v>0.16</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.66</v>
+        <v>9.73</v>
       </c>
       <c r="E8" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0.31</v>
+        <v>0.72</v>
       </c>
       <c r="G8" t="n">
-        <v>9.73</v>
+        <v>9.91</v>
       </c>
       <c r="H8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="I8" t="n">
-        <v>0.72</v>
+        <v>1.85</v>
       </c>
       <c r="J8" t="n">
-        <v>9.91</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
       <c r="L8" t="n">
-        <v>1.85</v>
+        <v>0.5</v>
       </c>
       <c r="M8" t="n">
-        <v>9.960000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="N8" t="n">
-        <v>0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5</v>
+        <v>-1.1</v>
       </c>
       <c r="P8" t="n">
-        <v>9.960000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.35</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="F9" t="n">
-        <v>1.83</v>
+        <v>0.48</v>
       </c>
       <c r="G9" t="n">
-        <v>8.390000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="H9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="J9" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="K9" t="n">
         <v>0.04</v>
       </c>
-      <c r="I9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="J9" t="n">
-        <v>8.59</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.2</v>
-      </c>
       <c r="L9" t="n">
-        <v>2.38</v>
+        <v>0.47</v>
       </c>
       <c r="M9" t="n">
-        <v>8.630000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="O9" t="n">
-        <v>0.47</v>
+        <v>-0.12</v>
       </c>
       <c r="P9" t="n">
-        <v>8.630000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="R9" t="n">
-        <v>0.47</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>51.65</v>
+        <v>52.2</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="F10" t="n">
-        <v>1.37</v>
+        <v>1.06</v>
       </c>
       <c r="G10" t="n">
-        <v>52.2</v>
+        <v>53.8</v>
       </c>
       <c r="H10" t="n">
-        <v>0.55</v>
+        <v>1.6</v>
       </c>
       <c r="I10" t="n">
-        <v>1.06</v>
+        <v>3.07</v>
       </c>
       <c r="J10" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="K10" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="L10" t="n">
-        <v>3.07</v>
+        <v>0.19</v>
       </c>
       <c r="M10" t="n">
-        <v>53.9</v>
+        <v>53.55</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1</v>
+        <v>-0.35</v>
       </c>
       <c r="O10" t="n">
-        <v>0.19</v>
+        <v>-0.65</v>
       </c>
       <c r="P10" t="n">
-        <v>53.9</v>
+        <v>53.55</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.1</v>
+        <v>-0.35</v>
       </c>
       <c r="R10" t="n">
-        <v>0.19</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="11">
@@ -1076,46 +1076,46 @@
         <v>4.53</v>
       </c>
       <c r="E11" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I11" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="J11" t="n">
         <v>4.53</v>
       </c>
-      <c r="H11" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
-        <v>4.51</v>
-      </c>
       <c r="K11" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.44</v>
+        <v>0.44</v>
       </c>
       <c r="M11" t="n">
-        <v>4.53</v>
+        <v>4.59</v>
       </c>
       <c r="N11" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="O11" t="n">
-        <v>0.44</v>
+        <v>1.32</v>
       </c>
       <c r="P11" t="n">
-        <v>4.53</v>
+        <v>4.59</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="R11" t="n">
-        <v>0.44</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="12">
@@ -1138,46 +1138,46 @@
         <v>9.83</v>
       </c>
       <c r="E12" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J12" t="n">
-        <v>9.85</v>
+        <v>10.22</v>
       </c>
       <c r="K12" t="n">
-        <v>0.02</v>
+        <v>0.37</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2</v>
+        <v>3.76</v>
       </c>
       <c r="M12" t="n">
-        <v>10.22</v>
+        <v>10.34</v>
       </c>
       <c r="N12" t="n">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
       <c r="O12" t="n">
-        <v>3.76</v>
+        <v>1.17</v>
       </c>
       <c r="P12" t="n">
-        <v>10.22</v>
+        <v>10.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
       <c r="R12" t="n">
-        <v>3.76</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24.04</v>
+        <v>23.9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.52</v>
+        <v>-0.14</v>
       </c>
       <c r="F13" t="n">
-        <v>2.21</v>
+        <v>-0.58</v>
       </c>
       <c r="G13" t="n">
-        <v>23.9</v>
+        <v>24.14</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.14</v>
+        <v>0.24</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.58</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>24.14</v>
+        <v>24.28</v>
       </c>
       <c r="K13" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0.58</v>
       </c>
       <c r="M13" t="n">
-        <v>24.28</v>
+        <v>24.72</v>
       </c>
       <c r="N13" t="n">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="O13" t="n">
-        <v>0.58</v>
+        <v>1.81</v>
       </c>
       <c r="P13" t="n">
-        <v>24.28</v>
+        <v>24.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="R13" t="n">
-        <v>0.58</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="14">
@@ -1259,25 +1259,25 @@
         </is>
       </c>
       <c r="D14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="J14" t="n">
         <v>1.88</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="G14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="J14" t="n">
-        <v>1.89</v>
       </c>
       <c r="K14" t="n">
         <v>-0.01</v>
@@ -1286,22 +1286,22 @@
         <v>-0.53</v>
       </c>
       <c r="M14" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.53</v>
+        <v>-1.6</v>
       </c>
       <c r="P14" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="R14" t="n">
-        <v>-0.53</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.22</v>
+        <v>5.34</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.32</v>
+        <v>2.3</v>
       </c>
       <c r="G15" t="n">
-        <v>5.34</v>
+        <v>5.36</v>
       </c>
       <c r="H15" t="n">
-        <v>0.12</v>
+        <v>0.02</v>
       </c>
       <c r="I15" t="n">
-        <v>2.3</v>
+        <v>0.37</v>
       </c>
       <c r="J15" t="n">
-        <v>5.36</v>
+        <v>5.41</v>
       </c>
       <c r="K15" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.37</v>
+        <v>0.93</v>
       </c>
       <c r="M15" t="n">
-        <v>5.41</v>
+        <v>5.45</v>
       </c>
       <c r="N15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="O15" t="n">
-        <v>0.93</v>
+        <v>0.74</v>
       </c>
       <c r="P15" t="n">
-        <v>5.41</v>
+        <v>5.45</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="R15" t="n">
-        <v>0.93</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="16">
@@ -1383,16 +1383,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.33</v>
+        <v>4.36</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.23</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="H16" t="n">
         <v>0.03</v>
@@ -1404,28 +1404,28 @@
         <v>4.39</v>
       </c>
       <c r="K16" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>4.39</v>
+        <v>4.41</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="P16" t="n">
-        <v>4.39</v>
+        <v>4.41</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.52</v>
+        <v>-0.62</v>
       </c>
       <c r="G17" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.62</v>
+        <v>0.31</v>
       </c>
       <c r="J17" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="K17" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.31</v>
+        <v>1.55</v>
       </c>
       <c r="M17" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="N17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="O17" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="R17" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="E18" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="H18" t="n">
         <v>0.04</v>
       </c>
-      <c r="F18" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="G18" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-0.01</v>
-      </c>
       <c r="I18" t="n">
-        <v>-0.33</v>
+        <v>1.32</v>
       </c>
       <c r="J18" t="n">
-        <v>3.06</v>
+        <v>3.17</v>
       </c>
       <c r="K18" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="L18" t="n">
-        <v>1.32</v>
+        <v>3.59</v>
       </c>
       <c r="M18" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="N18" t="n">
-        <v>0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="O18" t="n">
-        <v>3.59</v>
+        <v>-2.84</v>
       </c>
       <c r="P18" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="R18" t="n">
-        <v>3.59</v>
+        <v>-2.84</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>51.3</v>
+        <v>51.85</v>
       </c>
       <c r="E19" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>51.65</v>
+      </c>
+      <c r="H19" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F19" t="n">
+      <c r="I19" t="n">
         <v>-0.39</v>
       </c>
-      <c r="G19" t="n">
-        <v>51.85</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I19" t="n">
-        <v>1.07</v>
-      </c>
       <c r="J19" t="n">
-        <v>51.65</v>
+        <v>51.35</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.39</v>
+        <v>-0.58</v>
       </c>
       <c r="M19" t="n">
-        <v>51.35</v>
+        <v>50.6</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3</v>
+        <v>-0.75</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.58</v>
+        <v>-1.46</v>
       </c>
       <c r="P19" t="n">
-        <v>51.35</v>
+        <v>50.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.3</v>
+        <v>-0.75</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.58</v>
+        <v>-1.46</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>26.76</v>
+        <v>26.16</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.83</v>
+        <v>-2.24</v>
       </c>
       <c r="G20" t="n">
-        <v>26.16</v>
+        <v>26.26</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6</v>
+        <v>0.1</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.24</v>
+        <v>0.38</v>
       </c>
       <c r="J20" t="n">
-        <v>26.26</v>
+        <v>25.62</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1</v>
+        <v>-0.64</v>
       </c>
       <c r="L20" t="n">
-        <v>0.38</v>
+        <v>-2.44</v>
       </c>
       <c r="M20" t="n">
-        <v>25.62</v>
+        <v>24.94</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.64</v>
+        <v>-0.68</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.44</v>
+        <v>-2.65</v>
       </c>
       <c r="P20" t="n">
-        <v>25.62</v>
+        <v>24.94</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.64</v>
+        <v>-0.68</v>
       </c>
       <c r="R20" t="n">
-        <v>-2.44</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.53</v>
+        <v>4.68</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="G21" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="H21" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I21" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="J21" t="n">
         <v>4.68</v>
       </c>
-      <c r="H21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I21" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4.66</v>
-      </c>
       <c r="K21" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.43</v>
+        <v>0.43</v>
       </c>
       <c r="M21" t="n">
-        <v>4.68</v>
+        <v>4.74</v>
       </c>
       <c r="N21" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="O21" t="n">
-        <v>0.43</v>
+        <v>1.28</v>
       </c>
       <c r="P21" t="n">
-        <v>4.68</v>
+        <v>4.74</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="R21" t="n">
-        <v>0.43</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0.35</v>
+        <v>0.7</v>
       </c>
       <c r="F22" t="n">
-        <v>0.44</v>
+        <v>0.88</v>
       </c>
       <c r="G22" t="n">
-        <v>80.09999999999999</v>
+        <v>79.95</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7</v>
+        <v>-0.15</v>
       </c>
       <c r="I22" t="n">
-        <v>0.88</v>
+        <v>-0.19</v>
       </c>
       <c r="J22" t="n">
-        <v>79.95</v>
+        <v>80.45</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.15</v>
+        <v>0.5</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.19</v>
+        <v>0.63</v>
       </c>
       <c r="M22" t="n">
-        <v>80.45</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O22" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>80.45</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="R22" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20.7</v>
+        <v>20.76</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.02</v>
+        <v>0.06</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.7</v>
+        <v>0.29</v>
       </c>
       <c r="G23" t="n">
-        <v>20.76</v>
+        <v>20.36</v>
       </c>
       <c r="H23" t="n">
-        <v>0.06</v>
+        <v>-0.4</v>
       </c>
       <c r="I23" t="n">
-        <v>0.29</v>
+        <v>-1.93</v>
       </c>
       <c r="J23" t="n">
-        <v>20.36</v>
+        <v>20.12</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.4</v>
+        <v>-0.24</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.93</v>
+        <v>-1.18</v>
       </c>
       <c r="M23" t="n">
-        <v>20.12</v>
+        <v>20.06</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.24</v>
+        <v>-0.06</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.18</v>
+        <v>-0.3</v>
       </c>
       <c r="P23" t="n">
-        <v>20.12</v>
+        <v>20.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.24</v>
+        <v>-0.06</v>
       </c>
       <c r="R23" t="n">
-        <v>-1.18</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.91</v>
+        <v>13.86</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.55</v>
+        <v>-0.05</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.8</v>
+        <v>-0.36</v>
       </c>
       <c r="G24" t="n">
-        <v>13.86</v>
+        <v>13.48</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.05</v>
+        <v>-0.38</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.36</v>
+        <v>-2.74</v>
       </c>
       <c r="J24" t="n">
-        <v>13.48</v>
+        <v>12.89</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.38</v>
+        <v>-0.59</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.74</v>
+        <v>-4.38</v>
       </c>
       <c r="M24" t="n">
-        <v>12.89</v>
+        <v>13.05</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.59</v>
+        <v>0.16</v>
       </c>
       <c r="O24" t="n">
-        <v>-4.38</v>
+        <v>1.24</v>
       </c>
       <c r="P24" t="n">
-        <v>12.89</v>
+        <v>13.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.59</v>
+        <v>0.16</v>
       </c>
       <c r="R24" t="n">
-        <v>-4.38</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>23.66</v>
+        <v>25.96</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.28</v>
+        <v>2.3</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.17</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>25.96</v>
+        <v>24.52</v>
       </c>
       <c r="H25" t="n">
-        <v>2.3</v>
+        <v>-1.44</v>
       </c>
       <c r="I25" t="n">
-        <v>9.720000000000001</v>
+        <v>-5.55</v>
       </c>
       <c r="J25" t="n">
-        <v>24.52</v>
+        <v>25.04</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.44</v>
+        <v>0.52</v>
       </c>
       <c r="L25" t="n">
-        <v>-5.55</v>
+        <v>2.12</v>
       </c>
       <c r="M25" t="n">
-        <v>25.04</v>
+        <v>26.38</v>
       </c>
       <c r="N25" t="n">
-        <v>0.52</v>
+        <v>1.34</v>
       </c>
       <c r="O25" t="n">
-        <v>2.12</v>
+        <v>5.35</v>
       </c>
       <c r="P25" t="n">
-        <v>25.04</v>
+        <v>26.38</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.52</v>
+        <v>1.34</v>
       </c>
       <c r="R25" t="n">
-        <v>2.12</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>30.36</v>
+        <v>31</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.08</v>
+        <v>0.64</v>
       </c>
       <c r="F26" t="n">
-        <v>-11.85</v>
+        <v>2.11</v>
       </c>
       <c r="G26" t="n">
-        <v>31</v>
+        <v>29.9</v>
       </c>
       <c r="H26" t="n">
-        <v>0.64</v>
+        <v>-1.1</v>
       </c>
       <c r="I26" t="n">
-        <v>2.11</v>
+        <v>-3.55</v>
       </c>
       <c r="J26" t="n">
-        <v>29.9</v>
+        <v>28.24</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.1</v>
+        <v>-1.66</v>
       </c>
       <c r="L26" t="n">
-        <v>-3.55</v>
+        <v>-5.55</v>
       </c>
       <c r="M26" t="n">
-        <v>28.24</v>
+        <v>28.34</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.66</v>
+        <v>0.1</v>
       </c>
       <c r="O26" t="n">
-        <v>-5.55</v>
+        <v>0.35</v>
       </c>
       <c r="P26" t="n">
-        <v>28.24</v>
+        <v>28.34</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.66</v>
+        <v>0.1</v>
       </c>
       <c r="R26" t="n">
-        <v>-5.55</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>411.4</v>
+        <v>424.8</v>
       </c>
       <c r="E27" t="n">
-        <v>-9.199999999999999</v>
+        <v>13.4</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.19</v>
+        <v>3.26</v>
       </c>
       <c r="G27" t="n">
-        <v>424.8</v>
+        <v>425.8</v>
       </c>
       <c r="H27" t="n">
-        <v>13.4</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>3.26</v>
+        <v>0.24</v>
       </c>
       <c r="J27" t="n">
-        <v>425.8</v>
+        <v>425.2</v>
       </c>
       <c r="K27" t="n">
-        <v>1</v>
+        <v>-0.6</v>
       </c>
       <c r="L27" t="n">
-        <v>0.24</v>
+        <v>-0.14</v>
       </c>
       <c r="M27" t="n">
-        <v>425.2</v>
+        <v>423.4</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.14</v>
+        <v>-0.42</v>
       </c>
       <c r="P27" t="n">
-        <v>425.2</v>
+        <v>423.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.14</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>104.3</v>
+        <v>107</v>
       </c>
       <c r="E28" t="n">
-        <v>-1.1</v>
+        <v>2.7</v>
       </c>
       <c r="F28" t="n">
-        <v>-1.04</v>
+        <v>2.59</v>
       </c>
       <c r="G28" t="n">
-        <v>107</v>
+        <v>108.2</v>
       </c>
       <c r="H28" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="I28" t="n">
-        <v>2.59</v>
+        <v>1.12</v>
       </c>
       <c r="J28" t="n">
-        <v>108.2</v>
+        <v>107.2</v>
       </c>
       <c r="K28" t="n">
-        <v>1.2</v>
+        <v>-1</v>
       </c>
       <c r="L28" t="n">
-        <v>1.12</v>
+        <v>-0.92</v>
       </c>
       <c r="M28" t="n">
-        <v>107.2</v>
+        <v>110.5</v>
       </c>
       <c r="N28" t="n">
-        <v>-1</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.92</v>
+        <v>3.08</v>
       </c>
       <c r="P28" t="n">
-        <v>107.2</v>
+        <v>110.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>-0.92</v>
+        <v>3.08</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>105.2</v>
+        <v>105.6</v>
       </c>
       <c r="E29" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="F29" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="G29" t="n">
-        <v>105.6</v>
+        <v>108.5</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="I29" t="n">
-        <v>0.38</v>
+        <v>2.75</v>
       </c>
       <c r="J29" t="n">
-        <v>108.5</v>
+        <v>104.9</v>
       </c>
       <c r="K29" t="n">
-        <v>2.9</v>
+        <v>-3.6</v>
       </c>
       <c r="L29" t="n">
-        <v>2.75</v>
+        <v>-3.32</v>
       </c>
       <c r="M29" t="n">
-        <v>104.9</v>
+        <v>106.1</v>
       </c>
       <c r="N29" t="n">
-        <v>-3.6</v>
+        <v>1.2</v>
       </c>
       <c r="O29" t="n">
-        <v>-3.32</v>
+        <v>1.14</v>
       </c>
       <c r="P29" t="n">
-        <v>104.9</v>
+        <v>106.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>-3.6</v>
+        <v>1.2</v>
       </c>
       <c r="R29" t="n">
-        <v>-3.32</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>69.40000000000001</v>
+        <v>71.5</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.75</v>
+        <v>2.1</v>
       </c>
       <c r="F30" t="n">
-        <v>-1.07</v>
+        <v>3.03</v>
       </c>
       <c r="G30" t="n">
-        <v>71.5</v>
+        <v>71.8</v>
       </c>
       <c r="H30" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="I30" t="n">
-        <v>3.03</v>
+        <v>0.42</v>
       </c>
       <c r="J30" t="n">
-        <v>71.8</v>
+        <v>72.3</v>
       </c>
       <c r="K30" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L30" t="n">
-        <v>0.42</v>
+        <v>0.7</v>
       </c>
       <c r="M30" t="n">
-        <v>72.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="O30" t="n">
-        <v>0.7</v>
+        <v>6.64</v>
       </c>
       <c r="P30" t="n">
-        <v>72.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0.7</v>
+        <v>6.64</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>82.15000000000001</v>
+        <v>83</v>
       </c>
       <c r="E31" t="n">
-        <v>-2.6</v>
+        <v>0.85</v>
       </c>
       <c r="F31" t="n">
-        <v>-3.07</v>
+        <v>1.03</v>
       </c>
       <c r="G31" t="n">
-        <v>83</v>
+        <v>81.8</v>
       </c>
       <c r="H31" t="n">
-        <v>0.85</v>
+        <v>-1.2</v>
       </c>
       <c r="I31" t="n">
-        <v>1.03</v>
+        <v>-1.45</v>
       </c>
       <c r="J31" t="n">
-        <v>81.8</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.2</v>
+        <v>-0.15</v>
       </c>
       <c r="L31" t="n">
-        <v>-1.45</v>
+        <v>-0.18</v>
       </c>
       <c r="M31" t="n">
-        <v>81.65000000000001</v>
+        <v>82.05</v>
       </c>
       <c r="N31" t="n">
-        <v>-0.15</v>
+        <v>0.4</v>
       </c>
       <c r="O31" t="n">
-        <v>-0.18</v>
+        <v>0.49</v>
       </c>
       <c r="P31" t="n">
-        <v>81.65000000000001</v>
+        <v>82.05</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0.15</v>
+        <v>0.4</v>
       </c>
       <c r="R31" t="n">
-        <v>-0.18</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>56.8</v>
+        <v>57.65</v>
       </c>
       <c r="E32" t="n">
-        <v>-4.1</v>
+        <v>0.85</v>
       </c>
       <c r="F32" t="n">
-        <v>-6.73</v>
+        <v>1.5</v>
       </c>
       <c r="G32" t="n">
-        <v>57.65</v>
+        <v>56.2</v>
       </c>
       <c r="H32" t="n">
-        <v>0.85</v>
+        <v>-1.45</v>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>-2.52</v>
       </c>
       <c r="J32" t="n">
-        <v>56.2</v>
+        <v>55.55</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.45</v>
+        <v>-0.65</v>
       </c>
       <c r="L32" t="n">
-        <v>-2.52</v>
+        <v>-1.16</v>
       </c>
       <c r="M32" t="n">
-        <v>55.55</v>
+        <v>54.3</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.65</v>
+        <v>-1.25</v>
       </c>
       <c r="O32" t="n">
-        <v>-1.16</v>
+        <v>-2.25</v>
       </c>
       <c r="P32" t="n">
-        <v>55.55</v>
+        <v>54.3</v>
       </c>
       <c r="Q32" t="n">
-        <v>-0.65</v>
+        <v>-1.25</v>
       </c>
       <c r="R32" t="n">
-        <v>-1.16</v>
+        <v>-2.25</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>72.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="E33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F33" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G33" t="n">
+        <v>74.34999999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-1.25</v>
+      </c>
+      <c r="I33" t="n">
         <v>-1.65</v>
       </c>
-      <c r="F33" t="n">
-        <v>-2.21</v>
-      </c>
-      <c r="G33" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="H33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="I33" t="n">
-        <v>3.7</v>
-      </c>
       <c r="J33" t="n">
-        <v>74.34999999999999</v>
+        <v>73.25</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.25</v>
+        <v>-1.1</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.65</v>
+        <v>-1.48</v>
       </c>
       <c r="M33" t="n">
-        <v>73.25</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>-1.1</v>
+        <v>-0.4</v>
       </c>
       <c r="O33" t="n">
-        <v>-1.48</v>
+        <v>-0.55</v>
       </c>
       <c r="P33" t="n">
-        <v>73.25</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="Q33" t="n">
-        <v>-1.1</v>
+        <v>-0.4</v>
       </c>
       <c r="R33" t="n">
-        <v>-1.48</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>28.54</v>
+        <v>30.1</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.16</v>
+        <v>1.56</v>
       </c>
       <c r="F34" t="n">
-        <v>-3.91</v>
+        <v>5.47</v>
       </c>
       <c r="G34" t="n">
-        <v>30.1</v>
+        <v>29.26</v>
       </c>
       <c r="H34" t="n">
-        <v>1.56</v>
+        <v>-0.84</v>
       </c>
       <c r="I34" t="n">
-        <v>5.47</v>
+        <v>-2.79</v>
       </c>
       <c r="J34" t="n">
-        <v>29.26</v>
+        <v>29.16</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.84</v>
+        <v>-0.1</v>
       </c>
       <c r="L34" t="n">
-        <v>-2.79</v>
+        <v>-0.34</v>
       </c>
       <c r="M34" t="n">
-        <v>29.16</v>
+        <v>29.52</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.1</v>
+        <v>0.36</v>
       </c>
       <c r="O34" t="n">
-        <v>-0.34</v>
+        <v>1.23</v>
       </c>
       <c r="P34" t="n">
-        <v>29.16</v>
+        <v>29.52</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.1</v>
+        <v>0.36</v>
       </c>
       <c r="R34" t="n">
-        <v>-0.34</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>3.99</v>
+        <v>4.1</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F35" t="n">
-        <v>-2.92</v>
+        <v>2.76</v>
       </c>
       <c r="G35" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="H35" t="n">
-        <v>0.11</v>
+        <v>-0.02</v>
       </c>
       <c r="I35" t="n">
-        <v>2.76</v>
+        <v>-0.49</v>
       </c>
       <c r="J35" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.49</v>
+        <v>-0.74</v>
       </c>
       <c r="M35" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.49</v>
+        <v>-0.74</v>
       </c>
       <c r="P35" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.49</v>
+        <v>-0.74</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8.59</v>
+        <v>8.84</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.26</v>
+        <v>0.25</v>
       </c>
       <c r="F36" t="n">
-        <v>-2.94</v>
+        <v>2.91</v>
       </c>
       <c r="G36" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>0.25</v>
+        <v>-0.04</v>
       </c>
       <c r="I36" t="n">
-        <v>2.91</v>
+        <v>-0.45</v>
       </c>
       <c r="J36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.45</v>
+        <v>-0.68</v>
       </c>
       <c r="M36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.45</v>
+        <v>-0.68</v>
       </c>
       <c r="P36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.45</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>375</v>
+        <v>377.8</v>
       </c>
       <c r="E37" t="n">
-        <v>-4</v>
+        <v>2.8</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.06</v>
+        <v>0.75</v>
       </c>
       <c r="G37" t="n">
-        <v>377.8</v>
+        <v>375.4</v>
       </c>
       <c r="H37" t="n">
-        <v>2.8</v>
+        <v>-2.4</v>
       </c>
       <c r="I37" t="n">
-        <v>0.75</v>
+        <v>-0.64</v>
       </c>
       <c r="J37" t="n">
-        <v>375.4</v>
+        <v>379.6</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.4</v>
+        <v>4.2</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.64</v>
+        <v>1.12</v>
       </c>
       <c r="M37" t="n">
-        <v>379.6</v>
+        <v>373.6</v>
       </c>
       <c r="N37" t="n">
-        <v>4.2</v>
+        <v>-6</v>
       </c>
       <c r="O37" t="n">
-        <v>1.12</v>
+        <v>-1.58</v>
       </c>
       <c r="P37" t="n">
-        <v>379.6</v>
+        <v>373.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>4.2</v>
+        <v>-6</v>
       </c>
       <c r="R37" t="n">
-        <v>1.12</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.02</v>
+        <v>11.46</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.25</v>
+        <v>0.44</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.22</v>
+        <v>3.99</v>
       </c>
       <c r="G38" t="n">
-        <v>11.46</v>
+        <v>11.05</v>
       </c>
       <c r="H38" t="n">
-        <v>0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="I38" t="n">
-        <v>3.99</v>
+        <v>-3.58</v>
       </c>
       <c r="J38" t="n">
-        <v>11.05</v>
+        <v>11.42</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.41</v>
+        <v>0.37</v>
       </c>
       <c r="L38" t="n">
-        <v>-3.58</v>
+        <v>3.35</v>
       </c>
       <c r="M38" t="n">
-        <v>11.42</v>
+        <v>11.29</v>
       </c>
       <c r="N38" t="n">
-        <v>0.37</v>
+        <v>-0.13</v>
       </c>
       <c r="O38" t="n">
-        <v>3.35</v>
+        <v>-1.14</v>
       </c>
       <c r="P38" t="n">
-        <v>11.42</v>
+        <v>11.29</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.37</v>
+        <v>-0.13</v>
       </c>
       <c r="R38" t="n">
-        <v>3.35</v>
+        <v>-1.14</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>476.8</v>
+        <v>491.4</v>
       </c>
       <c r="E39" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="F39" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="G39" t="n">
+        <v>494.8</v>
+      </c>
+      <c r="H39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="J39" t="n">
+        <v>485.2</v>
+      </c>
+      <c r="K39" t="n">
         <v>-9.6</v>
       </c>
-      <c r="F39" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="G39" t="n">
-        <v>491.4</v>
-      </c>
-      <c r="H39" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="I39" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="J39" t="n">
-        <v>494.8</v>
-      </c>
-      <c r="K39" t="n">
-        <v>3.4</v>
-      </c>
       <c r="L39" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.94</v>
       </c>
       <c r="M39" t="n">
-        <v>485.2</v>
+        <v>467</v>
       </c>
       <c r="N39" t="n">
-        <v>-9.6</v>
+        <v>-18.2</v>
       </c>
       <c r="O39" t="n">
-        <v>-1.94</v>
+        <v>-3.75</v>
       </c>
       <c r="P39" t="n">
-        <v>485.2</v>
+        <v>467</v>
       </c>
       <c r="Q39" t="n">
-        <v>-9.6</v>
+        <v>-18.2</v>
       </c>
       <c r="R39" t="n">
-        <v>-1.94</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>37.5</v>
+        <v>38.34</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.5</v>
+        <v>0.84</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.32</v>
+        <v>2.24</v>
       </c>
       <c r="G40" t="n">
-        <v>38.34</v>
+        <v>38.48</v>
       </c>
       <c r="H40" t="n">
-        <v>0.84</v>
+        <v>0.14</v>
       </c>
       <c r="I40" t="n">
-        <v>2.24</v>
+        <v>0.37</v>
       </c>
       <c r="J40" t="n">
-        <v>38.48</v>
+        <v>37.84</v>
       </c>
       <c r="K40" t="n">
-        <v>0.14</v>
+        <v>-0.64</v>
       </c>
       <c r="L40" t="n">
-        <v>0.37</v>
+        <v>-1.66</v>
       </c>
       <c r="M40" t="n">
-        <v>37.84</v>
+        <v>38.62</v>
       </c>
       <c r="N40" t="n">
-        <v>-0.64</v>
+        <v>0.78</v>
       </c>
       <c r="O40" t="n">
-        <v>-1.66</v>
+        <v>2.06</v>
       </c>
       <c r="P40" t="n">
-        <v>37.84</v>
+        <v>38.62</v>
       </c>
       <c r="Q40" t="n">
-        <v>-0.64</v>
+        <v>0.78</v>
       </c>
       <c r="R40" t="n">
-        <v>-1.66</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="41">
@@ -2936,46 +2936,46 @@
         <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>-1.3</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>-4.29</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="J41" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="M41" t="n">
         <v>29</v>
       </c>
-      <c r="H41" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" t="n">
-        <v>29.06</v>
-      </c>
-      <c r="K41" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="M41" t="n">
-        <v>29.2</v>
-      </c>
       <c r="N41" t="n">
-        <v>0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="O41" t="n">
-        <v>0.48</v>
+        <v>-0.68</v>
       </c>
       <c r="P41" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="R41" t="n">
-        <v>0.48</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>73.84999999999999</v>
+        <v>73.36</v>
       </c>
       <c r="E42" t="n">
-        <v>-3.64</v>
+        <v>-0.49</v>
       </c>
       <c r="F42" t="n">
-        <v>-4.7</v>
+        <v>-0.66</v>
       </c>
       <c r="G42" t="n">
-        <v>73.36</v>
+        <v>73.94</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.49</v>
+        <v>0.58</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.66</v>
+        <v>0.79</v>
       </c>
       <c r="J42" t="n">
-        <v>73.94</v>
+        <v>74.47</v>
       </c>
       <c r="K42" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="L42" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="M42" t="n">
-        <v>74.47</v>
+        <v>74.34</v>
       </c>
       <c r="N42" t="n">
-        <v>0.53</v>
+        <v>-0.13</v>
       </c>
       <c r="O42" t="n">
-        <v>0.72</v>
+        <v>-0.17</v>
       </c>
       <c r="P42" t="n">
-        <v>74.47</v>
+        <v>74.34</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.53</v>
+        <v>-0.13</v>
       </c>
       <c r="R42" t="n">
-        <v>0.72</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>40.25</v>
+        <v>39.96</v>
       </c>
       <c r="E43" t="n">
-        <v>-2.19</v>
+        <v>-0.29</v>
       </c>
       <c r="F43" t="n">
-        <v>-5.16</v>
+        <v>-0.72</v>
       </c>
       <c r="G43" t="n">
-        <v>39.96</v>
+        <v>40.5</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.29</v>
+        <v>0.54</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.72</v>
+        <v>1.35</v>
       </c>
       <c r="J43" t="n">
-        <v>40.5</v>
+        <v>40.93</v>
       </c>
       <c r="K43" t="n">
-        <v>0.54</v>
+        <v>0.43</v>
       </c>
       <c r="L43" t="n">
-        <v>1.35</v>
+        <v>1.06</v>
       </c>
       <c r="M43" t="n">
-        <v>40.93</v>
+        <v>41.06</v>
       </c>
       <c r="N43" t="n">
-        <v>0.43</v>
+        <v>0.13</v>
       </c>
       <c r="O43" t="n">
-        <v>1.06</v>
+        <v>0.32</v>
       </c>
       <c r="P43" t="n">
-        <v>40.93</v>
+        <v>41.06</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.43</v>
+        <v>0.13</v>
       </c>
       <c r="R43" t="n">
-        <v>1.06</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.82</v>
+        <v>5.9</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.52</v>
+        <v>1.37</v>
       </c>
       <c r="G44" t="n">
-        <v>5.9</v>
+        <v>6.01</v>
       </c>
       <c r="H44" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="I44" t="n">
-        <v>1.37</v>
+        <v>1.86</v>
       </c>
       <c r="J44" t="n">
-        <v>6.01</v>
+        <v>6.08</v>
       </c>
       <c r="K44" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>1.86</v>
+        <v>1.16</v>
       </c>
       <c r="M44" t="n">
-        <v>6.08</v>
+        <v>6.04</v>
       </c>
       <c r="N44" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="O44" t="n">
-        <v>1.16</v>
+        <v>-0.66</v>
       </c>
       <c r="P44" t="n">
-        <v>6.08</v>
+        <v>6.04</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="R44" t="n">
-        <v>1.16</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F45" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="G45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H45" t="n">
         <v>-0.05</v>
       </c>
-      <c r="F45" t="n">
-        <v>-2.49</v>
-      </c>
-      <c r="G45" t="n">
-        <v>2</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0.04</v>
-      </c>
       <c r="I45" t="n">
-        <v>2.04</v>
+        <v>-2.5</v>
       </c>
       <c r="J45" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="L45" t="n">
-        <v>-2.5</v>
+        <v>-0.51</v>
       </c>
       <c r="M45" t="n">
         <v>1.94</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
         <v>1.94</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.72</v>
+        <v>3.73</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.33</v>
+        <v>0.27</v>
       </c>
       <c r="G46" t="n">
         <v>3.73</v>
       </c>
       <c r="H46" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>-1.61</v>
       </c>
       <c r="M46" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="O46" t="n">
-        <v>-1.61</v>
+        <v>-0.82</v>
       </c>
       <c r="P46" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="R46" t="n">
-        <v>-1.61</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.51</v>
+        <v>10.42</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.52</v>
+        <v>-0.09</v>
       </c>
       <c r="F47" t="n">
-        <v>-4.71</v>
+        <v>-0.86</v>
       </c>
       <c r="G47" t="n">
-        <v>10.42</v>
+        <v>10.4</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.86</v>
+        <v>-0.19</v>
       </c>
       <c r="J47" t="n">
-        <v>10.4</v>
+        <v>10.35</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.19</v>
+        <v>-0.48</v>
       </c>
       <c r="M47" t="n">
-        <v>10.35</v>
+        <v>10.41</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="O47" t="n">
-        <v>-0.48</v>
+        <v>0.58</v>
       </c>
       <c r="P47" t="n">
-        <v>10.35</v>
+        <v>10.41</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="R47" t="n">
-        <v>-0.48</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="48">
@@ -3370,46 +3370,46 @@
         <v>0.29</v>
       </c>
       <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="H48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F48" t="n">
-        <v>-1.69</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
       <c r="I48" t="n">
-        <v>0</v>
+        <v>-1.72</v>
       </c>
       <c r="J48" t="n">
         <v>0.285</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.72</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>0.285</v>
+        <v>0.29</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="P48" t="n">
-        <v>0.285</v>
+        <v>0.29</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="49">
@@ -3432,46 +3432,46 @@
         <v>4.24</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="G49" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J49" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="K49" t="n">
         <v>-0.04</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.95</v>
       </c>
       <c r="M49" t="n">
-        <v>4.16</v>
+        <v>4.14</v>
       </c>
       <c r="N49" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.95</v>
+        <v>-0.48</v>
       </c>
       <c r="P49" t="n">
-        <v>4.16</v>
+        <v>4.14</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.95</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.79</v>
+        <v>0.91</v>
       </c>
       <c r="G50" t="n">
         <v>1.11</v>
       </c>
       <c r="H50" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="M50" t="n">
         <v>1.1</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
         <v>1.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>-0.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>4.94</v>
+        <v>5.1</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.13</v>
+        <v>0.16</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.56</v>
+        <v>3.24</v>
       </c>
       <c r="G51" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="H51" t="n">
-        <v>0.16</v>
+        <v>-0.01</v>
       </c>
       <c r="I51" t="n">
-        <v>3.24</v>
+        <v>-0.2</v>
       </c>
       <c r="J51" t="n">
-        <v>5.09</v>
+        <v>5.06</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.2</v>
+        <v>-0.59</v>
       </c>
       <c r="M51" t="n">
-        <v>5.06</v>
+        <v>5.15</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.03</v>
+        <v>0.09</v>
       </c>
       <c r="O51" t="n">
-        <v>-0.59</v>
+        <v>1.78</v>
       </c>
       <c r="P51" t="n">
-        <v>5.06</v>
+        <v>5.15</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.03</v>
+        <v>0.09</v>
       </c>
       <c r="R51" t="n">
-        <v>-0.59</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.49</v>
+        <v>10.52</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.53</v>
+        <v>0.03</v>
       </c>
       <c r="F52" t="n">
-        <v>-4.81</v>
+        <v>0.29</v>
       </c>
       <c r="G52" t="n">
-        <v>10.52</v>
+        <v>10.43</v>
       </c>
       <c r="H52" t="n">
-        <v>0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="I52" t="n">
-        <v>0.29</v>
+        <v>-0.86</v>
       </c>
       <c r="J52" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.86</v>
+        <v>-0.1</v>
       </c>
       <c r="M52" t="n">
-        <v>10.42</v>
+        <v>10.36</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.1</v>
+        <v>-0.58</v>
       </c>
       <c r="P52" t="n">
-        <v>10.42</v>
+        <v>10.36</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.1</v>
+        <v>-0.58</v>
       </c>
     </row>
     <row r="53">
@@ -3680,46 +3680,46 @@
         <v>7.1</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.98</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>7.1</v>
+        <v>7.05</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="J53" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="M53" t="n">
         <v>7.05</v>
       </c>
-      <c r="K53" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="L53" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="M53" t="n">
-        <v>7.15</v>
-      </c>
       <c r="N53" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="O53" t="n">
-        <v>1.42</v>
+        <v>-1.4</v>
       </c>
       <c r="P53" t="n">
-        <v>7.15</v>
+        <v>7.05</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="R53" t="n">
-        <v>1.42</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="54">
@@ -3804,46 +3804,46 @@
         <v>0.615</v>
       </c>
       <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="H55" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F55" t="n">
+      <c r="I55" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="G55" t="n">
-        <v>0.615</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
       <c r="J55" t="n">
-        <v>0.61</v>
+        <v>0.605</v>
       </c>
       <c r="K55" t="n">
         <v>-0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.82</v>
       </c>
       <c r="M55" t="n">
-        <v>0.605</v>
+        <v>0.61</v>
       </c>
       <c r="N55" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>-0.82</v>
+        <v>0.83</v>
       </c>
       <c r="P55" t="n">
-        <v>0.605</v>
+        <v>0.61</v>
       </c>
       <c r="Q55" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>-0.82</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="56">
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="F56" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I56" t="n">
+        <v>-5.63</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="L56" t="n">
+        <v>5.97</v>
+      </c>
+      <c r="M56" t="n">
         <v>0.345</v>
       </c>
-      <c r="E56" t="n">
+      <c r="N56" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F56" t="n">
+      <c r="O56" t="n">
         <v>-2.82</v>
       </c>
-      <c r="G56" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="I56" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J56" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="K56" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L56" t="n">
-        <v>-5.63</v>
-      </c>
-      <c r="M56" t="n">
-        <v>0.355</v>
-      </c>
-      <c r="N56" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="O56" t="n">
-        <v>5.97</v>
-      </c>
       <c r="P56" t="n">
-        <v>0.355</v>
+        <v>0.345</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="R56" t="n">
-        <v>5.97</v>
+        <v>-2.82</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="E57" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="H57" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="F57" t="n">
-        <v>-1.94</v>
-      </c>
-      <c r="G57" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0.02</v>
-      </c>
       <c r="I57" t="n">
-        <v>0.57</v>
+        <v>-1.97</v>
       </c>
       <c r="J57" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.02</v>
       </c>
       <c r="L57" t="n">
-        <v>-1.97</v>
+        <v>-0.57</v>
       </c>
       <c r="M57" t="n">
-        <v>3.46</v>
+        <v>3.51</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="O57" t="n">
-        <v>-0.57</v>
+        <v>1.45</v>
       </c>
       <c r="P57" t="n">
-        <v>3.46</v>
+        <v>3.51</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="R57" t="n">
-        <v>-0.57</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="58">
@@ -4014,22 +4014,22 @@
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.078</v>
+        <v>0.077</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>-1.28</v>
       </c>
       <c r="P58" t="n">
-        <v>0.078</v>
+        <v>0.077</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>20.64</v>
+        <v>20.73</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.65</v>
+        <v>0.09</v>
       </c>
       <c r="F59" t="n">
-        <v>-3.05</v>
+        <v>0.44</v>
       </c>
       <c r="G59" t="n">
-        <v>20.73</v>
+        <v>21.35</v>
       </c>
       <c r="H59" t="n">
-        <v>0.09</v>
+        <v>0.62</v>
       </c>
       <c r="I59" t="n">
-        <v>0.44</v>
+        <v>2.99</v>
       </c>
       <c r="J59" t="n">
-        <v>21.35</v>
+        <v>21.14</v>
       </c>
       <c r="K59" t="n">
-        <v>0.62</v>
+        <v>-0.21</v>
       </c>
       <c r="L59" t="n">
-        <v>2.99</v>
+        <v>-0.98</v>
       </c>
       <c r="M59" t="n">
-        <v>21.14</v>
+        <v>20.96</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.21</v>
+        <v>-0.18</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.98</v>
+        <v>-0.85</v>
       </c>
       <c r="P59" t="n">
-        <v>21.14</v>
+        <v>20.96</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.21</v>
+        <v>-0.18</v>
       </c>
       <c r="R59" t="n">
-        <v>-0.98</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.11</v>
+        <v>0.05</v>
       </c>
       <c r="F60" t="n">
-        <v>-3.48</v>
+        <v>1.64</v>
       </c>
       <c r="G60" t="n">
         <v>3.1</v>
       </c>
       <c r="H60" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="K60" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>-1.94</v>
       </c>
       <c r="M60" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="N60" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="O60" t="n">
-        <v>-1.94</v>
+        <v>-2.63</v>
       </c>
       <c r="P60" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="R60" t="n">
-        <v>-1.94</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.83</v>
+        <v>0.835</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.025</v>
+        <v>0.005</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.92</v>
+        <v>0.6</v>
       </c>
       <c r="G61" t="n">
         <v>0.835</v>
       </c>
       <c r="H61" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0.835</v>
+        <v>0.795</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>-4.79</v>
       </c>
       <c r="M61" t="n">
         <v>0.795</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>-4.79</v>
+        <v>0</v>
       </c>
       <c r="P61" t="n">
         <v>0.795</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>-4.79</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-10-09 Close</t>
+          <t>2026-10-12 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-10-09 Change</t>
+          <t>2026-10-12 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-10-09 Change %</t>
+          <t>2026-10-12 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-10-12 Close</t>
+          <t>2026-10-13 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-10-12 Change</t>
+          <t>2026-10-13 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-10-12 Change %</t>
+          <t>2026-10-13 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-10-13 Close</t>
+          <t>2026-10-14 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-10-13 Change</t>
+          <t>2026-10-14 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-10-13 Change %</t>
+          <t>2026-10-14 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-10-14 Close</t>
+          <t>2026-10-15 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-10-14 Change</t>
+          <t>2026-10-15 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-10-14 Change %</t>
+          <t>2026-10-15 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-10-15 Close</t>
+          <t>2026-10-16 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-10-15 Change</t>
+          <t>2026-10-16 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-10-15 Change %</t>
+          <t>2026-10-16 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>145.2</v>
+        <v>148.1</v>
       </c>
       <c r="E3" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F3" t="n">
+        <v>2</v>
+      </c>
+      <c r="G3" t="n">
+        <v>150.7</v>
+      </c>
+      <c r="H3" t="n">
         <v>2.6</v>
       </c>
-      <c r="F3" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="G3" t="n">
-        <v>148.1</v>
-      </c>
-      <c r="H3" t="n">
-        <v>2.9</v>
-      </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="J3" t="n">
-        <v>150.7</v>
+        <v>148</v>
       </c>
       <c r="K3" t="n">
-        <v>2.6</v>
+        <v>-2.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.76</v>
+        <v>-1.79</v>
       </c>
       <c r="M3" t="n">
-        <v>148</v>
+        <v>147.9</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.7</v>
+        <v>-0.1</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.79</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>148</v>
+        <v>147.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.7</v>
+        <v>-0.1</v>
       </c>
       <c r="R3" t="n">
-        <v>-1.79</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
+        <v>224.4</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="G4" t="n">
+        <v>229.8</v>
+      </c>
+      <c r="H4" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="J4" t="n">
+        <v>221.8</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-8</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="M4" t="n">
         <v>221</v>
       </c>
-      <c r="E4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="G4" t="n">
-        <v>224.4</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I4" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="J4" t="n">
-        <v>229.8</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="L4" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="M4" t="n">
-        <v>221.8</v>
-      </c>
       <c r="N4" t="n">
-        <v>-8</v>
+        <v>-0.8</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.48</v>
+        <v>-0.36</v>
       </c>
       <c r="P4" t="n">
-        <v>221.8</v>
+        <v>221</v>
       </c>
       <c r="Q4" t="n">
-        <v>-8</v>
+        <v>-0.8</v>
       </c>
       <c r="R4" t="n">
-        <v>-3.48</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.49</v>
+        <v>6.66</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1</v>
+        <v>0.17</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.52</v>
+        <v>2.62</v>
       </c>
       <c r="G5" t="n">
-        <v>6.66</v>
+        <v>6.72</v>
       </c>
       <c r="H5" t="n">
-        <v>0.17</v>
+        <v>0.06</v>
       </c>
       <c r="I5" t="n">
-        <v>2.62</v>
+        <v>0.9</v>
       </c>
       <c r="J5" t="n">
-        <v>6.72</v>
+        <v>6.57</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06</v>
+        <v>-0.15</v>
       </c>
       <c r="L5" t="n">
-        <v>0.9</v>
+        <v>-2.23</v>
       </c>
       <c r="M5" t="n">
-        <v>6.57</v>
+        <v>6.8</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.15</v>
+        <v>0.23</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.23</v>
+        <v>3.5</v>
       </c>
       <c r="P5" t="n">
-        <v>6.57</v>
+        <v>6.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.15</v>
+        <v>0.23</v>
       </c>
       <c r="R5" t="n">
-        <v>-2.23</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.5</v>
+        <v>7.62</v>
       </c>
       <c r="E6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7.64</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="J6" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="K6" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="F6" t="n">
+      <c r="L6" t="n">
         <v>-0.92</v>
       </c>
-      <c r="G6" t="n">
-        <v>7.62</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="J6" t="n">
-        <v>7.64</v>
-      </c>
-      <c r="K6" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.26</v>
-      </c>
       <c r="M6" t="n">
-        <v>7.57</v>
+        <v>7.7</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.92</v>
+        <v>1.72</v>
       </c>
       <c r="P6" t="n">
-        <v>7.57</v>
+        <v>7.7</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.92</v>
+        <v>1.72</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.12</v>
+        <v>6.25</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="F7" t="n">
-        <v>1.49</v>
+        <v>2.12</v>
       </c>
       <c r="G7" t="n">
-        <v>6.25</v>
+        <v>6.26</v>
       </c>
       <c r="H7" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>2.12</v>
+        <v>0.16</v>
       </c>
       <c r="J7" t="n">
-        <v>6.26</v>
+        <v>6.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="L7" t="n">
-        <v>0.16</v>
+        <v>-0.96</v>
       </c>
       <c r="M7" t="n">
-        <v>6.2</v>
+        <v>6.16</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.96</v>
+        <v>-0.65</v>
       </c>
       <c r="P7" t="n">
-        <v>6.2</v>
+        <v>6.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.96</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.73</v>
+        <v>9.91</v>
       </c>
       <c r="E8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="F8" t="n">
-        <v>0.72</v>
+        <v>1.85</v>
       </c>
       <c r="G8" t="n">
-        <v>9.91</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
       <c r="I8" t="n">
-        <v>1.85</v>
+        <v>0.5</v>
       </c>
       <c r="J8" t="n">
-        <v>9.960000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="K8" t="n">
-        <v>0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5</v>
+        <v>-1.1</v>
       </c>
       <c r="M8" t="n">
-        <v>9.85</v>
+        <v>9.98</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.11</v>
+        <v>0.13</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.1</v>
+        <v>1.32</v>
       </c>
       <c r="P8" t="n">
-        <v>9.85</v>
+        <v>9.98</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.11</v>
+        <v>0.13</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.1</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.390000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="E9" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="G9" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.04</v>
       </c>
-      <c r="F9" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="G9" t="n">
-        <v>8.59</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.2</v>
-      </c>
       <c r="I9" t="n">
-        <v>2.38</v>
+        <v>0.47</v>
       </c>
       <c r="J9" t="n">
-        <v>8.630000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="L9" t="n">
-        <v>0.47</v>
+        <v>-0.12</v>
       </c>
       <c r="M9" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>52.2</v>
+        <v>53.8</v>
       </c>
       <c r="E10" t="n">
-        <v>0.55</v>
+        <v>1.6</v>
       </c>
       <c r="F10" t="n">
-        <v>1.06</v>
+        <v>3.07</v>
       </c>
       <c r="G10" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="H10" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="I10" t="n">
-        <v>3.07</v>
+        <v>0.19</v>
       </c>
       <c r="J10" t="n">
-        <v>53.9</v>
+        <v>53.55</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1</v>
+        <v>-0.35</v>
       </c>
       <c r="L10" t="n">
-        <v>0.19</v>
+        <v>-0.65</v>
       </c>
       <c r="M10" t="n">
-        <v>53.55</v>
+        <v>53.95</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.35</v>
+        <v>0.4</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.65</v>
+        <v>0.75</v>
       </c>
       <c r="P10" t="n">
-        <v>53.55</v>
+        <v>53.95</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.35</v>
+        <v>0.4</v>
       </c>
       <c r="R10" t="n">
-        <v>-0.65</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
+        <v>4.51</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F11" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="G11" t="n">
         <v>4.53</v>
       </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" t="n">
-        <v>4.51</v>
-      </c>
       <c r="H11" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.44</v>
+        <v>0.44</v>
       </c>
       <c r="J11" t="n">
-        <v>4.53</v>
+        <v>4.59</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="L11" t="n">
-        <v>0.44</v>
+        <v>1.32</v>
       </c>
       <c r="M11" t="n">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="O11" t="n">
-        <v>1.32</v>
+        <v>-1.96</v>
       </c>
       <c r="P11" t="n">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="R11" t="n">
-        <v>1.32</v>
+        <v>-1.96</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.83</v>
+        <v>9.85</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="G12" t="n">
-        <v>9.85</v>
+        <v>10.22</v>
       </c>
       <c r="H12" t="n">
-        <v>0.02</v>
+        <v>0.37</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2</v>
+        <v>3.76</v>
       </c>
       <c r="J12" t="n">
-        <v>10.22</v>
+        <v>10.34</v>
       </c>
       <c r="K12" t="n">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
       <c r="L12" t="n">
-        <v>3.76</v>
+        <v>1.17</v>
       </c>
       <c r="M12" t="n">
-        <v>10.34</v>
+        <v>10.08</v>
       </c>
       <c r="N12" t="n">
-        <v>0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="O12" t="n">
-        <v>1.17</v>
+        <v>-2.51</v>
       </c>
       <c r="P12" t="n">
-        <v>10.34</v>
+        <v>10.08</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="R12" t="n">
-        <v>1.17</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>23.9</v>
+        <v>24.14</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.14</v>
+        <v>0.24</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.58</v>
+        <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>24.14</v>
+        <v>24.28</v>
       </c>
       <c r="H13" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0.58</v>
       </c>
       <c r="J13" t="n">
-        <v>24.28</v>
+        <v>24.72</v>
       </c>
       <c r="K13" t="n">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="L13" t="n">
-        <v>0.58</v>
+        <v>1.81</v>
       </c>
       <c r="M13" t="n">
-        <v>24.72</v>
+        <v>24.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.44</v>
+        <v>-0.52</v>
       </c>
       <c r="O13" t="n">
-        <v>1.81</v>
+        <v>-2.1</v>
       </c>
       <c r="P13" t="n">
-        <v>24.72</v>
+        <v>24.2</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.44</v>
+        <v>-0.52</v>
       </c>
       <c r="R13" t="n">
-        <v>1.81</v>
+        <v>-2.1</v>
       </c>
     </row>
     <row r="14">
@@ -1259,16 +1259,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="E14" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F14" t="n">
-        <v>1.06</v>
+        <v>-0.53</v>
       </c>
       <c r="G14" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="H14" t="n">
         <v>-0.01</v>
@@ -1277,31 +1277,31 @@
         <v>-0.53</v>
       </c>
       <c r="J14" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.53</v>
+        <v>-1.6</v>
       </c>
       <c r="M14" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.6</v>
+        <v>-2.16</v>
       </c>
       <c r="P14" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="R14" t="n">
-        <v>-1.6</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.34</v>
+        <v>5.36</v>
       </c>
       <c r="E15" t="n">
-        <v>0.12</v>
+        <v>0.02</v>
       </c>
       <c r="F15" t="n">
-        <v>2.3</v>
+        <v>0.37</v>
       </c>
       <c r="G15" t="n">
-        <v>5.36</v>
+        <v>5.41</v>
       </c>
       <c r="H15" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="I15" t="n">
-        <v>0.37</v>
+        <v>0.93</v>
       </c>
       <c r="J15" t="n">
-        <v>5.41</v>
+        <v>5.45</v>
       </c>
       <c r="K15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="L15" t="n">
-        <v>0.93</v>
+        <v>0.74</v>
       </c>
       <c r="M15" t="n">
-        <v>5.45</v>
+        <v>5.39</v>
       </c>
       <c r="N15" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="O15" t="n">
-        <v>0.74</v>
+        <v>-1.1</v>
       </c>
       <c r="P15" t="n">
-        <v>5.45</v>
+        <v>5.39</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="R15" t="n">
-        <v>0.74</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="16">
@@ -1383,7 +1383,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.36</v>
+        <v>4.39</v>
       </c>
       <c r="E16" t="n">
         <v>0.03</v>
@@ -1395,37 +1395,37 @@
         <v>4.39</v>
       </c>
       <c r="H16" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>4.39</v>
+        <v>4.41</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="M16" t="n">
-        <v>4.41</v>
+        <v>4.34</v>
       </c>
       <c r="N16" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>0.46</v>
+        <v>-1.59</v>
       </c>
       <c r="P16" t="n">
-        <v>4.41</v>
+        <v>4.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R16" t="n">
-        <v>0.46</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.62</v>
+        <v>0.31</v>
       </c>
       <c r="G17" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="H17" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="I17" t="n">
-        <v>0.31</v>
+        <v>1.55</v>
       </c>
       <c r="J17" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="K17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="L17" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="M17" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="N17" t="n">
-        <v>0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="O17" t="n">
-        <v>1.83</v>
+        <v>-3</v>
       </c>
       <c r="P17" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="R17" t="n">
-        <v>1.83</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.33</v>
+        <v>1.32</v>
       </c>
       <c r="G18" t="n">
-        <v>3.06</v>
+        <v>3.17</v>
       </c>
       <c r="H18" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="I18" t="n">
-        <v>1.32</v>
+        <v>3.59</v>
       </c>
       <c r="J18" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="K18" t="n">
-        <v>0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="L18" t="n">
-        <v>3.59</v>
+        <v>-2.84</v>
       </c>
       <c r="M18" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.84</v>
+        <v>-2.27</v>
       </c>
       <c r="P18" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R18" t="n">
-        <v>-2.84</v>
+        <v>-2.27</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>51.85</v>
+        <v>51.65</v>
       </c>
       <c r="E19" t="n">
-        <v>0.55</v>
+        <v>-0.2</v>
       </c>
       <c r="F19" t="n">
-        <v>1.07</v>
+        <v>-0.39</v>
       </c>
       <c r="G19" t="n">
-        <v>51.65</v>
+        <v>51.35</v>
       </c>
       <c r="H19" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="J19" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="M19" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="N19" t="n">
         <v>-0.2</v>
       </c>
-      <c r="I19" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="J19" t="n">
-        <v>51.35</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="L19" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="M19" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-0.75</v>
-      </c>
       <c r="O19" t="n">
-        <v>-1.46</v>
+        <v>-0.4</v>
       </c>
       <c r="P19" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.75</v>
+        <v>-0.2</v>
       </c>
       <c r="R19" t="n">
-        <v>-1.46</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>26.16</v>
+        <v>26.26</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6</v>
+        <v>0.1</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.24</v>
+        <v>0.38</v>
       </c>
       <c r="G20" t="n">
-        <v>26.26</v>
+        <v>25.62</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1</v>
+        <v>-0.64</v>
       </c>
       <c r="I20" t="n">
-        <v>0.38</v>
+        <v>-2.44</v>
       </c>
       <c r="J20" t="n">
-        <v>25.62</v>
+        <v>24.94</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.64</v>
+        <v>-0.68</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.44</v>
+        <v>-2.65</v>
       </c>
       <c r="M20" t="n">
-        <v>24.94</v>
+        <v>24.32</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.68</v>
+        <v>-0.62</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.65</v>
+        <v>-2.49</v>
       </c>
       <c r="P20" t="n">
-        <v>24.94</v>
+        <v>24.32</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.68</v>
+        <v>-0.62</v>
       </c>
       <c r="R20" t="n">
-        <v>-2.65</v>
+        <v>-2.49</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="G21" t="n">
         <v>4.68</v>
       </c>
-      <c r="E21" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F21" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.66</v>
-      </c>
       <c r="H21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="N21" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I21" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.06</v>
-      </c>
       <c r="O21" t="n">
-        <v>1.28</v>
+        <v>-0.42</v>
       </c>
       <c r="P21" t="n">
-        <v>4.74</v>
+        <v>4.72</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="R21" t="n">
-        <v>1.28</v>
+        <v>-0.42</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>80.09999999999999</v>
+        <v>79.95</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7</v>
+        <v>-0.15</v>
       </c>
       <c r="F22" t="n">
-        <v>0.88</v>
+        <v>-0.19</v>
       </c>
       <c r="G22" t="n">
-        <v>79.95</v>
+        <v>80.45</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.15</v>
+        <v>0.5</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.19</v>
+        <v>0.63</v>
       </c>
       <c r="J22" t="n">
-        <v>80.45</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="L22" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="N22" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="O22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="P22" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20.76</v>
+        <v>20.36</v>
       </c>
       <c r="E23" t="n">
-        <v>0.06</v>
+        <v>-0.4</v>
       </c>
       <c r="F23" t="n">
-        <v>0.29</v>
+        <v>-1.93</v>
       </c>
       <c r="G23" t="n">
-        <v>20.36</v>
+        <v>20.12</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4</v>
+        <v>-0.24</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.93</v>
+        <v>-1.18</v>
       </c>
       <c r="J23" t="n">
-        <v>20.12</v>
+        <v>20.06</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.24</v>
+        <v>-0.06</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.18</v>
+        <v>-0.3</v>
       </c>
       <c r="M23" t="n">
-        <v>20.06</v>
+        <v>19.29</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.06</v>
+        <v>-0.77</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3</v>
+        <v>-3.84</v>
       </c>
       <c r="P23" t="n">
-        <v>20.06</v>
+        <v>19.29</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.06</v>
+        <v>-0.77</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.3</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.86</v>
+        <v>13.48</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.05</v>
+        <v>-0.38</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.36</v>
+        <v>-2.74</v>
       </c>
       <c r="G24" t="n">
-        <v>13.48</v>
+        <v>12.89</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.38</v>
+        <v>-0.59</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.74</v>
+        <v>-4.38</v>
       </c>
       <c r="J24" t="n">
-        <v>12.89</v>
+        <v>13.05</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.59</v>
+        <v>0.16</v>
       </c>
       <c r="L24" t="n">
-        <v>-4.38</v>
+        <v>1.24</v>
       </c>
       <c r="M24" t="n">
-        <v>13.05</v>
+        <v>12.27</v>
       </c>
       <c r="N24" t="n">
-        <v>0.16</v>
+        <v>-0.78</v>
       </c>
       <c r="O24" t="n">
-        <v>1.24</v>
+        <v>-5.98</v>
       </c>
       <c r="P24" t="n">
-        <v>13.05</v>
+        <v>12.27</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.16</v>
+        <v>-0.78</v>
       </c>
       <c r="R24" t="n">
-        <v>1.24</v>
+        <v>-5.98</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.96</v>
+        <v>24.52</v>
       </c>
       <c r="E25" t="n">
-        <v>2.3</v>
+        <v>-1.44</v>
       </c>
       <c r="F25" t="n">
-        <v>9.720000000000001</v>
+        <v>-5.55</v>
       </c>
       <c r="G25" t="n">
-        <v>24.52</v>
+        <v>25.04</v>
       </c>
       <c r="H25" t="n">
-        <v>-1.44</v>
+        <v>0.52</v>
       </c>
       <c r="I25" t="n">
-        <v>-5.55</v>
+        <v>2.12</v>
       </c>
       <c r="J25" t="n">
-        <v>25.04</v>
+        <v>26.38</v>
       </c>
       <c r="K25" t="n">
-        <v>0.52</v>
+        <v>1.34</v>
       </c>
       <c r="L25" t="n">
-        <v>2.12</v>
+        <v>5.35</v>
       </c>
       <c r="M25" t="n">
-        <v>26.38</v>
+        <v>27.08</v>
       </c>
       <c r="N25" t="n">
-        <v>1.34</v>
+        <v>0.7</v>
       </c>
       <c r="O25" t="n">
-        <v>5.35</v>
+        <v>2.65</v>
       </c>
       <c r="P25" t="n">
-        <v>26.38</v>
+        <v>27.08</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.34</v>
+        <v>0.7</v>
       </c>
       <c r="R25" t="n">
-        <v>5.35</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>31</v>
+        <v>29.9</v>
       </c>
       <c r="E26" t="n">
-        <v>0.64</v>
+        <v>-1.1</v>
       </c>
       <c r="F26" t="n">
-        <v>2.11</v>
+        <v>-3.55</v>
       </c>
       <c r="G26" t="n">
-        <v>29.9</v>
+        <v>28.24</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.1</v>
+        <v>-1.66</v>
       </c>
       <c r="I26" t="n">
-        <v>-3.55</v>
+        <v>-5.55</v>
       </c>
       <c r="J26" t="n">
-        <v>28.24</v>
+        <v>28.34</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.66</v>
+        <v>0.1</v>
       </c>
       <c r="L26" t="n">
-        <v>-5.55</v>
+        <v>0.35</v>
       </c>
       <c r="M26" t="n">
-        <v>28.34</v>
+        <v>24.98</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1</v>
+        <v>-3.36</v>
       </c>
       <c r="O26" t="n">
-        <v>0.35</v>
+        <v>-11.86</v>
       </c>
       <c r="P26" t="n">
-        <v>28.34</v>
+        <v>24.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.1</v>
+        <v>-3.36</v>
       </c>
       <c r="R26" t="n">
-        <v>0.35</v>
+        <v>-11.86</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>424.8</v>
+        <v>425.8</v>
       </c>
       <c r="E27" t="n">
-        <v>13.4</v>
+        <v>1</v>
       </c>
       <c r="F27" t="n">
-        <v>3.26</v>
+        <v>0.24</v>
       </c>
       <c r="G27" t="n">
-        <v>425.8</v>
+        <v>425.2</v>
       </c>
       <c r="H27" t="n">
-        <v>1</v>
+        <v>-0.6</v>
       </c>
       <c r="I27" t="n">
-        <v>0.24</v>
+        <v>-0.14</v>
       </c>
       <c r="J27" t="n">
-        <v>425.2</v>
+        <v>423.4</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.14</v>
+        <v>-0.42</v>
       </c>
       <c r="M27" t="n">
-        <v>423.4</v>
+        <v>417.8</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.8</v>
+        <v>-5.6</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.42</v>
+        <v>-1.32</v>
       </c>
       <c r="P27" t="n">
-        <v>423.4</v>
+        <v>417.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>-1.8</v>
+        <v>-5.6</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.42</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>107</v>
+        <v>108.2</v>
       </c>
       <c r="E28" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="F28" t="n">
-        <v>2.59</v>
+        <v>1.12</v>
       </c>
       <c r="G28" t="n">
-        <v>108.2</v>
+        <v>107.2</v>
       </c>
       <c r="H28" t="n">
-        <v>1.2</v>
+        <v>-1</v>
       </c>
       <c r="I28" t="n">
-        <v>1.12</v>
+        <v>-0.92</v>
       </c>
       <c r="J28" t="n">
-        <v>107.2</v>
+        <v>110.5</v>
       </c>
       <c r="K28" t="n">
-        <v>-1</v>
+        <v>3.3</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.92</v>
+        <v>3.08</v>
       </c>
       <c r="M28" t="n">
-        <v>110.5</v>
+        <v>106.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>-4.1</v>
       </c>
       <c r="O28" t="n">
-        <v>3.08</v>
+        <v>-3.71</v>
       </c>
       <c r="P28" t="n">
-        <v>110.5</v>
+        <v>106.4</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>-4.1</v>
       </c>
       <c r="R28" t="n">
-        <v>3.08</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>105.6</v>
+        <v>108.5</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4</v>
+        <v>2.9</v>
       </c>
       <c r="F29" t="n">
-        <v>0.38</v>
+        <v>2.75</v>
       </c>
       <c r="G29" t="n">
-        <v>108.5</v>
+        <v>104.9</v>
       </c>
       <c r="H29" t="n">
-        <v>2.9</v>
+        <v>-3.6</v>
       </c>
       <c r="I29" t="n">
-        <v>2.75</v>
+        <v>-3.32</v>
       </c>
       <c r="J29" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="M29" t="n">
         <v>104.9</v>
       </c>
-      <c r="K29" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="L29" t="n">
-        <v>-3.32</v>
-      </c>
-      <c r="M29" t="n">
-        <v>106.1</v>
-      </c>
       <c r="N29" t="n">
-        <v>1.2</v>
+        <v>-1.2</v>
       </c>
       <c r="O29" t="n">
-        <v>1.14</v>
+        <v>-1.13</v>
       </c>
       <c r="P29" t="n">
-        <v>106.1</v>
+        <v>104.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.2</v>
+        <v>-1.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.14</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>71.5</v>
+        <v>71.8</v>
       </c>
       <c r="E30" t="n">
-        <v>2.1</v>
+        <v>0.3</v>
       </c>
       <c r="F30" t="n">
-        <v>3.03</v>
+        <v>0.42</v>
       </c>
       <c r="G30" t="n">
-        <v>71.8</v>
+        <v>72.3</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I30" t="n">
-        <v>0.42</v>
+        <v>0.7</v>
       </c>
       <c r="J30" t="n">
-        <v>72.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="L30" t="n">
-        <v>0.7</v>
+        <v>6.64</v>
       </c>
       <c r="M30" t="n">
-        <v>77.09999999999999</v>
+        <v>75.45</v>
       </c>
       <c r="N30" t="n">
-        <v>4.8</v>
+        <v>-1.65</v>
       </c>
       <c r="O30" t="n">
-        <v>6.64</v>
+        <v>-2.14</v>
       </c>
       <c r="P30" t="n">
-        <v>77.09999999999999</v>
+        <v>75.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>4.8</v>
+        <v>-1.65</v>
       </c>
       <c r="R30" t="n">
-        <v>6.64</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>83</v>
+        <v>81.8</v>
       </c>
       <c r="E31" t="n">
-        <v>0.85</v>
+        <v>-1.2</v>
       </c>
       <c r="F31" t="n">
-        <v>1.03</v>
+        <v>-1.45</v>
       </c>
       <c r="G31" t="n">
-        <v>81.8</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="H31" t="n">
-        <v>-1.2</v>
+        <v>-0.15</v>
       </c>
       <c r="I31" t="n">
-        <v>-1.45</v>
+        <v>-0.18</v>
       </c>
       <c r="J31" t="n">
-        <v>81.65000000000001</v>
+        <v>82.05</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.15</v>
+        <v>0.4</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.18</v>
+        <v>0.49</v>
       </c>
       <c r="M31" t="n">
-        <v>82.05</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>0.4</v>
+        <v>-3.7</v>
       </c>
       <c r="O31" t="n">
-        <v>0.49</v>
+        <v>-4.51</v>
       </c>
       <c r="P31" t="n">
-        <v>82.05</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.4</v>
+        <v>-3.7</v>
       </c>
       <c r="R31" t="n">
-        <v>0.49</v>
+        <v>-4.51</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>57.65</v>
+        <v>56.2</v>
       </c>
       <c r="E32" t="n">
-        <v>0.85</v>
+        <v>-1.45</v>
       </c>
       <c r="F32" t="n">
-        <v>1.5</v>
+        <v>-2.52</v>
       </c>
       <c r="G32" t="n">
-        <v>56.2</v>
+        <v>55.55</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.45</v>
+        <v>-0.65</v>
       </c>
       <c r="I32" t="n">
-        <v>-2.52</v>
+        <v>-1.16</v>
       </c>
       <c r="J32" t="n">
-        <v>55.55</v>
+        <v>54.3</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.65</v>
+        <v>-1.25</v>
       </c>
       <c r="L32" t="n">
-        <v>-1.16</v>
+        <v>-2.25</v>
       </c>
       <c r="M32" t="n">
-        <v>54.3</v>
+        <v>52.15</v>
       </c>
       <c r="N32" t="n">
-        <v>-1.25</v>
+        <v>-2.15</v>
       </c>
       <c r="O32" t="n">
-        <v>-2.25</v>
+        <v>-3.96</v>
       </c>
       <c r="P32" t="n">
-        <v>54.3</v>
+        <v>52.15</v>
       </c>
       <c r="Q32" t="n">
-        <v>-1.25</v>
+        <v>-2.15</v>
       </c>
       <c r="R32" t="n">
-        <v>-2.25</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>75.59999999999999</v>
+        <v>74.34999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>2.7</v>
+        <v>-1.25</v>
       </c>
       <c r="F33" t="n">
-        <v>3.7</v>
+        <v>-1.65</v>
       </c>
       <c r="G33" t="n">
-        <v>74.34999999999999</v>
+        <v>73.25</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.25</v>
+        <v>-1.1</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.65</v>
+        <v>-1.48</v>
       </c>
       <c r="J33" t="n">
-        <v>73.25</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>-1.1</v>
+        <v>-0.4</v>
       </c>
       <c r="L33" t="n">
-        <v>-1.48</v>
+        <v>-0.55</v>
       </c>
       <c r="M33" t="n">
-        <v>72.84999999999999</v>
+        <v>72.95</v>
       </c>
       <c r="N33" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="O33" t="n">
-        <v>-0.55</v>
+        <v>0.14</v>
       </c>
       <c r="P33" t="n">
-        <v>72.84999999999999</v>
+        <v>72.95</v>
       </c>
       <c r="Q33" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="R33" t="n">
-        <v>-0.55</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>30.1</v>
+        <v>29.26</v>
       </c>
       <c r="E34" t="n">
-        <v>1.56</v>
+        <v>-0.84</v>
       </c>
       <c r="F34" t="n">
-        <v>5.47</v>
+        <v>-2.79</v>
       </c>
       <c r="G34" t="n">
-        <v>29.26</v>
+        <v>29.16</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.84</v>
+        <v>-0.1</v>
       </c>
       <c r="I34" t="n">
-        <v>-2.79</v>
+        <v>-0.34</v>
       </c>
       <c r="J34" t="n">
-        <v>29.16</v>
+        <v>29.52</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.1</v>
+        <v>0.36</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.34</v>
+        <v>1.23</v>
       </c>
       <c r="M34" t="n">
-        <v>29.52</v>
+        <v>28.58</v>
       </c>
       <c r="N34" t="n">
-        <v>0.36</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>1.23</v>
+        <v>-3.18</v>
       </c>
       <c r="P34" t="n">
-        <v>29.52</v>
+        <v>28.58</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.36</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="R34" t="n">
-        <v>1.23</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.1</v>
+        <v>4.08</v>
       </c>
       <c r="E35" t="n">
-        <v>0.11</v>
+        <v>-0.02</v>
       </c>
       <c r="F35" t="n">
-        <v>2.76</v>
+        <v>-0.49</v>
       </c>
       <c r="G35" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.49</v>
+        <v>-0.74</v>
       </c>
       <c r="J35" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.74</v>
+        <v>0.99</v>
       </c>
       <c r="M35" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="N35" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="O35" t="n">
-        <v>-0.74</v>
+        <v>0.99</v>
       </c>
       <c r="P35" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="Q35" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="R35" t="n">
-        <v>-0.74</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>0.25</v>
+        <v>-0.04</v>
       </c>
       <c r="F36" t="n">
-        <v>2.91</v>
+        <v>-0.45</v>
       </c>
       <c r="G36" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="H36" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="I36" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="J36" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="H36" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I36" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="J36" t="n">
-        <v>8.74</v>
-      </c>
       <c r="K36" t="n">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>8.74</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
       <c r="O36" t="n">
-        <v>-0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="P36" t="n">
-        <v>8.74</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Q36" t="n">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.68</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>377.8</v>
+        <v>375.4</v>
       </c>
       <c r="E37" t="n">
-        <v>2.8</v>
+        <v>-2.4</v>
       </c>
       <c r="F37" t="n">
-        <v>0.75</v>
+        <v>-0.64</v>
       </c>
       <c r="G37" t="n">
-        <v>375.4</v>
+        <v>379.6</v>
       </c>
       <c r="H37" t="n">
-        <v>-2.4</v>
+        <v>4.2</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.64</v>
+        <v>1.12</v>
       </c>
       <c r="J37" t="n">
-        <v>379.6</v>
+        <v>373.6</v>
       </c>
       <c r="K37" t="n">
-        <v>4.2</v>
+        <v>-6</v>
       </c>
       <c r="L37" t="n">
-        <v>1.12</v>
+        <v>-1.58</v>
       </c>
       <c r="M37" t="n">
-        <v>373.6</v>
+        <v>371.4</v>
       </c>
       <c r="N37" t="n">
-        <v>-6</v>
+        <v>-2.2</v>
       </c>
       <c r="O37" t="n">
-        <v>-1.58</v>
+        <v>-0.59</v>
       </c>
       <c r="P37" t="n">
-        <v>373.6</v>
+        <v>371.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>-6</v>
+        <v>-2.2</v>
       </c>
       <c r="R37" t="n">
-        <v>-1.58</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.46</v>
+        <v>11.05</v>
       </c>
       <c r="E38" t="n">
-        <v>0.44</v>
+        <v>-0.41</v>
       </c>
       <c r="F38" t="n">
-        <v>3.99</v>
+        <v>-3.58</v>
       </c>
       <c r="G38" t="n">
-        <v>11.05</v>
+        <v>11.42</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.41</v>
+        <v>0.37</v>
       </c>
       <c r="I38" t="n">
-        <v>-3.58</v>
+        <v>3.35</v>
       </c>
       <c r="J38" t="n">
-        <v>11.42</v>
+        <v>11.29</v>
       </c>
       <c r="K38" t="n">
-        <v>0.37</v>
+        <v>-0.13</v>
       </c>
       <c r="L38" t="n">
-        <v>3.35</v>
+        <v>-1.14</v>
       </c>
       <c r="M38" t="n">
-        <v>11.29</v>
+        <v>11.3</v>
       </c>
       <c r="N38" t="n">
-        <v>-0.13</v>
+        <v>0.01</v>
       </c>
       <c r="O38" t="n">
-        <v>-1.14</v>
+        <v>0.09</v>
       </c>
       <c r="P38" t="n">
-        <v>11.29</v>
+        <v>11.3</v>
       </c>
       <c r="Q38" t="n">
-        <v>-0.13</v>
+        <v>0.01</v>
       </c>
       <c r="R38" t="n">
-        <v>-1.14</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>491.4</v>
+        <v>494.8</v>
       </c>
       <c r="E39" t="n">
-        <v>14.6</v>
+        <v>3.4</v>
       </c>
       <c r="F39" t="n">
-        <v>3.06</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G39" t="n">
-        <v>494.8</v>
+        <v>485.2</v>
       </c>
       <c r="H39" t="n">
-        <v>3.4</v>
+        <v>-9.6</v>
       </c>
       <c r="I39" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.94</v>
       </c>
       <c r="J39" t="n">
-        <v>485.2</v>
+        <v>467</v>
       </c>
       <c r="K39" t="n">
-        <v>-9.6</v>
+        <v>-18.2</v>
       </c>
       <c r="L39" t="n">
-        <v>-1.94</v>
+        <v>-3.75</v>
       </c>
       <c r="M39" t="n">
-        <v>467</v>
+        <v>448.6</v>
       </c>
       <c r="N39" t="n">
-        <v>-18.2</v>
+        <v>-18.4</v>
       </c>
       <c r="O39" t="n">
-        <v>-3.75</v>
+        <v>-3.94</v>
       </c>
       <c r="P39" t="n">
-        <v>467</v>
+        <v>448.6</v>
       </c>
       <c r="Q39" t="n">
-        <v>-18.2</v>
+        <v>-18.4</v>
       </c>
       <c r="R39" t="n">
-        <v>-3.75</v>
+        <v>-3.94</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>38.34</v>
+        <v>38.48</v>
       </c>
       <c r="E40" t="n">
-        <v>0.84</v>
+        <v>0.14</v>
       </c>
       <c r="F40" t="n">
-        <v>2.24</v>
+        <v>0.37</v>
       </c>
       <c r="G40" t="n">
-        <v>38.48</v>
+        <v>37.84</v>
       </c>
       <c r="H40" t="n">
-        <v>0.14</v>
+        <v>-0.64</v>
       </c>
       <c r="I40" t="n">
-        <v>0.37</v>
+        <v>-1.66</v>
       </c>
       <c r="J40" t="n">
-        <v>37.84</v>
+        <v>38.62</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.64</v>
+        <v>0.78</v>
       </c>
       <c r="L40" t="n">
-        <v>-1.66</v>
+        <v>2.06</v>
       </c>
       <c r="M40" t="n">
-        <v>38.62</v>
+        <v>37.2</v>
       </c>
       <c r="N40" t="n">
-        <v>0.78</v>
+        <v>-1.42</v>
       </c>
       <c r="O40" t="n">
-        <v>2.06</v>
+        <v>-3.68</v>
       </c>
       <c r="P40" t="n">
-        <v>38.62</v>
+        <v>37.2</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.78</v>
+        <v>-1.42</v>
       </c>
       <c r="R40" t="n">
-        <v>2.06</v>
+        <v>-3.68</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
+        <v>29.06</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="G41" t="n">
+        <v>29.2</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="J41" t="n">
         <v>29</v>
       </c>
-      <c r="E41" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0</v>
-      </c>
-      <c r="G41" t="n">
-        <v>29.06</v>
-      </c>
-      <c r="H41" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I41" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="J41" t="n">
-        <v>29.2</v>
-      </c>
       <c r="K41" t="n">
-        <v>0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="L41" t="n">
-        <v>0.48</v>
+        <v>-0.68</v>
       </c>
       <c r="M41" t="n">
-        <v>29</v>
+        <v>28.99</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.2</v>
+        <v>-0.01</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.68</v>
+        <v>-0.03</v>
       </c>
       <c r="P41" t="n">
-        <v>29</v>
+        <v>28.99</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.2</v>
+        <v>-0.01</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.68</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>73.36</v>
+        <v>73.94</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.49</v>
+        <v>0.58</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.66</v>
+        <v>0.79</v>
       </c>
       <c r="G42" t="n">
-        <v>73.94</v>
+        <v>74.47</v>
       </c>
       <c r="H42" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="I42" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="J42" t="n">
-        <v>74.47</v>
+        <v>74.34</v>
       </c>
       <c r="K42" t="n">
-        <v>0.53</v>
+        <v>-0.13</v>
       </c>
       <c r="L42" t="n">
-        <v>0.72</v>
+        <v>-0.17</v>
       </c>
       <c r="M42" t="n">
-        <v>74.34</v>
+        <v>73.75</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.13</v>
+        <v>-0.59</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.17</v>
+        <v>-0.79</v>
       </c>
       <c r="P42" t="n">
-        <v>74.34</v>
+        <v>73.75</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.13</v>
+        <v>-0.59</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.17</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>39.96</v>
+        <v>40.5</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.29</v>
+        <v>0.54</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.72</v>
+        <v>1.35</v>
       </c>
       <c r="G43" t="n">
-        <v>40.5</v>
+        <v>40.93</v>
       </c>
       <c r="H43" t="n">
-        <v>0.54</v>
+        <v>0.43</v>
       </c>
       <c r="I43" t="n">
-        <v>1.35</v>
+        <v>1.06</v>
       </c>
       <c r="J43" t="n">
-        <v>40.93</v>
+        <v>41.06</v>
       </c>
       <c r="K43" t="n">
-        <v>0.43</v>
+        <v>0.13</v>
       </c>
       <c r="L43" t="n">
-        <v>1.06</v>
+        <v>0.32</v>
       </c>
       <c r="M43" t="n">
-        <v>41.06</v>
+        <v>41.69</v>
       </c>
       <c r="N43" t="n">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
       <c r="O43" t="n">
-        <v>0.32</v>
+        <v>1.53</v>
       </c>
       <c r="P43" t="n">
-        <v>41.06</v>
+        <v>41.69</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
       <c r="R43" t="n">
-        <v>0.32</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>5.9</v>
+        <v>6.01</v>
       </c>
       <c r="E44" t="n">
-        <v>0.08</v>
+        <v>0.11</v>
       </c>
       <c r="F44" t="n">
-        <v>1.37</v>
+        <v>1.86</v>
       </c>
       <c r="G44" t="n">
-        <v>6.01</v>
+        <v>6.08</v>
       </c>
       <c r="H44" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>1.86</v>
+        <v>1.16</v>
       </c>
       <c r="J44" t="n">
-        <v>6.08</v>
+        <v>6.04</v>
       </c>
       <c r="K44" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="L44" t="n">
-        <v>1.16</v>
+        <v>-0.66</v>
       </c>
       <c r="M44" t="n">
-        <v>6.04</v>
+        <v>5.92</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.66</v>
+        <v>-1.99</v>
       </c>
       <c r="P44" t="n">
-        <v>6.04</v>
+        <v>5.92</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.66</v>
+        <v>-1.99</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="E45" t="n">
-        <v>0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="F45" t="n">
-        <v>2.04</v>
+        <v>-2.5</v>
       </c>
       <c r="G45" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="I45" t="n">
-        <v>-2.5</v>
+        <v>-0.51</v>
       </c>
       <c r="J45" t="n">
         <v>1.94</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>-4.64</v>
       </c>
       <c r="P45" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>-4.64</v>
       </c>
     </row>
     <row r="46">
@@ -3246,46 +3246,46 @@
         <v>3.73</v>
       </c>
       <c r="E46" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.27</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>-1.61</v>
       </c>
       <c r="J46" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="L46" t="n">
-        <v>-1.61</v>
+        <v>-0.82</v>
       </c>
       <c r="M46" t="n">
-        <v>3.64</v>
+        <v>3.57</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>-0.82</v>
+        <v>-1.92</v>
       </c>
       <c r="P46" t="n">
-        <v>3.64</v>
+        <v>3.57</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R46" t="n">
-        <v>-0.82</v>
+        <v>-1.92</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.42</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.86</v>
+        <v>-0.19</v>
       </c>
       <c r="G47" t="n">
-        <v>10.4</v>
+        <v>10.35</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.19</v>
+        <v>-0.48</v>
       </c>
       <c r="J47" t="n">
-        <v>10.35</v>
+        <v>10.41</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.48</v>
+        <v>0.58</v>
       </c>
       <c r="M47" t="n">
-        <v>10.41</v>
+        <v>10.25</v>
       </c>
       <c r="N47" t="n">
-        <v>0.06</v>
+        <v>-0.16</v>
       </c>
       <c r="O47" t="n">
-        <v>0.58</v>
+        <v>-1.54</v>
       </c>
       <c r="P47" t="n">
-        <v>10.41</v>
+        <v>10.25</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.06</v>
+        <v>-0.16</v>
       </c>
       <c r="R47" t="n">
-        <v>0.58</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.29</v>
+        <v>0.285</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="F48" t="n">
-        <v>0</v>
+        <v>-1.72</v>
       </c>
       <c r="G48" t="n">
         <v>0.285</v>
       </c>
       <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="L48" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="N48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="I48" t="n">
+      <c r="O48" t="n">
         <v>-1.72</v>
       </c>
-      <c r="J48" t="n">
+      <c r="P48" t="n">
         <v>0.285</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="N48" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="O48" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0.29</v>
-      </c>
       <c r="Q48" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>1.75</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="49">
@@ -3429,49 +3429,49 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.24</v>
+        <v>4.2</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="G49" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="H49" t="n">
         <v>-0.04</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.95</v>
       </c>
       <c r="J49" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="K49" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L49" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="M49" t="n">
         <v>4.16</v>
       </c>
-      <c r="K49" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="L49" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="M49" t="n">
-        <v>4.14</v>
-      </c>
       <c r="N49" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="O49" t="n">
-        <v>-0.48</v>
+        <v>0.48</v>
       </c>
       <c r="P49" t="n">
-        <v>4.14</v>
+        <v>4.16</v>
       </c>
       <c r="Q49" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="R49" t="n">
-        <v>-0.48</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="50">
@@ -3494,46 +3494,46 @@
         <v>1.11</v>
       </c>
       <c r="E50" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="G50" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="J50" t="n">
         <v>1.1</v>
       </c>
       <c r="K50" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N50" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L50" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="M50" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N50" t="n">
-        <v>0</v>
-      </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>-0.91</v>
       </c>
       <c r="P50" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>-0.91</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="E51" t="n">
-        <v>0.16</v>
+        <v>-0.01</v>
       </c>
       <c r="F51" t="n">
-        <v>3.24</v>
+        <v>-0.2</v>
       </c>
       <c r="G51" t="n">
-        <v>5.09</v>
+        <v>5.06</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.2</v>
+        <v>-0.59</v>
       </c>
       <c r="J51" t="n">
-        <v>5.06</v>
+        <v>5.15</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.03</v>
+        <v>0.09</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.59</v>
+        <v>1.78</v>
       </c>
       <c r="M51" t="n">
-        <v>5.15</v>
+        <v>5.03</v>
       </c>
       <c r="N51" t="n">
-        <v>0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="O51" t="n">
-        <v>1.78</v>
+        <v>-2.33</v>
       </c>
       <c r="P51" t="n">
-        <v>5.15</v>
+        <v>5.03</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="R51" t="n">
-        <v>1.78</v>
+        <v>-2.33</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.52</v>
+        <v>10.43</v>
       </c>
       <c r="E52" t="n">
-        <v>0.03</v>
+        <v>-0.09</v>
       </c>
       <c r="F52" t="n">
-        <v>0.29</v>
+        <v>-0.86</v>
       </c>
       <c r="G52" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.86</v>
+        <v>-0.1</v>
       </c>
       <c r="J52" t="n">
-        <v>10.42</v>
+        <v>10.36</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.1</v>
+        <v>-0.58</v>
       </c>
       <c r="M52" t="n">
-        <v>10.36</v>
+        <v>10.12</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.06</v>
+        <v>-0.24</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.58</v>
+        <v>-2.32</v>
       </c>
       <c r="P52" t="n">
-        <v>10.36</v>
+        <v>10.12</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.06</v>
+        <v>-0.24</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.58</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7.1</v>
+        <v>7.05</v>
       </c>
       <c r="E53" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="G53" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I53" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J53" t="n">
         <v>7.05</v>
       </c>
-      <c r="H53" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="I53" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="J53" t="n">
-        <v>7.15</v>
-      </c>
       <c r="K53" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="L53" t="n">
-        <v>1.42</v>
+        <v>-1.4</v>
       </c>
       <c r="M53" t="n">
         <v>7.05</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
         <v>7.05</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3766,22 +3766,22 @@
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
       <c r="P54" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
     </row>
     <row r="55">
@@ -3801,49 +3801,49 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.615</v>
+        <v>0.61</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="G55" t="n">
-        <v>0.61</v>
+        <v>0.605</v>
       </c>
       <c r="H55" t="n">
         <v>-0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.82</v>
       </c>
       <c r="J55" t="n">
-        <v>0.605</v>
+        <v>0.61</v>
       </c>
       <c r="K55" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="L55" t="n">
-        <v>-0.82</v>
+        <v>0.83</v>
       </c>
       <c r="M55" t="n">
         <v>0.61</v>
       </c>
       <c r="N55" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
         <v>0.61</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-5.63</v>
+      </c>
+      <c r="G56" t="n">
         <v>0.355</v>
       </c>
-      <c r="E56" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="F56" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0.335</v>
-      </c>
       <c r="H56" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="I56" t="n">
-        <v>-5.63</v>
+        <v>5.97</v>
       </c>
       <c r="J56" t="n">
-        <v>0.355</v>
+        <v>0.345</v>
       </c>
       <c r="K56" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="L56" t="n">
-        <v>5.97</v>
+        <v>-2.82</v>
       </c>
       <c r="M56" t="n">
-        <v>0.345</v>
+        <v>0.34</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="O56" t="n">
-        <v>-2.82</v>
+        <v>-1.45</v>
       </c>
       <c r="P56" t="n">
-        <v>0.345</v>
+        <v>0.34</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="R56" t="n">
-        <v>-2.82</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.55</v>
+        <v>3.48</v>
       </c>
       <c r="E57" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>0.57</v>
+        <v>-1.97</v>
       </c>
       <c r="G57" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="J57" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="L57" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M57" t="n">
         <v>3.48</v>
       </c>
-      <c r="H57" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="I57" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="K57" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="L57" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="M57" t="n">
-        <v>3.51</v>
-      </c>
       <c r="N57" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="O57" t="n">
-        <v>1.45</v>
+        <v>-0.85</v>
       </c>
       <c r="P57" t="n">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="R57" t="n">
-        <v>1.45</v>
+        <v>-0.85</v>
       </c>
     </row>
     <row r="58">
@@ -4005,31 +4005,31 @@
         <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0.078</v>
+        <v>0.077</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>-1.28</v>
       </c>
       <c r="M58" t="n">
         <v>0.077</v>
       </c>
       <c r="N58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>-1.28</v>
+        <v>0</v>
       </c>
       <c r="P58" t="n">
         <v>0.077</v>
       </c>
       <c r="Q58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>-1.28</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>20.73</v>
+        <v>21.35</v>
       </c>
       <c r="E59" t="n">
-        <v>0.09</v>
+        <v>0.62</v>
       </c>
       <c r="F59" t="n">
-        <v>0.44</v>
+        <v>2.99</v>
       </c>
       <c r="G59" t="n">
-        <v>21.35</v>
+        <v>21.14</v>
       </c>
       <c r="H59" t="n">
-        <v>0.62</v>
+        <v>-0.21</v>
       </c>
       <c r="I59" t="n">
-        <v>2.99</v>
+        <v>-0.98</v>
       </c>
       <c r="J59" t="n">
-        <v>21.14</v>
+        <v>20.96</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.21</v>
+        <v>-0.18</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.98</v>
+        <v>-0.85</v>
       </c>
       <c r="M59" t="n">
-        <v>20.96</v>
+        <v>20.89</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.18</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.85</v>
+        <v>-0.33</v>
       </c>
       <c r="P59" t="n">
-        <v>20.96</v>
+        <v>20.89</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.18</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R59" t="n">
-        <v>-0.85</v>
+        <v>-0.33</v>
       </c>
     </row>
     <row r="60">
@@ -4114,46 +4114,46 @@
         <v>3.1</v>
       </c>
       <c r="E60" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>-1.94</v>
       </c>
       <c r="J60" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="L60" t="n">
-        <v>-1.94</v>
+        <v>-2.63</v>
       </c>
       <c r="M60" t="n">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="N60" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="O60" t="n">
-        <v>-2.63</v>
+        <v>-3.04</v>
       </c>
       <c r="P60" t="n">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="R60" t="n">
-        <v>-2.63</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="61">
@@ -4176,46 +4176,46 @@
         <v>0.835</v>
       </c>
       <c r="E61" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.835</v>
+        <v>0.795</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>-4.79</v>
       </c>
       <c r="J61" t="n">
         <v>0.795</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="L61" t="n">
-        <v>-4.79</v>
+        <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>0.795</v>
+        <v>0.77</v>
       </c>
       <c r="N61" t="n">
-        <v>0</v>
+        <v>-0.025</v>
       </c>
       <c r="O61" t="n">
-        <v>0</v>
+        <v>-3.14</v>
       </c>
       <c r="P61" t="n">
-        <v>0.795</v>
+        <v>0.77</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>-0.025</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>-3.14</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-10-12 Close</t>
+          <t>2026-10-13 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-10-12 Change</t>
+          <t>2026-10-13 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-10-12 Change %</t>
+          <t>2026-10-13 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-10-13 Close</t>
+          <t>2026-10-14 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-10-13 Change</t>
+          <t>2026-10-14 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-10-13 Change %</t>
+          <t>2026-10-14 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-10-14 Close</t>
+          <t>2026-10-15 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-10-14 Change</t>
+          <t>2026-10-15 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-10-14 Change %</t>
+          <t>2026-10-15 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-10-15 Close</t>
+          <t>2026-10-16 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-10-15 Change</t>
+          <t>2026-10-16 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-10-15 Change %</t>
+          <t>2026-10-16 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-10-16 Close</t>
+          <t>2026-10-19 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-10-16 Change</t>
+          <t>2026-10-19 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-10-16 Change %</t>
+          <t>2026-10-19 Change %</t>
         </is>
       </c>
     </row>
@@ -577,49 +577,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>148.1</v>
+        <v>150.7</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="F3" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="G3" t="n">
-        <v>150.7</v>
+        <v>148</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6</v>
+        <v>-2.7</v>
       </c>
       <c r="I3" t="n">
-        <v>1.76</v>
+        <v>-1.79</v>
       </c>
       <c r="J3" t="n">
-        <v>148</v>
+        <v>147.9</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.7</v>
+        <v>-0.1</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.79</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>147.9</v>
+        <v>149.7</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1</v>
+        <v>1.8</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="P3" t="n">
-        <v>147.9</v>
+        <v>149.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="4">
@@ -639,49 +639,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>224.4</v>
+        <v>229.8</v>
       </c>
       <c r="E4" t="n">
-        <v>3.4</v>
+        <v>5.4</v>
       </c>
       <c r="F4" t="n">
-        <v>1.54</v>
+        <v>2.41</v>
       </c>
       <c r="G4" t="n">
-        <v>229.8</v>
+        <v>221.8</v>
       </c>
       <c r="H4" t="n">
-        <v>5.4</v>
+        <v>-8</v>
       </c>
       <c r="I4" t="n">
-        <v>2.41</v>
+        <v>-3.48</v>
       </c>
       <c r="J4" t="n">
-        <v>221.8</v>
+        <v>221</v>
       </c>
       <c r="K4" t="n">
-        <v>-8</v>
+        <v>-0.8</v>
       </c>
       <c r="L4" t="n">
-        <v>-3.48</v>
+        <v>-0.36</v>
       </c>
       <c r="M4" t="n">
-        <v>221</v>
+        <v>223.6</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.8</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.36</v>
+        <v>1.18</v>
       </c>
       <c r="P4" t="n">
-        <v>221</v>
+        <v>223.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.8</v>
+        <v>2.6</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.36</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="5">
@@ -701,49 +701,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.66</v>
+        <v>6.72</v>
       </c>
       <c r="E5" t="n">
-        <v>0.17</v>
+        <v>0.06</v>
       </c>
       <c r="F5" t="n">
-        <v>2.62</v>
+        <v>0.9</v>
       </c>
       <c r="G5" t="n">
-        <v>6.72</v>
+        <v>6.57</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06</v>
+        <v>-0.15</v>
       </c>
       <c r="I5" t="n">
-        <v>0.9</v>
+        <v>-2.23</v>
       </c>
       <c r="J5" t="n">
-        <v>6.57</v>
+        <v>6.8</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.15</v>
+        <v>0.23</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.23</v>
+        <v>3.5</v>
       </c>
       <c r="M5" t="n">
-        <v>6.8</v>
+        <v>6.74</v>
       </c>
       <c r="N5" t="n">
-        <v>0.23</v>
+        <v>-0.06</v>
       </c>
       <c r="O5" t="n">
-        <v>3.5</v>
+        <v>-0.88</v>
       </c>
       <c r="P5" t="n">
-        <v>6.8</v>
+        <v>6.74</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.23</v>
+        <v>-0.06</v>
       </c>
       <c r="R5" t="n">
-        <v>3.5</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="6">
@@ -763,49 +763,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.62</v>
+        <v>7.64</v>
       </c>
       <c r="E6" t="n">
-        <v>0.12</v>
+        <v>0.02</v>
       </c>
       <c r="F6" t="n">
-        <v>1.6</v>
+        <v>0.26</v>
       </c>
       <c r="G6" t="n">
-        <v>7.64</v>
+        <v>7.57</v>
       </c>
       <c r="H6" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.26</v>
+        <v>-0.92</v>
       </c>
       <c r="J6" t="n">
-        <v>7.57</v>
+        <v>7.7</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.92</v>
+        <v>1.72</v>
       </c>
       <c r="M6" t="n">
-        <v>7.7</v>
+        <v>7.59</v>
       </c>
       <c r="N6" t="n">
-        <v>0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="O6" t="n">
-        <v>1.72</v>
+        <v>-1.43</v>
       </c>
       <c r="P6" t="n">
-        <v>7.7</v>
+        <v>7.59</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="R6" t="n">
-        <v>1.72</v>
+        <v>-1.43</v>
       </c>
     </row>
     <row r="7">
@@ -825,49 +825,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.25</v>
+        <v>6.26</v>
       </c>
       <c r="E7" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="F7" t="n">
-        <v>2.12</v>
+        <v>0.16</v>
       </c>
       <c r="G7" t="n">
-        <v>6.26</v>
+        <v>6.2</v>
       </c>
       <c r="H7" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="I7" t="n">
-        <v>0.16</v>
+        <v>-0.96</v>
       </c>
       <c r="J7" t="n">
-        <v>6.2</v>
+        <v>6.16</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.96</v>
+        <v>-0.65</v>
       </c>
       <c r="M7" t="n">
-        <v>6.16</v>
+        <v>6.14</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.65</v>
+        <v>-0.32</v>
       </c>
       <c r="P7" t="n">
-        <v>6.16</v>
+        <v>6.14</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.65</v>
+        <v>-0.32</v>
       </c>
     </row>
     <row r="8">
@@ -887,49 +887,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.91</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.18</v>
+        <v>0.05</v>
       </c>
       <c r="F8" t="n">
-        <v>1.85</v>
+        <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>9.960000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5</v>
+        <v>-1.1</v>
       </c>
       <c r="J8" t="n">
-        <v>9.85</v>
+        <v>9.98</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.11</v>
+        <v>0.13</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.1</v>
+        <v>1.32</v>
       </c>
       <c r="M8" t="n">
-        <v>9.98</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="O8" t="n">
-        <v>1.32</v>
+        <v>-1.2</v>
       </c>
       <c r="P8" t="n">
-        <v>9.98</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="R8" t="n">
-        <v>1.32</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="9">
@@ -949,49 +949,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.59</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2</v>
+        <v>0.04</v>
       </c>
       <c r="F9" t="n">
-        <v>2.38</v>
+        <v>0.47</v>
       </c>
       <c r="G9" t="n">
-        <v>8.630000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>0.47</v>
+        <v>-0.12</v>
       </c>
       <c r="J9" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>8.619999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-1.62</v>
       </c>
       <c r="P9" t="n">
-        <v>8.619999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-1.62</v>
       </c>
     </row>
     <row r="10">
@@ -1011,49 +1011,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>53.8</v>
+        <v>53.9</v>
       </c>
       <c r="E10" t="n">
-        <v>1.6</v>
+        <v>0.1</v>
       </c>
       <c r="F10" t="n">
-        <v>3.07</v>
+        <v>0.19</v>
       </c>
       <c r="G10" t="n">
-        <v>53.9</v>
+        <v>53.55</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1</v>
+        <v>-0.35</v>
       </c>
       <c r="I10" t="n">
-        <v>0.19</v>
+        <v>-0.65</v>
       </c>
       <c r="J10" t="n">
-        <v>53.55</v>
+        <v>53.95</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.35</v>
+        <v>0.4</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.65</v>
+        <v>0.75</v>
       </c>
       <c r="M10" t="n">
-        <v>53.95</v>
+        <v>53.25</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="O10" t="n">
-        <v>0.75</v>
+        <v>-1.3</v>
       </c>
       <c r="P10" t="n">
-        <v>53.95</v>
+        <v>53.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="R10" t="n">
-        <v>0.75</v>
+        <v>-1.3</v>
       </c>
     </row>
     <row r="11">
@@ -1073,49 +1073,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.51</v>
+        <v>4.53</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.44</v>
+        <v>0.44</v>
       </c>
       <c r="G11" t="n">
-        <v>4.53</v>
+        <v>4.59</v>
       </c>
       <c r="H11" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="I11" t="n">
-        <v>0.44</v>
+        <v>1.32</v>
       </c>
       <c r="J11" t="n">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="L11" t="n">
-        <v>1.32</v>
+        <v>-1.96</v>
       </c>
       <c r="M11" t="n">
         <v>4.5</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.96</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>4.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-1.96</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1135,49 +1135,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>9.85</v>
+        <v>10.22</v>
       </c>
       <c r="E12" t="n">
-        <v>0.02</v>
+        <v>0.37</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2</v>
+        <v>3.76</v>
       </c>
       <c r="G12" t="n">
-        <v>10.22</v>
+        <v>10.34</v>
       </c>
       <c r="H12" t="n">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
       <c r="I12" t="n">
-        <v>3.76</v>
+        <v>1.17</v>
       </c>
       <c r="J12" t="n">
-        <v>10.34</v>
+        <v>10.08</v>
       </c>
       <c r="K12" t="n">
-        <v>0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="L12" t="n">
-        <v>1.17</v>
+        <v>-2.51</v>
       </c>
       <c r="M12" t="n">
-        <v>10.08</v>
+        <v>9.99</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.51</v>
+        <v>-0.89</v>
       </c>
       <c r="P12" t="n">
-        <v>10.08</v>
+        <v>9.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="R12" t="n">
-        <v>-2.51</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="13">
@@ -1197,49 +1197,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24.14</v>
+        <v>24.28</v>
       </c>
       <c r="E13" t="n">
-        <v>0.24</v>
+        <v>0.14</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
+        <v>0.58</v>
       </c>
       <c r="G13" t="n">
-        <v>24.28</v>
+        <v>24.72</v>
       </c>
       <c r="H13" t="n">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="I13" t="n">
-        <v>0.58</v>
+        <v>1.81</v>
       </c>
       <c r="J13" t="n">
-        <v>24.72</v>
+        <v>24.2</v>
       </c>
       <c r="K13" t="n">
-        <v>0.44</v>
+        <v>-0.52</v>
       </c>
       <c r="L13" t="n">
-        <v>1.81</v>
+        <v>-2.1</v>
       </c>
       <c r="M13" t="n">
-        <v>24.2</v>
+        <v>23.96</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.52</v>
+        <v>-0.24</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.1</v>
+        <v>-0.99</v>
       </c>
       <c r="P13" t="n">
-        <v>24.2</v>
+        <v>23.96</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.52</v>
+        <v>-0.24</v>
       </c>
       <c r="R13" t="n">
-        <v>-2.1</v>
+        <v>-0.99</v>
       </c>
     </row>
     <row r="14">
@@ -1259,7 +1259,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="E14" t="n">
         <v>-0.01</v>
@@ -1268,40 +1268,40 @@
         <v>-0.53</v>
       </c>
       <c r="G14" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.53</v>
+        <v>-1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.6</v>
+        <v>-2.16</v>
       </c>
       <c r="M14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.16</v>
+        <v>1.1</v>
       </c>
       <c r="P14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
       <c r="R14" t="n">
-        <v>-2.16</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="15">
@@ -1321,49 +1321,49 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.36</v>
+        <v>5.41</v>
       </c>
       <c r="E15" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="F15" t="n">
-        <v>0.37</v>
+        <v>0.93</v>
       </c>
       <c r="G15" t="n">
-        <v>5.41</v>
+        <v>5.45</v>
       </c>
       <c r="H15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="I15" t="n">
-        <v>0.93</v>
+        <v>0.74</v>
       </c>
       <c r="J15" t="n">
-        <v>5.45</v>
+        <v>5.39</v>
       </c>
       <c r="K15" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="L15" t="n">
-        <v>0.74</v>
+        <v>-1.1</v>
       </c>
       <c r="M15" t="n">
-        <v>5.39</v>
+        <v>5.42</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P15" t="n">
-        <v>5.39</v>
+        <v>5.42</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="R15" t="n">
-        <v>-1.1</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1386,46 +1386,46 @@
         <v>4.39</v>
       </c>
       <c r="E16" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>4.39</v>
+        <v>4.41</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="J16" t="n">
-        <v>4.41</v>
+        <v>4.34</v>
       </c>
       <c r="K16" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="L16" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="M16" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="N16" t="n">
         <v>0.02</v>
       </c>
-      <c r="L16" t="n">
+      <c r="O16" t="n">
         <v>0.46</v>
       </c>
-      <c r="M16" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-1.59</v>
-      </c>
       <c r="P16" t="n">
-        <v>4.34</v>
+        <v>4.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="R16" t="n">
-        <v>-1.59</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.22</v>
+        <v>3.27</v>
       </c>
       <c r="E17" t="n">
-        <v>0.01</v>
+        <v>0.05</v>
       </c>
       <c r="F17" t="n">
-        <v>0.31</v>
+        <v>1.55</v>
       </c>
       <c r="G17" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="H17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="I17" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="J17" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="K17" t="n">
-        <v>0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="L17" t="n">
-        <v>1.83</v>
+        <v>-3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="O17" t="n">
-        <v>-3</v>
+        <v>0.93</v>
       </c>
       <c r="P17" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="R17" t="n">
-        <v>-3</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="18">
@@ -1507,49 +1507,49 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.06</v>
+        <v>3.17</v>
       </c>
       <c r="E18" t="n">
-        <v>0.04</v>
+        <v>0.11</v>
       </c>
       <c r="F18" t="n">
-        <v>1.32</v>
+        <v>3.59</v>
       </c>
       <c r="G18" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="H18" t="n">
-        <v>0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="I18" t="n">
-        <v>3.59</v>
+        <v>-2.84</v>
       </c>
       <c r="J18" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.84</v>
+        <v>-2.27</v>
       </c>
       <c r="M18" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.27</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="R18" t="n">
-        <v>-2.27</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1569,49 +1569,49 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>51.65</v>
+        <v>51.35</v>
       </c>
       <c r="E19" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="G19" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="H19" t="n">
+        <v>-0.75</v>
+      </c>
+      <c r="I19" t="n">
+        <v>-1.46</v>
+      </c>
+      <c r="J19" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="K19" t="n">
         <v>-0.2</v>
       </c>
-      <c r="F19" t="n">
-        <v>-0.39</v>
-      </c>
-      <c r="G19" t="n">
-        <v>51.35</v>
-      </c>
-      <c r="H19" t="n">
-        <v>-0.3</v>
-      </c>
-      <c r="I19" t="n">
-        <v>-0.58</v>
-      </c>
-      <c r="J19" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-0.75</v>
-      </c>
       <c r="L19" t="n">
-        <v>-1.46</v>
+        <v>-0.4</v>
       </c>
       <c r="M19" t="n">
-        <v>50.4</v>
+        <v>50.05</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2</v>
+        <v>-0.35</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>50.4</v>
+        <v>50.05</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.2</v>
+        <v>-0.35</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.4</v>
+        <v>-0.6899999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1631,49 +1631,49 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>26.26</v>
+        <v>25.62</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1</v>
+        <v>-0.64</v>
       </c>
       <c r="F20" t="n">
-        <v>0.38</v>
+        <v>-2.44</v>
       </c>
       <c r="G20" t="n">
-        <v>25.62</v>
+        <v>24.94</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.64</v>
+        <v>-0.68</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.44</v>
+        <v>-2.65</v>
       </c>
       <c r="J20" t="n">
-        <v>24.94</v>
+        <v>24.32</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.68</v>
+        <v>-0.62</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.65</v>
+        <v>-2.49</v>
       </c>
       <c r="M20" t="n">
-        <v>24.32</v>
+        <v>23.62</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.62</v>
+        <v>-0.7</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.49</v>
+        <v>-2.88</v>
       </c>
       <c r="P20" t="n">
-        <v>24.32</v>
+        <v>23.62</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.62</v>
+        <v>-0.7</v>
       </c>
       <c r="R20" t="n">
-        <v>-2.49</v>
+        <v>-2.88</v>
       </c>
     </row>
     <row r="21">
@@ -1693,49 +1693,49 @@
         </is>
       </c>
       <c r="D21" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G21" t="n">
+        <v>4.74</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.72</v>
+      </c>
+      <c r="K21" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="M21" t="n">
         <v>4.66</v>
       </c>
-      <c r="E21" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-0.43</v>
-      </c>
-      <c r="G21" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="J21" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="L21" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="M21" t="n">
-        <v>4.72</v>
-      </c>
       <c r="N21" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.42</v>
+        <v>-1.27</v>
       </c>
       <c r="P21" t="n">
-        <v>4.72</v>
+        <v>4.66</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="R21" t="n">
-        <v>-0.42</v>
+        <v>-1.27</v>
       </c>
     </row>
     <row r="22">
@@ -1755,49 +1755,49 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>79.95</v>
+        <v>80.45</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.15</v>
+        <v>0.5</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.19</v>
+        <v>0.63</v>
       </c>
       <c r="G22" t="n">
-        <v>80.45</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="I22" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="K22" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="M22" t="n">
-        <v>81</v>
+        <v>80.95</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="O22" t="n">
-        <v>0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="P22" t="n">
-        <v>81</v>
+        <v>80.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="R22" t="n">
-        <v>0.12</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="23">
@@ -1817,49 +1817,49 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20.36</v>
+        <v>20.12</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4</v>
+        <v>-0.24</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.93</v>
+        <v>-1.18</v>
       </c>
       <c r="G23" t="n">
-        <v>20.12</v>
+        <v>20.06</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.24</v>
+        <v>-0.06</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.18</v>
+        <v>-0.3</v>
       </c>
       <c r="J23" t="n">
-        <v>20.06</v>
+        <v>19.29</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.06</v>
+        <v>-0.77</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.3</v>
+        <v>-3.84</v>
       </c>
       <c r="M23" t="n">
-        <v>19.29</v>
+        <v>19.47</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.77</v>
+        <v>0.18</v>
       </c>
       <c r="O23" t="n">
-        <v>-3.84</v>
+        <v>0.93</v>
       </c>
       <c r="P23" t="n">
-        <v>19.29</v>
+        <v>19.47</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.77</v>
+        <v>0.18</v>
       </c>
       <c r="R23" t="n">
-        <v>-3.84</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="24">
@@ -1879,49 +1879,49 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.48</v>
+        <v>12.89</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.38</v>
+        <v>-0.59</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.74</v>
+        <v>-4.38</v>
       </c>
       <c r="G24" t="n">
-        <v>12.89</v>
+        <v>13.05</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.59</v>
+        <v>0.16</v>
       </c>
       <c r="I24" t="n">
-        <v>-4.38</v>
+        <v>1.24</v>
       </c>
       <c r="J24" t="n">
-        <v>13.05</v>
+        <v>12.27</v>
       </c>
       <c r="K24" t="n">
-        <v>0.16</v>
+        <v>-0.78</v>
       </c>
       <c r="L24" t="n">
-        <v>1.24</v>
+        <v>-5.98</v>
       </c>
       <c r="M24" t="n">
-        <v>12.27</v>
+        <v>12.4</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.78</v>
+        <v>0.13</v>
       </c>
       <c r="O24" t="n">
-        <v>-5.98</v>
+        <v>1.06</v>
       </c>
       <c r="P24" t="n">
-        <v>12.27</v>
+        <v>12.4</v>
       </c>
       <c r="Q24" t="n">
-        <v>-0.78</v>
+        <v>0.13</v>
       </c>
       <c r="R24" t="n">
-        <v>-5.98</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="25">
@@ -1941,49 +1941,49 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>24.52</v>
+        <v>25.04</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.44</v>
+        <v>0.52</v>
       </c>
       <c r="F25" t="n">
-        <v>-5.55</v>
+        <v>2.12</v>
       </c>
       <c r="G25" t="n">
-        <v>25.04</v>
+        <v>26.38</v>
       </c>
       <c r="H25" t="n">
-        <v>0.52</v>
+        <v>1.34</v>
       </c>
       <c r="I25" t="n">
-        <v>2.12</v>
+        <v>5.35</v>
       </c>
       <c r="J25" t="n">
-        <v>26.38</v>
+        <v>27.08</v>
       </c>
       <c r="K25" t="n">
-        <v>1.34</v>
+        <v>0.7</v>
       </c>
       <c r="L25" t="n">
-        <v>5.35</v>
+        <v>2.65</v>
       </c>
       <c r="M25" t="n">
-        <v>27.08</v>
+        <v>26.66</v>
       </c>
       <c r="N25" t="n">
-        <v>0.7</v>
+        <v>-0.42</v>
       </c>
       <c r="O25" t="n">
-        <v>2.65</v>
+        <v>-1.55</v>
       </c>
       <c r="P25" t="n">
-        <v>27.08</v>
+        <v>26.66</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.7</v>
+        <v>-0.42</v>
       </c>
       <c r="R25" t="n">
-        <v>2.65</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="26">
@@ -2003,49 +2003,49 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>29.9</v>
+        <v>28.24</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.1</v>
+        <v>-1.66</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.55</v>
+        <v>-5.55</v>
       </c>
       <c r="G26" t="n">
-        <v>28.24</v>
+        <v>28.34</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.66</v>
+        <v>0.1</v>
       </c>
       <c r="I26" t="n">
-        <v>-5.55</v>
+        <v>0.35</v>
       </c>
       <c r="J26" t="n">
-        <v>28.34</v>
+        <v>24.98</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1</v>
+        <v>-3.36</v>
       </c>
       <c r="L26" t="n">
-        <v>0.35</v>
+        <v>-11.86</v>
       </c>
       <c r="M26" t="n">
-        <v>24.98</v>
+        <v>25.12</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.36</v>
+        <v>0.14</v>
       </c>
       <c r="O26" t="n">
-        <v>-11.86</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>24.98</v>
+        <v>25.12</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3.36</v>
+        <v>0.14</v>
       </c>
       <c r="R26" t="n">
-        <v>-11.86</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -2065,49 +2065,49 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>425.8</v>
+        <v>425.2</v>
       </c>
       <c r="E27" t="n">
-        <v>1</v>
+        <v>-0.6</v>
       </c>
       <c r="F27" t="n">
-        <v>0.24</v>
+        <v>-0.14</v>
       </c>
       <c r="G27" t="n">
-        <v>425.2</v>
+        <v>423.4</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.14</v>
+        <v>-0.42</v>
       </c>
       <c r="J27" t="n">
-        <v>423.4</v>
+        <v>417.8</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.8</v>
+        <v>-5.6</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.42</v>
+        <v>-1.32</v>
       </c>
       <c r="M27" t="n">
         <v>417.8</v>
       </c>
       <c r="N27" t="n">
-        <v>-5.6</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.32</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
         <v>417.8</v>
       </c>
       <c r="Q27" t="n">
-        <v>-5.6</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>-1.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2127,49 +2127,49 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>108.2</v>
+        <v>107.2</v>
       </c>
       <c r="E28" t="n">
-        <v>1.2</v>
+        <v>-1</v>
       </c>
       <c r="F28" t="n">
-        <v>1.12</v>
+        <v>-0.92</v>
       </c>
       <c r="G28" t="n">
-        <v>107.2</v>
+        <v>110.5</v>
       </c>
       <c r="H28" t="n">
-        <v>-1</v>
+        <v>3.3</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.92</v>
+        <v>3.08</v>
       </c>
       <c r="J28" t="n">
-        <v>110.5</v>
+        <v>106.4</v>
       </c>
       <c r="K28" t="n">
-        <v>3.3</v>
+        <v>-4.1</v>
       </c>
       <c r="L28" t="n">
-        <v>3.08</v>
+        <v>-3.71</v>
       </c>
       <c r="M28" t="n">
-        <v>106.4</v>
+        <v>108.8</v>
       </c>
       <c r="N28" t="n">
-        <v>-4.1</v>
+        <v>2.4</v>
       </c>
       <c r="O28" t="n">
-        <v>-3.71</v>
+        <v>2.26</v>
       </c>
       <c r="P28" t="n">
-        <v>106.4</v>
+        <v>108.8</v>
       </c>
       <c r="Q28" t="n">
-        <v>-4.1</v>
+        <v>2.4</v>
       </c>
       <c r="R28" t="n">
-        <v>-3.71</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="29">
@@ -2189,49 +2189,49 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>108.5</v>
+        <v>104.9</v>
       </c>
       <c r="E29" t="n">
-        <v>2.9</v>
+        <v>-3.6</v>
       </c>
       <c r="F29" t="n">
-        <v>2.75</v>
+        <v>-3.32</v>
       </c>
       <c r="G29" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J29" t="n">
         <v>104.9</v>
       </c>
-      <c r="H29" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-3.32</v>
-      </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="M29" t="n">
         <v>106.1</v>
       </c>
-      <c r="K29" t="n">
+      <c r="N29" t="n">
         <v>1.2</v>
       </c>
-      <c r="L29" t="n">
+      <c r="O29" t="n">
         <v>1.14</v>
       </c>
-      <c r="M29" t="n">
-        <v>104.9</v>
-      </c>
-      <c r="N29" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="O29" t="n">
-        <v>-1.13</v>
-      </c>
       <c r="P29" t="n">
-        <v>104.9</v>
+        <v>106.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1.2</v>
+        <v>1.2</v>
       </c>
       <c r="R29" t="n">
-        <v>-1.13</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="30">
@@ -2251,49 +2251,49 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>71.8</v>
+        <v>72.3</v>
       </c>
       <c r="E30" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="F30" t="n">
-        <v>0.42</v>
+        <v>0.7</v>
       </c>
       <c r="G30" t="n">
-        <v>72.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="I30" t="n">
-        <v>0.7</v>
+        <v>6.64</v>
       </c>
       <c r="J30" t="n">
-        <v>77.09999999999999</v>
+        <v>75.45</v>
       </c>
       <c r="K30" t="n">
-        <v>4.8</v>
+        <v>-1.65</v>
       </c>
       <c r="L30" t="n">
-        <v>6.64</v>
+        <v>-2.14</v>
       </c>
       <c r="M30" t="n">
-        <v>75.45</v>
+        <v>75.7</v>
       </c>
       <c r="N30" t="n">
-        <v>-1.65</v>
+        <v>0.25</v>
       </c>
       <c r="O30" t="n">
-        <v>-2.14</v>
+        <v>0.33</v>
       </c>
       <c r="P30" t="n">
-        <v>75.45</v>
+        <v>75.7</v>
       </c>
       <c r="Q30" t="n">
-        <v>-1.65</v>
+        <v>0.25</v>
       </c>
       <c r="R30" t="n">
-        <v>-2.14</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="31">
@@ -2313,49 +2313,49 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>81.8</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>-1.2</v>
+        <v>-0.15</v>
       </c>
       <c r="F31" t="n">
-        <v>-1.45</v>
+        <v>-0.18</v>
       </c>
       <c r="G31" t="n">
-        <v>81.65000000000001</v>
+        <v>82.05</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.15</v>
+        <v>0.4</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.18</v>
+        <v>0.49</v>
       </c>
       <c r="J31" t="n">
-        <v>82.05</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>0.4</v>
+        <v>-3.7</v>
       </c>
       <c r="L31" t="n">
-        <v>0.49</v>
+        <v>-4.51</v>
       </c>
       <c r="M31" t="n">
-        <v>78.34999999999999</v>
+        <v>79.45</v>
       </c>
       <c r="N31" t="n">
-        <v>-3.7</v>
+        <v>1.1</v>
       </c>
       <c r="O31" t="n">
-        <v>-4.51</v>
+        <v>1.4</v>
       </c>
       <c r="P31" t="n">
-        <v>78.34999999999999</v>
+        <v>79.45</v>
       </c>
       <c r="Q31" t="n">
-        <v>-3.7</v>
+        <v>1.1</v>
       </c>
       <c r="R31" t="n">
-        <v>-4.51</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="32">
@@ -2375,49 +2375,49 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>56.2</v>
+        <v>55.55</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.45</v>
+        <v>-0.65</v>
       </c>
       <c r="F32" t="n">
-        <v>-2.52</v>
+        <v>-1.16</v>
       </c>
       <c r="G32" t="n">
-        <v>55.55</v>
+        <v>54.3</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.65</v>
+        <v>-1.25</v>
       </c>
       <c r="I32" t="n">
-        <v>-1.16</v>
+        <v>-2.25</v>
       </c>
       <c r="J32" t="n">
-        <v>54.3</v>
+        <v>52.15</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.25</v>
+        <v>-2.15</v>
       </c>
       <c r="L32" t="n">
-        <v>-2.25</v>
+        <v>-3.96</v>
       </c>
       <c r="M32" t="n">
-        <v>52.15</v>
+        <v>52.4</v>
       </c>
       <c r="N32" t="n">
-        <v>-2.15</v>
+        <v>0.25</v>
       </c>
       <c r="O32" t="n">
-        <v>-3.96</v>
+        <v>0.48</v>
       </c>
       <c r="P32" t="n">
-        <v>52.15</v>
+        <v>52.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>-2.15</v>
+        <v>0.25</v>
       </c>
       <c r="R32" t="n">
-        <v>-3.96</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="33">
@@ -2437,49 +2437,49 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>74.34999999999999</v>
+        <v>73.25</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.25</v>
+        <v>-1.1</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.65</v>
+        <v>-1.48</v>
       </c>
       <c r="G33" t="n">
-        <v>73.25</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.1</v>
+        <v>-0.4</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.48</v>
+        <v>-0.55</v>
       </c>
       <c r="J33" t="n">
-        <v>72.84999999999999</v>
+        <v>72.95</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.55</v>
+        <v>0.14</v>
       </c>
       <c r="M33" t="n">
-        <v>72.95</v>
+        <v>73.75</v>
       </c>
       <c r="N33" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="O33" t="n">
-        <v>0.14</v>
+        <v>1.1</v>
       </c>
       <c r="P33" t="n">
-        <v>72.95</v>
+        <v>73.75</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="R33" t="n">
-        <v>0.14</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="34">
@@ -2499,49 +2499,49 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>29.26</v>
+        <v>29.16</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.84</v>
+        <v>-0.1</v>
       </c>
       <c r="F34" t="n">
-        <v>-2.79</v>
+        <v>-0.34</v>
       </c>
       <c r="G34" t="n">
-        <v>29.16</v>
+        <v>29.52</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.1</v>
+        <v>0.36</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.34</v>
+        <v>1.23</v>
       </c>
       <c r="J34" t="n">
-        <v>29.52</v>
+        <v>28.58</v>
       </c>
       <c r="K34" t="n">
-        <v>0.36</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>1.23</v>
+        <v>-3.18</v>
       </c>
       <c r="M34" t="n">
-        <v>28.58</v>
+        <v>29.3</v>
       </c>
       <c r="N34" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="O34" t="n">
-        <v>-3.18</v>
+        <v>2.52</v>
       </c>
       <c r="P34" t="n">
-        <v>28.58</v>
+        <v>29.3</v>
       </c>
       <c r="Q34" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="R34" t="n">
-        <v>-3.18</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="35">
@@ -2561,49 +2561,49 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.08</v>
+        <v>4.05</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.49</v>
+        <v>-0.74</v>
       </c>
       <c r="G35" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.74</v>
+        <v>0.99</v>
       </c>
       <c r="J35" t="n">
-        <v>4.09</v>
+        <v>3.98</v>
       </c>
       <c r="K35" t="n">
-        <v>0.04</v>
+        <v>-0.11</v>
       </c>
       <c r="L35" t="n">
-        <v>0.99</v>
+        <v>-2.69</v>
       </c>
       <c r="M35" t="n">
-        <v>4.09</v>
+        <v>4.03</v>
       </c>
       <c r="N35" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="O35" t="n">
-        <v>0.99</v>
+        <v>1.26</v>
       </c>
       <c r="P35" t="n">
-        <v>4.09</v>
+        <v>4.03</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="R35" t="n">
-        <v>0.99</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="36">
@@ -2623,49 +2623,49 @@
         </is>
       </c>
       <c r="D36" t="n">
+        <v>8.74</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="F36" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="G36" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="E36" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="F36" t="n">
-        <v>-0.45</v>
-      </c>
-      <c r="G36" t="n">
-        <v>8.74</v>
-      </c>
       <c r="H36" t="n">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="K36" t="n">
-        <v>0.06</v>
+        <v>-0.23</v>
       </c>
       <c r="L36" t="n">
-        <v>0.6899999999999999</v>
+        <v>-2.61</v>
       </c>
       <c r="M36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="N36" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="O36" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.17</v>
       </c>
       <c r="P36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="R36" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="37">
@@ -2685,49 +2685,49 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>375.4</v>
+        <v>379.6</v>
       </c>
       <c r="E37" t="n">
-        <v>-2.4</v>
+        <v>4.2</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.64</v>
+        <v>1.12</v>
       </c>
       <c r="G37" t="n">
-        <v>379.6</v>
+        <v>373.6</v>
       </c>
       <c r="H37" t="n">
-        <v>4.2</v>
+        <v>-6</v>
       </c>
       <c r="I37" t="n">
-        <v>1.12</v>
+        <v>-1.58</v>
       </c>
       <c r="J37" t="n">
-        <v>373.6</v>
+        <v>371.4</v>
       </c>
       <c r="K37" t="n">
-        <v>-6</v>
+        <v>-2.2</v>
       </c>
       <c r="L37" t="n">
-        <v>-1.58</v>
+        <v>-0.59</v>
       </c>
       <c r="M37" t="n">
-        <v>371.4</v>
+        <v>374.6</v>
       </c>
       <c r="N37" t="n">
-        <v>-2.2</v>
+        <v>3.2</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.59</v>
+        <v>0.86</v>
       </c>
       <c r="P37" t="n">
-        <v>371.4</v>
+        <v>374.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>-2.2</v>
+        <v>3.2</v>
       </c>
       <c r="R37" t="n">
-        <v>-0.59</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="38">
@@ -2747,49 +2747,49 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.05</v>
+        <v>11.42</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.41</v>
+        <v>0.37</v>
       </c>
       <c r="F38" t="n">
-        <v>-3.58</v>
+        <v>3.35</v>
       </c>
       <c r="G38" t="n">
-        <v>11.42</v>
+        <v>11.29</v>
       </c>
       <c r="H38" t="n">
-        <v>0.37</v>
+        <v>-0.13</v>
       </c>
       <c r="I38" t="n">
-        <v>3.35</v>
+        <v>-1.14</v>
       </c>
       <c r="J38" t="n">
-        <v>11.29</v>
+        <v>11.3</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.13</v>
+        <v>0.01</v>
       </c>
       <c r="L38" t="n">
-        <v>-1.14</v>
+        <v>0.09</v>
       </c>
       <c r="M38" t="n">
-        <v>11.3</v>
+        <v>11.49</v>
       </c>
       <c r="N38" t="n">
-        <v>0.01</v>
+        <v>0.19</v>
       </c>
       <c r="O38" t="n">
-        <v>0.09</v>
+        <v>1.68</v>
       </c>
       <c r="P38" t="n">
-        <v>11.3</v>
+        <v>11.49</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.01</v>
+        <v>0.19</v>
       </c>
       <c r="R38" t="n">
-        <v>0.09</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="39">
@@ -2809,49 +2809,49 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>494.8</v>
+        <v>485.2</v>
       </c>
       <c r="E39" t="n">
-        <v>3.4</v>
+        <v>-9.6</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.94</v>
       </c>
       <c r="G39" t="n">
-        <v>485.2</v>
+        <v>467</v>
       </c>
       <c r="H39" t="n">
-        <v>-9.6</v>
+        <v>-18.2</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.94</v>
+        <v>-3.75</v>
       </c>
       <c r="J39" t="n">
-        <v>467</v>
+        <v>448.6</v>
       </c>
       <c r="K39" t="n">
-        <v>-18.2</v>
+        <v>-18.4</v>
       </c>
       <c r="L39" t="n">
-        <v>-3.75</v>
+        <v>-3.94</v>
       </c>
       <c r="M39" t="n">
-        <v>448.6</v>
+        <v>440.8</v>
       </c>
       <c r="N39" t="n">
-        <v>-18.4</v>
+        <v>-7.8</v>
       </c>
       <c r="O39" t="n">
-        <v>-3.94</v>
+        <v>-1.74</v>
       </c>
       <c r="P39" t="n">
-        <v>448.6</v>
+        <v>440.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>-18.4</v>
+        <v>-7.8</v>
       </c>
       <c r="R39" t="n">
-        <v>-3.94</v>
+        <v>-1.74</v>
       </c>
     </row>
     <row r="40">
@@ -2871,49 +2871,49 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>38.48</v>
+        <v>37.84</v>
       </c>
       <c r="E40" t="n">
-        <v>0.14</v>
+        <v>-0.64</v>
       </c>
       <c r="F40" t="n">
-        <v>0.37</v>
+        <v>-1.66</v>
       </c>
       <c r="G40" t="n">
-        <v>37.84</v>
+        <v>38.62</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.64</v>
+        <v>0.78</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.66</v>
+        <v>2.06</v>
       </c>
       <c r="J40" t="n">
-        <v>38.62</v>
+        <v>37.2</v>
       </c>
       <c r="K40" t="n">
-        <v>0.78</v>
+        <v>-1.42</v>
       </c>
       <c r="L40" t="n">
-        <v>2.06</v>
+        <v>-3.68</v>
       </c>
       <c r="M40" t="n">
-        <v>37.2</v>
+        <v>37.46</v>
       </c>
       <c r="N40" t="n">
-        <v>-1.42</v>
+        <v>0.26</v>
       </c>
       <c r="O40" t="n">
-        <v>-3.68</v>
+        <v>0.7</v>
       </c>
       <c r="P40" t="n">
-        <v>37.2</v>
+        <v>37.46</v>
       </c>
       <c r="Q40" t="n">
-        <v>-1.42</v>
+        <v>0.26</v>
       </c>
       <c r="R40" t="n">
-        <v>-3.68</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>29.06</v>
+        <v>29.2</v>
       </c>
       <c r="E41" t="n">
-        <v>0.06</v>
+        <v>0.14</v>
       </c>
       <c r="F41" t="n">
-        <v>0.21</v>
+        <v>0.48</v>
       </c>
       <c r="G41" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="H41" t="n">
-        <v>0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="I41" t="n">
-        <v>0.48</v>
+        <v>-0.68</v>
       </c>
       <c r="J41" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="K41" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="L41" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="M41" t="n">
         <v>29</v>
       </c>
-      <c r="K41" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="L41" t="n">
-        <v>-0.68</v>
-      </c>
-      <c r="M41" t="n">
-        <v>28.99</v>
-      </c>
       <c r="N41" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="P41" t="n">
-        <v>28.99</v>
+        <v>29</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>73.94</v>
+        <v>74.47</v>
       </c>
       <c r="E42" t="n">
-        <v>0.58</v>
+        <v>0.53</v>
       </c>
       <c r="F42" t="n">
-        <v>0.79</v>
+        <v>0.72</v>
       </c>
       <c r="G42" t="n">
-        <v>74.47</v>
+        <v>74.34</v>
       </c>
       <c r="H42" t="n">
-        <v>0.53</v>
+        <v>-0.13</v>
       </c>
       <c r="I42" t="n">
-        <v>0.72</v>
+        <v>-0.17</v>
       </c>
       <c r="J42" t="n">
-        <v>74.34</v>
+        <v>73.75</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.13</v>
+        <v>-0.59</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.17</v>
+        <v>-0.79</v>
       </c>
       <c r="M42" t="n">
-        <v>73.75</v>
+        <v>74.11</v>
       </c>
       <c r="N42" t="n">
-        <v>-0.59</v>
+        <v>0.36</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.79</v>
+        <v>0.49</v>
       </c>
       <c r="P42" t="n">
-        <v>73.75</v>
+        <v>74.11</v>
       </c>
       <c r="Q42" t="n">
-        <v>-0.59</v>
+        <v>0.36</v>
       </c>
       <c r="R42" t="n">
-        <v>-0.79</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>40.5</v>
+        <v>40.93</v>
       </c>
       <c r="E43" t="n">
-        <v>0.54</v>
+        <v>0.43</v>
       </c>
       <c r="F43" t="n">
-        <v>1.35</v>
+        <v>1.06</v>
       </c>
       <c r="G43" t="n">
-        <v>40.93</v>
+        <v>41.06</v>
       </c>
       <c r="H43" t="n">
-        <v>0.43</v>
+        <v>0.13</v>
       </c>
       <c r="I43" t="n">
-        <v>1.06</v>
+        <v>0.32</v>
       </c>
       <c r="J43" t="n">
-        <v>41.06</v>
+        <v>41.69</v>
       </c>
       <c r="K43" t="n">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
       <c r="L43" t="n">
-        <v>0.32</v>
+        <v>1.53</v>
       </c>
       <c r="M43" t="n">
-        <v>41.69</v>
+        <v>41.61</v>
       </c>
       <c r="N43" t="n">
-        <v>0.63</v>
+        <v>-0.08</v>
       </c>
       <c r="O43" t="n">
-        <v>1.53</v>
+        <v>-0.19</v>
       </c>
       <c r="P43" t="n">
-        <v>41.69</v>
+        <v>41.61</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.63</v>
+        <v>-0.08</v>
       </c>
       <c r="R43" t="n">
-        <v>1.53</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.01</v>
+        <v>6.08</v>
       </c>
       <c r="E44" t="n">
-        <v>0.11</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>1.86</v>
+        <v>1.16</v>
       </c>
       <c r="G44" t="n">
-        <v>6.08</v>
+        <v>6.04</v>
       </c>
       <c r="H44" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="I44" t="n">
-        <v>1.16</v>
+        <v>-0.66</v>
       </c>
       <c r="J44" t="n">
-        <v>6.04</v>
+        <v>5.92</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.66</v>
+        <v>-1.99</v>
       </c>
       <c r="M44" t="n">
         <v>5.92</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>-1.99</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>5.92</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>-1.99</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -3181,49 +3181,49 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.05</v>
+        <v>-0.01</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.5</v>
+        <v>-0.51</v>
       </c>
       <c r="G45" t="n">
         <v>1.94</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>-4.64</v>
       </c>
       <c r="M45" t="n">
         <v>1.85</v>
       </c>
       <c r="N45" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>-4.64</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
         <v>1.85</v>
       </c>
       <c r="Q45" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>-4.64</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.73</v>
+        <v>3.67</v>
       </c>
       <c r="E46" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>-1.61</v>
       </c>
       <c r="G46" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.61</v>
+        <v>-0.82</v>
       </c>
       <c r="J46" t="n">
-        <v>3.64</v>
+        <v>3.57</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.82</v>
+        <v>-1.92</v>
       </c>
       <c r="M46" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="N46" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="O46" t="n">
-        <v>-1.92</v>
+        <v>0.28</v>
       </c>
       <c r="P46" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="Q46" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="R46" t="n">
-        <v>-1.92</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>10.35</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.19</v>
+        <v>-0.48</v>
       </c>
       <c r="G47" t="n">
-        <v>10.35</v>
+        <v>10.41</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.48</v>
+        <v>0.58</v>
       </c>
       <c r="J47" t="n">
-        <v>10.41</v>
+        <v>10.25</v>
       </c>
       <c r="K47" t="n">
-        <v>0.06</v>
+        <v>-0.16</v>
       </c>
       <c r="L47" t="n">
-        <v>0.58</v>
+        <v>-1.54</v>
       </c>
       <c r="M47" t="n">
-        <v>10.25</v>
+        <v>10.39</v>
       </c>
       <c r="N47" t="n">
-        <v>-0.16</v>
+        <v>0.14</v>
       </c>
       <c r="O47" t="n">
-        <v>-1.54</v>
+        <v>1.37</v>
       </c>
       <c r="P47" t="n">
-        <v>10.25</v>
+        <v>10.39</v>
       </c>
       <c r="Q47" t="n">
-        <v>-0.16</v>
+        <v>0.14</v>
       </c>
       <c r="R47" t="n">
-        <v>-1.54</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="48">
@@ -3370,46 +3370,46 @@
         <v>0.285</v>
       </c>
       <c r="E48" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="I48" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="K48" t="n">
         <v>-0.005</v>
       </c>
-      <c r="F48" t="n">
+      <c r="L48" t="n">
         <v>-1.72</v>
       </c>
-      <c r="G48" t="n">
-        <v>0.285</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="K48" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="L48" t="n">
-        <v>1.75</v>
-      </c>
       <c r="M48" t="n">
-        <v>0.285</v>
+        <v>0.28</v>
       </c>
       <c r="N48" t="n">
         <v>-0.005</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.72</v>
+        <v>-1.75</v>
       </c>
       <c r="P48" t="n">
-        <v>0.285</v>
+        <v>0.28</v>
       </c>
       <c r="Q48" t="n">
         <v>-0.005</v>
       </c>
       <c r="R48" t="n">
-        <v>-1.72</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="49">
@@ -3429,34 +3429,34 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.2</v>
+        <v>4.16</v>
       </c>
       <c r="E49" t="n">
         <v>-0.04</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.95</v>
       </c>
       <c r="G49" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="I49" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="J49" t="n">
         <v>4.16</v>
       </c>
-      <c r="H49" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I49" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="J49" t="n">
-        <v>4.14</v>
-      </c>
       <c r="K49" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.48</v>
+        <v>0.48</v>
       </c>
       <c r="M49" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="N49" t="n">
         <v>0.02</v>
@@ -3465,7 +3465,7 @@
         <v>0.48</v>
       </c>
       <c r="P49" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="Q49" t="n">
         <v>0.02</v>
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>-0.9</v>
       </c>
       <c r="G50" t="n">
         <v>1.1</v>
       </c>
       <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K50" t="n">
         <v>-0.01</v>
       </c>
-      <c r="I50" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="J50" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>-0.91</v>
       </c>
       <c r="M50" t="n">
         <v>1.09</v>
       </c>
       <c r="N50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>-0.91</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
         <v>1.09</v>
       </c>
       <c r="Q50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>-0.91</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.09</v>
+        <v>5.06</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.2</v>
+        <v>-0.59</v>
       </c>
       <c r="G51" t="n">
-        <v>5.06</v>
+        <v>5.15</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.03</v>
+        <v>0.09</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.59</v>
+        <v>1.78</v>
       </c>
       <c r="J51" t="n">
-        <v>5.15</v>
+        <v>5.03</v>
       </c>
       <c r="K51" t="n">
-        <v>0.09</v>
+        <v>-0.12</v>
       </c>
       <c r="L51" t="n">
-        <v>1.78</v>
+        <v>-2.33</v>
       </c>
       <c r="M51" t="n">
-        <v>5.03</v>
+        <v>5.21</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.12</v>
+        <v>0.18</v>
       </c>
       <c r="O51" t="n">
-        <v>-2.33</v>
+        <v>3.58</v>
       </c>
       <c r="P51" t="n">
-        <v>5.03</v>
+        <v>5.21</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.12</v>
+        <v>0.18</v>
       </c>
       <c r="R51" t="n">
-        <v>-2.33</v>
+        <v>3.58</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.86</v>
+        <v>-0.1</v>
       </c>
       <c r="G52" t="n">
-        <v>10.42</v>
+        <v>10.36</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.1</v>
+        <v>-0.58</v>
       </c>
       <c r="J52" t="n">
-        <v>10.36</v>
+        <v>10.12</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.06</v>
+        <v>-0.24</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.58</v>
+        <v>-2.32</v>
       </c>
       <c r="M52" t="n">
-        <v>10.12</v>
+        <v>10.1</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.24</v>
+        <v>-0.02</v>
       </c>
       <c r="O52" t="n">
-        <v>-2.32</v>
+        <v>-0.2</v>
       </c>
       <c r="P52" t="n">
-        <v>10.12</v>
+        <v>10.1</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.24</v>
+        <v>-0.02</v>
       </c>
       <c r="R52" t="n">
-        <v>-2.32</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
+        <v>7.15</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="F53" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="G53" t="n">
         <v>7.05</v>
       </c>
-      <c r="E53" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-0.7</v>
-      </c>
-      <c r="G53" t="n">
-        <v>7.15</v>
-      </c>
       <c r="H53" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="I53" t="n">
-        <v>1.42</v>
+        <v>-1.4</v>
       </c>
       <c r="J53" t="n">
         <v>7.05</v>
       </c>
       <c r="K53" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>7.05</v>
+        <v>7.04</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="P53" t="n">
-        <v>7.05</v>
+        <v>7.04</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="54">
@@ -3757,31 +3757,31 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="K54" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
       <c r="M54" t="n">
         <v>0.425</v>
       </c>
       <c r="N54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>-1.16</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
         <v>0.425</v>
       </c>
       <c r="Q54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>-1.16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3801,31 +3801,31 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.61</v>
+        <v>0.605</v>
       </c>
       <c r="E55" t="n">
         <v>-0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.82</v>
       </c>
       <c r="G55" t="n">
-        <v>0.605</v>
+        <v>0.61</v>
       </c>
       <c r="H55" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.82</v>
+        <v>0.83</v>
       </c>
       <c r="J55" t="n">
         <v>0.61</v>
       </c>
       <c r="K55" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
         <v>0.61</v>
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.335</v>
+        <v>0.355</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="F56" t="n">
-        <v>-5.63</v>
+        <v>5.97</v>
       </c>
       <c r="G56" t="n">
-        <v>0.355</v>
+        <v>0.345</v>
       </c>
       <c r="H56" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="I56" t="n">
-        <v>5.97</v>
+        <v>-2.82</v>
       </c>
       <c r="J56" t="n">
-        <v>0.345</v>
+        <v>0.34</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="L56" t="n">
-        <v>-2.82</v>
+        <v>-1.45</v>
       </c>
       <c r="M56" t="n">
         <v>0.34</v>
       </c>
       <c r="N56" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>-1.45</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
         <v>0.34</v>
       </c>
       <c r="Q56" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>-1.45</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="G57" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J57" t="n">
         <v>3.48</v>
       </c>
-      <c r="E57" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-1.97</v>
-      </c>
-      <c r="G57" t="n">
-        <v>3.46</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-0.02</v>
-      </c>
-      <c r="I57" t="n">
-        <v>-0.57</v>
-      </c>
-      <c r="J57" t="n">
-        <v>3.51</v>
-      </c>
       <c r="K57" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="L57" t="n">
-        <v>1.45</v>
+        <v>-0.85</v>
       </c>
       <c r="M57" t="n">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="O57" t="n">
-        <v>-0.85</v>
+        <v>-1.15</v>
       </c>
       <c r="P57" t="n">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="R57" t="n">
-        <v>-0.85</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="58">
@@ -3996,40 +3996,40 @@
         <v>0</v>
       </c>
       <c r="G58" t="n">
-        <v>0.078</v>
+        <v>0.077</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>-1.28</v>
       </c>
       <c r="J58" t="n">
         <v>0.077</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>-1.28</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.077</v>
+        <v>0.078</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="O58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P58" t="n">
-        <v>0.077</v>
+        <v>0.078</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.35</v>
+        <v>21.14</v>
       </c>
       <c r="E59" t="n">
-        <v>0.62</v>
+        <v>-0.21</v>
       </c>
       <c r="F59" t="n">
-        <v>2.99</v>
+        <v>-0.98</v>
       </c>
       <c r="G59" t="n">
-        <v>21.14</v>
+        <v>20.96</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.21</v>
+        <v>-0.18</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.98</v>
+        <v>-0.85</v>
       </c>
       <c r="J59" t="n">
-        <v>20.96</v>
+        <v>20.89</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.18</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.85</v>
+        <v>-0.33</v>
       </c>
       <c r="M59" t="n">
-        <v>20.89</v>
+        <v>21</v>
       </c>
       <c r="N59" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="O59" t="n">
-        <v>-0.33</v>
+        <v>0.53</v>
       </c>
       <c r="P59" t="n">
-        <v>20.89</v>
+        <v>21</v>
       </c>
       <c r="Q59" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="R59" t="n">
-        <v>-0.33</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.1</v>
+        <v>3.04</v>
       </c>
       <c r="E60" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>-1.94</v>
       </c>
       <c r="G60" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="I60" t="n">
-        <v>-1.94</v>
+        <v>-2.63</v>
       </c>
       <c r="J60" t="n">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="L60" t="n">
-        <v>-2.63</v>
+        <v>-3.04</v>
       </c>
       <c r="M60" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="N60" t="n">
-        <v>-0.09</v>
+        <v>0.03</v>
       </c>
       <c r="O60" t="n">
-        <v>-3.04</v>
+        <v>1.05</v>
       </c>
       <c r="P60" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="Q60" t="n">
-        <v>-0.09</v>
+        <v>0.03</v>
       </c>
       <c r="R60" t="n">
-        <v>-3.04</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="61">
@@ -4173,49 +4173,49 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>0.835</v>
+        <v>0.795</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="F61" t="n">
-        <v>0</v>
+        <v>-4.79</v>
       </c>
       <c r="G61" t="n">
         <v>0.795</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>-4.79</v>
+        <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0.795</v>
+        <v>0.77</v>
       </c>
       <c r="K61" t="n">
-        <v>0</v>
+        <v>-0.025</v>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
+        <v>-3.14</v>
       </c>
       <c r="M61" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="N61" t="n">
-        <v>-0.025</v>
+        <v>0.02</v>
       </c>
       <c r="O61" t="n">
-        <v>-3.14</v>
+        <v>2.6</v>
       </c>
       <c r="P61" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="Q61" t="n">
-        <v>-0.025</v>
+        <v>0.02</v>
       </c>
       <c r="R61" t="n">
-        <v>-3.14</v>
+        <v>2.6</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-10-13 Close</t>
+          <t>2026-10-14 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-10-13 Change</t>
+          <t>2026-10-14 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-10-13 Change %</t>
+          <t>2026-10-14 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-10-14 Close</t>
+          <t>2026-10-15 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-10-14 Change</t>
+          <t>2026-10-15 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-10-14 Change %</t>
+          <t>2026-10-15 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-10-15 Close</t>
+          <t>2026-10-16 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-10-15 Change</t>
+          <t>2026-10-16 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-10-15 Change %</t>
+          <t>2026-10-16 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-10-16 Close</t>
+          <t>2026-10-19 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-10-16 Change</t>
+          <t>2026-10-19 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-10-16 Change %</t>
+          <t>2026-10-19 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-10-19 Close</t>
+          <t>2026-10-20 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-10-19 Change</t>
+          <t>2026-10-20 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-10-19 Change %</t>
+          <t>2026-10-20 Change %</t>
         </is>
       </c>
     </row>
@@ -577,31 +577,31 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>150.7</v>
+        <v>148</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6</v>
+        <v>-2.7</v>
       </c>
       <c r="F3" t="n">
-        <v>1.76</v>
+        <v>-1.79</v>
       </c>
       <c r="G3" t="n">
-        <v>148</v>
+        <v>147.9</v>
       </c>
       <c r="H3" t="n">
-        <v>-2.7</v>
+        <v>-0.1</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.79</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>147.9</v>
+        <v>149.7</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1</v>
+        <v>1.8</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="M3" t="n">
         <v>149.7</v>
@@ -639,31 +639,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>229.8</v>
+        <v>221.8</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4</v>
+        <v>-8</v>
       </c>
       <c r="F4" t="n">
-        <v>2.41</v>
+        <v>-3.48</v>
       </c>
       <c r="G4" t="n">
-        <v>221.8</v>
+        <v>221</v>
       </c>
       <c r="H4" t="n">
-        <v>-8</v>
+        <v>-0.8</v>
       </c>
       <c r="I4" t="n">
-        <v>-3.48</v>
+        <v>-0.36</v>
       </c>
       <c r="J4" t="n">
-        <v>221</v>
+        <v>223.6</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.8</v>
+        <v>2.6</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.36</v>
+        <v>1.18</v>
       </c>
       <c r="M4" t="n">
         <v>223.6</v>
@@ -701,31 +701,31 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.72</v>
+        <v>6.57</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06</v>
+        <v>-0.15</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9</v>
+        <v>-2.23</v>
       </c>
       <c r="G5" t="n">
-        <v>6.57</v>
+        <v>6.8</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.15</v>
+        <v>0.23</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.23</v>
+        <v>3.5</v>
       </c>
       <c r="J5" t="n">
-        <v>6.8</v>
+        <v>6.74</v>
       </c>
       <c r="K5" t="n">
-        <v>0.23</v>
+        <v>-0.06</v>
       </c>
       <c r="L5" t="n">
-        <v>3.5</v>
+        <v>-0.88</v>
       </c>
       <c r="M5" t="n">
         <v>6.74</v>
@@ -763,31 +763,31 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.64</v>
+        <v>7.57</v>
       </c>
       <c r="E6" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>0.26</v>
+        <v>-0.92</v>
       </c>
       <c r="G6" t="n">
-        <v>7.57</v>
+        <v>7.7</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.92</v>
+        <v>1.72</v>
       </c>
       <c r="J6" t="n">
-        <v>7.7</v>
+        <v>7.59</v>
       </c>
       <c r="K6" t="n">
-        <v>0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="L6" t="n">
-        <v>1.72</v>
+        <v>-1.43</v>
       </c>
       <c r="M6" t="n">
         <v>7.59</v>
@@ -825,31 +825,31 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.26</v>
+        <v>6.2</v>
       </c>
       <c r="E7" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="F7" t="n">
-        <v>0.16</v>
+        <v>-0.96</v>
       </c>
       <c r="G7" t="n">
-        <v>6.2</v>
+        <v>6.16</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.96</v>
+        <v>-0.65</v>
       </c>
       <c r="J7" t="n">
-        <v>6.16</v>
+        <v>6.14</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.65</v>
+        <v>-0.32</v>
       </c>
       <c r="M7" t="n">
         <v>6.14</v>
@@ -887,31 +887,31 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.960000000000001</v>
+        <v>9.85</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5</v>
+        <v>-1.1</v>
       </c>
       <c r="G8" t="n">
-        <v>9.85</v>
+        <v>9.98</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.11</v>
+        <v>0.13</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.1</v>
+        <v>1.32</v>
       </c>
       <c r="J8" t="n">
-        <v>9.98</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="L8" t="n">
-        <v>1.32</v>
+        <v>-1.2</v>
       </c>
       <c r="M8" t="n">
         <v>9.859999999999999</v>
@@ -949,31 +949,31 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>8.630000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="F9" t="n">
-        <v>0.47</v>
+        <v>-0.12</v>
       </c>
       <c r="G9" t="n">
         <v>8.619999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>8.619999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.62</v>
       </c>
       <c r="M9" t="n">
         <v>8.48</v>
@@ -1011,31 +1011,31 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>53.9</v>
+        <v>53.55</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1</v>
+        <v>-0.35</v>
       </c>
       <c r="F10" t="n">
-        <v>0.19</v>
+        <v>-0.65</v>
       </c>
       <c r="G10" t="n">
-        <v>53.55</v>
+        <v>53.95</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.35</v>
+        <v>0.4</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.65</v>
+        <v>0.75</v>
       </c>
       <c r="J10" t="n">
-        <v>53.95</v>
+        <v>53.25</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="L10" t="n">
-        <v>0.75</v>
+        <v>-1.3</v>
       </c>
       <c r="M10" t="n">
         <v>53.25</v>
@@ -1073,31 +1073,31 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.53</v>
+        <v>4.59</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="F11" t="n">
-        <v>0.44</v>
+        <v>1.32</v>
       </c>
       <c r="G11" t="n">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="I11" t="n">
-        <v>1.32</v>
+        <v>-1.96</v>
       </c>
       <c r="J11" t="n">
         <v>4.5</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.96</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>4.5</v>
@@ -1135,31 +1135,31 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.22</v>
+        <v>10.34</v>
       </c>
       <c r="E12" t="n">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
       <c r="F12" t="n">
-        <v>3.76</v>
+        <v>1.17</v>
       </c>
       <c r="G12" t="n">
-        <v>10.34</v>
+        <v>10.08</v>
       </c>
       <c r="H12" t="n">
-        <v>0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="I12" t="n">
-        <v>1.17</v>
+        <v>-2.51</v>
       </c>
       <c r="J12" t="n">
-        <v>10.08</v>
+        <v>9.99</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.51</v>
+        <v>-0.89</v>
       </c>
       <c r="M12" t="n">
         <v>9.99</v>
@@ -1197,31 +1197,31 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24.28</v>
+        <v>24.72</v>
       </c>
       <c r="E13" t="n">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="F13" t="n">
-        <v>0.58</v>
+        <v>1.81</v>
       </c>
       <c r="G13" t="n">
-        <v>24.72</v>
+        <v>24.2</v>
       </c>
       <c r="H13" t="n">
-        <v>0.44</v>
+        <v>-0.52</v>
       </c>
       <c r="I13" t="n">
-        <v>1.81</v>
+        <v>-2.1</v>
       </c>
       <c r="J13" t="n">
-        <v>24.2</v>
+        <v>23.96</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.52</v>
+        <v>-0.24</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.1</v>
+        <v>-0.99</v>
       </c>
       <c r="M13" t="n">
         <v>23.96</v>
@@ -1259,31 +1259,31 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.53</v>
+        <v>-1.6</v>
       </c>
       <c r="G14" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.6</v>
+        <v>-2.16</v>
       </c>
       <c r="J14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.16</v>
+        <v>1.1</v>
       </c>
       <c r="M14" t="n">
         <v>1.83</v>
@@ -1321,31 +1321,31 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.41</v>
+        <v>5.45</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F15" t="n">
-        <v>0.93</v>
+        <v>0.74</v>
       </c>
       <c r="G15" t="n">
-        <v>5.45</v>
+        <v>5.39</v>
       </c>
       <c r="H15" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="I15" t="n">
-        <v>0.74</v>
+        <v>-1.1</v>
       </c>
       <c r="J15" t="n">
-        <v>5.39</v>
+        <v>5.42</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M15" t="n">
         <v>5.42</v>
@@ -1383,31 +1383,31 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.39</v>
+        <v>4.41</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>0.46</v>
       </c>
       <c r="G16" t="n">
-        <v>4.41</v>
+        <v>4.34</v>
       </c>
       <c r="H16" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="K16" t="n">
         <v>0.02</v>
       </c>
-      <c r="I16" t="n">
+      <c r="L16" t="n">
         <v>0.46</v>
-      </c>
-      <c r="J16" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="L16" t="n">
-        <v>-1.59</v>
       </c>
       <c r="M16" t="n">
         <v>4.36</v>
@@ -1445,31 +1445,31 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.27</v>
+        <v>3.33</v>
       </c>
       <c r="E17" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="F17" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="G17" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="H17" t="n">
-        <v>0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="I17" t="n">
-        <v>1.83</v>
+        <v>-3</v>
       </c>
       <c r="J17" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="L17" t="n">
-        <v>-3</v>
+        <v>0.93</v>
       </c>
       <c r="M17" t="n">
         <v>3.26</v>
@@ -1507,31 +1507,31 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.17</v>
+        <v>3.08</v>
       </c>
       <c r="E18" t="n">
-        <v>0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="F18" t="n">
-        <v>3.59</v>
+        <v>-2.84</v>
       </c>
       <c r="G18" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.84</v>
+        <v>-2.27</v>
       </c>
       <c r="J18" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.27</v>
+        <v>1</v>
       </c>
       <c r="M18" t="n">
         <v>3.04</v>
@@ -1569,31 +1569,31 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>51.35</v>
+        <v>50.6</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.3</v>
+        <v>-0.75</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.58</v>
+        <v>-1.46</v>
       </c>
       <c r="G19" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.75</v>
+        <v>-0.2</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.46</v>
+        <v>-0.4</v>
       </c>
       <c r="J19" t="n">
-        <v>50.4</v>
+        <v>50.05</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2</v>
+        <v>-0.35</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.4</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="M19" t="n">
         <v>50.05</v>
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>25.62</v>
+        <v>24.94</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.64</v>
+        <v>-0.68</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.44</v>
+        <v>-2.65</v>
       </c>
       <c r="G20" t="n">
-        <v>24.94</v>
+        <v>24.32</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.68</v>
+        <v>-0.62</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.65</v>
+        <v>-2.49</v>
       </c>
       <c r="J20" t="n">
-        <v>24.32</v>
+        <v>23.62</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.62</v>
+        <v>-0.7</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.49</v>
+        <v>-2.88</v>
       </c>
       <c r="M20" t="n">
         <v>23.62</v>
@@ -1693,31 +1693,31 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.68</v>
+        <v>4.74</v>
       </c>
       <c r="E21" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="F21" t="n">
-        <v>0.43</v>
+        <v>1.28</v>
       </c>
       <c r="G21" t="n">
-        <v>4.74</v>
+        <v>4.72</v>
       </c>
       <c r="H21" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="I21" t="n">
-        <v>1.28</v>
+        <v>-0.42</v>
       </c>
       <c r="J21" t="n">
-        <v>4.72</v>
+        <v>4.66</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.42</v>
+        <v>-1.27</v>
       </c>
       <c r="M21" t="n">
         <v>4.66</v>
@@ -1755,31 +1755,31 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>80.45</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="F22" t="n">
-        <v>0.63</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="G22" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="H22" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="I22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="J22" t="n">
-        <v>81</v>
+        <v>80.95</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="L22" t="n">
-        <v>0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="M22" t="n">
         <v>80.95</v>
@@ -1817,31 +1817,31 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20.12</v>
+        <v>20.06</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.24</v>
+        <v>-0.06</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.18</v>
+        <v>-0.3</v>
       </c>
       <c r="G23" t="n">
-        <v>20.06</v>
+        <v>19.29</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.06</v>
+        <v>-0.77</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.3</v>
+        <v>-3.84</v>
       </c>
       <c r="J23" t="n">
-        <v>19.29</v>
+        <v>19.47</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.77</v>
+        <v>0.18</v>
       </c>
       <c r="L23" t="n">
-        <v>-3.84</v>
+        <v>0.93</v>
       </c>
       <c r="M23" t="n">
         <v>19.47</v>
@@ -1879,31 +1879,31 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.89</v>
+        <v>13.05</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.59</v>
+        <v>0.16</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.38</v>
+        <v>1.24</v>
       </c>
       <c r="G24" t="n">
-        <v>13.05</v>
+        <v>12.27</v>
       </c>
       <c r="H24" t="n">
-        <v>0.16</v>
+        <v>-0.78</v>
       </c>
       <c r="I24" t="n">
-        <v>1.24</v>
+        <v>-5.98</v>
       </c>
       <c r="J24" t="n">
-        <v>12.27</v>
+        <v>12.4</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.78</v>
+        <v>0.13</v>
       </c>
       <c r="L24" t="n">
-        <v>-5.98</v>
+        <v>1.06</v>
       </c>
       <c r="M24" t="n">
         <v>12.4</v>
@@ -1941,31 +1941,31 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>25.04</v>
+        <v>26.38</v>
       </c>
       <c r="E25" t="n">
-        <v>0.52</v>
+        <v>1.34</v>
       </c>
       <c r="F25" t="n">
-        <v>2.12</v>
+        <v>5.35</v>
       </c>
       <c r="G25" t="n">
-        <v>26.38</v>
+        <v>27.08</v>
       </c>
       <c r="H25" t="n">
-        <v>1.34</v>
+        <v>0.7</v>
       </c>
       <c r="I25" t="n">
-        <v>5.35</v>
+        <v>2.65</v>
       </c>
       <c r="J25" t="n">
-        <v>27.08</v>
+        <v>26.66</v>
       </c>
       <c r="K25" t="n">
-        <v>0.7</v>
+        <v>-0.42</v>
       </c>
       <c r="L25" t="n">
-        <v>2.65</v>
+        <v>-1.55</v>
       </c>
       <c r="M25" t="n">
         <v>26.66</v>
@@ -2003,31 +2003,31 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>28.24</v>
+        <v>28.34</v>
       </c>
       <c r="E26" t="n">
-        <v>-1.66</v>
+        <v>0.1</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.55</v>
+        <v>0.35</v>
       </c>
       <c r="G26" t="n">
-        <v>28.34</v>
+        <v>24.98</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1</v>
+        <v>-3.36</v>
       </c>
       <c r="I26" t="n">
-        <v>0.35</v>
+        <v>-11.86</v>
       </c>
       <c r="J26" t="n">
-        <v>24.98</v>
+        <v>25.12</v>
       </c>
       <c r="K26" t="n">
-        <v>-3.36</v>
+        <v>0.14</v>
       </c>
       <c r="L26" t="n">
-        <v>-11.86</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>25.12</v>
@@ -2065,31 +2065,31 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>425.2</v>
+        <v>423.4</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.6</v>
+        <v>-1.8</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.14</v>
+        <v>-0.42</v>
       </c>
       <c r="G27" t="n">
-        <v>423.4</v>
+        <v>417.8</v>
       </c>
       <c r="H27" t="n">
-        <v>-1.8</v>
+        <v>-5.6</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.42</v>
+        <v>-1.32</v>
       </c>
       <c r="J27" t="n">
         <v>417.8</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.6</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
-        <v>-1.32</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
         <v>417.8</v>
@@ -2127,31 +2127,31 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>107.2</v>
+        <v>110.5</v>
       </c>
       <c r="E28" t="n">
-        <v>-1</v>
+        <v>3.3</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.92</v>
+        <v>3.08</v>
       </c>
       <c r="G28" t="n">
-        <v>110.5</v>
+        <v>106.4</v>
       </c>
       <c r="H28" t="n">
-        <v>3.3</v>
+        <v>-4.1</v>
       </c>
       <c r="I28" t="n">
-        <v>3.08</v>
+        <v>-3.71</v>
       </c>
       <c r="J28" t="n">
-        <v>106.4</v>
+        <v>108.8</v>
       </c>
       <c r="K28" t="n">
-        <v>-4.1</v>
+        <v>2.4</v>
       </c>
       <c r="L28" t="n">
-        <v>-3.71</v>
+        <v>2.26</v>
       </c>
       <c r="M28" t="n">
         <v>108.8</v>
@@ -2189,31 +2189,31 @@
         </is>
       </c>
       <c r="D29" t="n">
+        <v>106.1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G29" t="n">
         <v>104.9</v>
       </c>
-      <c r="E29" t="n">
-        <v>-3.6</v>
-      </c>
-      <c r="F29" t="n">
-        <v>-3.32</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="I29" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="J29" t="n">
         <v>106.1</v>
       </c>
-      <c r="H29" t="n">
+      <c r="K29" t="n">
         <v>1.2</v>
       </c>
-      <c r="I29" t="n">
+      <c r="L29" t="n">
         <v>1.14</v>
-      </c>
-      <c r="J29" t="n">
-        <v>104.9</v>
-      </c>
-      <c r="K29" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="L29" t="n">
-        <v>-1.13</v>
       </c>
       <c r="M29" t="n">
         <v>106.1</v>
@@ -2251,31 +2251,31 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>72.3</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>0.5</v>
+        <v>4.8</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7</v>
+        <v>6.64</v>
       </c>
       <c r="G30" t="n">
-        <v>77.09999999999999</v>
+        <v>75.45</v>
       </c>
       <c r="H30" t="n">
-        <v>4.8</v>
+        <v>-1.65</v>
       </c>
       <c r="I30" t="n">
-        <v>6.64</v>
+        <v>-2.14</v>
       </c>
       <c r="J30" t="n">
-        <v>75.45</v>
+        <v>75.7</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.65</v>
+        <v>0.25</v>
       </c>
       <c r="L30" t="n">
-        <v>-2.14</v>
+        <v>0.33</v>
       </c>
       <c r="M30" t="n">
         <v>75.7</v>
@@ -2313,31 +2313,31 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>81.65000000000001</v>
+        <v>82.05</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.15</v>
+        <v>0.4</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.18</v>
+        <v>0.49</v>
       </c>
       <c r="G31" t="n">
-        <v>82.05</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="H31" t="n">
-        <v>0.4</v>
+        <v>-3.7</v>
       </c>
       <c r="I31" t="n">
-        <v>0.49</v>
+        <v>-4.51</v>
       </c>
       <c r="J31" t="n">
-        <v>78.34999999999999</v>
+        <v>79.45</v>
       </c>
       <c r="K31" t="n">
-        <v>-3.7</v>
+        <v>1.1</v>
       </c>
       <c r="L31" t="n">
-        <v>-4.51</v>
+        <v>1.4</v>
       </c>
       <c r="M31" t="n">
         <v>79.45</v>
@@ -2375,31 +2375,31 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>55.55</v>
+        <v>54.3</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.65</v>
+        <v>-1.25</v>
       </c>
       <c r="F32" t="n">
-        <v>-1.16</v>
+        <v>-2.25</v>
       </c>
       <c r="G32" t="n">
-        <v>54.3</v>
+        <v>52.15</v>
       </c>
       <c r="H32" t="n">
-        <v>-1.25</v>
+        <v>-2.15</v>
       </c>
       <c r="I32" t="n">
-        <v>-2.25</v>
+        <v>-3.96</v>
       </c>
       <c r="J32" t="n">
-        <v>52.15</v>
+        <v>52.4</v>
       </c>
       <c r="K32" t="n">
-        <v>-2.15</v>
+        <v>0.25</v>
       </c>
       <c r="L32" t="n">
-        <v>-3.96</v>
+        <v>0.48</v>
       </c>
       <c r="M32" t="n">
         <v>52.4</v>
@@ -2437,31 +2437,31 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>73.25</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.1</v>
+        <v>-0.4</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.48</v>
+        <v>-0.55</v>
       </c>
       <c r="G33" t="n">
-        <v>72.84999999999999</v>
+        <v>72.95</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.55</v>
+        <v>0.14</v>
       </c>
       <c r="J33" t="n">
-        <v>72.95</v>
+        <v>73.75</v>
       </c>
       <c r="K33" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="L33" t="n">
-        <v>0.14</v>
+        <v>1.1</v>
       </c>
       <c r="M33" t="n">
         <v>73.75</v>
@@ -2499,31 +2499,31 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>29.16</v>
+        <v>29.52</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.1</v>
+        <v>0.36</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.34</v>
+        <v>1.23</v>
       </c>
       <c r="G34" t="n">
-        <v>29.52</v>
+        <v>28.58</v>
       </c>
       <c r="H34" t="n">
-        <v>0.36</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>1.23</v>
+        <v>-3.18</v>
       </c>
       <c r="J34" t="n">
-        <v>28.58</v>
+        <v>29.3</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="L34" t="n">
-        <v>-3.18</v>
+        <v>2.52</v>
       </c>
       <c r="M34" t="n">
         <v>29.3</v>
@@ -2561,31 +2561,31 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.05</v>
+        <v>4.09</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.74</v>
+        <v>0.99</v>
       </c>
       <c r="G35" t="n">
-        <v>4.09</v>
+        <v>3.98</v>
       </c>
       <c r="H35" t="n">
-        <v>0.04</v>
+        <v>-0.11</v>
       </c>
       <c r="I35" t="n">
-        <v>0.99</v>
+        <v>-2.69</v>
       </c>
       <c r="J35" t="n">
-        <v>3.98</v>
+        <v>4.03</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.11</v>
+        <v>0.05</v>
       </c>
       <c r="L35" t="n">
-        <v>-2.69</v>
+        <v>1.26</v>
       </c>
       <c r="M35" t="n">
         <v>4.03</v>
@@ -2597,13 +2597,13 @@
         <v>1.26</v>
       </c>
       <c r="P35" t="n">
-        <v>4.03</v>
+        <v>3.98</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="R35" t="n">
-        <v>1.26</v>
+        <v>-1.24</v>
       </c>
     </row>
     <row r="36">
@@ -2623,31 +2623,31 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8.74</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="H36" t="n">
-        <v>0.06</v>
+        <v>-0.23</v>
       </c>
       <c r="I36" t="n">
-        <v>0.6899999999999999</v>
+        <v>-2.61</v>
       </c>
       <c r="J36" t="n">
-        <v>8.57</v>
+        <v>8.67</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.23</v>
+        <v>0.1</v>
       </c>
       <c r="L36" t="n">
-        <v>-2.61</v>
+        <v>1.17</v>
       </c>
       <c r="M36" t="n">
         <v>8.67</v>
@@ -2659,13 +2659,13 @@
         <v>1.17</v>
       </c>
       <c r="P36" t="n">
-        <v>8.67</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="R36" t="n">
-        <v>1.17</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="37">
@@ -2685,31 +2685,31 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>379.6</v>
+        <v>373.6</v>
       </c>
       <c r="E37" t="n">
-        <v>4.2</v>
+        <v>-6</v>
       </c>
       <c r="F37" t="n">
-        <v>1.12</v>
+        <v>-1.58</v>
       </c>
       <c r="G37" t="n">
-        <v>373.6</v>
+        <v>371.4</v>
       </c>
       <c r="H37" t="n">
-        <v>-6</v>
+        <v>-2.2</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.58</v>
+        <v>-0.59</v>
       </c>
       <c r="J37" t="n">
-        <v>371.4</v>
+        <v>374.6</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.2</v>
+        <v>3.2</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.59</v>
+        <v>0.86</v>
       </c>
       <c r="M37" t="n">
         <v>374.6</v>
@@ -2747,31 +2747,31 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.42</v>
+        <v>11.29</v>
       </c>
       <c r="E38" t="n">
-        <v>0.37</v>
+        <v>-0.13</v>
       </c>
       <c r="F38" t="n">
-        <v>3.35</v>
+        <v>-1.14</v>
       </c>
       <c r="G38" t="n">
-        <v>11.29</v>
+        <v>11.3</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.13</v>
+        <v>0.01</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.14</v>
+        <v>0.09</v>
       </c>
       <c r="J38" t="n">
-        <v>11.3</v>
+        <v>11.49</v>
       </c>
       <c r="K38" t="n">
-        <v>0.01</v>
+        <v>0.19</v>
       </c>
       <c r="L38" t="n">
-        <v>0.09</v>
+        <v>1.68</v>
       </c>
       <c r="M38" t="n">
         <v>11.49</v>
@@ -2809,31 +2809,31 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>485.2</v>
+        <v>467</v>
       </c>
       <c r="E39" t="n">
-        <v>-9.6</v>
+        <v>-18.2</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.94</v>
+        <v>-3.75</v>
       </c>
       <c r="G39" t="n">
-        <v>467</v>
+        <v>448.6</v>
       </c>
       <c r="H39" t="n">
-        <v>-18.2</v>
+        <v>-18.4</v>
       </c>
       <c r="I39" t="n">
-        <v>-3.75</v>
+        <v>-3.94</v>
       </c>
       <c r="J39" t="n">
-        <v>448.6</v>
+        <v>440.8</v>
       </c>
       <c r="K39" t="n">
-        <v>-18.4</v>
+        <v>-7.8</v>
       </c>
       <c r="L39" t="n">
-        <v>-3.94</v>
+        <v>-1.74</v>
       </c>
       <c r="M39" t="n">
         <v>440.8</v>
@@ -2871,31 +2871,31 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>37.84</v>
+        <v>38.62</v>
       </c>
       <c r="E40" t="n">
-        <v>-0.64</v>
+        <v>0.78</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.66</v>
+        <v>2.06</v>
       </c>
       <c r="G40" t="n">
-        <v>38.62</v>
+        <v>37.2</v>
       </c>
       <c r="H40" t="n">
-        <v>0.78</v>
+        <v>-1.42</v>
       </c>
       <c r="I40" t="n">
-        <v>2.06</v>
+        <v>-3.68</v>
       </c>
       <c r="J40" t="n">
-        <v>37.2</v>
+        <v>37.46</v>
       </c>
       <c r="K40" t="n">
-        <v>-1.42</v>
+        <v>0.26</v>
       </c>
       <c r="L40" t="n">
-        <v>-3.68</v>
+        <v>0.7</v>
       </c>
       <c r="M40" t="n">
         <v>37.46</v>
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>29.2</v>
+        <v>29</v>
       </c>
       <c r="E41" t="n">
-        <v>0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="F41" t="n">
-        <v>0.48</v>
+        <v>-0.68</v>
       </c>
       <c r="G41" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="I41" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="J41" t="n">
         <v>29</v>
       </c>
-      <c r="H41" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="I41" t="n">
-        <v>-0.68</v>
-      </c>
-      <c r="J41" t="n">
-        <v>28.99</v>
-      </c>
       <c r="K41" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="M41" t="n">
-        <v>29</v>
+        <v>28.92</v>
       </c>
       <c r="N41" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="O41" t="n">
-        <v>0.03</v>
+        <v>-0.28</v>
       </c>
       <c r="P41" t="n">
-        <v>29</v>
+        <v>28.92</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="R41" t="n">
-        <v>0.03</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>74.47</v>
+        <v>74.34</v>
       </c>
       <c r="E42" t="n">
-        <v>0.53</v>
+        <v>-0.13</v>
       </c>
       <c r="F42" t="n">
-        <v>0.72</v>
+        <v>-0.17</v>
       </c>
       <c r="G42" t="n">
-        <v>74.34</v>
+        <v>73.75</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.13</v>
+        <v>-0.59</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.17</v>
+        <v>-0.79</v>
       </c>
       <c r="J42" t="n">
-        <v>73.75</v>
+        <v>74.11</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.59</v>
+        <v>0.36</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.79</v>
+        <v>0.49</v>
       </c>
       <c r="M42" t="n">
-        <v>74.11</v>
+        <v>74.45</v>
       </c>
       <c r="N42" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="O42" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="P42" t="n">
-        <v>74.11</v>
+        <v>74.45</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="R42" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>40.93</v>
+        <v>41.06</v>
       </c>
       <c r="E43" t="n">
-        <v>0.43</v>
+        <v>0.13</v>
       </c>
       <c r="F43" t="n">
-        <v>1.06</v>
+        <v>0.32</v>
       </c>
       <c r="G43" t="n">
-        <v>41.06</v>
+        <v>41.69</v>
       </c>
       <c r="H43" t="n">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
       <c r="I43" t="n">
-        <v>0.32</v>
+        <v>1.53</v>
       </c>
       <c r="J43" t="n">
-        <v>41.69</v>
+        <v>41.61</v>
       </c>
       <c r="K43" t="n">
-        <v>0.63</v>
+        <v>-0.08</v>
       </c>
       <c r="L43" t="n">
-        <v>1.53</v>
+        <v>-0.19</v>
       </c>
       <c r="M43" t="n">
-        <v>41.61</v>
+        <v>41.64</v>
       </c>
       <c r="N43" t="n">
-        <v>-0.08</v>
+        <v>0.03</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="P43" t="n">
-        <v>41.61</v>
+        <v>41.64</v>
       </c>
       <c r="Q43" t="n">
-        <v>-0.08</v>
+        <v>0.03</v>
       </c>
       <c r="R43" t="n">
-        <v>-0.19</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.08</v>
+        <v>6.04</v>
       </c>
       <c r="E44" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="F44" t="n">
-        <v>1.16</v>
+        <v>-0.66</v>
       </c>
       <c r="G44" t="n">
-        <v>6.04</v>
+        <v>5.92</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.66</v>
+        <v>-1.99</v>
       </c>
       <c r="J44" t="n">
         <v>5.92</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="L44" t="n">
-        <v>-1.99</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>5.92</v>
+        <v>5.91</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="P44" t="n">
-        <v>5.92</v>
+        <v>5.91</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="45">
@@ -3184,28 +3184,28 @@
         <v>1.94</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.51</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>-4.64</v>
       </c>
       <c r="J45" t="n">
         <v>1.85</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>-4.64</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>1.85</v>
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.61</v>
+        <v>-0.82</v>
       </c>
       <c r="G46" t="n">
-        <v>3.64</v>
+        <v>3.57</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.82</v>
+        <v>-1.92</v>
       </c>
       <c r="J46" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="L46" t="n">
-        <v>-1.92</v>
+        <v>0.28</v>
       </c>
       <c r="M46" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="N46" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="O46" t="n">
-        <v>0.28</v>
+        <v>1.12</v>
       </c>
       <c r="P46" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="R46" t="n">
-        <v>0.28</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.35</v>
+        <v>10.41</v>
       </c>
       <c r="E47" t="n">
-        <v>-0.05</v>
+        <v>0.06</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.48</v>
+        <v>0.58</v>
       </c>
       <c r="G47" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="I47" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="J47" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="M47" t="n">
         <v>10.41</v>
       </c>
-      <c r="H47" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I47" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="J47" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="K47" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="L47" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="M47" t="n">
-        <v>10.39</v>
-      </c>
       <c r="N47" t="n">
-        <v>0.14</v>
+        <v>0.02</v>
       </c>
       <c r="O47" t="n">
-        <v>1.37</v>
+        <v>0.19</v>
       </c>
       <c r="P47" t="n">
-        <v>10.39</v>
+        <v>10.41</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.14</v>
+        <v>0.02</v>
       </c>
       <c r="R47" t="n">
-        <v>1.37</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="48">
@@ -3367,49 +3367,49 @@
         </is>
       </c>
       <c r="D48" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F48" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="G48" t="n">
         <v>0.285</v>
       </c>
-      <c r="E48" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.29</v>
-      </c>
       <c r="H48" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="I48" t="n">
-        <v>1.75</v>
+        <v>-1.72</v>
       </c>
       <c r="J48" t="n">
-        <v>0.285</v>
+        <v>0.28</v>
       </c>
       <c r="K48" t="n">
         <v>-0.005</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.72</v>
+        <v>-1.75</v>
       </c>
       <c r="M48" t="n">
         <v>0.28</v>
       </c>
       <c r="N48" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>-1.75</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
         <v>0.28</v>
       </c>
       <c r="Q48" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>-1.75</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3429,25 +3429,25 @@
         </is>
       </c>
       <c r="D49" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F49" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="G49" t="n">
         <v>4.16</v>
       </c>
-      <c r="E49" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="F49" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="G49" t="n">
-        <v>4.14</v>
-      </c>
       <c r="H49" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.48</v>
+        <v>0.48</v>
       </c>
       <c r="J49" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="K49" t="n">
         <v>0.02</v>
@@ -3459,19 +3459,19 @@
         <v>4.18</v>
       </c>
       <c r="N49" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
         <v>4.18</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3494,46 +3494,46 @@
         <v>1.1</v>
       </c>
       <c r="E50" t="n">
+        <v>0</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="H50" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F50" t="n">
-        <v>-0.9</v>
-      </c>
-      <c r="G50" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>-0.91</v>
       </c>
       <c r="J50" t="n">
         <v>1.09</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.91</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="P50" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>5.06</v>
+        <v>5.15</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.03</v>
+        <v>0.09</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.59</v>
+        <v>1.78</v>
       </c>
       <c r="G51" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="I51" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="J51" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="L51" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="M51" t="n">
         <v>5.15</v>
       </c>
-      <c r="H51" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="I51" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="J51" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="K51" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="L51" t="n">
-        <v>-2.33</v>
-      </c>
-      <c r="M51" t="n">
-        <v>5.21</v>
-      </c>
       <c r="N51" t="n">
-        <v>0.18</v>
+        <v>-0.06</v>
       </c>
       <c r="O51" t="n">
-        <v>3.58</v>
+        <v>-1.15</v>
       </c>
       <c r="P51" t="n">
-        <v>5.21</v>
+        <v>5.15</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.18</v>
+        <v>-0.06</v>
       </c>
       <c r="R51" t="n">
-        <v>3.58</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.42</v>
+        <v>10.36</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.1</v>
+        <v>-0.58</v>
       </c>
       <c r="G52" t="n">
-        <v>10.36</v>
+        <v>10.12</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.06</v>
+        <v>-0.24</v>
       </c>
       <c r="I52" t="n">
-        <v>-0.58</v>
+        <v>-2.32</v>
       </c>
       <c r="J52" t="n">
-        <v>10.12</v>
+        <v>10.1</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.24</v>
+        <v>-0.02</v>
       </c>
       <c r="L52" t="n">
-        <v>-2.32</v>
+        <v>-0.2</v>
       </c>
       <c r="M52" t="n">
-        <v>10.1</v>
+        <v>10.07</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="P52" t="n">
-        <v>10.1</v>
+        <v>10.07</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="53">
@@ -3677,49 +3677,49 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>7.15</v>
+        <v>7.05</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="F53" t="n">
-        <v>1.42</v>
+        <v>-1.4</v>
       </c>
       <c r="G53" t="n">
         <v>7.05</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>7.05</v>
+        <v>7.04</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="M53" t="n">
-        <v>7.04</v>
+        <v>7.01</v>
       </c>
       <c r="N53" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="O53" t="n">
-        <v>-0.14</v>
+        <v>-0.43</v>
       </c>
       <c r="P53" t="n">
-        <v>7.04</v>
+        <v>7.01</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.14</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="54">
@@ -3748,22 +3748,22 @@
         <v>0</v>
       </c>
       <c r="G54" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
       <c r="J54" t="n">
         <v>0.425</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
-        <v>-1.16</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
         <v>0.425</v>
@@ -3801,22 +3801,22 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>0.605</v>
+        <v>0.61</v>
       </c>
       <c r="E55" t="n">
-        <v>-0.005</v>
+        <v>0.005</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.82</v>
+        <v>0.83</v>
       </c>
       <c r="G55" t="n">
         <v>0.61</v>
       </c>
       <c r="H55" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="J55" t="n">
         <v>0.61</v>
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.355</v>
+        <v>0.345</v>
       </c>
       <c r="E56" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F56" t="n">
-        <v>5.97</v>
+        <v>-2.82</v>
       </c>
       <c r="G56" t="n">
-        <v>0.345</v>
+        <v>0.34</v>
       </c>
       <c r="H56" t="n">
-        <v>-0.01</v>
+        <v>-0.005</v>
       </c>
       <c r="I56" t="n">
-        <v>-2.82</v>
+        <v>-1.45</v>
       </c>
       <c r="J56" t="n">
         <v>0.34</v>
       </c>
       <c r="K56" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="L56" t="n">
-        <v>-1.45</v>
+        <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.34</v>
+        <v>0.325</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>-4.41</v>
       </c>
       <c r="P56" t="n">
-        <v>0.34</v>
+        <v>0.325</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>-0.015</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="57">
@@ -3925,49 +3925,49 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>3.46</v>
+        <v>3.51</v>
       </c>
       <c r="E57" t="n">
-        <v>-0.02</v>
+        <v>0.05</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.57</v>
+        <v>1.45</v>
       </c>
       <c r="G57" t="n">
-        <v>3.51</v>
+        <v>3.48</v>
       </c>
       <c r="H57" t="n">
-        <v>0.05</v>
+        <v>-0.03</v>
       </c>
       <c r="I57" t="n">
-        <v>1.45</v>
+        <v>-0.85</v>
       </c>
       <c r="J57" t="n">
-        <v>3.48</v>
+        <v>3.44</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="L57" t="n">
-        <v>-0.85</v>
+        <v>-1.15</v>
       </c>
       <c r="M57" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="N57" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="O57" t="n">
-        <v>-1.15</v>
+        <v>-0.29</v>
       </c>
       <c r="P57" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="Q57" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="R57" t="n">
-        <v>-1.15</v>
+        <v>-0.29</v>
       </c>
     </row>
     <row r="58">
@@ -3987,49 +3987,49 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>0.078</v>
+        <v>0.077</v>
       </c>
       <c r="E58" t="n">
-        <v>0</v>
+        <v>-0.001</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>-1.28</v>
       </c>
       <c r="G58" t="n">
         <v>0.077</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.001</v>
+        <v>0</v>
       </c>
       <c r="I58" t="n">
-        <v>-1.28</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>0.077</v>
+        <v>0.078</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="M58" t="n">
-        <v>0.078</v>
+        <v>0.076</v>
       </c>
       <c r="N58" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="O58" t="n">
-        <v>1.3</v>
+        <v>-2.56</v>
       </c>
       <c r="P58" t="n">
-        <v>0.078</v>
+        <v>0.076</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.001</v>
+        <v>-0.002</v>
       </c>
       <c r="R58" t="n">
-        <v>1.3</v>
+        <v>-2.56</v>
       </c>
     </row>
     <row r="59">
@@ -4049,49 +4049,49 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>21.14</v>
+        <v>20.96</v>
       </c>
       <c r="E59" t="n">
-        <v>-0.21</v>
+        <v>-0.18</v>
       </c>
       <c r="F59" t="n">
-        <v>-0.98</v>
+        <v>-0.85</v>
       </c>
       <c r="G59" t="n">
-        <v>20.96</v>
+        <v>20.89</v>
       </c>
       <c r="H59" t="n">
-        <v>-0.18</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.85</v>
+        <v>-0.33</v>
       </c>
       <c r="J59" t="n">
-        <v>20.89</v>
+        <v>21</v>
       </c>
       <c r="K59" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="L59" t="n">
-        <v>-0.33</v>
+        <v>0.53</v>
       </c>
       <c r="M59" t="n">
-        <v>21</v>
+        <v>20.78</v>
       </c>
       <c r="N59" t="n">
-        <v>0.11</v>
+        <v>-0.22</v>
       </c>
       <c r="O59" t="n">
-        <v>0.53</v>
+        <v>-1.05</v>
       </c>
       <c r="P59" t="n">
-        <v>21</v>
+        <v>20.78</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.11</v>
+        <v>-0.22</v>
       </c>
       <c r="R59" t="n">
-        <v>0.53</v>
+        <v>-1.05</v>
       </c>
     </row>
     <row r="60">
@@ -4111,49 +4111,49 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="E60" t="n">
-        <v>-0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.94</v>
+        <v>-2.63</v>
       </c>
       <c r="G60" t="n">
-        <v>2.96</v>
+        <v>2.87</v>
       </c>
       <c r="H60" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="I60" t="n">
-        <v>-2.63</v>
+        <v>-3.04</v>
       </c>
       <c r="J60" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="K60" t="n">
-        <v>-0.09</v>
+        <v>0.03</v>
       </c>
       <c r="L60" t="n">
-        <v>-3.04</v>
+        <v>1.05</v>
       </c>
       <c r="M60" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="N60" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="O60" t="n">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
       <c r="P60" t="n">
-        <v>2.9</v>
+        <v>2.94</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="R60" t="n">
-        <v>1.05</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="61">
@@ -4176,46 +4176,46 @@
         <v>0.795</v>
       </c>
       <c r="E61" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>-4.79</v>
+        <v>0</v>
       </c>
       <c r="G61" t="n">
-        <v>0.795</v>
+        <v>0.77</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>-0.025</v>
       </c>
       <c r="I61" t="n">
-        <v>0</v>
+        <v>-3.14</v>
       </c>
       <c r="J61" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="K61" t="n">
-        <v>-0.025</v>
+        <v>0.02</v>
       </c>
       <c r="L61" t="n">
-        <v>-3.14</v>
+        <v>2.6</v>
       </c>
       <c r="M61" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="N61" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="O61" t="n">
-        <v>2.6</v>
+        <v>7.59</v>
       </c>
       <c r="P61" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="R61" t="n">
-        <v>2.6</v>
+        <v>7.59</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/stock_closing_prices.xlsx
+++ b/outputs/stock_closing_prices.xlsx
@@ -454,77 +454,77 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>2026-10-14 Close</t>
+          <t>2026-10-15 Close</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>2026-10-14 Change</t>
+          <t>2026-10-15 Change</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>2026-10-14 Change %</t>
+          <t>2026-10-15 Change %</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>2026-10-15 Close</t>
+          <t>2026-10-16 Close</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>2026-10-15 Change</t>
+          <t>2026-10-16 Change</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>2026-10-15 Change %</t>
+          <t>2026-10-16 Change %</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>2026-10-16 Close</t>
+          <t>2026-10-19 Close</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>2026-10-16 Change</t>
+          <t>2026-10-19 Change</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>2026-10-16 Change %</t>
+          <t>2026-10-19 Change %</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>2026-10-19 Close</t>
+          <t>2026-10-20 Close</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>2026-10-19 Change</t>
+          <t>2026-10-20 Change</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>2026-10-19 Change %</t>
+          <t>2026-10-20 Change %</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>2026-10-20 Close</t>
+          <t>2026-10-21 Close</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>2026-10-20 Change</t>
+          <t>2026-10-21 Change</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>2026-10-20 Change %</t>
+          <t>2026-10-21 Change %</t>
         </is>
       </c>
     </row>
@@ -577,22 +577,22 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>148</v>
+        <v>147.9</v>
       </c>
       <c r="E3" t="n">
-        <v>-2.7</v>
+        <v>-0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.79</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="G3" t="n">
-        <v>147.9</v>
+        <v>149.7</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1</v>
+        <v>1.8</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.22</v>
       </c>
       <c r="J3" t="n">
         <v>149.7</v>
@@ -604,22 +604,22 @@
         <v>1.22</v>
       </c>
       <c r="M3" t="n">
-        <v>149.7</v>
+        <v>144.7</v>
       </c>
       <c r="N3" t="n">
-        <v>1.8</v>
+        <v>-5</v>
       </c>
       <c r="O3" t="n">
-        <v>1.22</v>
+        <v>-3.34</v>
       </c>
       <c r="P3" t="n">
-        <v>149.7</v>
+        <v>144.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>-5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.22</v>
+        <v>-3.34</v>
       </c>
     </row>
     <row r="4">
@@ -639,22 +639,22 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>221.8</v>
+        <v>221</v>
       </c>
       <c r="E4" t="n">
-        <v>-8</v>
+        <v>-0.8</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.48</v>
+        <v>-0.36</v>
       </c>
       <c r="G4" t="n">
-        <v>221</v>
+        <v>223.6</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.8</v>
+        <v>2.6</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.36</v>
+        <v>1.18</v>
       </c>
       <c r="J4" t="n">
         <v>223.6</v>
@@ -666,22 +666,22 @@
         <v>1.18</v>
       </c>
       <c r="M4" t="n">
-        <v>223.6</v>
+        <v>214</v>
       </c>
       <c r="N4" t="n">
-        <v>2.6</v>
+        <v>-9.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.18</v>
+        <v>-4.29</v>
       </c>
       <c r="P4" t="n">
-        <v>223.6</v>
+        <v>214</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.6</v>
+        <v>-9.6</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="5">
@@ -701,22 +701,22 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>6.57</v>
+        <v>6.8</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.15</v>
+        <v>0.23</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.23</v>
+        <v>3.5</v>
       </c>
       <c r="G5" t="n">
-        <v>6.8</v>
+        <v>6.74</v>
       </c>
       <c r="H5" t="n">
-        <v>0.23</v>
+        <v>-0.06</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5</v>
+        <v>-0.88</v>
       </c>
       <c r="J5" t="n">
         <v>6.74</v>
@@ -728,22 +728,22 @@
         <v>-0.88</v>
       </c>
       <c r="M5" t="n">
-        <v>6.74</v>
+        <v>6.71</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.88</v>
+        <v>-0.45</v>
       </c>
       <c r="P5" t="n">
-        <v>6.74</v>
+        <v>6.71</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.88</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="6">
@@ -763,22 +763,22 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>7.57</v>
+        <v>7.7</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.92</v>
+        <v>1.72</v>
       </c>
       <c r="G6" t="n">
-        <v>7.7</v>
+        <v>7.59</v>
       </c>
       <c r="H6" t="n">
-        <v>0.13</v>
+        <v>-0.11</v>
       </c>
       <c r="I6" t="n">
-        <v>1.72</v>
+        <v>-1.43</v>
       </c>
       <c r="J6" t="n">
         <v>7.59</v>
@@ -790,22 +790,22 @@
         <v>-1.43</v>
       </c>
       <c r="M6" t="n">
-        <v>7.59</v>
+        <v>7.49</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.43</v>
+        <v>-1.32</v>
       </c>
       <c r="P6" t="n">
-        <v>7.59</v>
+        <v>7.49</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="R6" t="n">
-        <v>-1.43</v>
+        <v>-1.32</v>
       </c>
     </row>
     <row r="7">
@@ -825,22 +825,22 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6.2</v>
+        <v>6.16</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.06</v>
+        <v>-0.04</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.96</v>
+        <v>-0.65</v>
       </c>
       <c r="G7" t="n">
-        <v>6.16</v>
+        <v>6.14</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.65</v>
+        <v>-0.32</v>
       </c>
       <c r="J7" t="n">
         <v>6.14</v>
@@ -852,22 +852,22 @@
         <v>-0.32</v>
       </c>
       <c r="M7" t="n">
-        <v>6.14</v>
+        <v>6.11</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.32</v>
+        <v>-0.49</v>
       </c>
       <c r="P7" t="n">
-        <v>6.14</v>
+        <v>6.11</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.32</v>
+        <v>-0.49</v>
       </c>
     </row>
     <row r="8">
@@ -887,22 +887,22 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.85</v>
+        <v>9.98</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.11</v>
+        <v>0.13</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1</v>
+        <v>1.32</v>
       </c>
       <c r="G8" t="n">
-        <v>9.98</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="I8" t="n">
-        <v>1.32</v>
+        <v>-1.2</v>
       </c>
       <c r="J8" t="n">
         <v>9.859999999999999</v>
@@ -914,22 +914,22 @@
         <v>-1.2</v>
       </c>
       <c r="M8" t="n">
-        <v>9.859999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.2</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>9.859999999999999</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="R8" t="n">
-        <v>-1.2</v>
+        <v>-0.8100000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -952,19 +952,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>8.619999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-1.62</v>
       </c>
       <c r="J9" t="n">
         <v>8.48</v>
@@ -976,22 +976,22 @@
         <v>-1.62</v>
       </c>
       <c r="M9" t="n">
-        <v>8.48</v>
+        <v>8.51</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.62</v>
+        <v>0.35</v>
       </c>
       <c r="P9" t="n">
-        <v>8.48</v>
+        <v>8.51</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.14</v>
+        <v>0.03</v>
       </c>
       <c r="R9" t="n">
-        <v>-1.62</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="10">
@@ -1011,22 +1011,22 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>53.55</v>
+        <v>53.95</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.35</v>
+        <v>0.4</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.65</v>
+        <v>0.75</v>
       </c>
       <c r="G10" t="n">
-        <v>53.95</v>
+        <v>53.25</v>
       </c>
       <c r="H10" t="n">
-        <v>0.4</v>
+        <v>-0.7</v>
       </c>
       <c r="I10" t="n">
-        <v>0.75</v>
+        <v>-1.3</v>
       </c>
       <c r="J10" t="n">
         <v>53.25</v>
@@ -1038,22 +1038,22 @@
         <v>-1.3</v>
       </c>
       <c r="M10" t="n">
-        <v>53.25</v>
+        <v>53</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.7</v>
+        <v>-0.25</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.3</v>
+        <v>-0.47</v>
       </c>
       <c r="P10" t="n">
-        <v>53.25</v>
+        <v>53</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.7</v>
+        <v>-0.25</v>
       </c>
       <c r="R10" t="n">
-        <v>-1.3</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="11">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
       <c r="E11" t="n">
-        <v>0.06</v>
+        <v>-0.09</v>
       </c>
       <c r="F11" t="n">
-        <v>1.32</v>
+        <v>-1.96</v>
       </c>
       <c r="G11" t="n">
         <v>4.5</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.96</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>4.5</v>
@@ -1100,22 +1100,22 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
       <c r="P11" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.04</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="12">
@@ -1135,22 +1135,22 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10.34</v>
+        <v>10.08</v>
       </c>
       <c r="E12" t="n">
-        <v>0.12</v>
+        <v>-0.26</v>
       </c>
       <c r="F12" t="n">
-        <v>1.17</v>
+        <v>-2.51</v>
       </c>
       <c r="G12" t="n">
-        <v>10.08</v>
+        <v>9.99</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.26</v>
+        <v>-0.09</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.51</v>
+        <v>-0.89</v>
       </c>
       <c r="J12" t="n">
         <v>9.99</v>
@@ -1162,22 +1162,22 @@
         <v>-0.89</v>
       </c>
       <c r="M12" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.89</v>
+        <v>-0.1</v>
       </c>
       <c r="P12" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.09</v>
+        <v>-0.01</v>
       </c>
       <c r="R12" t="n">
-        <v>-0.89</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="13">
@@ -1197,22 +1197,22 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>24.72</v>
+        <v>24.2</v>
       </c>
       <c r="E13" t="n">
-        <v>0.44</v>
+        <v>-0.52</v>
       </c>
       <c r="F13" t="n">
-        <v>1.81</v>
+        <v>-2.1</v>
       </c>
       <c r="G13" t="n">
-        <v>24.2</v>
+        <v>23.96</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.52</v>
+        <v>-0.24</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.1</v>
+        <v>-0.99</v>
       </c>
       <c r="J13" t="n">
         <v>23.96</v>
@@ -1224,22 +1224,22 @@
         <v>-0.99</v>
       </c>
       <c r="M13" t="n">
-        <v>23.96</v>
+        <v>24.22</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.24</v>
+        <v>0.26</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.99</v>
+        <v>1.09</v>
       </c>
       <c r="P13" t="n">
-        <v>23.96</v>
+        <v>24.22</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.24</v>
+        <v>0.26</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.99</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="14">
@@ -1259,22 +1259,22 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6</v>
+        <v>-2.16</v>
       </c>
       <c r="G14" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.04</v>
+        <v>0.02</v>
       </c>
       <c r="I14" t="n">
-        <v>-2.16</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
         <v>1.83</v>
@@ -1286,22 +1286,22 @@
         <v>1.1</v>
       </c>
       <c r="M14" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="N14" t="n">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="O14" t="n">
-        <v>1.1</v>
+        <v>-3.28</v>
       </c>
       <c r="P14" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1</v>
+        <v>-3.28</v>
       </c>
     </row>
     <row r="15">
@@ -1321,22 +1321,22 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>5.45</v>
+        <v>5.39</v>
       </c>
       <c r="E15" t="n">
-        <v>0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="F15" t="n">
-        <v>0.74</v>
+        <v>-1.1</v>
       </c>
       <c r="G15" t="n">
-        <v>5.39</v>
+        <v>5.42</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.06</v>
+        <v>0.03</v>
       </c>
       <c r="I15" t="n">
-        <v>-1.1</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J15" t="n">
         <v>5.42</v>
@@ -1348,22 +1348,22 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>5.42</v>
+        <v>5.32</v>
       </c>
       <c r="N15" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.85</v>
       </c>
       <c r="P15" t="n">
-        <v>5.42</v>
+        <v>5.32</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="R15" t="n">
-        <v>0.5600000000000001</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="16">
@@ -1383,22 +1383,22 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.41</v>
+        <v>4.34</v>
       </c>
       <c r="E16" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-1.59</v>
+      </c>
+      <c r="G16" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="H16" t="n">
         <v>0.02</v>
       </c>
-      <c r="F16" t="n">
+      <c r="I16" t="n">
         <v>0.46</v>
-      </c>
-      <c r="G16" t="n">
-        <v>4.34</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-0.07000000000000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-1.59</v>
       </c>
       <c r="J16" t="n">
         <v>4.36</v>
@@ -1410,22 +1410,22 @@
         <v>0.46</v>
       </c>
       <c r="M16" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="N16" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="O16" t="n">
-        <v>0.46</v>
+        <v>-0.46</v>
       </c>
       <c r="P16" t="n">
-        <v>4.36</v>
+        <v>4.34</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="R16" t="n">
-        <v>0.46</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="17">
@@ -1445,22 +1445,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.33</v>
+        <v>3.23</v>
       </c>
       <c r="E17" t="n">
-        <v>0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="F17" t="n">
-        <v>1.83</v>
+        <v>-3</v>
       </c>
       <c r="G17" t="n">
-        <v>3.23</v>
+        <v>3.26</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1</v>
+        <v>0.03</v>
       </c>
       <c r="I17" t="n">
-        <v>-3</v>
+        <v>0.93</v>
       </c>
       <c r="J17" t="n">
         <v>3.26</v>
@@ -1472,22 +1472,22 @@
         <v>0.93</v>
       </c>
       <c r="M17" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="O17" t="n">
-        <v>0.93</v>
+        <v>-1.84</v>
       </c>
       <c r="P17" t="n">
-        <v>3.26</v>
+        <v>3.2</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="R17" t="n">
-        <v>0.93</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="18">
@@ -1507,22 +1507,22 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.09</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.84</v>
+        <v>-2.27</v>
       </c>
       <c r="G18" t="n">
-        <v>3.01</v>
+        <v>3.04</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="I18" t="n">
-        <v>-2.27</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
         <v>3.04</v>
@@ -1534,22 +1534,22 @@
         <v>1</v>
       </c>
       <c r="M18" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="N18" t="n">
         <v>0.03</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="P18" t="n">
-        <v>3.04</v>
+        <v>3.07</v>
       </c>
       <c r="Q18" t="n">
         <v>0.03</v>
       </c>
       <c r="R18" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="19">
@@ -1569,22 +1569,22 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>50.6</v>
+        <v>50.4</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.75</v>
+        <v>-0.2</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.46</v>
+        <v>-0.4</v>
       </c>
       <c r="G19" t="n">
-        <v>50.4</v>
+        <v>50.05</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2</v>
+        <v>-0.35</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="J19" t="n">
         <v>50.05</v>
@@ -1596,22 +1596,22 @@
         <v>-0.6899999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>50.05</v>
+        <v>49.2</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.35</v>
+        <v>-0.85</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.7</v>
       </c>
       <c r="P19" t="n">
-        <v>50.05</v>
+        <v>49.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.35</v>
+        <v>-0.85</v>
       </c>
       <c r="R19" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="20">
@@ -1631,22 +1631,22 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>24.94</v>
+        <v>24.32</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.68</v>
+        <v>-0.62</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.65</v>
+        <v>-2.49</v>
       </c>
       <c r="G20" t="n">
-        <v>24.32</v>
+        <v>23.62</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.62</v>
+        <v>-0.7</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.49</v>
+        <v>-2.88</v>
       </c>
       <c r="J20" t="n">
         <v>23.62</v>
@@ -1658,22 +1658,22 @@
         <v>-2.88</v>
       </c>
       <c r="M20" t="n">
-        <v>23.62</v>
+        <v>23.02</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7</v>
+        <v>-0.6</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.88</v>
+        <v>-2.54</v>
       </c>
       <c r="P20" t="n">
-        <v>23.62</v>
+        <v>23.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.7</v>
+        <v>-0.6</v>
       </c>
       <c r="R20" t="n">
-        <v>-2.88</v>
+        <v>-2.54</v>
       </c>
     </row>
     <row r="21">
@@ -1693,22 +1693,22 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4.74</v>
+        <v>4.72</v>
       </c>
       <c r="E21" t="n">
-        <v>0.06</v>
+        <v>-0.02</v>
       </c>
       <c r="F21" t="n">
-        <v>1.28</v>
+        <v>-0.42</v>
       </c>
       <c r="G21" t="n">
-        <v>4.72</v>
+        <v>4.66</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.42</v>
+        <v>-1.27</v>
       </c>
       <c r="J21" t="n">
         <v>4.66</v>
@@ -1720,22 +1720,22 @@
         <v>-1.27</v>
       </c>
       <c r="M21" t="n">
-        <v>4.66</v>
+        <v>4.59</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.27</v>
+        <v>-1.5</v>
       </c>
       <c r="P21" t="n">
-        <v>4.66</v>
+        <v>4.59</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="R21" t="n">
-        <v>-1.27</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="22">
@@ -1755,22 +1755,22 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>80.90000000000001</v>
+        <v>81</v>
       </c>
       <c r="E22" t="n">
-        <v>0.45</v>
+        <v>0.1</v>
       </c>
       <c r="F22" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="G22" t="n">
-        <v>81</v>
+        <v>80.95</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="I22" t="n">
-        <v>0.12</v>
+        <v>-0.06</v>
       </c>
       <c r="J22" t="n">
         <v>80.95</v>
@@ -1782,22 +1782,22 @@
         <v>-0.06</v>
       </c>
       <c r="M22" t="n">
-        <v>80.95</v>
+        <v>80.5</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.05</v>
+        <v>-0.45</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.06</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>80.95</v>
+        <v>80.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.05</v>
+        <v>-0.45</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.06</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1817,22 +1817,22 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>20.06</v>
+        <v>19.29</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.06</v>
+        <v>-0.77</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3</v>
+        <v>-3.84</v>
       </c>
       <c r="G23" t="n">
-        <v>19.29</v>
+        <v>19.47</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.77</v>
+        <v>0.18</v>
       </c>
       <c r="I23" t="n">
-        <v>-3.84</v>
+        <v>0.93</v>
       </c>
       <c r="J23" t="n">
         <v>19.47</v>
@@ -1844,22 +1844,22 @@
         <v>0.93</v>
       </c>
       <c r="M23" t="n">
-        <v>19.47</v>
+        <v>19.63</v>
       </c>
       <c r="N23" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="O23" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="P23" t="n">
-        <v>19.47</v>
+        <v>19.63</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="R23" t="n">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="24">
@@ -1879,22 +1879,22 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.05</v>
+        <v>12.27</v>
       </c>
       <c r="E24" t="n">
-        <v>0.16</v>
+        <v>-0.78</v>
       </c>
       <c r="F24" t="n">
-        <v>1.24</v>
+        <v>-5.98</v>
       </c>
       <c r="G24" t="n">
-        <v>12.27</v>
+        <v>12.4</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.78</v>
+        <v>0.13</v>
       </c>
       <c r="I24" t="n">
-        <v>-5.98</v>
+        <v>1.06</v>
       </c>
       <c r="J24" t="n">
         <v>12.4</v>
@@ -1906,22 +1906,22 @@
         <v>1.06</v>
       </c>
       <c r="M24" t="n">
-        <v>12.4</v>
+        <v>12.46</v>
       </c>
       <c r="N24" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="O24" t="n">
-        <v>1.06</v>
+        <v>0.48</v>
       </c>
       <c r="P24" t="n">
-        <v>12.4</v>
+        <v>12.46</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.13</v>
+        <v>0.06</v>
       </c>
       <c r="R24" t="n">
-        <v>1.06</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="25">
@@ -1941,22 +1941,22 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.38</v>
+        <v>27.08</v>
       </c>
       <c r="E25" t="n">
-        <v>1.34</v>
+        <v>0.7</v>
       </c>
       <c r="F25" t="n">
-        <v>5.35</v>
+        <v>2.65</v>
       </c>
       <c r="G25" t="n">
-        <v>27.08</v>
+        <v>26.66</v>
       </c>
       <c r="H25" t="n">
-        <v>0.7</v>
+        <v>-0.42</v>
       </c>
       <c r="I25" t="n">
-        <v>2.65</v>
+        <v>-1.55</v>
       </c>
       <c r="J25" t="n">
         <v>26.66</v>
@@ -1968,22 +1968,22 @@
         <v>-1.55</v>
       </c>
       <c r="M25" t="n">
-        <v>26.66</v>
+        <v>27.06</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.42</v>
+        <v>0.4</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.55</v>
+        <v>1.5</v>
       </c>
       <c r="P25" t="n">
-        <v>26.66</v>
+        <v>27.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.42</v>
+        <v>0.4</v>
       </c>
       <c r="R25" t="n">
-        <v>-1.55</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="26">
@@ -2003,22 +2003,22 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>28.34</v>
+        <v>24.98</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1</v>
+        <v>-3.36</v>
       </c>
       <c r="F26" t="n">
-        <v>0.35</v>
+        <v>-11.86</v>
       </c>
       <c r="G26" t="n">
-        <v>24.98</v>
+        <v>25.12</v>
       </c>
       <c r="H26" t="n">
-        <v>-3.36</v>
+        <v>0.14</v>
       </c>
       <c r="I26" t="n">
-        <v>-11.86</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="J26" t="n">
         <v>25.12</v>
@@ -2030,22 +2030,22 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>25.12</v>
+        <v>24.92</v>
       </c>
       <c r="N26" t="n">
-        <v>0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="O26" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.8</v>
       </c>
       <c r="P26" t="n">
-        <v>25.12</v>
+        <v>24.92</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="R26" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="27">
@@ -2065,22 +2065,22 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>423.4</v>
+        <v>417.8</v>
       </c>
       <c r="E27" t="n">
-        <v>-1.8</v>
+        <v>-5.6</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.42</v>
+        <v>-1.32</v>
       </c>
       <c r="G27" t="n">
         <v>417.8</v>
       </c>
       <c r="H27" t="n">
-        <v>-5.6</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>-1.32</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>417.8</v>
@@ -2092,22 +2092,22 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>417.8</v>
+        <v>410.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>-7.4</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>-1.77</v>
       </c>
       <c r="P27" t="n">
-        <v>417.8</v>
+        <v>410.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>-7.4</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="28">
@@ -2127,22 +2127,22 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>110.5</v>
+        <v>106.4</v>
       </c>
       <c r="E28" t="n">
-        <v>3.3</v>
+        <v>-4.1</v>
       </c>
       <c r="F28" t="n">
-        <v>3.08</v>
+        <v>-3.71</v>
       </c>
       <c r="G28" t="n">
-        <v>106.4</v>
+        <v>108.8</v>
       </c>
       <c r="H28" t="n">
-        <v>-4.1</v>
+        <v>2.4</v>
       </c>
       <c r="I28" t="n">
-        <v>-3.71</v>
+        <v>2.26</v>
       </c>
       <c r="J28" t="n">
         <v>108.8</v>
@@ -2154,22 +2154,22 @@
         <v>2.26</v>
       </c>
       <c r="M28" t="n">
-        <v>108.8</v>
+        <v>104.9</v>
       </c>
       <c r="N28" t="n">
-        <v>2.4</v>
+        <v>-3.9</v>
       </c>
       <c r="O28" t="n">
-        <v>2.26</v>
+        <v>-3.58</v>
       </c>
       <c r="P28" t="n">
-        <v>108.8</v>
+        <v>104.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.4</v>
+        <v>-3.9</v>
       </c>
       <c r="R28" t="n">
-        <v>2.26</v>
+        <v>-3.58</v>
       </c>
     </row>
     <row r="29">
@@ -2189,22 +2189,22 @@
         </is>
       </c>
       <c r="D29" t="n">
+        <v>104.9</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="F29" t="n">
+        <v>-1.13</v>
+      </c>
+      <c r="G29" t="n">
         <v>106.1</v>
       </c>
-      <c r="E29" t="n">
+      <c r="H29" t="n">
         <v>1.2</v>
       </c>
-      <c r="F29" t="n">
+      <c r="I29" t="n">
         <v>1.14</v>
-      </c>
-      <c r="G29" t="n">
-        <v>104.9</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="I29" t="n">
-        <v>-1.13</v>
       </c>
       <c r="J29" t="n">
         <v>106.1</v>
@@ -2216,22 +2216,22 @@
         <v>1.14</v>
       </c>
       <c r="M29" t="n">
-        <v>106.1</v>
+        <v>104.4</v>
       </c>
       <c r="N29" t="n">
-        <v>1.2</v>
+        <v>-1.7</v>
       </c>
       <c r="O29" t="n">
-        <v>1.14</v>
+        <v>-1.6</v>
       </c>
       <c r="P29" t="n">
-        <v>106.1</v>
+        <v>104.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.2</v>
+        <v>-1.7</v>
       </c>
       <c r="R29" t="n">
-        <v>1.14</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="30">
@@ -2251,22 +2251,22 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>77.09999999999999</v>
+        <v>75.45</v>
       </c>
       <c r="E30" t="n">
-        <v>4.8</v>
+        <v>-1.65</v>
       </c>
       <c r="F30" t="n">
-        <v>6.64</v>
+        <v>-2.14</v>
       </c>
       <c r="G30" t="n">
-        <v>75.45</v>
+        <v>75.7</v>
       </c>
       <c r="H30" t="n">
-        <v>-1.65</v>
+        <v>0.25</v>
       </c>
       <c r="I30" t="n">
-        <v>-2.14</v>
+        <v>0.33</v>
       </c>
       <c r="J30" t="n">
         <v>75.7</v>
@@ -2278,22 +2278,22 @@
         <v>0.33</v>
       </c>
       <c r="M30" t="n">
-        <v>75.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="O30" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="P30" t="n">
-        <v>75.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.25</v>
+        <v>0.4</v>
       </c>
       <c r="R30" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="31">
@@ -2313,22 +2313,22 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>82.05</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4</v>
+        <v>-3.7</v>
       </c>
       <c r="F31" t="n">
-        <v>0.49</v>
+        <v>-4.51</v>
       </c>
       <c r="G31" t="n">
-        <v>78.34999999999999</v>
+        <v>79.45</v>
       </c>
       <c r="H31" t="n">
-        <v>-3.7</v>
+        <v>1.1</v>
       </c>
       <c r="I31" t="n">
-        <v>-4.51</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>79.45</v>
@@ -2340,22 +2340,22 @@
         <v>1.4</v>
       </c>
       <c r="M31" t="n">
-        <v>79.45</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>1.1</v>
+        <v>-0.85</v>
       </c>
       <c r="O31" t="n">
-        <v>1.4</v>
+        <v>-1.07</v>
       </c>
       <c r="P31" t="n">
-        <v>79.45</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.1</v>
+        <v>-0.85</v>
       </c>
       <c r="R31" t="n">
-        <v>1.4</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="32">
@@ -2375,22 +2375,22 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>54.3</v>
+        <v>52.15</v>
       </c>
       <c r="E32" t="n">
-        <v>-1.25</v>
+        <v>-2.15</v>
       </c>
       <c r="F32" t="n">
-        <v>-2.25</v>
+        <v>-3.96</v>
       </c>
       <c r="G32" t="n">
-        <v>52.15</v>
+        <v>52.4</v>
       </c>
       <c r="H32" t="n">
-        <v>-2.15</v>
+        <v>0.25</v>
       </c>
       <c r="I32" t="n">
-        <v>-3.96</v>
+        <v>0.48</v>
       </c>
       <c r="J32" t="n">
         <v>52.4</v>
@@ -2402,22 +2402,22 @@
         <v>0.48</v>
       </c>
       <c r="M32" t="n">
-        <v>52.4</v>
+        <v>51.2</v>
       </c>
       <c r="N32" t="n">
-        <v>0.25</v>
+        <v>-1.2</v>
       </c>
       <c r="O32" t="n">
-        <v>0.48</v>
+        <v>-2.29</v>
       </c>
       <c r="P32" t="n">
-        <v>52.4</v>
+        <v>51.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.25</v>
+        <v>-1.2</v>
       </c>
       <c r="R32" t="n">
-        <v>0.48</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="33">
@@ -2437,22 +2437,22 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>72.84999999999999</v>
+        <v>72.95</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.55</v>
+        <v>0.14</v>
       </c>
       <c r="G33" t="n">
-        <v>72.95</v>
+        <v>73.75</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="I33" t="n">
-        <v>0.14</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
         <v>73.75</v>
@@ -2464,22 +2464,22 @@
         <v>1.1</v>
       </c>
       <c r="M33" t="n">
-        <v>73.75</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>0.8</v>
+        <v>-0.1</v>
       </c>
       <c r="O33" t="n">
-        <v>1.1</v>
+        <v>-0.14</v>
       </c>
       <c r="P33" t="n">
-        <v>73.75</v>
+        <v>73.65000000000001</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.8</v>
+        <v>-0.1</v>
       </c>
       <c r="R33" t="n">
-        <v>1.1</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="34">
@@ -2499,22 +2499,22 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>29.52</v>
+        <v>28.58</v>
       </c>
       <c r="E34" t="n">
-        <v>0.36</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>1.23</v>
+        <v>-3.18</v>
       </c>
       <c r="G34" t="n">
-        <v>28.58</v>
+        <v>29.3</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.9399999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="I34" t="n">
-        <v>-3.18</v>
+        <v>2.52</v>
       </c>
       <c r="J34" t="n">
         <v>29.3</v>
@@ -2526,22 +2526,22 @@
         <v>2.52</v>
       </c>
       <c r="M34" t="n">
-        <v>29.3</v>
+        <v>28.7</v>
       </c>
       <c r="N34" t="n">
-        <v>0.72</v>
+        <v>-0.6</v>
       </c>
       <c r="O34" t="n">
-        <v>2.52</v>
+        <v>-2.05</v>
       </c>
       <c r="P34" t="n">
-        <v>29.3</v>
+        <v>28.7</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.72</v>
+        <v>-0.6</v>
       </c>
       <c r="R34" t="n">
-        <v>2.52</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="35">
@@ -2561,22 +2561,22 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>4.09</v>
+        <v>3.98</v>
       </c>
       <c r="E35" t="n">
-        <v>0.04</v>
+        <v>-0.11</v>
       </c>
       <c r="F35" t="n">
-        <v>0.99</v>
+        <v>-2.69</v>
       </c>
       <c r="G35" t="n">
-        <v>3.98</v>
+        <v>4.03</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.11</v>
+        <v>0.05</v>
       </c>
       <c r="I35" t="n">
-        <v>-2.69</v>
+        <v>1.26</v>
       </c>
       <c r="J35" t="n">
         <v>4.03</v>
@@ -2588,13 +2588,13 @@
         <v>1.26</v>
       </c>
       <c r="M35" t="n">
-        <v>4.03</v>
+        <v>3.98</v>
       </c>
       <c r="N35" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="O35" t="n">
-        <v>1.26</v>
+        <v>-1.24</v>
       </c>
       <c r="P35" t="n">
         <v>3.98</v>
@@ -2623,22 +2623,22 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>8.800000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="E36" t="n">
-        <v>0.06</v>
+        <v>-0.23</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6899999999999999</v>
+        <v>-2.61</v>
       </c>
       <c r="G36" t="n">
-        <v>8.57</v>
+        <v>8.67</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.23</v>
+        <v>0.1</v>
       </c>
       <c r="I36" t="n">
-        <v>-2.61</v>
+        <v>1.17</v>
       </c>
       <c r="J36" t="n">
         <v>8.67</v>
@@ -2650,13 +2650,13 @@
         <v>1.17</v>
       </c>
       <c r="M36" t="n">
-        <v>8.67</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>0.1</v>
+        <v>-0.13</v>
       </c>
       <c r="O36" t="n">
-        <v>1.17</v>
+        <v>-1.5</v>
       </c>
       <c r="P36" t="n">
         <v>8.539999999999999</v>
@@ -2685,22 +2685,22 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>373.6</v>
+        <v>371.4</v>
       </c>
       <c r="E37" t="n">
-        <v>-6</v>
+        <v>-2.2</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.58</v>
+        <v>-0.59</v>
       </c>
       <c r="G37" t="n">
-        <v>371.4</v>
+        <v>374.6</v>
       </c>
       <c r="H37" t="n">
-        <v>-2.2</v>
+        <v>3.2</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.59</v>
+        <v>0.86</v>
       </c>
       <c r="J37" t="n">
         <v>374.6</v>
@@ -2712,22 +2712,22 @@
         <v>0.86</v>
       </c>
       <c r="M37" t="n">
-        <v>374.6</v>
+        <v>372.4</v>
       </c>
       <c r="N37" t="n">
-        <v>3.2</v>
+        <v>-2.2</v>
       </c>
       <c r="O37" t="n">
-        <v>0.86</v>
+        <v>-0.59</v>
       </c>
       <c r="P37" t="n">
-        <v>374.6</v>
+        <v>372.4</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.2</v>
+        <v>-2.2</v>
       </c>
       <c r="R37" t="n">
-        <v>0.86</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="38">
@@ -2747,22 +2747,22 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.29</v>
+        <v>11.3</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.13</v>
+        <v>0.01</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.14</v>
+        <v>0.09</v>
       </c>
       <c r="G38" t="n">
-        <v>11.3</v>
+        <v>11.49</v>
       </c>
       <c r="H38" t="n">
-        <v>0.01</v>
+        <v>0.19</v>
       </c>
       <c r="I38" t="n">
-        <v>0.09</v>
+        <v>1.68</v>
       </c>
       <c r="J38" t="n">
         <v>11.49</v>
@@ -2774,22 +2774,22 @@
         <v>1.68</v>
       </c>
       <c r="M38" t="n">
-        <v>11.49</v>
+        <v>11.32</v>
       </c>
       <c r="N38" t="n">
-        <v>0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="O38" t="n">
-        <v>1.68</v>
+        <v>-1.48</v>
       </c>
       <c r="P38" t="n">
-        <v>11.49</v>
+        <v>11.32</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.19</v>
+        <v>-0.17</v>
       </c>
       <c r="R38" t="n">
-        <v>1.68</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="39">
@@ -2809,22 +2809,22 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>467</v>
+        <v>448.6</v>
       </c>
       <c r="E39" t="n">
-        <v>-18.2</v>
+        <v>-18.4</v>
       </c>
       <c r="F39" t="n">
-        <v>-3.75</v>
+        <v>-3.94</v>
       </c>
       <c r="G39" t="n">
-        <v>448.6</v>
+        <v>440.8</v>
       </c>
       <c r="H39" t="n">
-        <v>-18.4</v>
+        <v>-7.8</v>
       </c>
       <c r="I39" t="n">
-        <v>-3.94</v>
+        <v>-1.74</v>
       </c>
       <c r="J39" t="n">
         <v>440.8</v>
@@ -2836,22 +2836,22 @@
         <v>-1.74</v>
       </c>
       <c r="M39" t="n">
-        <v>440.8</v>
+        <v>411.8</v>
       </c>
       <c r="N39" t="n">
-        <v>-7.8</v>
+        <v>-29</v>
       </c>
       <c r="O39" t="n">
-        <v>-1.74</v>
+        <v>-6.58</v>
       </c>
       <c r="P39" t="n">
-        <v>440.8</v>
+        <v>411.8</v>
       </c>
       <c r="Q39" t="n">
-        <v>-7.8</v>
+        <v>-29</v>
       </c>
       <c r="R39" t="n">
-        <v>-1.74</v>
+        <v>-6.58</v>
       </c>
     </row>
     <row r="40">
@@ -2871,22 +2871,22 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>38.62</v>
+        <v>37.2</v>
       </c>
       <c r="E40" t="n">
-        <v>0.78</v>
+        <v>-1.42</v>
       </c>
       <c r="F40" t="n">
-        <v>2.06</v>
+        <v>-3.68</v>
       </c>
       <c r="G40" t="n">
-        <v>37.2</v>
+        <v>37.46</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.42</v>
+        <v>0.26</v>
       </c>
       <c r="I40" t="n">
-        <v>-3.68</v>
+        <v>0.7</v>
       </c>
       <c r="J40" t="n">
         <v>37.46</v>
@@ -2898,22 +2898,22 @@
         <v>0.7</v>
       </c>
       <c r="M40" t="n">
-        <v>37.46</v>
+        <v>37.6</v>
       </c>
       <c r="N40" t="n">
-        <v>0.26</v>
+        <v>0.14</v>
       </c>
       <c r="O40" t="n">
-        <v>0.7</v>
+        <v>0.37</v>
       </c>
       <c r="P40" t="n">
-        <v>37.46</v>
+        <v>37.6</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.26</v>
+        <v>0.14</v>
       </c>
       <c r="R40" t="n">
-        <v>0.7</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="41">
@@ -2933,49 +2933,49 @@
         </is>
       </c>
       <c r="D41" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="F41" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G41" t="n">
         <v>29</v>
       </c>
-      <c r="E41" t="n">
-        <v>-0.2</v>
-      </c>
-      <c r="F41" t="n">
-        <v>-0.68</v>
-      </c>
-      <c r="G41" t="n">
-        <v>28.99</v>
-      </c>
       <c r="H41" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.03</v>
+        <v>0.03</v>
       </c>
       <c r="J41" t="n">
-        <v>29</v>
+        <v>28.92</v>
       </c>
       <c r="K41" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="L41" t="n">
-        <v>0.03</v>
+        <v>-0.28</v>
       </c>
       <c r="M41" t="n">
-        <v>28.92</v>
+        <v>28.8</v>
       </c>
       <c r="N41" t="n">
-        <v>-0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="O41" t="n">
-        <v>-0.28</v>
+        <v>-0.41</v>
       </c>
       <c r="P41" t="n">
-        <v>28.92</v>
+        <v>28.8</v>
       </c>
       <c r="Q41" t="n">
-        <v>-0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="R41" t="n">
-        <v>-0.28</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="42">
@@ -2995,49 +2995,49 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>74.34</v>
+        <v>73.75</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.13</v>
+        <v>-0.59</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.17</v>
+        <v>-0.79</v>
       </c>
       <c r="G42" t="n">
-        <v>73.75</v>
+        <v>74.11</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.59</v>
+        <v>0.36</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.79</v>
+        <v>0.49</v>
       </c>
       <c r="J42" t="n">
-        <v>74.11</v>
+        <v>74.45</v>
       </c>
       <c r="K42" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="L42" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="M42" t="n">
-        <v>74.45</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>0.34</v>
+        <v>-0.02</v>
       </c>
       <c r="O42" t="n">
-        <v>0.46</v>
+        <v>-0.03</v>
       </c>
       <c r="P42" t="n">
-        <v>74.45</v>
+        <v>74.43000000000001</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.34</v>
+        <v>-0.02</v>
       </c>
       <c r="R42" t="n">
-        <v>0.46</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="43">
@@ -3057,49 +3057,49 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>41.06</v>
+        <v>41.69</v>
       </c>
       <c r="E43" t="n">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
       <c r="F43" t="n">
-        <v>0.32</v>
+        <v>1.53</v>
       </c>
       <c r="G43" t="n">
-        <v>41.69</v>
+        <v>41.61</v>
       </c>
       <c r="H43" t="n">
-        <v>0.63</v>
+        <v>-0.08</v>
       </c>
       <c r="I43" t="n">
-        <v>1.53</v>
+        <v>-0.19</v>
       </c>
       <c r="J43" t="n">
-        <v>41.61</v>
+        <v>41.64</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.08</v>
+        <v>0.03</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.19</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>41.64</v>
+        <v>41.42</v>
       </c>
       <c r="N43" t="n">
-        <v>0.03</v>
+        <v>-0.22</v>
       </c>
       <c r="O43" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.53</v>
       </c>
       <c r="P43" t="n">
-        <v>41.64</v>
+        <v>41.42</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.03</v>
+        <v>-0.22</v>
       </c>
       <c r="R43" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="44">
@@ -3119,49 +3119,49 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>6.04</v>
+        <v>5.92</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.04</v>
+        <v>-0.12</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.66</v>
+        <v>-1.99</v>
       </c>
       <c r="G44" t="n">
         <v>5.92</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>-1.99</v>
+        <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>5.92</v>
+        <v>5.91</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>-0.17</v>
       </c>
       <c r="M44" t="n">
-        <v>5.91</v>
+        <v>6</v>
       </c>
       <c r="N44" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="O44" t="n">
-        <v>-0.17</v>
+        <v>1.52</v>
       </c>
       <c r="P44" t="n">
-        <v>5.91</v>
+        <v>6</v>
       </c>
       <c r="Q44" t="n">
-        <v>-0.01</v>
+        <v>0.09</v>
       </c>
       <c r="R44" t="n">
-        <v>-0.17</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="45">
@@ -3181,22 +3181,22 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>-0.09</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>-4.64</v>
       </c>
       <c r="G45" t="n">
         <v>1.85</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.09</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>-4.64</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>1.85</v>
@@ -3208,22 +3208,22 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>-1.08</v>
       </c>
       <c r="P45" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="46">
@@ -3243,49 +3243,49 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>3.64</v>
+        <v>3.57</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.03</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.82</v>
+        <v>-1.92</v>
       </c>
       <c r="G46" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="I46" t="n">
-        <v>-1.92</v>
+        <v>0.28</v>
       </c>
       <c r="J46" t="n">
-        <v>3.58</v>
+        <v>3.62</v>
       </c>
       <c r="K46" t="n">
-        <v>0.01</v>
+        <v>0.04</v>
       </c>
       <c r="L46" t="n">
-        <v>0.28</v>
+        <v>1.12</v>
       </c>
       <c r="M46" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="N46" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="O46" t="n">
-        <v>1.12</v>
+        <v>-0.28</v>
       </c>
       <c r="P46" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="R46" t="n">
-        <v>1.12</v>
+        <v>-0.28</v>
       </c>
     </row>
     <row r="47">
@@ -3305,49 +3305,49 @@
         </is>
       </c>
       <c r="D47" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="F47" t="n">
+        <v>-1.54</v>
+      </c>
+      <c r="G47" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J47" t="n">
         <v>10.41</v>
       </c>
-      <c r="E47" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F47" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="G47" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-0.16</v>
-      </c>
-      <c r="I47" t="n">
-        <v>-1.54</v>
-      </c>
-      <c r="J47" t="n">
-        <v>10.39</v>
-      </c>
       <c r="K47" t="n">
-        <v>0.14</v>
+        <v>0.02</v>
       </c>
       <c r="L47" t="n">
-        <v>1.37</v>
+        <v>0.19</v>
       </c>
       <c r="M47" t="n">
-        <v>10.41</v>
+        <v>10.4</v>
       </c>
       <c r="N47" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="O47" t="n">
-        <v>0.19</v>
+        <v>-0.1</v>
       </c>
       <c r="P47" t="n">
-        <v>10.41</v>
+        <v>10.4</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="R47" t="n">
-        <v>0.19</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="48">
@@ -3367,31 +3367,31 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0.29</v>
+        <v>0.285</v>
       </c>
       <c r="E48" t="n">
-        <v>0.005</v>
+        <v>-0.005</v>
       </c>
       <c r="F48" t="n">
-        <v>1.75</v>
+        <v>-1.72</v>
       </c>
       <c r="G48" t="n">
-        <v>0.285</v>
+        <v>0.28</v>
       </c>
       <c r="H48" t="n">
         <v>-0.005</v>
       </c>
       <c r="I48" t="n">
-        <v>-1.72</v>
+        <v>-1.75</v>
       </c>
       <c r="J48" t="n">
         <v>0.28</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>-1.75</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0.28</v>
@@ -3429,16 +3429,16 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>4.14</v>
+        <v>4.16</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.48</v>
+        <v>0.48</v>
       </c>
       <c r="G49" t="n">
-        <v>4.16</v>
+        <v>4.18</v>
       </c>
       <c r="H49" t="n">
         <v>0.02</v>
@@ -3450,28 +3450,28 @@
         <v>4.18</v>
       </c>
       <c r="K49" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0.48</v>
+        <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>4.18</v>
+        <v>4.23</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P49" t="n">
-        <v>4.18</v>
+        <v>4.23</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="50">
@@ -3491,49 +3491,49 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>-0.91</v>
       </c>
       <c r="G50" t="n">
         <v>1.09</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.91</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>0.92</v>
       </c>
       <c r="M50" t="n">
         <v>1.1</v>
       </c>
       <c r="N50" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
       <c r="P50" t="n">
         <v>1.1</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>0.92</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3553,49 +3553,49 @@
         </is>
       </c>
       <c r="D51" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-0.12</v>
+      </c>
+      <c r="F51" t="n">
+        <v>-2.33</v>
+      </c>
+      <c r="G51" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="I51" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="J51" t="n">
         <v>5.15</v>
       </c>
-      <c r="E51" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="F51" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="G51" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="I51" t="n">
-        <v>-2.33</v>
-      </c>
-      <c r="J51" t="n">
-        <v>5.21</v>
-      </c>
       <c r="K51" t="n">
-        <v>0.18</v>
+        <v>-0.06</v>
       </c>
       <c r="L51" t="n">
-        <v>3.58</v>
+        <v>-1.15</v>
       </c>
       <c r="M51" t="n">
-        <v>5.15</v>
+        <v>4.99</v>
       </c>
       <c r="N51" t="n">
-        <v>-0.06</v>
+        <v>-0.16</v>
       </c>
       <c r="O51" t="n">
-        <v>-1.15</v>
+        <v>-3.11</v>
       </c>
       <c r="P51" t="n">
-        <v>5.15</v>
+        <v>4.99</v>
       </c>
       <c r="Q51" t="n">
-        <v>-0.06</v>
+        <v>-0.16</v>
       </c>
       <c r="R51" t="n">
-        <v>-1.15</v>
+        <v>-3.11</v>
       </c>
     </row>
     <row r="52">
@@ -3615,49 +3615,49 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.36</v>
+        <v>10.12</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.06</v>
+        <v>-0.24</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.58</v>
+        <v>-2.32</v>
       </c>
       <c r="G52" t="n">
-        <v>10.12</v>
+        <v>10.1</v>
       </c>
       <c r="H52" t="n">
-        <v>-0.24</v>
+        <v>-0.02</v>
       </c>
       <c r="I52" t="n">
-        <v>-2.32</v>
+        <v>-0.2</v>
       </c>
       <c r="J52" t="n">
-        <v>10.1</v>
+        <v>10.07</v>
       </c>
       <c r="K52" t="n">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="L52" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
       <c r="M52" t="n">
-        <v>10.07</v>
+        <v>10.11</v>
       </c>
       <c r="N52" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="O52" t="n">
-        <v>-0.3</v>
+        <v>0.4</v>
       </c>
       <c r="P52" t="n">
-        <v>10.07</v>
+        <v>10.11</v>
       </c>
       <c r="Q52" t="n">
-        <v>-0.03</v>
+        <v>0.04</v>
       </c>
       <c r="R52" t="n">
-        <v>-0.3</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="53">
@@ -3680,46 +3680,46 @@
         <v>7.05</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.4</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>7.05</v>
+        <v>7.04</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>-0.14</v>
       </c>
       <c r="J53" t="n">
-        <v>7.04</v>
+        <v>7.01</v>
       </c>
       <c r="K53" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="L53" t="n">
+        <v>-0.43</v>
+      </c>
+      <c r="M53" t="n">
+        <v>7</v>
+      </c>
+      <c r="N53" t="n">
         <v>-0.01</v>
       </c>
-      <c r="L53" t="n">
+      <c r="O53" t="n">
         <v>-0.14</v>
       </c>
-      <c r="M53" t="n">
-        <v>7.01</v>
-      </c>
-      <c r="N53" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="O53" t="n">
-        <v>-0.43</v>
-      </c>
       <c r="P53" t="n">
-        <v>7.01</v>
+        <v>7</v>
       </c>
       <c r="Q53" t="n">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="R53" t="n">
-        <v>-0.43</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="54">
@@ -3739,22 +3739,22 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>0.43</v>
+        <v>0.425</v>
       </c>
       <c r="E54" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>-1.16</v>
       </c>
       <c r="G54" t="n">
         <v>0.425</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.005</v>
+        <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.16</v>
+        <v>0</v>
       </c>
       <c r="J54" t="n">
         <v>0.425</v>
@@ -3804,10 +3804,10 @@
         <v>0.61</v>
       </c>
       <c r="E55" t="n">
-        <v>0.005</v>
+        <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="G55" t="n">
         <v>0.61</v>
@@ -3828,22 +3828,22 @@
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.61</v>
+        <v>0.605</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
       <c r="P55" t="n">
-        <v>0.61</v>
+        <v>0.605</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>-0.005</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>-0.82</v>
       </c>
     </row>
     <row r="56">
@@ -3863,49 +3863,49 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>0.345</v>
+        <v>0.34</v>
       </c>
       <c r="E56" t="n">
-        <v>-0.01</v>
+ 